--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The Princess of Wales dazzles in deeply personal Cartier earrings on Christmas Day - Tatler</t>
+          <t>Inside the Bullring's giant beauty hall featuring Dior, Gucci and Armani - Birmingham Live</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 11:51:59 GMT</t>
+          <t>Fri, 26 Dec 2025 05:46:00 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNTE85eUQ4NTg3OXd3UHFiajNZanRZRXMyMXdKck1oaWVYRTF4d011NzBoVHROZ1R3RUY3VDJLVzk3NzhHajN5QWxwcU1yV1VtZW8wWFkxZHNKRi1lRVdQemlGc2EzOFc5ZDVLZjlzczVvUk9QbUd0b1lnNmMzRXZJeU5lTHFNSEhlSEhUOTBuRmk3UGJ4UzZTbXpPcXlfM2JzeG1FZlNaU0lkQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOTi05TWJfVEJRLVROTUN0anJrSlM1bkU4d0RfS2tZbVRjOFZHXzJEX3dnQ3N1OVpyOFZoZ1UxQjZmdldkZ2U3T0dVNnY4RTNLOGVZMGJVenRielRmR1UtWFZVaXZXeUhCUVdwOUVCZWlCYjFlT2RoYS1VckQxUmRwSk9Ed25kQjM0NFh2a0llOXQzN0VoTlVsZzhLcnJjQXVjQzJoaDN2dmNEM1XSAbABQVVfeXFMTnkwSEstdmU3c2ZGMWZEaHd6WmpzUS05YTZ3dkt5c0hnLWtQaExfVnFXY1dVRVZlQjF4b1JveklWenNsU1JhUDljejk2WjFlelJHWVV5WXFHOEdkYS0xNEYydi1FXy03UEVibXN5YXppb3NjbV8tcWxJczRWaHM2Vl9UNWE2OEpLc21fRk5FVmEwUjZEVEhoOTlqVTNyUWI0d0lqMXVYbTEwUlRVV0ZGdS0?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46016.49443287037</v>
+        <v>46017.24027777778</v>
       </c>
     </row>
     <row r="3">
@@ -515,24 +515,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Swedbank AB Acquires 25,000 Shares of Ralph Lauren Corporation $RL - MarketBeat</t>
+          <t>Kate Middleton Wears $4,000 Cartier Earrings on Christmas Morning in an Under-the-Radar Nod to Princess Diana - instyle.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 11:23:19 GMT</t>
+          <t>Thu, 25 Dec 2025 17:57:56 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQWDU3a2hNNTdmUG13NjFFMWVNR1FsZ25OdFZJdjAydFhXVDVoU2dkTk44b3UtR3dhZDh0c2FlZ2lXQm9PMi1yYjFuaFlVVncwNE50SmNFZFBHQTBfYWtkZmtSbDBaaEZwbWpmdGVIRVR5NFZhMHAxV3FYZW1mVEZXeFBZblRaUXBDVE05dE9ZMTdnOWJTa1hTVHI5bWFVeFoxU1VlWjc5SVZNNUVTTEdoZTdvazJZMmgwb0xpMldIaWhNa0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNb0hzVWY0cERJOUl2WFdBb3pwSDRFRXU2U0hfYW45VkNWTHVvUXJuQXFVWDJqRTFZLTN0Q09Rd094M090cnppNHB4LW9RUUtmSUpOZXpkM1lSWElJSk80UmhHTEhjYWNiNEdDSmozaWZvVVk1WjdTWFNXbFgzNElJRkppaE10UllqcXh5eXF3aWg?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46016.47452546296</v>
+        <v>46016.74856481481</v>
       </c>
     </row>
     <row r="4">
@@ -548,816 +548,2895 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cartier Resources (CVE:ECR) Trading Up 16.7% - Still a Buy? - MarketBeat</t>
+          <t>Percy Jackson: Dior Goodjohn on Clarisse's Quest, Annabeth Alliance - Bleeding Cool News</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 11:19:15 GMT</t>
+          <t>Thu, 25 Dec 2025 21:37:03 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNckh6QldiR2E4eUtaZDVxTVFGaTZIZ1M0Z3Bia1haZTJsVnlHeXNnR3psS3RacS1ITldxV0VqSi1ZaTRUZVRpc2VINFZESU1zVzZLU0pLMmt0cmowUFRELUw5TVBEV0Q0d2NfT1AxX24zNGloNmFHTXZQRE9FUHlVTU9QMnlpbElTajkxUkdJeml1V1BvM1Nlc29vakRIbW9ibnVLc0FycFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQamotTWI2enJKWWNZQUtidmtBUUl0NWRoTGdyNHNFOW4yZk5YOHV3SVdwYWN5cFBOTVRfYThxZG5mX25YdDFyS3Nzd0RrWC1HbU9uRHVxRUo1WTEzV21GdjByTmFxa0d4SUFjRFJNd21QVW1MYzJ1R3ZHWTZVaHFXUk5VUGk3dlZ0T2doaXdzN054V2RHLTZIdg?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46016.47170138889</v>
+        <v>46016.90072916666</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Value Retail</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The outlet shopping centre near Cambridgeshire perfect for Boxing Day bargains - Cambridge News</t>
+          <t>Maison Louis Vuitton Sanlitun: A fusion of tradition and modernity in architectural elegance - China Daily</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 11:00:00 GMT</t>
+          <t>Fri, 26 Dec 2025 00:12:00 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQTmJCdzlRVlY4VDN6OFpfSWExS0tSSXViSG1yUmZ5bFE2YUMyYWdWLUdQZXdQZl9VTU1IXzFNbE85dnZfMlBhQndFSWNWbzZzVWlYeWh2eE1DcTRfWnYxeHdWQU5NWWFLelUyT0RxN3dzN2FSRVhNV0ItcTVPbFF2MzJWbURnTm5BSi1fRzlHU2ZFSnI3b3puNDlFQXM5R2l3RjBPX0k1MVJ1QdIBqgFBVV95cUxQTmJCdzlRVlY4VDN6OFpfSWExS0tSSXViSG1yUmZ5bFE2YUMyYWdWLUdQZXdQZl9VTU1IXzFNbE85dnZfMlBhQndFSWNWbzZzVWlYeWh2eE1DcTRfWnYxeHdWQU5NWWFLelUyT0RxN3dzN2FSRVhNV0ItcTVPbFF2MzJWbURnTm5BSi1fRzlHU2ZFSnI3b3puNDlFQXM5R2l3RjBPX0k1MVJ1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1qZUpCMXduNGZsT0R1SzV6UUgyblZOQTA1YVlUUkV6QVQxQkVOdy1qZnQ0OUxuWmdwZjQwRGUxS004RkowY3F6SHJxSWJEc1dsT2hjbjJVdE9PSDVOUHdKcnFhYmh6X0lMdVNEWHBKSTNxd0dsSnR0UGFSdlZSUQ?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46016.45833333334</v>
+        <v>46017.00833333333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Value Retail</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Retail sector poised for rapid growth in 2026 - News Arena India</t>
+          <t>Giorgio Armani: Milano, per amore - www.upscalelivingmag.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 10:39:23 GMT</t>
+          <t>Fri, 26 Dec 2025 02:39:57 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNa2UyRUU0NU13b0pPNXpFQWU3cUtGY2hrcWhIclVYN2FNMzdOOEsza3hrSDE5aGdValRsaGV6c1NTS2s0M3hncFhucm5IMUN4MGs2YzQwVzEwc2FsMGo1Rk9MOEdDZ0YteWhqUVp4T2RQTkh4R25KQV96dWJ4TjhXVktYd3RHaTZnSkhmQkJOWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOVTVjdENOLXl5cHhseGdLMTdPcDZGUGlMY3ZvYXB1eWgyZnZJWlpGU0FjLW1oWjhXTjB1c25CMGd6em1OVm9jdkxQemdFZ0dFRjFjWU5CQ3ltNXZTbi1fa2xTTTAtSTZDQ3RKOEtIMHFOU255enFDbGNPZHVmSWVDQ1daZHVRdHl2X0xhSWJzR3g?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46016.44401620371</v>
+        <v>46017.11107638889</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>You Can Now Tip Your Amazon Delivery Driver for Christmas – at No Extra Cost - AOL.com</t>
+          <t>Cartier's Marlin Yuson on crafting the latest leather bags - Condé Nast Traveller Middle East</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 11:32:03 GMT</t>
+          <t>Thu, 25 Dec 2025 21:00:00 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE8zRmpzQkY1LUpwSWlrdWpPUm9PZ2dRREdRdklMdkpzTDA4WGxfSUpWaU5SaUswaE1xODNnaU53V1BnTzlrcnppUTY0UTdJOWVqQndVTURvSVJaZlpIU3FkNDZBMzdFNGF0ZzNteDNjaFR0V1pWSjV2SklDSXYybUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQaVJoMmc1ZVNMR3k3RFhEUEd2LVFicy1zaE00QXRqS2VvZm45UmtpSkgwOFNVYnloeVRTOXYwa1RNMW5KQUt2SDI2RTlDdG9JVGVLSHVOVlVFTXpnVUdETTZfbWtYUG1KOG1mWlFZaWdIN0NvUDhOcTNfNHo0ZmZJTlB5bkUwNzRDTHF1X0Q1ZTE4cVl4aXRnaA?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46016.48059027778</v>
+        <v>46016.875</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Why Swiggy, Zomato, Amazon delivery partners are on strike on Dec 25, 31 - Business Standard</t>
+          <t>Jonathan Anderson Gets Downright Whimsical for Dior Menswear Fall 2026 - Esquire Singapore</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 09:32:13 GMT</t>
+          <t>Fri, 26 Dec 2025 04:03:56 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQNDhFWFBkWXhrWktpcFNfSGdyMUlFaThsNXl3Z2NsZUs4bnc5X2JNVjhzMU1vQkN4VVB2a1Y4am5NbjdVVk1UZDl5dDAzMXRGajlHLVhiTlo5eUpibUg4U0VQOHdtV0Fmam9ENzJod09fSmdBVWRnUXNVVVhpVHlVZEtST1pwTXRSOW42SHp6eUp1Q25Qc3JsbjkzZGNTOS1oOGRFWlE4NGhrZkljQjB0MkdiOU04cVZNV1VqQi1IM1VZc0cyZnI2LVUtWS1JNUptOTRUZdIB2gFBVV95cUxNTVZlQk9CMGVtQThXZDZ5NWxLSkRtNDk5RE92dk5OblIzWGFqWndfOGYxbmE0VWNVbUJPb2FnVmVvSnU1SHJ4LVplQjVjNVVsU3F1UTdUQWllTUk2LUNLdTRYdWFWMkZXS09yc0Y1bnNWR3dqUUYzbmlqTWNILXRPVnVYR1F4cVBlMnJUdjhPNFBuOGJ2VHdrUUVHYjdoeFBqSFphSnRGckFmR3BJbmJBbE5iMTIxZzFuRl8zaHBCNjRlaWt2V1RpeVgxNk9PVGtJem84cmJVemViZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE11MEJDQjRFUTJ1aFhQckVCb21ScEV6eUhsem53REtCc05JNkluYjVoaWU1M3BtMEduNGxOUmZtamZVY1VhZHhaQ3FjTWs1SUNVQUNHLXlvNTRVNmhqOFUwRmtZdXIxZU1JeG9lV2hOV0xoQQ?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46016.39737268518</v>
+        <v>46017.16939814815</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium English language</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>("brussels" OR "Maastricht" OR "Antwerp") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Retail crime")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Individual seriously injured in Christmas Eve stabbing outside Brussels Stock Exchange - VRT</t>
+          <t>Burberry Group (LON:BRBY) Stock Price Passes Above Two Hundred Day Moving Average - What's Next? - MarketBeat</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 08:39:56 GMT</t>
+          <t>Fri, 26 Dec 2025 05:40:52 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPelU1QUNTRmhiX196cGxvaUlMcUVBelg0aVJYdHdoTmZkcXkwQUxLc1AtcGVmZEcxWFFQRlVRa3F4RVZPblQwaUJDOWFfOUJGUV9zdHJiVF9obEE4d3dyR2NDUUY3TDJiQ1VZM0R2bFR2T1k5RUhVWmZHQ0VpWmlkcFZULUgzR2NvbXl5aTBmTGZGbGQtb3I0X2s0Uy1IZ29jaC1nb2NoNng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOVnV6Wm9TVU5vSTJ0Smp5MXZXU3MzX0dTR2ZjcThMOEhoRHJFYTIyTUQ5WWZJSXlWSWJDZEZwSkhZZmM1czNCWVdCRUZablVnMzhQNEZ5bktlSmNDc0liOWg1b3kyYUc0WHlJbGVNQVNGUnIwV0JCOVUwWmkyNWg5aWNQQlJLcFFhSjBoTDFpWVgxRHFZZlRZa2t6ZjlKUXhMRnd6MkxQVC1MZ0dJQ3pRSzlsMkNrU01lWXpmTlRHT05UNTJsbWtDQnhpSGktenM3VUlDSTB4Vl9GNHc?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46016.36106481482</v>
+        <v>46017.23671296296</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Muller hails Bayern Munich whiz Karl: Just like Podolski - TribalFootball</t>
+          <t>Paris Haute Couture Week Spring/Summer 2026 Official Schedule and Participating Brands - ouispeakfashion.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 11:47:30 GMT</t>
+          <t>Fri, 26 Dec 2025 04:59:00 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNOXBuc25sdHNwVWRtcjFYUWJ5NjV5eDN6MVo1M0V1d3VxeUFNN1RGSmpWaGpZeHZrang5cndocy1PMzU0YlZxaUM3VWpSdFdqLThYS1FucmRfcTF6RWhGLUV3R29jZVVIM05BM2RUbVBsZUlMTDNTLVFPb196WXhGUmNJZkx5aTZBUXhGT1d0bDFtVzV0ZERkU3hvcG1QZkRPeGd5cjkzcUsxeVlfYVNnSXo3SkFBcUFUeDA1QTdxa3NkbmFkUEpfNVRCQWp1bjBPRmNVNzNBUDExQUgwYk84TTEyMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE42T1ZJTFVFVjF3Ymd5NDZpRVlaeGFtVm4yMGhFLTFRbkVaR1o2X0R2M1JMSjN1eTBTaWgyNEFIN1ZMWDJ4d3hTd0JRUFZrVGtORUVNemJPWGhZcVpjemhTdlgtVGVOOGdTbWt1SVE3NFI4RmRBUjYzVXlwRVE?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46016.49131944445</v>
+        <v>46017.20763888889</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indo Farm Equipment Limited Inches Above Key Support — Safe to Hold - Options Trading Strategies &amp; Best Stocks For Explosive Growth - Bollywood Helpline</t>
+          <t>Indian Retail Sector Eyes Margin-Led Growth In 2026, Driven By Tier II &amp; III Cities Demand - Free Press Journal</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 12:13:44 GMT</t>
+          <t>Fri, 26 Dec 2025 03:21:28 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQOE9DOVI3U2JLU0x3ZDlaX3RnYlk4LVJiV000UlZ0bTRoR20zdXZOS1ptMVNZTUp5OHhTVEt6VjktZkVqWnh5UzJuMzNJQzA0WWhzaTZpcE43blM0bDFBby1PeEpCMEc1ZVFRZzRsYW9icXdBSnlxRE5KekJtYlYzZGI2NnFmWHNRc2FkcUZWampEdTJtREQxU1p3UHRrZzBqUHlreWVLdXRuZnpjWUxj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNbGZVT1BGMUh1blZvZFktdlBfLURieDNaRmhFV0Vocm55WTk4UzYzdlktTkxZTEFLcEpYMDd4aGNMb2k4SFlwblltVm0zX2RWejN4V3lfeWQ2THJBU2N2ajBzRUxMb0NQSG93VUFoVmhBU25DN05YdnhCLXR3THBrdVlXSDZpYUVMZWZGOWh5VVhYVXN5WHUzN0JBMHljMEQwRHZLeDE2WFNlbmNnVUZoWFhVaEl1UU1OWXVLTzNqaHlUdGdDdFdKbjUwazHSAcwBQVVfeXFMTWxmVU9QRjFIdW5Wb2RZLXZQXy1EYngzWkZoRVdFaHJueVk5OFM2M3ZZLU5MWUxBS3BKWDA3eGhjTG9pOEhZcG5ZbVZtM19kVnozeFd5X3lkNkxyQVNjdmowc0VMTG9DUEhvd1VBaFZoQVNuQzdOWHZ4Qi10d0xwa3VZV0g2aWFFTGVmRjloeVVYWFVzeVh1MzdCQTB5YzBEMER2S3gxNlhTZW5jZ1VGaFhYVWhJdVFNTll1S08zamh5VHRnQ3RXSm41MGsx?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46016.50953703704</v>
+        <v>46017.13990740741</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Extra police patrols across North Wales as part of Christmas crime crackdown - Wrexham.com</t>
+          <t>Royal Mail December 24: Christmas Delivery Delays Hit 92 Postcodes - Meyka</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 11:03:27 GMT</t>
+          <t>Thu, 25 Dec 2025 17:09:13 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNTDh4SW81Vmk4WHdCZElTOFVuVEVuQnVRSVIxRlJDM2ItVGlMVWFYSldXWDRsQUZnTGowM2FXRUR0R3ljYkg0MHlQelJQaW1BQmU2cXl2am1SSE1sR0dxSWdDc3JkWlJ3VEllNmFoUS1YalZkRmVJMlpLSkYtSFJGb3hqVnBWZlVLcjI5NGZMN2xDUy1sVWF6ZlRXS3UxaFR5eFEzMnI3d3Y4MmVMTkhzTy1MWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOc3hpVDE0VmVPNTh2XzdHbG1yUWg0dWl5eFVMdndnNW5UcnRHb01NMW9vbUdfanhfTVM3WlZJcFd0RFp4cG1uZ2doaXNHT29ib0dBUGRkV29uZ3RmN0E5d3g3ejBBZGFIWTBMWWwtb0VvcnZndWFrcDBrM1JuNVc1ZDR2MzFzdWF5Q284QnhvTUdtQno1Z0RLRDhn?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46016.46072916667</v>
+        <v>46016.7147337963</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PILFERING SPREE Bognor Regis Thieves Nabbed After Festive Spree - UK News in Pictures</t>
+          <t>Why Swiggy, Zomato, Amazon delivery partners are on strike on Christmas, New Year's Eve - MSN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 10:29:00 GMT</t>
+          <t>Thu, 25 Dec 2025 20:27:30 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPYXhrUjVzRVoyZmdKYzhHTkUxcUpmbjdCTERoSEg4Qk9iY3ItMzN5MjRLYXEyWXNSaGJNUUkzTlNmeFFRSHluSWJSUm9jR2k1Z3QwcjFFaU15eDRWWlVNLWNxRWFhQTJ4cDN3QjcxclE1c0tnODZ2S3ZFUEVHLWhLRWNCRndsdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wJBVV95cUxPYVFSVTVxOUN6QmhVYVVaSWlhOF94NFdWZ2ltQlp6a0hGd1BfM09qVTQwSEJLYmh0dUFndXRtYndyR3JtS1lmREVJSGNBYXJGVDBBYzdoVXJya0dZM003WFhEV3psOGVldDhaSFNUQ2gwcFRjYjdxLWh2aUtJSzAyMEZOT1VyVks0Vm5kVDlUUmRQOHZkZzJPdDRYcFA3RmdjY3lTejhERDlPam15RERSUVoyUjZxQ3ZuZlZrMTZTUDBpNEh4N2ZKOWtwbXVDT0Y4WnJ0X1Rma3NNZ0dPeUVtaE9icTE5TVFTZlhiV0k1Q2d0SWxvaExmb2JCalYzNUtCbXBjRjRvRGpySE1QM1RMM0hZUEpSd3FUdGc4WElTV0lINGhfZlUxZEhDUjhJV3BVWnlVVERuV19GWFdKTXFPYVVtUWNnMElLN0FFNktJVGFWaHJQMFVCTTNLSUI1SWJPMWdv?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46016.43680555555</v>
+        <v>46016.85243055555</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>52-Year-Old Man Found Dead Under Rubble and 25 Injured in Explosion After Suspected Gas Leak - AOL.com</t>
+          <t>Discounts surpass Black Friday: Amazon starts Christmas campaign with guaranteed delivery until December 25th - Mix Vale</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 10:50:21 GMT</t>
+          <t>Thu, 25 Dec 2025 18:12:46 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFAzbnlId3JELUF1alowMVB1WmZlMjV5enNpbF94Xy1MaDZyM0J1MlF4RGRSd3h1ZW1pQ2ZCSWR2R05YbVM1LWc0OENLREUzdC1RaWwwNDhDRS1wcDBUM3NNekpUU1p0aEUtX2lmOHJpT0dDSlk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxOdWpzQkptU0xjUjBPVURmNlVGWlNfQ1ktSlMtM1dzdGFaWFFMRjFWRDdSNl9sUVRVdTNQTDNxZUg0OHQ3cE9zZm42VkVoeFFXMUN2TUtCSUFtYUZaNHFJU0MyUmhXTzVBRHVsOE1jejVLUVhJR0YyV0k3SHkzb1dRdW1hdnp2NVM1MDNES1FBelBDUS1WTTExQTIwUmE4VjBhVjRLNnpPZ3duZ0hRWXZLQjBMNUt5M2x6TEhnM05ORXVBTk5SSlBwS2lIWlVaSWJUUzNhblpyVUlzSGltbFNFd1Nfd1HSAeQBQVVfeXFMTnVqc0JKbVNMY1IwT1VEZjZVRlpTX0NZLUpTLTNXc3RhWlhRTEYxVkQ3UjZfbFFUVXUzUEwzcWVINDh0N3BPc2ZuNlZFaHhRVzFDdk1LQklBbWFGWjRxSVNDMlJoV081QUR1bDhNY3o1S1FYSUdGMldJN0h5M29XUXVtYXZ6djVTNTAzREtRQXpQQ1EtVk0xMUEyMFJhOFYwYVY0SzZ6T2d3bmdIUVl2S0IwTDVLeTNsekxIZzNOTkV1QU5OUkpQcEtpSFpVWkliVFMzYW5aclVJc0hpbWxTRXdTX3dR?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46016.45163194444</v>
+        <v>46016.75886574074</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea, Japan, Spain, and Singapore Witness Explosive Surge in Chinese Independent Travelers – How Korean Airlines, Iberia, and Luxury Hotels Are Cashing In on the Gold Rush! - Travel And Tour World</t>
+          <t>Amazon 2025 Deep Dive: The $6B USPS Standoff and the AWS AI Pivot - FinancialContent</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 10:57:33 GMT</t>
+          <t>Thu, 25 Dec 2025 14:41:00 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgJBVV95cUxObnNFdXdZdGR2Y1pUQkJKS0huTjZIbFBiOFRaTWMxZ3ZEQWlBeC1rcWdDQXNvMjhMSFlqTGM5SDVVblEzMk8ySFkzTkc3enVmaUIzTV9UYlh3UzR6endDWjRTVmpXdUFMcjk4U0VLZi1UMHU4TEx2blVpYzd6dEVjZjl6Nnp3OVpPUXBYQ2U3SGN1eWN4c3BSRmdiSDM4Q0xrMmx4dV8yNDE4eVN3dFJoMVFkekx2Z1VnekUxa3F5M2FxRjVMb05XcHBCS0I1Y2xhQW9RR3FLUnZZV3N2WEZSMTRYcnBrZHpZMmI3OVFIOTVPZUFKTFdvQVB5ZU1PaTRkTlNETjJCZGQ2RVNrRDZzekI0bldzakRHb2V6aEIzX0dCbklCQS1mNXRJUnVaTUJpTm4zbGZTaWFtdkRyZ3FNWVV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNUXBpdWl1V011UEJTMlBKZzZFU2FwaUs1WXl2NWZLSkktd2dJRUY1ajNsczZVRUJ4NVdpMjVqRUNpRjhqV3RSTi1TMFFHSlAxaExTbTBQdVhZb0Q3RW13ZnNnTjZDNVdzbVVlMkk1R0l4eU5wSGgwTmRsS0pWYUY3c2hYX1pmbEZfYWdlVzlmS2JtNXF6RHhreDJzT1ozQ2UxYmlEMEtDczBHM1NWSDB5SkVGc2ZHZ3VOb1dYaHlvNXFvYVZyRUo1LVpsZ1pzQjg0S0tTOXRKcw?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46016.45663194444</v>
+        <v>46016.61180555556</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rashford signals end to Man United partnership with move to Barcelona - CHOSUNBIZ - Chosunbiz</t>
+          <t>Interested in FedEx? Mark your calendars for June 1, 2026. - MSN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 11:58:00 GMT</t>
+          <t>Fri, 26 Dec 2025 05:19:31 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5UcUJrRzlXOU5mTTd1QXVTZ2E4XzFkUHF5ZHA2d3ViRzhIXy1MWlpWSTEtVnozblNpMGt3eVF4T1c0SmdrdU9FSGxiZ0hacERnRGpfdjVGbHJQMnVMU3o3TXhqc3ZUcWhVOEV1Tkk2SFZic3BGU01fb00waXBYQkHSAZMBQVVfeXFMTzh5bGFCYjlhTHV6TU5Dd09SS2hKY2JxMDBZb1pnY21QQko2bFFEbUZyOG5nMml4Z3BDQ3RBZmRoZktfQlU5Ri00V3dESzBPMWk1eTFOMWktM1V6bWtjWXdYX19CTHpWQWJPeDN5S0VVc0VuTGppUjh0d09lbGdBTThxRmFBdHNhQ0lnRnRIamxtRlFv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPWUYtbDFzT0Z2MUYzWDBuOUtTN0FFWFVkU2QzcWVSYmtOczBFbkEwQl9ybXB4RllPX0RGYjdFZ09oVnEwRDBJX3FmSGNQT3NiaGhjVGlyTXhfMnFSbmFvSThFWFAtSkRxbmQ1RjA1a1NBTzNkcjRsYjk0MjFYUl9hcm9mTlRuQTJtTGE3Z0o5N3NJanFuRUFRTmViUlFRNk5kTXhsaWt5MXlCRDBtR1pMNGJVNlhGRUxWcGNOMUJOalFtLWpvVk9ZcUFoTVpSSkV6?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46016.49861111111</v>
+        <v>46017.22188657407</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Xabi Alonso intent on recovering the best version of Real Madrid heavyweight - Madrid Universal</t>
+          <t>Swiggy, Eternal under pressure amid Amazon's quick commerce expansion says Macquarie — check downside - MSN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 13:07:30 GMT</t>
+          <t>Fri, 26 Dec 2025 05:15:28 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNlhPTnFPTmpwX2Y0U09mSGtKR0RLdnVnNEFtbEhzeHZJQWRlenFwZTBHRWlpQlJuQTZrWVZLQ1B1dlF5eC1FQllWUFhieVlKZkVWYy1GR3ZuZjd4emJ2a1N5WW9RTTVHSlVZeWdIR1BzNHJWWU1BT3UzSTFoR0lQd29DU3h2eW1vR0Zjd3VfZGxpMEhJMkkxOURSTVd4Nnh0V293dXczX0I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxOVG4xRGl4VFh2WjFkU3daTTZEMnBOd1JYTjVLS21OUWRVajNYSE9LOWVlT0h3QzZjRjRBOGJVdTktZzBSd1F1SFdoVlRVWVNvUEtSOWIyM3l4TU9fZVoza0p6ZlByaVgxejBfVzRqT1d6cHN3WC10Wmdvd0RIby0xaDZuank3R0pid0VUSEh5VDF6eFJDQ2VkTXZGNFlpYWVqZFlGeEJHYWJOUUFCMmZ4c1dNbTFlbDFrcUZ0bS1wekNTZGcwVE9qbUhWbGZuZlVrN1pfQVZEeG1STThjVF8xNUtyZjQ0Y0pOaTIxZVdOTENHUjF6VkNN?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46016.546875</v>
+        <v>46017.21907407408</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Surprise! he leaves Saudi Arabia to play at the Bernabéu: he is better than Dani Ceballos - madrid-barcelona.com</t>
+          <t>Lucky Redditor scores $6,000 in free Samsung 9100 PRO SSDs after Amazon shipping blunder - Notebookcheck</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 11:30:00 GMT</t>
+          <t>Thu, 25 Dec 2025 18:48:00 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOOE9qS1hEdXRfY1d5bXpfWjlvdEdGVUloOEU4S3lDYTdfWEFIUlBnMEhRdlMxZ0laVWxMLW1KcDdsZHQyenFqX2piT3hIcnVWSnJ6R2c2QTVWN0JUdUoydE1ENXkzWk1JM1Y0ZE5NQ2p2Rk9EbmExYjFfQV9ETWNNeFpsSmMxNHNyWllEM0NKX1A5clJkT2ZIVDRtWjdrQk9pSHZtRlNCLXllZVdSQmtiMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNenE2anhHbVF2a2VTUEJENWpZeGhkODR0OUFBRGJkUHNweXR1eDdxYWxob3VaNGE2elpWOG5XUmhJMGR1RlJWbmNXWXRCUDZnSTVVcE5ETFNWUXlkSDZOUWpnSHRWblpZZmpxb19NeHZ1ZFJrdlk5MVB1Q1c2bzZUS2ZEVnd6Vk1VUTJONGNBS29ORjUxems1amNjUGNpcFJZSHRtbl9XOXdhT21FeUQ0Z0h0ZlZNYkI5aGxJaEF3M09yOWRnLTZIcXpHQUo?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46016.47916666666</v>
+        <v>46016.78333333333</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Knife fight erupts on Tube platform in front of horrified passengers - London Evening Standard</t>
+          <t>Thailand Emerges as ASEAN's Premier Logistics Hub Amid Global Supply Chain Realignment - Nation Thailand</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 09:37:07 GMT</t>
+          <t>Thu, 25 Dec 2025 23:31:00 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPQ1NoTXVwV056cXBDZXRmT1BOWG1GVElPYzd6allIeFBrd2dkSEl6S3gwLV9FNXhlM3VMb2NzQVlRdUpaME1YNTRzSmVCWHFEb0FURmlvVGZ3WWlSMVl0eTVBWFhMTGFoVDNnV3VaYmk5R19DWGYzTDdTcU1RbDRiS2JFLWxVWmlTV0RGUGU5aUNlTEJvTkdXVFRUM0NBRGY2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1FeHMtZElyaml4NGcwSE9jOGdBM0J0NmxsSmREMXFFdHppSW9IMUluUzdGYU1nQk04S3ByYVdmSG1lU2pHUlJObEVweUNILUQ4eEdnQUZ4a1RoV0NUYXlrRmpaUFA?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46016.40077546296</v>
+        <v>46016.97986111111</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Test your EastEnders knowledge with our iconic Christmas episodes quiz - My London</t>
+          <t>Where Will UPS Stock Be in 1 Year? - AOL.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 11:54:25 GMT</t>
+          <t>Thu, 25 Dec 2025 14:31:04 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNYk5ucW5xOWFaeExlN0JxSjNHaVdBZTYxWDJZaDJDX01ISXdkbVoxRno1SE5IOFFtWEV5dURsOVlldFcwZy1IamVZemVjb3B2cUVyYk5PelVJVktwNjJLSU9XNUZMc1hmaXB1QzZrWkgyTFZROG1ZQlZjRENpT3ZTYWh1cWs0MFB0YmhqeHJSZTY4M200ZmdaM2RiUEFTa3Np0gGMAUFVX3lxTFBQbkJESHBPaGV2WjQ1UFhNa09lUXh5TFE5Tm9vak1DMFIzV04tTjhmZ2xaTkNXMFNEWDdDSmZfbkExN1VZRHZfNktCZ3NtcnpUb0NJLVBWdS0tNWVjUmx3VEdBUzh2allLNm5rNnNWcXRNVzNqc0lZdUtoY1ctS0xLV0dGLWh4Z1dqcUVz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1UUG5rVmlBcFV2VzBNRkFkdWJfX2dPNWgyOGhickVZbWlJWVpqQWxBNUdKeDJpVGxMalJIcEcwM3JvWlFwS0Q5SVR5ZE1mSUJFVFREY3Vyb3FobzdBcEROWnZHVUhzZkVxcnFUNA?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46016.49612268519</v>
+        <v>46016.60490740741</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>25 chocolate bars that vanished from UK shelves that are seriously missed - My London</t>
+          <t>Is the post office open on Friday, Dec. 26? Does the mail run? - NJ.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 09:05:53 GMT</t>
+          <t>Fri, 26 Dec 2025 06:18:30 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5ZZjMyWVdCazVSUzBFZHRWaHhNOVR5X2V6QU9hS2dXRHp4LXcwRXJMdFVjZUtyZjRTZzd2SnVndDV2V05DLVFQLW1GVzItLThURGU1eFllTkxON2hvbjlMZFE3QnUtdm5zNE5wenk1MElrQ05nXzczMGtzdHkzelHSAYQBQVVfeXFMUGNvQk9RRXBFR0tpczQxaDBvT3Y5am9PbUlpMUlWNHFNcEt1R1BCQ3llcTZyLXh6M05wa19lci0zZmhlRjdxbE1xdUV4czZqZ1E0dGhlbEoteVhER1MwdXlkcEJNQUo5akR6emo5NGxNX1hBV0lWYWRkQS1VQkROOTRlS2hY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOa2pEcDc1cVRhSTMzZ1BSOGZhVkdncEJfZm5MRUFra2xqSFRINTMxRU84am9JMkxJWWw3Q0w5TDc5YzhfaU50VzlkMUYybGVBM3ZoQkRmTF9rQ0pjc0k4MVl4UzJDSkJjY3RLcG51RklpMkVWTzF6ZUt3TV8tbFFnT1k4TG81Z9IBmgFBVV95cUxPVHdaanFuNzczb2NMUW9iV0M2bjBzUEFTbEZSQUctYk5NdFRHQ0w3UXZZN1ExRG1HYXZENWpJcWhxcFRHREpUSnBfckw0MzFmeUsxN2tjLXNvY3A2UTdVdU1SUnM5VU9rMDg5UC1PR1otN0J5aTdhcllFOHQ2dGJvWmstZXVubUk3S1hwSjFxN1JXaUxKbFNLSTlR?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46016.37908564815</v>
+        <v>46017.26284722222</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Horror as construction labourer lynched by vicious gang on suspicion of being a migrant - Daily Express</t>
+          <t>Delivery workers haul more NYC packages than Santa Claus - Gothamist</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 13:01:00 GMT</t>
+          <t>Thu, 25 Dec 2025 22:07:00 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPZFhJUUNYU1JkZ1NrR3N4U0xpODUybjFXb2hfX08xNkNheDI4VEtzUUJ6S0VKbjZEZ2V0c012YndLUE91REx6UERLZEluVnRYVlFpMnJFdmtNekNNTmtTLUFSOFpZZ1dGTlNUVDVYT2djU0VCOFZFV29lekctQ1NqOUdFdWVhWllm0gGOAUFVX3lxTFBRenJOZFIwM2dOWTdIT09fdXo1VTFCTndkeHpBbDFkRTUyWlZ5SmU5SWhLeUplM1BRSFR3Rm1xY1M5OHNwTUVoMHFVckpUaFpyWTYxMDdEM05QQ1VGU0JJekR3NnZ2VFNrcUZYby1oTlRoSmRtcG5DMFc2OHcwTnpFdjlPbE0wa3R4MjhKUEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNWjNPblZNVEJ6LVQta21YU1BWamE1NlhzdzhWY1BtVzkxZmJLTDFMNHFkQXlzY2ZGWlQ4ZDN4YjJ3dkZVaEs5aUJ0WHlIYmRlanVralJGaGRLRHJRZ2ZPYnMtLV9ldmpldWFnUmZEQkx0a1E3TjQwUDZ6M0k5b2xzNDMxaWM1LXRKOVpj?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46016.54236111111</v>
+        <v>46016.92152777778</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Major sports events in India 2026 - full schedule - Olympics.com</t>
+          <t>FedEx H-1B hiring sparks outrage amid firing of American employees, Indian-origin CEO faces heat, 'They are now awful' - MSN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 11:54:00 GMT</t>
+          <t>Thu, 25 Dec 2025 19:51:53 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQc0RwX182RlFOVWtuXzRrRGJFYTZSdUsyYzhkYXJaYzRlV2UyT3VmMl8xU3lsaWtGX2ZRSlR0cWFfdnFqVXV3dEE2aTVDOHZvcEZXMl9ZYTZkRzBtRGl3YTdwZUhibS1vUzhCS0lPQ0djeDMyWFJXRDVMdmJ6a2JRckJWTG5mREVLMnBj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgNBVV95cUxOeHlPM3hoTW5jTzl2VURnSk9LZkNRTDlDYWFaZkZmdXo2Njhuc1ZrOXlwQzd0c2I0anMwMjhIN3R3dFAwQlBBMzVNcXVsdXRXU01NVllwdTJtNkswNFJSQWkzY0luS05zcFNIYkY4Y1I2aHo4eTRKMkFrbzVIckJlSjBHN2VnREkyc1VIeUVmRGtxLURBYjNNV2hkY3dqdlZpVkxQMmZURVUxVEV4ck92VXkzYTNuMFB4Rk9WeTBmek5IT0Zma0xGS1U0RnU4emhlaHl2b0oxd1k2dzVxczIyLXpqdk52ajR4OGtFdDBhdmtaSDg5Sktab0J4bVlqU01VeTlFOC13dUd3dnYzdFVHUVB2X2p1M1JGa3JQSjFuMDNVMGRMTUxsam5OWWZqTWZCdmdsNlFfRzJwQzdqbWloTjBNZU5sRHd4UEIyZzUyYU92OGZwdkM2Y0JqN1Y4SnNiMGJoU252aXlPQzZMSnk2cnd2OVd3WXlHcHNMR2xXLU5BUjFGZkpsemJWQmlTdXBkN0YxQm9UbXhlNDJxcFZRTmlyUGdLZWxWLUJFSS1B?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46016.49583333333</v>
+        <v>46016.82769675926</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kinetic Trust Limited Building a Base Near Support - Earnings Beat Highlights &amp; Budget Friendly Trading Strategies - Bollywood Helpline</t>
+          <t>Is Christmas Day a federal holiday? What stores are open? What to know - Cincinnati Enquirer</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 08:38:37 GMT</t>
+          <t>Thu, 25 Dec 2025 14:47:00 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQYU9uLW95VW95ZlRQNEVKUjRvRWVSaHlKdXJDdTd5blRaZFhtQWlrSnlTOWJHUUNyazdUN3NteFZQX2hXWDFYdVl0bnJVcEYwdUt4NTJIX3Y1ZlZGNDJoOUt4MEwtcE4tczc4Q0M3bVdvWTZ6d2hoOTlXT1NaTW9YZGhiWE0xTlY1SVhUS0JR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQQW1KODloTFVYakxhU3pURTRiU0hiTHdtZTFrNXhXODFGczRGOGl5bGhHeFdRRFpDMXVRWVViblVNd0RmN290TG9XeEJLRUxyRGJ2V1Z1Q2xUZHlaV1dLNjRSR1lGWnBlWEc0TXJSNUs0Q1RGNW41VkVnV1ROTjVOZkplRjdwOHM3VUI3MGl3endfekExcjBNUlJnUXlCY090Sl9OV01QMEVadUZBRGlRREE3Y2w2Z1M5Z3c?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46016.36015046296</v>
+        <v>46016.61597222222</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches Belgium French language</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("brussels" OR "Maastricht" OR "Antwerp" ) AND ("Bombe" OR "alerte à la bombe" OR "explosif" OR "colis sans surveillance" OR  "explosion" OR "colis suspect" OR "tournage" OR "poignarder")</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Is Autoline Industries Limited Forming a Consolidation Base - Market Sentiment Shifts &amp; Buy Sell Signal Notifications - Bollywood Helpline</t>
+          <t>Brussels unveils historic housing plan - financial-world.org</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 11:49:30 GMT</t>
+          <t>Fri, 26 Dec 2025 01:00:50 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPbS1kS1BuUXBFOWcxUE9UTHczUlI2ODNtSk02ZWpjTzB1UmpiSEMtaWd5T3doVk5jaXZjdmhDdlA5V2Z1VjdpMmQ4WGNMSXdwNG1ScFdLcUlqNURKaHNwc09JVXMyWXJVR0ZuSk1aWFlRbWJyQnNCTVQyRWMtU2lxemVYWkFmWGlIM3J2c2FZOE1RNzBLVmlQOHlXcTdld1FCMUx5cnZTTUpXRFNDMmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNZi16RVR5RGVNaGMzZktjMkI3azFRUndhc2NwYVlRTHphbGY5QnJqX196UmVQbDhaX0ExSGNmR3dWZS0zTHJWVWNlRHVYOVJ2aDlaS0trMm9rRmUwdWRIeGNZaFlaSVlVaWVkQ1BUWFAybTlEOHBTMU5ScVh6Y0ttWkgyLVdIYmJENFhGX21EeWt4LTJrYjNqdzV2ejJuZ9IBnAFBVV95cUxQSDlUVWFFMlZFZk1SOU9DVTlURWhLdHpHRjhtcFNxYW1ZLUFIamtEUDFUbGtybTBYV04xQWJFWllYS0kzaXh1WEUwNnhHVzJfQlFUZG82cnBNWVJTZWl6bXBZRE53eEVKN0gxMlBNYVdNeUFCZXZFRzZyWEZ1SURyVUMxLWw1MUVDYmJkcTdZMHJWZFR2dlprMkNWS0U?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46016.49270833333</v>
+        <v>46017.04224537037</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Man shot by police in the centre of Bruges, leaving him critically injured - The Brussels Times</t>
+          <t>Hinrunde Wrapped: Looking back on Bayern Munich’s first half - Bavarian Football Works</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 09:02:03 GMT</t>
+          <t>Thu, 25 Dec 2025 15:30:00 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxObDZKVDladlB2QnR2cE5GejdBLWRtbTJLNVE1blFhOEtJaUtsWnVuWHBGYnA4cmJBSkVFWXNxVFprbGJsNGhURnJ4eGV2cUhEZjZodE9BSzVqTktTQXBWN1lXSlZma3FqOWI4TDVwMXVoN29CaDZVZnZnN3l2N0pCYW9MaWhMRWg5Sy1KQUFnaEhzeHp2YUdqbndtekNWOWVPUFR1Qno0aWpBaUR5Mi11RFJDdlhEeFIzYi0w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOazJXb3ZtQ01lOHpqZTRWbFJlZHEwNGJ2ZHZBYXZKWU1DTjNsUWhrRFdiOEU5Mkd5ek1TVVM3NFVIQlFyQ0x5anMwMFZnaE9ROHVCQ0ZaRnFJTVNpT0pQTFQ2OXIwX2pzMGxnYk1WQUY2TDBOZEp5YjF5OUdZZXg1UVpWTFVwbEZYMV96TTVqclYxbEtudHJiOEtqQXZ1eUZweE9QR1VPZVRwUGgtc1RqdDA0TzFKaWpuc19UOHlidjhxVDJVbzdV?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46016.37642361111</v>
+        <v>46016.64583333334</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Prison staff angered as government fails to act on overcrowding - belganewsagency.eu</t>
+          <t>Short Term Trend Reversal in Deep Polymers Limited Possible - Monthly Performance Summary &amp; Explosive Capital Growth - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 11:41:00 GMT</t>
+          <t>Fri, 26 Dec 2025 00:16:57 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOa0JZczJ5VkVoMUZSUS13VnZGSVVzQjdqYzg2VFRtY3NHN0c2ZzEzWXRiUTNVOXQ3UU1VNHJDQ3NCa3J0elRqdzNoQmkxR3IyYXplOFZROF81OWhnVERBRVBieVBNcHVRclQzV1RERGhlYkxJc25mRXZxWXU1RU1Vb3NnYk5sQ0ZiXzMwSm42OFBhTjhOMTRzcWln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxONGxXVUY0OEZfeFFrcEN1SjVuMkMwOVRuN1poZnU3eEEzOENrTldmM2JtV2FWZFphVnJSMTZrZk9XSzl0WVJXODAzSGl6emF1WDhfX09JTnlTOHFyd1lMcEd2ZGctVXRUY3phQnlhYmUzT19fX2V6WWdFc0V5Z0dtd3ptUEt3VFhIbF9UVElNTGpmaThMSU1IRUV3?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46016.48680555556</v>
+        <v>46017.01177083333</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>North Kildare RNLI Raises €117K to Fund New Lifeboat for Wexford - afloat.ie</t>
+          <t>Piccadily Agro Industries Limited (530305) Hits 52 Week High - Breakout Stock Watch &amp; Explosive Growth Opportunities - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 12:17:56 GMT</t>
+          <t>Fri, 26 Dec 2025 04:29:26 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNeWwzN3NYYzMxMFBJSWlXcDBuOTFtS2NXZzA2VzI1Q0xrNG84NFdaX1d6NTZpWlNOckRpbTlScnlPVlliMUp3VHgwbmNJR1p3OG9KUHk0dDVEOE5yblNLVmlMZWp0T09icEpWZmV5X2NwbmZfNGZ1aXBZaHMtWlVTa3F1Y194emJCX1o0dUFEY3RUbzg1dDNzNXJ6R2FYcGhhdmFVX0dPQUEyZ1E2ckE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNZ05vWkVWOVhjbFBGejZxYkw0ZjAzQkpxV3ZzOTREYnA4TWp3bks1c1R6ZmRKMFFkWGNkMHg4b0ZGb2swM1NkX2QtbWtWYmpHaThfcUtGcklzS2pyX3JQSU83bU85emp5ZGUxTnFnT01MZkZoRmtnYnBDSTRGT2d2ZzUzM05jYXd6MVdSSjNoMmtNX1Z1VTJRZ1l1UEpzNU51cVgxbWV3?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46016.5124537037</v>
+        <v>46017.18710648148</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>XR and JSO Broad search</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>"Extinction Rebellion"</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>The impact of the Palestine solidarity movement - Red Flag (AU)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 01:26:12 GMT</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNM2tCeDFiY3N2cGNfUjduWXdkWjd3Vi1zMmlhMlpsY2ZCbnlPU3FmTjZFZklBaGdlMkVCNUhvbTc0VXRFa0gtMmZLYlVISDh0RHROdDZnM21PQ0VIbTMyNjdGRHRFd0dFVHZYLV84M19OT0tIVElQQTk0dWxNS3Z5UURJY0w?oc=5</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>46017.05986111111</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>C.C. Citizens Police Academy Alumni Association responds to officer investigation - KRIS 6 News Corpus Christi</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 03:26:54 GMT</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPZFpLbFZFRld0eDZ2Qy1ScWlOTkJ5bGt5aGo2OWhKbE5Md2xoMlk3dDV5eDh4ZGo5UFFSbndNUDRicW9zRWdGR1ptU3FfU0t3NTQzdk4yQnpuZEFXVHk4OW1SYlg4Nkd3VVhUTFBKSUhkOXMzdTVnbzU1UkhHbE1QYmR1QlpNOTZTNFIwQ01PYm1DRC1HcDVzUUMxbmFPZDVNY3dITFJpQzBIUTN0SC13WmpWNzdxa0hMYkllSzBnQnZodGc3YmpqWUJnX1FHcDh1UlN2Q19GRnEtRVR5MGtnS2o1RnJFQ1hLaEw0?oc=5</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>46017.14368055556</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>$400K shipment of live lobsters hijacked on way to Costco in possible ring of thieves - New York Post</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 19:56:00 GMT</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxON3VOVFpIeTUxREdqeUhZX193ekxoOHpFQ01hbWVWT2VpcXo0TXVmQURRTU9QMmhUclFvdmczSFhWSy1nYXlkQkZxcmNVM1N3a2M0bloyNWVWQm4tQ05QblU1bDBTdTRRQ1VzUVpvNEdBdHU3QWxqUW0wSjJhb3UycHdIN1Q0b2dzdXk5c0hPY2lWc3pzc05wY3FvOERLY0FWMDU1bVBISk10SGg1a0R5UlBqU2R0S1U?oc=5</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>46016.83055555556</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Fabrizio Romano Transfer News: Man Utd ONE TO WATCH, Barca PLAN, Glasner BOMB - FootballTransfers.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 07:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOQmRKbzBENlRjT2t2VkdwU3dhajZGRFYxMmY2TkFsUUthcUUtNWtTRTJsNkhESTJZaXJjMG5PNGRWbEc5MkJtRlFYcnk2VWsyUnUyTnNVQlV2bUJMWXdqR0FQS29KXzJ6YW9JTHNCN1F0bzU3UEJULW1VUzVXRGdUbk9OVjBWSGdGbTFNNFJfTTJZUE5MS0tqcTh2Vmd2ZmlGanpBR1pORzNQOEZiZXQycU43YUstZmhpT3V3eFdySzBHbURLZ3QtNmVxMjNLelJvRGNyVHllcDZVSS1sWmZlaTAwSV9tUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>46017.33263888889</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Can KFin Technologies Limited (KFINTECH) Maintain Its Valuation - Emerging Market Stocks &amp; Capitalize on Stocks with Explosive Potential - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 00:11:20 GMT</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNOU9mbEdGbFBGbTlja2RpVUV1V01kZ2gzeWFMVnlTeHhKb2hNNWlOZDRkbWYzRVU1OHZ6SGNQbnhBMzhyVGN2VDBDWXFuZnh6czM4UTJMbktoVDRGZWRtU1R4eTRXbEVCQjVNdjF1RXJZV1JGbTVDUC1ldkR1aGNTZGFrT1A3eElEeWszbjhlVmhLQl9kOTJfcmtrMHRtQVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>46017.00787037037</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Andreas Christensen and Marcus Rashford send Barcelona into Copa last 16 - IOL</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 03:26:45 GMT</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPU0o1WHA1OVFZTTQ4LVlaZWdnT3BZY0pteWowcHZLcVg1Ni13b0I2aWFGMHhoZFZianNiZlBVQWxvR0NicDFMSFI2c3VmS3VST1pkQkVFTTdBUlpFMjVZZDFqZFZoU3cxbnNPZGJSM1I5VjdfLWw1ejJKOU9QN2VTbWVldTVEWGRGbzFvSTlJY0xSbFdsZEw0QXFqbE9jdlBZODh0YWVkOWhLR1J2bHctTEtjSHpYUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>46017.14357638889</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Football transfer watch: Liverpool beats Real Madrid in the race to sign the ‘new Vinicius’: Report - lokmattimes.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 17:04:24 GMT</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOLXplSUczRlM5VVVaSThvdi1XVW5ieUw1dXJxd2ZPMmdwVFdMaC10X1FENHpJTmNpaW1uOFZDSVpnSk4wNW15X2RYWWlKbGpRWFhtc2tmTTZIbDRIVDRSU1FnbUh0OTFsQVBrdFU1a3VNUkNmWTE2c3hvVFVCSkNoSF9kZmVLUTI5VmxjdUdXVWRDVHBqWkplUEJYTm9oOGM5VHc3dHhBSGFtdnpxSWxKQ2g4NUNrYVBsSnNoTVUyZ09mR0pDSnlEcS1CbW5hNlpSNGpFU0t3M0bSAdgBQVVfeXFMTi16ZUlHM0ZTOVVVWkk4b3YtV1VuYnlMNXVycXdmTzJncFRXTGgtdF9RRDR6SU5jaWltbjhWQ0laZ0pOMDVteV9kWFlpSmxqUVhYbXNrZk02SGw0SFQ0UlNRZ21IdDkxbEFQa3RVNWt1TVJDZlkxNnN4b1RVQkpDaEhfZGZlS1EyOVZsY3VHV1VkQ1RwalpKZVBCWE5vaDhjOVR3N3R4QUhhbXZ6cUlsSkNoODVDa2FQbEpzaE1VMmdPZkdKQ0p5RHEtQm1uYTZaUjRqRVNLdzNG?oc=5</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>46016.71138888889</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Heatmap Data Shows High Activity in Remsons Industries Limited Sector - High Dividend Yield Stocks &amp; Explosive Capital Gains - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 02:31:54 GMT</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQUlJKV0dGbW5xdXdmR3NCcTJvSmlWdFNJQWg0RC1zcEpzbTBUMkJvNGp6dFprS0NKbll5WkhvLXdTMGVXWnlQbi0wbXlXWWJsQk92bTk5dTFmNWpUa1VpRmc0bWpsM1FRQzgyRzQ5RFBXR0J5NmxwNGJWOEpJb0NXdzQ1QkVCdDRYTHNfVHUtQlV3VjZwc3RSbi1hbGRmenR4cjJKZXJwbmNNZkpMMUJmdXhoLW5rU1VFTlIw?oc=5</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>46017.10548611111</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Would You Accumulate or Wait on The Ugar Sugar Works Limited (UGARSUGAR) - Stock Liquidity Analysis &amp; Outstanding Investment Returns - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 06:09:31 GMT</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPOTQxNDdCazJTU1g4Tzd4ekVGSWFCV2FLRmctMHZ1eFAtaGZOMVRsOS14Z05jMmxrSThmaWk1UTNPUFNtUjhQTkVJaDlRYnIzeUpnck5NQi1NdVF4bUVkWG5CcEswWDlxWnhvTi1pWF9YV1V2eVp5Wjl6OU9uLUJoM01NaDFzVFhVMzlMX1BXMEF0VENmbjJaNFpYM0NLUlV0SkRyVHdjNEFZQUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>46017.2566087963</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>“Has been offered to” – Fabrizio Romano provides shock update on forgotten €44.5m Chelsea ace - chelsea.news</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 06:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBVU2RjOHA1LTRHQjZVMUtfOWVId002bkJsWmFkTUtIYTJHWGd3Z3JoWURnVmZtam5CMkNSVDNtV1NRM3ZKX1ZDMm8xdXFIMzBvNmZSUm5jb1FyQzB0MHdXUGJkU3BzekFWTGhjS2hDckg3MGtTUjRN0gF8QVVfeXFMT1dDNlo0TnViczNCV0xXOEd6WlpUMlZucVBrdHdYOWIza3JnRHlsUWQwUHhpUmpqbXBwa05KSXlNS1dhVVZKeUN3ZnlwRE81aTJrblhTS0xlZzlKbnZtNkxxQjdRdHBVVVZSSW9xTzJxZ3ZsZUhoT2ZtN2NVRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>46017.28125</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Flamengo fans cry foul after defeat against PSG, Cherki “bomb” gets people talking in Spain - French Football Weekly</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 02:11:26 GMT</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPYXZxWExDZDNJc1gzTFE2X2VYNktXZzlpSmhfTW1vNWFWZ2JBdk5Da0F4WllNcDJNLS1oSnZyV0lEWmFNRUx4Y19OWDZjUjlORnpBVDVwMGlpZ25qQUdWOUtCNWlyWFBzeXRxMXhBM1hQMkQ0d0Rrb01mdXZEZUItXzl3ZURxLTgtRy1GaXJOem9NRnBXa041bEVOdHFNZFBFWXVyd29jak1RLTVWZDdQX3dzT3haeTd0VGpmMnhxVnpIWmNJbWV4S1JlUjcxQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>46017.09127314815</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Local Town Searches Bicester and Kildare</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>(Kildare OR "Newbridge" OR "Bicester") AND ("protest" OR "boycott" OR "bomb" OR "shooting" OR "explosion" OR "stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Police hunt suspect following Bangor stabbing attack - kildare-nationalist.ie</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 15:25:35 GMT</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQNFNaRk5qb2dMZDM1TkFIcEZrNnAzamtuQXBlN3JOVnJieFp4RG00cW9IVC1GQnFPeHFxRkVkYjZpOXFRZmNCWk9UaW10Wk9RbHM0UkpvdXVYci1lNXB1UG9sakpkN1hrU2owTE1HTGpGTEdsbXJfTWpESVZyWVdDTVlYSlEtekE0WXFhVV9SaUFJUnhhWjl4OVhubkUzTFJLUHAxTVhDd1JDVk9v?oc=5</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>46016.6427662037</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Village Search Bicester and Kildare</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Discover the ultimate shop-and-relax treat with voco The Club’s €50 Kildare Village gift card and stay package - MSN</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 05:51:33 GMT</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxOY1cwd05RU2VQbmtzS3NmejlJN0Nhd1RUdjRmX3NjWXgyc0RqaXNnTUZhcVExRGNIQnJvamNxazJialBOWFpiUXp6d3ZMajJWaFFsY2FIOXlPRVlIOGlvN05zR2I3bnF0UVlNSFpnamJ4XzJac09LR3JFaWNVekcyU0IweVZVa1BUWVJQV2xrOFlYaFY2dWtoblBMY1ZOdlFTbkl6T2NKR1h4VlBYOHNYbGpmanN1VkVENHZ5LW9BWnM1WlFWZDVoZ0VHMldOSUtRTlNNcWJvWV9hak1FUVRQMFlHWEFNa1ZjaFNVMDFFckFtZDVHaS1fS2NB?oc=5</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46017.24413194445</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>New Covent Garden bar inspired by New York's cocktail scene set to open in 2026 - Wimbledon Guardian</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOZFF6RDJsSHlmNVk3SEl3dGpEeF9OZjFHYTNPSjRESGp4WDZGdE5ET0pRb1lhODUxVjFfNXdlX1RCd3djSU5YVEJFR3BvMGRFRkdSMDhJd2VIellkU01UdlA5Q0xhSzFCT2UzWGk1M3I1U0FtWUZXQk1OOERneGxJR1F5OGRhS1VIZXNnWm5qeF90cDhvaHcxZzh0ZWdDcHRwdk1ibW5oN05ocTZkZFhaVDcyN2xFTmREeGhEZg?oc=5</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46017.20833333334</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>'I'm a bin man - don't throw away your wrapping paper this Christmas' - My London</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 17:34:59 GMT</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9BMUZibTcyc0doZ29ySFk1RElZa3Q0cHdRZjR4X1MzZG1kTER6dVJ1V0RkbmhLVVUxMnphbF81T3RvdDNMdUpWTzJfb1VwOGFuQm9penZpTGZoUWg5V0YtMXpJRExmS1hiSExta3R6a01tZmh10gF6QVVfeXFMTjZ6Q1VBRy1ZLUl3UkF3ZzRxakNYby01NEtqbTFpQUdoVzZVMm93RTNsS3JSMkZ2TDJ0dFdpci02YkxlRXVtRG94ZEJuUG1STXVhLTBqVWctLXFzaWtBb2o2QS03cGc5LTN5bXZqQkxuUnZUc19IdHZZVHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46016.73262731481</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Danielle Galligan selected for European Shooting Stars 2026 - MSN</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 03:24:52 GMT</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOTGFtOEpiTE56SlZpVUxhTVBHUmJaYm9BOUlPNEJxU0tsVFhYNUpyM2dWU3ZsSFJ1MkpZNEJaeGkyQ0NFUWhvVGoycHBJU2pSRVVUNXpBTHRMblJYeWFUUkNSQ2t1VTNQMXNGMTVtb1pTZm5HMmVBYzJ3a3BxX1RlNnNPNUtoNjFjREFNSHJHR1BHcHRIZzc3ODFQajRYdDdORHQ2QThPVEN6V2NxaWhkbTl4NUVVZDN2U1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>46017.14226851852</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Early Christmas morning shooting injures man on London Avenue in Gentilly - WDSU</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 15:02:00 GMT</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQRDRVY19iS1JnemI1Z01yc2szblc1S3JubVpVSTdaMmExdmdVai01a3VTTllIWGxMbFVhZTVpX00yVUpMY3UxY0pRVEVhQmx6MFlkcTJGX253RF9pdmctVHpIbWh5UkpCUGRiNHFiT2stM3ZWeFdSYl9paGJzMnNudW5vOVROTnJpZ25Qd0I1M1dXa3ppRUdhZ2FGcTl2dVoxUUJISUJBMHZrNEt0MktsWTln?oc=5</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>46016.62638888889</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Michigan teen gets life in prison for Oxford High attack after wrenching statements: ‘I’ve done terrible things’ - nwitimes.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 16:45:59 GMT</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOdzByTkdWdXdFa2h3eWxPSkFHMm84TmRKRTN3WGxBNFN5ZGY0RFFwM2VsMmxHS0VSM0FMa0poNFhKNENmbG9Pb0FkcTdPR25Vc3JKMkJ5TzZIbnVPazBEZ1doZ0FGLWUzYjdfcWRkckh0X052b2ZybW9CdVlxeWowaDlvSGJ6OWkzb0hJVTFwMWdQLURpWV92NGdsQnItbTRxTjNxVnNnNm1FTkd1emNJWTJ1eVIxcUxQN29XWmhQMUNIVS1Hb1FOeUpkaDk1QkxoU0hONWEtN0thTDM2aUxWS3pYMEM1NUNQMEZVSTdVTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>46016.69859953703</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Published on: 2025-12-25 21:18:12 - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 22:50:30 GMT</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOUXgwdUZERVRDcjNYVEtNX2VBNjhDNFZrTkJQUG1Mc296SGhmNXFYRXkyeW44VVQ4c2F0ZUhNZ19vV0hraTV3MVdURFVNNFRGbkU0c0JuWFFMdHZYVV82ajNiY2xXRk1UYzJhRXJpaTAwWkIzRVR2clpNYmpDcDBpanFKaXVya2Z2Q0d0UXEyaW1nc244WXYxaklESlMwTm50U0tYN0ZOa2VIRVplS1dLcGlsMnFCMlhucXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46016.95173611111</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>‘Build a Bangla, we dream of’ - The Hans India</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 03:03:32 GMT</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOS0FkQllzM3NmSVVzSXY4RDUta0VFckZsc2swWWRONldtbjE2OUZmYl9paXNXRV93aS1SZjh1Z21zVHJRM1VaNVYtQWYzNzFreEZBRUtnZDVsdjZ6WkpraEwzOS11NVlBVFVEalRfZkNCNmdmNDJsT3BVMHB2SlJSZ0gtekw2eGdT0gGIAUFVX3lxTE5LQWRCWXMzc2ZJVXNJdjhENS1rRUVyRmxzazBZZE42V21uMTY5RmZiX2lpc1dFX3dpLVJmOHVnbXNUclEzVVo1Vi1BZjM3MWt4RkFFS2dkNWx2NnpaSmtoTDM5LXU1WUFUVURqVF9mQ0I2Z2Y0MmxPcFUwcHZKUlJnSC16TDZ4Z1M?oc=5</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>46017.1274537037</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Hyderabad's RGIA gets bomb threat for Flynas flight; lands safely - irishsun.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 15:31:00 GMT</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOek1CclNaWXVrem9xZUZ1ckdENkxVWVVfRzdYM1JIVWVEbG1kZWIzQlUxUjE1aXEyUzJubHVsSG16OHdLRlpTWlhobW9JUnFVcnBQVlV4dngzVHY2aGlQak9EbVFQck02NHE4TjY0YzRncS1NRkxFYkdqNTNCa0R1TGNWMnZkcEpMMGZNZ3dOUWlkeEx0WV9fenJsOG1QdHpMUjBjRw?oc=5</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46016.64652777778</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>The 5 best fish and chips in London according to reviews you need to visit - Tottenham Independent</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNY3E2VTc3dFBUM1JidDU5MjRDd2FUTWhDVEpsQ2wtNEI2XzA1czVXWnpXa2NydVY3Sktpa1hISFNCa21RRENNU05ZLURyaS1qemNqNFlQaFBRR3VPVEVsT0Z0cU1Gb19SUnp4elRMazA2R216Z3ZjMEU2WHg4WEo0UmZIVERVMUlPeUNJSmpKUWNHa0JMbmZhazVmVVZSdGdCTThqUHUzYmE?oc=5</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>46017.20833333334</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Bromley women living longer than those in neighbouring boroughs - london-now.co.uk</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNeXBYSU5XVWNocTlrU1hpZzVrRWhlcjJUN29xTzZfbWY1VXJzMExZR0YtcEdhMmFfeGJtcUdZTXJIMjBja01Ld0d4VzZKdGlhclRUa2RMOFVDZjUzcm9CSkZDSm9jdWFqZEVGVnVSVjA2blNFN1hTSEwyUXQtcTJBR0kzZC1vRWQ0WU5xNEl6OXdvS2p1ZXpabXlrbmNUd0xJdTRV?oc=5</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>46017.20833333334</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Businesses across Havering that we lost in 2025 - london-now.co.uk</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQeGw4b0dmQUwyT09PMU1waUlNTzJnODRhM25NVGR2bF84MDdYWHZWN0VTVkpVanNZOWwwZ1RvekFhd0tfNlNoTjVucGZFRGl1am9WekhGU1ZxYllFQTFYWTkteFFQdWJ2eXdrck44YUZabzE0WHR4SWZSUnlRQVRfbmZXaUZweXRrUDJCMkJMcFllUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>46017.29166666666</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>All the biggest developments coming to Southwark in 2026 - london-now.co.uk</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOV3NjRFBjb1UxUEhqM3FXV2RGLUtielVGZEdqTi1SUnEzdnRXaDI1ZUVPTmZwOVVhUGlsbUNDMFFyd0huTnpzNk55TlhjRnFJX00tZ0FJLXRzb1lUejk0ZzctYkdPUS0zNmpFTzdWVWRiaUdZcGNFOVJNVVRvTWRUQkJDTnVlMkpwb05SblE1MFpWN3I2U05N?oc=5</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>46017.20833333334</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>New 'fantastic' shared ownership homes launched in Epping - london-now.co.uk</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOb1p1R2dDLUVGQWJ1aTRpSC1XaG5SdkVDaXdLbGVtaWZSVFBzVkRJOXF6QW5PUjhrLVNSaVFIQ0djWkg2aXR2TDZ2TkJRRHhaMjJxakdVYWFUNDJqeC1VbkRzaWZtX28taU4zVUQ2c1NvaVRDa0pFbFIxdVRaODlhLTFOUFhvc1p6dmlFamZRak1ndDYxd1l3ejg2WmJpLWY0ek5MQg?oc=5</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>46017.29166666666</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Vue Bromley to screen a packed Christmas weekend of classics and blockbusters - london-now.co.uk</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNS1FndnRnb2pITi1qblh5cEtUX0RhdE44S3ZES1EtRDE0Uk5IbE1tRjBIV29RdXVEWkpaNDlaNnRweWdSbV9iY1dZYzVYb1ZVemZpdkM0NnRyNllnazcyaXNkbU9EeHIxNXVMZmc0TENudVplSVpadGFOdElFYWdGQ3ZHbUhKa0plUGV4bGNjSWFjanpWSzFyNUVraXNoM3F6MEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46017.20833333334</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>UK snow maps show 13 counties to be hit as far south as London in Arctic blast - The Mirror</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 21:32:00 GMT</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE5RdDNWUmc1eTg3eHI1MmlFaEdQVzNLU3BuYzlLZmhtbW1qNXk2RVVKME1oNFBYNWZDWXpkdGJXdHF6d0gzWUlpVHBBSDdiT3h6akFJYjF4bEJFMVJkaXZnUmVjREVWdUc1S0x1d1FpMkFXRjBqX2FiTGRlONIBe0FVX3lxTE5RdDNWUmc1eTg3eHI1MmlFaEdQVzNLU3BuYzlLZmhtbW1qNXk2RVVKME1oNFBYNWZDWXpkdGJXdHF6d0gzWUlpVHBBSDdiT3h6akFJYjF4bEJFMVJkaXZnUmVjREVWdUc1S0x1d1FpMkFXRjBqX2FiTGRlOA?oc=5</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46016.89722222222</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>UK faces 739-mile snow storm 'lasting two days' with 13cm set to settle - Birmingham Live</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 06:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPLW42STFjN09zM1FxSm1EZzgzQUdrTFp5cV9tY0VvOXY3UFF2ZUFrR1hnbkJIbWVoeHBqNENGWERiVnM3YkZsLXRlNmxGZDRHQlhjNzJvWkloMms3dnhGSmczTmtPYm40RG90WHk0R0pxYXlQTkhPNl9kcDJ6QW9KajRHR0JIQzRrNko4WTBjaDg?oc=5</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46017.26736111111</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>King Charles pays homage to Bondi heroes in Christmas speech - AFR</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 22:11:00 GMT</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPNndTSEd2RHZORzl2eGlBMEpPY1NHcUdpVU1RZGttSkZmX1ZXZ0VuMHZmTExDdXhKVHZjMkFBbmZLTjVMd2VCVXBoQjBCVnVEeHc2SW9vSzlXQlR5SlVhaEtkNkM4RDFIWlZWTDEycmtBTTN1MFFpSm1tWE5aMi1TR2FYbjdjVlBOSjFzU282ZEZyZVFla2NvUWJ5aFhhemdnckpmVjM3UnNhRGpBM0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>46016.92430555556</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Call the Midwife icon gives huge marriage update after moving out of family home - The Mirror</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 21:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPYlhVTS0yQ3BMZ1hQS3pOZFNIa213VmdYZnlTOGxKVUZ2elZkMFdzQWEwM0F3cTI0ajFQV21BQWg5aGNVcHRUX2xXMVAwbmk2TG9YNmJObTZPbUJDV2kxSGo2cHRET2taelNZZVpwT1JlRnNVUnI3MXdfZmE3eEtpREUtMNIBgwFBVV95cUxPYlhVTS0yQ3BMZ1hQS3pOZFNIa213VmdYZnlTOGxKVUZ2elZkMFdzQWEwM0F3cTI0ajFQV21BQWg5aGNVcHRUX2xXMVAwbmk2TG9YNmJObTZPbUJDV2kxSGo2cHRET2taelNZZVpwT1JlRnNVUnI3MXdfZmE3eEtpREUtMA?oc=5</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>46016.88541666666</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Irrfan Khan’s health deteriorated while shooting Angrezi Medium, was in immense pain, reveals costume designer | Bollywood - Hindustan Times</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 03:18:09 GMT</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxQOGlRNDlIUlNGN0c1SUpfd1dxWnFLSmo5MzR5UDZqc2lPQkpPaGZGYXd6eTY5X1o2WEdhMEs5U1VXX0Fta2NaVmpyeTBpUzVtdlRpTE5FRFQwUU5IbkdMUXVfZGp1QnhpMEpfMHVvZGEzRWZ1aEgwOXU1NmRPR1VNOFRYZ1NnUV9MaFBlSkFnN3lmN3JEMjNETHdGYlI4Nl9oT1UyeDJZRjBQUnF1dndsb3l5WFZzVlNKQS10czR5SnRuQmNLbHdYT090a2RESk5hWTlWdFZwMC1HZ2V3bm5lc2lqdk56OXVxeFZBS2M2SWpJOWl2MzZkQ2dCaUpCcTM2dFpxSFBockNxT1BjSnJzYVJB0gGXAkFVX3lxTFA3MHhoaV9nbWFOR1lpRURxNUZFbHRqUWJNUWxTN0NSMjRZMnBiVVBKSW5KRWwzOENNdWFLOEdXci1FRWJZelk5ZjBybTgyV0hlcjB5VGNIWlAtODRqc0ZDeGlRQmFTRjB0YVcwc1VLYkdVanRfY2gxeUtfVW5UcnhaOTFXS1B5UnJUY21WQnFPWXZfMHMtdVF4NjFId1lpU0VWdGtkRVBzajBtdDc0YmtnN3hFUVJ6ZEhGZ01PeFdzZVBSZDd4SGVlc2xpT3RVUkJER2JLNk5OSWZrY2pST2VLWU01Y2RTbFNOd0x2ZGNkazRONF9pN2ZQSm1jdWtsR0tTczNITUd2UFhmNm1BUWhxUzFlSndYMA?oc=5</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46017.13760416667</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Festive joy for parents as Christmas Day babies born at Ireland's maternity hospitals - Irish Mirror</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 14:42:26 GMT</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNUlYwUV9TUGtfcjhKNFZxYi0tUlhSVVh3SWRiTWlkbU5EaUdhSlFLVnZuenRCVHN0N1RwTmxyWlRaQUdRNkhVS2dzblBUeUdmeTBsLVJ3Ym1aVVJkRnpkWGFuRVFHWU1rSXFsTk1uT2JJV3NSU2J3ekJZRVZUMkdGQWd4QWZGRkFEdktBVVB3UFhLUknSAZMBQVVfeXFMTVJWMFFfU1BrX3I4SjRWcWItLVJYUlVYd0lkYk1pZG1ORGlHYUpRS1Z2bnp0QlRzdDdUcE5sclpUWkFHUTZIVUtnc25QVHlHZnkwbC1Sd2JtWlVSZEZ6ZFhhbkVRR1lNa0lxbE5Nbk9iSVdzUlNid3pCWUVWVDJHRkFneEFmRkZBRHZLQVVQd1BYS1JJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46016.61280092593</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Bangladesh news highlights: Tarique Rahman meets Khaleda Zia after homecoming | World News - Hindustan Times</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 19:55:51 GMT</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdXFCNDYtTzRNWXNxbi1iNmdabkxZYTR3LXV6OXZtSXhsWTU0bXFNQS03UG1YQktpbzRHQktrZE5Lc1NBVVFJZEpGRWFjRFM3NU5XUUZrT3FBbVctY1hCZXJ5cmF6eWg0UXdfMDR1dVlHSENaZGM4bDVCWnNWV3dfdm5LWXJHMTBXVjktZ1cybk1MeU1tQXR4WVVDd2ZZYmlTaURDVWNwMTk5THhUaUU0NGxDVk1iYnVncnRTOS1JaThtbDd2SE8zdWpBUy1QQ2tNNE42YXdrX2swbHZxbTljNHdYR2hWMHZHZGFlWi1obXYwN3dn0gH6AUFVX3lxTE9ld1I0d0ZGQTZvSGllMktSUkVzZFg1eGQ5dm1GanNHVVhPSy1SQjEzeWZ1NGlNakJSczRFb2UtX05LUjNvQWRMMVhhdEFSRzNRb0FEVFFwTHNWaFhsRGR2N2IyY3VBZjNLVzI5VktOeG9lVEZCVlBkN0ZRdmpoNWJtR3RWTTFrSUlSdFRuVmNyYjZ6aS1PWlZ5QWVUUWVYelVoN1lKUm9iel93SG5wLU15STFQeFFrVUxscnZJX1ZybTc0eVJSUzBrNmFsT19ITkphQ21ma1pEem5XMVZ3cmowTjMyVFNLb0RzMmxYVEQwSGtBX0duZnNPd2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>46016.83045138889</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Woman in her 80s dies on Christmas Day after 'serious assault' in UK market town - Daily Express</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 16:19:00 GMT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQbURheXYzRUZTSzVMc1pGdFRMbFE1SFZpQWppNFVvWDlWSDNsNVlSOUxPWmRsTU84VEFxRmdTbHhvS1VpYlp1Qks0RG5WUVNDY1JLb0FMUmMtQ3F1SXdXRmxJZVFnamU5NzlOOUJheWUtRXE0UVR6Z0V1bUJuWThKdzBweDhpQXFTMWdkZjBnZ0NWbGPSAZgBQVVfeXFMTUg5QjFwbDlKTTR6Qm1xTi1DNVpVYWdWeTFuLWQ3U1RYSGdUOWFOU21HdndjZUppbVpXbVJyNXlrZFNIakJCZVAxSXlMS1ExcDQzckw1LVAyeUs2MzZ4NGNtUXJ1VWttbE5pdlhuYmFOZV8wOGVQR2NuTDFlUWd4VGxIREY3MFJWOHdpUHpRQ2JHSlhhSzExeVY?oc=5</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46016.67986111111</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>All Koreans want for Christmas is a better cake - Nation Thailand</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 02:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE8tQXhhT1BYcEhIVDJ6dkc1N3NPa0dUaEF4Z1g2cGRGVjRSc3BYVDBQTzZIQnk4eTVIc3M0TE1IME1NQnV4LUd4OVFzU2M4eTZmTEZIZi1fUW1RNGJucDQxMjRhMnhaUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46017.08819444444</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Lily Collins On Her Struggles Filming Emily In Paris As New Mom - News18</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 04:55:04 GMT</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOa3AwMlRQTFpJcjNsVWpTaDg4bzVOWHhGZTllMFI1RWZfWlF0akNlX0d3NEkxeWFaamQ2ZjlXNVZUdnVZVDc3MTM0aUItOUhqUVhkdUo3ZEdxVDFvN1BoUEo5R1RSMC1HN2dzTEdkQ1lUVkdzSmZnV3ZCV3lrYWVhNjdyU3ZqSE5vS0diME4xVlA5cUQxNC1FTjM2QWhjZ2gyN1dqQ2xYazlhb0hPYXc0b3FaT0Q2cU0tcDA00gHAAUFVX3lxTE00MmhNLVVnbGFIcXhUR19qOUthenl5aWhENlZwWWliVlNfc20yYktQNGVyeWZVWUk3NURIYkZmdjZwcExfOVZ6cEFRVTBaUXpkX3ZZUi0xby12MV9zM2VPWUtZdWlQMWVON0MtY1c1Ql8xV2dzMHFETms1bjQxWE1GaWk3djZWUjk4Z0hNNDR5WnJ3RWU1NEp2cHAzZi1QZThVdWVscFFjTHRYN3N5U0ZnZi1hMEgzSlgzRk5QS1hCWg?oc=5</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>46017.20490740741</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2025: Her Year – How Paris Olympics setback is fuelling boxer Preeti Pawar - The Indian Express</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 03:16:18 GMT</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQdDUtSUtrelB1S0c4OWxSSU85X1FWdUp6ZGJ2UXQ0ckhqbTY5REVuLU9PMnJGWjVCTUZFVGNGVl9YVW9aTjlndEJxRGNNcW9nNEI0ZTA5c3BkaVVHNVBEQzVOTHVqNVduN3FoaFk1bFdxWFp3dC1XbDBHZ19vcHNsUENGRnE2eXphQUUzTUJlcml2bzFKRGdhZWhDN3lHZ2xselE4d1ZEb09BLVNscEpGWmp5YzFnYllIbWww0gHCAUFVX3lxTE1YMjdINFdKVHM2Rm1hMlVjVHQ5TGJ4czhYekh1cXdLT2t4SWxJTTN3aURQbnNoWUhPUEdRY3otSDNGQWQ4a19ZU2k4WklBU1lEX3gwUThnRlFWVFQ3cGhhcFFMUlRUMkwxRUNNQTFtOXZCVmh3ZmxqMm5oMzZEV3E2X2laRk9teG1BcndaanZLOERsbXFjX3FkSzVwbGRkMGJxaWp3MHh5MVB1c0hhTW4wb3lydTEzc1BQMFZSYmVtaU1B?oc=5</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>46017.13631944444</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Zenith Drugs Ltd: Hidden Pharma Star Poised for Explosive Growth - Price Momentum Alerts &amp; Budget Friendly Portfolio Growth - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 04:07:01 GMT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQWXBrdXJxVWFrcGtuUk1aMklLRWJTQkFKSkpyQkl2YUw4bEVibWJPWnVQRC1YQWlEak1weEEwOVM3cFItZER2SWdtZmJhQjN5NmJJaXlzd3ZwRDFpb3RnTENQb2xUYjhTekg4b2wwT3JHODJUcGxoQU5lUGxwMlE5WE5uODBmZHBXREV1NnBLTlRDLXZvSVZrV08zY3dUVFZn?oc=5</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46017.17153935185</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SoCal mother and 2-year-old daughter who were living in car surprised with fully furnished apartment - ABC7 Los Angeles</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 18:25:46 GMT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxORHYzWG1UcnItR1FBRXBsMHV0NnhCaDRXQmlrNmxTQXFJSEdMNFpMdElmb0pyUDNLVm1XLXhHRXRyVTN6SWwzeGNYZWNfTkp2VVdNSGR0eDd6a1J0SGZwa3Z2ZGs3Rng5SVYzbm9xbVZva2l4WFZiVWVZQzFVdGJQS3BGem1od0xta0xVbmgzY1Bhc3BYSWJ0WTRQOWVCTm5VQTJfQjYtalE1QUFGZVFZaWFrbU1vanPSAbwBQVVfeXFMT3FjT3JCazVVS2ZILW51dGE0ZTRHYzdBbGpoZlhHSUYwSWZ4b19RUzBSZDFaQjBJUng5emlaSXlkbTYxWjIxNHZDWUZOaVdwMFNlWUxtM202eGZiZXlYb1dVTFdzUmoyd2prLThmVndmY25hVXlWOHRwR1QxOFlaZkxVb0JXX1FNbTA5ZnFPMW1SMkJMdkVzSGNYT3RqdElDajYxLWxXVkZhZVlDS1N6bEdxTGZLdTRrcll0UnY?oc=5</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46016.76789351852</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Following the Bondi attacks, a US rabbi’s plea to the Australian government - SBS Australia</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 05:04:48 GMT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUjNYRlVOUWFfQTFsLUhzY2RrRG1qbUFLSE55WkFrLTNFeTZReTRwU0lvOVc1bFl4TDdaZUhzMjM0R3JZUEdvQ3JibzNlTG1weXZyYUw4bUZ5NDdiUnd2UnQ3c0hhNndsdnBPWXY5MjZMT2prR0tsTHR6bC1CUFF5RjVfanZidFFGTzNEUGVBSE8zQTlkOGJVUmdZRmhIUDVyZHMwYmVfMXdSMjRPazVDN1dlUXBrMFlBcWRHOGgxZVA4YWk4SE00Q2FDSnoyamR6ZF81WTR6TzY?oc=5</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>46017.21166666667</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Mehuli Ghosh Interview: Arjuna Award Nomination, Asian Games 2026, Road to LA28 and more - Sports News Portal</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 04:48:04 GMT</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQZXVDRlBXY1VtWHdvNUQwUWE4ZkM3ZnQxWjFnZm5IMGwwLXc2TFdldjllSWtEVV8yZ09DbXRkMkhYakxKcGtIR1d3bktPclNQeklLbllFOWNJY0JtTVRaWTh1NV9GNU1ITm9sSEdtbUY2OHpVNlRwb2pCZ2hWcmwxMV9XNTNEdW9FdUQ4OWY3SzZnSEV2ZFAxYjNSN2k4eXdMa00tZ2lKc3ZuRDjSAbMBQVVfeXFMTTR5OTJQTUJiM3Baa0lsUmlkc2tnNVJzQklhTzg0dHBGR2VOTjFDSXRFNlpJRFRFemQ2ZFM4ckNYZEJqX1kzME1TWXNDRDVMajd1QWV6QUsxUmxnQm5YYzBRWlhTRUtwNlNaaENsU3BuZHlqaDVnczBycFZjQXRpUWR0SVZ2SXFTMFJudmFpb2RkQmx6dkxTb0NjMWoyRlhvaU9KVHd0OUlRYVgybWdRc0RXeVU?oc=5</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46017.2000462963</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Sentiment Tools Show Shift in Trader Mood on Mayank Cattle Food Limited - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 05:40:04 GMT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNS2pkNHhqRVdHNENkWXRXNGdhZS1qMGlWcTNwbEE5MUlQb2RlLWZBdU1XMVh0eDlyMEtoSE1UVG80UGlDRjlKVXNJV3NERTlyRWtMNkR4cThPbUtMRExGT3B5N1liVDdPZjhwUVlmLVdHcUJqemlkRndGa0xQcUNIaEhXLWVqak5rRnNGUEd0UmwycmRtSW1OMlplZ2dKWkM4UkJISjN1dWl0Qm84MTFnelgwRzI?oc=5</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>46017.23615740741</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Used when: Market is flat or expected to stay in a range. - Dividend Aristocrats List &amp; Free Explosive Wealth Accumulation - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 23:32:47 GMT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPcGJsZkVRTHlkWUxkMzBiMnJFc29rbkUwVnJuOC1NUmg5SlRQTi1XTkszZ1I5czRQcXRLRUFwZWdCTlk2cDBkWTlBTW9FdVdQSTZueUtwZzRlLWJmOFc3U3NYeVl1ODFDSlNuaVRzakx6SW0wSDhHQ0VLbjBJNnFIYXFvNHp0UmZYb2hYOFQ4MENGcmZFZkZNR25nb0pEZ3E3aGc?oc=5</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>46016.98109953704</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Earnings Chart Overlay Points to Bafna Pharmaceuticals Limited Upside - Earnings Beat Highlights &amp; Free Rapid Return Acceleration - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 01:14:23 GMT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPZ2VJRG40VUtCYVdSRkE0akxqTlBoVk5kZmhsZ21HNXJfUnBZendVNmdlWnBVY2NxLXlCMWgweUdYbEhObVl0OENlV0p1dEJNaVRZZUJFMmRpZDdUWWl5V201QUtxdjZVSllmVktFclZyVmowd2hoYWxaWVVZVFBkSkM1NDNJcTZKd3hXOVBKTVJNNXlmaFlMcG9xVDBtZnowMmVlTnYteWRMenhVRmNCOTZR?oc=5</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46017.05165509259</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Is Sakuma Exports Limited Starting a New Uptrend - Retail Trading Trends &amp; Capitalize on Stocks with Explosive Potential - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 17:59:20 GMT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOTFhmQ216UnppQV8zTlgyNkhRVm1Fd2ItdkZIYXUwZWd0ajUtV0NEb3VUdmlKU25PTkMzaEgyT2FwNkpnLWVlS0gtZkxBUWJrSWdlR0JBZ25mUW8yLXNNZzN2SS1uby1meU4wZkpKU2Nid0tqY2NEdldYNDA0TXMtT1JhbU9LMmFwZ2RNZzlFdl9STHdEaHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46016.74953703704</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Honeywell Automation India Limited (HONAUT) Announces Strategic Shift - Stock Liquidity Analysis &amp; High Yield Stock Picks - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 22:53:53 GMT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeUg0NUpqQ0NxQlNCVmhsV0lDR2pVNzVXdGoyRE52aGg3UnVTdkNFeVRjQlAta2duUW1adi1pb2tJNXhrX1BGa0s1U0NXdl9qWmpJOEdURE90UVFvYzVGb19WdVFWRmV0SFVLMlJDWFhaWE1oMlkxd2tlR0lkYjRBdU5iOTItTWdPc0NYWDlVbUM3czRmVV9wNXQ1UVQyMm40TTB4YjFPTDBsMkZtTGxUSnhaWXBWekZRLTgw?oc=5</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46016.95408564815</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Pacific Industries Limited (523483) Expands into New Market - Volume Profile Analysis &amp; Interactive Charts for Smarter Trading - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 16:58:49 GMT</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOMTg1YjRmdDg0alFIRG4tZ2JSeXhYbVlkellOWGxGVXZOMFF3UUFONE5aMlRRQzJjYVZkbXNNV1lleXdGeVdTM09DVGl4Q1dRenoxdElzbUdMbVdmcmJWVUU0TDlaRlJRcXZvcWlFaHhTMEd1bE9kbE4tYU05bG5iUEF3eTdRZXRoUHVrVm9QN3l4OUNZLVhaNjJUSTJKZVRQMGZTdHJ3WEdxbHgyVkE?oc=5</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46016.70751157407</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Wyckoff Accumulation Phase Possible in Saboo Sodium Chloro Limited - Sector ETF Performance &amp; Rapid Portfolio Strategies - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 23:47:50 GMT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQQU8zR1g2Ulo1NWYxT1RJUnVjSm9BQ1NveFRMOG5LQ3hjd1FGNk1RRWotR25PbE84aDl2MUhZQjd1MUFCbXM0UGZIZzMxejRvcENMSC1VNTdiYldIUkVxWU9vWVFCMU8zZ2dCdU9WTWlUV0RkWDIyN3NCSXowTEZlOEVqa2oxUy1vbWlGRkhnd3VWVkdrbWt0WXFYTlJVOURvOTg0?oc=5</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>46016.99155092592</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>The Best Celebrity Memoirs To Add To Your TBR List -- Ranked By How Juicy They Are! - Perez Hilton</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1RTWZSYkdyNXk4LXN2OGRFOUpfdHFwQVJybWQ2eF9wTFB2TU85a1Y5UXdwV1pVcm1oQ1B0OENzMjlkbFpiVXpSTUczdC1lSldteE9rdU5lZWRjVnROVU1lQ0RxZVpVbnBYa3ZIdjFvVzFBYVVhZDlSY2ZR0gF_QVVfeXFMTnpDNVBXUHRFLWd0UlFjTW1ocmRzdkFkbFd2djlFVzdFRGlfeXNTLWFaQ1RERlJLa1JGYUZjZkNabVVENEFvX3hyVmxKVmdaVTYweHdwV2lfR2lBaG9hNUlvYmIyQ0ttc1djWjdPakk3SlpIOTk2UW1adHI2M0MyNA?oc=5</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>46016.66666666666</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Nanterre vs Paris – Preview &amp; Prediction (Dec. 26, 2025) - basketballsphere.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 15:35:34 GMT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNSHF3cno1S19mNV9rMS1DUHVaRy1sNUhkSGp6YTNtZHhPaXMwWXpyNWNOMGlKOUhnZU81LWU3M192M3FVR2twbFFtYlNYMHg3RWdJb0RJdFlQTEtGcmhTZGtxVENVV3owNE81VmFzcGEzNkx4Zmg2M0ozRmRhMlZQZHJkZVhTazE2?oc=5</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>46016.64969907407</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Can Diligent Industries Limited (531153) Maintain Its Valuation - Market Correction Analysis &amp; Budget Friendly Growth - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 04:14:18 GMT</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQNUpGak5DNmRsd1EwYktSaWdQSjZyNEVIb1BUWVFDTTBBTzFlUHp0ekJKNURNU0ZiZk5BMVNETFBjSlR2WnZSOHpkMHJZVEVtZmhZTmxKTUhRY2hSeDdTR05hZ1h6RUFEaURveTVqMVZGYTRFN3lSTVVaMlItSWVCSkpkN0lRNnZhdjNsc0FyZ0N4ZzlzN0ItaDZGR0VpUS1Yc3BzZXNfZFZJZWVjTkRDWnVCRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>46017.17659722222</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Can Traders Expect Breakout From IntraSoft Technologies Limited This Week - Dividend Reinvestment Plans &amp; Explosive Growth Opportunities - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 18:44:15 GMT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNLUZac1dDajROVjZiaklmaXV4YVZTZ0RicXEwTW80U25Eb3V0OGJJVDF6ZWFSQVdkbXdNY1pkbmFvSXFvX2VYZC1iRU5oel9FLU9JTjdVMDNVbWVDMnJrYTJCdEh3SW9kVzdyYUNOTE90UFk1OVktOHBwckJPaEpYcXhDZlhKanhIRGtJc0JraGQxREdnMnRiM2hRYVhGNi1MMVFQSUpEVXg3MlNV?oc=5</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>46016.78072916667</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Oriental Hotels Limited (ORIENTHOT) vs yyy - Candlestick Trading Patterns &amp; Explosive Capital Gains - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 14:53:44 GMT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQSkM2NzBpWklnZVB2TF9CNXZfb3VxdTdTTWFBRUtnel9lTi12d0lvaUp5WVhTMDRMVlBoRldzOGh2VGgxLUhmM2l3dS1Ocl9STnlmX3MycXhlcjdGekpNZ2tSMzZpYTRfal8wbHRTTHJ0SjBNQ0Y4RDk0YXVidldncjk2M0Q3V1BmUjhlN2NB?oc=5</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46016.62064814815</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Not Antoine Semenyo: Top three Liverpool targets to replace Mohamed Salah - LiverpoolWorld</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 19:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOdnZKNnUwejVEa1dzUHlWTlVFNkhvT1drTUVjSlB6dC1SNDNOYk9lelU1VUM0QXpETFlWc2stV1FCUWtiblVnYWhvRXdBa0tNWGVuSVZ6d2RvZVZLQ1JCbE5nak4tN3RCdnpnRlFmcUlGTFZ2MTVaWDVuYm5nMFpycTNudERYVXktbVRTek5RVVBWRm5FQk44dEg5OGI3eHl6V3QySTE1c0RDT0J6dzR6ZC1wMEVEdUU?oc=5</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46016.81180555555</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>From ports to streets: The spread of organised crime violence in Europe - belganewsagency.eu</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 06:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPVXNTdFRMcWtqeGp1NFItNXphNmQxZHlfdG4waHZYZlJ1SEEtZFMzQUdNTjlBUnAzcnhfYkhrZFJyMUtHM3IxZ1hZT3FaLWxxYklqQmdGRWhRQ1dIRzhUV3dNUlEwZ2tWZldMaG5pVk5zTmhLR2dkelhGNDVHM0R0UEFnUGxNRkUyejA5c1RkTVJpM1NYY1AxSTEtU09rRlpULUFZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46017.25</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Man shot by police in the centre of Bruges, leaving him critically injured - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 20:30:02 GMT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQdmxGOW9IRkxJbUJielFaRHB0NWM2MkdRVzFsMjhYY1NyYzNWOVdwdlU1YXFBcy0tRllvVTRiZUFVbUlab1NhOHpJWFk5bTFnTENxVzBUcnpCWm9PcVNQOFVtbVFSRHJocUlCRXptY3lJV2Fla3F4b05aa0Y1bVltelBhNW9vRTBOY2dDTGZyWGQ1cGpEeFpiRmdwQUlKcWxmdmlTbC1oc2VPS1ZVb1k0bg?oc=5</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>46016.85418981482</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Zelenskyy says he's open to creating demilitarized zone in Ukraine's industrial heartland - bastillepost.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 00:25:55 GMT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNRWNITnBlRVg5N2IzWGlQUE1USTVGYU55TzdxZVp6VmhqaDdvMEgxTEdia3R6S3lkblZaYTVMSkctMXNKYzRjM2FRRU9ORnc3bUtlajlELV92OXRERHEzOUdITmRiWjVSb3RTM0FzbWtxZkhQeVFJelIyNVJCV1cyczBJT3BDblpWQ01yMnpxM0cyU3YzYm1XTkppREh2akpqZjV5ckh5NkdSa0RJNTVNd0FJWjJvcXhNSE5yNHVYRi04NENwdFpmbmI0bWlZV0dBTE5mYW13?oc=5</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46017.01799768519</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Monika Kryemadhi: Brussels' number one condition, Edi Rama's departure - Balkanweb.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 17:20:25 GMT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPazNqYTJ1Y19EVFF2WDBZTmhNcGxMMmlFX0NLR0RkbWtKZVNzSWEwTmg5b1c4UVlEM0RLR1hCcTgxUTZELS11YWJ3UUdnNE5XZEFNUGNDQXI1SHdRdC1XTENpOFpJUXRTbnQ3ZEhxbThQdnZKRkI2d25oajhUR09MYzVaU1lMQ3VOUXlyU3p6b1R2NFhIZGllb3ZfOXRvQUZl?oc=5</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46016.72251157407</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>The European laws curbing big tech... and irking Trump - Kuwait Times</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 17:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxObm5VY2FYOHVDYWdERlFRRUduUk01LVVjUWljVVJHaVNnMllMNWFwQlpKZ2NUZUpUbmc2QnUxenk2YWRCby15U3pJVk1GemFTTV9UbmZlSkNBOURjaTh3STB2ME5DanFTVGptNmJMcVBFc1FxOElLSXVjbEpDRDNZX1kyMzcxX25WVWhqbXpTTkNrY2o5Q2ZlS0NpT185QnBSdWx0X9IBpAFBVV95cUxObm5VY2FYOHVDYWdERlFRRUduUk01LVVjUWljVVJHaVNnMllMNWFwQlpKZ2NUZUpUbmc2QnUxenk2YWRCby15U3pJVk1GemFTTV9UbmZlSkNBOURjaTh3STB2ME5DanFTVGptNmJMcVBFc1FxOElLSXVjbEpDRDNZX1kyMzcxX25WVWhqbXpTTkNrY2o5Q2ZlS0NpT185QnBSdWx0Xw?oc=5</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>46016.71458333333</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>How the Art Nouveau soul of Brussels was saved - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 14:34:23 GMT</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPeFFrVVFBNTZseVpvc0VhSmQxRllRUHJsckNFRGpJZ3FYd01NaWY0Mm9Kd2VnbU43SmNvV2FvUVZYMEJ3QmQwLXdEdGR0VWVIUzR4ejZLalM0aTIycVFUQzhxYTJkUm9aOHBwUWVWNXBNLXViaG5iMVVLanRXQ1gxVnFhSFpWQ3QtT3NPcE1aRDhyU2l4YzU4?oc=5</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46016.60721064815</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Local Town Searches  Maasmechelen Dutch Terms</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR boycott)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Two men killed in separate Christmas Eve crashes in Zwartsluis and Maasdijk - NL Times</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 15:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOaWY4cEhRaXBQNDhkTnlyMExXNXRScTNfZWtBelFTVGRvY2trMkJiay1ZcDRGejh5di1MdjR5WWhKdENvdmRYdzNsbmtHVVY3TGc3MGtuVlY0bTVobGduUVIyOVhYT1hvUjhCbmxzWWtRUHlWRGV6WWpXaWtqaXlHMjZUQXQzYUhrSTRuanRqYTdVY0hhY2c1QnV5Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>46016.64236111111</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Local Town Searches Wertheim German Terms</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>("Wertheim" OR "Wurzburg" OR "Aschaffenburg") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR boycott)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Wurzburg vs Trier – Preview &amp; Prediction (Dec. 26, 2025) - basketballsphere.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 15:37:24 GMT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOVFd3SVlmbXRxeUpUdHVKc1FHdlZ3S3lzTEpSOU9Rc2preGs4MkdGQll2Nmk2ZFd6dGVVb1FNRzFlMmR3cmlyLWt1RFBFNDZ2XzRtQ2sxbWIycTFuU0JGbThpQ3diX1UxelNVTlByYXlEdlEtYThPYXFqbGJhUFNkTnBKcXV3a1Ri?oc=5</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>46016.65097222223</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Audio Amplifier Testing with an Oscilloscope: Roberto Armani on Square Waves and Bode Plots - Elektor Magazine</t>
+          <t>How Louis Vuitton’s monogram monopolised the world - Financial Times</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 12:00:00 GMT</t>
+          <t>Tue, 30 Dec 2025 07:00:29 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9jQXI0ZlI2N2x4VFUycDJvdElaMG5mTHc4czZfQVEyYTB6bWplbnFYa0V2TENaLVp3WXV5MnpGY2FyOVJKTEwyQ2x5aVU1eVAwQS1Ydm1oeTdzLS1CeHJZaW1yc3pPOXdQbDduQg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1lQjBoVXpNT0FLemF2WVZON2VDaS0xQ1hodE1fSVo5eXBRaDRNa2VNNGg4elNYRWk3dmxpNF9zQ0d6bWRBbXI3SGp5Z3lNM2hBT19oX21FQXFnMFB1LWI4NGNJa2F3aWVXQ0JrN2pMc28?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46020.5</v>
+        <v>46021.29200231482</v>
       </c>
     </row>
     <row r="3">
@@ -515,24 +515,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dior Beauty hits update on Addict franchise - Luxury Daily</t>
+          <t>Celebrities Love Louis Vuitton's Classic Monogram Bags, Here's The 19 Most Iconic Looks Of All Time - ELLE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 13:25:50 GMT</t>
+          <t>Tue, 30 Dec 2025 08:00:41 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9ZT0Y1aHBRYXROTFFFMzRiNjJKWTdibklXdC04cnlzaGphRUJIcTFndm1YbFpUWEtJREw0TFpLNENoR0U1U1dJRTh0Qnd1TmJla01KdzZMZWdCM3c4LWM1Rjh2V25DQVRWaXA5Q0JDWXZPYUdBcHFHUGJrd2Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOeTFPWlJQU3dVT1MtbjBiRm1PbTUxM2VENEg4VkRnWS1RakZJdXp2X1hna3dLNVpySTRBQlk3SUZ2NURuMm1PTUNXeGNKZW9CQTc1a2ZvZkY3eElheWdKdkwtNG80RlRhSGtGbjZZZUt4VXVPUkRjUWdfWVJhbTRCajA1LU9nV2VxdW5nb0JTTVZFNjBLS0Nlbw?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46020.55960648148</v>
+        <v>46021.33380787037</v>
       </c>
     </row>
     <row r="4">
@@ -548,24 +548,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>How Après-Ski Style Became One of Fashion's Most Enduring Trends - W Magazine</t>
+          <t>Valentino Rossi is in ‘never-ending discussions’ to take VR46 to Aprilia rival in 2027 - motogpnews.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 13:00:25 GMT</t>
+          <t>Tue, 30 Dec 2025 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5kUGpBblRmRzdncWdMVDdXOVVvNlhWX0JNeF9wNklrVURvU1VsT0tTaUdrWUd6cjY4UkZsdU96UmRoNTNfRGlEVUxBeWQwYm42b1lOWEFxYUFqZXVXdExueGlqZ0gwanNFNXozekx5ZmZrZVQzcEhYMEdB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOSVJtM3l0Ym8zZXZwWF85UXhxdkF6Tlhxd2c4MTRvNFlBVXpWQ05RUEFEMXp4VmgyTC1VNTNzby1zWks5VEhaS2RvcnVRenRZZ0pRVm9iYUlkQnlVZWVUaWlkMlpGa1RtSFpFMVhBSWtjYUtCRl9MSFJFOEJZYjNuVHBVdE1XdFY1MkFDUWxVOEZubTQ1TXJZbHpBcnU3UHdzVUttRVhZdk9GY3Bxc1pnNzF2VnI3NjhCQUhxcGN4ako?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46020.54195601852</v>
+        <v>46021.33333333334</v>
       </c>
     </row>
     <row r="5">
@@ -581,24 +581,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The Fortunate Ones - V Magazine</t>
+          <t>Armani Casa expands in Shenzhen - IFDM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 13:00:00 GMT</t>
+          <t>Tue, 30 Dec 2025 08:00:24 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1hMVhKX1dUaGVncV9PV3g4OURCZV83VkZsTi1VcE9xSDIyU1NWNEk2eE5mZndzQzVEWk92SGZocDlvY2ZFLWN6TlJ1c2wwQTBHSWs0MzZHa2VOamJuZlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9aR3VTM25MZkRKdkRwY094YU5EdmhSWkdXQ3VFZHJZVy11dzhxeFBGaHdid2k4cHh0SkR2ZDNnZjFOaE0xOGFrZmw5UnFDMFJEcjdJckQ3YzY2NUZndjRDZjFUazVHRUxtSUE2bjJoM00?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46020.54166666666</v>
+        <v>46021.33361111111</v>
       </c>
     </row>
     <row r="6">
@@ -614,2037 +614,5040 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kylie Jenner Flaunts $57K Cartier Jewelry for Christmas Celebrations - theFashionSpot</t>
+          <t>From Jonathan Anderson’s Dior to Grace Wales Bonner: The fashion shows that defined 2025 - Monocle</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 10:33:34 GMT</t>
+          <t>Mon, 29 Dec 2025 20:03:09 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQUkxmTlpZQXpLT0M5X3ZlcG9sV3VYWG82OXpBaWFNLV92cjZZMWJkR1lZR184VngxcEJJYWd6WHlkWUhpNnRVWFBLZkNtSFVYenNHRC1KMWc4b0l4VFgwVjNkdGh0QjNybU1vNDhTZGh1NGJJUnBpMmtBUllYNGFTZ25La3FvNzJGNkxWSkI2TUR1ZGFSWGs3clc3c1pFZmlnSGlZQ3NSdG9FcC1qQUhOWldiWEfSAboBQVVfeXFMTzd2T1dhM0JOdVI5bWNNTjZ5RUVPS01jdlAyVnlXZnM5ZGdzVy1lci1TZGtncnBWTHlhUDNzR0JPd29RM0pIbUtsbkthM3lHbW5pQTRvZUN6b2hDX0t6NllnWjlIVnZrZlhVS1YwWTUxSDF3ZzB1LVd2cU9aUWltV1lVYUtlSmlybjQ5WTczcWpJSjU0cFpQel82bVdCQ0wyMzA5MkNGdGlQSmtGQ1RzaFN2YzJJd0N0VGR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFAxdkhxOUZFUktKTDRjbjBDOWJITGNVQmJlamEzQ29mSGhKWm9KemdtOGgwWDdPdmxVY24xV2F2dFVhdk5HU3pOX2hsNV9sUXMwRGR2Ql96SDd3MmwwNGRDdHNaaTg?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46020.43997685185</v>
+        <v>46020.83552083333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>London Marylebone</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>("marylebone station" OR "london Marylebone") AND ("incident" OR "delay" OR "closed" OR "delays" OR "protest" OR "boycott" OR "bomb" OR "Bomb threat" OR "shooting" OR "explosion" OR "stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>One dead after incident on Oxford-bound train - Herald Series</t>
+          <t>Murder most stylish! Mia McKenna-Bruce dazzles in Dior on the February issue of Tatler as she stars in ‘Agatha Christie for the next generation’ - Tatler</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 10:23:29 GMT</t>
+          <t>Tue, 30 Dec 2025 00:01:00 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQdkgwd1RwTFQ1U2Z4aml0RndTSUhPOU1kemxBaFU5UXJDZFdYanRSb2NGS1RFbk5OTjZLcVBMQlBXZUl2UjhKMURFelk3Qm8tMFFySFpCU3RkVWppVHQ1dkpKMFdvTEFmZ2Z2THlScGc4ZVV0alRyczNtRlA4MEJZMDVzS2FJclVya2RaSWY1UU54R2tPRFVBeC1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9JLXZoYUV3V1czRVRPajNLaHJOYmI5VEVVSVhpdFhIUGFudEdZZGpDRFhJUGNJUzJGV21QejN3eWhCWkNvMzNSTFY4a3RrYXpWb2Y5VDMtYW93THp4SWdURktVQVNQclJ0dGpsMW1VT1NRb1JuYmZBYk90amVGdw?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46020.43297453703</v>
+        <v>46021.00069444445</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Delivery start-ups finally get the K-shaped economy they need - Financial Times</t>
+          <t>Osaka: Gucci Giardino bar opening - superfuture</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 13:11:13 GMT</t>
+          <t>Mon, 29 Dec 2025 22:46:49 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE91c3FzS2xxVnMyYThndTl0UzRLT2k1S3RxYnhFTGppY2NNLVRMX090WWhuWjFXY0V6X0NXU0dac1ptcWJ5YkRlV280RnFKNlJWZFBDd1dXS09ib0g0d2RLaTlkMDBROFlMcFZiNnRLVUI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOSGZ5M01aeWhKcUp5WlB3aFdvUUNnYm5qTHZNT2dQOElQR2IzWTk2YmtSWko2OENnTEUzdEE0RlVmLWJCYnFScDNMN1dQT3lrZXRDUmt0RzZfTzNFYmJvQU1jcHdqUE1GaXVDUjZGU0VGWWc5Q1VZNnJKNnJiUThkWnFQUGwybkxrMk5NTl9QTQ?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46020.54945601852</v>
+        <v>46020.94917824074</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amazon shelves commercial drone delivery roll-out in Italy after review - Retail Insight Network</t>
+          <t>Top 10 global luxury brands in 2025: Chanel overtakes Louis Vuitton after 45% jump in brand value - The Indian Express</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 12:29:10 GMT</t>
+          <t>Tue, 30 Dec 2025 07:43:32 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOSHFhQWh6b0pmb3JYaHF2S0k1TmgzWUdvNndudGE1bEpjRmp1WnNDd2JnTnZTV1pUMjlldXNhVFktT29UdEpodmhVWFpURVRLdFlGclhYdjJRaWZwZ2dkd3IxYUQ4VlZPYkxEQTFYaGxrRlJDX1VQX0hadnpkazNxamk2SzR2eEdkWDZEQlFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOdkhFd01yRk5KLXZwamRiNVRkZmhXbW1QVGRFOXZkYlprMXFGU1lHS0toTnJWNWYyc3ItcGhYYzh5VHptcnJTeG91YmZ0TVVvd0FycjREN0VVdDJrdk5RaV9pQXBib0dhcWRMcEh2bUpmMEdRY2I0em0zRy12SkI0dzVQRXVWdkdhOUpvT29NVDlrNlk4cENRel9mTU5MbWRtWFZmdW14aHp6Yzg5NW9PbXNR0gG4AUFVX3lxTFBQUFVKSXdUV3NyNzVEVkNLR043NHJON0IzQUhtUkdZMGtQZG1vUlZhcVphZE13RllsUWFHb1J6ZzNZdHFKd2lpblZJRDQ1QkVSbjlrSk5ZUWdmTDRDT0ViSEdJNXFzX3JvUXNFSFlJZTRMNXlmRElDNk93ZjZ4cy1nQUxjWnlYVkhvektiQmE5OU1wQkRLUFpld1VoZXpEQlhaNl8yR3huVFVHZFZyU0JDQUZqVFU1R1I?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46020.52025462963</v>
+        <v>46021.32189814815</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Siemens Mobility signs contract with DHL Supply Chain - Logistics Manager</t>
+          <t>Christian Dior's (EPA:CDI) investors will be pleased with their favorable 43% return over the last five years - simplywall.st</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 09:06:45 GMT</t>
+          <t>Tue, 30 Dec 2025 04:21:34 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNVi1yNHQ0YjZYZkVLdFBNcElsaXBva3h3TVJQTGlRT0puRXVWQjFoYVQwQXF3MmpXMFhrZ1BUWTdHcDhCaVhjZjA3WmFJNlJOUTlyUnFUNTZ6UmoxSUVoMUVkWmVDM2w0VV9UbTV5Znp6eG5tR08wU1YtanZOOEFnTWZtSTNmcDlzeDdod251TDY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPTXYwaFozQlJCejE5X1FyeDFKckFfM2g1MDl0c2FmdzBIbzFEMEhRSGZTNHpocUJrdlhwNHBWeWE5dE9Gd1pFd3NkMklNeURQaVJhUU8yX3BwbExIeEVVLXJvajlmckNablBVcEFybnNjTXN4QXdrNVZFa2xETnhOOE0xVTI1RDM0bTZVUXpGWHA5ZE9IM3MzVXJoc01UaHJleG5sWENKa0RDMElrQTNrY242SFVXMkExdW83cnl2U3FsN2Q3YVVUT2QtVmF5WVFSdUhMNE14RXh1SlVf0gHiAUFVX3lxTE8tMnFoc1hOWWZENnM1RHZNTFhEc3dVd3lPZmJpRXY0bFd6MzdBMXRmQUJxb3Ewb3hPclhnOHlXZVhkdE5CT09rQm00c0lOLTBNd2RQTjltUGJVQWNWQWp3bzNkNWpyRHVvbEFRSjNudWM3a3FESzBjcXczS2h1N3VsU201alJZSTZZWHRIWHZDTjd4VkFyczJrd3NxYjc1LXloT2NJaGxIemZkS2VIdzljcjNMLWFkV09zeXRxWUtweVYwc1RVek00REg5WW5jb0dOcG5DLWk4MzBmQ0tkM1FFSkE?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46020.3796875</v>
+        <v>46021.18164351852</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Here's how to quickly tell if your Amazon order will arrive by Christmas - AOL.com</t>
+          <t>MAISON VALENTINO PRESENTS THE SECOND CHAPTER OF THE VALENTINO GARAVANI DEVAIN DIGITAL CREATIVE PROJECT – ANNIE COLLINGE - vanityteen.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 10:27:54 GMT</t>
+          <t>Mon, 29 Dec 2025 14:59:06 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOVFZNYXZDbmZpaWljejRYMGJ0MFBhck51SmNKWTVqSDE1X2RLSmtOazN1cVg4YTJ1VkppdFQ5TFp1ckl4TERTbTRaOFlOLW5TMk04YTBSSWZ6YS14X3dVUVdNQ3RCVmZmTG91ampocW84NzdtcUdQbDh4XzBMSDZXVVo1QTRuelFMeGNOajBQNlotWDE3ZWwwUWxxN2RoUy1SWk1Qc0V5dGVuVFdlT2UyajZ6Zklaa0VQbmpLTU1vYXRpNGRpWGpmR3h5cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNeEh3QVhIazBqMDZkbVJqMlZrTDl1akhWM3RiTkhEaG9BUE80ZUtRN3RxcFRMZTV6RFZETnI3SXZLeDRBX0JFTTN5c29oMmYtRldvb3l4RnAwWkdoWU00YktqcHd1UndYZnlOa0JTd2I4ZlRSYk1wZVF5T2habS1uSTgyM095TDFDQ3JaZzItM0JCeERaMW5wYzYxRlNOY3FWd05oeWZDbFoxaVpZamJqWm41R0w3REFGaHRqZ25zTTQ5cVRTRnBET1RscENlTDVnMTRIUVFGVS1NbFpJN2c?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46020.43604166667</v>
+        <v>46020.624375</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Delivery workers linked to Zomato, Swiggy, Zepto, Blinkit, Amazon and Flipkart, have announced a nationwide strike on December 31, 2025. The strike follows a similar nationwide protest on Christmas Day, December 25, over the same set of demands. Worke - instagram.com</t>
+          <t>Blush-Inspired Perfumes - Trend Hunter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 09:21:55 GMT</t>
+          <t>Mon, 29 Dec 2025 18:15:41 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTFAzRDEzRlF2cm1LZmNxcWhIaTRDSUUxRzRMa013VnBKeVJRblYxX09Xa3BudVlLcnB6cERTRFl2WHV0YUFwQ2pWQmxfNTBqM3MtM0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE5zcFVJVVBITkNFUlZHRUQ5T2VmWTRLNjZib29seDFDWU83ay1DMXVtZ1phZEswV2RVWnZIUXNzZGFQRWpiRnVFTE5QS2ZZRG1samxCVEhkQnBWSzc0YlZPVtIBZkFVX3lxTFBVNU01NXlKVEZ6aHJ1S2ZIclctSlVlNlRlUG51bzdHVmtLdFJMWjVyTzBCcVhmWXFKbk1zUnJtYkExMUs1VWdKLWpDN2Y2T3dUQ2NnV2RaNXltbHNHekJ4c2tZZ1cyQQ?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46020.39021990741</v>
+        <v>46020.7608912037</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bayern Munich starlet Lennart Karl garners praise from legend Thomas Müller - Bavarian Football Works</t>
+          <t>Jisoo, Anya Taylor-Joy, and Willow Smith are the Faces of New Dior Addict Fragrances - L'Officiel Philippines</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 09:30:00 GMT</t>
+          <t>Tue, 30 Dec 2025 01:16:52 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxONzVoZV9SMGxfcTB0XzFXcklvR20xWlNidGVrVFFXbTdtX2lMZ0xTeGpFTjVhU2tHYkNCcFlCUHdIa1UwWlhpcVFyNldGQ1VZZzg3Y3BSSGhsbDN3bmhTVXNfQTI3S0VRU2FtQlg5azhLNjl6NS1mRm1kQW5GdFJJUkhjVW5BaERyQU0wclc2Nk1fUk83a3k3c1VQYnlmdTN1ZkpaVFVFWGVUeTh6anpjN1NWc3NIb1U3Uy11TkM3WUp2UEFEUTAwYnBXSzBqS3I3dEdweUYxQk0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPZXJ0UUtNcm5PZmt5cFpjZEdOVUNCdTJSdlpXckUtMlMxNVJlNjZ2U2hlX3cyM0dBOVFUdGdFcHZydENnazFlWUExSHZIYnB3SVUyRTVhLU9qdmVzT2VneUJZX3BzMjF6N0oteFFJUjd3MmdxUHJJTV9Yb2dzSVZkSlctYk9KSUxIYU55T29LM1ZhSlhKdVVTWmxKTkR1NzBQVHc?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46020.39583333334</v>
+        <v>46021.05337962963</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>The True Meaning of Support and Resistance - Price Momentum Alerts &amp; Market Analysis Tools You Can Trust - bollywoodhelpline.com</t>
+          <t>Kylie Jenner's $30,000 Christmas Jewelry Will Make You Purr - E! News</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 11:41:36 GMT</t>
+          <t>Mon, 29 Dec 2025 22:55:00 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNOTFieXVtUnJaaVlEYThhQ2ZIeS1WVm9VYk1BQTVtb212U0l3TWVYcUFrWUpfd3lYejcxcFdULURZSGc5Z3hNeVA1VExwcm4xMjltbkdmSW9McFg3MVU3bEJhSjZRSThZeGktWjladGlvVlo0QXE1ajVWcTNjdkRkNHBkNjJyMVJyMm9RQVFR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPSDZqM25wN0RzTUc4dEVROWlqdWJiZGFyU3dSRzllQlhTQm9UTkZEQ3dTTlN4VUxCNlRpVkdfVHVHRjVJQk5EWGo5VXVaNEFSUU5TcWR6ODAyNl9vQUlWc2p6LWlkX25DVmQySndEVmZidEVTV3V4RFo5TGxUTlUxX28xazdWRnhqQVgwY3d4MlRJRUU2SWdN?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46020.48722222223</v>
+        <v>46020.95486111111</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Manipulate price to create breakout traps. - Straddle and Strangle Trades &amp; Explosive Capital Growth Plans - bollywoodhelpline.com</t>
+          <t>Diddy’s Sons Justin and Christian Announce Docuseries Slated for 2026 - Variety</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 12:09:59 GMT</t>
+          <t>Mon, 29 Dec 2025 17:48:00 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOXzJRX19IVHRvNzJKWW5WMGVnbXM1eHI1MldKRERsREo3bDh6U3pJWTB0X2YtSzNPU1pVMGc2MmxXNHNCcDc2ekJENndSTHNHb1FkN01qNWVfNW5PY0YxWUFsb25FT1Y3UjFrelJJOHpZb3FMdk9JSnItNWNkMjM0blJtYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQRFh1MEFCT3piMU1XSjhyR0RpeXRVeklGV09jLWpvdlNoM0RQMXNUZndVTXAzaDhKNk1CWVVOTXVHMEFDX3otNHR5TkdldUpva0xyT09mTW1lS2s2dndhMzdVb2lOYUszRHd0TjQzdTJackpPVktBMTJTcC1kWGMzRWtqTUU2VE9PeFMzZXo5YjJwb0UxR1RwY3ZjR0ZUQQ?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46020.50693287037</v>
+        <v>46020.74166666667</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Reversal Traders Monitor Benares Hotels Limited for Entry - Options Trading Strategies &amp; Explosive Growth Opportunities - bollywoodhelpline.com</t>
+          <t>How Product Roadmap Could Affect Transchem Limiteds Future Value - Retail Trading Trends &amp; High Return Wealth Building - earlytimes.in</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 11:57:22 GMT</t>
+          <t>Tue, 30 Dec 2025 02:14:42 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNaXNubUJ0bEZERnhlMnhQd3BFTmFpbUQ1QVJURjYtbktoRWFCUy03QW9wZXo0Q1BYM0FZYXIzRkN1Nnc1UDRUZE9RRk5QRWVxTTdhcE1oTHVWcGZnTW5haUZPX3pzMUJkOHNrM1ZXYXAxWUNoMXB4SUcxc0lsa2phcmVBSG9lYlRPS0xHcGIydllhLWFxbDItZGsxVFNfX3h0MVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPU3NGYVFUTzNyYThnLXZZWHdKc3JOY0VWUzFFNFdmWExGWklobHZLdHBxRmJndmY4dURvUVpVUTRJTHlrS240WlhrTnFzaTIyN1pucV9CNzR0bElFRHlYdmRmUnNRVDg2UEV5UkVpd3piRXFrc1p0OHJwZ285TDJzdlU3X3NGWjNjS215X1VrWjhNNjEzSzVYMXRxcFc?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46020.4981712963</v>
+        <v>46021.09354166667</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Will Autoline Industries Limited Hold Gains Into Close - Industrial Stocks Review &amp; Outperform With Our Smart Trading Calculator - bollywoodhelpline.com</t>
+          <t>B&amp;M European Value Retail (OTCMKTS:BMRRY) Shares Gap Up - Here's Why - MarketBeat</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 11:11:15 GMT</t>
+          <t>Mon, 29 Dec 2025 15:59:20 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOSTV3ay1ITnI3LXVhVWRWeVFTV1lCcEpMdFFEMVl2UHphcjBQZHVWdU9CNWlIZEhhSFJSNE1wcXNYc0stMFE3dm9tTnMxTXFKM2RUcE1jSm4xczcyTkUtQ1RkOFp0azRKUUowYmp0TGhCUDVHdnFRQUJ2djY2RTM0ZHdSQk44U2ZrN0VrMnRwOF9OLWpx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQOVZpUW5BbDc4dHJQTE9CWGdKZGxPaVpNOU5wUndOVU5TQlhwczdkLWJFYlZZZzJJakFQMDFLRkZlTU8wNXBESHktcTJCaVRFUnF6S2Z1Q2lNMFpxNk5ZdkdXRTdRUnNOdVo1b0Q2LUM0Y3dlWG41UEZjUFlqZjZyZ2JNUFc0RHA5Wm1xdFlDUEdOMlkyZDVMVkRnS09IZ3J1TWp4TzZ6NmdxWWt5UTJaS0VKSmVYZw?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46020.46614583334</v>
+        <v>46020.6662037037</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Are Bears Losing Grip on Mason Infratech Limited - Risk Adjusted Returns &amp; Free Explosive Return Secrets - bollywoodhelpline.com</t>
+          <t>U.K. shares higher at close of trade; Investing.com United Kingdom 100 up 0.04% By Investing.com - Investing.com UK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 09:14:55 GMT</t>
+          <t>Mon, 29 Dec 2025 17:42:49 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNX3JYUTQzOXdXTnFFY2RpdlJqcTc3Qkg2SG1sVHNHRU0yblFkd0FkN1hRTlpKbXpVOE9ET1AzUmY1bGVja1NPdjVhTWJHNnJTSVN5Ml9tNGtycU5lLTNDZ2pmMVFidk5ad1hYSHlmNlgxb0lwTXV4b2lsUGl5SDF2cnNGQXQwQTRGcGJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdWE5NkdQN2dnWGkyWUJoN0RoTUdqVVhGS2JIemlSUUdkYU42MFl4VWwtelFNcDRHcVNNc2FwNTd0R1Ffa2JVZ0pNNElWaHVKaGhZalh3YTJURTE1N2dyTmtPMFFXWlYweklTMDZ4cHpiVXZjVHpJSzFwbnNTb1ZIREN4MFJoNlJDZXBHcFBTbmpRVlo3YWktZzVSZVNCU3RNcTN1cHB1bW9Da01CZlEycUlreTF3RUVWVTFVTGozX0dIZjg0LXltZVduWXppWllWUmNicGhvaXA?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46020.38535879629</v>
+        <v>46020.73806712963</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>International Exposure: Diversified revenue streams from 67 countries - Institutional Buying Trends &amp; Outstanding Profit Investment - bollywoodhelpline.com</t>
+          <t>Korean Air raises Naver point conversion rate, reducing mileage accrual - CHOSUNBIZ - Chosunbiz</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 10:22:05 GMT</t>
+          <t>Tue, 30 Dec 2025 02:30:00 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNZkpfYzZnWXZDMlRKT2haNGRLRXo0Z0w1WG5Sbm1hWTV2NDVWQ2N4VWhLUmYtbTJvSnJobFZYLUZJOXczbW1wd3NqdzAyVHhxYTdQR2FSRjgzdFNrdDh1X0k5aXF1ZzNYV0tWanZ0X1M3RG1adUN6VjVlSnNuUG1Yc3djdkNkM1B0Z1JQblBxVkR1VjY2UVM3bkVoVEZHUXlpVkdWZVFzNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPMmFxSjZKZlpray05UVMwOEM3N3JDWlg2UnJFNGo0SXJzR1huN0J3bUpzV2pWcElWRExpc0hsMnJBOHhrd0ZzWFR6LUdybms5aC1VVGF1YVRqaEFvNGgyREd6MlJsdmRPOUxfRFdsNXV6YnhPbVlXS3Q1N09NWUtXSDln0gGWAUFVX3lxTE5jUTAybHZnQ3RNNmVMMzdLYXA5dDlLdy1ocTdmOEZMUDFIYzVPY2hIbHRPU1JrdlNxMWtja29aclFfajlVbFpKMHEzZVpKS19OdDczcGtyQVgwcTlMb0FYTm5DQ3ljTXVBVWluNkdXTVpXYUplYjhBYllIa0VCVFl1TjVpX2ZLOWQ3YjM5Yzg1cjFVNUw4QQ?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46020.43200231482</v>
+        <v>46021.10416666666</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Aurangabad Distillery Limited (AURDIS) Signs Major Deal - Insider Trading Activity &amp; Invest With Confidence - bollywoodhelpline.com</t>
+          <t>Amazon suspends drone delivery plans in Italy - RetailDetail EU</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 12:17:24 GMT</t>
+          <t>Mon, 29 Dec 2025 15:56:29 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQQUlKXzBVSnZnQU56YWxnbUJHSjJLRGJBR2Y5YzNlT2g3Q1FHZThXRmdaZ0FuV3Q0SUM0eHp5LTFVUEhvUmJybzFxYW5DRW9vZkxKVThyVUlHWFo2LXd4NU1hOURkX0tieGFhdFNWaTVGcjJ5c1VRMmlDN3psMHFEWk1Sa2Q4LVNneDBoVS1vVXFmWWs1UDZ6SGlWTXJMT1k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOSmpGVi1yMlhzMWlpaXNtQ3YyWWVJWU5OQzJBU0ktck16Q1Q5SXd4WV9uVXdMdVlCQ29qT0JCSkpLVHBxMlFQc3g3aWFvWm5Bc09fbFhVcjlJamg4NHdvZHRBRzNYNGV3UFlhRkVVelcza2VEUUVwTThnaXB5d3RJZG1ROWlhS2lrYm5UMk1pMHU?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46020.51208333333</v>
+        <v>46020.66422453704</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>‘Organised’ shoplifting gang operating in Fermanagh - The Fermanagh Herald</t>
+          <t>‘BS’ delivery guarantee promise sparks outrage as Amazon orders arrive late for Christmas - The US Sun</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 13:43:00 GMT</t>
+          <t>Mon, 29 Dec 2025 20:02:11 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOYUhRUkxobGpnUGtVcWhaRVE0VmNQUnJvT1o3c3VWNXkwbEZoS0ZUbEY1bzJpT3RKRURlNGVlOTM4amhJdUpFa0x4SmdBM1plZ2FaNDF2RU9BTWZ3VVFUeXdqVnpxWkVTMldELWVwODA2MzBtOWNYaTFEQS1fOVk4Y2dvX3pRY0RkVE1UdFFLNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPLV9JYXc4OGxhT3Z4VkFNYkhUNjhXa2lrTUs4TFFtd21oQ1NSUW5HR0VoSVBBOWNheWxFa3pfelpiTlRrV3U3S2d4Z0hSdW51cEdSQTJKMXB5aWRIU1lRRDlWbjRfdV94UmxCZk96YTV0STY1TzVrckJkZ3hiVm80T0pTMXd3R2N2a0F6cVRrS25NWTA?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46020.57152777778</v>
+        <v>46020.83484953704</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Worksop shop theft crackdown sees over 10 years of jailtime secured for offenders - Worksop Guardian</t>
+          <t>DHL Supply Chain Eyes Fleet of Tesla Semis - Transport Topics</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 11:42:00 GMT</t>
+          <t>Mon, 29 Dec 2025 17:32:08 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPWGxVRWwyeDI3WW1adEg0UUNQb3hpN3Y0ZV9jWUJuU2xsQURKdlhISlVVcG9BbEJSRzNnSGo5Z3I0Z2VZazhNOGZVYzZNSzRScW1OUGFCQmxtZUFpd1JDanhPYWNtMzdKSGJzNWJmV0N6WHloM2hjSktHb3BidGlnRmpUcW5EcUVTNWpYNHFvZDllcW9Id3lsWmFmRG1GMFQ3dUZEVy1xbGZaMjZnMmNVTUY3bk1lakRJbzJ5NHJtRC00UjJLc0gyUkF3czB6aEk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE8zSks3Nmp0ZDZRNGRNRzltZ3lTSERidkpPVVY2RnBqUjc4RjQ1OTVtN2V3Y1JSWkFMMk9PNVVMUjFfdGJwYzdZVVRwYndHbzdwdWJYUkkwam1NcW0zdFQ2WVRSMG5jSzl2NUVvUA?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46020.4875</v>
+        <v>46020.73064814815</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Prolific shoplifter Jason Christopher Evans jailed for series of thefts - The Purbeck Gazette</t>
+          <t>Aeromexico Cargo, Amazon Strengthen E-commerce Logistics - Mexico Business News</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 12:26:06 GMT</t>
+          <t>Mon, 29 Dec 2025 17:26:42 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQd211Y21oLXdBUXkwX0x6TElGUE43MkcxTFhyOE1aRWJ6WW45UVZnX0VvT21Ta3pod3dkU3BWbjZYM2doUlk2VXVWSklZYmhaOXFQUHAxdWNuYXJSVzF5S09YMTJIam1IdUZuMTVHMEdzUGhabFo0MFBwYnBIcXhiNXhieWZqbmViRTFQSm9XWE10VlRkRnJKSXU5Tm95ZmR0ZkpQelp4Smg0Um8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQbVdJalNMNXdiSUowRG9DbTlfM0lmQ2pwaTFuSXBjQTNfZ04tbGktalBocVhKZ2Z6bi04YXhCUnFQLThqRVVkQlBVZ2ZwUUpXODRKakhmNXdIYW1vcEgtRjlNQl9YQ2x6TDBhMUFYQ3pJOExVY1o1NGppRFhJaFMzdzQzV0xsVlJvdG0wb05FdlY0dzUtbmlPOHotSjdhSHc?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46020.518125</v>
+        <v>46020.726875</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Organized crime is a problem, and it's getting worse. | Opinion - The Palm Beach Post</t>
+          <t>UPS warns of shipping delays as plane crash halts package sorting at major hub - AOL.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 11:03:00 GMT</t>
+          <t>Tue, 30 Dec 2025 00:29:59 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOekkzRVhiUDBzbEdQYXVSMmNQb3JaU3lHS1FPdmV2N1MwanMySVM2d2dzclk0SklQS0tuSEhjYU42VkVTN3VncDJSTlYwZ29BQTNIaEdDUENKbk9oeTJ4RnNsazdmZlBRX1N1REF1Ny1WM0k1QUdRUURCQ01JQi1nUkY5RGtXMkFxQnlKenhFMnFNZUpyYVJnRFBGRkxubFZQM2xTaTJ3NlVGZG5XRTdTYkJfMzZNTjZmZjFBSXAydzlKeHNFblBLOHRZSHh5N19LYjQw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNUlFTejlFNldtYnpIUWlydlBkY0RHVlVweHVxajVSZDhZZmNQVm1QSnVlVWFtX0RZZFRNdDhZQ0laZHBXWkNzdk1wclRRS2lyZU16Y1podUlMcGxPMml5N1IwbDJnV3BodXVkZGk1Nm9YV1lhMFVTN1R3enoxS2ZhMQ?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46020.46041666667</v>
+        <v>46021.02082175926</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>QUIZ: What happened in 2025 across Barcelona and Catalonia? - Catalan News</t>
+          <t>‘If You Have A Package And You Know It’s On The Way…’: Ohio Amazon Driver Calls Out Homeowners For This Common Customer Behavior - BroBible</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 10:27:45 GMT</t>
+          <t>Mon, 29 Dec 2025 16:09:29 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1xVmNCSF9WRzJLenVHZ1kyZ09yVkdqNUhHRjFjNy0zb3phT0NoLWZubzF2MmsybDdnTjlRUU1pSVp2YlF4YmhGZ3g2YTNiakFNMHdWaWUxQ2c3cktMY3ZtNy1NeFdENWVSYUJCeE9VUHJEaU53UTh5cVdRSVppeU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOWDBPUkptcGhHdEZvQWVIYWhCQTlCajVuMU01aElqemI3ZzVWM3IyMS1ZNjcyUU1zOU95MGZ2MC1pcl9ucXhmUURTYlB3eUdMV1V3MmppeEtHWV9feUZ0aEFWeWN3QW04WDJNdWZGQVlUZk5XQ0pLNFBvQllsVDhxZTJ6TDlPUzI0OXIteA?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46020.4359375</v>
+        <v>46020.67325231482</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cristiano Ronaldo wants to keep playing until 1,000th goal - The Malaysian Reserve</t>
+          <t>Delivery start-ups finally get the K-shaped economy they need - Moneycontrol</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 11:26:34 GMT</t>
+          <t>Tue, 30 Dec 2025 07:08:31 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOLWd1elVfenFYLTFKYjcyNWQxRjN1S01LMVZ2Ynp0RUZUOWlvWkJYX29ZWjZFY0U5dXJiXy1tZzNfM3B4Z3NtWGNzeEZoMVZ0ZTdRN0tXblFyVUJFdGpFYzctcEtvazlHVzFHZGtfWE0yMEptOTJCRHhkNG5HN19VaHoyRGtjZ2tLNFl2TEdsOHJMZUNTc3FwalBGQmVjM0pQWmlhM2JCZ1Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxONGVzTHhvTjNCUEJCUS1ySHZtRks4VUw1LUJxSk9kRXRfVS1NS1VPLXZxY1hRYWZyblZzRnJyVEIycDZ1Qkd3Ym9sR2h2bl8xM0Z3aVFuaDJoRHVFTzdSRUVfS2o4UHBnY0FKN0VJbFVrTzBUd2M0aDFEemRDWnJOVGZ2a0R3MjNUZm9pS01aWURKVGhoazNJRUU2dV9Jb1NUaU1qQnY4eG1lOTdoUUlEYTAtSlhlMzRI0gG-AUFVX3lxTE40ajhwYW93VXg0OXpNcjRyYUM2TkxySk1UTjdhQ21sdl81T1RPQ1lFd0xGTGd0YUhXcEs4c0R5OXpGaE1tN0dBVF9DcnlrT21kWE9VbVRpZkp3dy1VNUdiM25oUlVqNjhWT3hfbjZJaG9NVkZXbVJCWk4zbU9JVklzUFdnaTlabnd2THpUY0dqTHF3bXRmOGxhbzAybzZveTlmaE1rUk51WkJha3JybllBakVCTE53bC1tMkhwV1E?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46020.47678240741</v>
+        <v>46021.29758101852</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>False bomb alarm at Adem Jashari Airport - Gazeta Express</t>
+          <t>Amazon to pay $1.5 billion to millions of customers over 'deceptive' Prime sign-ups - Mashable</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 08:35:00 GMT</t>
+          <t>Mon, 29 Dec 2025 23:00:00 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFAxaDhPTS1OR29IQkhoZ3UtNTBFZnRVY0hSbWphdlJ2bURqWUpHNTVfT1hTMFhOaTI0a0d2X2FJQWdHMkhCZUlUVlU4NDYyUG5OSVA5SHFmZjZOOEs2R3VUSHZqSXI3S0xRZVJxc0F1R01OOHVQWkU2aUpRQ3BWWGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9DNlJadzRjcEdRSWVuSFk2aFNnMXBmZzgxV2RyaUMzREdFUDdndThmNXhoVHRmbW5JanZFQnNnd1NSbUNrOXMtYWo3TmtFSVE1VkFxNUtNM3lObmV3cWNv?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46020.35763888889</v>
+        <v>46020.95833333334</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Is It Too Late to Sell Cupid Breweries and Distilleries Limited - Stock Split Announcements &amp; Free Explosive Trading Growth - bollywoodhelpline.com</t>
+          <t>Hat purchase on Amazon goes awry when a scorpion venom-laced drug arrives instead - Mashable</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 12:17:17 GMT</t>
+          <t>Mon, 29 Dec 2025 23:00:00 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNZFJRNXJrS0o2VUNGRDF0QUFPUGpERzJicVUtZ1cxNEdOZ1NKZWJUQlJyT0VvaWhwbmJHVF9xbUV2RGVrOUkwdFZaV2Q4QlhsUDk2R1lObHljcFhYd2k5YnpvRGZrSDlkRGlMOXVwZ0hvOHNNZEpVVlFkc244SDJnZ1FaSzRyUmVNWDV4eWprTWY4ekY4NExJbjVxSTMxeGFjbENfZ0dLZ3A0UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1vNldKRjBlUFJueUUwUTF0Y2xLRDN1bXpBNWlPNGRjbi1OVnp6VHZYVXlMQ3ZEZFp4bmc4ZXVXNkFCRUNXcDhUOFh2RXowcEEtaDlGQjlMUkFnZFhxc0s3Ym80aEVnWGtfQmh0QTQtRWZ1S29ZOGtGTg?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46020.51200231481</v>
+        <v>46020.95833333334</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AI Trend Models Suggest Bounce for PlatinumOne Business Services Limited - High Dividend Yield Stocks &amp; Outstanding Growth Strategies - bollywoodhelpline.com</t>
+          <t>Amazon is reportedly training humanoid robots to deliver packages - MSN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 09:04:35 GMT</t>
+          <t>Mon, 29 Dec 2025 14:59:12 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOVlZWSTZic1FQU2FHQnBONjNWeG1BTmNJNTJ3RWVCamlwVWdsVTAyaER5MnZyM0lBVnR5T0NDR19QYXVCcVQ3d2hKLUxJbmZGYzhFVVQ2LTZSTEdWMk8zN0pUWU5ZSnpESEtBdHpXa3VRc2pNV3Z2bS16NWJzdkZweWZNeGNocW9BLXJvbTJHSHlEVnBydlE1OU5KVU9FNnNsU21OOHpXNWV0a3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AJBVV95cUxQUWhVV0tOWGx3clgwZnEyTEd1WmJoU3BlZFA5Y0pMNEJlR0E0dFBJd2dxRkVkd3YwX3AxZjBtRUUzRkRvcHlKNmpfRmk5cXZzeDIzSmdRN2lFdUFEOTAyT0lOZnpxa3pnY3BWUC1LeGt4NGFPYm10bnRoMGp0Nkhyd0Rmc2syRFJCZkZVdHkxX3JMeEFZdTRvQlIxTXZTNU1zNzk5RGlaMDlnR0x1bnVvaGtrcnd6QTdfWjFoa2M3cG1peVh2NF94NDRzdjhfZVZDWmJsM1RUNGNaUUhZdkx5dF9rY2dMOUJ3SVAtS01JR0twUVJObGlHcURRVjBpdFVGMk5IZU1wTXVDb3FuYWpIOWlVSzhFSXVITU1QLUNhUENpYmdlUU5FbHY1X21DOF9GSEpvWFZBOEU4N2pLZEFPV1FmeTI5cmJleFRNVmFhYkZqUllxR2VJWjBOM3ZkYWZkcXBhNw?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46020.37818287037</v>
+        <v>46020.62444444445</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Energy Limited (540649) Signs Major Deal - Earnings Per Share Trends &amp; Advanced Stock Screening Tools - bollywoodhelpline.com</t>
+          <t>Amazon finalizes $7.25M property purchase for another Rochester-area facility - Rochester Business Journal</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 12:43:50 GMT</t>
+          <t>Mon, 29 Dec 2025 16:46:02 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOY0hrNzJRYUFGLWNVWEhQNFN5LVF0TXBrVy1IN0p2Q3NESUNnNXZCTWVnejd5YUFfWEd1MmJmdmlyX0VidDd2MnNJTDNpbFJPbkJDTUVuNFk3dkFCTUxfSzNVQWtsdzJwaTR1OU5QMG5hMGZmbElVWHFNZUwwSEhFVlZwT1BBWldFajhmWGJUR0VNbTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNbVBLajJ6QWFOamZrMnZ3emJOR0FXa3dlYklZQW5Dc0d2SW1GY3lpRVNjX2kyYWVMRE01LXlGVVowbVp4dkxLdXBwRlp0cDFNSGlrcUNILWhLeUpKVXl2OGZzRng1T3hUcUJpM3kzek03V19ZaVhONXJXVEd5T1cwRA?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46020.53043981481</v>
+        <v>46020.69863425926</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mewar Hi (540150) Gets Regulatory Approval - Market Capitalization Trends &amp; Free Gain Edge With Data - bollywoodhelpline.com</t>
+          <t>Missouri Amazon delivery driver shot in the head, investigation underway - MSN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 10:26:04 GMT</t>
+          <t>Mon, 29 Dec 2025 14:41:47 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOam8yRDBiTG9ib1hJSHZWc2o0a0FDVmFxYWZlWl9DMlloaGlFWDV0RXhjUXhfQjRsZl9xd2NmMW1GengzU0FlbzF0ZGd5SllwQ0ZfZ2NXOE9pMUJBNHhGT3h6REMtV0E1VmRHQ3M4M0FJOEp3a012MzI3WWtEODRoYjRsZUoyQnRZdWlWSWpQRzY0bmhGakRxUA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AJBVV95cUxPZnRKNTRRQUxvUm5wbWxPVWZVLVVoa0xVT3B3WjBGalN1Qm1PU0JXS2Nqa0tWNUhzZTllNlRoZzh5R0VWV01ZdWFqemh1UDR6OUt3am1raURhU3FUNnNXVWI1d3k4RjJnRHFKLWo1SXhveFlES2ZIQk52UmhGYy1jRThmY2NTRVZoTDV5QmtHTVJpT3VyWVRwN0RGUDFIeXZ5Y3ctWDYtMEc3cHlBWE5hQ0NJSEd4MFoxM2I3aGlSeklDdEhGRlU5bGNWTTQtWXBzVUk2T2RtazhnMU1Xa3JyNjFDVDRSYndVVHJRMWtjY29iajNlaFY4OEcyRjlQYjZrZmlPbXhoQ3dXMlpPS3pCSlpnNmRrcUtfQmpCYVdzd2x3SGhJZU1QUXZ4akY4OVZoNi1SUzFETDRxZnYzN3lTNTUzMC1NTXlENFM0NFJSYmJyaU1y?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46020.43476851852</v>
+        <v>46020.61234953703</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Can Honda India Power Products Limited Bounce Back From Weekly Low - Candlestick Trading Patterns &amp; Best Stocks For Explosive Growth - bollywoodhelpline.com</t>
+          <t>Amazon Flex to pay $3.78M in Seattle gig worker settlement - AOL.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 12:59:05 GMT</t>
+          <t>Mon, 29 Dec 2025 16:22:32 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQZ05fY0Z5dWdpMlV5VDRHUy1SVlotdnlIY1VRVk4wMG9ZT0hiS1JYS1JScDZ2MGhWelo1UXAzOHA5eVI4UG9lN29QLXhLZ05zTENOTWIwb3EyZ1dMb25OUnI0WW1BejA4V2VlUWcydUo0T1cxaHk5bVM4NzlpdlpDNGp5Qi14VTU0bUp4cmdFUlZuN2laZF90bGNLV1Nzc3JTdU1UVGhPT21YVlBuWXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1fZU9QT1F4ZVdFYVZlRG82NUgtNnpQUFNGQ2J4Yk9OUWgtUHdjWTlKZnVxWXp5NTNzMV9iODNSQmhKYVgyMU9LdjJXNFYtSGV1aHVncDFwYnk1UHBldVNNdFRaSXhLNUxwVHI3Qk80M0F4Z0E?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46020.54103009259</v>
+        <v>46020.68231481482</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Menon Pistons Limited Recovery Linked to Earnings Surprise - Large Cap Stability Picks &amp; Explosive Profit Growth - bollywoodhelpline.com</t>
+          <t>Year in Review: Top businesses stories included new Amazon site, tire store - Sterling Journal-Advocate</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 10:42:55 GMT</t>
+          <t>Mon, 29 Dec 2025 15:41:13 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQa01GaDdHdHd6UGxBci1fMTh4Tm9CWlVHZzNEcU1rVFRPMlFvdUxEZ2lIalBRQmhDeWlkLUx1eHZNWDBwaUVqd2xUQTdVTkVEOWpaZVp5MHpSbWtKNDBnV0Z5WG1HX1MwUnpNcTJwXzhCbERuS29LMHhQa1poMFU4SHd6T0E0Z205cG9VLVhjUmZRYzlJWEY0cHRQQkJyc3U5X2hF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQSkJ3QnlLQk1XY3duQUpKU1JoMXd2OGJ3S0loZC1weVRNS19wbkNsSWhlNlpuQ0hOQnpjRTdsZ2trTFhVVTRMWjh3a0NmRWhXcTh5TzEtYTk5OGtZekxrTVZoaThlb0J0a3gxdTFQTVh5U05mNUdnNWJoWC1wN3dpaXBXQjkybkN2dzBFV0FWekZ6ak1IQm9sRlp2WkFKb3lvOUl4cWhjMHBQWXJNWGlhSVNNX0lyNkdFQXc?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46020.44646990741</v>
+        <v>46020.65362268518</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Marcus Rashford: Atletico Madrid will exploit Barcelona’s decision - The Peoples Person</t>
+          <t>Amazon center, 4 more big Redding projects to open in 2026 - Record Searchlight</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 13:00:49 GMT</t>
+          <t>Mon, 29 Dec 2025 16:21:00 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPdE1WNXJhNmxYQlNJMlJmcEpPNHZhRnFjX2F2RnhrQzNwSFZrNUZNOWlfNjUzZGtFd2dFcGZVYnUtZzRteHlDcG9Iamd0dDBZY1Y1bDZxZEk5YUdfbWY5Q1lCc1ZDT0F5amJ4OC01SEEwVUJQMzR6a2hkOU9Xdl9odldRUkxFQm1GWUNJREt1RnJraXZOT3J4MUNGTUJNSTdBbUFvNmdKa0Z3TFRhNG5ETXNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNdHkya0JMbTdDR0RJX3JnNzdibUd2ZXZ5dHgwanJodDM3YVB5VUlmSDR0WE1ldS1KcUZ0NmRpTmdMVld1Z2t3d2k0aHFlb0ZGdThub2dYVkJJM3N2TFVjT2FfbGphSHplamZNZzZKeVhsWmIxY1l2Mkpjd1NPQURxZFFWUHhRWV94d0dETW16NTNDRVZBZGFjRFdTNW05WFgwVEt5SmlUeFFJNENFSDBpRjhCWmdEWVBVQ3N2cmRYNmszN0tfbW9tUA?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46020.5422337963</v>
+        <v>46020.68125</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>The Lancashire man on Britain's 'Most Wanted' list after double stabbing - Lancs Live</t>
+          <t>Boston man charged after assaulting neighbor over delivery package, DA says - WCVB</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 09:07:58 GMT</t>
+          <t>Tue, 30 Dec 2025 03:27:00 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQdkZjWlVidmNub01TR25YTVZ1T05wWDgxZmNHejdhdTdyT0FEMEFPS3pDQVBZWTNTU2JGWW0wdTR1bVdGVVNSQkt3QkpGQUxOa2xobTN2RXlNMjRBSU1uZ2ZkdFZIcTlERXhzamdPbFI4VTJRWks5QnFVTGpsRnRIbVNJWkJ0Sm1XQUR1WmNac3pZUdIBlwFBVV95cUxOWUNJVjZ3ZTJPWHA3NDk1UE83M2NoakZkYjg3c0dsek9qOU9lRXBiNGVCa2FpQ21NaTRXSFF1aW5jYVhSbTFrU1NQRHNvNmVPbnNqMF9uYUVBeUMzMlRlV1lXREVTTGo5TkNXeFRLZklqSUhYVXp2SHl3RkNEOGljQ1FnaG9oemVrYVlKWjNndVJXYlpqcXhB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQcWoyWFMxczRVZy1qTjBvQ2lVSFJ2eXpUdXlTeHlUQWNyYjctZTlmQlFJM1JLWG9KN185d2FzX3NRWEw0WVB0dUQ2aUFSVUdSSlcxR3dRS01wVGF5aVNYbEJWcmhyeHhiWFFySE1ESndJN2tDSUJiYVk2UmhfUFRPZVNzdXBDRC1IRFF6N1RlQzFmTlNZYkw5X0JvdHU?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46020.38053240741</v>
+        <v>46021.14375</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Village Search Bicester and Kildare</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lululemon founder launches proxy fight for board changes, WSJ reports - Reuters</t>
+          <t>Eintracht Frankfurt sign Elversberg forward Younes Ebnoutalib - bundesliga.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 12:50:00 GMT</t>
+          <t>Tue, 30 Dec 2025 05:15:00 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOY3NHbEFJU1JxWk5xNElPdGxneW9PWV81MkdBbzJnRi1DVlJnUG55bHlab1lSNVhmSWtzaFBzZ2Vra1ltWEotM05CQmdwQTQ0cjJURUpjY3h5ZGlkTVg2Z0pzR0lNZ0twcDFwSnZrYlRqUmEtdW1wT2NFeUZVU3R6VkdveXVKVnd6V21meTQzZXBINkFtUmF5VDR1VS1FeE9Qam92dzBoNURqV2FnNFFZbDlDWXRtNWlfUVhNUkRLSWpsblVkbnJPaW5DMVVaa2I0YWh2MmdndmtDX0QtMmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOYlpDY2JVUWcybHZYaHdRYTA4S3hYU3FFZWQ5aU81R2Vic1VOMkJiMVVzSzVjT2M0cFlQTGYtOVJfSHVJc2JFa09xaldYRTVaWVoxY2hkWnh2aHNCd0xxTThwUGZlUU1jZjhuaUp6bWdjMGVYLU5Nd3g2MHFoVkJFQkJrNloxZE9lR3k2WkJjSGJZbU1EaU83YXlzdVY2SS1iejI0TkNHSDY?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46020.53472222222</v>
+        <v>46021.21875</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LIVE updates as busy road closed by 'police incident' in Greenwich - News Shopper</t>
+          <t>Bayern Munich forward Harry Kane realizes there is life outside the Premier League - MSN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 13:23:22 GMT</t>
+          <t>Mon, 29 Dec 2025 18:05:24 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPTGx3VUVyMC1nYjIwNU5uUGJRRWtzMVVmdkRtV1djRGhlTERvZW8wVHpXS0xLNVY2eG9TSV9MQXB3cnluWjNIV3RYNEx1azNRekM2UWRLd0dyMWFvNWQ3ZzJ3MnJlMHNsakNpZnpCcVJubkhHV0U0czV3ekJCTTdFQ0RFRDZ2N0VFYkFLVVYyczhwZFBEM0xIR0R6c0VKV1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQVDJmWnBKSlItOXl1cFRDX3RQT3QxMDZVNVRHbERxQVNuOF9qdEJTYkVVUDM5QS1pWE1MS1NKQlJjV0ttMnBRRkFoa25JcUxoNHR3VXV2dHZfc2NGM3ZHeEYxSlBEWjRSUzhTZzh6Z2xjVjZac3kzOUI3TEZmeUtaRTROMmRoemZIcDBNbEo4Ql9ZNHFqdlJOcU5ocDdXemp6c1g0b1lleXhVNUc0TWY3dzVJeVNLUUhsODZ3R2Y2Rks4RVZsaGhva19YOXZ3LUU?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46020.55789351852</v>
+        <v>46020.75375</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Man shot dead by Norfolk Police in Thetford after two-car crash - BBC</t>
+          <t>Skillet Announce Massive Europe 2026 Tour - That Eric Alper</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 11:18:08 GMT</t>
+          <t>Mon, 29 Dec 2025 20:30:17 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1HTzlEbmplTkdmVlZCNXJkSzFWWHY4dWF3YkFDYXEzSEVzenhCRjM0OG1FUGlJQXVJaE9vWjRfcGZpWEp6Vkc3QjVidldXZjdZRGlfSEIzZmI5Z9IBX0FVX3lxTE1UVFNJSUNybXV6aWRILThrbmE2eVRUcjRiRDgyX0Z3eHlZX3JzcFJnWEY5N01fcGJvQ0VNbktPNjZzMGFfWk9zYjBiTE9HSGJGblpIMElIUXJ6bVZwZDQ0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNOXdDazZ6X1ExMTR5RTlndTh4WmFsZkhpZ3pxU041bjhHaE1VcHdMbmlVZk9QZHNmYjZ2MVdGQ1BjT1BKek5hQlZ5UVVIOVdORngtbnlrRm5OZHpkWkJPQnhVc3hPN2l3WlRGRUxqbUJCb1dKT2RIX3Vrc1JTc0NJZ0pDTmU5ZURkRzhJ?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46020.47092592593</v>
+        <v>46020.85436342593</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Limerick style icon almost nabbed by UK police with suspected IRA bomb threat - Limerick Leader</t>
+          <t>1 dead, 1 injured after double shooting Monday in SE Atlanta - FOX 5 Atlanta</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 10:02:50 GMT</t>
+          <t>Mon, 29 Dec 2025 17:32:14 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOTzlTb05PbnRLck8tNlpDMndENWNLbXhNYjBEdDQzcHltbm9QYXQ5UEZ3dVJVbE53aFk3aGRpdHFjcVNlUjgwVjNoVnA4dTZNVjNtT0Q5N1B0bnI0ZnlwNENjS0pwS0Q0MkRvXzU1ajBrUHJWYnpCa2RDcVFUaXFBSHNjd3FRY1VBbjFRUlhseVk2VVVZaEh4UDN3bHNmOFEwazJFdXJmbl9GeEtJa0xvZ1oxMUs2eHBUODl5SEUxV0tkNFNYRk9Bblpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNUmFrbkExdHZ2a1p0QTY4NXRXVFFxN24yZjEwbWdhRHpBQkU0NzJyNjJCZnZxRTdNbmR6UkVhNkhsOGkxXzFlZ1V4a1ZPVXV1cmhCNXJ1bzROSUlPeEFUYXlWak5KSUpzWGF3dDNTM3AyLWlHaDJqMnJZYVJYOTZ2LUFEUm11ZUZmVTlBbnpVaGp5QmPSAZgBQVVfeXFMTlUxZ0JVeUFMbmVRS3ZYT0FQWFpfU3JLVmJ6aG5oTGpvaGhvTzB6WDJsR1YyWkctRko2d0xzMWhweHhDSTcyOXJHRnJhVzVTdGF0VlQyM0lnN04xMjBuSWNyeGxXdG5LT0t2eW1GVUQtSFpsZXhPNVFINjdjV1dGdjFINjVRUTE5R2JOaVRhMlJYWHJGLThvdXI?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46020.41863425926</v>
+        <v>46020.7307175926</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remembering Bardot: ‘sex symbol', ‘crazy cat lady’ and far-right supporter - RFI</t>
+          <t>Man killed, another hospitalized in early morning shooting in southeast Atlanta - WSB-TV</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 10:14:00 GMT</t>
+          <t>Mon, 29 Dec 2025 15:40:05 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTnpHTTcySFd4Z2J4REJHVDNvZGJ6UHY2cUh5b3dyZUcxODhCNzd1NkVWeVFKTnRhN1B1U1BPTWhmb3hGV21MNDh4ckptV25PbFpmRXRmeHNydUlWU3ZqVkFKZWhVZmFuWWR2SmswY2NFZ1psVU5weGVrNkRGVUVIaTNMbkp6eXMya0NkeG5kVmJFX0kwQUxWa2ZIUmtMNjNuQkJnUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQSkJMY0xNOW1pZlBISE9iTFVBUlZFSU5IdHpNcU4wUnNkcDlNSzJkdmZJLVdDZGt4c3BCazZUSXpiLU9iTWM0bjM4amZLaGZwazkzTjJTdldUbWo2OFQyTFJOR2xHSENKaEpRWXNQQ1JHbExWLTJBUjRUX1Rlbk5vTGhJWlhWNFdRQTdCdFUyNjNyZkE2eWl3Q21ZZU82RDd4QXFMOWYtX3QwbTJYUFQ0ei1rSlBvYy1JT3czNE5saG1zYldZQXJpRHFyWkxIZ9IB4gFBVV95cUxOTzhzcExkOFJnRHhjekFMUlZXYWs5MnFIeFkyT3lBaWpSWGk1TVN1Z3pkYVlZZnZqVDJTbEd2S1I0UW1oUHVEQ25fOEl0SFBUdDFka0hSZGFNODBBd1hiTmVfeTBKendfVWtndXc1VjZWb01OM2N3LXpONk1saE9oSXd4X1pWN216UmZDNVVfeHhNSW5QYnF3Z0c3ckRVbmxFc3g4MmNLSnNpWE9Nc1k4WWdQVE5qNDJPbVdmbGxseFY4MFBidHpaaTFBN21DbnVQb2VubEZJNTgweW54R3pMSUh3?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46020.42638888889</v>
+        <v>46020.65283564815</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mysskin’s London plan for sequel! - IndiaGlitz</t>
+          <t>Federal (505744) Hits 52 Week High - Earnings Beat Highlights &amp; Low Entry Investment Growth - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 11:27:46 GMT</t>
+          <t>Mon, 29 Dec 2025 20:11:05 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxObk01eG53VE9Sek1VRmF5V0k4MklteGlYT21EamowU19nNEVfUk13MW10MTRGSVAycEkxWS10WEJmMUkya3RLYy1pVGU0bkJYRC1RY2VycGZuWXlMTkxSVVNqYTNrVGpPMzNlbUpFd2dqdFZucmQ2MnhyOThYaVdIckI4OFZyQnhZNjhMTThB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBESnhNWUp5bDh2S29uT25YUTRsQlNXYVVQUnRWQjVyTGZRakJQRm1EZGpDVW9aOUwzVGVMNXNDNF9GdTU2UlItTGxIVWstZmVjQzZlRmphTEcxeUVzN3FhNFN2VU96ak9pNXVmZDNXLTVISXlBMkFVMw?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46020.47761574074</v>
+        <v>46020.84103009259</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Police send Durian Tunggal shooting audio to CyberSecurity Malaysia - Newswav</t>
+          <t>Hyderabad airport receives bomb threats to three incoming flights - MSN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 08:52:07 GMT</t>
+          <t>Mon, 29 Dec 2025 17:01:48 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPRVhSOXJnTHdiQ0RfNWluUzIzdFB1c3FVNE01V3MwMWRJOWdVTHVia3ZyT29SSDNSR3AwcTRKd18teXFvZTFYN3NLZkloZ2ZxenoyRVYxN2VFd1N6Z0lwQjd3aWpmVTZGM1hVZ3dDakdjS2dRNkRQMkQxZk5OQ2JPY1NWWGtLXzd5U3pNa18xeTQ1ZFY5NERKUlVjWlQ1UHF4bWhGZTdWOGFpU3B2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywJBVV95cUxNVW1Eall0TWkxMldhak5fVl9fdVpybU10Qm8wSHNHSkRsSlRKeVhRQmN0ZTJPR3pPQWxUU2plUXl3bmU1OGlXd3BfRXVnV0hmV19YRnYzMGV4T0lrZkQzVm1ORjVpQ1Byal9wVEtDVmF6bFNYSEpIUkE0RkZWTHJVLWtNZ3I4WGg4V3UzTDFvc3JhQzliYkpWWmluWGlHRjVhbi1qNGxiOWgyb1E2cUlCenlQLW0tQkc2aWFPRzNheWMxQ2JEdGJpTm90RmUtQnN3Z2hvOXZpUkFQMVJxRFR3emdtRWQ5STh5V19mTVBNNDhTcGJzek41eEpnbnUzRG40cmlTd29xSW43anV3bXdxdGdGSnhMcC1wRm9RVHZiS19ZejM5UHFkb1lSWXBNWnktMVZleTVoc3Bldk1sZDRYQTlLM3IwWVdjQUxn?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46020.36952546296</v>
+        <v>46020.70958333334</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New Year's Eve terror threat prompts major cities to cancel celebratory events - GB News</t>
+          <t>International Exposure: Diversified revenue streams from 67 countries - Institutional Buying Trends &amp; Outstanding Profit Investment - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 10:52:30 GMT</t>
+          <t>Tue, 30 Dec 2025 04:11:07 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOYjJFbWdOV3hrQ1pSZ3Vjd0dIT1AwTjkzSTdUQ1lqeTFKbU5ZWnJnZkFJNFFtTEZOekRKWkV0X1NCWGcteHZmQkpZUGd6UGFRckJFbHNpYTlNRWV0YjFobTFBSjQxQmNlUjdXeXVpQ1R4cW95WVdvR3VFSFdyMWtiQnMyYUVNd1FMSWo4MVVkUHZIS2JKSEIwUmpkMzlRTVYwTkN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNZkpfYzZnWXZDMlRKT2haNGRLRXo0Z0w1WG5Sbm1hWTV2NDVWQ2N4VWhLUmYtbTJvSnJobFZYLUZJOXczbW1wd3NqdzAyVHhxYTdQR2FSRjgzdFNrdDh1X0k5aXF1ZzNYV0tWanZ0X1M3RG1adUN6VjVlSnNuUG1Yc3djdkNkM1B0Z1JQblBxVkR1VjY2UVM3bkVoVEZHUXlpVkdWZVFzNA?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46020.453125</v>
+        <v>46021.17438657407</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Paris train station partially evacuated after soda-maker exploded - The Local France</t>
+          <t>Hyundai recalls more than 50,000 vehicles for fire risk - Atlanta News First</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 13:23:56 GMT</t>
+          <t>Mon, 29 Dec 2025 16:27:00 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNZDljZnI4R3dzT2V1Wk1xeGlWRV9Bc3p2M3pnVEN2VkxmWml4U1JCM284WUw2VHNLU2ZXdXZmRkppNW1FVGFHeEJ6SXg5TjBUeWJ1eFhMTXBjNGVTSDZyVVU3cDl6NjE5Ym1Nd2FqWWJWWGk0Q3NBTnlENVAwTDlDNFlZSjVZQ3hDYm5nVU5fTURFYm1DSzZFM2ZQaWQ2NlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQNlV6UnR1eU9XcDNaN0ExV0JVX3pwT0lsTkkwc1RGRzRGMTgxaUJ0dWx0ZUU4LWNLaW0xQnRQV0Z0ZExDV0dTVHZFTjdsR3VPcFFxRGFPRHRqYXgtSVhJTE9NNDBRQkliSFFtazdLNC1oU2N3eGV4YkhUTV8tZFdnOERyaUpkWjBnNEtVaEc4YTE1QXp0eGNqTlc1QVVQbWh1SXkyT3lveEVFZXVsQTJn0gGvAUFVX3lxTFA2VXpSdHV5T1dwM1o3QTFXQlVfenBPSWxOSTBzVEZHNEYxODFpQnR1bHRlRTgtY0tpbTFCdFBXRnRkTENXR1NUdkVON2xHdU9wUXFEYU9EdGpheC1JWElMT000MFFCSWJIUW1rN0s0LWhTY3d4ZXhiSFRNXy1kV2c4RHJpSmRaMGc0S1VoRzhhMTVBenR4Y2pOVzVBVVBtaHVJeTJPeW94RUVldWxBMmc?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46020.55828703703</v>
+        <v>46020.68541666667</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>All the Filming Locations of ‘Emily in Paris’ Season 5 That You Can Visit - Prestige Hong Kong</t>
+          <t>Orlando International Airport launches its first direct flight to Germany - MSN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 09:46:03 GMT</t>
+          <t>Mon, 29 Dec 2025 18:40:47 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOVXZjQjRnOGRiVUlVdFlOYm8xV3RTSmFDeUlycWZNZlFMMjk5QnJSaGJKQWlsZmZLMjhnd3VreUVmTFV0T3FuT3J6QmJlSS1sQkYzSlByS0Nna1ktMURFOUFJekZaX3BwdjFqdy1xRnpHdUhGQzJweWl4U0Z5TDdEZFIycnduVV9VSnNCRVozd9IBlAFBVV95cUxQV2RqcGJ0elNzRVE3WDJUNmFjQVBCM1RZckpoLUJ2ZnJ0RGRPOFU4TlByUHo3NzZhS3kyaHBTOWc4UHBud24zSU9YNzdqQnUyZ0hpQ3ZaWGhlSjVrZ3lUTS1mV0ZCRGhGVWZ2dllmbkFXOFd6aVlObjhSMVpXZllncWgxTTVZeC1zcXNGVm9QeFBvS0Nl?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wJBVV95cUxOTWh4bzhkUVlQeVVlU0p0M25tbmsyemJvcW5rLVVoMEdQbXNSX0w4cEVCSHd2bUR6WjFYbFE4Y3ZveGdORXRubnpQN1c5VS1Kc0lPaW13Q0duc0hxSmNJTGI5dDFuQlJwUzZPRnFNNGNtVnl3cGU0RXZ1T05lLWQ2b244ZE5hOERzOE9MOGcydmt3V0NqUXBzcC1WQTJLX0dtQ2FIWVFjSkFXT2kzWkJoNXBELXdSb0pDaGMxQ1l2NGVnbGVvV2tXQkRtZGhGNzRwZXI1R0otdFpFUS1sWmY3ZkdWajNJc3JycE1sY2U0MVZWX2VQNldQMzRwd2ZUMEhoeEtsOGY5MmFxVGI5YUdqUXNyejBYTzZNWTh6NkpNODNDTlo2TkVia2JjZk5nQ3BOb215ZUlXUTVsZ2VkellIZFdrUWRvSDZaelpxbVJOV1BkbWo1dzJQX2tRblFfdTlleW02c1ZiSQ?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46020.40697916667</v>
+        <v>46020.77832175926</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Paris metro stabbings suspect moved to psychiatric hospital - Diamond Fields Advertiser</t>
+          <t>Second pilot also died following midair helicopter collision in New Jersey, police say - Atlanta News First</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 11:12:35 GMT</t>
+          <t>Mon, 29 Dec 2025 16:34:00 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQZGN6QjdRcTZMUEtwT2Y3T29iOTY4SElGUkd0UUFhZzhTZEkxb1JuaWlob25rTy1JVFB3Zm9vdUtaenM1UGs5VkFMQVpKU1B4Tk80a0RudUp0MHlCVTVOTndEYy1qb2FHVmxmdVJnT1NId0tLajVFNUYwcFhESDJHcnF5V3g5bDI2RW9HemllVFJReEJRUTZibGJkbUkwNTZudnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPOGpZVGtZa0toVG1kOGY2cDBDRmdfOFoyd3NzWlYyMHBVUGhwZ2NEeHpNR2tiVDN6cUtsYWZlU3lybHZlM1QxeWU5Sm0ySTEwM0ZFSHNKSG9qS0FsV0ZlM0RoblVEcWFGRzJRRmN1TEpyTXJ1blFqSVhtTGNCWFptYVBlcW52WEItNXVYbE9mTnJ6ZWFwZWthbTRNOGdvQXZXQXdGYmp6Zjh2U1E5eHZ5TUV4M2llajAtSFEwci04aGtDcWVMYXVMbTN5QXBhdXdfbFZNWXBWcV9FQdIB2gFBVV95cUxPOGpZVGtZa0toVG1kOGY2cDBDRmdfOFoyd3NzWlYyMHBVUGhwZ2NEeHpNR2tiVDN6cUtsYWZlU3lybHZlM1QxeWU5Sm0ySTEwM0ZFSHNKSG9qS0FsV0ZlM0RoblVEcWFGRzJRRmN1TEpyTXJ1blFqSVhtTGNCWFptYVBlcW52WEItNXVYbE9mTnJ6ZWFwZWthbTRNOGdvQXZXQXdGYmp6Zjh2U1E5eHZ5TUV4M2llajAtSFEwci04aGtDcWVMYXVMbTN5QXBhdXdfbFZNWXBWcV9FQQ?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46020.46707175926</v>
+        <v>46020.69027777778</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Alkem looks to offer explosive move in the near term. - Candlestick Pattern Analysis &amp; Free Real-Time Stock Market Data - bollywoodhelpline.com</t>
+          <t>JD Vance’s joke about Greta Thunberg and Elon Musk bombs at Munich Security Conference - MSN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 11:55:18 GMT</t>
+          <t>Mon, 29 Dec 2025 18:16:11 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQQ3hXcmdKVWI1NWxBUFRELWxPbVpRM3Q3QkdwYkpoMU1xV0F2S3EtY0NuUWJRSG0wV1doSGtoVm9xaTV3QkhtdDIyRFMxMEh3QlJ5dTJZY3ZXY3ZzZkVNX1A2d0pnZzVCOXBMNjRfT3F4SDU4UGV0RHhQOGRGdHpiVUpTUDRNcE9mQk0ybWZreFg5UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gJBVV95cUxPaFRfd243eXdhM2dhX1hhQ2lRdTFjeGlZVFN6cnVZbDh1YWlaeXRDN0N5Y0FNWEhVVmh2WjJPUmcxZ3dUN0lsWjV5dlhhQUp0MXlCMGJtMHJtSnA1blRxRWFUUW5FLVZtZWNaX1dpRl9ta1hVdWVYYnJnLTZRWEt2aEFrVXpOcUJlVXVqNkZmVTNRQlR0MkhPUTV2VDBRNE5BX0ZNUHNEaGQzWW9jTElVNmoza2RDMDVsbEhMVzM3bmZydHM5cWVzaWtpRzhGUjZ0R0pIRWZxRTZJV3FUYkVWZ0NpcXBVTl9VaEF3cFlBYlk3UGdMRFBiV0xYMEZ5Z291TEY5dWktRXNBNzg2TnVvMFZsVGpBZlJpZ1JEVkJzRHE2Ykx6LVRhRXBHN0FvSW54UzlGM3N6QkhSb2dqQ2tyeFYzTWcxcHZPTnFUUlZlWFA4ZlZ1SGJGakNfTWRRM0ptNU9wbmdQS3FFU3FIMFN5blRqY3Z6QQ?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46020.49673611111</v>
+        <v>46020.76123842593</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vardhman Special Steels Ltd (VSSL) - Candlestick Pattern Analysis &amp; Free High Profit Capital Plays - bollywoodhelpline.com</t>
+          <t>Starbucks plans to close about 400 locations - Atlanta News First</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 13:38:52 GMT</t>
+          <t>Mon, 29 Dec 2025 16:43:00 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBaYzNvcmN6QXN1cGxkR0g0N0cxRXhOa1BCcmQzcDA2X1pkUlJ1Zk1XV21jdVVEUnR4QXBXSlczaGt5QnpPVTNzbkNJRDNJZEY5QWhROTVXV2FBWXlfX3hydDdHbHo2cEs1RGd0SG1CT2ZsclFRaVZEag?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNU19id1BXcndyakhHRkpmUlpscFJUVUJkaUcwckxpdlBtM0FPTXB0eV9ZMVFBZEk3bm16WHdkMzdOdkRMcVVkUE91eXBjbWRMcXkwUlNodWNUdkE2emZYSjdDOE5kNGt3ZTFCRmVyVzUwNUg2aHBxVUxjam5XUTI3T0txNDh3bUJqbG9KNGRxVTdlREpjTmFQOHFTT1YtTGVOSldz0gGjAUFVX3lxTE1TX2J3UFdyd3JqSEdGSmZSWmxwUlRVQmRpRzByTGl2UG0zQU9NcHR5X1kxUUFkSTdubXpYd2QzN052RExxVWRQT3V5cGNtZExxeTBSU2h1Y1R2QTZ6ZlhKN0M4TmQ0a3dlMUJGZXJXNTA1SDZocHFVTGNqbldRMjdPS3E0OHdtQmpsb0o0ZHFVN2VESmNOYVA4cVNPVi1MZU5KV3M?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46020.56865740741</v>
+        <v>46020.69652777778</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2025 in Review: Discover Our Top Gaming Picks of the Year! - Sortir à Paris</t>
+          <t>15 crash deaths, 274 DUIs reported statewide over Christmas holiday travel period, Georgia DPS says - Atlanta News First</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 11:28:45 GMT</t>
+          <t>Mon, 29 Dec 2025 19:03:00 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQOXdpSjVaWUZsc1MtOV83WDl2SlhoVy00Nmk5bHV5WXlUVHlxVTk0Q0FGZXI3STBUY1U0cUxBUm5MQnUwUFdJR2JuLVk5eU9NYlVVb1dvclZHZmNJa3VZUGtzTHpIek5Qenp5OHpJZURYV3dHTjFaaTB4cWYyWFNhdTVlSjByNGtJRXNkVFNYTGQyU0JLa01penVXSVljbFpTZ3hadlFIZWpyMzNRSGJyWWZoeUpEd0Vaa1dHakhDTEJQWmdXOWdDVXJxLXRkdWh3WlhWV1Naa0Z1NU5FNEZrSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNMExEbHZyZ1Y2bkh0d1l2MlF6b2RzXzVtMGxMb3IybGtseW16dXFEZG90Z0pzbkRKbXd3WlQ0eUplSGpJWnhUT0pGMlpRbDJTajhzRk53VFQzMUVpRVUzVGR3THNrX0w5eHU1SjR5MzhFdzhxTHpZSUl5X3lBXzhPMEszSkVGaHBFd01FeG9qSkxRd1RVUVZiaGJwVmtxTGVNa2pnSWhILU1pUWREYkplQlpwYnFWYTlVdmRqRmdCb3d0eWVTdjMzZjEwN282RExHMGRZMHlId29iUTFwZzVFYW1nTFNxWUJnY094Z2N30gHuAUFVX3lxTE0wTERsdnJnVjZuSHR3WXYyUXpvZHNfNW0wbExvcjJsa2x5bXp1cURkb3RnSnNuREptd3daVDR5SmVIaklaeFRPSkYyWlFsMlNqOHNGTndUVDMxRWlFVTNUZHdMc2tfTDl4dTVKNHkzOEV3OHFMellJSXlfeUFfOE8wSzNKRUZocEV3TUV4b2pKTFF3VFVRVmJoYnBWa3FMZU1ramdJaEgtTWlRZERiSmVCWnBicVZhOVV2ZGpGZ0Jvd3R5ZVN2MzNmMTA3bzZETEcwZFkweUh3b2JRMXBnNUVhbWdMU3FZQmdjT3hnY3c?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46020.47829861111</v>
+        <v>46020.79375</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Suvidhaa Infoserve Limited Bounces Off Moving Average Support - Capital Gains Strategies &amp; Free Explosive Return Secrets - bollywoodhelpline.com</t>
+          <t>Breakout Traders Target The Baroda Rayon Corporation Limited on Recovery Setup - Price Channel Trading &amp; Ask Experts in Our Investment Forum - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 09:19:56 GMT</t>
+          <t>Mon, 29 Dec 2025 19:47:34 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQZDlZemhlRTEzOEwzclR1eUtTMk4zWTExWjc1YjNHa2dqdmJROE9ZTE52SkJ2Mm5YX01NNEdzYmoxRDVwRWtKZjREX3c2TW4yd2xvaERmdGFEa2JITHRrRy1kMkxzRWNPMlV5aHU0Zm10ZDF0enJiaW9TX1FaWS1za1Q2SmQwUU0ya2M1WG5KSlM5eWJVZ1JTQmQxenF0aE5DUFdDaWU0aWJqVGJIbXE5Mg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPS19uN0RoMFYzX1o5OTFnMDdGWDhvNDJhZlBrSDczLWlIS0hkWUZxOEMtbS1PaDJZYTZ1eHNfdzAxR1hCVm1JclNKTjFydTcwd3o0aU1PVVdwSkJJUW0xOE1nek5FRXg1a2tyYUI4ZjVOTkwyOHp5SmxaUFdPejRiVDlRYk5LdE9XTlVtTGNYVkhPdDlUMk9LTUZtVFQzYTFTTXB3X1pQMVJUZXdBanNRa05HYw?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46020.38884259259</v>
+        <v>46020.82469907407</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Site of Mariupol-theater massacre reopens under Russian occupation - TVP World</t>
+          <t>POT POURRI - The Shillong Times</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 10:51:00 GMT</t>
+          <t>Mon, 29 Dec 2025 23:48:14 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQd0xTVHBuZGFZcmRlTTlZUUhhY19USXNpOUpOZHJZdzlGWkNEUlBfdV9ab3htWjdJX2RKQnk2eF8zZFdHN3JYRTJkWUl6VDJLZjNRQXdxcWhhZlc1eld6bGJTWmVmczBHRFdBRDc1TVNqOUpPZjVUNmNRX0Y4dWM5alVVR3FUbWdDTDNtU2VqR0prVDg5ZzlDZ1IxcExqUEc2TmtMMnZjemFPaGo2bDJxVzJDNnhiSkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBWT2hzYUlrdUVzTDZYSUV5UjZxeUhZMldQc0Z6VXpHTVhCXzVsVUlOWWtRMUkxZnVVbGk0c3E0a0doYzBUcHpBanh3X3FqNU0tUE1EYTBDdDZNZzZ3eXo1aVFOZGVXdw?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46020.45208333333</v>
+        <v>46020.99182870371</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>PETA Twitter search</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>peta (gucci OR dior OR armani OR lv OR valentino OR vuitton OR polo OR ralph OR klein OR hilfiger OR prada OR balenciaga OR goose OR burberry OR lvmh)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Analysts Apply Wyckoff Model to Vision Corporation Limited Stock - Short-Term Trading Alerts &amp; Set Your Capital Stop-Loss Limits Effectively - bollywoodhelpline.com</t>
+          <t>Kim Kardashian slammed by PETA for giving each child a puppy - NewsNation</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 09:57:09 GMT</t>
+          <t>Tue, 30 Dec 2025 00:49:06 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPdjJwemZiaUVUZ2l3dEVKdWRXazBwSkpCWDBwYzV1NjRGeWF1ZnlBYTNXNm5Fc0VlNGdTVGtnRDZxMURzQ1NTNmVPT3hSNWoxLXBMalZ6SlFycEQxWTFOMjhsQzJpWTJ5bWxJUV9lZ3hNaGVONVNfVmowYUFuWHR5Q2p1cl9WS2kxazdzWExueUhzRUpKV0JKWEZhOWNZbVgx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPenJSdlZPZV9OQUx2M2xUWFp0d1JBcGoxVW5aZDB4STJibzVjbkloRnhhVGxZX0F0OEZzZ1pEaGgybjR3dWkwWGpUT1ozUExKR0RZMVZrVjZSNnVNNmRkQ0w1RnQ5cXBELXIzTHg1UXlkRUxPSTFYemtoQ2FzdThkT185dlpkZmxhWjVfc0dSMXJ2R0s5eFdURlRGQjF5VFlT0gGmAUFVX3lxTE96UEpfN3RRcGZBRGw1ZUxiRUVYQWVCWjlnVUpmWnhrcVgxdzNmQXRQeUIxbmh6cTFQQmt2Z0JRV0pRM1czX1pNWEF3RDBiZFJWTTBRZFVBSjdLZXFzS1ZMOXVTN1h1dFRUZjVKNVVaZVV5eF9iYlh4al9TbjZxSlVjV2F6MXZTU1ZuTFdEQ2F2N0tXaEk5ajY5dnJZMjNDUGNoR2dpdUE?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46020.4146875</v>
+        <v>46021.03409722223</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>PETA Twitter search</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>peta (gucci OR dior OR armani OR lv OR valentino OR vuitton OR polo OR ralph OR klein OR hilfiger OR prada OR balenciaga OR goose OR burberry OR lvmh)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Investors Hope for Bounce in Ambo Agritec Limited After Selloff - Earnings Volatility Patterns &amp; Free Explosive Trading Growth - bollywoodhelpline.com</t>
+          <t>Dec. 29: Get ready for some of the coolest air of the season - WPLG Local 10</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 08:31:44 GMT</t>
+          <t>Tue, 30 Dec 2025 02:48:31 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNNm53R0Q3ZnZxQWJ0NmppRGF1ZXUtV0ZyVTQzTlluVEo5Q3haODEyNmQxSkdhbGE4elNrelBoLVFISHNLQUVIOGdZRS1ZZVQ0LTctMEUxQjU2aFVDT3FpbGxIel9GdnFGZm9XRDd1UFpLM1BtRWJWb2NNY3RmVXJKbkQwZ01ON05Bb1dwMmItR29nclIyZV9TWWc1alRCd3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxObEpLdVhSMWpyemd5aVZZOFlxQk1Da1RmVVF3WTVjSjFFVGliNUVVNGowVWZmMmF1YnpBVEk0NzAzdjY2SHZ1TEtLMGJVUjM0bXBoTDkzM2RxZHBfUG9zdjJ5LXNSdG12SFZkdV9aYnhpb3lWemNadF9yMWVFTU5kZUpoTEN2X0RZN2d5QnBNQmJwN3hzYUlGREZ6TnZoWXZIa0ZLaw?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>46020.35537037037</v>
+        <v>46021.11702546296</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Trapped Investors in Hilton Metal Forging Limited Await Breakout Signal - Stock Watchlist Updates &amp; Free Explosive Portfolio Gains - bollywoodhelpline.com</t>
+          <t>'We want people to feel safe' - Doncaster police chief issues 2026 warning to criminals - Yorkshire Live</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 08:34:42 GMT</t>
+          <t>Tue, 30 Dec 2025 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOMVRwWkl3dVVjVlJLaWFxWmpDekZiRF9nNVVQeWZPcnVOZFlvQnhHc3hoQlF6eHNPdVNkNVNrbnRmdUdSTm5uQlZWYncxVGpPaVU5SmV4cTgxZG9QVEZRU2hvSC1RVmZIbWVZNzBZZ0laNjdCaUxEemFaZ0hsZTNmeGRVQ1VyWm8tNGd3Umk0Y0k1VzdxbXNHMC1ZV3ZEQnRPYVRGeGhVUGdPM2h5a2stUjVwT24?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOZ2FMX1hmcGZGMTFEZTFEdUZ5cjRTZTJQUFJva1lGLWRMU05pRUVxVW1nc081bTIwaEpZUGU0UFUyVUpiTUhPWXZsNjFkajJ1LW94ZTFvMmMzcGhXWF9obEpyOWhHUURiMXZHQ2hmQ3ZmalB0MVVkQnZraDV4a0hfTENTeHZlc03SAYwBQVVfeXFMTW94cEVTMHRYNUZMSFlzNXRjUTlTeFllcnV2cUR1SlI1ZklfamQ3WWNTUmdPNEdyZDBoMmk5c3duYmNodU5xT2xuMGc1MVpfMUl4TDYyZ21aSmowTHRUTGstNWtCZDBUOF9RWFAwVzdzYkJINEp4MlBkZzlCSFZEaGJqd3dDMEJTSGk3Ti0?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>46020.35743055555</v>
+        <v>46021.33333333334</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Steel Co. (Gujarat) Limited Matches Institutional Buying Filter - Fundamental Stock Analysis &amp; Explosive Profit Potential - bollywoodhelpline.com</t>
+          <t>More than 100 arrests as part of crackdown on retail crime - AFR</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 08:34:38 GMT</t>
+          <t>Tue, 30 Dec 2025 05:17:00 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQYW13VUFUZ2JSV1RoOThESlRqMnBvRGJmcEZOOW85WXdyZlB6QVE2WURVSnFNX0VhRUZCWEtmNGFEUGwwb0c5WFllT1NqeXRpOVhhMHZXZ0V3NnZHTU9KQTg0NEtOOG1FY3NYeE9LNDZTZ3JXUnBOdmI1d0Qzb1Zsby1PNmpsLWdNTFI2Q0FLU2xQNDJOQVljTUxjejFuSmpsdmZVelhIUm9FbTdQVFlxWHpXUzl4dmNKRC1nUTJqczlyNUxfS2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxObmQ3RzV0WXB3Nl9mS29xeHpJbkdyXzc5V2FyZmhYNVdCT0pDSDhtNDZ6ZlNRQXhFSll0QUcwX3dIX09fVDhMa3ZxOWowYjBoU1hXVnVFd3NaY0ZHWklJTzc0MW54czJsZnB4dWhIdEdPeE0tY2JlcHg4SkkzRjV0VnByV3ZiWGpSd2d0a2g3SW1ZNzZ1b2RDTGFpT1hBSUV2Qkx0VlVR?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>46020.35738425926</v>
+        <v>46021.22013888889</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Morris Engineering Company Limited Possible - Stock Valuation Metrics &amp; Outstanding Growth Opportunities - bollywoodhelpline.com</t>
+          <t>Local Insight And Fast Action Leads To Recovery Of Stolen Goods - Scoop - New Zealand News</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 08:39:45 GMT</t>
+          <t>Tue, 30 Dec 2025 03:03:00 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPcUQyRVQyUndOVEQ2ZF9YWDhZbnJkRWtWWDduSG04WFFyUlJzYXo2MFZNb1N0YUl4WHBNZ1BaNm5sTXgtNDRNQ0NvZC1oVk1NRGxYX2xhQVhFMnZKTGRPUUVlcFp5dTIzYWVHQnpPeUNTblVXRkNtRHN0LWE3SS03bE5oS2RMV3BEdjhGRVBhUEc4elVfRF84YkRHemkyaXJRc20tTmE2UFVoNGFvd0hyejlVMjY5dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQRUtYNFRMMk9paXdVNkR5WTNDY1hDR2VMR3dNVEhfOHVWSnczdXBvM3lDTjBPYVVlTlFCWjU5ZTFhQ2lhRGdydlg0R3lRWDA4ekFsUS05dWZWSHNoaDhERkVLZ3BGYXZVNjB0am8tN1FlRmZvWkcyLU5NS1NXUGxmeGNYTHEwR2dkWU1hWkpWMUd5ZlJZWWFqbUJYRG92OWFiOUZqNFlYTEJDcWRuczBld2ZGMA?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>46020.3609375</v>
+        <v>46021.12708333333</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston Christian visits No. 3 Iowa State following Momcilovic's 27-point performance - FOX Sports</t>
+          <t>Georgia expands crackdown on organized retail crime, seeks more funding - WJBF</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 09:43:40 GMT</t>
+          <t>Mon, 29 Dec 2025 22:17:59 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZklKeXFnVWw3T3l4YVE5bkxLYlF1bFd6MThYV1puZkp0NW1oVzlFRGtDZjg3V2dhTUM0NjZaOFBaNWljbTYxWlpUd0ZIb0duREVoMnFMOE9jZU5YdXZwcXFJMTU0SjdCVUJjRDUyU1BWV0JBY1ZQRU5Xem4tRkpkOFROZTQxcDN3M1FlX2VLSW13ano2YkpXZzZWekNRV1pRT2R2NkVtMGlYTllMM01fY2REMTdIZ2ZZNWZTUFlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWEQ4SVhRV3liM3FNS0Z3SWQ2TEk2ZjZmdVU1bzNzZk9zMXdDakZwUTUyajVYcDREM3dZRkQyaXlkb0RhMjZmckdEVlN0UDNiOGpPOFl3c1drUXVPbHpXUGoyUWFQRFRaZnBJQnhvSjAtcU5MYWhqSllrcFhORGN1aC03UlNYZ0ZjbndmV3JqTVRNZ2JWMjc1cktCZ0pGMXlUNXNlcC1YZE44VGNBbnlr0gG0AUFVX3lxTE5kUUowNEN2VWpuaF9BLUxnekttR2lHM0dGNTVpaE55U25ORHRwVDg4aHpHSUQ2Qm5CUFZYdFpJazBxMmNpb0xhSDJyQXZJZXpibUdaaWdRaFYwbjRPZDJoeHJkTzZFYXdiVTVPaFk0RDVfeVlqRlJ6TVV6ZFdrV2xZenJZX1FSX3NjMGpyRHdHV21tWlhRSkZXS2RqOG5CMTlVb1ZWb1JGZi1tanVvUl9WUE1Ecw?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>46020.40532407408</v>
+        <v>46020.92915509259</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Christian Pulisic denies dating Sydney Sweeney and asks media to stop - CHOSUNBIZ - Chosunbiz</t>
+          <t>Woman arrested after $1700 grocery theft from Hamilton supermarket - 1News</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 11:36:00 GMT</t>
+          <t>Tue, 30 Dec 2025 06:49:00 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBPcG9tOVlRbUpzUHZuX0tncTA0ejhoUkhJUGxfN0dBZ1hEanNoOHA4dzBzQl9qUDVmNUo3V1R1MUxUQlZlenNQbVc3eEw5MUcyeV9SRVZNaGR4UGxac3VqQUlVc3d1WFhuYTVwSnd6bXhMalVCM0lRdDJtdWoyQmvSAZMBQVVfeXFMTVdkQ2ZfS2FMcDBaZ0xFWXB5TGZ5YjhUNHpleDZXOUdjSkJXcUhUTUQwRjBzVGlabWNqRVBTNGUwQkZUMFhqM2g4SWV4S0hVUWRBUVpwa3B2dGVQYlBYTVhfNXRnRzZxbEdEU3RmRjBIdGtkQ1Z5cUVQMUlmdVlmV3UxbDFfbkIxaDZGSkRRb3d4ZjVZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNd1BtNVlPUGVLSTNhb0ZCX05xRXNRQ3RTbWhxT0FOVUx2anJoSVlZbnlFaFFjQ3kwMENBZzVtMmI4TXNlMnd3Tml5dm9zNUg0TmhhNFcwSkdlS1VKRGNvM2hhdnZ6OWdaMGdLRWpjN0x2bUtEcDVZNUJrbmhVU1MxLVJQU0J0R2M2WlZsMjVUeUtMTk9xNVRZUG9JZzd0WU5nWjJJ?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>46020.48333333333</v>
+        <v>46021.28402777778</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Doncic and LeBron calm the storm at the Lakers - MARCA</t>
+          <t>$400K worth of lobster hijacked on the way to Costco, shipper says - MSN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 10:35:48 GMT</t>
+          <t>Tue, 30 Dec 2025 04:43:53 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPcjc2b2Vha1kwRUJFV244cHhCN0xxZGZYSXoyT2wwYmpFRkJaa1cyVTQ2dGc4eGFRSkRXUVlRM2FfaC1zb1g4YTJFb3pxRXRhNU5naC1uQ2NJZFRqR21nQXVsaDE5VzYxSXJhZEx0MUI1VXp0bXN3SjBWeXJYUXYycFlGWW9jRzNONDd5QzZNTGE1amNsdnk5WUpiV3NIZGM00gGgAUFVX3lxTE9yNzZvZWFrWTBFQkVXbjhweEI3THFkZlhJejJPbDBiakVGQlprVzJVNDZ0Zzh4YVFKRFdRWVEzYV9oLXNvWDhhMkVvenFFdGE1TmdoLW5DY0lkVGpHbWdBdWxoMTlXNjFJcmFkTHQxQjVVenRtc3dKMFZ5clhRdjJwWUZZb2NHM040N3lDNk1MYTVqY2x2eTlZSmJXc0hkYzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOUVdZV1VIRXQtMkdHZXJRaF9Wa0psMldJdWVvaEFNUWxsWjJ0MFc5VW5KajVvRC0yMDl2WmtaOWpqcWlsYlBYRFlnQzBobGxhX1dIemp6UXdvNzRFQTJBOG9qWThCbmRETC1OYjFiS04tZzN1VFVBWDZfY3A1Yi03ZERiUmhoa19ILVVpa3F3bzRqUkE1NVFzdUYxUmZOMlllakloamFGdEVxQUJfTnZqRFdRVG1xcWdXNE1BZ0NZS3NwTk4temc3XzNkNFpEZFgxdURuMUVB?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>46020.44152777778</v>
+        <v>46021.1971412037</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Independent fashion shops see Christmas sales fall despite busy city centres - belganewsagency.eu</t>
+          <t>Governor Newsom Discusses Ending Organized Retail Crime Rings - Mother Lode's News - myMotherLode.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 09:09:00 GMT</t>
+          <t>Mon, 29 Dec 2025 17:10:11 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQbk9iZElhQzBEZ2hiN0xPdFlPaHJ5ZW95NXRld0JRdVoxeVdncUxJMkx6UGJxUndoeGJxWmtOWGJ1LTlhSkI0YnZVWVlCdjZSQzI5b0ZEdFdlZTRKYzk5LTJJRmdueEM0ZFhja2h4bzc2SEtYNUw2RnVxemtIVDRVNUpTdElCODV5UmphWHFGU2gySGpDV0lqV2daTV9LcEpUaGNjY25WOFRUMFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNaXYwM1JqRTVtaEFobXhSbGpmSEdZckoxbWdGNFZ2Q1FpZHNId3lWdFBoenBvQnlDMkc3dmVyYWZXb3NfdFl3VmRmNXhtMFZaNjFVa2lVUWRaV2M2dmp0ZGh4THhFM0Y0d251alJDQXZlMjF5b3ZTTG9ZZENfMjlnVmNYdmVNTGZtbHZqMFlTRU5udzdxdE5FaHJDWGVjcjQ2eEVxclRmOVF1dkE0LWpCaDctWXXSAbQBQVVfeXFMTWl2MDNSakU1bWhBaG14UmxqZkhHWXJKMW1nRjRWdkNRaWRzSHd5VnRQaHpwb0J5QzJHN3ZlcmFmV29zX3RZd1ZkZjV4bTBWWjYxVWtpVVFkWldjNnZqdGRoeEx4RTNGNHdudWpSQ0F2ZTIxeW92U0xvWWRDXzI5Z1ZjWHZlTUxmbWx2ajBZU0VObnc3cXRORWhyQ1hlY3I0NnhFcXJUZjlRdXZBNC1qQmg3LVl1?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>46020.38125</v>
+        <v>46020.71540509259</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brussels sanctions, fertiliser wars and European farmers paying the price - Brussels Signal</t>
+          <t>Stolen shipment of protein powder worth more than $500K recovered from Bridgeview, Illinois, warehouse - CBS News</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 10:55:50 GMT</t>
+          <t>Tue, 30 Dec 2025 00:54:00 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPVkczd0xBQU91bUFQbkVGT3l0VjVmODJrWVoxU3ZlZjFXVzZpTHJ4NzUwLWtnc25zdnNjNDBsOFI3Q2tUeVdxWnRWRzgwMUhTRklZMkwxMzYwT2I1WjFHVzM3c2MxZXJhWWlidWtMel9pcU1wNDJTeWV0OEhGWXgwNjQxRTRINFR2SzNOdTNLX2RqTF9ydlI1OVV1NmVyVUs2MnFSM0ptR185RGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNOU9MUVRnOE5QMkhsdG52N3V0a1hFWTJWTlRBcVYwNUlYSjNzeGhpamVqTlpyaHU3ZGhSVDRadGZWWDBCeXAzVVNUczI5VnlSLUgxNzJkbkphWGJVaERRSk9oREFsSDM2VFhabjR0dUpDQ3lBQk1uUTdrTDg5Y3huQXJDVnM2SndkTjNMazRycUdDb0tRd2FzN1l6dTB0aHVheVE?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>46020.45543981482</v>
+        <v>46021.0375</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Activist daubs red paint on the front of the British Embassy - VRT</t>
+          <t>New PSA warns consumers to beware of gift card scams - 95.5 WSB</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 08:55:14 GMT</t>
+          <t>Tue, 30 Dec 2025 02:27:00 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOZ01JZUN6dFFEOG56NkJjd2dBNVNpWUt6cVZMS2tPanBsN04wSjJHRVpMZGw3TzdTOG1vTGVGNFU3TmhaVjI2SnFBWVBzcExJR2xQTThqM1gwYUJrY0xrNUdPdmlYcWNiRTJNSGcyNTVCMm93QWVCN19icVUwd1cxVk1JSXIxRmowQTBRMnVZZ2E0dGw3V1VnSlNFU2FYb0kyQ1FJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOcUpCdElGVEsxcW5NRnVoVVZFUUcxOHM3RUlMTGV2Sll0b2tuZ1hyZXcyZEt6MEY2eTlZYk5VemJuREduN2NzcUY0dS1qSk50MEJFeHhZdnhNMS1EdVZ4enA4Vm1ON091YjBoelJtR2NrRjNSeFItZlJHNlVSLUM3NF9kbnluRXVpdTZhbjRjNHFVd3Y0dEJMNDdHN0wzRDg5YS1keDlvamRma1BfWG530gHDAUFVX3lxTFBfR1luOFJYOUEwZTdDZWNERDhJT0E2YnFwa0hncG9sWjRLdnAwdVUtempiaEduZGVmeHM1VVBMTC1XZnZjaUxLWDN2NG9sX1VkVS1BLURMM0pCNGNTVkdDNVVWZVpPWWtGWVlZQjc1SHZoUmdBTEg5d01CbWxDUXkxU081SzVvT2VXMGZQYUtmSWpsR1BURVlSTEdSb1cxbjF0cDIxcGtlampjYjh0ZjZid2JQLWh4NWd5YkJXWjNXRkt3MA?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>46020.37168981481</v>
+        <v>46021.10208333333</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hoti returns from Brussels: No compromise with Serbia! Only mutual recognition. At the dialogue table until an agreement is reached - Balkanweb.com</t>
+          <t>Transvision Vamp - Turismo Madrid</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 09:53:27 GMT</t>
+          <t>Mon, 29 Dec 2025 20:33:01 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOQzZoLTI2QmVwY3FyZmNFTUtzUTd0Nk9rRGVsVW5kb3VBM3pibG0zS2Q4eVdYYnVwem42d1JHRTdQdzA3Tmo3WFlQdTdldUNUdW8tdzY2VjI2dGpwQ2Z2REFLb1EzYjdfNlREZzlSOWhQMUJsSGNNdmliT1dYd1JHZVM3MnFVSWxzOUwzUGsweGE5Mk9XbnR0Nzdab3VOTk9Ja1QwaThzU2RSbXRtc3BIUmU3VlNqTXN5R2JRdVB1eW16VWFsb2VxX1pOZ21pUW9LUFJ3NFh3dWpINEFDV1NRYkZ4d1U0b25fZWQzYlFtd1lsUnB1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1wSXVqRkx1ZFM4eXlpeGtPd3FkeHBuVnVkcTl1X21sZHN5amdrcmNzMVZGbkJRV0x5Q1A3cnQwYXN0SDBCQ3VEMWdCOXdsYXpfZ0NxVzRBUG8tVlo0d25vWFhvU1FDdWROVTJtOGc5TmJvZw?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>46020.41211805555</v>
+        <v>46020.85626157407</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>What happened overnight? Police blotter report for Monday, December 29 - Newzjunky</t>
+          <t>The Incendiary Season That Made Explosion W - Horse Network</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 12:24:00 GMT</t>
+          <t>Mon, 29 Dec 2025 20:57:51 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQS3Boek0wZXdsaUFnTUV2dmwxWllNcnRiWjdzMTl5RzM5dzdtb0ZJcExKRmtvQWxkZEZFWXEtN0R4MWtFMVV6Yy1PX1EzUHBaVk45TlhkTFd2RExnYTRXYUtlNnJsbi03eXJpeUZOenBTWGZNZnNIQ0FxRE54OFltazVja2U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPRXRRRVNaX2R0MlAyYW1tbHd5Sm5ra0NWWTZ0anFyRUdCX1FpRGdPdFloSlIxc2pKTE1pRzBFLU9XNmFvWGlITUloVExUR2ktWnFFVEFuYkw0TnBEa0FyenZMOTctS1pMREtXQktQQUtfdGFGLVFGRjVYV3VldWhfQ3NkUQ?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>46020.51666666667</v>
+        <v>46020.87350694444</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Police name man found dead in Co Down - kildare-nationalist.ie</t>
+          <t>Man Utd ‘close’ to next exit after Rashford as Juventus look to add £72m flop in double deal - MSN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 13:01:27 GMT</t>
+          <t>Mon, 29 Dec 2025 21:00:50 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOd3JpNGN6QkFpR1FkV3NLeHp5N0JwakxwdjJOZjR6RW4yZC1ISkFjMXY3dE1hZElFaklMOEV0a2s4YnUyNVhOZVY1V0NsdE1PSUVWek5RUlQwc3NWVkJJWmpNUVlFX2VIT2FaN1E0eE02U1J5ZkJ0NDBqNExNcXBEYldvYTdYbXFTM1g0SHJmVGhxc0o0WURtSg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wJBVV95cUxQb3JXeGRLYjdSTkJKRlc1T1JTZ3pBX1BObEZTdDBCY1B3OHVpOW9fWVJpeVZ5VHlGMThWLWxWcm5lZ1B3X2plOFoybEJzTzJCU1ZDLTIxTDhKajJQMGFaRkwzaXdqOGxEMG4yWEtYUG1yYWttYktXd2lwcnhYS19lUXZqVk50RkhreW1IYzNFdlpWTTBWVDhMRXJQM0tiZ2dHbTd3el9lSDVBalprTmM0bEhUdlhYd05BQWtqaWdmd1F0VFNVTjRqNzRNNTlRVlM3SHhSQWw2N1dxQy1oU1U5c3RvZW5GdnQxLVF4cm1LQTYxYmd2LUdtNC1zMTEyMUZNQkZqLWE0Rm9TU1IzMy1BMllmS0FyVjVPRzZLT0RLUGhMWWptWFlJZ25NVzJ0QlhoZDEtQ1lKci1UY0lZemhwNXNTR1I1dnZJTUtQeVU5em1LaHprYWU4aUpqYkNlZkptamNCazJDck5sMk0?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>46020.54267361111</v>
+        <v>46020.8755787037</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Applications remain open for fund aimed at supporting historic buildings across Kildare - Ireland Live</t>
+          <t>Live updates, betting information for Texas A&amp;M basketball vs Prairie View A&amp;M - Houston Chronicle</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 13:33:40 GMT</t>
+          <t>Tue, 30 Dec 2025 02:49:26 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOTEZiQS1TSXpxSUd1YWFHVmlHOUViT3hzSG1VYVMzUWhjUHZPd1JDUEtTSmFlcjliWjBKUkNqblV5RU5HV2lCRXc0ZFZjNFk0ZFprd3BuaGRXSXEzb3VnNktLRkZsRzFuN2dTeTR4SlpIaTF3S0hib1dwTFJYVU1SX1UzVS1KUnBjQ0U4clk0eUJrRUREb2ppTjJnUGFZMWhKdThRZFdDVkEzVjA1VXF5ek4zZ0I3SUc2V0VyX2J6Vk5wa2JIWi1COHRrWnRXUlhqOXF3blV5Z2VGa1F5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNeFBqN1RTenRlWUlYZkFwWGZyR2tETlV5T2FDZmRwME9BR0RqMGxJV3c0WTlOczlycXFVVlZQaHNnbzA1UFk4RVU1SUI3SEs0bFlaX1JtRFgyc3QtY3BFenRsQXdnYm1jOVNncng3aHRKZGJGM0tyNHJCZjkxVjNfTmpXeE03cFh6SjNubU1kakZ3UFY4OEJFMmdpOC1GNmh6ZTFTMERmNlo5ajRTQW9WcTNvR1F1NmdiZmU1SkFB?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>46020.56504629629</v>
+        <v>46021.11766203704</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Espanyol supporters’ club urges ‘cool heads’ ahead of heated Catalan derby vs Barcelona - Barca Universal</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 15:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNQ2RDWjdoT3AtSzNSbkFYVU5tTk53MnZ6UDVEcU5uQWZoTkRpQTVPellwMmk0UWdWT25Ya1YwVUIzNDhvZHdIa1g1bWVVSWRxNlhWUzF6XzF5ZVdaX1REbkZHQ3VoemNrV1lNNl9wRFo5OGxvdVg1anZmeFl0WFljUUZVendrRW9OVFdWUGZ6Y2dCNkktT3pVVG9wUExvcGtGaGVSc1pBLUp6NXl6RmJhamxn?oc=5</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46020.65625</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>LIC Hosuing Finance After the Scam - Fibonacci Retracement Levels &amp; Explosive Capital Gains - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 01:55:38 GMT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOQUtqRUlQdS1UWklzckFsU1VKcDNoeW45UEN4NEc2WHpObVBMZjZLVnBFeWFaU2lmVzQ1OG1QX3lpYmtyOEZiSjNxYklfa2RhWDBBRDIzOFRTb3IwMFRDNzByaWtLbGR4X2xwRWVxUWtXT2RUcU9ob0o5ejRqTV9mRGp2OA?oc=5</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46021.08030092593</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Luka Modric scores long-range wondergoal to help Real Madrid beat Girona 2-0 and draw level with Barcelona at the top of LaLiga - MSN</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 18:50:55 GMT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-wNBVV95cUxOZUl0ajg2NkN0S2tPOXBJblV2ZzFkRnEyUWx1aHp6dWcwS3dpSkNUdEowMWNjU0JhUjdYNmJiQW8wYko2eDlkeHMyLWMwTGkxTkU3c0pzN3lsYlRhYjU1REtuRDFleVlnTnprOVdpRXVYUTJaVDYtdkVkZ28zTldzckdtSzl0eV9pNGdGNmtHcl9pb19ET2ZXdGVGUm41WVFrbk1Zbk43YnM0U0cxRnVQZXNJenB2NEZIYTFnUk5BUjVFaGN6MjFtdkdRdFpmRlRGZjR5dFpKMzJRSmVhYU5uVUtkRTlWemFCZ3lZb280ZmU2YnAwdG9ES042YV9BNW9JMVVRS3psMjRfOEhJSzQ0VS1PdG5RbUk2WnhrUFFnd1BQUHZNdE1selFqM3V2OElqNGN5ZzhwMFdLNERUOUlaaGNCQUVVaU1EZGJVZHNyUkxBOVplS1Npa0luS3JNVmdOWGJwb3RROHVQVE9kTkdLdkc3RkhUQzJYVURjYlE1VHYzZVQzei10a3U3MTl1Q2R3OXdlZ1JwRXFBS1ZDaXJFQi1jakp3QVBYQ21YZEVwQ3JuY3RScm4yalB1ZHlsUjhCS3MxUkUzNDlxdXlqWHY5bXB1NVZHcG1FajZHSEtVM2ttUkpWdkN5dXc3UTVoc0hwOGxVS2hER09fbUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>46020.7853587963</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Kuantum Papers Limited Stocks Attracting Dip Buyers - Market Breadth Indicators &amp; Explosive Capital Growth - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 19:55:06 GMT</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPS3d6NmVoN0tYTnRTekR3N0lrdVBoNVFMTVN5UlZfLWZnXzFCU00weG1qZXlnZGkwbHRPV0FyVHA0bnIxTW9Tdkd5ajJSMWNXcFdKTnJpMy1lY01VZHlSYl9RUVp2VV9FdXd0dklURmdGZ0RwWDlLeU5HSlBDOFp1WXB3YU9kak1PS0l4UmdRTDdaZ3FXZXB0WjRn?oc=5</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46020.82993055556</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Medieval Shipwreck Unearthed Beneath Barcelona's Mercat del Peix - MSN</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 17:09:11 GMT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxQaVhCb0R1VU02SVNhd1dyNXRJLWxiVml2MmUxbkpwQWozaHpaRzloRGpHUzJiY0otNGdaSkdhc3Bmc3RIQ1VZd0pMcU44M1J3NzdzTUVEVi1OSEYyWjhDamVfT01ydzI4LWQ2a25weEZ6Y3BRTmF6SmIxQXdnTEYtbUNzRFB0bGdRckJQMmdLeHdYakUxWVgwZW96S3NtTWxfMTFqaGdTMHJOMzFIclBxYWpteHI3R0tMU1Y4VEVmOVJjMDVTTV9lcVEtTHlleUZKTG5nYmRSbkQ2ZXJJVWR6ZFkwUmU0Y05pb09SelZHVF8wc0RSQUdHci1NT2ZOSUROcnRfb2lIQVhNSHpwOGtWdlB5QmlhNjBpRUcxRHBZMEJyTzdQWHVhMlprRFRlQkotVVVGLUtnSzNRcDE5cTNidVNaZ0NybGc?oc=5</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>46020.71471064815</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Blair refused intelligence-sharing with Ireland over Sellafield threat - The Wiltshire Gazette and Herald</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 00:09:45 GMT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPcGlfcWdxcTdVUF9RWnpYUEJlZ253ZU5vNWQzN0dRWGo0eGtJTGs1MTdLcTlHd2VuZ0E2Wk4wblJPX3E1ZHI2Mmh3OVlsUWhPa1BfN1cwYWY5TjRWbjlVSUZxM1hRN3cwcjZnNkwyOHZKY2d5am5tYmJpYmtfU3l6cDM3SENUQ3lDdnJZRlVnOWRxeGhyRWJELU11cGRwT1NUSk85VmVFZlVUVHJyUXhQWDlFemhYT21pdDE0?oc=5</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>46021.00677083333</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Osel Devices Limited (OSELDEVICE) Quarterly Results Are Out - Sector ETF Performance &amp; Explosive Profit Trading - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 18:36:55 GMT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPM3JpNmZ3TjBQMkhVMFlqVVBVVFJGaFVBdkRuSDBEWDU0ZkNaYTVmWmpWWnYyVmlIOWcwdm1mV3JHbmRMX2xraHBEYy16VnphcDZNS2ZLYVNwaU9vSjEyZUFkZ1o0N2JYeGZOLXZkR0l2YnZmbDYyMkpSeUR3aFdQaTJaaFJ1SzlaVDI5UTNUVlViZXhlOVROQWpxYzlFRHVQdml5ZA?oc=5</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46020.77563657407</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Barça. Crazy offers come in for Lewandowski - MSN</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 15:08:34 GMT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOcnpoSTR4NXNyZzhCb2libmJ1d0dyaG1EbXFOSmx1MV9IZDQtakk1ZUI0c0dRcnBfc0djLU5TQkE4Q0lCemszMFg4ZkZXbjR4d2VUeWpjeHBNd3pSNW1jX19Bc0lBMzBPTk5HTVFDNEhiTG9WYjl3QW1mYm1MZTRKVm1wTXNhOUpPelhkcEExQTFaUTZVWWE0WV9IZzlVNEdX?oc=5</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46020.63094907408</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Barcelona boss dragged into explosive fraud case as investor demands answers - Lentedesportiva</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 08:17:26 GMT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOSFNCRkVjUS14M1ZCaVZ3SWh6WEVCNDF5RlRKRWdkSTYwdHBrUVNvNGpLcFdVaHR1OXF6VDlCQlU3QjhBRjhOYzdZUDA5SGlPck04OGZCMmVEM1RJQUs1eXUwc2xUV2piV0JWUU1teGVMUExpaFlFdnpGY2Z0T3JwanFkeG10eExyd2piZmNLamdkalM0WDk2Ql8xNmtFMGxaZXU4aS1rdjc?oc=5</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46021.34543981482</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Murcia vs Real Madrid – Preview &amp; Prediction (Dec. 30, 2025) - basketballsphere.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 14:59:21 GMT</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOVVUzV2RFT3A3clE3OG9RalpLTEZubWpzQWM3eG1DSWVvbmE1aTNVZkVlcnhOMDdGNFZBdkdKelB6NGJKdWQtS0UzLXNKZ3RHUndNUE0yMGViTHZPX18xMUs3OHlWLUJBdUhMd1NScmh4czVvbTRLc0VjUHNUVTdXY0QyVVdBdGxUdVpQTlRR?oc=5</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46020.62454861111</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Village Search Bicester and Kildare</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Lululemon founder Chip Wilson launches proxy fight for board shakeup - Reuters</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 21:08:01 GMT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOY3NHbEFJU1JxWk5xNElPdGxneW9PWV81MkdBbzJnRi1DVlJnUG55bHlab1lSNVhmSWtzaFBzZ2Vra1ltWEotM05CQmdwQTQ0cjJURUpjY3h5ZGlkTVg2Z0pzR0lNZ0twcDFwSnZrYlRqUmEtdW1wT2NFeUZVU3R6VkdveXVKVnd6V21meTQzZXBINkFtUmF5VDR1VS1FeE9Qam92dzBoNURqV2FnNFFZbDlDWXRtNWlfUVhNUkRLSWpsblVkbnJPaW5DMVVaa2I0YWh2MmdndmtDX0QtMmc?oc=5</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>46020.88056712963</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Village Search Bicester and Kildare</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Elliott builds over $1 billion stake in Lululemon, WSJ reports - MSN</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 01:28:35 GMT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxON3VTNWMwdnZZRktfOXRWdWVfa0EzZmYzRm02TlZrOUIyMFliR1MzLU5YWmViamhrTlo2Z3ppTUpoYnZmVWt0SjZRS3VtS05pbkx4eWUwQTVlczdXQlNGNUd0SHVIcmNXMWk5ak5uWnF4azE0ck1Rd0NDWDY0MGlUUk9qYzE0R21FUUQzQ21VLXlOZVpnQmtPTTRBM3dwZDhZTHNFVGVwVVpCTzU1LUQwaS1RX3k?oc=5</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>46021.06151620371</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Man in 40s rushed to hospital after Christmas Day stabbing - My London</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 07:59:54 GMT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQLTN2U3RwdDlhSmp6TEVLSFM2b2JMaUxNOGxkOXYtU2F3MWZ4TG5uSW5aZ2FvZF91czRpSFJQNW85dmR4NzFzTlVYemRZUkpXODZlZmgtTFRYTXlrblZKdTQxUkhBUWVxOTJmSzFrVDJYcmlFREs5eGpGQkRmVDZYSlJqcm5qMXJUQWVn0gGQAUFVX3lxTE9HQ1hHcWVaNEcyUFV2R0FCaVl4LWRlR1BPZjVWZm1hT053c3BnOW1rQWdGT3JvRXdydkc3ZFFmbUI1a2xZS013bGlleF9hS0YwcVM0THYwdVdVX0RwV0pXV0ZFN2tReDR3b1g2R2RBanIzWE51QzYtX1lDZWtpdlFlUnQ5RDVzYTlqc1VDLVpfXw?oc=5</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>46021.33326388889</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Police fired twice during fatal shooting in Thetford, says IOPC - BBC</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 19:47:35 GMT</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1HTzlEbmplTkdmVlZCNXJkSzFWWHY4dWF3YkFDYXEzSEVzenhCRjM0OG1FUGlJQXVJaE9vWjRfcGZpWEp6Vkc3QjVidldXZjdZRGlfSEIzZmI5Z9IBX0FVX3lxTE1UVFNJSUNybXV6aWRILThrbmE2eVRUcjRiRDgyX0Z3eHlZX3JzcFJnWEY5N01fcGJvQ0VNbktPNjZzMGFfWk9zYjBiTE9HSGJGblpIMElIUXJ6bVZwZDQ0?oc=5</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>46020.82471064815</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Major road reopens following a police shooting | ITV News - ITVX</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 19:02:14 GMT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPUTdLcWg5TGtaa0psSkFCRzYwV2pHbUFERVkzb0NfU0JNTWhQUWo5ajJYWk45ZHY5RlpyTmZaaElnLWlWdE0xSlN6dHdKenZFMFVqOGVSWGlsNFNHUXZZQzRnM3AyZGFJWFJ6ZmJtcmE1NDR0UV9QT3p1T0JHUzI4OF82dU9nQXVGZ3VmQjFWZlB0WTJlZzBMeXhvSFc?oc=5</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>46020.7932175926</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Dramatic images show scene on A11 after 'gunman' shot dead by police - Eastern Daily Press</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 15:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOVUNzMnB2ZzA2RmJ1a3ZHN18yRGFGazg1TkpmVERPMF9aLXJNRi0wcHo1bTFCUkJobUV0LTNjY215QlJRQTdtY2ZHWUtVY2I5S2hjQWNfb3l2SmxEbkhyYlN1dE1PNzZvV0JGZWRFVVZQeTVBWERiRXhRLU42d3dIWi1ZV091NEwzRlhR?oc=5</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46020.62986111111</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>‘I wanted to detonate a bit of an explosion’: Creator Steven Knight on season two of Disney+’s A Thousand Blows - Express &amp; Star</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 06:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxQWVZJSXE3X0l0Qnc4dGZNNUIxNFIxX20zcENXakpSRk9COFBlNXVUdl9reFNEWFFSN3RySEpZNnIxRGg5U3lGTUw3S3prMUpjaUNoUldKUlFKU094b0luQk5hMXJhZmxTdGJoajRMNVZXZ28ybW43SE9GYW9qM2JmZWlvQU8yLTBHTDU4VExLeExNR3FjV1NCMGtKQzhicm1XcTJaeGVXNElOYzRDSWVqYWllRGtBdUFJN3g4TWFVcVJsVXdhSk1iN3JsODNRX2tLejZiT3Z0ZDE5MmNlY21Rc2xQSnBiNXRGNG13U0VHQkV0WUNiQktDNDdrYll3UWZ2?oc=5</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46021.25</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Chatham youth arrested for London shooting - CK News Today</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 19:20:57 GMT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxONWRTcG5CZmZaM3FwUUhfSGdUQmNtN2ZjZ1NiY0U5RUpsTUZMNHFyT3c5YWhHdW9jUlNJTTU2Tk16c3FTTjhicG10bjVKVmNfTmtLUDh6dUR5ZVU1UHRzWkNXTF9IZjYzNHZpb0dHbkZ6Z0JPbzlJeEpRaW5pNXZmLTdVeFhqZmJYYVYwc25HT205amc?oc=5</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46020.80621527778</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Blondie &amp; Garfield - December 31, 2025 - The Korea Times</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 07:01:02 GMT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPcVdnaHM2eXdWQ1dEZUxLN3ZxSnEyQmVOMF9GbHQyV1YyRm4yZEx1endfbExiY2FPc2RzUEJqRUhZMnE3RHJFeTBXVWVuTXYtRmxtdTdkT0N6ZnUyUHhVLXVaRnI1RGpobDRpclFDMGw4V1lJOHRsVDNEQ1piWkNCakY5TjEwUdIBiwFBVV95cUxQVjlzQzJxT3JJUHpscmN1bmRDazFhcmI3dUdteXJQbEctV3pYN01oVnV0V09rekFhQW5mcmFKTWlocTZzRU5UM0lyN20tcGE2cGZuMDc3ZXUwNUZFTjFWZDUtWTM0N29vNzlZQ01RWHc5bjk5ZzZ0SUlSUlUycm5PN0Y2M1c4ME5RY2RJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>46021.29238425926</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>GBI investigating after man found shot in head in Dublin - 41NBC News</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 01:51:22 GMT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPcGJWMlZ6MzRuZFAzRFFhb0N1SXRDMzQtTzRxY2xISGUzZmxhZFB1WGZoYjhLcjFjX2FudjNMNS02Q0Q5Ni1ZUkdEQzREcm84aGhzenBhUjZWM2NtZ2dzekw3V0tONmxWUUMtNjlpbDk1TlhPV19JMUZoVFV5TzVwaVd6Nno4Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46021.07733796296</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Virgin Atlantic Supercharges London Heathrow-Bengaluru Flights: 11 Weekly Flights in 2026 to Meet Explosive Demand and Enhance Global Connectivity - Travel And Tour World</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 23:28:21 GMT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwJBVV95cUxQVS1fSHFiVFB2T0hZVFJzNkJ3NGZIaDdBbl9tTHF5MW1scW5ueG9sWktZME1mVUp1OURBdFBKVkhfcEUtMWhSdTEwXzVnTXdBT21XdEtyZUFxdGV6YlpqZHAxLVVNNUp5dFMwbkNGaHhJNFJQbEtXLW9UdW92WklHaU44RFZ6aVRxU2VVUXE5XzZKUm1PZ19jZVVPYlItX3pwT29DUWdDVDBmcDF4VnJDcVJUYU84Rzk4LXBTNmlTcG43OVZ4NVBJR2RhMHRQTG1yamhfWEdzOURBR2tOTkRpLTEtemxsXzdXaklOTUNBUGxfOU1BZU5NQUkyczdUX09XSlZvR2YyLUtrVl9QZG4wTTk0VWcwdzFhLXN6c01uTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46020.97802083333</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>UK snow: Five-inch snow bomb turns weather maps white as 'Nightmare AFTER Christmas' forecast - The Mirror</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 18:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9Nem1TUTN4a3oxZ3ExUnZVRXprQ09ZdEswMGR1a1lGd20tUDFFeF9ydXZYUV96UmNUNVhETlJuRHRWOEtKYjMwWlJ1Y3B6WnJDT1JIZDlCSUpWMl9xTi11akVsOE1KaFBPM05yZHRONVRqekh3OHJsbtIBfkFVX3lxTE5WQXpJSFFYVW1TVDRGZmwyNGpzRXdTZTkxVXdzZXlYMFc0ejNxZWZKbjNjaU52MWN1VGREZlRXd3Z5Slp1RXZtZjlhV2c3OFJqY210aTBoM3FJUnBvWnpZQ21ZM2lhdm1ETkJiT1k0bTR1dmI2RVdTMFU5dHFoZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>46020.76597222222</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Appeal to find missing North London boy, 10, last seen near London Dungeon - My London</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 19:53:30 GMT</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPaVhhMFhWSmRUdlV0Z3UzZXNZYjFWQ1JzY2N0VVdfaG1pQ3ptZW81OVV3LXY3N2VPa09FQmx1ZHJweC1PVlBqNmZONTEzbUJ1bko1UmtVdjJHZUNSQ0dkQjkzYVR5SktkUHpwZ1ZvUmNoMmtlTnBZT0MzNnl2TG1JVzYtaEVzZ3p2cW0zV3lmcnV6WUVl0gGaAUFVX3lxTE1Wem5wUk04eGhVU1RPWHhIT2t1UHczN2ozdW1SMkxDamcxNjNtOExFcXo2Y0xkNFJlc2gzOFNwb2x3SnlzQlg1ZHJScFNWWFpxVnAwMEIzeFBFdDFTN0hQRFBvZmJrZm1heXZfQ2FXQVRWajhOZExDV0N3SmRFcmRqbkVCSkdIU091U3pEWEFoa3hBclhvNkVWQlE?oc=5</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46020.82881944445</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Live Review: Hanabie and Lake Malice | Electric Brixton, London | 07/11/2025 - Noizze UK</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 14:53:00 GMT</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQamFtUERneE5JRUJGVXN4Y09teG1famh0WmRmOUtZMjJIaEZFMkNVWEV3dUpjalZwWGdqUzY0bWhuU2tPQTZRN0RmaWtTaG40NVZLandGUklGS204MFNuM0hzRURXdHhadnpuUDg0UDdENzlpbUFEUGtPZi1WUXhXaHZxTUhqU2NHWjAzR1FXRjZPMF9hVzdQWUZNTWg?oc=5</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>46020.62013888889</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Erin Doherty leads gunpoint showdown and Stephen Graham returns to the boxing ring in explosive new pics from A Thousand Blows series two - Daily Mail</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 14:59:01 GMT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPV0otNFVpWlVmakZMUzZma045aXd3Tk5zWUYxMjBjWEN5bUxpVndiU0VhNTdoeklQMThYdTd1aEFjQlJQNG1JdU5qY0NiVkxhdlQ1aTlfWjlXTEhsUG15Q1doUEpmUXg5T3ZnN3NCU0kwaXc5ZktuZXFLdFBRRHVNdDJRd3dmZWh2U0d6OG41X1R3VXdETFJxZWt4MS1NV25sWFlGYVhIdVBUaXI1RzZwVnZFWkVmUWFIaG9Fa0JYSWEwY1UwTzhldW9uQXJOTjNRRUU2eXVB0gHbAUFVX3lxTE5RVm9pM0l5cktOWHRpOXluc2pncHl4ZzNua2lnZmNxd1kzUTREU2VSZERXMnA0eHZWMnFndnJkNjVHM0Q5WUx3OE1JZmRuNEpBVDhxMDFzX0tLT05LdmZ2dFpnR0NpQjl1cWJScWpvbk9TYk9hMldFdUk0NWl5UDhqWS1xcWV5aTFHOE1scUNrd2JJa0M3R3FnNkctamt6aHNyelhiMWZQOW1seHowQ3U3RkVsVWZkUDFQQ3p3OTh4a2tnRTNLc1RMeTBTR3RwWDhnYjNjVlViWXd5RQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>46020.62431712963</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Live updates as ALL Eurostar trains suspended between London and Paris - MSN</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 04:12:01 GMT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gJBVV95cUxONmtQaWZYZnJ1VEZ2cVZXdmZ4QmxCVEdFM1dTM1VaLUM1NGhGVTh5VDVaVVowbF9TZ0RfTV9KWTRCVzlNSV9Nb2FQd19wSE9RQkxUZkZvcjdMcmg2M1pyS1BUNTAyTEdvUmdBT3lkb2tyMm9zTFFja0xCWWYyZ1ZaWWtucElrMm5yOEtnQV8tRHZCX3BaaW9GakVRYnJCdjhxemlIVW5Ic20zbUFmYlJZVGE1RE9LcXBlbF9tMTdZZGlpYUk5YXdWUllhTmFtbTlCNGhsejRLUkp5b1Z3eFVHRkQ0OE1aNGJ2dE5xczBoMkpRR3dubTR1dHBKMW1XYWNfUHpGWEZGOC12Tk9oTHpZMUxPR19OVGpCUUswanV6ZkdjSURGUWkweDFNdlRCU3lkeXFpTHc1YnUybkVGTjBYZ0NuYVo3VmpCU3JHSndvbm8zZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>46021.17501157407</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>'Bomb hoaxer', 44, sent US Embassy into lockdown after 'planting fake IED device', court hears - MSN</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 01:34:06 GMT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wJBVV95cUxOS2dIaDFJS0lmNWl6MVFKVTJrVWhGRVFIcXJjZUxscDVTVS1GRDc2TWJtQklQel9JRXlSaGJUN3NZa1NoQ210bzJRTEJIcjRNV2w0T2JfN3ZBVVNjLWp1NDB0UUJlQnc0ZTdINWVNZzluMFlQUHlNejdjZjVZREdHUk4xTnZETkNDcUpsR1ZaR3d5VkpZX0FoLTlEMEJPNjM0aHA5bXJXLWY4aXBxUmFSdXdWTFRtelc2dDdzQnZxV1YyeVVLUW9tM0tYaHpTM2FYdWs5Q2lSbXFhYk9lYUkwd282UUxyYi1jOVY2S1dvcjRsMlpfRURET3ZZSjV6N2s4YkJKNnFZM3dJeWhqVEtVWFJOV1pHTVlVUXl2WjVhQ2pVNjk3Rml0cHV6X2p1clQ5eEZmX0ZLMElTUjdnLUlUclF1a0RMU0Nkb21wWGZJVlotVEZlOFVfN2NsaEgtaUNwT3ZFRkdaUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>46021.06534722223</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>TCAPS Accepts State Funding Tied to Controversial Mandate - The Ticker</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 05:01:47 GMT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPbllaejlrOFAzelhjQTRKdGlsZnRVRnB2Vloza0Z4akYtaEJlUXFfWFlyTUtWSTFySXA5TXYxYXNmSmZXdFFnTGl6WDRzZ25CX1JJSk5KTF9YaDJVVVprWEtLVGJXaUVoX3kyYXM3Sk0waEN6cm53Y1JXdXgxcGZWUUlkcXh4SGFweFQyWjVEYzBseXJVdHdGNGhB?oc=5</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>46021.20957175926</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Josh Hubbard scores 22 on 9-of-13 shooting, Mississippi State beats Alabama State 94-56 - Toronto Star</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 03:06:08 GMT</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNeHdFLVpuamVydWdnb3BGa1MzV1NiRTJyMUdQYm9NMk01U04yYVFnOVQ4bEpzaDhPRzRFMGpFLXgxSDctZUFCV28wZEhoRWRfMFdWbHo4b043aVdFWkNHSmcxWU1Ec3FYMnV0czFFb1hlMGJoQkpUMGM0dVdYM0VvZmotWlQ4LXp4aGcyLXd6Slk2VzFwU0RyOE9XdzhhWEtqU2YxT3FuT3dGZXRJenVJSmItakxZMEFBcWtCdVFmbHpGc0xVdXVOWXl0eUZvX3NwekdWa05CSmNkd2d2bnB0a0FKMUxONGRFNTI0S3gxa3VGZ2NTSFF3djFRLVU0UGhOOEFHaVZB?oc=5</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>46021.12925925926</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Prep basketball - E.A. Sports Today</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 04:10:38 GMT</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1kUk51Nm9Nbi1HNmJpa1A0ajRyeHRPUDlkYTllTDJIS25iY09GSWpKbkJjYkY0TGthd1J6b1BnS3BUNXVjdjBfWGJqbFlIZUxfUHIwOWpHNnhUbXlNeGxSUEJ5UExXZ3A3VTBIUkNR?oc=5</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>46021.17405092593</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>90 km/h wind gusts, snow squalls and a ‘weather bomb’: Why Ontario travel could become hazardous today - Inside Halton</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 17:52:00 GMT</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPNXY2dDlRS2wzMGFEcVdmY3JKcXRZT3Vxcl9FNmI1UTlPZGZwdXFaaVZXVnBpM1dZZFl1T1Y1YWZlZkVNU2xYQXdRbS1CT3g5cmpMTzhUVFhFdUdST0lxVTVDaV83aFo0UHZySW9vWVlMdGxqWWxWUWlJTXY0NHJ1a252ZmFGd2RfRW1VU2w0NnNxSVpOVVVYR29vdkNnYjZ2WWJmTEh0TTlLb2ROU2lVT1ItMW44eUZ3alNDTUNpT1FXQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>46020.74444444444</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>General Hospital Monday, December 29 Recap: Willow Keeps Scout’s Secret from Drew – Kevin Leaving to Du... - Celeb Dirty Laundry</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 22:30:21 GMT</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPOG9FcG53TUtBSEZXZTFvWTQtVDF2NE1ZMjJ4TS1ZZUE0N0tnZjlYNW4wYkY3R2lvc29oYjNXbVFlNE1QdkYzUDl1NUo2Skg2eHFLREpkZUF0QS1RdUJGVG4xdmttbEtDc251NDFMeFBraDRHZGt3S2JHbllwcURCWjFqUU1MNkZsRHFEVjBwZW5UWjVXTzZNUzBmVGtTQ1phZE9wSkRhVVFxZkNIV3RVMDhKX1Bxd2dXaEcwb0xidXY3OHU0YW83aHA3N1NfRXJxVXZQZGhyUDY0QdIB3wFBVV95cUxNVmcxeGpmZG5CWmpVOEh4cEtRaTZJdTlrRVBOQkh1Tm9wRWZHNFMwVXpjdzE4cTFMQ0VxaVBfTmZpWS11WXQzd0lXaGdUUlNtOWZScEE2dnlIdWIyTjlPd2YzbEpyTUFETm9qdWJzM2FSRmZJWlBoUjBDOHF6UWlrWmlsQkd6SF8ySHpHS1l1Ym5kckxKcG9oc0RDeE5vMHA0WDBCcEs3WVJMcEpkQm0zTWRQTEJJMEZXMThQN3NxV05XaDlPWFlhVi1VSFMwczhJN0xoME5tOVJ2TkJyUUlV?oc=5</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>46020.93774305555</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Durian Tunggal fatal shooting: Police send audio evidence for independent forensic analysis - Newswav</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 22:53:31 GMT</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQU3RHSWxLYWZoRElMNUpMVjcwMHk2WjFJRnctc2VDUzRHTHJhVXlMSFA5Ry1XOU5ldUxzVEozZ1NvSVctaGdYQ2EwOGNjb192RXVVWmwwVVpaRTJsZmVZSU1UTWdRWERFQm10Y2syUmpkbG54T0p4X3ItUjZfX0dWeTBFWG1xMkdRNU13YVRrOVdUT3M4bXpxX3JnMHRZZFRfbjJpZ1lBY2t0bThPR2tPQUxRVXBJX1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>46020.95383101852</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Kowloon Stabbing: The Shocking Incident Everyone’s Talking About!: The Shocking Truth Everyone Needs To Know! - sohh.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 18:26:35 GMT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOTnlXb3JOR09Ed0UwUlBIOVk3WDIzOFpIVUdqZEtWYWluVW1CYXE1a1RkeVgtVmk3dEtld0pEN3JidndfWU1DUnI0VDVHTGZSOTFKeWJXMmxtOHljZWJtTm1PRHdhNk9UNHNDU3BjQ0FqcFZmb21yZi1ndDNUajIyX0lZczVhRUtCd3FuSzYwaDVrUlhlRUtDZWN1bFllOVJOXzVEek8xbzd2TFJ2dlJjY3FrNjFzVV82eFpIbGpxRzdadGNpWFl1a3psNE9YYTBU?oc=5</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>46020.76846064815</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Authorities say Malian suspect in Paris metro stabbing is also French citizen - RFI</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 14:41:20 GMT</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPZHpwajBpb0NLdkhqOHJZTldzaDJOTVlUdlNBMFROclZJcThnNlcyUWZkNExpOHJsVHJMa1BEQWZGUHA2Uk1reUhWY0p3Z000LTY3dmJyd2hHMHpfVWhHX3M3SnZ4NnZLM3hDMXVrdG1lNDFuVHBKQmJYY000TUhEUEJCcl9ia2NNOXpMb3BIYzhCM042UkpSVWtjLUw0cG0tUTZNRUhQc0hwN3ZQcHRxbDZ2aUFDZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>46020.61203703703</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Taken 3: explosive trilogy finale with Liam Neeson on Netflix June 5 - Sortir à Paris</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 18:19:08 GMT</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPbkUtM1QtLVVtMXFHRjNmYTdVQU01SXE1TXlWV2VHRGtPcmJqRFJ5MzVRWWRlazRQYnpWYnNGVjh0MC1RTEJ3ZXl3dWdOc2wwdVVaR3V1T1hvYWtkY1l4bzh3V2FORHpXaHM1UGZpMVFVdDZEeG0zVklrVS05Z2UtUWFua19qY2taWEg2RzNNWEh0R1ptTjVTNC1MYUJfcHpWMWFMS1BYNmdpRDlBRVpDSjNiaGxUNTZQTjdTeUlpRUxpUEN1Z20tX3UwMjNCZllqUDJZZDJiV1UwYlNTNWtpcng3RE9qLVIy?oc=5</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>46020.76328703704</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Gamecocks Face UAlbany in Non-Con Finale Tuesday - University of South Carolina Athletics</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 18:56:12 GMT</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQNjJ5aUg0N1gtdk1kNlVjRFdac3JpUVloZkw3T0ZWNFlDOTBLV0pIRDloaFprWExFS0JRU0dhS1dBTWV3Nk5sS3RzWmliRk9YT0RsMWNqRzJhaHpFN3JLeEd2a1VKRktZTjhkSG40R05hT2NXd0xBdFg3ZjJaekYzbE5WY2JqU2FBRXRQWlVuSkM4UV9hcW5pWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>46020.78902777778</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Finish Line 2025: Shooting excellence, boxing promise &amp; stagnant shuttle service - The New Indian Express</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 18:13:57 GMT</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQMnp2UTlfdm53TEFudWpjSlVVX1dWcE5kT2FJV1A1XzJjMFZFVGc2dlRRcWpRTzV5cGo4Uk9KdFNtUjVMVE9BMVpTMXpweTQ5ei0xQkdxaUR1OFltNXZ1aU9PWkU0eVktc2w2T2RJby1EeXlhdDE2X2M0QmZGbnJBQXktdTBuaU01M3NwSGxRNFNJR1BLeUxPQTM4bjAtOWtpY0Z4bFUzYXJZelp1MVc3bGZmbmdoZkQ3WXFmTjBVV3BYZGFqQ28yVTlPRdIB2AFBVV95cUxORnZHZGNJZ09UV3JXLWhsemRzT1NXYjM0TjJENkdOWXZKUENfdzBlSmFEcWV6ME81c0tkS2pIWm1lZnpuTl9TMlV5MFF0Nml6NzlTazdKVjJNVmc0Q0J6aEo1ZDlWSFNhcnhUNzFTeWZURUhYV21UMXduOXhveHhyT0pJelJzOU1Fb05tZ2x1RTFrV0M4TkxtVy16NEhyY3JCcVFBZUk3Sy1pamxOTFdMNGxIME1BemFFT1ZGWG1uQjF6QTg1ZGVQUlF4MjFIOThkSU96TXItd3E?oc=5</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>46020.7596875</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Bail for suspended police sergeant charged with misappropriating cab - Times of Malta</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 15:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQY1N3M2NyaVAtOXpxSGpnT0hldkdReXFhTDMxXzRiR2RVYm1qNjI3U2dBQVFHbUt4ODh4VzU1a1ZsOERvOXlpV3BxVTlBalo1REFDa3QwNzZ6akRLd2pvbEJIRndxekNSM1E1cEFSaDhqSzU0NTl3OGVCTjc2cTZzMTdHYlM2Z19VQmtLR1pkNy1PWWdEX19faFR1elhSR1VvUWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>46020.63541666666</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Sydney, Paris and Tokyo cancel New Year's Eve events amid terror and stampede fears - Wales Online</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 02:34:00 GMT</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPX3RpOTJNUnlJRTRBdTZ5MERudnEzeHNwY24tVUxzeXJaWUx2Wm1UYnZTTnpUd0hYcm9XSXAyN21yaXFVQ2FfQVRBSFVjM3RRR1AtSmdjbHNCUHFTcm84b1JBRUV6cWNWLWxETk9aT1l5bXhsS0pKbmdyb0NTdzlpSXNDUHdiWjhrd2F3T9IBkgFBVV95cUxQMmZNMGRXYy1ORDB5SkJrNVdXUERkTGp5ZGVTYzFjZmtvc09xdFFvams0VU5DUHFIRVIxck02T0gtRnozNHNvUVBNMVNZYXlwMjdtclVrdWR5Z3dQQXZZMWdNTFpJTXU4RVZUc2htU242bElaVi1pRkZqZWQ1Vkw2S1otZXE4WlEyZ0RxLVVUWHFMUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>46021.10694444444</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>New Year's Even plans cancelled across major cities amid terror attack and stampede fears - Birmingham Live</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 01:44:00 GMT</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPaDJFcTlMakMwLVVEVTNWQjNMX2ExRDdWaWNMS3pwNnFtcG5vd2hsRUR2U1J6b2tWSk1pUGQ5R2U4YVFxa0VYMjcxNkE3YS10MFZiQTd3UXJtUUI3RnE2NXhDZ3kycmpDOHp5WFdNX1R6UTNiTlRxMnlZVE5oelhBV0lCSmp4T0JkTHV4aldULTFOQdIBlwFBVV95cUxNdGkyQm9BZG9ka09PS3pWSXZoUTNNNEs3eXlrMkx0ZkFmUjJSM3JFc3daMFIyNGluRG54V2xxemVnX1hnRV9fWGUyT2g0U2VJOF9Ud2NSeFNSTkhtRDBxQ0tnVXZJUHpWdml2WTNRWVlTQm5jY2VONXZ3RlJ3LUVCaldGcC1IeUJJcTItMjdhaGY2Vjd5TUJJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>46021.07222222222</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>'Father Mother Sister Brother' Costumes: Using Red, Tom Waits' Hoodie - Variety</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 18:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPc1h0dHN2RGE4aV9xeFowLXZoVVV1MEdnQXcwcVZmTEl0S2tqSjdTTmJnVXFTUk90RVB3RXBhZHE4dmJxMnZSLVdqazR6QzNiRzhQR2RjR0JsbG9INWNVUzFsM0ZpV0lxM01pcVJkUnNGYWlDN3pmUGs3MXlqd3cyaTh3eGw3bGFIcFBBb2toTktDLU1tTWphWmIxcExJNEppNDRmVmxqeEs?oc=5</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>46020.76666666667</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Russia Says Ukraine Tried to Attack Putin's Residence so Moscow's Negotiating Stance under Review - Asharq Al-awsat - English</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 15:52:08 GMT</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOOTJwRkJLVnktN1Y4WW9iVkFKeHAwNmJ4WFBSZ1VZaG9VZEk4Z1pnUXZYa0JEUEtZX2ZveWRKSXdXdUZPdjF6OEJfNDlUeThyV0ZYODRodHRvZEZSYzg2ZHpzeENwUmhkU2I4T0dmU19VM2NrdWJwT1VHb2YzaHFFclJHMGtVUTl4cnB4RjhhSjhDdG5kTVlBODI4LUNrbVlsRGZER1Y0UTFJSWEyZVdLUHFxWVMtelJvbnVZbGluZ0tfUWU0ODUtLXF3?oc=5</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>46020.6612037037</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Thunderbolts*: the MCU's anti-heroes back on VOD - Sortir à Paris</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 18:17:08 GMT</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNOE5xMjNTWE1BUkNjZXEzYUE3YUxsbldGOHFsRDM0RlczWWZ6ZkczTWo3NWJkQnJpend5emJ2Tm5vei1kWUlOelJld2VobUtNcmlEUHBabXRfODl4QklKNjlPN1NjMTZTZGd2bVJDQTg2N1lkVjcyMUI5TmdvdlBfRTFGZjhueURXX3Awci1qdmZUd2hqVTQ4ME1welotVW90dS1ZczVYeTRWbWxkekZ0am91cTlxeC1yOXh2QWJmU1JzbU5JLUFodDFvY2tTTlBsT1V5WmFjRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>46020.76189814815</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Trump Hints at Land Strike as Venezuela Pressure Mounts - Asharq Al-awsat - English</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 17:32:51 GMT</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNNFkxLVRnYk9CZ1RkYUdNakZBbVdpVVpwQm9sNmg5d1hPYlllSlkxOEYxQWZZMDdyRW04VnY4dDl5U3hHSnFuNnJIOVF5VXhGN3ZCU3JjcXpyMm5IMVhUSHFySEc4b2E5elYwS3VmcFNwMmVfMlZQSXBGOWtIQjhPQTFLVk55OS1BNjc4YWF4SHpRdkVrYkN6SnlR?oc=5</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>46020.73114583334</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>UN Chief Says ‘Get Serious’ in Grim New Year Message - Asharq Al-awsat - English</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 17:04:35 GMT</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPbmtUQWlrZzJqTHM5RGlIQUloUEZnU3o0NzdTclJ5ZUhWT25hS2EyVVZwam9oSGNkaTBJOEJwSi1sRlh4S3loMEFvcjVFUERvaXY3RzlPaFRDUWJlNjhjUGxMalZ3UW1YcF94NXV4Wmh3X0pqTXFWdzU2azZuaDFCbTFBSmpua2xNYm00OFVjQ2VRak5QODRxNUR4ekdCb01wY2NPZ3BBdURDMGQ2Qnpv?oc=5</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>46020.7115162037</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Groom in $59 Million Paris Wedding Set for January Trial After Firing Gun at Police, Faces Possible 99 Years: Reports - AOL.com</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 15:22:39 GMT</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE8zTTdLWl9RYWxUSlN5NUg4TFE1NFZ0QU9GMnVacHdEQ3FyQmRuTmI2c3Y5R2FicWxYNDlVak5hSUFmUTRJV1Vld3BlLUowWi1yODYzY2o2ZWVIa3NQYUx6emhLYUpoeHdzRC1kN3R2eDJrOHh1RV9SMEhTRnlrd28?oc=5</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>46020.64072916667</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Breaking News Live December 30: Trump-Netanyahu meet in Florida; US President asks Hamas to 'disarm' - Times of India</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 06:19:11 GMT</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPSU9iR3o0N2Z6M3RfZWtIdDhYeG83Wldab212aERGclVtdFpvOU1kMTV3SXJRUHI0TU9oUGpPZW5oNUxwY09hdmluelZGekhyb2dTcDA2MjhuaE43cVNmNF82Z2EzWk84ejFwazI4V25zcWswUTRRVzRkdi02anN4SFpOZzZyVkJNSGRDcGxXekJxZUoxX3dQTFJPNzJFdzRZajV2d2ttdDgzZ2xqdkcxY0pHYUVablnSAbwBQVVfeXFMTUc3Sm8yZ2Rob0F1VTl4dTVqLTc0dnVlc05mTWRqRmJLUmliRDFGN243Q1ZVUzgtcFI4UjJiU3pBc2xTaWdaMzRtLUJLWUlFTEZ4cXZyLUduTjBMTVZmWjNkRERuY0piUzRWWU9YLU94QnpNM3lidW9RTC1WbXdQa0N0ZTQtRzJnNURaOEZNcTFuZmNMX3ljaWhkZURlbXJLWVFHSlZHSl8wZjNHUk5BZExhR1JnTmxxRi1sOEM?oc=5</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>46021.26332175926</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>South Carolina hopes to find shooting stroke vs. Albany - KQSM-FM</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 00:02:42 GMT</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQRWFhYWtpX3FqVUdld0FBMUZyWWFwdWlHMkduM1BST2VQbHRuT25CeGN5b2luakVEazRaWEZ4Qnk1VURwY1NMZl9oczg0N1F2dUgxUTdMUnhPSGJMUVRMN1JCSlJWR0t3YW1nVU1xNWVPQWN6Y1BUVUkzVXI0bnpZUWhpNjNKUkZ0cGZKd2JCYjQyVU1EYTFBWFlocw?oc=5</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>46021.001875</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Suvidhaa Infoserve Limited Bounces Off Moving Average Support - Capital Gains Strategies &amp; Free Explosive Return Secrets - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 17:22:12 GMT</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQZDlZemhlRTEzOEwzclR1eUtTMk4zWTExWjc1YjNHa2dqdmJROE9ZTE52SkJ2Mm5YX01NNEdzYmoxRDVwRWtKZjREX3c2TW4yd2xvaERmdGFEa2JITHRrRy1kMkxzRWNPMlV5aHU0Zm10ZDF0enJiaW9TX1FaWS1za1Q2SmQwUU0ya2M1WG5KSlM5eWJVZ1JTQmQxenF0aE5DUFdDaWU0aWJqVGJIbXE5Mg?oc=5</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>46020.72375</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Price Clustering Detected in 7Seas Entertainment Limited Stock - Industrial Stocks Review &amp; Explosive Profit Growth - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 17:47:33 GMT</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNZVMtWGp0cTdTNlphYTEzdkd3T0pFeEczY3NXamQtc2VIVnE2cmFxcGdHZDRjN25TZ001TEkzN3JIYVVMMU5QM2s0eTNvc3Q4U0NBQk9hOUJQM0dGald0bWxpd1luc3NQQUFYcDVjdEZDSXVoZkFmSzdFdFBQY2NBaFVCOVAzNVRPbkxybDlaMWxvenJMVkZmeXVfeG4wUzI4UkQwdlRYOEM?oc=5</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>46020.74135416667</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Paris: Gare de Lyon partially evacuated after a bottle of sparkling water exploded in luggage - ENTREVUE.FR</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 16:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQUjl2VnlWNFVTWDRoTjhka2lzd25La1YybGVWZFFCeWR6SEczeWFBZEtLSUg4d3ZNSjZ6clBwRERaU1J4bEhxM0FZTG1vU0w1bjdLUWdkSWVWdGpWLWp1VFU5b0Qtb21BNU4xTUQ3Y2xBd1B5YkpiY29nZTJQX241anhBdnRUcUV5MDIzN1NkazBEVHBJaTZiUTFpM18wTkpFQTZUMWJRV2JyWlRRZmtkSmsyS0hZNzdQUi1FTzNZLVV0WnFibG1qdWNoeDkwdXN5?oc=5</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>46020.68402777778</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>RSI Crosses Above 30 for Blue Chip Tex Industries Limited — Reversal in Sight - Dividend Yield Trends &amp; Capitalize on Stocks with Explosive Potential - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 04:17:28 GMT</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxObTJQZGRjNTVma1ZGWVd0VUtnNlR1UmVwRTRWUmRBcS1kbUt5MUhDblFQY1gtemR0RWh1WE5MQVFfX1JRSGsyZHBUVFVPbU9zbnBpcjRBT0JwbDVZVUFteXppam1lUHBlLVFMZnRsTGZhLW11Q2N2RmpMQ0JXOTZyZ3JfSjJHZl9nbkVVb09jcjlDN2lIVUNSWUVuTVJuUkVqS0tqZFM2QjNZckJRYXFELTZ1MUE5aGs3R2RiRg?oc=5</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>46021.1787962963</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Live Chart Scan Detects Wedge Pattern in Empire Industries Limited - Earnings Volatility Patterns &amp; Explosive Profit Growth - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 18:44:16 GMT</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNdXRPcHJqTGVvc3JuN3pNQXdGSDY5TzJSaEFUYjd6aFV3MlZPMjFLTWluOTNLcmVoWFM2YmFpcHhPNng0OG9mUTlnRWJieHVNaTdBQTF6cGdmS014cnIzeFdTYm10WE1oS2hLZzM5UTdmYkYzRklnQmhzRE5LZVZsUHd5S0pTWEstOTJJYWhLUUxhbldDeTZGRWllOGZpZXBsMXozN1RQSGwzSjEtTzAzUFpQQ0RuWEk?oc=5</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>46020.78074074074</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>The Weeknd at the Stade de France in 2026: Here’s who will headline the opening act - Sortir à Paris</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 17:00:03 GMT</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxNMmU4cXdqNGZ6QTM4eDZGdDNxaUkwUUxYOGpHYXNkeWZoYnkxUzBTSWgyN0JZSVpYalhBTzVyLXdQUUFpYzBhd3FRU0pSSy1faDJjMnhGVU5jZGwwazZ1NE9pamc0WDNsc2UyajN3TGlUQU1RblJNcFFKSWZUMlJvX3VoeFhPb3JkRU5WZHUteXVUUG9SVmRVY3Mtbm9kM25FZmw0dmx2QzRBY1psUFNtN2VFT3EzSDJDbkJ1OUp5WnBJbHJHV2RIczBhdWFJRWNhZlI0UUxlNWhVRmpyQ3JMaldLdzF4WG5xR1FDVXQtQS0xYUJi?oc=5</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>46020.70836805556</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Alkem looks to offer explosive move in the near term. - Candlestick Pattern Analysis &amp; Free Real-Time Stock Market Data - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 19:53:40 GMT</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQQ3hXcmdKVWI1NWxBUFRELWxPbVpRM3Q3QkdwYkpoMU1xV0F2S3EtY0NuUWJRSG0wV1doSGtoVm9xaTV3QkhtdDIyRFMxMEh3QlJ5dTJZY3ZXY3ZzZkVNX1A2d0pnZzVCOXBMNjRfT3F4SDU4UGV0RHhQOGRGdHpiVUpTUDRNcE9mQk0ybWZreFg5UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>46020.82893518519</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Holdings Limited (TEXINFRA) - Sector-Based Investing &amp; Achieve Explosive Results - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 18:20:25 GMT</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPbnRVMWZ4QV9tcEllc2ZBY3FOZ196N3hZZ0RkbDZFdWFtQlpKempvWkNpcEpnZVEzSlhfcUVQazBuZ2NPTEtxcnR1WGowQUQ4ekhHbkV1a3A0SVAxMVVMUkJBX2RnbnF3b3RHZnBONnF0SlRLMmt0b05UOGJubTQwWmRpTThTeEVKcWd6SXh5SlVjaTdoc2lPUkZXX1hXSHNEYVo4V08wbzBOdExuRldVMjZybXFOcjNwUXhIMg?oc=5</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>46020.76417824074</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Is It Too Late to Sell Cupid Breweries and Distilleries Limited - Stock Split Announcements &amp; Free Explosive Trading Growth - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 19:35:10 GMT</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNZFJRNXJrS0o2VUNGRDF0QUFPUGpERzJicVUtZ1cxNEdOZ1NKZWJUQlJyT0VvaWhwbmJHVF9xbUV2RGVrOUkwdFZaV2Q4QlhsUDk2R1lObHljcFhYd2k5YnpvRGZrSDlkRGlMOXVwZ0hvOHNNZEpVVlFkc244SDJnZ1FaSzRyUmVNWDV4eWprTWY4ekY4NExJbjVxSTMxeGFjbENfZ0dLZ3A0UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>46020.81608796296</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Earnings Chart Overlay Points to JPT Securities Limited Upside - Risk Management Strategies &amp; Market Monitoring and Alerts - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 23:48:51 GMT</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNelhrZGJhS250VnJDdFh5TUo2RkdOX0hldTh0YjdwTURHX1Q4VFJJYUg5M01oRW9SeXl0aGxqWnFxVGk4aUNiN2FvNF9vMDhOY3RrRDljUEllQlJCY2dfOHk5YWFXX3ZQOEtaZk1HMk5oSUJsc21NYnJ2elNwNEJqOUpiRnVaUGJZTmlKZG5wMFBLWnFsWWFhUGtTT09zZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>46020.99225694445</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>NCL Industries Limited May Be Forming Higher Low — Chartwatchers Alert - Market Liquidity Analysis &amp; Explosive Capital Growth Plans - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 18:57:50 GMT</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOYzV5RWpPNFotUW10M3NkVXBSRmJ5Y0l2eVNyLUZuNnc2aFppQjhCWEFCc2xPTXdZWWFGdU85VlJ6WFZWMUtqR3BpVC1mQXRNZW11dDZaVHV4TWlDbW96MUVGdXhBZDF1Z01QLXozaktCb0d4TW1vSnJOYVM2WEV4Y3lITEUzZ2hkbFFGcmEwLXFzcGt4UmI0bDkxdWIyWV9VUUhTbEtaMklwUm5lRDZMeS1OVjIyVXloN3pXTHdR?oc=5</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>46020.79016203704</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Analysts Apply Wyckoff Model to Vision Corporation Limited Stock - Short-Term Trading Alerts &amp; Set Your Capital Stop-Loss Limits Effectively - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 02:56:28 GMT</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPdjJwemZiaUVUZ2l3dEVKdWRXazBwSkpCWDBwYzV1NjRGeWF1ZnlBYTNXNm5Fc0VlNGdTVGtnRDZxMURzQ1NTNmVPT3hSNWoxLXBMalZ6SlFycEQxWTFOMjhsQzJpWTJ5bWxJUV9lZ3hNaGVONVNfVmowYUFuWHR5Q2p1cl9WS2kxazdzWExueUhzRUpKV0JKWEZhOWNZbVgx?oc=5</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>46021.1225462963</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Investors Hope for Bounce in Ambo Agritec Limited After Selloff - Earnings Volatility Patterns &amp; Free Explosive Trading Growth - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 17:08:57 GMT</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNNm53R0Q3ZnZxQWJ0NmppRGF1ZXUtV0ZyVTQzTlluVEo5Q3haODEyNmQxSkdhbGE4elNrelBoLVFISHNLQUVIOGdZRS1ZZVQ0LTctMEUxQjU2aFVDT3FpbGxIel9GdnFGZm9XRDd1UFpLM1BtRWJWb2NNY3RmVXJKbkQwZ01ON05Bb1dwMmItR29nclIyZV9TWWc1alRCd3M?oc=5</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>46020.71454861111</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Published on: 2025-12-29 18:36:51 - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 03:21:11 GMT</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOZ0xkYVluMlBVQ181T1plZ2JzNi00TFhjX3FoTmFycm9xd1BPYm01QXJxSmNtRkxQanRaVzFPbEZ6Ul9QSmZrNDJsX1o4eTZqeVYwd2dwNmhON0FEamFROHpCaXpJLWljbFBJU0ozRmE3RjZnV1lkblY3dlJmWEZQOWwtQ0Q3NGFMNHdLYjQ5RENpcmJDYVJxTF93cEhDVU5LNkUyd3dCb0Ftc1N3ckdhdFdTRmNiRVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>46021.13971064815</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Babysitting: Philippe Lacheau's cult comedy arrives on Netflix - Sortir à Paris</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 17:41:02 GMT</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQY3ZmMVhKa00xRURNdzEyZS1GZjREajhHN3oxdUZXZUQ0ejdVQm5UTkdpMFVTX3NCNDQ4TG1BclJNdUUyY1B1RGo1LU56ZlpCR0dLWUN6TUdTbEV3UHVuWk0walZFUDk5R3JoRmlIMHp6N0U0ZXV1LUd2SFJRV1luRGxGd2Q4S0NzbG5RdE5EaG5CaFVVbGhTcTJoT2xLM1hWWlJWdThXM3RHMWczN0I0a3NacHJVd1JqRHJVbjlEZmQtd3ZrOWctYmd4NEptVk13bWlMQzdsYllhbXdMbVlnT0dPTWQyWGtHaHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>46020.7368287037</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>MACD Signals Flash Warning for Continental Petroleums Limited Stock - Protective Put Strategies &amp; Free Superior Profit Margins - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 03:33:19 GMT</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPV1ZEb3hrQnd1ZmIwOERLU2RkaHhadUVtRHYwMFM0NVFJY003c3MtcG8xb1NzY1MxZzZKcjZralVVenlxTkNuMWY0ekllemFNeG50MTRDQkFZS2FPUENVVVdkNUFHMzV2Q0xwdjlJbEpCTFFUdC1TTlJKNlhOemdETWZ5WGs5eGhMZjNhQ2JwSzBlWnNjcC1iYVoxTktnck5HaU5IYUEtME5nSkR6RTNybG5qWG1teHg0?oc=5</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>46021.14813657408</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Moving Average Crossover Confirms Uptrend in Cello World Limited - Stock Screening Results &amp; Free Explosive Wealth Accumulation - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 21:52:13 GMT</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPVnVqSFlfMXdTVUo3YzVZNl9IejFOaEdjRV8zTjl1T29Ma0tYbGNubURhYVFWa0FaU0s5T3FwQlJwSTVGclJ3TWZ3cV93THo2MzNpbTZWdURiSkFwOG5md25IZTh6TzBQb1JKcmR6Qmh3clR3eWZHY0ZqbGZJNmh4MHRGNW56X3RYOHp4aVJrQUVfdzlYNXVfcTdCZmtKVURHYWtiWkZGQmNzRzBK?oc=5</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>46020.91126157407</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Will Perfectpac Limited Benefit From Sector Tailwinds - Volume Profile Analysis &amp; Affordable Trading Techniques - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 14:26:18 GMT</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOY1gwY0pVbXljWFkzdlBYVE1DOWxKMXhJQVFLR2Fna3ExYjlRLXhjbUw3ZnpWU1hxMUNIcERQc1hOeGVWR2U1NG5pMVRQLWhXS2J3djBuQmhSME15dm5ON1lOYkdZT1hpbE9HSWhZNXQxa1Zkc2pCVHZuekVlMEF2WHJwSXl5UkFIOGVvajh0MUNxZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>46020.60159722222</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Emily in Paris star Lucien Laviscount's forgotten romance with Kerry Katona - Daily Express</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 14:43:00 GMT</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNc29pNUxTbjc0eU5YbUxQcFRXSlNONmZVV2R1YkVObkJmZk95bklPQy0xd0JDVDZkVENtb19MM3hQd2lQVlNqRksxUHN5cVY4a295eUdadG5NZGJaeTNpcVJFdTFvcVdBREF4S2c0cGYydGczMWJYVXBBUEROaWtRSnUwSUxreG9qT1h5Z9IBkgFBVV95cUxNa29kYjlVRnYtWlJ5dEdWVWpJOXdUQzhpRE03LU12MW1Nd3lRTm1MWU40U2tYU282eFZYV3B3eXlFVlEwVk1FM0ZYWDB4czI0RVBkSlJaQnNnUFFCY0lGc2lvejgxTWdsVTdSakZGT0EyNmc1cHNNQTYyNUoxaUpyT3BreGtuM2pZcU5GVEpMdUdPZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>46020.61319444444</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Milan handed Rafael Leao injury boost for Cagliari clash - Football Italia</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 14:38:15 GMT</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNSHFmMS10TE5KTEVlS0VsanVjdDFzMEY2TmJDSUp3cmJfUjFNNFJsLWlNSGNQclZKNVhDZEhnNERuWEdna2sxdjQxS1ktNkF1VUtFc3JMSU5FNXNhM1JaaW1xUElENzktTkwwUG1TZW1qTWVHLWw4WjhLMEpMMW9YZ3BXcU_SAYQBQVVfeXFMTUhxZjEtdExOSkxFZUtFbGp1Y3QxczBGNk5iQ0lKd3JiX1IxTTRSbC1pTUhjUHJWSjVYQ2RIZzREblhHZ2trMXY0MUtZLTZBdVVLRXNyTElORTVzYTNSWmltcVBJRDc5LU5MMFBtU2Vtak1lRy1sOFo4SzBKTDFvWGdwV3FP?oc=5</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>46020.60989583333</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>T.J. Otzelberger on Iowa State's accomplishments on and off the court - The Des Moines Register</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 04:25:27 GMT</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxPVTEyVmp6YkhTdDNaLUF0ZU55Z19fMEw3eEpvWFg0X1RDaktySTVhUy1oYlRqbGZLdmYzWDFMMVhpSHpWN2ZvLUJybDhBRl9vNmt0eWU2OVVvTUNDMHFydF9NcmZ6SnVJVjdZSVdZTVJ6YmhHMnFXanZzWS10Ry1TUUN2R1dQeE1WajJCX0dlN1hPQ0VybUlFaDF1THVPZUZralhDWXA0Q2t5TjZnZ2l4UmFPNEZ1QmZwX1ktc2I1amh1Sjd0SjRTa2FMZTVxNHRpUHVrT0xXcm5kR3dQVEU1dHRwTFpZaVB1bkpKUVpEcWhOajlQLTJSN0JhTnBhVUhjdEdqZA?oc=5</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>46021.18434027778</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>What Top Men’s College Basketball Teams Should Resolve to Do in New Year - Sports Illustrated</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 20:20:55 GMT</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNTFJaTGtrdTdHTlNQNGNFU196NFFMRFNuUHNpQ3JSaVpZeDFuSlBZUFREVUktMy1XUnlfQmtJc3F4bXlwcEUxay1sNU5Ucm40Zm1iLXZnWjEwZGsxREsweWs5Qlp5cGk1LTRBRDhtT3M3dHdCUmxvS1c0aGZBcFhaSkNfeUZfMl9lakhhYzF6cVFtVHZOck5oQkUtXzEybXFiYVozMDZNR2xvVnpVeVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>46020.8478587963</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>The top photos of the day by AP's photojournalists - Rocky Mount Telegram</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 18:54:33 GMT</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQcGxCUnhIM2NmRkUxbkMxdWh5eXFqMTZ0ZXczTU1XV2t5TmxmYVhsY0k5MTBYeVlYRHdkY2Q1Ump3WTNseDJFb01tcDQwekR3WDZqVXk4ZDE5VTY0b2hpbmV6Y3FRV0taUldrRjJhSHQ3YXRRYmFCdlB4WjFyRXduM2VlYnExYTRZMF9nQk5PQzRLTE1Ybi1XSW9zaGRMcVhWX1d6UVlCc0JmSmtYOUZaeG5XRGZsSHJvLXM1ajRYNnd3Wm53VnRrMUVKcWU4STc1eEZGcXNhODVKSVVrYl9nVjFn?oc=5</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>46020.78788194444</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Virtus wins in Trieste and returns to the top of the standings - Quotidiano Sportivo</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 22:18:31 GMT</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOZHh2ZXhTMTZaTExfbVp2TDhUVWVvcFcxa3V6RWtlcG9CRmllUi1HVGs2NHRFczhkNW5pc1dOdEJ1c282VHFDR0hvR09kTlcxa0d2dDhINlR5YWxWdFg5dXR2NEp3R1ZEN3FFaGZqMWpEMnpySnhaNnNhNG9CUzBsd0JKQkZabk04WllLenlGNzF2Q3lzcGRyUV9MM3hPSkRkbU5rb1VPZVE1dWFBN3dVSHNYaw?oc=5</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>46020.92952546296</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Belgium braces for New Year's Eve 2026 after past years chaos - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 03:59:56 GMT</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOQjY0eFhVX1RYMmIyd1dIRzUtanEzWDVadmRsZGNwd2J3QWJEc0RuZ3R2clpBcWdZT0Uxa0czWm1YWEl1VzBqcXYtc25vWGs0c2piamRDcFVyNGJsclB4cnQ4b294dTVEWVRHY1FRU1p3Q3JxTmxuV29IWk5VMXpSVWtWSGRqOEMzVGdmMnlBOTVlVjlseExSZWtYU291cGc?oc=5</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>46021.16662037037</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Facts Matter: Belgium protest wasn’t against Christmas - Daily Herald</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 20:29:39 GMT</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNNjVBRWx2Um5wdFItRnc5XzMtUE1uZnZvcVJIeVI1X1dpYkVwUTRPdnJzVmhneWlqbE82Vll5NFMtRFZ6dkJFZWI3ay11NzRmRW4zUVQ1TFRzUzZvNDQ4VEVuNmREZ0h0dWF3ejZ1Y1hwY1gwWFFFNW5tSF9XS0gtUkg2eW1kVEF6Z0lSVVpla0ViNTRoZGI0dUN4UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>46020.85392361111</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Brussels Bets The Farm – OpEd - Eurasia Review</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 00:09:37 GMT</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1DTGZoTHF1WG5mdVFfeXBHelZIY0ZXNWhjZlBjWE1UWlFvQWVUamZvY056RFFJVV83M0owY3gwX09kNU80NTRsX2MycDI3WERMUTBLQ1c3dVM2dnYzNjBvU2owM3hZSnU5UUF5b2daU0w2a3R6MVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>46021.00667824074</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Iran’s Currency Collapse Pushes Protesters to the Streets - The New York Times</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 02:27:51 GMT</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOMVNSd2QxTEhwRFlaTDZ5OFFzWFlRVDVtbHR4aEZiRnl5WmhMVjZ6dDRheVN1N0pqTDgyWGJQajdDMk1waEthX3lpN0tHY0hXYkdicWMyMDFNblAyTGp3T2VkT1VHeVNIdnQ3VWJXSjRHMFVIMEJwcWNUQ0QzMGppc2lhSHpKUzF3a2J2Z24tRUNxYXJSdEg2TnJmXzFwSG45MDdmYnRR?oc=5</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>46021.10267361111</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Investigation launched after federal police assault rifle stolen - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 08:23:11 GMT</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNdDRzUG43WVZZS2NKRkY1TFdiQ2JGM0QwQUlLR21yemQzVXVuMzhCc01vMnVpRWJscF9PUG43cVpRdGlMUFhDazlIV3Bibno5LWxMZ2t6OWRKM1AxX0tTaGNJSVVJNWpqVlJucU02NlBOT0VnbnhpVXF0Yno3SlJwRDRZNWxaMG54YjIwbmo3dmJPVVpxdndmSmZRcjZPMXpvanVrR3k4T1pZM19NM0U0?oc=5</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>46021.34943287037</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>No safety in UK: Knife crime, gang rape by those with ‘protected characteristics’ - Brussels Signal</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 07:30:47 GMT</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNMGkwZjliUTRxeEJ6T0JaZGJGQzFhN3UzdEpDUEhLbmhtR2NKcTlVOXBWT0VYdG9ldFU3RWVqbXB3c2p0V2RBQW5FekhQTnExYzBXZ29lYzZDOXBJSWVRUW5fTmhTSXM5LVN0NnNIMk1jWTRudDNjamlaNXAwam00VnlMbHhrNUhRVVE5RjMzdmlESVdoRFM4RHEwLU5WSG56V2txYmpuTlczVUxDUF9KX013?oc=5</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="2" t="n">
+        <v>46021.31304398148</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Federal Aviation Ombudsman: Current weather-driven runway use at Brussels Airport is safety-critical and t ... - Aviation24.be</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 15:06:11 GMT</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxOOHlUVWxpRUZrNm5QMENwbmstNGh6ZXdHdFJJanVJWFJ0b2lnblVVTTNSdVFicXNtU1pXajhGOWRscV92RHpjZFlRdHp4MzRsVzZPYm1BU29FNmZ0d3pWOE13QlllWEhSZVVmbmlHNml5clJsdDVIbHE1TjRGWkdBMXdROHRKRThEcllZaGFQdkFrMDlTbFBmWGNMMFBNa2U4THR0aUpFS2pVeUxRTE95UmVVbFhxakt1aWV1dnBka2tfdkFQTjdzd3FxNU8wR0t5VEZ0bjJJbnpaeFU2elVxLS1EajNnZW94ODIzY29zRkhwb1FzSWZyR2xaT2tvckRFN1E1TdIBhAJBVV95cUxOOHlUVWxpRUZrNm5QMENwbmstNGh6ZXdHdFJJanVJWFJ0b2lnblVVTTNSdVFicXNtU1pXajhGOWRscV92RHpjZFlRdHp4MzRsVzZPYm1BU29FNmZ0d3pWOE13QlllWEhSZVVmbmlHNml5clJsdDVIbHE1TjRGWkdBMXdROHRKRThEcllZaGFQdkFrMDlTbFBmWGNMMFBNa2U4THR0aUpFS2pVeUxRTE95UmVVbFhxakt1aWV1dnBka2tfdkFQTjdzd3FxNU8wR0t5VEZ0bjJJbnpaeFU2elVxLS1EajNnZW94ODIzY29zRkhwb1FzSWZyR2xaT2tvckRFN1E1TQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>46020.62929398148</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>BMW Driver Saw Potatoes and Decided It Was a Challenge for Him - ТопЖир</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 22:04:00 GMT</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVDgyY0t4V1B3YzMxOTQ4ZlpFWHUzR2dYb0lCalIxZFFxbFB0MHA2N09rOWM0MF9Ia21DeEpjOE1tTnpiU0l1bU91NHlOWmdvWnREUF80NHBUZThsVWtLRUotQkE4NExnTGJHVU5VRXVRZXJSeG8yUWRycmsyQi1HTmU0VW9LcWR1Zl9kVkFjNmg2X1I3QVduazUyYjU0U3fSAZ8BQVVfeXFMTlQ4MmNLeFdQd2MzMTk0OGZaRVh1M0dnWG9JQmpSMWRRcWxQdDBwNjdPazljNDBfSGttQ3hKYzhNbU56YlNJdW1PdTR5Tlpnb1p0RFBfNDRwVGU4bFVrS0VKLUJBODRMZ0xiR1VOVUV1UWVyUnhvMlFkcnJrMkItR05lNFVvS3FkdWZfZFZBYzZoNl9SN0FXbms1MmI1NFN3?oc=5</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="2" t="n">
+        <v>46020.91944444444</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Number of judicial investigations in Brussels almost doubled in one year - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 03:14:43 GMT</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOeFR6UGdFQTBXZDdERzBncTBxWldXTlZyUGQwN0hvckpfM1Bhd3p0R1dLcXBBVHhoZ2NmLVBRbEwwREg2cVlPaHNjSjFMV3ZXWWJra1pHWFB5V04wOWxfSGdzRXlQeU5KRGN3ZGZyMV9KUmVXaUxaczlta2pFOGQ3aXFTOVItV2VVU3JNdm1NVXBYY1ZtUnVXQTIyelpIT3E2R1k0M0J6U3RpS1UtMmFv?oc=5</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>46021.13521990741</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Investigation launched into fatal shooting of young man in Liège - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 03:14:41 GMT</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQeVJ4czVTSmFGazFqVm5YdGsyb0lPS2pBeDZWdnVtTktjVkszaGlJR0tMdnMySUh4ZUYtS2tNQzlYTWRJMjh0RDJ1TGpaVDNFdVh5SXVvdUJRWWIxY0FXd1o0OThxQjNrNV90NnpaY1I0cUpjUVVQZTJNYkJLSjNpSHd2c0RRN1BZWjJPaFViWkY1MW1EcVhMaWg2emlMNFJsRDBsag?oc=5</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>46021.13519675926</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>New Year's Eve prison strike notice withdrawn in Brussels - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 03:14:40 GMT</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQdzFTdUNfWlpoWWNxYVJxbldqdElHT3g1NGVGV01EZ3NDQlhRQjRtZnUyVTNpWTBlbHVTcjBFRm1odi1BRG1WQkEyZGtoY2w4OUFyQTBtM1FKSTJzN3FKS3Zmb0hSa0g3azk2MzRsNDB6S0g3ZEhaV3NscVFsMTN3RlJDMjZqa2VpRjdPMGNvdWprMTJKdVhmMWNR?oc=5</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>46021.13518518519</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Average of three indecent exposure reports filed every day - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 03:12:36 GMT</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNOC1xTmphcnB5TFJET0RnNHBSZUswcG04dm5LNXNYd3BrcVVPY01NaDdtcDFacFpMdjB3SFp0dC16Qi1PM0NQMW14R2dpMXZadkh6bmZmb1ZhRmxJUEtKcG1NT2I4OWRpQ0FtS3lKX2Fsd2E1Ujl6Y1EtU1pmd0h5OVRBMjg5dVF1ZVd3a2VvQlNtd3IyMzJSMlRMMFI?oc=5</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="2" t="n">
+        <v>46021.13375</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Interpol announces 85 arrests in 17-country operation - Qatar Tribune</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNakJOdElIM2JGSndtRGx3MHJ1OFhNUThpTV9qOUliRUEtZjNCRGhnVHF0a0NqYTJmRnVmd1VQOWN1eWVJcXA4NWl4eEhYTGRVbGlrazVYOHdBMDR4RnBaYW1WNVhIOXBGNTdYcEl4VFFEVDdIU050anFkQ2tkVXM3N1ZaRXV1MU9FMThwUWVfOEdjeERMWENwY1gzd3J5aHhzYk9rWDNCU0VfSnBH0gGsAUFVX3lxTE1qQk50SUgzYkZKd21EbHcwcnU4WE1ROGlNX2o5SWJFQS1mM0JEaGdUcXRrQ2phMmZGdWZ3VVA5Y3V5ZUlxcDg1aXh4SFhMZFVsaWtrNVg4d0EwNHhGcFphbVY1WEg5cEY1N1hwSXhUUURUN0hTTnRqcWRDa2RVczc3VlpFdXUxT0UxOHBRZV84R2N4RExYQ3BjWDN3cnloeHNiT2tYM0JTRV9KcEc?oc=5</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>46020.875</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>What happened overnight? Police blotter report for Monday, December 29 - Newzjunky</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 17:05:38 GMT</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQS3Boek0wZXdsaUFnTUV2dmwxWllNcnRiWjdzMTl5RzM5dzdtb0ZJcExKRmtvQWxkZEZFWXEtN0R4MWtFMVV6Yy1PX1EzUHBaVk45TlhkTFd2RExnYTRXYUtlNnJsbi03eXJpeUZOenBTWGZNZnNIQ0FxRE54OFltazVja2U?oc=5</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" s="2" t="n">
+        <v>46020.71224537037</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Looking back at 2025 – with Nina Mallevaey: “I am so grateful for everyone around me” - World of Showjumping</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 04:59:28 GMT</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNaW5RWmYtUVRzQW02Q2poamd6YW5rd1JzTGRqQWxlVkY3ZV9CcUo1SXQwdjFNc2RvQ3N3YWlxb1doVERlQXR5eUZlVVh1anNydGxPSl9Ebk1VWHdhdGVSaVptMUZicFdEOEF1d2lnQ2NON29TUHdBT1VQcmE0ZFZxRXdJdHBXZUdOTXQ1blIzUFY3WW5TOWFDYzd4MVVOS2g2cW1UZU9rdUVpWVg1MnAxcWtBUm5yZlBfOXRpbzk2UnhJakFkNnFHMUZSbmloRkFLaVhySFl1ZjFRalZpdHNr?oc=5</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>46021.20796296297</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Visa game beyond the EU notes: Restoring visa-free regime for Turkey is not in line with Brussels policy - vijesti.me</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 17:08:30 GMT</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxNcjhlczZkTjBtNEtRNU9nV3lkZHZOY1Rhc1hPMmFIUU03NnZxS0c1a2VDeHVzQ1lOMkc3aEZiaE9nQ1Q1bWR0dm51b0ptTXlJXzFJY3FSUUVlOEd3QjNfWHNGRmVNb1VuVnh1M1A3WE93T0NEVU5LRUp1UWhJOW1xNXNVa3pZOE1iZ2NsLWgwTGdEMmNQTVNvX0JjRlFIYThORC0wX0MzNkUzclMtUXQ3Wk1BS1NjSzVVWHd3eDV2UkdyYTg5d0pUdk5MM3I4Vm13YjRyNE43N1p4NlVHSUs3WXdUS0Z1Rkt5R2hSLWFKUU1jTjdxTjVOZnlrRVdGUEXSAe8BQVVfeXFMUHYxZ0Z2cXJsVjkxNzVfdGNrSi1XaEtkTG1TUUNaQUJHekU2RzRrV1VLY0F2QmEzSzNKdUZ2WlZyQXEtaG9RdkkxR18zTUZyak50dTBJZjcwajJTZWo2Zk5VSWRVNklOTmNxdjFSc0hjXzJwdHMxVEVHbHd6VFdOUXhMVXRraHpNN0hVa1VZRURqdXRoZXZZenk2Y3Q0RmNlV0p5S2tXcXVqRjhIMWxaZmhucjZSX2ZTMWg0WWc5cjc4WURmLUY4b3ZIOVAtQUZnUUhXelY2ay1ZTXpMNmh3ejR4V2xtRnRVclQwTndESDA?oc=5</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="2" t="n">
+        <v>46020.71423611111</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
           <t>Ireland / Kildare Protest Groups - Social Media</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>John Major reprimanded John Bruton for ‘stormy’ speech in 1995 - kildare-nationalist.ie</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Mon, 29 Dec 2025 13:45:42 GMT</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNc3o1bi1IdW5yTHd6WVdnNmY5SkpOaV9naVloVWV0RlZVZkJydjhIaUNCcmYxMlFuR3BacDVZTHk3T05JN0JFZTFLWXNjel9BbUtON1B5aTVrMWRmVnFjZVVOcGFyTjVsNURwTHpBRmZ0NmE0ZEhIUlZwN3pGU2RZYTlpWjVTQnRtUkc2MFZtQWlYd1lpVGtORVBrTUJjbVlQWkc3bG1qQkQydnVULS1DOWI0SEN2dEU?oc=5</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>46020.57340277778</v>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>His car was involved in a crash - he hasn't been seen since - Wales Online</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 00:38:32 GMT</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPamhKQzROTnRqdlBTM1hmMGpTVlo0d05pX3ZZMGtlU2IwLXpPMk1jb0c4TjNMNUVFNFEzeGxDRTZaS1hvcTVoMkwwcVVqbU5kQ2hzVWhldHR5X0QtR2hfQW9rUC1ZMWV3a1haMjJVaml6WUJmR0VLU0FlNGJOaWVWdFQ0dVVudGhza3fSAY8BQVVfeXFMT3ljZnFkUFZ1Q09rYi1BYTd4TFg4eTd1MTVmMFlwX0pqaWlOSDkzQzVEczdkZ29Eb0hha19hSll3MHVHZGhSdzRmQVdHUFgzbmYzbVM2Zjl1TklsN3d5Yi1CWHRwWS1VNFBHTnk0dTZpN3h4eDdMOWdRSWYwcFRkYkJaaTB2NXhqdUFEcHNIMDA?oc=5</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" s="2" t="n">
+        <v>46021.02675925926</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Father of missing man says his son's 'murderers' are 'still walking around' - South Wales Argus</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNTldWb01RaGo3X0d0bTl1YUVJSWNGXzE2N2NqWm9pY1V0Z2UyMmszNUNMVXU3aVM0NjljdGRrU2doSnhnQ1Z6Znh5MFR3ekZ3ZjIwSTg4bHZsNmppNlZzOGtoQmJ4N2FTWWduRGhUUVlUWmhManIzSFpzYWZNcXVQOGpkSEFnNHZmLUF2NnNFMzdLQ0dKN1F4TGMxa2g2WEhTMTRkUV9lLUk?oc=5</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" s="2" t="n">
+        <v>46021.16666666666</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Brick thrown through window in arson attack in north Belfast - kildare-nationalist.ie</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 18:27:31 GMT</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQSDI1d3VELTUxbVdLU2dPVlk2QTVOVzg1VFZoM3RWeHhlamMtX3gxUW9IYS15dGJKMGh3LVJGV3JhNW0yUnM1cjMxaVczbWlEVjM1WEx5MmE4SFJGNldadjl3V2lBcHFELWZOenN3OGR6eXZPVEhNNzh4eEJ5YXVpUXRuNUFrYjNLdVowQW9LU05NNG9fMWlyLVFIT0Y2X0JsNVFieEtOQkFFSjhSUzUzdUxnLXFPWVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" s="2" t="n">
+        <v>46020.7691087963</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fashion's Most Iconic Patterns Turns 130 - Grazia Daily UK</t>
+          <t>Burberry’s CEO on Turning ‘Britishness’ Into a Global Language - The Business of Fashion</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 09:46:37 GMT</t>
+          <t>Tue, 06 Jan 2026 05:30:00 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOMjNpQW16a1g4Rk9WMWtGOV9JNWdLSWZ0QVc4MHZMNlFYWWNPYkdLUkVzcWlLX3FDc0ZvNGRHbURQYWRTb1J1TktvM1BBSnFKMGM3WHdDY0ZZNTJ6b0N5TW1sb242NVdkYmRRbnpWeUQ4RUpIQ3RyeXpBTDFYeW9RRGluMDY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPeVowRWxkZ3d3TzBER2tCV0p3YlhhOFR5dlNkdWQ3NEQtZ21sa3d4YzY5LXlORWFRWlVnQTdQeGZLRXAyMEd1OXQ1d1ptVjRhSDRaNVRjRmdiVTVTMUN1S0ZPTmlSNFpBMmNJZmR4c1dKVHYwTGtvUEc0dS1QdGtkaHVwdlNGdWczWnJqTkhqRWZnVXhQbENRa19HbnhHWXpQY1pkMzNpNUZBRUFJWHZ1ZFdoSDJ2TF9LQlE?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46027.40737268519</v>
+        <v>46028.22916666666</v>
       </c>
     </row>
     <row r="3">
@@ -515,24 +515,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dior Presents their Spring/Summer 2026 Campaign - PAUSE Online</t>
+          <t>Burberry taps Olivia Dean as the face of Burberry Her Parfum - FashionNetwork - The World's Fashion Business News</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 13:11:27 GMT</t>
+          <t>Mon, 05 Jan 2026 21:57:28 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOUWRUZmVWcVpqSTZmOWRHdHdMZm5acWN0c05NMDktZGwzY1RYOHBJZ2hISTVkSkVqYnhNdHQyNTZMV0l0azF6TXNjRGNpNHphal9iNXJvNTNHZlZRcDYtT3FqMjNrRkFMeFRfX1QwanBabXdodkExRDhxMHhtS1hGSzczOEFHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQdzZva1hKMkdMN0VnamtRRG5JU0w0QVQ1MzZYNXAxSXlTY0EtVlV5OWNKOGszdjU3dnZOQ1VSOW11MGRWYnFZRlVTeDQ4a2IzZ3RWZDMxVm9xdUVpVTZMV1NKS2did1BDWU5IeS1vTzh6YUVuVzZnZnZnbUl6OU5WODFLdFNyM25ySjF4OW1BclNVRE9GYTlaeEhwT1JnUHFHdmtEOUZ0a3NuSEdt?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46027.54961805556</v>
+        <v>46027.91490740741</v>
       </c>
     </row>
     <row r="4">
@@ -548,24 +548,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Shinsegae Duty Free expands Cartier presence with fragrance debut at Incheon Airport - DFNI</t>
+          <t>EXCLUSIVE: Kendall Jenner Named Emporio Armani Global Fragrance Ambassador - WWD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 10:17:12 GMT</t>
+          <t>Tue, 06 Jan 2026 06:01:17 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOWGYySFRZYTBfWUR5aU1KVUpQSlJ4azlwSU1EU21USW15R1VXRGNFeGltbXJUeVZNMUNzV25pS2VtcDBJWnU2cWdOcF9VbkZIUjJwMGpfVGtiNGJsalphS2FNb3JUbkJ0dEFQVFN6MEZHQVQ0NUxxdnBIRHREZE5Wa1VEM2dfcURzenlpdnhyTy1IYzNlR2ZqN1BpQUk3NlJFeEtfSlJNSkxRbUhSUC1VbzJNbEVXU3lXM05oWGkteU94RDlTTjJ3bFVHbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPQU9na2RnWlFYZUI2MVpFNjZfWGJsbHZKaEkxVzlQRUd2V1l1NVM2Wml0a0ZQZ3U1aFE5bTQzZzJ1V01oSVFiU3N0S25rNEhhc05GeEFmQWJPWDdPT1B4a0t5RVQwQjRmNTV2b1F1VlVyRVdDaHZsRUI1NjdWTDFjSG5FTFdkbWVMZ1pkLUpDTzgzd0VLaGE2RDdzVXdkc2FNTy1ITW5HU00ydkpGR29EYjFHQVhmMnlzcXB1dHg4OA?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46027.42861111111</v>
+        <v>46028.2508912037</v>
       </c>
     </row>
     <row r="5">
@@ -581,24 +581,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BURBERRY HER PARFUM: A NEW WOMEN'S FRAGRANCE STARRING OLIVIA DEAN - Yahoo Finance Singapore</t>
+          <t>Dior SS26 - Office Magazine</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 14:01:00 GMT</t>
+          <t>Tue, 06 Jan 2026 00:28:55 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNOFBpUGdmeFBYMlVQTl9aMkIzT25GbFZoSm1rSmx5YXc2YjFRS3dPTlo4bmdzRjZPQVQ2OU9oWUdTUS1yZ2dzakhfdThYdDR5bE9GSm14a2psd3VraFVCdVpDOG1vTHZaQ2tNWDFNdndXcnYxRTREYXJGcmpmaFAwOUVEQzVJUThqeVZCMjNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiTEFVX3lxTE1uMmN5dGpxMVN5ODdOWmRmSnVuT20xM2NyRTVQcG1IdHdMWTduSkRjY1RxRlNDQ002dlA1UV9hR0FNcmgtajdrU2VNejM?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46027.58402777778</v>
+        <v>46028.02008101852</v>
       </c>
     </row>
     <row r="6">
@@ -614,24 +614,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Louis Vuitton distresses, softens and goes archival for 130th-anniversary collection - AD Middle East</t>
+          <t>The most stylish ski collections to wear on the slopes this year - A&amp;E Magazine</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:54:10 GMT</t>
+          <t>Tue, 06 Jan 2026 06:41:03 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPSWZBN1I4MG9TVmZEYXdGbXVMRzhEYmJGeG9LRUYwbmpWd0xReGhCUi1qUzd2cVo0UnBwMUFIdWVfLVRERFpybG9KQjNDWmRyWjJ6QkFMRXdjTjNrWUlZYkdGS3FBTHZtTWRBSHN1WUZTQU1qZXQySVY0TVVtUGlNUDljaFlFb0haNjlGMnA4ZzR4TmRuZXBrTEdrUDVFZ1FpSi1oQ0tadHVrNW93eEFMUmthV1BJRVRDQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPSlhfV1FmU2xtNHhYaldJWEtoSUkxQnlhR190SGZwZUpYRjRVSVBQZ1cxNmJDY2xxQmNGN1NJUWhoTng4X1ZWT1F1bUhzcTItZVRlQ3N0OExjMVR6OEZzckRDMlFqV2VUc0h4aFk2TGRFVzREZ2JDcThkUkRuTjFUMHl3UkZJTHFMYVRWdXNIRUtHLXc3WWlLXw?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46027.53761574074</v>
+        <v>46028.27850694444</v>
       </c>
     </row>
     <row r="7">
@@ -647,24 +647,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>From Co Derry to Dior: Anderson’s collection hits stores as stars step out in his designs at Critics Choice Awards - Derry Journal</t>
+          <t>Ten Loves: Louis Vuitton Monogram 130th Anniversary Collections - 10magazine.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:21:00 GMT</t>
+          <t>Mon, 05 Jan 2026 15:01:55 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPdXo3VnlQcUpYUi1pU0pua2VKenR1b3RFeFVMSlFuRXk4Mi1OZV9NOG5RWmZsRW9LeU5hZkstUTk0Zk1MbW9zQzA2Wld5eXhTUzZLb01sTWRUSGF6T2JuQ1RRcnZ6NVU1X0hFWE1zZDRYaDRXWm9hZzh0NHBDQ0hTbG1SRnJTdnJvZXphNU9OdFNReUtlNTJqUGwteXJ0ZUZKTHgzTVdzRnN5WlR6YVVRclpsU3FXUTNyZWowVlVNMGtFdjI3N1BIVmZPREtSQ0h0anFEUUhWQW9qNVUwMkNzR2M1UzBWR3NTdWl0cG9LV2pMXzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPUDYxaVVLdHlweHJJNDVqWWZ5ZnhwUm5fRUlacWxWOUhxTHYyMFVndXUtRWhheVFZQVFLeEdFWjB1cU12WEI3OGFHS0RyOHVOb0x4SDFyYkV3SnlraUkyTzA5WFFHdWVEYXI1U0ZHcW9PejE2OFJBeEdJNHhtelJscUZB?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46027.51458333333</v>
+        <v>46027.62633101852</v>
       </c>
     </row>
     <row r="8">
@@ -680,24 +680,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Louis Vuitton Scores Win in China Over Upcycled Luxury Bags - The Fashion Law</t>
+          <t>The Dior Grand Soir Year of the Horse captures the magic of the lunar new year #YearoftheHorse - senatus.net</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 13:48:31 GMT</t>
+          <t>Tue, 06 Jan 2026 05:21:29 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQWDVKNC1YWHhpZjJqQVVhVG9TZEUyNVRrNmRwMUJlUnhoa3hmcE03Z09CVkpYVk9zUVlKN19jZmk3RFV5WERiQm1SdURuMHZKT0pMb0FUY21hRlRuT3JYTkNCNmtZcVdVR1poaVdrY0tTeVRrQmMxQXFqaVJnclVnVmh3WnFUT3dkRlF0Nk05T1c3VzZJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYS1Oc1JwbVFRQnRWOFRVV2FQQW1OaXdoUjlPNG1zWjJaamp4Smh3X1VXN29UX0NXNnZ4cmNRMzNnYTlMSFhPSEpESEN1NTFpQUdlLUZObFFtNEV0aGZrbzRqWWVpQUlYYUpsVG9oU3JubXJlZjF6XzRGaXJXWVQ5b3RZMS1DU2VZNXVSaUl0UFJEQ21CQnFtSGFmYXc0N09ZMEE?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46027.5753587963</v>
+        <v>46028.22325231481</v>
       </c>
     </row>
     <row r="9">
@@ -713,24 +713,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cartier to open Beverley Hills boutique second-only in scale to its New York flagship - WatchPro USA</t>
+          <t>“Valentino Rossi’s group” blamed for Pecco Bagnaia “underestimating” Marc Marquez - Crash.net</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 10:17:11 GMT</t>
+          <t>Mon, 05 Jan 2026 16:51:28 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPSGpQX3hPVWdVb1RrTUhldjMySnlZOHBOTlpDNzVESkJmRnFmeGFaRmd0X01wU1VodGNWYVBibTlMRUVCbzFnYW1CSi1NQ01TN0J3TFNEYUtXdVlTSHZCRWdreWU1cXhfVXVQajhlSFJYMlphejJuZzRVVnIwemlYNy0wTTV3U0ZGWGFBdzBLVU93MlhBVm1JUmFBZHQ2eVZfaVR6Z3hYTFdoNzhhVGk4Wg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOYXhLbDdIbm51WEtTQlA5a0hiOVB2MkUwNWNvVkRMUWFYR19oN1UwcktvUFIyNS0xV2phNXNfSXg3TVhabkhXQ1d4MU96Y3VyRm1oMkZLeWZ4d3VGYWFiSDFPNXZtb0tleGxBYmQ0T1Nlc2VBVmFsbE5ZSXcxUWFma1dVSV8tem0tQ2h3cXF5R0szem9zajhvZ0dsNE9LRXM3MFk5NWY1UjVVWXBkWF9fV0I3Nzg2Z0k?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46027.42859953704</v>
+        <v>46027.70240740741</v>
       </c>
     </row>
     <row r="10">
@@ -746,24 +746,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kylian Mbappé leads spring/summer 2026 campaign from Dior - Luxury Daily</t>
+          <t>Introducing Louis Vuitton Fall–Winter 2026 Men’s Trunk Edition: A Modern Study in Timeless Style - Haute Living</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 10:08:11 GMT</t>
+          <t>Mon, 05 Jan 2026 16:45:33 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNZlBnbnR3aGM4amUxUUp3bVFnbkd4MmdsVHlBT3hMcTYwN3A3NkhXX1dWQWFZU0FsR1p4NzQxcjZUeV9WT3k2V1ljV3U2WDBCb0VHNDk1QVdtLXZIMU5NdlBPTWp0UDZtUGJIX3hBV2l3bGNjb1JLMXZfdG1uY1dFMDlqMmZkTElnUDhEbWVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOWnhrYWxmanlPa1pTSDFpNzZEelhWbEpBVDdQcWIzSGhXV1JFMDVfcjZtVmxudjlTaUJ6NjJES1BaSDR1bTRtUTBKaXYwQU1fVVhFcUpFTEJYQW5vak1lZUQ2RGR2NlprYXF3MkhfQTBxYVlCWGdRcHVQLTdvNXk0NkJpaUlIR0hEU0NXLVdyeF9POHVJUjRvWUNMcGs0R2JYd2FacURyQzRNZ0tyLWg2ZGZnQ043T0JFMXdjZEhveWpQMlJZdF9pd3hpaEJhakE?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46027.42234953704</v>
+        <v>46027.69829861111</v>
       </c>
     </row>
     <row r="11">
@@ -779,24 +779,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JISOO Fronts Tommy Hilfiger Lunar New Year 2026 Capsule - dscene magazine</t>
+          <t>Elle Fanning Brings Early Aughts Runway Fashion to the Red Carpet - WWD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 11:53:15 GMT</t>
+          <t>Mon, 05 Jan 2026 16:44:02 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOZVkyMG9MQk9mZ01ySkg4cW92RTc5S0hxaldBdFMtMkVGc3BvNFNSNDdYdWNtUklUWFRJMUx3c1RLQy1UOXhTbzhhMjUxa2hfV1gxWGtxRDFQQ1lSOEtFRFhpWngzYktPTVRPVTJmX1Z0Sld5MEU1WTl0bDNIMi1tV2RWcmFBLW95?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNQ0psT0xweGNueVVSbVF3NUFVYVhQN1hzNV9JbzZ4UUVwNG5RZTB2M1hhTWpqZEhRMV9FYU1ndFNzbVBkZHJ2TWZWZjBHS3RSSGg3LXFyREhMZzZsMVlRaFlxNl8yZ3laSjVUbTJNanJ2cngwOHU4RlhyTDFxVW5FaTBoa1RnRTRydTZOeWdnZmlvN1pidy1HOG1HRExMbjVoOWZTeGhqOVV5YXdFRjRn?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46027.4953125</v>
+        <v>46027.69724537037</v>
       </c>
     </row>
     <row r="12">
@@ -812,24 +812,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The best January beauty launches to start the year glowing - HELLO! Magazine</t>
+          <t>Princess Rajwa's daughter Iman is the cutest ballerina in Dior dress - HELLO! Magazine</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:22:03 GMT</t>
+          <t>Mon, 05 Jan 2026 14:58:25 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOeWhLUDhpZ1pKeGdnckV3Z3FxRkFpX21aTjNUbExSTWtSRms2UlRhREtXZk5uVWNfWkxKVDRJNzR5QXBjcldXSG1hd3U3c0JTME1HdFp1TkoxQi1GaHN3LXNSUG9ueWNGZDAzV0tnQzZIYk5ybkZoa2pSQlJQMm1qM2p3WDk3dnpEejI1TzB0c2RhR3PSAaIBQVVfeXFMUG9qeG1FUHg2TGNFQ2pDYnpiS2d2NGpaOEdxSE1hdWxuXzREMDFwYkk4amY3dGJWa054Smc4V3ZHcHRBdFVGRFgxWmgxRHRuOFhPaXg4MFN6Q0VFUE1tVzZqX2JScGVVa1d0cDhUa2pFQmw4azYwSng1YWpyVTYxYjduWFRwdEJUazFmYjFLVzVxR1FRcDU2XzdHblFQZWJvWFpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPNDVOTnZNdjJyTzllVHNlWC1RQWoxRjlCMU4xcjJPTVltbGxudUktUS1tNEhSdi0ydHFIMDdpZ2ZhemFMaGNvRHN6T2NNdEdCTVZscGUzV0FidmRQYkFHaGF2OXpGNGFMbEZMUVJTVnI3VXNOU3Z4Z3lVTUZOZWRkc0NZOHktOTZwVktIUUduWktoeGlBRjBERjVFcTlLcl9uQ3B4eWhrR3M3YzZtUGFyVGhRMzPSAcMBQVVfeXFMT1oycmdmUGI0WFlIVmg0TFVGLXhpZld6eC1JcHJFaE1GYm9nNzlQYm1KRjVvTldnUk9ZS09CU0l3amlWRWlUY01LRE9BYzZmc1o4eWN4MURhejNGREhReDRMOTZpaDgydEk3d3dmd1ZqbzdXbWxGb1VuVy1PcTU0bXAzUUpuVFVRT1ZKa2lId0Nnckhtb2ttLWVPT0tkR09HTFNyUTNlUXg4Z2hqaV9OVEtMak1XYy1IaWVsemdYdG1sVGJ3?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46027.5153125</v>
+        <v>46027.62390046296</v>
       </c>
     </row>
     <row r="13">
@@ -845,24 +845,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How 2025 Reshaped Fashion: The Year of the Creative Director - MEGA Magazine</t>
+          <t>Getting Ready With Miles Caton for the 2026 Critics Choice Awards - WWD</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 09:13:12 GMT</t>
+          <t>Mon, 05 Jan 2026 21:25:19 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5TVXh4dUtsZkZ4R1ZIVllLOFZ2VG9JQXUtMDlsQkc1enBPT1E2bm5PSXhpdXJqNy1jdG93eFF1SFowQUwzVnBVbW9HSmt2eHRvalhiT2NiZzdEVDlBTlAwTmJybERnc29TWGJDUkVCTmY2QllubU9jYXRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQLVVPSmlqeHJQbE14aHJwV2V4ZzVsVFJVclk1SHlTQVh1Z3E4TXJKWXY3TmtUcHY1eFBPN1lGQndoQ2RQRVRYc1FuVlNoaDRqUWphUjlEOTg2c0VMX00tNE1jX0NIREVKNzg1Slc0SVg4R2RCWDdtLTUzbXFtc1hEX05YQURXWDZaMEM4QTJqQ0lSemg5cVE?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46027.38416666666</v>
+        <v>46027.89258101852</v>
       </c>
     </row>
     <row r="14">
@@ -878,288 +878,288 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11 Ralph Lauren-inspired Winter Travel Clothing Finds on an Amazon Budget—Cozy Styles Start at $20 - Travel + Leisure</t>
+          <t>The BEAMS x Polo Ralph Lauren "JAPANORAK" Expected To Be Reissued - hypebeast.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 11:00:00 GMT</t>
+          <t>Tue, 06 Jan 2026 07:05:19 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPYWF1SEZYQ3FqblNMajhVSHlDcXBoN0hwSzFseVdVN1RoMkJlSzFSWEx3ZkQ1Z28xekxUcTVUMG0tanJtZC1sOUpJWlBZR19HektTWnJJSTU5UkI4ZXN5aHpsT0VIUHNYUmV1QlpGMUhRT0dzX09NR3hXaVNteDNsSkRrQmg0d1MzbGs1cVlWNDRBTnNQMGRCUzBibDdHXzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQbWtlTFFwUG54cHhCUW41NVBWT3FmWG9ESlRZWU5VdEcxNVp4emNmREVfcWxpdjdDZ2ppLUEzREN0OU9NUEl3cERnOVI1YVRITm05Yl9JVllJWGxfMF85NHVzc1hBc1JBczdnRWYtQzFFN1ZDVWswZUEza3VOZ1pPNV9hcm82RHBHR1ZF?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46027.45833333334</v>
+        <v>46028.2953587963</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Value Retail</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ignore quarterly noise, focus on long-term trends: Sameer Dalal - The Economic Times</t>
+          <t>Pol Espargaro shares why Valentino Rossi changed his mind about Marc Marquez after he joined MotoGP - motogpnews.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 08:59:00 GMT</t>
+          <t>Mon, 05 Jan 2026 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPaVNGajk3TjRsVFBKY3ZlRmdxZmQtT0dXQVVQV2F5aThjaEtId2NiZWt4OUNaZWNOU2lzNE1QMkM4ckY3WkNaYjJzMVB3cnptQURFRXM3NGVmeHVxbUd4ay1lQXZZSUVlUGtieV9EYWhDLThoN0JvaF9yNHdaU2trc2M2bFVRVExmSUg2azRJUVRKTUxhVWtxc3U0VHhrcmZOTWZLVEN5NndMNXgxYV9Bc3l0b3gtRERlNTJXdnUwTFRXUjZSVTJ3dEhyUmJyRE9DVUN2ZzB30gHWAUFVX3lxTE9pU0ZqOTdONGxUUEpjdmVGZ3FmZC1PR1dBVVBXYXlpOGNoS0h3Y2Jla3g5Q1plY05TaXM0TVAyQzhyRjdaQ1piMnMxUHdyem1BREVFczc0ZWZ4dXFtR3hrLWVBdllJRWVQa2J5X0RhaEMtOGg3Qm9oX3I0d1pTa2tzYzZsVVFUTGZJSDZrNElRVEpNTGFVa3FzdTRUeGtyZk5NZktUQ3k2d0w1eDFhX0FzeXRveC1ERGU1Mld2dTBMVFdSNlJVMnd0SHJSYnJET0NVQ3ZnMHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPNEgyMF9fWHdPWUJQNU1hZXhJaWJaTUxvOTg1Q1h6TUg1NVpoZW9mR193b2VGM2ZkMF9sRjlCOTRaY0ZCZGZhbmhDOWxiQTJzdzlWOHhENzF2X1JjTUI0RFNhUldzVDY5RWx6MC1ZS1FZT0xTQ1RsY2pxaXRSRkVIcXM3N3h4MXZzNy0tS1JvM3JtNlNqbXN1WXNzN09SVzJQdWtHcTB6VldoaDgyU1EyaEdiUzhOSjFaUHk0TlFCdGgwQjNJZVdSX2hWUl9LSk1BbUJpNw?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46027.37430555555</v>
+        <v>46027.625</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DHL Supply Chain: Introducing First Cobots to Latin America - Supply Chain Digital Magazine</t>
+          <t>Men’s Fashion Week A/W 2026 is almost here. Here’s what to expect - wallpaper.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 11:05:21 GMT</t>
+          <t>Mon, 05 Jan 2026 17:30:00 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNMjZ1TUkzTm8tTFllRklmd3VmbG9YWTF0dF85WEg4azFTbE5teFlHNnl1QUZrTnZQTFB2YXZwOE5icU9aOC1ybk9SU0hObzNkQW90SUtERXp5QUMyWmdqSDdtN0tPQ1Nla2ZRUTR3cXdHQ3ptdHd0X2U0NmUtYmtPZVhUb3NHMXVtc2JBZG5SQWg2ZzlxZWh3eE1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNSnoxN2FSVUdCTy15cGV1aDFLZ0RWdlhaSlQ5N1dBNWVXUFNSU19FUjIzdkFFc0piOV8yYWFUazBSc3NHWmp3R1RYeFZueVNmMm1WOE80S2ZjZ29fS1o2c1B6Ung1RncycFBfd1hVbHNscm0xcUI2U1BwNzhxUUd3aThnNTNnSUZz?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46027.46204861111</v>
+        <v>46027.72916666666</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Amazon completes its first drone delivery, in England - Arab News PK</t>
+          <t>What to Watch: Bigger Is Better in China, at Top-tier Cities at Least - WWD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 11:24:39 GMT</t>
+          <t>Tue, 06 Jan 2026 05:03:39 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5uSWthTEhpbi1fbnJYa0hMdm45WXN6LU9saHZRd3lZaFRGTEJJbXFJNFkzWWpib3JnN3g2ekF0NWxOT2ptTUo3SU9rVnZjZGtMY2FlbUV2ZUhSZFlEdVNLeW8yOFhwd2RoRU5GVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPWUhjNVNhdEctSHRtdWJDV0g0V3RxbXB4MTdZeDFkNkcxc2R0a2JWRm82MExMLWdGN0o0Q2RITmdRcG43c19aZUlFUl9kUTVPU2g4R2JVWUl1SzZwN2t5MnprOVFxTkJQX1lVSHJONGFJRlN6alptRnBJRGxaQS1meWplNFU3Y3pmZ1UtNWdPRWVWRTFKLWJCVERmbGdtc3NPcWhhZw?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46027.47545138889</v>
+        <v>46028.21086805555</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Amazon plans a new 'rush' pickup service as it doubles down on rapid delivery - AOL.com</t>
+          <t>Dior Roadie: Jonathan Anderson’s First Sneaker for Dior - hypebeast.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 13:10:43 GMT</t>
+          <t>Tue, 06 Jan 2026 03:43:10 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQRjNxRy1hbXVBRjA4SWFFeFZzOG1zejh3WlVRNDNBYlNBUlBDbUU5cDgxcFFHLWFsV2NVT2Qxb0tKbjBSUVRNQ19ZWEozR0U3aDhPMFZ5S0dtSGJWZlRlQkFscDR4ZTVadnlOMlVYblpJNHYybXVMQ2VFYXdYcGc2RmVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPdW5zS19ubmZ4VjdzS0lvSDYwaXJmZWpnSXJBZ1NGMHNpX0p6WHRwRnIxdV8tWi1PNHdXWC1fMFdaM2pxNXR3UUFjc2prazFDUlVWajY4YnVERGdMR1Qta1hCaHVuUzZQSVZxTW5aUFNIVEV1THI2Q2h3ckVjb0swNEd2MklSVHJ1?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46027.54910879629</v>
+        <v>46028.15497685185</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FedEx Garners SDG Corporate Award for Outstanding Sustainability Leadership and Community Impact in Hong Kong - FedEx newsroom</t>
+          <t>Singer-Backed Modern Perfume Campaigns - Trend Hunter</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:00:17 GMT</t>
+          <t>Mon, 05 Jan 2026 21:33:45 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNU2lENFZnemZhamxkdDUzNDBwaUVsc19hZDlJcm5rZjNjbzNaVE1WYWVZVngwVnN0US1kZm5say1yV2hKQkhFNDBjT0g5eE1kaGZ3bjhFaWwyRGRjMVU3ZXFWMzJabGoybE9vQTYxeTBEajhOd2k3YUZ3dEY3dDYzVk42cEU2QlFaUnpFcTdvRXQ3OFEzcEwwMEhnZDFJWDQtVm54N3QtU1YzSXY5elBnUVpMT3V1WElPbXBEaXZYS2xKbGt1bXVPaE13Uk9GNXFmUEFTWnp4X1ZwNVNZVU9IbU9tdEl4NG01dXM3Sg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5VUHpsOHZSb1Rpb21aOWFjdTlJeUJfQk13aFdMVnZLaUx4VkdnOHJlRDlJdW5sM0ZkdVdmYjRmSFhKN1NBd0NUbzhWLV94aXE0Nlo4RzBJVkRwZmdlVUtSRkJUU0vSAWpBVV95cUxOUUJ4WjNLQkwxWGhxMEQyUDZqN2tWWDAzTUFRTmlMM1pCczVJQnlXYlBjSXdaRkhlRUpoS2lBTFNEa0Z1YUZNeV9IT0Y5ekViM0lvSE9mQUhYVEd6QVYza21oV0lTeEkteXNn?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46027.50019675926</v>
+        <v>46027.8984375</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DHL Supply Chain expands Dubai and Riyadh logistics hubs ahead of demand - Logistics Middle East</t>
+          <t>Shinsegae Duty Free launches Cartier fragrances at Incheon Airport - TRBusiness</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 10:20:00 GMT</t>
+          <t>Mon, 05 Jan 2026 15:01:00 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQTWh0dlplX21pcXlrNkRxS0Jmc1E3YUI4YWstWUhjd0xhRFpQWTJacUU2cmNBeEszRlFhZ2M2bDdiNnB1YjFCVk9KN0ZHWG83Yy1YWUdvREFfaWtiZ0RvYjdxc3N4dGpsVEREdldFbnZxbVZDdUZuejA5MkJsMFl2bENuY1RSQUl3T0lhMkxIcEdFUU84WkRwNlUySERad3FXUFJsZHd5ak8yQzctUGJKRjlFWHBQVERo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOb1BuOExNU3RfQncyS19henIyeGV3c1hCQnAxMkJVU1BRY1FaN0o4c3p3amhOMzgxWDIwMFU0dkZGWnF3VU12S1Z0WmRIbDRaeXZLTndFYl96VV84RWNraVB3NzNnQjhZcll2YW5xSGZkVmlhcFdRWXJNTmRTalVURmVoVEtPSlpBVnFJb2M5NnNFakItRkZIQWlzSHl0UWJBZHVDSEJJekFFUVJiU0JyOXRpRDdKd201Q3o5WjNZOHFzdHk5R0E?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46027.43055555555</v>
+        <v>46027.62569444445</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Q3 Rundown: United Parcel Service (NYSE:UPS) Vs Other Air Freight and Logistics Stocks - The Globe and Mail</t>
+          <t>Dior Spring 2026 Ad Campaign - The Impression</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 11:51:33 GMT</t>
+          <t>Mon, 05 Jan 2026 21:13:46 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxNTFgtME83S2dKRDlLVUJ2eXhsanBRYjNxbUhqNmk3bkJCOGYzNEhXQ3pzZjl0M1E3NjVpdVViNGpvNC1yXzRMcncyc01FTV84Sk4xNDhBcjk1WV9xMURsejFLZ2hORkM1Rm5xbFNRVEVyaU5ESVNqRjhsSTFKeXV6SUZjX280bE14X0U5aEwteDVKQllvQ3Z5YkZ5dVVpZDYzS0VsaXZLOUpURTJ0Ym0xeXhsbE93U19fY0V6cDRjbEtidy02NW93c3BDR1Z5RDJ6TURsZUNGclE4TnMtYnNDWFVUNGhUQVh5MFpOZE5ZRW5ZazdRa2pJQ1NwRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1ZR0s0OGQ1cjM5Y0hOTXNFa3A1ZW1hQ1JxQ0VmZUVaNUFXUzZxS2dJVkFxOUlEbUt1dzlVWVhhTFRiOUg0a0hjMjAyWkR4bFBGM2RyWGdYZHo1NzRkOUxJamhZNThUUGtJUkdoU0RaUQ?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46027.49413194445</v>
+        <v>46027.88456018519</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Amazon launches same-day grocery delivery from West Jacksonville - Jacksonville Daily Record</t>
+          <t>V-Mart Retail rallies after revenue jumps 10% YoY in Q3 FY26 - MSN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 09:20:00 GMT</t>
+          <t>Mon, 05 Jan 2026 20:57:22 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPTnVXUnJEM1RiNnd2ZDg4aU5nTkVKR1A5bzF0dlhseVNjdkdJSDl5cm16SzFhRjBGa2FpWUIwM0xyUU5LbVlpRUpRUlA3WDZzWUFlUDl4cjhTTUZJRFpkSFo4X1pVWmlNQWM0UG00bUN6QktPNnVNbDA3TV9NcElVUER1RktxMDFRbzNmTEhPb21lSkVVUW9ZdGxSb1poUGxURmRyQnQ1cDBaSG9IN2Q2UWxWMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOVzI1QjZzRmFUVXJyRjVjVGd3aFZnak5GWFlVOGJ1WTAxZXJjQkd2VlVIamhZQlItclhpRDFCZURYMnRMQW55R19rTDRqQlA0bGZ2cVgtemRNMzNsbVI1RFZtOXd4ZEtWbllxcEM2SHlwR3BGVTJ0aUFRNnZzVllFYUNXamU0S0M3RFJYenBQUnpwSUhVMUdnNmg2cUhvWmw1Z2g4Q09Jc012WmZNMkpweld1YWE?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46027.38888888889</v>
+        <v>46027.8731712963</v>
       </c>
     </row>
     <row r="23">
@@ -1175,24 +1175,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Loss of “large” customers in 2024/25 pushes turnover and profit down at Fedex UK - Motor Transport</t>
+          <t>Cat delivers an iconic moment during FedEx driver delivery - Yahoo News UK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 13:38:32 GMT</t>
+          <t>Tue, 06 Jan 2026 03:00:00 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPakZ1STVjdGxiVXhkeEZIRFVBSTBudlRLQlpJUkNkRGRoTFhxcG9uWkloMmNaVEVWMENuamNzT0JlNTVCSm16LXpMTEVKdkFoUmJXRVBqclpKOUhfcWV1dlEzVzRfVzRya1Z0TFlKclNYa09OV3Ffbl9DMDh4WXFENnlTdkthRktBWFpQVFhsOTRqU2VhT1lSemxMMGRsTEFETlBCRFZWWmNBbmFDRUw4WkRZUFdESG5scW95Z0JfNmlfQWZYSTRWbkFfaWxoZ1lH?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1NcFBHaG1LX1Q2VWYxbUppSU9YY09fS29EQ2ltdlVtb0hweW5UOHBWQ2ZPWXpFa191V0JoUF91ZHpMXzZXbk8ya1RFb2VTSHByblNCeFpmWFh3TkJUYl9pTmJocWxNTGtZWXozeUFBX2F2SkVmWmVOaTUtLXlDYlU?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46027.56842592593</v>
+        <v>46028.125</v>
       </c>
     </row>
     <row r="24">
@@ -1208,24 +1208,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Royal Mail bans postie for kicking over rainbow-coloured gnome and Pride flag plant pot - scenemag.co.uk</t>
+          <t>UPS suffers profit plunge in 2024 due to “negative” economic conditions - Motor Transport</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 11:01:20 GMT</t>
+          <t>Mon, 05 Jan 2026 17:38:44 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNMHM0LUhqQVhTNHpoNXA1YlZpRVA1NzVmUlBDVkNkSFNmdmtHTEM3NmpSUlFYRXlrbHo3b0JoeFJiVVlFaGdLNldzTDVrb0lmMzJKSERONTRMVE9KNmRPSXR3YllwQWdsM24xblVfTU1Lamp4Sy0yckVwZFp4VmtSX19TanRhVnFlM3ZjdWo3ek1KNnFaRlhjQ3RDaWk5dXl6RUlWY3lNNzBhWTg3bzBxWg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQenAzbzJ3T2hlM3hOV2EwMlktNmJPYnFSYjZuV1pzWC1HZlRHd2d3UXF0MW9CTVFDVWZ4c2xBcUh4QVBCUEJJRnlTeDJwUG9vYmU0UDdyeWdFRGJ6aTAwS1diT1FEQ2hZcHhzekI2SXFjeVRDc1loTmtwUzgwT0R5c2JaeGVaNnJoc2Jvc3lTUEY3cndYX0k3QTlOak5CY1ItMXhSUjZVai1YaENKZ01qWHgzSXNXMFVhODFFcVZscUQ4N0pl?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46027.45925925926</v>
+        <v>46027.73523148148</v>
       </c>
     </row>
     <row r="25">
@@ -1241,24 +1241,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Samsung, SK Hynix seek up to 70% server DRAM price hikes as AI boom tightens supply - KED Global</t>
+          <t>Royal Mail and courier service Evri criticised over delays - Armagh I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 11:50:00 GMT</t>
+          <t>Mon, 05 Jan 2026 19:02:54 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE85R0ZiNnZ6SVdlUHFzRlBkRndDc25mNWdLSzM0V0JLU1lMdUtOYjNtZXZld29OZUdONUN5TmhlT3UySWVyWmFoSFhJZHo0YV9nMGlwbThXaEZ1Ymp5cE1ZbFJ2YWJHN0FNcEVpaVB2X19rSlF0WDNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNZkNZdUJsN2UzLXJnMWJVdy1oT3FHQkROZ2FJaG9YdWNSN3RRVlFNWVV4aTN0dHJlV05wZzlrVlY3YnRFX3VBQ1hTUTF5Y29Ub2E1YUlfcExlRi1CNTdGUFdncDU2YXQzdW5ZV3BjdEJzMXJTU01IRFpxb3FnVUJMNFlkSzB6OUMwVGY4WDNUcW9GcTQyT1R6MG9fZklZOHZBNFRHTG9fdTE?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46027.49305555555</v>
+        <v>46027.79368055556</v>
       </c>
     </row>
     <row r="26">
@@ -1274,24 +1274,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Interested in FedEx? Mark Your Calendars for June 1, 2026. - AOL.com</t>
+          <t>Amazon knocks 25% off plug in radiator with next day delivery as temperatures plummet - Liverpool Echo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:34:48 GMT</t>
+          <t>Mon, 05 Jan 2026 15:24:00 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPakFhTGRfTUlxQXZnQ2RlVnF2QkhfZTJEdndmTkpOOUdodjRocDlUTVVaeXplUFBhVTR3SUFNeExLdjE1a3F0d09wM1B5QzBXcmpQX1ZBTVQyVFdEcTZsYTNOZ056T3lmd0E5QTBDcFBCMG9lWkU0SHVqX0ZPU01EbHFXZEZDZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNVG5zUFFXNDgyVUFiRkZtX3lmQnRrdzFuY2dHejlJNEFJZkpPNDNlVGdMenZUZ3ZkMEp5VzNjbjNYQzZPeWJ1U0NpdGpHcllwNEFmZjBGRWFQZWNGYXBqZXNMX2xlNE96N3ZId1B5YVA2MXh0U2JsMkUzdGJpQktnSmdyLUZNOEpkd0FhN0JrUVJQYW_SAZgBQVVfeXFMTkRHZ3VSWmlmRVY2U09hdEE5R3VaQ1dOV21Ldmw4MHVhd1pLa1N4YXpvbThUZjhvWVUzTEhiRXh5eFlnb2VYcUtrdTlxd1ZxYWVkUXMzMnJOOUg3clluVENDZk5ybGZzVU8zVUxvMkZmRDRrMlN0ZEVEV0lMVEN0Z0ItQ1JpWnZDLU9USDkwaGUzZ2FsbUlKMmY?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46027.52416666667</v>
+        <v>46027.64166666667</v>
       </c>
     </row>
     <row r="27">
@@ -1307,24 +1307,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Amazon loses court fight over NLRB process involving DSPs - FreightWaves</t>
+          <t>Amazon is testing out 30-minute delivery in Philadelphia - MSN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:00:00 GMT</t>
+          <t>Mon, 05 Jan 2026 16:06:48 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPV2Q4TG5qcnhRTjZXUnpvSXJ0Y0RfUkZBcmk1dlBDdUxtRzctejE1dl9WWF9aUWpZdmlxc2Z6Y0tQSGRNUVBfa0VaMUVmMjZYb3FnSkpKc3IzdmQxRGdGQkQwbEozUGdIQUk1WEZ6YzhrV2doTWdlU3dlYUdKRjhhemszT2ljWGcxOF9nQ0R5b0ZlNmpNekE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAJBVV95cUxQNkFzc1F1T0VPZjhRbWdnWWowYjNJUVU0UUpWMWdMYTZxdHk0NlFFMW9McTJNNm56Ykk1NFJZcGFhclRVWDhsRjR6eTZtRDdBNk1MRi12TmgtTHUycWhNVGZBbDJ3M09HMzd5N3VtekhEbERFUWp5djRTVUJFczNPdUNpdGdPZFRwUkFXU3RYUms1aWVXQ2RHUzlXYW4weWVwOTVjYm9WVE5OQ0tqdWJLRy0ydWhsZmtINGRYeE5OVDJwb19pZjUtUzZhYllCYmRFQ0Z0TGRtQ1NPeDB1TmRHSFZaNGFtSlNJdnpMak1tQ2ZrT19PUERMeXRHd1NYbnkxd3VSS1NmWlRpam1sUHlNdGlCTDRNSnp2TFBGMXplc2dJRnlSY2hIdV9iMklrTkVFb19lQm1RTTdNUXJ6b0M1Q1BqMU4?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46027.5</v>
+        <v>46027.67138888889</v>
       </c>
     </row>
     <row r="28">
@@ -1340,24 +1340,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yezdi Adventure &amp; Roadster now available on Amazon &amp; Flipkart - Team-BHP</t>
+          <t>DHL Opens Innovation Center and Invests in Contract Logistics Facility in Dubai - LM - Logistics Manager</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 11:08:14 GMT</t>
+          <t>Tue, 06 Jan 2026 06:45:59 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOVGVkamg5ay1Ya2xiaDlGRXB0NldzemkyeWl2R2pYYTJ5bk1nSFEzUDNLWWMwc3ROQmZzRm1ZTlF6RTdjX0s4YnB5NzdpbXdlOHF3X1V4YnB4cEpQQzRNbEdvLVUyWHhlOHQ0cGhkTVBCb0t6eFBsbEZUMko3U3ItLVlMRlJMb2NnS2N0SNIBkgFBVV95cUxOUkZPSEJld2wyX2hmV3FDb19Ia0h0UHNOeTFoSGdySmtRTVBZRDc5ZllzUEVOQ2M0bF9NVGRfRnJJRGVkZHAwcTU5VnVQVjNEVDZiUVR5eERTdTB2c0dlWXdrUGIyblhwX0Vod2dwZmtYd2pnZjkyT3ZsaUU3eEFtWkljT2hhUkFBYWZMei1pZ3B3dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOWkduUGNYYW1FWGVlZkRkTW9uVmtJY2EwWWFvcFpaRnhqcUR6NVQwM2E3MnVJclcxMHFTYlo1UnVyT2h5UExjckFUSFdHM0t5VFg5d3lCQjZELVVpQUQwTzQ3WllwSkpIbDU4c0tTYV9TRmdka2ZvS2JxMThpbnZocXdnRmEtVF9xcFRGdGVRYjBNX1gzc0pITmpZY2ozbGNvVEVZOXlvOXlYa0wzV29B?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46027.46405092593</v>
+        <v>46028.28193287037</v>
       </c>
     </row>
     <row r="29">
@@ -1373,24 +1373,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>U.S. Marshals Arrest Amazon Driver in Philadelphia Road Rage Murder - The Auto Wire -</t>
+          <t>Say Hello to 247 New AWS Competency, Service Delivery, Service Ready, and MSP Partners Added in December - Amazon Web Services (AWS)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:05:03 GMT</t>
+          <t>Mon, 05 Jan 2026 17:10:21 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1UeWhmYTdHN3RpRU9CZ1VQaDQyNkhsUExnY0lZV3JLbzBYMHN1R0V3dWUwRl96bWZoel9hTC1NdHZGZlZJN3JTM3pSVmEwY0JXWDRqY2dDV3lEbm54eDNzcE01bjhRV0pnTVNPczNuRzlJcHRVTk12OA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNdVZ6LU1KblYyUm5FaDczczAyMGxxdmplX05GOF9MczYyVmpIbUNnLUVOcDJYbjlmQzM1R2QwRHJTRmVxRTY5N0stN2hGaXdtMlJhUzV3cXlBdG5WNU9Yd21WZ0JDX2J1OW0zaTA5eVJZRTR1X1hmSWV5ZDl3VmItSTZQNXJlb2dXVGhMUEZRcHJtMGR6dXV3dmxsTmctQy1oRk9KUHpHY1hWRGNoRzZDWHo3ck9lU2R3cmppdTMxNlBfX1otdzVJQ29XaEhCYXpK?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46027.50350694444</v>
+        <v>46027.71552083334</v>
       </c>
     </row>
     <row r="30">
@@ -1406,1773 +1406,2796 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Viral: Swiggy rider with young child refuses cash tip, only requests good rating - Dynamite News</t>
+          <t>Woodsboro family searching for puppy after delivery driver drives away with dog - KRIS 6 News Corpus Christi</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 11:17:31 GMT</t>
+          <t>Tue, 06 Jan 2026 01:27:24 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQSE9EZ2kyMFZJQkJlQ0s4enEza1JtekxPbUJBVml4cWxtRlhkYlk0d1ZwbDFRdkNKVWNrUEgzTC1xZXZOWWpGQUhyc0R0T0dRb1VMa0NNdWFJaEhfTW9QeldaVGlpSWZFWlloa3pDa0FxU3BBbndaUmdIYzdaQXVvZjJFWmktYzNXVFZtclY1NFJudGpRUERMdFdtSWpWbWIyZ0xObWFqNDk5cVdKX1VraXg0VzdBTG800gG4AUFVX3lxTFBIT0RnaTIwVklCQmVDSzh6cTNrUm16TE9tQkFWaXhxbG1GWGRiWTR3VnBsMVF2Q0pVY2tQSDNMLXFldk5ZakZBSHJzRHRPR1FvVUxrQ011YUloSF9Nb1B6V1pUaWlJZkVaWWhrekNrQXFTcEFud1pSZ0hjN1pBdW9mMkVaaS1jM1dUVm1yVjU0Um50alFQREx0V21JalZtYjJnTE5tYWo0OTlxV0pfVWtpeDRXN0FMbzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxPSXRNeGVkTEFQOWhiMHJDalRidDdnR1BOU3lsWWRkbVBKbm1yRHRiVTdIU1pPbmstR0hNUVpNVUdsbHFNUEFwb1Z3d1dZTnpjMGlETFM0TC11Q19mZkNaeDIwOFMyWDNvQW1BbmZvekhWaEp3eWw5T0l6aktLTVM1N0RkV1RlaGdtV19SQWlIdUJIX2wwNzNZVzl2MlY4ZTk2di04MnBKcTNSQWd0V1R2TDRXMjI1N1J5SUF2YjZRZW1vbmpOSlp5Yk1odVJTMVBaMDgyUTYyTkV2a2VtbkpKWldka2t2TzBYb0E?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46027.47049768519</v>
+        <v>46028.06069444444</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LIVE: Ruben Amorim sacked by Man Utd - all the news and reaction as Red Devils axe manager following explosive outburst at club's board - Goal.com</t>
+          <t>Dozens of Fort Worth FedEx workers will lose jobs in March. Here’s what to know - Fort Worth Star-Telegram</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:06:22 GMT</t>
+          <t>Mon, 05 Jan 2026 19:11:13 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPU1ZwYzlJYV9la2RyLVhscWpoLXRwX25wZmtlTHlCNWFvNmNrbVZHaWZKQnF4RE10S0o2V0J2bXVjODVEWlA0NUZDUll5Sk83Tkt1ZFRrSEstOHpiMVhCMkFnTGc3ZXR1elhfRklacDBtSDZ5QS1xZmY4SnRXb2ZFRTVYRTVfeFBPZFJLTHRPLUtPckVvaUs1VW1BSnZncElHSGxwcU14bnI0TXIwZ2NsT2ZJdWYxTEExa1R6SEVzamZ2bHdC?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQcGhDenJhSDBKVkw2SE1rV2xGNmp1VTBNdkttRGp3QWpIYi12aU02cmVNa0xjaUt1TjJYM0FkLVlIZ09uSi1jc1hCWmVIWWtvZ3F4UzRvMnBzaFgxU3JVXzZPd3NjUm5RWTM5NnMyMXB1QTljbGhxbHNYdGRoZUtpZi1n0gGCAUFVX3lxTE96MlZrbFZXbVhua0VWMkZ5VWRSMzdOQlJ4OEJkU1h2R2dzSnQ0a2toMU1UTVNjWDlCdVgzRkxQNWY4c240bmVBMi1HTlB4NjVBZWxUZU1Ibmw4WW56MTJoVlkxdnRUTW1WT3ltenVyZGJhTkhMdGw4WWVDX1ktazRHWmc?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46027.5044212963</v>
+        <v>46027.79945601852</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>The 'geopolitical bomb' in Venezuela pushes Defence, Leonardo flies in Milan - Il Sole 24 ORE</t>
+          <t>Amazon Driver Rips Open Package, Dumps Wrapping On Lyndhurst Lawn: Cops - dailyvoice.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 09:51:14 GMT</t>
+          <t>Mon, 05 Jan 2026 22:41:00 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPVmhXYmE2OVpTT01UNHRWQko0TGFLX0tDRnJJSXMtbDlKYW5zenBKcTFOQWdCdlRPNmZ3T2xIaFAtS0c0QVkwcmliWmFncmdGb2oyTVdBSlpLemR3YzNoZlV1Qmd6WU9abVVhLUZIaHA5bjMtdHNvSGk0Y3JDZHBDeFgwWGt3VTBHU1lPM0hKenlyeXZuekItT3lqWFduV3BRLWNkaU1ESVBJSjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNaW0tU3dvNnRvQkZnaUJ6SHdoM0UwZTlOVkc0V09MTGxSbWV3d1VXaGlsbmstTWo0SDdOR3A5c01OV3BvbWgydDJGbUdXVS14MF9zMU55Nk9neUVkbDIxc3h5SFdKc3BwUlpaSmh0c1lRaEpHTnZ2cGJSNVRjQ1hmQmdhOU5vU2pyZnJWVkxNZ25vOVRlN3JkU2RYbnRZYm9MWGhVTWplcUpXaU5MSERpUTNnNU0?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46027.4105787037</v>
+        <v>46027.94513888889</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scientist believes that humans are definitely heading for extinction - here's why - Indy100</t>
+          <t>LPD: She delivered a package, then stole it right after - theobserver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:49:19 GMT</t>
+          <t>Mon, 05 Jan 2026 21:56:38 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQeWNLaGFaQ2d1RzMxV3VoTURkODE0SC03eUk0YWJvN05ucnVrMVBKWER4bFJZb2QwV21CbjVOQUtGMGZOYUFxaWo4eTdlVEpjVE5JMk1JNWpNbWREYTV5aFFkN2taTlRTZkxhcS1uaTBOMnE0d0FvU0VrRWNEbE9oa1NjaVR4bVR2WUFWSVdJLTlQWkF0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObWxGRnAzREhMaG41a1ZyT2N5VWVsZHlZdk8zdDZ0VUxHV084V2FYWmNRbGVORktNQUdGWXUwSGxoTlFrSzlZTnduUjFtaXQyWjZFODJVeG1ZalVfeXhSalpVaXNfZ1V6Y2FYQ29xX1dla2h2bGNZWUo1X3dCajY5eGpDbi1TN1hoTUZtY0d4YWFfSEZXZUFtUg?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46027.53424768519</v>
+        <v>46027.9143287037</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mensch Publishing announces first graphic memoir – a preview - downthetubes.net</t>
+          <t>Amazon delivers same-day groceries in Jacksonville - JaxToday</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 11:43:29 GMT</t>
+          <t>Mon, 05 Jan 2026 16:00:29 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOMzJXMUt6NVV6TW85aEg4SHpPUTVSV0VZdU05dmRlUWg2T3FDdl9BMVhPSV9DVGZuRnBzWGVFdHVITmZYVHJyUjl0dVYzbkJqc2ZFYWc2V3NUVEtveWZIYkNhTm1mRTJHdG8xeWJRU2pVWnJlaXRKUG5uc1BVVWVWZ0FqUzY2bFhPUHo0aQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9aWEh5Z1hPZmU3WHktakJxSVZVWmxMOWl3S0VGaDVlamp2blVvSkUteWJqUlI2T3ppbFU2ekM4cXQ0aWR5XzczUXlrQXdYaGxtNEFLdk1sc2FjUFZvdXdubWVaU3M3bjE3cGc?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46027.4885300926</v>
+        <v>46027.66700231482</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>647 arrested by Knox County retail crime holiday task force - WATE 6 On Your Side</t>
+          <t>Now you can get your Amazon parcels delivered by robots instead of humans in Milton Keynes - Milton Keynes Citizen</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 13:05:36 GMT</t>
+          <t>Tue, 06 Jan 2026 05:41:00 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNSWlFZFJELUJTb085OUVlODB3VS1PdGxyUkZYWGNXVEh3dTJxZmNzVGZ6SU93eTRxd3d5OW1LVldNbTUzNVo2SmFhcmFRNWw1OUFucVBEb3VjWFkwVjEzbmRRdDU4NFdyM3JKbllyelFEbnVkSnFScWpzcHdPZ3Y1TzVFSzM3bVlMRlBpSFpDWGxtd0pJMDNvRGJwa1VWVHVMMjdxN2Zn0gGrAUFVX3lxTE41R1Z4NHZlRHlCcjZFZy05NDd2WEhlY0NVRm1VQkd4MUp5Vm1rZzNQN2Nzel9kaENIR1hkWVJWdlJQV2pTQjNReEtYQ1ByQ25pSkIxMzl2MHZoQ2JVTTQ2cU1jSm1GZ2RVUF9kdFdHYjgyR3daeGF2aERteEtSOW9KTWJVMzNQVFNTUWVnUl9oY3hxajlqWjdlRGNyc3M5U1hRRjc1NHBmbVU2NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPcElWVjVFTm5TVzdHZzRGRlF1Nks5ZTJxQnl6bDQtNlhIbHRPNFB1MGxia01YQkNGazdMcml2MFRwalU1dGxrQ2syTkwtOHplTEJjOUUtMC1KMnFYOUM2S21ySUxfLUM3T25YZVQzTnJhUThQQWJfc0ZBSkFmYWlCc0tpZnd6YUNnNTFHdTRTSUZ3dFhOU045bl9IMHNCWm5VcWVIdnFTMy02dVpmVV9GN3hsZmpXel84dUFFRFNMTVl2WUFfUGZ5aUxoTlVYczFpUWgwekQ5N2g?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46027.54555555555</v>
+        <v>46028.23680555556</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Waitrose bike thief banned from scores of shops across Sussex - Brighton and Hove News</t>
+          <t>Pictures show progress at Amazon's giant new warehouse beside major road - The Northern Echo</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:24:00 GMT</t>
+          <t>Mon, 05 Jan 2026 18:00:00 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQejJPODU0Tl9hQnVhY3MtangyZUppRFljTWhyWEl1bXBlczNXTUNicTBlbHFpeEI4czlTZ3l3dlJPX1JSTHlfc1dCV1JuZnZQT2dxNW1KNGpWdWdBSFJTc08zREtESjVhampHQ0JqWGhqWVpBNk82aUxLcmVfeU1CeEtxMzJFbkRoRzNnNUdsaU9xam4wbXdZenY0Uk5TcGV0NEdQbzQ4TXZYaHV2bVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNckNJREhibGdzaGdMLWYzU1A0bE9HUUhaMVpael9mOGY2UWZyU1p1MmRCWFR6UXVMTlZFUnJ4LWRacEtzamFEUlVhb2ZsQmhPVmx3YXFwSWZEVDFaSHBpVE9wR2VRLTFEdzl1OE9sTjNDcTdabGVzLWNZTDJiMktTWlBjazdFUWNWaDloTDZpWGJxX2ZFUkRLd3ppM1ZFLWxWVHc?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46027.51666666667</v>
+        <v>46027.75</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Three charged after New Year's Eve assault in Grimsby - Grimsby Live</t>
+          <t>Implementing consistent DNS Query Logging with Amazon Route 53 Profiles - Amazon Web Services (AWS)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:09:00 GMT</t>
+          <t>Mon, 05 Jan 2026 19:50:59 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPOWdjVHBpWjlTZ3dyOG1Pb2xOVDJDOGdBTUFnQnQ4NlFZRG9SN0hkS0J6OFFsYlVzZnFEQWJUdVRvWTVvaFQ3X2Rhajg3QUNmTXlXWjFLSk54SFlUZzZjNF9xTXFfNktOeElhMlJXcE9MM21aR2FEcXdBd2xzOXkzdGFPUEhObkxaV1V3ZjgyOHI0VVltaXfSAZsBQVVfeXFMTUVVZC1QejNDemRKcFo5X1NSekhMZ2dnV2RKTEJKblV3OTJ4THNHTzQ1TzVhN0wxaUxCRUhacU45Zi1pWFBPYkpoNkVMMENGYjRQbEhoQUY1Nmk5X2ltTFRqMXpCWEV4ci1UZzlxalYxSkFQd1U1VDMxNDhHcHdiWFROLVlEY09lUlZJNncxbHo0c1R1Ulp3dnVLLWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQeVZiak55bXZVdV9hdEs2MW9CT0QxUjZsQnIwTi12akduSnF5dEZ5ZFJuRmZRNi1QdlJSc3E3a1Z0aEEycEdGdzVaWkROVEFYMmx5MDhPTTAyWW9YXzZqdDEwNFdjMUJtRk5ETXM5b2JDUFlUYmw5bUpzZy13YkdSNXdGSnkxV0pKcDBMOEJiY3k4WThGSjB1MkdtUTI1d29ENGFWY09fSkpNTHNsLS0wRGIwRW1sbTF3RFFCd25CbUx3UEJIMFU2RGl6WVpYQQ?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46027.50625</v>
+        <v>46027.82707175926</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fagin gangs are recruiting children from care homes to shoplift - Daily Mail</t>
+          <t>From SAF to solar: DHL’s bold steps toward net-zero by 2050 - American Journal of Transportation</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:14:16 GMT</t>
+          <t>Mon, 05 Jan 2026 16:48:00 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxObGgtckxJX3BTSTA3azhUcmdZbTBtT3o4cjhnRW5GZHRvZVY3U01iZHlUcHUzOExvWXhnbVFsRHVrUHRSeW1tTFJxTUFMc19SN3dNQk85Q0tmMEhTbUZZcHI4T3djZXlzQzhYM2Ita2pNVU9PVXVwbWhJYnB3NDRFQVdiZWNvQ3RxWEx4RnF6cW1objBvUTN2SlMxSHFjaldGcFNBRl9oY2NTN25XaHlvRDdHb1hOUS1ldGVmc2hVbmFLR1V2SnZYQld2cmtlZnVtcmRPWG94Q21KMDF3NEZBamFrUDVTSW96S0FfRVliUEQyb1JtM1Rn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPRU5GOGdWZGg4TXpheUhPa3psNFBKNElWYk10a01MUW43QndVbGx6ZTdLXzFIRFZwdERQcnlnS2szaTV2ZGhLNFFhSF93czNmX3FxWk9MbGwySnFpRkEwaTJxdWRyMVRhQWtqc2k2U21XLUxPeWZSeVJTMXM1UmtiSFAwSDdscTJRX1dB?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46027.50990740741</v>
+        <v>46027.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Holiday task force leads to over 600 arrests, Knox County sheriff says - WVLT</t>
+          <t>A scrapyard worker injured in the UPS plane crash dies on Christmas, raising deaths to 15 - OHS Canada Magazine</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 14:10:00 GMT</t>
+          <t>Mon, 05 Jan 2026 15:20:32 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPMG9PVXdTT2ctUnBHYnJMQVNwbF9oMHZoSHVZME5CZWVZVWRzU29nYWxiMXB5X19MX0p4b3lnQU40Vm4wYzZ2TW4wU3FGRV80WVpZVXV3MEdkTlg3blZEVmtSZ2U0UEZSWFEwTHFLMWM1aVBTdC1fU20xRnlVUDhHVXpUNlRFT0RkcGItY0Z4NUcwWHZGU1hWdVcyZWlqbVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQTzJEQ3hFMmctSm4xMV9KbVhpUVlLaFJXNVRBclhjb18zUXZ4THAzTzFlZWpZeGQtLVdTNmVuQ2Q1bXBZcTdsRlE1dFZHN2hFZzVnR0lmaUNiMDFBS2twazMyRmFXbGctLXgxVzRhNXVmOWszYXA3UEpCb0I1ZXViUzVQWkJYNWIwUWljS09fU0JQTUJRcGVDRHA0aVNYQkFmNmNSdC05djk5c1dyZGptSE1UTklRdw?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46027.59027777778</v>
+        <v>46027.63925925926</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago area cops find $2 million worth of cargo theft merchandise - Truckers News</t>
+          <t>1.3Mft² building to employ hundreds in Visalia, city believes another Amazon could be coming to town - ABC30 Fresno</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 11:15:48 GMT</t>
+          <t>Tue, 06 Jan 2026 02:38:32 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOZl85UlVaU01PSWVIQjNkNHc5REtNNE90T1F0RHdsNF9zdFJfcHZuOVJud3phV29lckMtbzhFTkxvSUdDOUNIaE9GYlcxWWRmZ0NLQVN2ZGZvby1BanY4ZWdzRVdoYkpHOXlzc0tYRXJWRUx6WTB1RC1TVUMyZ3ZtM2puWEhmeUh2UDNCYTZsRzBkOFdCa0pjeHZmSFJYSWo1QXV0dTZvZ3FFekVFUUtHaUtGeWZINzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNTDcybTNmbFR6Z01HeU9YV1FieE1vbHU4MWNoWG9UT3hVMk1HTXJpaVo4c0ZmTWJTei1SSjBTc0RYMmlmUHliUWpqdTd1ZW8wT2NucXM1eU5EX3R5ci1GcTdjMFpIZC1qNlBjVU1ZWnFwTG1qOE5hd0Z3LXV2YlJWM1dPV0RpYmktUGt5TlE0TjY1N2ZGRnJwTUhTOHhvWnVxR1hleXRrVFF6OTlHNTdJS1lJV3Z2VjUtT0HSAb8BQVVfeXFMUHBMNmtFVWc3RjhubnJBLTBvcTVMWXlYYVFCVjhpdDVRV3AxVm9PVkRGTmk5LVhyc2ktVXhaSE93Mmd5aXZrNlJUazdXVlZURE80VFRXMUtXbjR4U2FRMy1WZWs5VGhtS1JDYVJSTXpSd0NWY3VDbUtzZGRzLVFtUmI0SUpMRGdDRlVuYUF4bThVb09jTFdwd3p0NS1TWG5SRjk4VXFCVlMtRUtjMzdJRlBhLUo3S1JsNWk1b2FjNlk?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46027.46930555555</v>
+        <v>46028.11009259259</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Real Madrid's Adam Wharton stance 'revealed' as Man Utd, Liverpool are given transfer update - Sports Mole</t>
+          <t>IKEA battles Amazon, Temu as market shifts bring pain to flat-pack dynasty - Orange County Register</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 09:07:00 GMT</t>
+          <t>Mon, 05 Jan 2026 20:55:46 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxQUzVJellCNFd0MUh4NkRoTkpvSThHaWljVloyYmtRNEpKS0pnOEMtOFgxVTNkOGppYkF3RzNRZF9CbDJyNFF5WmJpUklZaXN5a3UyTGdaVU9senFyTm1Wd2ZBdnZoeXhIaTlTTktFNi14U0VISjZwOXlBU0JXa1hjZ256b3A3MlFxTzFNTVdhUTNQUDIxZGxIMjRzbHJCVW05SzFicEhNb2tUUDJsMWRraGhPNGJYcjV4WGc2X3J0UFloWS1ZRFJUN3h0TG82ckxoaE9ZMmFCcklPdVVjVDViNG1KTUtpQ0hHWWxRUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOLTNhaE9uTVBicFdTbkdYTnlKNktUWDFwM3hSZmpqVUpMUHMzZXpsUEFfREJhel9aVXo3SnBqLUs2dHEtS0JmZkU0TEZkb2luLWRYYnRKZ3VtcGZrMzJrSExkN0d2V2NfYlRWWTVWM2h4REZtUXdhVlNnbHZYQURjZUNRbGc5LWZiNlhnMDBGbWJ4akszbDlaY1d5UQ?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46027.37986111111</v>
+        <v>46027.87206018518</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Real Madrid injury, suspension list vs. Atletico Madrid: Kylian Mbappe, Dean Huijsen, Trent Alexander-Arnold, Eder Militao latest - Sports Mole</t>
+          <t>Last Call: $250 Amazon Prime Visa Bonus Ending Soon - CNBC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 11:30:00 GMT</t>
+          <t>Mon, 05 Jan 2026 16:21:26 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxPaVJNdUJDd0RNVzcyMGFJTVB1SkFnTEJhRUpIZ1BmeHNOa09HQTd3TzBKeThjSVBJWUxoNGlkVVBOSnJkVy1ZQ2NWdHpaWVlwTUlYRXNndGtwTUsyWEFSR25ndXhwX2dkZElfMkxpTEVLcUlaZ0x1eGRYNmIyYXdTV0N0RU9Kbl9MNF9fMnUxWXVIT3BnckFDQ1h6NTJXMWtJcjNmUkF2aWtqUDFOZ2ZLdEp1bjJKNWxHVnV2dFFCMkhhMlo4YkxIczlnLWhKTU5aUVBNaDJYajQ0b2gzSXFFVFFXYm5nVGNWYWF3b3BHWDVqNy1GY0dBTVQ3aDlEaldSX2VCOW9ZUXg4c2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE81c2twamlkQlk4R1BXSzJCUXJOZW9hSHc4Z0xyWW1sdVZtQjNFZ2V1eFQ2WW5nR01QNU1LNE9reGlsV1k4S2Mxbl9zeWlreUI4YXpxTUxrWXJPMEczSVVMT3loQmozY0Rzdzk1bXZ6UElvTklEX2NBdjMzNWdocmM?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46027.47916666666</v>
+        <v>46027.68155092592</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kobel smiles away rumors ++ Gregoritsch back in the Bundesliga instead of FCB - bluewin E-Mail</t>
+          <t>The Truth About DHL Group (Deutsche Post): Is This ‘Boring’ Stock the Sneaky Winner of Global Sh - AD HOC NEWS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 08:48:45 GMT</t>
+          <t>Tue, 06 Jan 2026 04:58:25 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPdS1NLUhIQklGT2NmcjBZbnZ2WTA5WU05a1hPUjd2a2JqZUhUSnhQSEVkNk1xVHh1SW1iZ2tjN0VxRlRvamROYWN2Z3JzS3JFZWRzVTlZVXBHTmR4T3hjN2NSa0Fkb0w4RVdMSExYRC05SGpra190S2hwQ19EcGdyQno1NXRBbEdmS0d2WUUtajh6UXFLdEVIWkRJTjZoSWg5cTVOZWNTZlp4WXlUc0pGREhyWWRCaUtia3B6WE9YeDk2YXpJUW93?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOaTdMNGpXX3BEV1dyT2lCdFJnazlpLWlCRjRNZnRpQjhUVURFZklJQzJOZkd0MVJIbG1GY3BPclR1blo5SUNWaHhXSEl6YUZmLWxTN3RCVDBQTFhhcDByM0FnazBKaTl2TTZSN3JyOW9NZmhFWlYtN0ZxeUNxT2wxVVZNelFrNms5bXE1VXc3eUQxcDV2RGlIYmJLdjlaSHJmUmdwZDM1ekZvWGhndTlzV09yZDFMTlhrRXhYTjFwQjk?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46027.3671875</v>
+        <v>46028.2072337963</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Next Man Utd manager odds: Clear frontrunner in race to succeed Amorim - London Evening Standard</t>
+          <t>This ‘Very Powerful’ Ego 4Ah Battery That's 'Built to Last' Is Nearly $100 Off on Amazon Right Now - Men's Journal</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 10:25:29 GMT</t>
+          <t>Mon, 05 Jan 2026 18:00:00 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPS3pGTXo3djgzaEtKaHFPMG90eGw5Tzg0OHMzcVJjbXNXdlc5YndncTM3bFFQUDRKQmp4TnIxcElpd19KeUVFU1pzZ1YzUVhxcUZESEd2ajRBYlFLQjFMWDNVcE5yUGQ2aE44WjB2THNScTEta0Zad2otZkVOenZmNmJFT2l0ZDQxU1BUR1ZYUWZNWXZZRkdmc3VkZ2R0dFZWaGo0aEs5aDV3Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5LbjluTmdGNnBLZXBtTkZGMEtPMUZBYUtITkhfbk9qTmF4WEM0b0ZnM0tOQ1d4ZFlXZDZ3cE9hbTFibzc3ZWFKdDJiX3VxUi1uRlRuNTdiOS1HcmVJTlVmS1p2LVRuZUdRYUI5RXA0N29XU1ln?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46027.43436342593</v>
+        <v>46027.75</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Five football managers who have been sacked after fiery press conferences - Flashscore.com</t>
+          <t>Amazon is selling a smartwatch for 91% off as a New Year’s deal - thestreet.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:43:07 GMT</t>
+          <t>Mon, 05 Jan 2026 18:51:18 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPd0U1eWJ6Y29UZXlYa2JybjFNb2N5UjVNZFRENGRwT1MzZTE5OE9mR2U0ZzdOSWJCaFdwa2V6SlNyazhiRUp4NGI2UUVET2Q0YnZoc25ZYS1GNjkyUTZ2V2FZRXhJd2J6bWpKb2tMTzh5WFdybDdlZzZTak1xUkxjMWFSR2tQU2QyT2stYlZQN0J3Qi1SeHpRRU1aX3U5ZGpjU0hodGZCczllX1B6TkRuTUc1cGk0OF9PbWpSaHF2c1lvRjgtR0pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE4zcU9QZTRuOGcwbml4WDk3N25yRUVPMnBEeFJGMmxMNVp5dDB6ZlJHcUlfNl9hdnN4OVo5SFh6UVFLbFpqVVk3SFhocEREOUdYY1FTMi1JbU9xWGRhN05tdVdYQnVyM1BhQjBNaVByNzFfeGpVYmFLWFo5SFU?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46027.52994212963</v>
+        <v>46027.785625</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bayern star offers himself to Real Madrid, he is the new Lamine Yamal: 'someday...' - madrid-barcelona.com</t>
+          <t>Motorcyclist dies after colliding with COTA bus in Hamilton Township - The Columbus Dispatch</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 11:00:00 GMT</t>
+          <t>Tue, 06 Jan 2026 01:00:00 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQYUlXSHR0MGxNRHAtTE5URk1sWHR1VzVvWDk3bldEeTZtQU51RkFhYWRLQ3VFSko1YW1WUTBnd2JZOXdOU2JkNmp0ZWVRdTdSeTdLREQ2OWxrN0FlUll4QllMMUxDZ21WbjB1YzhIMHJrc2NIeWpUUnQ1Ry1KX3NxcWY3RnJoR3drLXZ6YW1jSzB6aENtMXBvRlBSdENMR3AyQ3MzWWZuVUN6dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPeDJ4VVU1U1MwQ3RoM2paOGpDRFpfNzVMRzR4VEZScTh1eXRuLXRVZ2FOOVZ3VzdVSVhielo1RTF4SFd5RU1fSTBmYWROY2NVbExxXzZfYVAtRV9XSGZWTFdQRm8zdXc5dUQ0M056cXVzZGxxM2V6WnlZNGtWSHplX2ZtWV9EX09rdFAxMEZaV3E2N25YNkxTeDRCLURodTZlNm5KdklucTlkTy1sUlNMUm12dWR6UDNZb0hUcFI2OHpJY3ZYbUVuTTRtR1pUeElwWlRB?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46027.45833333334</v>
+        <v>46028.04166666666</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Village Search Bicester and Kildare</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Motorists caught speeding in this Kildare town despite freezing conditions - Kildare Now</t>
+          <t>Two-to-One- Ninth Circuit Aligns with the Third Circuit in Circuit Split on Injunctive Relief Under the Norris-LaGuardia Act - The National Law Review</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 14:00:00 GMT</t>
+          <t>Mon, 05 Jan 2026 18:49:40 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOYVpheUUzT0tQdkF6cEUzaUdrMjBSVzZ6dEdoQ3VBMS1NLWZCOEpiYmVqLUhHWG1pWktkNXlpSXBTY01lZV9ZT0pCcURPTC14ejlsUXVJSHdsdzVRSGNnYzJqQnNXWVRkMGQxSkk5SFdpQkVoYjlCS2dCVGkxdVRuRFlYNjFGNVlVUXA3ZXZYcVpUTzUtVGFqbW1ReC1SeGdPa0hlZTlSdTg2Z3UzUmFtYUhpNFl1R3kyWW51LS1FZ3NDMEtqVXE3QTN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQVlViMmpaZzFyOUxIUkRBanVJVnV2OThpbDNLN0t0YjFMNVVENkhrM3oxMEZub0pKTFNGaDRJenM5U3QtWEd3YnFFN0pWdHlaUmdDMlJLMmI1b2NWZ0M4Y3NoLTRyYUZ2WDJ2Sm5XY1YzaXJULWNPUmI1em52MGdWSll6TUdERmp1TkVKY1V1SW0yVF9yWXlQTzZpQW1QMlFfUHh2ZkIzZGVBc3lPR1hlenV3ZDFDT2h30gG4AUFVX3lxTFBWVWIyalpnMXI5TEhSREFqdUlWdXY5OGlsM0s3S3RiMUw1VUQ2SGszejEwRm5vSkpMU0ZoNEl6czlTdC1YR3dicUU3SlZ0eVpSZ0MyUksyYjVvY1ZnQzhjc2gtNHJhRnZYMnZKbldjVjNpclQtY09SYjV6bnYwZ1ZKWXpNR0RGanVORUpjVXVJbTJUX3JZeVBPNmlBbVAyUV9QeHZmQjNkZUFzeU9HWGV6dXdkMUNPaHc?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46027.58333333334</v>
+        <v>46027.78449074074</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Man in stable condition after London shooting, police say - Sky News</t>
+          <t>Bayern Munich Prodigy Lennart Karl's Real Madrid Dream Angers Fans - 조선일보</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:10:42 GMT</t>
+          <t>Tue, 06 Jan 2026 01:52:41 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNaFp3QnppcHo3VkVTUE5tOTkzeVhBT0lSam5DVEsyc09VdFN1eGMyRUZaZ2IyMWZxdFFkUG9pTTlidUhIN2ZRMzAwWEsybXFQeGxlOWs2UFlwSDNUdGdiRXVxWGRxUlJrSkc4VDBmTjlJdmp1eS12U0tHSEpLaXFrLXplM3JneUJWeVdTX1l0UXhMM3pqZWtJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOOEU2bjc1bzlMeUpVV3dKNnpiLXBtX0dSV3ViclNIbVFsaXBKLUJORGJWQl8tajg3SlFOeWd2ZWV3dmI3NU10UVhoRERYSWFDSFBQNzlvT0l5LUZGQmlaRktORlZaUFEwdWRoM1VnNUpVYmZRSENJdjBEb3ZJVzJkbnluNjhQZw?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46027.50743055555</v>
+        <v>46028.07825231482</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Edgware Road triple stabbing left man fighting for his life and other with life-changing injuries - My London</t>
+          <t>Scientist believes that humans are definitely heading for extinction - here's why - MSN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 10:40:31 GMT</t>
+          <t>Tue, 06 Jan 2026 01:07:42 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNekVHX3l4XzdnbnJjUll6VjdKVjhHNEFULXVlNzl3V0ExaXpDTE4zUHVxSDROZmJUT0tuSTB2OGE2dUl1bWJQTWJmOTVwV1NmY3FWV21VNVNSM3BUMHFLZG15RU1RV1lFX2FVeFhZQm1GSzZzQTR1YjhDX2k0ZlI1aGFfUnNWSW9nYXJ2eDFBcklQRV9DTlHSAZsBQVVfeXFMTVMyYUlkSE4wNFJTcXBQNVJvbXdpb0ludkV4NHhURmtmQXBhNmc4N1hieDU4Z1MzTlByaS1ydmFIenJQbW9hUFZsQWhzeGthcnRyaVM2SlBtSWJzWHV2ZkhsZDE5OG1FdlpyVVNlWU9ZY3Nzd1hhUVJRQnI2UEZOc1REdXhRd0Joc2g2akRaOUhHbnBsMFh3X0IxZ00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQTS1zMml0X0N6ZkZCY3FPZnh2Wlk0Vm4tdnNjQjE4Y29kZmFBZHJWQnlLNHFBRjFfOTJSMlk4OVMyTVNZcHVfdmhWMFZ3bGhZVTFTZkhQb0k2QnZtMmluYlRZM2loSzc5OTJnV2JXY1ZHQWg2bEdhSTUzUnNxRmNfbmNzSlMzRlpJWHc5RkJfZW1ydC1ETmM3UXhIcGg1M0Zxc1loeFEwRTRMLVVuenVwbDdKSnJxdERkY2JzY0JNa3hQU1FPallF?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46027.44480324074</v>
+        <v>46028.04701388889</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sunday brunch at Ariette in the Pullman Paris Centre - Bercy - Sortir à Paris</t>
+          <t>Prolific shoplifter jailed following thefts in Christchurch and Poole - Dorset View</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 13:40:26 GMT</t>
+          <t>Mon, 05 Jan 2026 15:43:17 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPMUNGYWxUaEc1eUZtdmJ1RnVBUWZoaEZOZlNkNGRaT184bkdHbkxKNGpzNEctM2RGSlRKZWZ2WnBMLXl6dXpSS2oyNms1VTdBNHE4NTItRWNLZW1rMllEZ0VXMVZlUmpiUFRUMnNyWGxERndPYmZjTkRwdVdNeEJfTVJWOWtON2VuNWNHbkVoMUVRYjFqZDNRWWRFRGlzZ21MSktMNVg1YTJqQkVVOFE4cmFOXzlBcHhOS1V4X1AyZEVaSVlMTktVRTJrZXBEazFaWEZvNlhB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPb0NiVHktNnYzWFZROGNnRVBjY3I0Z3RuVXY2WUxoUXhjdzV3LTBFZ0ZDOFpEZnd6bnFINDRzdXQ3SklYckI4Z1J4QV9xelA3QzJZTWZBOUl1ZjFDR1NRSi1pNlBPM3VOYzM4a3NtUGpWYVQ2djJZSC13NlNQc1QtTTA4bHRLbWJEcFpObU5EMkpQdEg3VGFneEpQRQ?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46027.56974537037</v>
+        <v>46027.65505787037</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ISSF extends one of its Platinum sponsorships - Francs Jeux</t>
+          <t>Franklin Police's "Not in Our Mall" Campaign Nets 76 During Holiday Crackdown on Retail Crime - Hoodline</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 10:43:32 GMT</t>
+          <t>Mon, 05 Jan 2026 20:12:23 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQV1UzUHlSOXFTSGdlNE9TME4yN0VXbTh0WXZ2R0pHM1pkN01JdGdDTUR3bmhZNEdkLXNLYmdBcF9rY1JsU0FybXdqbUlPNGZXdlVjOHQyR3dhZDFqazJmNk5jYUgzSzFScGVxVncxSlNVLTJETy03ajBjZ0FUdmloYnAzYklacXh4aFZHWEFXV0Z2MUpoQ1JXcnM4cEQySnNpVDE1RElTWFBnaEpJTVRUT1V1OUs1Y3lob3FZQ1F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPRnphTmh3OHhxSlJ0VkFETHF0RVJvMlFuMDI1Z2R2U1IxcEI0SUd2OXBUYzJBWC1Lb3FpRGpUdktUWm05bFJPOXZLWS1aOFVZTE41UDRnNzlNcVhGeFc0Yndla3VvbG9nUGw2R29Cdk1nOVA2TmNmc0Y2TnhLclpncGhSSFZ4ZzRMNUIyRHdqQnlWOTRXeW9yM3BsYThPOTNtZUlEbnRkdEVZWldYQzY2VTVWOTBkMlBHLUllWU9B?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46027.44689814815</v>
+        <v>46027.84193287037</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Zelenskyy replaces Ukraine's security chief ahead of Paris talks - Times Union</t>
+          <t>KCSO's Organized Retail Crime Holiday Taskforce results in over 647 arrests, seizure of over 50 pounds of illegal drugs - WBIR</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 14:17:49 GMT</t>
+          <t>Mon, 05 Jan 2026 14:43:00 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNdmk1UDhMNlhFTnRjaTNSNkZ3VHVIeFozRWE3UGhreld1UEFncmdCOHFDSVJBdTVGWXZmQVU2ejNSVkhwS1JCa0YtUWlTUXhadWFLVm1kSjZoclNjODBSTV9UbTJuMW5IaVJTX3h2czBSNURzczdlQUNQWTMyRHVlNjFEUXVBamY0eWhFOGlnUVRkOV9rVFlNUE95SGxCa3k5V3dkeWFvaVdnLUs5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPVmpCUHlfNXQtZFA3X1UycTR6OWFPdmIxbVlxbG55RVlweTNNY3FaSjRSWnk5SENGTXc1NTdYdHNMYW5PTFNFN1RCMHpwaEpheFJzd2U2YjhOMENTQUFnM0NCdG5XYUNhS1Y4MXRCeVptd3VWNVBsOEMtSFM5NkluaGRkLWFvR1oxQ0NqdF9leU9zU3dJdzlQZG5QcUlHXzJxOHFoUkVKYXVsQ1VkV0tOS2tIYXE5N2xtM1dlVFlhN3BKT3c1WTJtQ01XNllxamJfNHplRUhvOExmSVFWd3c?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46027.59570601852</v>
+        <v>46027.61319444444</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Syrian and Israeli officials set to resume US-mediated talks in Paris - Click2Houston</t>
+          <t>Anchorage sees drop in retail theft after coordinated enforcement strategy - Your Alaska Link</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 11:39:20 GMT</t>
+          <t>Mon, 05 Jan 2026 22:08:00 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOZHJKdXRHeDZnR01DV1V2bHpOdVNMUVdOYnpqZmlzWmFtd2JwclQya3Y3LVZoTklaTnJJa2QxcG8wNzBiYkkzQ3F5TUZ1aDBVWU1vZXdCTWJqYy0wV1ItUnlxOFYtbVJhUWxFZXNOaURwcHRUcTdTUFRJZ0tMcVdCbGNkS1pXWEl5TWwyLVN6VEJEaGhDbEgtV19BUldGOVZDQjlXUmdPSVB2b2U2b041bUJWamVqeTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxPM3F3akJ6QVRidzk2czdpXy13ak9lWVI5cEVnSlk1LVZ3NDNBMTNIN0hSSlpxeEpPbHBMNEs5UDZpZ3FOQVlBU1F4WUg1Y2Q3Q2pTMnN5eXRqZFVSNklNOVZyd0xENERWR2xwXzJqMU1TaGFxcWRKUERhTHc5YlhWakZ3VThSemRCd3JmU2RSWEdNTE5pT0REREEzWEpySlVIS3pCNkR5R3EzZnlNZy1zSURfNkhXMndHS2EyNC1NZEJlT216Qk4yNU9iV1E1ZXN1X2s4Y1pOSVlnTC1NMVdYRzJhdUdNZ3Uxck5razNrWjhRZnBmT2FuSkVn?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>46027.48564814815</v>
+        <v>46027.92222222222</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mala Boom: A Burst of Sichuan Flavors Perfect for Wrapping Up Winter in Paris - Sortir à Paris</t>
+          <t>Stolen Wawa Coffee Worth $100K Seized in Chicago Area - DELCO.Today</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 14:00:29 GMT</t>
+          <t>Mon, 05 Jan 2026 17:27:57 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQU3IyazROUndCbkpMM1pvTkdER282QVNiSVFfdl9ieVltREhzWkhtdDN3QmtvaHZWVE8xOUpsa3ZWVC1INXdTc0I1QnhfcTVMTzBxcWlwcnY3dmxuYkxtRmJWU2xJT1lGYlBkZDI3VUtydHNSMFBIZ1lwTlJoczNNYTFzLTh5cWE0NGdYOHliejV4azh2dzg4UWU0TjI2M2gwNlBlLTlwU2N5RUNwendVZzZ0MXBwOUVXY0RGQTBNWVMyNjRKMXlpNVY0UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBJcmdrbWw2bDYwZUNSZW9maHlUN1hIN2hMOGo2dmRLVnd4b2pXU0dIeXdCc0g0R3kwZ1Fodnl2Mlp5WDlwX2lycmRKSzMtT2hlbW1HQU9HNkR5bkpRZG5JQi1fYnV4Q09XZnJ5ODZQblY?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>46027.58366898148</v>
+        <v>46027.72774305556</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Paris court to rule in case involving alleged cyberbullying of Brigitte Macron - WPRI.com</t>
+          <t>Florida Targets Border Gap With New Interdiction Post - Newsmax</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 10:16:37 GMT</t>
+          <t>Mon, 05 Jan 2026 18:57:25 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQbFpMbDVnUHpuUVg1NElpVEJEaG1vcWVBZ1B4aVRSMUVjZy1sNU5vblU4X0VPWDdheHZwcmpMU3FmZjE1ZTVMSXNpcUhaMllBTl9oUEFNbExLR0pmQmt1YUJJNk5nNGFQM1d2YVNkdmRuWWJhTVh0anZoalR2ci15S1hwSGFvZTR3YVBycElWNVdjbklwN3huRmJvUDJ2UDh2b0ZxVFhQRm1DN1F2Rl93NW1ubjhmZEFfUkNUbmJn0gHDAUFVX3lxTE00MmxJamcyd0ZtbF9fUXZTYzJwSVg3RFdXYm5vekRoLVJ4cGYtZmlzb2xueG9VaXRjVVZZN1o0T2J4LWVGTzljaVBPU05NQ3pXM2RjUWMtRm56WGdEc2JTejJBaUd1eGdCdWNnSkxFTTdYNlQ0UVR4Q1NZZkQ3dTlEWFZBZmRkS0J4dlJIaktyTU5KTW1mdWtPT294Tm1ZWW1jZVlUaVRzOEszUjJ6STd3dVpXdmJSTkFLZXhMMVZtNDBZdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQTmdJdExyUVJ4c09oT3RxM1VMODUtUWs0UEJ0Q1ctellkT0s0Vk9ZeWloLUljQUQ0SFYxUU83SW9fNnptSjZzZjlhQnVpQ0FqWHNlQUU2Y3JVWWdfOUVtbTVNV2FmalRJOFVjdnRVYVIycEQ3cUEwaDRUZlZIUXJfUTduM1RkZS1mSGE5NGpTTS1zNV9ieWE5RVlUVQ?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>46027.42820601852</v>
+        <v>46027.78987268519</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Somizi Mhlongo and Thando Thabethe enjoy international vacations in Paris - IOL</t>
+          <t>Fabrizio Romano Transfer News: Chelsea AGREEMENT, Barcelona BOMB, Man Utd to APPOINT Solskjaer? - FootballTransfers.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:03:33 GMT</t>
+          <t>Tue, 06 Jan 2026 07:47:00 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOWUVRTVd6dmpFSmVzRUR1c1g2UW5DaklxaFVOazQxTmoyS2x1UmRBU2ZoVVV0Q3hPWHQ2LXk2c3RXc1EzLU1RbnNhMGlhbWdISjFxR0lxZ01CLVZYb2ZKVEpPREdWMFp1YkJDSzVfajlCbTdrRURBV2IzS1dEZ1R5Tk5Cb3VRc3c1UHUzaXU1S1JYdkJiUFpkOU92bG9Ta3d4VkpkRVVwRmk3TUNBYmdv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxObVZ4MTF0YVdnZFNPdGdwc3NVOVFCSGMtNEZaS1FFOGw3NE5UcE02MC1MQUZvbXpNdG1GM0RRaS1PSFc0cE0wREh3SDB1ZnIyVmRNaHZoQzFVTUxTeDU3YkxXMTlTUk8ybVlMUERueGdmNjVnY000OTEweC1GbDdtQmZhTVpYamhnN1AwRHBxTjBLLTZIZDdaS0pfNGNEemM5d2ZIQ05IZl82dS1UNlpQcVVCZTZlYnhZa0hXN2FxLS1rSGRQRmZmeWVIZmxEWWJQUU9QWGppY1hlTzFSWVVzejhvTkt0VnZMVjVVelhQakFlTXJianJOZ3NhcXJoQldEWXprUVprZWxEb09l?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>46027.50246527778</v>
+        <v>46028.32430555556</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mission: Impossible - The Final Reckoning available on VOD in September - Sortir à Paris</t>
+          <t>Trial begins in fatal stabbing on city bus - abqjournal</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:26:54 GMT</t>
+          <t>Tue, 06 Jan 2026 01:42:00 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNLVhRZHd1d3p1bE1VaENMcFI4Z3VQSTNyY0F0MXRQT2dqRlhGbDlWLUJ0UERJa3FpcEhhSzJ4OGZiX0QwMmh6QjUxTERsM0lzR0ZZVmtXbG9LeEQxWjR5NHBHXzVzT3RUejRvaGE3RmxjdVNubHhMQTRERVhRamtuZ1c4MU1Pc211Znl0VTNvanpaUDJVdGc0VEVvd0d1bjRrN3BmZnhIMDFvNF9XMUc0TkNGdzh5VDFpRUtfR3hCQjNZczZuR3Z5Tk5tclVHWGREa090Zk9ySDFFU1JzNnJF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNajVvRkxCZjdxblcyMjFqa2QzN1daN293dThSRHJleGllWFhnaWRicW1GTXhHNmhIeF9fNlBsVERhd2tTT2I3dG0tM1VvQmpLUXlWdEwzUnc4U0ptZkN3LTZkUjBqUkxoaDlMb21xQ2RRWjRiWjcwUHZWNVRoU3UwRE4wMWtmQXROaWc?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>46027.51868055556</v>
+        <v>46028.07083333333</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Horror as 'passenger attacked by man carrying knife' on train as urgent manhunt launched - Daily Express</t>
+          <t>Manchester United sack Ruben Amorim hours after explosive press conference - London Evening Standard</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 08:59:00 GMT</t>
+          <t>Mon, 05 Jan 2026 18:32:13 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPSWlPYnctdXlXQTJzRW1ZT3pWcmZGVmRhVjRGaDNnTnIwQ0dwaUQwaktjdGpRVlhXNGdkQUk0REZwRzZIeVRKaml4ek5jWDJBbTNlNnI3cVlVQl81cTJXbkVLOVF1NC1nUVlFWEZBaXRMRmdPVWFFS2txaVJvbTZhX1NuRlFweWZXbmJHUUh30gGTAUFVX3lxTE9sUHdDTElLd3lkTVdPcVFZNjFxUzY3dXFzU1NvaXJWdldodGFfbU4wOTJKVGIwVWhZQUN6ZS1feU9tZnNZNWZXcDYxSXZybzFlMzJvS1lSclprblBDVjNINVdCOW4wc05TYlgzZXR2N2xZaWtKTTBzaExfYXRONGRlU05ZSkdxdTRSWHRIaVVnTm5NQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNU3VBTkxLcjJPM1V5T19uRk5NVk5iN2w0X3YzQ0M5QkJwZ1BXMmd5NmRPYzVDd1JkZXc3UVdzTUxTMFZNNGZjcUhmaF9rOXdmbjBYd0Yzd2tpZXBaOEtXZlIyU1FpamM5MkJwVEVibzVUVWw0N1Z0M3l0QVV5cEhCeg?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>46027.37430555555</v>
+        <v>46027.77237268518</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PSG edge Paris FC in historic French derby - News Arena India</t>
+          <t>Atletico Madrid vs. Real Madrid: How to watch, date, time, live stream, TV channel for Super Cup clash - Sports Mole</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 11:03:13 GMT</t>
+          <t>Mon, 05 Jan 2026 17:31:00 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOLUZKdVNwOWgtUXplY05QdllFTmRkV2VyYWZ5MHFHdTU4NVFlWk54dkpYWXRDQTdzN3l3dENXUGRSZEt4cU9hTi1Ob3hwY1UxVndmR2U5NWJ2QURUQV9Vc0wwWE5zZnQ2dkdKX3Y5QTg2VldsN2w5a05JMmVFVWJwR0FxTkllaVpy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOZDV2TGZ0Znk4Q0RSQ3JIVUJ2MWlreFNrb3g4OWZkUVIyQWc4amdKNV9CZ0R2SXhxS2NoZVJXNE15XzE1VWl6bElRRjB3OW1qRExfNkc0b2hOX3JtQ3RwNzdSU3VNRFJmTkRWdlkteFc0emhoTDJ3NlJDOVBrY1o2S3UzWTYzRTItRlhCQ1JJU2RQZjdtLTRRZGZpZEpNMUtMcjJGZmQ5MHJfM0s1YlkzV1hnQ1B4WXpJYlVCQnJXVTV3YnZMQ0lUV2dBd2pIaFRYZlRFLUFPWjhseDQ?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>46027.46056712963</v>
+        <v>46027.72986111111</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>The Paris Swindler: Lies and Gastronomy – A Canal+ Investigation into an Elaborate Scam - Sortir à Paris</t>
+          <t>La Liga: Why Atletico Madrid players were forced to train barefoot - MSN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:05:02 GMT</t>
+          <t>Mon, 05 Jan 2026 23:59:51 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQaG4zaWRNTHhSdUFEd1RlR01qRk5YaUltZHdnaFVobmRJZXBKbkYxcnhjNVBUcHBGdHA4YmtIVE1vb00xaEFxclBKczJoSG9QS1ljaEJVcTVtQkE5T2xCbUtJcm9ra09ua2lOUjh0REp6NkNURUcyMlVPNEdoY0tfOUZjUkdDb0V2NkJwZUxJVjRhVTkyaDVFWVUyb3FhQkdXTkhPMUpnMFlqQmowMGZNbFRZcjNnTEJ5RHp0WF9LZ25MaXc4cVFlNWlBVjA5bzVpaUJMYVgydE9zUGZsTExZb3doR3hPNFlnbjl3RmR5Zk8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwNBVV95cUxOR0ZRT2lfSTVRSU9JVENXc1NVcXc2Uk1Id3I2TTRwalRJRlo4SDgtVmh4OXpROXJYb2U2NXBzM05rb1FkTzB3bk1QSEZMdnJzTG5aS05BTTUtLWJxdWZEMExJeTNHLTR2dnpWaXRfalNLOUxsRkhTRnM5YllJaVhLSEMxTG82YlNsZTRnRWdxNXNDVk12N091a2oxVDRDc2tiaG9oblRDT0xUUk9CRHRqbmVSdlQxN0NQdHJDdTI3eWlpZjRqcGRQcjlLZG8wemktWG5HN1pIaWhEVFkzdGQ3TXpZc2Nza1dPYnpoLUZPbEFGdGV4WkV1UE5hTkQxaVdnNWl6MUNpWi03bWFjT3FWNFVpTlRza1FaZllRQVJKdnJSS1VlSUUxQjZmbFB5Wnc4UFJrcnQ3d1o4dnFGUWdUNWluZmcxMUJ5enNCcm5zbzljZDNYYkF0RGNFWGlqVXdsTjJrX1l3blV1Nm1qVXo2N1dkTFRfSHJ4Mm44d1Y1Tl9VeDBaYWt4aDdWY1ZJdm8?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>46027.50349537037</v>
+        <v>46027.99989583333</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ONGC well fire: Loud explosion, massive blaze at ONGC in Andhra Pradesh's Konaseema—Here's what caused it - livemint.com</t>
+          <t>From Amorim to Conte: Managers that have talked their way out of a job - TribalFootball</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 11:11:28 GMT</t>
+          <t>Mon, 05 Jan 2026 19:14:42 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQZjQ4N3pLZlRBcUt2U1hHUlNKbGZaNGhBeUVWWnQxNmszOE9FV19WMm5wMldZMU16TFNFejd2NmotYk5VYTZWUVd5TElKd29DR1piV2ZBTGVuZnpCNy1RYnVvUV9xS3dwSElrSlIyRm9OczVYcnNfLTdRUk9pZFNtdW1lNTFTd21IcGptMlotMDBBb3A3by1qdkR5ZWJHYUFuY1JTYXBRR0JpWUx5Zjl1VFVUaUxyWUJsQjFoLUZ0MzVXaEZMYVpybU11elpPT3fSAdQBQVVfeXFMT3dIUFhMa0EzeEVuYy1TZ0Zpb3pfMHE4d2UyNXBQU3ljcDl2R01mME9mODVXVFBOVXJrY1YzbFpybVY1WFRmYnlVYmVXWGV1RV9hWFBOVDRpQndEMHRLb1lweVhqOUJ0eWtVYTFjaUE0TG1UbzROMWFKblF6RVd0WUE3SWFDWjZHNllLWW41aFVxX0RkZEJRN181dFJqVEtjWk5fb01sYnR0TjZJQlhJeE42RmRUSUpoWlpHSFFHcnpJTFpNbUI2eHdkbk9fUzZiNjFVbWo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNaHBLMWxNeDZSb1prUGJLUnpJbldhbk53empzTzM3MGwxX0QwZlVCSE9KdWxPRVIzdXpfdzV5VktXeUJoMURaSnZuSzE5eHY4M2JXM05INDNlcEpoam9Lalp3WVZNb2JDN05na2RYUUdObi1pemVTOWZiUnhMeERQSm9pNThHWDdEWVJGQTU1b2tDVlNEeUlubkYwVVlCYXF0S1hhN09tNF9HeXdNWVpud1Awb2RFR2Vtd29RWlJGUEx1U2lBVkUzZTF5bDlsY29NdmRwRl8wSF9TM2dYTk9PRU1EeVpUTVVubllaekdYd0k?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>46027.4662962963</v>
+        <v>46027.801875</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>From the universe of John Wick: Ballerina, an action-packed thriller premieres on Canal+ - Sortir à Paris</t>
+          <t>Marcus Rashford's Man Utd olive branch after Ruben Amorim axe and Barcelona 'uncertainty' - Daily Express</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:26:54 GMT</t>
+          <t>Mon, 05 Jan 2026 15:19:00 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPUjJjQWVkb1VfRERPVHVBS2t0Nzh2SmV2Vk5rUm02Y2I5Y1JQbFNvd1VSU1VBN09TSk5IUko2eGdLSUlYYWl5aVNQbkNsYmcyNkgyQ2FlaDZweDgySzRLUVpzUWpVODhNT1Z2dVJoc0JxYTlGX1BoQXdqYTNYUUdjbUFqNEJ5cm5wbXdwZkVBamVIUFpfRUl1WXptWlY5TFhhdndPbGFzXzVZQko5TUlZbVJQWV84Uk1qT1NBZk1zakRhb3IwODVXWXNTQXhNWEVCY0w2XzNGMDZnOGlwUi1YX1JoRnR6UWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNLVhIV2F4U04tUmpHNWdhT2xEZkdCcVQ0MjVoT2RqdEhYU0JZYmZTQmJhYlNVb19iRndOMmNxOHdLU3FLZlk4NjdCLUNYOTNKMG52TkhPV2huNDc1VWxfdkl3bTN6bHF5dmx5WElJV0J4NkdaZklpMk93Y1VGdXZJRF9fZTFVR3R6Vk8yUTY1cVMzLVQ1eF9rTVFSSdIBoAFBVV95cUxQMGdXMHdGS1ZlMmFlSDFiNThPazNLOUdmcl9OM1N5akJtUlBrazJvcHpseFRCY3RlVktnV1RwMzdIV0dkWHpfbGVmUG9CSWVCUEJtMWpNdVgyRjBETHFPblFWNFJvd2F1QnctQnh3bGduQzk0NE53b3VUbHFiNWFVbVJIQ285NUlxelkxUmhmYlhGSTU5VC13dGE1YjZIN0oy?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>46027.51868055556</v>
+        <v>46027.63819444444</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>It Was Twice, a Time-Travel Thriller, Airs on France 2 - Sortir à Paris</t>
+          <t>Road Rage Shooting Case Ends in Plea Deal - LoudounNow.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:15:02 GMT</t>
+          <t>Mon, 05 Jan 2026 19:20:00 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQS0E0VXZwZk92MXA3dkNxYm1aY0d5SU1HN2U1U3N3czVnM0xfcm54azVUamJKX1RXYk0yOUdfd0Q4SHFYZEtES1VJaWtqY2NWZGFEbGROQ0w2ajZMUURVUDl6am1teGhtdXhfcDZQdVlmdGZ3V0xmZlRmWlNMMGJOeEFrSmpfRDZfYlJhT3IzeVk5Q2FYUzdQNXlSc3pGZXFLNDc2Y2xHa2RXalM5MTlTNkVDMkJ3SU5zb2V1ZlJxUUVFWE4x?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPOVFZbXdUNlctdjlkRTRVaWZuMG1OdzNkaGstS1hGOEJyOHZkc1Vra2d3enpZR2hNM2hxZGlnZjlETC15SVFpVEgxV2FjLW9wR1U0S0Yzc3ZYamRCM01oWGFUUGxRby1hQ1J6YzdoZHJSQWNZcHB2UEhUaXhHMTJxbW9YdVJpQUVyaUNGbTF4S0RRUlQ5SkVZa0hZb1RxMXpvM0tkbTBRRUV1akVBVTFWRnNoUEo3MEZPODZtVkV0Ync?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>46027.51043981482</v>
+        <v>46027.80555555555</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy flies home bodies after deadly New Year's Eve fire and explosion in Swiss resort - Reuters Connect</t>
+          <t>Next Man Utd manager odds: Clear frontrunner in race to succeed Amorim - London Evening Standard</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 13:31:00 GMT</t>
+          <t>Mon, 05 Jan 2026 18:48:39 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOVDdzeEJtclVoc29BTWpHa1JaRjBOdG1penNMM25YTUxwaDJQOGV4Xzc3c2Q5OEhfUm9USmJXMHZ2eDM4Tngwb3pnSWZCdmhXdEtYNjFyWFM0R2trcVpvSXhYaE5hVnpLcjhuQnVTUE5EVzlHVUEyNlFZNURlemRjWHJUelQtME9KNGVxRTRwOW1zOUdiUkhZWUNKR2VhcVNFMVVFZnR1bzVvRFJaMFV5TFBNQjdIa0ZrNk52RmFEVmtDbFBaaTlYa01rOFFzeTZBWndMcFEwR3N3Rm9tUHY4LUk5V3VTR19PWHZqdmRMaXd2MG5yc0RybU5QSzVQaVI5cmdJbjJacw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPS3pGTXo3djgzaEtKaHFPMG90eGw5Tzg0OHMzcVJjbXNXdlc5YndncTM3bFFQUDRKQmp4TnIxcElpd19KeUVFU1pzZ1YzUVhxcUZESEd2ajRBYlFLQjFMWDNVcE5yUGQ2aE44WjB2THNScTEta0Zad2otZkVOenZmNmJFT2l0ZDQxU1BUR1ZYUWZNWXZZRkdmc3VkZ2R0dFZWaGo0aEs5aDV3Zw?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>46027.56319444445</v>
+        <v>46027.78378472223</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Francesco Ferrari, the "predestined": from the A2 record to Virtus Bologna - Backdoorpodcast.com</t>
+          <t>Security Concerns Force Real Madrid vs Maccabi Tel Aviv Match Behind Closed Doors - Devdiscourse</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 09:45:46 GMT</t>
+          <t>Mon, 05 Jan 2026 15:52:51 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOZWw5aXMwbFA0ZV9TODZldFd4WTBhTkZTNk5ObFFzOUlsVzZPR2dJNk5PLU5WQUxhY1FHdllITGlxQjNPSExKVDFuSnYyUFVoZnl5c041Y05FUFVaclFxSTFvUVlpOGQzNEFvXzYtSlFNVEtmd2d1akgwMmh0M0NOeHJSRFJJdzl6NHNYazhVYlk5VzAwQ185SUo5aHdJWVhZdkpJM2hZNjA0UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNanNERjNiY3d5TUVpWmJ4dEM2N244OFQzQ1JZQi01VmVpTjZGVTZvSWN4UHptWHJPcVEyX1RkaFpsSlVjS0ZmUnFFM245SGJQNUZjcWJQRW5PbUsxd1N1YVdzeFdoVTFjYkF4RW5fY3RQdW9sNWUycmk2Z2FGeHBJSFU2cmQ2Zlo3Z2JiZXFraVp4eWY3YUt3V2IwNzE1OTNUaTFkMnlmMUpma1pzSExvY0l5c2c4RjZzTGNBNENuZmNDS2tUM01ZZXJEampmSU9XYWdMSWFHdXpodknSAdsBQVVfeXFMTWpzREYzYmN3eU1FaVpieHRDNjduODhUM0NSWUItNVZlaU42RlU2b0ljeFB6bVhyT3FRMl9UZGhabEpVY0tGZlJxRTNuOUhiUDVGY3FiUEVuT21LMXdTdWFXc3hXaFUxY2JBeEVuX2N0UHVvbDVlMnJpNmdhRnhwSUhVNnJkNmZaN2diYmVxa2laeHlmN2FLd1diMDcxNTkzVGkxZDJ5ZjFKZmtac0hMb2NJeXNnOEY2c0xjQTRDbmZjQ0trVDNNWWVyRGpqZklPV2FnTElhR3V6aHZJ?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>46027.40678240741</v>
+        <v>46027.66170138889</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Panathinaikos owner teases blockbuster transfer - TalkBasket.net</t>
+          <t>Deadly Sikeston shooting leaves neighbors concerned about safety - WSIL-TV</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 09:20:25 GMT</t>
+          <t>Mon, 05 Jan 2026 23:50:00 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPV3Z4VEZsNVZRNU5SQXZ6UGR3djRpcnFCTGkzdmxWZzNTRzZSeVRpckhnQzZoRkdkc1hMRWhpWklWRVNmOHIyUUlIYlJRWkZoVTRuRXItakNRc0prUHU1bjg3WmdZQldWczlVM1FyeWxFVjBJcU1mSlBFZ2lfUW9RdEczSDg2d2Rt0gGQAUFVX3lxTE1mdVdaX1JxcFJmX3hRMVBoSEU0em54bTlpQWYwVEhfb2NWRUwyazlhLXRCT1ZxZmZoaWRlWkFGYWJQRFQ0aHRDaEN6XzZ6Sk5pekE5STkwUVV0YTd3SFlPZEJvYTR6UUJHVmJVRTZBdVFQSV9ZSEFXb1NZaURmTnVqeG5FXzUzcm9lQlVPOWRfWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOU0tsS0w4OHJ1Mi1seV9RSGREaWRjZHUtVU1nWE9rY09xTEpVOHNKeklLYkc3T2IxREZNUTVBTnVNTjQ0LVNfWElVMnp4eWVLUDdTd2ZZcEhDb0VzXzhyOWJvNldxWXFZXzJZdlctVXFxUDVFYU83MzZobHBmTDd3MTdqNHZlMGV1Y3ZLU1hhV1kyUHNBSXZnS0djczAzYzR2bWxGLXIwV0JoMkRYdWRvUnV1YXlpcWgwNXV0UTN6cFJLZlZNWWtIOEN2TUVtbTFyUWFwM3Q2WlEtSzhCOEp6YjJabTFxNVNnMHc?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>46027.38917824074</v>
+        <v>46027.99305555555</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fenerbahce signs Nando De Colo to boost EuroLeague title push - TalkBasket.net</t>
+          <t>Bernalillo Co. DA’s Office – Jury Trials For the Week of Jan 5, 2026 - ABQ RAW</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 09:03:08 GMT</t>
+          <t>Mon, 05 Jan 2026 20:03:53 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPanN3TzJrWEpucFZvVGV5UnRVMS13V3R3RGJsT2hnWWlPb1o4aEx5YUttT0owalpLZ280b0xfTnZTSGFwLVVGcXdPeXR6UXhKSG9rZjl4U0x6RmZqUzdJZG5xbHVneUZqU3BPZEpDbWVEa0ExT29OYWJlRzJrMXRzRGFJczNYQ25BUHRwQlVOby1OcHpkQ210YlEwa9IBowFBVV95cUxOQTRod3dIQ3QyX1R5a3NBdnVGSG1WOFVBeEJFT1hCMEROSmdMbjlTYzI3SnhaRmFaWmZXY0g5RTRYb0stdi1TLUlGRnFsT29pYjlMRkJNYXhDLTVsNVA2M3JOcndJWVhoN0VFdnFTMi1RaUZfU3IzY1NJbU41ZkVZZ3Q0eG8zNnVxSnltMWR6azhCWTFfZDF5enRiR1dSeGFZNkFN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOR3d6ejA4cURHbmxTWTQwS0tnMTFFSlVSVHFKV1ZIclhYVW45R24zd2c1bGZRRVlYWkVESzN3OURldmJQVlhoazEyRmJ4OEVBOGdBWVF1VFN1RWFVLWRaVkFCdEpwVGV4MFN1RGlFM2pzSl9QV2h1Q0dhcmFZQzF5aUJHalNYem9jRzg5cDZ3Q1NZQQ?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>46027.37717592593</v>
+        <v>46027.83603009259</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Outbursts, honesty, tactical rigidity and poor results will be Ruben Amorim’s epitaph - The Straits Times</t>
+          <t>Bombshell! €160M for Vinícius Júnior (25): the offer that brings his exit from Real Madrid closer - madrid-barcelona.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 13:35:00 GMT</t>
+          <t>Mon, 05 Jan 2026 16:00:00 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNZ2lnRnE0ZmJrc19Ra1g1N2RqekJfeUdZZXQtSmp4a3BDdlJzSXZvZTdtQ0ZVU3lQUURWQ3I1NS1sekVwWXNSeUUwNG1vWEFlazVIWVlWcDBScXV0SzRrTTRXcnJCNW52M3A2a2o2WktsX05QaWFfVXpYdzRsU0NmRnl3T0xaNzdoM0RMdGtmV0g0T3FhaG1tbkJkMGp3SmNnVnVnVExjYTJMWE9ic2FOUFBETjR0emhfdWlOaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNYXhKRldjWU04aE4zdE9yZEF0WEc1alUteHdnYVUybUF3Vy1aQWw1R3V2SkJZWldFTzJHejN1U3lwOXY2azduOUtrdFk3NVhaVzBESDA5X19aaHZUUDZlN2RRY0hjMjkyY1NLejdqdXRJN1o1Q2ZUTVNjMmQxMUd3VzFWc29henBsaVFZYlJlYjE4d1RyTUM4aXlIM1diaDQyMV9xaWVmbEpuaWdfR0MzNEV1MnNNTHJXcC1DdHBfaVN5MllJSHRrNUtPcU40aXdUN1VvZXFn?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>46027.56597222222</v>
+        <v>46027.66666666666</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>How New Year works in Europe now: Fires, riots, immigrants - Brussels Signal</t>
+          <t>Yamal and Lewandowski: The Barça veteran admits he learns from Barcelona's young star - Pasión Fútbol</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 13:57:14 GMT</t>
+          <t>Mon, 05 Jan 2026 18:59:22 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQTVFYRC12em9jZldjS2R4S3BUb3lhaG9nZkVuNHBTUUYwZTJJZThBRWZNbTBJOVpIYUVaVzdLY1ZERC1yZ2UycGxQbWx5NFdDbWpBRmNCbnlta3ZZTTNHZjdYVkRPcjIzeUVLLWVIcnh6Rm5ZTDFoWTlIM2t1ZU5VMUZhdm1oSVBXWmNPQVhrbnlERzZq?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQN1QwSWxLLXpnYnJNbGtCdUw1YWp5QUw4Y0QzT0g1WS1CMnByXzBndWllQjd6amxWNkJ2VVVTeVpyWU9WdEE1UWF0NThnalo0ZFZ6TkUwMDJnV0RzTndnOVZIRGFneWNsdGpkTkI2dkE4RUh2UnpSdkFKdVRsdlBYMXlkYVNwVFBBMTdIcU94NlAtdmgzc2FuNVVLcDFBV2toUEhRZ2dlN3JlcUxSZkhMSDlwOTNDNmxLUU12Q3QtVnRrbXhoMmlYLUtfZ0p3dVBTTkVkdi130gHWAUFVX3lxTFA3VDBJbEstemdick1sa0J1TDVhanlBTDhjRDNPSDVZLUIycHJfMGd1aWVCN3pqbFY2QnZVVVN5WnJZT1Z0QTVRYXQ1OGdqWjRkVnpORTAwMmdXRHNOd2c5VkhEYWd5Y2x0amROQjZ2QThFSHZSelJ2QUp1VGx2UFgxeWRhU3BUUEExN0hxT3g2UC12aDNzYW41VUtwMUFXa2hQSFFnZ2U3cmVxTFJmSExIOXA5M0M2bEtRTXZDdC1WdGtteGgyaVgtS19nSnd1UFNORWR2LXc?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>46027.58141203703</v>
+        <v>46027.79122685185</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Gorman urges farmers to attend Mercosur protest - Agriland</t>
+          <t>ASVEL vs Real Madrid Live Stream &amp; Predictions – ASVEL to Cause Problems in the EuroLeague - freetips.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 13:15:00 GMT</t>
+          <t>Mon, 05 Jan 2026 23:45:17 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPeGdWUFRGZEM0ZHIxaW9ORllHQmFzMUpVYUh6c2Q1YWRYcWl6bnMzbVhaa0VvMEJScXNMMTBpY01rakZURmcwT1JiNldMSTF1WkFXTTMtUDlTVlV0ZkRhbGh4WjZlM01mSEx1ek1RRVBzS2ZGV2szdlRxUFJhcEZzR2l6UzY1QWdvZkpWRnVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPQy1ramZBWjEzN1NFM1ZLVHZTb01HZld1ajhxcDBjS2w0NFpWWjVRZUk1Vkc3S0FScWVZLVNkQjFhbVB3ZVNkX2lBbkNSSnpOTi1MYko4dFhkaXZLM0JlaDQyREV4WXlMcHFCMFVndF9rWnlvUUZBMS1TVm5FRlJaczRxQkhLeGJlVDlF?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>46027.55208333334</v>
+        <v>46027.98978009259</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IFA calls for ‘united front’ on opposing Mercosur at Saturday's protest 05 January 2026 Free - Irish Farmers Journal</t>
+          <t>Boy, 17, charged with murder after New Year's Eve fatal stabbing - BBC</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:48:37 GMT</t>
+          <t>Mon, 05 Jan 2026 15:15:50 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNQXJ2VzV3azdfTWk4aDJPX2F1aTR4VzZEVmllVGJDLU14R1J3eGlXV1A5RlBuQUJLMFBWM3NlTlZzc0VPd1VldnFMdVdlVEs2VUdOU08tbHVkMEVNWDdHY285TXVncUJTdE83WHY4OU90azBSbVppMktRSWJweFFscTFPcWRMVkI1S0NobGk2TXdxdHp4UWhsMDl6MVVzQmc0YV9MTmpGckRnSjRqWGxKYTRwX1FfTDNTN0tZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1WQTNkWHF6U1dyY0oyTzJ5cTktRmVTLWhEdGpnalVNNUpuLTVlZnJ3eUhfUjlRc0dyWnNjVU14bHBybm93dXRFM1N6M0ZTUjg1YmNIV0d5Q2xGbW9i0gFiQVVfeXFMTzFiOGhHdmlMem9SaG5UWTd1MUxxWjJmdHYwRXZKVklNaHhrcDRJQWlBWG5tSzZURkJkYnVCbGV4WUgwZC1pX2RzU3FaVm9BYnBZRjRTbDh2TXU0M01NN01EQ3c?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>46027.53376157407</v>
+        <v>46027.63599537037</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Full details for Longford people attending the Mercosur protest on Saturday - Ireland Live</t>
+          <t>Bexleyheath: Arrests after man found with gunshot wound - BBC</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 08:40:30 GMT</t>
+          <t>Mon, 05 Jan 2026 14:57:10 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNNWp6X29WbzliY2VzMURsT0xSVUk3VmlpcUxqWUtPRUZVdGxTY1dLbmVGcTBOYWpPcjdra0MwclRJRW1vaDVFVjJIQTNTWFI3dk8xWmRjREpOc2V1dFlLMzlIY2ZCazBKUUJiV0NCbGk2dXQ2T20tcVlGT2x2MmVVUjRXVVVjUzFJcUgxSV9pYVZmYV9ZU0R4RllWNC1FMVQ1dHNkdl9rS1dqLWlXMGJqSkhQSld1Y3F4dUNCeGY1dFJyLWdmVk1nTFIzdHN6UUxH?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE53UlNPMThqaHROWURoWE5HMmZ2c181dmxIM01QanlFei1pT0FSRHRFS3hKcTdaNEx5em5tbW8xTDk0VlQ2Q2Ftc0dFXy1pVE1PSGNpMUpVMWtoMVUx0gFiQVVfeXFMT0Z2NFNseXBBSy1XM1lnQzBvbHI2QXBXQUJLdEdDREtzdmp3ZUxtWVpVR2FZRjVpTDI1bmFMZV9Yb2ZFbl9nQ18yMXBvX1YtU2kyTjNkSnYwaGwtSk91QnVoM3c?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>46027.36145833333</v>
+        <v>46027.62303240741</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fix this mess you created; leave London and Brussels out of it - The EastAfrican</t>
+          <t>Second man arrested following shooting on south London street - London Evening Standard</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 10:00:00 GMT</t>
+          <t>Mon, 05 Jan 2026 22:32:13 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNUFY4Y21WRWVzRlVLWWYzLVkzV1RlQ21XbXBHTVZvYW8zVDFaNDVMaTdDMUVjYURUMng1cGZmNU10VTFhSnNKSUlOa0R4S3JIbnI4UTRQQk9JMUhYNlpHR2wzal9rczUwM01vOFJONjlDN1JaUkNTSGtQRDlfR1Y3c1hhNm5pVjBYRGY1aExnRkI1bUF4NERYNW1JeUZHc0RVUGZWZThzaVk5WHFkbUNrS3M2QWV2YnhVYWFEWVI1MVR4YTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNNjZZUXJkOFQ0Xy1mVFRROE1SOFlTemltWjF0SXhLTEM2OEtMQWwyT3QxZnNqVmJabnJ5cExKajhVQ20tcGMzdlFLd0FYbEZEakNmUEV2S25zbmZxdkZmbFZVWHNBZ05WWk80WjJERFMyaUk5RDZaQVRleUNYcnB2czBjU1R0V2ZELXZGcEJETU9TYjhjSFhUYQ?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>46027.41666666666</v>
+        <v>46027.93903935186</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France says it will not support EU agriculture policy reform - Brussels Signal</t>
+          <t>Man in stable condition after London shooting - Inbox.lv</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:06:51 GMT</t>
+          <t>Mon, 05 Jan 2026 17:12:20 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNS1lMVnBTWWlBeWNHUS1VVVZIdkVLVFJtV2pIOTZENG9OV3lKTGQ2N2FCSE5CeTc0dUZRN2lncjJhUEt0MlRMU2RUR2l1UUQ0VTRkX2ZsTGNlTG9fX2NLNEFDdlliNV84UHlTUklkbnBYS0VURjVKTWNLYTVSajNJWHRKRV94VzlfajlRMWVlZlg0QnZfMjA4bG40SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQcXRtSExkYWx0aEhPOTZsdV9zM3hYcFdtcTRUVE1yNHFBck82X3NHeVRnLWI4Z09nTFJxa0pvNE92WTh0NVRIanVlcTZSSnhrV0JxdTNaeWxfTGt2M1NOQXNjU0lJVW5lTHRaZFVkejN6TGRLVWdUcWpCSE13YldJTGo5QVdMcmNrNG9CS0ZUSG8?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>1</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>46027.50475694444</v>
+        <v>46027.71689814814</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2025 beef exports from Brazil to exceed 3m tonnes for first time - Agriland</t>
+          <t>19-year-old man arrested for alleged role in deadly shooting on Indianapolis' near northeast side - WTHR</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 10:27:03 GMT</t>
+          <t>Mon, 05 Jan 2026 14:35:00 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNVlVnYk02M3N4U2gtS0N2Sl9zLWVBd0oyU3NLckU5RkxaWGxWUG1PSEx4VG5CMU1mYlBmUTRjOGFjY2FRWTZUUklpZENucXB2UUU2LWhuX041bUp0SzdrMjRHd2FtR3J3Y3FzSVJWckctcGtiUWJrZDRxeEZLdWVvYmRsdzRqSDJFOFJJVWJIX0pUNVhiTmlid29JX0M2czc2dTVpdA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwJBVV95cUxOcHJDdUFDZXFoY0E0R3pDRy02QkpNbUpBenIzODhseDRDVVFpSXY1R1JINkRFUExxYnhzOVRnbWJ6TjEyME15cmNWVVRadmhVVkZfVUwxY1lKbjhSbFdlUGNIOEpaM1dYaXE0MjZuaUNheS1wdmoxOUtYcldGaWtTMFFKVzlqWHNhUzJPZWp1dFJDLUZqVlNpckhxLUhueWh4ZHRWQUhtRVZQbnlhTU9OdG02RDlyelVfUDIzckNzT08xTWpqMzg5ckdidXQ5VmZFWldVUmNzRS1HOTNhMVlLZ1dKU2tWX2ZyaWtPSE1nWWxTbXM1ZnRrUmQ1WEhHTTRsbWdpRDBkWUlCdmt2cWFXdDRBZzQtb2FJeVJZSG5tTVhyb29CTXVyTmdsdUxsU293THRhdVNHc2RHb3pEOVBz?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>46027.43545138889</v>
+        <v>46027.60763888889</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Trump says Iran will ‘get hit very hard’ if protesters killed - Brussels Signal</t>
+          <t>How the Duffer Brothers Scored Two Prince Songs for the Stranger Things Finale - Netflix</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 08:54:00 GMT</t>
+          <t>Tue, 06 Jan 2026 05:45:28 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPTnVEV0dzWVk2X2lvdUs5SVMtVTQ2ZlR2QkUzcUhwT29MdFNVZ0RkZUZYQlVYZno0NnE4d09ZWVJkemlJaUstcFd1TXN2SEZzMlBWSHlBeERFd3JjNDJ0REg5RjFodW9yUG5wNFY4RWxUdmpLTkVjT1dOVnAzSVJuVS1sdTJlZ0FyYjBwUkRSdnc3bERlcGhyNXpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPQWVCSHpXWjJ3WUJUNDNnZHZZaHVRT015TzRXMEtmQXowNFlWVFNuMUgydzV0bF90SjR5czlZbEJUWENCUzBmSmRFZnh4R1ozWFEzc0FtX0hVaHJNdmhrZ21kOW9fVWFiVXk1cnBWc0tBWnE5V045U2hvT3dwUDNoMHAwVFQyY0g0N0c2Mm8wOE50S04wYnc?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>1</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>46027.37083333333</v>
+        <v>46028.23990740741</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Switzerland identifies victims of Crans-Montana ski fire, with half of them children - Brussels Signal</t>
+          <t>“I feel like I only just started making beats”: Hit-Boy is free and pushing himself to the limit - MusicTech</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 13:58:46 GMT</t>
+          <t>Tue, 06 Jan 2026 08:03:18 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPWG9wQktJYVJNcU8ya3RMNTYtaFpVWDVYbm9HSTlYSk5DaHBCUExIcjR0eUxaaUJiS1RWS1hYQjVxVm80dUZWM25tMVpCc2FpU1NzanhfclVoZ1plN3kyVHdpQUNPMDAxOG5BRTYwSUprdDNWTzNma1dRdXVFN1hSWWhwWG5GdnB3cUE2dWtqR2lTM2k0NlEyZlZVS2JTRVdsSm83WlhiZWFhaV9BaUdBS3UySEtHUTlHZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9FWHA3MGhVWkdFU2VwVGZfOVI3LUc5S1E1eWJyZGg3VkQ0MEhPNXk0MGQwcnJxVkdQdDQzcU1hMjRSd1A0NmRiOGpBR01ReTNvVll6bWVpUDNNVXZBXzVj?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>1</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>46027.58247685185</v>
+        <v>46028.335625</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>EU, for Crans-Montana assistance to Switzerland from 21 European countries - European Newsroom</t>
+          <t>Emily in Paris Season 6 Confirmed, Will Lily Collins Head to Greece, Rome or Remain in Paris? Creator Comments - Pinkvilla</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 14:00:38 GMT</t>
+          <t>Tue, 06 Jan 2026 05:15:26 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQcnZRcjBEOXJFVlN1OVdUM0d5WDVWajFkNWNzeDBKcnRPejBQaHE0azZ4SGVsSkNHZE41dG4xRDNBN2hlQ3N2aW1ibFdmT2ZxSDREczYxcnhvU0J1eVdGUUZlYndHVW1aUkNlMDlOelQ4bEtOUDNPQW1DNlY2RVo5b3Y0bGp1SXdyampRNE5HZHpkLVM0YkNLOTQzQW90Z01VOUNvWW5R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxOWE84YkhuNmFFelJadTFaRTBPY3Q3TTVPZ0w2OE9lTDlFZ1d6MF9tMEp5UTF6RWxrbGFrT1dVMFdwMEFrcjhjczZKbTJTdkZudWdQdWdvM3huck41bXdJbGIzTkgwWHFZdTlOVktsQ2xQRkhyQkE0OEFaNmxvOFB2NEJkeTFRcUtmSDlfYzMwcWhJR2ZmZXJ0eFNDUkFzUlhRbm4wNVFWRVFBdTlwdExVaWgyXzRaSl83b3Z2U1Vjc09fdmxsYldJQzdBczlyMlNqZmFzWEF3LWxreGtmZElnMEVUd0xaeHdZeWM0LVRXdFhQeElSZXhLatIB_gFBVV95cUxPVGhZeTdSRlNVak0yMTZBU3loQjl3SzRmRTBOZlZWZURrTGVTNGt5eTBwQmMzdXVVbHlQd1RVOENqaGkxTXNsR2FaOG16bG1UcGVLWTNsR1c5NjItUVBobkt6cnQ2YkQ5dzZFYkZQQlUzOG9BZHFDS29YRU1xbW56NGNkYXNySF9qbGw2cXhSM2Zwa1pQLVMwUzRoQjZjakhhR1Z6Wmx0ZTFhQTJaSWRMbUtkNG9vWHFfdU02NHd6YkhxWS10UzQ1TzYwTkFCSnMxcDBucDZyUG43LW93VjNmUnNqLU9aYmo5MVNwdGRsUTdQLXVyeG9COUhCbmNIQQ?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>46027.58377314815</v>
+        <v>46028.21905092592</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ryanair routes to six countries under threat at Charleroi airport - Luxembourg Times</t>
+          <t>Mitsotakis to attend Paris summit on Ukraine security guarantees - eKathimerini.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 12:30:00 GMT</t>
+          <t>Mon, 05 Jan 2026 20:09:47 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQTTZYcGlHTTR2TXNXS2tzQmJEaWJaSGFIYzZJWkdnNzdZeFQxekhGc25PRkFkZW96YlZCVWFmSms0bjNROFRXUjFoUFJEazhNMy1jbmZ0RVdnY05keldKeWdSSnZsbXo4bS02MEtqT0pCM3FURXJaUVBkZjhkSjMtLTBYUjFBVC1mdTBTUkVFamZ0Tl9XdDJaVTFoSlNGbGJOdFBSS3dZc1ZseFJzRGkwemgtSFRFUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQb0d4N2pyLWJ3c01jb0xRcDJOYzc2dmdITVRhZG50VmdCOEpMMU4yUm9XeEdwVnhwS3BfaVYyZFRqMG54LVFNSUhIamo0WlBZSDIzT1BGV0d3a1h3VGsydEhaYnVqLWZGQ0tUMy1hSE1PaEpzMlFYNXlJb3B0Q0ZBMnF6TkpoTTYtZWhkRExLTEJ5THdCQmk4T3ZlUkpvakh5SkFOSFBKMnF6a0s5R29ndkxSTENxZmI4VVlnTUFvVE5SZXNj?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>46027.52083333334</v>
+        <v>46027.84012731481</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>EU sees opportunity for democratic transition in Venezuela, spokesperson says - The Straits Times</t>
+          <t>Ryan Murphy's The Beauty chilling first look as Disney Plus drops explosive trailer - Manchester Evening News</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 11:45:00 GMT</t>
+          <t>Mon, 05 Jan 2026 20:13:00 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNbHUzQXNvVGN5VHlndnRuZF85UzNQRUFLcExvcGcwR2VhTF96eW1LcGd3MHpYTmtBeTNpVWtGaEt2WGd1TXV0YkxFSm1zRFM1Vmp6ZWVjbFY0b3A2VndKa0o0REpmYkliM2dZeGxrdEpZZDlOcnhsTEJZZENXdFZJUGtBc2RXRHRreEFzaXp6Y25iQmxwT0V3WDZ3ek10aEptR0NnWmdycHVkTUExU2ptVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQRE9uZW1CMkRZM1FUOFY1UjAzZGluOEpJYWxDMTI5enB6cWRIckU5ZXVFZzR5T1hFeTlSZ1phMVoxQVBmS29zaHFhZUhPdUdPN1Y4RzhOdlJpbk85YW5NVHRGb1c4REtjOUxLNE1jU3dneXpvSllJQ1dKSS1Db0VUY1A5RzM4MDZyZjc2UTZxaktkWEVBWEHSAZsBQVVfeXFMT2FGOWZaV281Z21sdHBYNWZZQ2ZJM1VtNGJXcS1GYWIwZGNDQkJtUVRlVnVFeGFucnNfYmZtcVJLb2NCN1FjTkRySm14aXF5NTZKREpzQmxTQnM5ODVwbjc3OVREM2d0bG9xbTJDbkt4Wk5HZmZTZzBHU0xTTi1GajkyOV9kMnZIdTh5WHhzWF93X1hpVTRaaS1DUGs?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>1</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>46027.48958333334</v>
+        <v>46027.84236111111</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Snow and ice alerts in place as temperatures drop - RTE.ie</t>
+          <t>Venezuela, shooting in the night near the government building - Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 09:47:10 GMT</t>
+          <t>Tue, 06 Jan 2026 06:26:56 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE95UFR3ZnR1YUwtejRtTE96bEtpT2dvNnhsWHRjTjk5ZklNdjZKMUoxMF9WQTgwTjFyUTVxWnp2cm4wQm1BdkRjci1kREZZY2RqUzdNNmhDSktldmJDd2p3ZzJFNVg5REsxcy1zTTF1YTgycjZv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNVDcxbzJNWUNOZnpEVHduVkJuYnlRSThmanlHU2UwQVBsRXlMQ0wtVUVicXJTVGx2VWM5OXM5ZEZ3ajJBdlFZNGc1TGtfWDJ6TG9tX29mLXVTcnFOdmJMUVJubWRvQ0JOMU5oalNmdEhaMHgtUGx2LTFnN05wSTE2X1ZNZlZfZkRPbmZHaDBzUnZOUQ?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>46027.40775462963</v>
+        <v>46028.2687037037</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ireland weather: Met Éireann's 22-hour snow and ice alerts for multiple counties - RSVP Live</t>
+          <t>Pressure mounts for answers over Swiss bar fire after victims identified - Reuters</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mon, 05 Jan 2026 11:46:25 GMT</t>
+          <t>Mon, 05 Jan 2026 20:34:20 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPbVZVUUxaUmxaRWZTOEFndDdtd2NUdHBjeHRDRkw2RWpLai04MnZ3OV8yWWpoQjRUTHFKX3g4NlhZbXVUVHczam84Ql8zR25aamVMZG9lN3JrdjdYWWlsa0JYZm5YcW4xS1RjWHI0QnRfOWE0akl1cVFRaFBVYjhrdk9naHBXd1Vqay1wVEJVZ0RwbGJqbW5NR1NBY0c5Skg10gGMAUFVX3lxTFBHcXhiUFE5dEhIekRGMFFpajJRYXFOUmhSbFFZQlpueXAxcmU0Nm4wbjFLTkFSTDVoc1otaTlyVXdrRXNDbEVRUFFfWXVIZ0dLTWlrTVZMZHFSWUxoZjc0elRIUElQS2ZwNUZnbGpuVFVSSVVlV2VuVWtLczNIWnljc2dsUExzWE1MckZh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPSmRTRi1JaGI3RlZXcEtWakhQRWJZWU9jMGJYVmhaTDN5VWQzYVNRSG1GOXBsNVlvMV9qZ29ZZXJCejM5OUtmRnl5MldZM2ExWl9iMXVtMjExX2dPQ0pQZ0Q5MUNFVURYazAzSmhkV0wzalFVV1BzdmNvcE43NDF6ZTJoRHdNT0VsUHltRkxlemxySndzamFrcUZJVEJZTXUtMUFjNjRXc3lYQU5Tcll3XzNxU1dtTDZM?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>1</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>46027.49056712963</v>
+        <v>46027.85717592593</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>South Carolina Faces LSU Tuesday in SEC Road Opener - University of South Carolina Athletics</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 20:28:06 GMT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOM3FEdHdsRGlhVFlacjB2RGlkcWdBeGo0THZRNHc0eVh6S1gtdktRQTAxTFhPU05UWVQ2U19XXzdSX3VNbDAtVkZXdmhoT01ZMDduVkVkeVM5TENhMHBTanlSS01zR1Vqal9UYTRQRG44ZDlJUUdqcmxaREt0VHJWSk5RaGJpakJ1RTVFekU5QV9rbVJxSUN6eUhsLXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46027.85284722222</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Bella Hadid and Meghan Trainor make their acting debut in explosive first trailer for The Beauty - and it's perfect for fans of The Substance - Daily Mail</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 16:53:05 GMT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPVGwxR19FZnZkWFg4OFJfZzJNS0VkNHE4OUdpRFc2QjkyZ05SV3cwdTh6b0xYUHRxc0hyTmFJOU4tMHNubnE0Mk01dDhUVU95SXhKSF9aYm1ZMVZtbWlFTDZVMTJUNFFVTDEtcGNBazN0aTk4YVlNekE2a1dZR0p2V3hyTGkzdmVDeGFUcUNVb09OeVppazhPOFVydXI1SVJn0gGmAUFVX3lxTFA4Ykl1SEk1OFNYeXVLWk5aaERvVzRmOUkxc0otU2FkbDNDTnRrb29FRGxQWHFrQmFsS0h4RkhlbDUtQWZHRkpjeUkzUTdnbC16Y1k5c3NHYXR4eWpSdlY4cTl4WWtLdUVoWXpJT3BDS2xXbEgxeDYzYzBoMVlGNnJZM0dsM2Y2OHlVZ3ZuUU5KRjY5VUpqRUFZMzZOWDk1V0FHdjhNT2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46027.70353009259</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Michael Jackson's daughter makes explosive claim about his wealth - hungamaexpress.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 14:37:32 GMT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOLW5QOXJOTUxzZk1nMmV3YkZRN0Z3NDJuUWhKTUVpSHMtUC1NczNGY0JVUVBMOWJJSzJMLVpGd0ZzSXh6S0QtZVFqcV9nWFA5REZ6Y3RBLVF3M0Z0dUVRWVRseklxNzVQSENLQmh5b0xRVmdmZ1pjT25FMGgtNkJLcmFsNU9vWldfTXpUMXY4cGZOTWstUTdYMm9TYWFsYUcyamxHVE9HeWR3UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>46027.60939814815</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Snow cripples air, train and road traffic in Amsterdam and Paris - RNZ</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 20:42:50 GMT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOT3RNWWl4bnk0V201a1p3Y3JlRE1MQ3pLb1Jid0I5U0hkZ0pEcUt1WWpwcl80eWdBTWMwZjJBdUJQVi0zZDdNRl9KcVdzb01rVVdWeFpwWHdvZFBGVXpfRzRUblMyQzNRQ2VTVFNOSVRJai03T3JTbm9SbjcxSEpHSVRLUkluNXNHTG5TSWc1LWJlWThDMXVNRUdhejRPcTZtMzNHQzNn?oc=5</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46027.8630787037</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Jury seated in trial for ex-officer accused in police response to Uvalde school shooting - theparisnews.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 02:02:55 GMT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNbG5ZQ0RkTlpyNW9EQ2VCV0Z1OS1lWjBhX2xtNUpWT2E2N0szRjZsangzdUNkU2xNdmdiRWR2VnFXYjlfVVFab2lZQ284cUNJWjh2Y0t6VnEzWk1FdlBudm9PS3JyMDlrdXBDRUswc1paRkNjQ3lOTGpTdm9pRThEekN6NEZuUzZENFVST3VPVlI3TkY2X2NTRkpDRnVWWVdkZ0JFaF84RnR3eGM2QjdXc2pscWlteFpMX25peElXVFZSMHdRSmlPTklZdF9yODNpVG5obWJjM3FMd1VObUJsem9VNGs4U1ZVOHB3Y3FzNzZHLWpBZ2Q0bGd1UW8zTldjbWpLMEJn?oc=5</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46028.0853587963</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>NATO Secretary General Mark Rutte to Attend Coalition Meeting in Paris - Букви</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 14:44:16 GMT</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQaTNTc293OFZiaWdlOGxla0t5T0c3ekJiT2xibm1ac3dPbUdoM3d3UURMMy12MWdDTlZpXzgySXJiWDhvQnlwdGd3RmxwWUd5TjIwekN4MXlrQzFnNjNFMWZEeTh4MnVtLV9qclIyTFBCcVdyc1E1UFYxUEs2d080MVJlUFVVeW12Q3p4ZjM0VkZNYks3RGcxZHF5RW04TXE5RXhGRE9R0gGmAUFVX3lxTFBpM1Nzb3c4VmJpZ2U4bGVrS3lPRzd6QmJPbGJubVpzd09tR2gzd3dRREwzLXYxZ0NOVmlfODJJcmJYOG9CeXB0Z3dGbHBZR3lOMjB6Q3gxeWtDMWc2M0UxZkR5OHgydW0tX2pyUjJMUEJxV3JzUTVQVjFQSzZ3TzQxUmVQVVV5bXZDenhmMzRWRk1iSzdEZzFkcXlFbThNcTlFeEZET1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>46027.61407407407</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>State Police issue Silver Alert for missing West Paris man - WABI</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 23:27:00 GMT</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPNS1LV29qeDVzSDZ6dVpZbUM2Yk9Za2F0bnE3aFBwbVZDUDdZWUFwbXdWdTJTc1VyRlA3a3ZTVnVjZ09nS0xCTVUteFRxa3Baa0pucFl3bFpBRzlfYVRYRGlIN0xRc29PSE1Hb0J0Y1hhd2NORGFVdGNEek1pU0x2M1NWSTJoR0tpeUp6aFlGcFl2UE9rSm1LanhuWHlHdlZ3bGNF0gGjAUFVX3lxTE81LUtXb2p4NXNINnp1WlltQzZiT1lrYXRucTdoUHBtVkNQN1lZQXBtd1Z1MlNzVXJGUDdrdlNWdWNnT2dLTEJNVS14VHFrcFprSm5wWXdsWkFHOV9hVFhEaUg3TFFzb09ITUdvQnRjWGF3Y05EYVV0Y0R6TWlTTHYzU1ZJMmhHS2l5SnpoWUZwWXZQT2tKbUtqeG5YeUd2VndsY0U?oc=5</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46027.97708333333</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Who Has Ashley Park Dated? What to Know About the 'Emily in Paris' Star’s Private Romantic Past - Yahoo</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 19:15:14 GMT</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVXp1VlF3RjRMcllGMEdVSGV1Z1hOcGVmUnR1Y2NraEhzbUx1VExzM2Q4ODhvcXB4WTYzOVlDT2Q3MjlQQjdDcDFwSzFtSGlNeVZ0VTdGUlp2Z25Xc0ZJZUVGNy00QnREbnFuUGwwVEFGamgtUFVPbC1oa2c3aUxzdXdhU1dYOHFDWWltN2hwdV8yVGFTelRJcG5lMHJ3bEk?oc=5</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>46027.80224537037</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Iran says no leniency for ‘rioters’ as protests persist - Arab News</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 15:26:11 GMT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE50bDVXRG5kX09RcEFmbDBkVDlvaXloaV9uY0ZEelk1LWVfUkxhTVhJYU5QMUF6ZzNoTFBEUGhLUjFZLW9tdGREWTRSMEY2aEFjeS1z?oc=5</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>46027.64318287037</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ukraine allies to meet in Paris as Russian strike kills two - The Central Virginian</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 16:55:38 GMT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxPdVNxT3FSOFBxMmpTRGZVOHZjTkxPM0h1UENHbGkxM096d0xtY1dRNFJXLTNvdWxzVUpXZWNPQ19HQ3FVaDJPM0FqV2JvUnhRV0s5Vnl5UUxITUNrcTI0T3dNNURiRDBjRUJkS1NrR0huRnR2eDA4ZnBSRU5Gbzljd1A1c3Iwci1ibU1QUXM0MXF4ZDlsUFN5dmNRX29ULVh4S0dMb0JZR3dRa2NNaXBpclNqMzNZVlh2U19wZmFtQWhBUnlDVUlWdDN1M2RxYlplX2NtVXdSNlVmNE41OHVPQnViTEhOMnFidzNEU2JHNkw?oc=5</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>46027.70530092593</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Drone strikes kill 2 in Russian border regions ahead of Ukraine peace talks - fox23.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 16:27:41 GMT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxQcWpBdVFLdXlxYlozUHRVZ2NmblpaSFVDVmVlc1U3SXFsM2xELVpIaFZoS1g2bkFZZEFUdTBQZlJxcld6VWpZb25DVkFkZm1ERXM3bjJ5WThsM3B5UHlSbjNUbGRsekJ1T1ZUSnkyeGZmdkh6clBJX0FwbmQwX0NyOXVQRkxzTXZSSGhtM2VFc3NZTE9DbS1qMTFkNVJoRXdvUzNEMThub1BLYzRWeXBSdDlxYnZGaXM1V0pjUlk5ck43am91VVJRcElYeVE3aUJKcWRiaGFLb3R0RFR1aTlDcU4wZmpPdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>46027.68589120371</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Local man shares reaction to US capture of Venezuela' president - fox23.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 02:47:00 GMT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNc1VZaDgxTnA2U3gzTlVyZ0luVUpCWG90R0ZZQ1g0NjgxRDB6bExZazBwRVM3czhXZk5FdXpweEVuRmprRFJaOE9SeDBCeURZanpxMFZCYVd0UTJ0M3hJSEdGTF8xRmZFMXFfYS1WUWRQeW5HS3ZJbGNIaE92aGM0Y0psZkFXYWctaGtPLW02cmVHNVU0TzM3dVEzakFNam5VWDVsNDlDNFBfa0wtZFJScHc4UVdmX2xtU0dlRmhZV1ZQMDQ5NjVUNVFKbzZLOTFfeFNQSnFn?oc=5</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>46028.11597222222</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Explosion rips through a bar in luxury Swiss ski resort town of Crans Montana; several feared dead - visuals emerge - MSN</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 03:11:41 GMT</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQQ2o2U2VfRVlXZHo3c01tZE5CZ3plNElCQlhyanY4MFVYd1JDUXc0MllfMFZpY29OcElKRGZ1UVE2WXJndF9lZGxrYkVTMW1pZ3VXczVKZUVzU3J5a3FLR1BkMjJFRHVCbGM5TVM1REl0c20wRVYtZlJwXzlkdGphQkd2NGF0ZzlTbWJ4cDR5NDJJZmViTG00T1AtQjl2bTBFRlZoSWVrOGRIM2pydWwzT2NDR2U1V2pYYURKaWNSVVZBQWNSV0g5MjJCcnhfQkt2dlpkYlFvdmNIZ01sWDEzSVUtejlWNzhSU0kzVThNcVlHQUU?oc=5</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>46028.13311342592</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Winter Olympics 2026 guide: All you need to know about the Milan–Cortina Games - News 12</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 19:53:23 GMT</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOSTF1R1c5RjlOUFBPaGNpMzNVTjFiZ1pUN0toNDc3Wnpkd1ZSdWJYbnJUMU1zVGdKcTlGRGoyajg5VVR1U2N6TDdWOTl1SVo0MV8xMjhhQVh3bzVFbHd5VFBncGxmaGJlUlROYTNPcjJjLTQ3aGdfOEstWGNuMUc2VEFCRGpxVWdGSTBRdUhKSmpWWlJSamtjMWxlS3MyWXdUbGxBMDlyWE1SZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>46027.82873842592</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Laser rifle program, new shooting ranges means growth for biathlon in the US - Buffalo News</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 19:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPYVVSTmgwbkJvX0t4aEY2RjdXY1V1c1U4ZHFVQWg2MTExbGF3dE1sT2JwMk9sN0xmTUE5Nm1YT05nMFhnb09PeXJuWmFQUWtLNUNiTWp2WXlpTDhFSTlIY2tSZjlkZzFYdVUtUEpBNml5R0dHT3lrazZwQ21sa1VuWjZuLTB4VC1yTktRWWRpQnJvQ3hGYVl0X2ZhWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>46027.8125</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Speed skater Erin Jackson is all about the '80s and trivia - NBC New York</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 20:29:07 GMT</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOak5FaUdIeHRJZ3NpVC1XQWRvRmVFcWl5M1FCSTg4Sjg4aG54Q1pxdDMzb1A1bU5wdHFmZGVLdHNaNXYzUzl0VFdkdGpwVDFWU29CUzV4cHotMFFiekU1dVJFa0prZlh2UlhJaEg2WW5wdEFtRnprVXlONmJMTl9LZ1ZlQ0lyNWQ1dEhMVUZOU3otWEttVHhMekRHZmF2QdIBpgFBVV95cUxNV2tYS3BzUjNfOG1OdnFscEowdk43STZwNE96aXRLYjY0RjFULVVuakNFcnNjYVlxSkpaSHpfdGoyNm1SZ2N1dUlNRTBkdzhGaEV6OEttaUxWLTF5N3lEZzYtWGpYdzFfMjRpa1VUS1ZkaWJVWXJEN1pyc201XzItbDA0Y3ZlRGhNSXA2RmxQOTJORjFqYXZPcVNoTkU2eGhpZkFZS2FB?oc=5</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>46027.85355324074</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>The causes: a clear fitness issue. Extremely low batteries. From Fergie to Odgaard, many big names are underperforming. - Quotidiano Sportivo</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 07:49:46 GMT</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNG5QMVktSkZuLU9lVEx1T19HM3ZpWGFrTTR2V1U3T1ZjUHNncTV2eEJ6T21YbldVSFQ4cUtfd2lrQ0NTRERnWDdwYnNoNWd0Y29TUmZJU3ZjYkJoWlR0NWF3TkIwNWY3UU9FSEUtRmYyX0tBXzdsRHZXVWRIVXIyNElLUzIwVXBfQjZJWkVn?oc=5</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>46028.32622685185</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Brussels lines up farm funding concessions to get Mercosur deal over the line - politico.eu</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 15:46:00 GMT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOenZxZG13Tl9RSTRWLWpVZWNGdVliTU1xTUpnWVBLNFAxZFJUOEtsUnBnRkZuQWl0Vm9CUlNKVG4tY0EzckNJSWE5M2xtRnlXdmxEOWQ1bHN0MGNDZmhBS3dDaWFsMTlwT0xKUTYzYXNJa28wVGRGaHYxZ3I4NWlsaWJvTnZleFBXOHVVN2Q4M3hHbzQ1QjQwLWFISGgzV1RhWHBZQUsxX1dkd3Vh?oc=5</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>46027.65694444445</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Laois farmers urged to unite against Mercosur at protest in Midlands - Ireland Live</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 07:38:05 GMT</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMFJnWVFtZTlsdFdSWXVEWHEwcUtic3U0NUZjOWpKMzYtRHRuTS1vZzVOUmJNdnFXWjRiUzR6NUZZS3k4YnpENUp0QkU2aXplX3RPbkJYbjdzSWdQU0FuTXgyZjV6NnZnNjhubm9DRDctUENnNC1oLURWQkZvR1Q5MXViRjdyOUtrVTFRSzN4VmxLa0lZcktaWlM1MWM3OWo3ay1ham01UWF6LWg2aGJIR3FIdEkxYTM2el94T0FwRm0wQlE?oc=5</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>46028.31811342593</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Up to 10,000 expected at ‘No to Mercosur’ protest as EU vote could be Friday - The Irish Independent</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 05:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOUnliNnpvWEdfWVFuOXNBZjFVS0VZczNSZlNhRjZoUVhpMzYyc1pVbk0wWW5LOW13YXptalVfdUMzd0dLQU5jX1VEV3NnMGlmOV9zTmhFZFJONnVWajR4VUFTYlQ4WDVyZmNybk5XS1ZOam54ZDh0dGFlS1p1UTZFTG5oWDhfWjFQY2NyT2hROWkxSFZZY2JwR0N5Skw2dlRFTGpDRmVMZFhvT0plbkNjdllDSDFFME5TSkR6QTl6dDZPZkROZDBpMQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>46028.22916666666</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>EU urges end to Venezuela tensions, questions Maduro's legitimacy - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 00:31:20 GMT</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxORXJYbWtYdFlZZkpXTC0xNXlNakhzNTY0RGZib3lVMzc2NTVJWWFZU2lGZzJfdUMxSFJHRDhBUnpzQjZualNUTzQ2S09IeGJOYXJCVUFqMmNfTlVxVmZuZU5Rc09DQk43SmhGWnZKZG1BbHVIS1UzbXNTV1M1aFFpazE3VnZybGsxWVVYaTRFR3BZSWlJQmV3cDhXanZOMkxSaUxZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>46028.02175925926</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Man, 26, allegedly raped 15-year-old girl he met on Snapchat - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 22:02:31 GMT</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPVXVlQnM3dEl3U2tKV3JEZ3JLeXU0SFhPekFEbXFYeW5ScTZkRXlfRmhCc1pUcGpDYUV6cWJYZmJGc3ZtbUJEQ2Y1Q2tVUXdBWFcxdXJFVnJWZkJoYVB1NEozNDVRcTZKRW5Bb1VZOW4tN0tBZnN5WmFHQy1zV3lKMXk2UlVCaHExa2I1NE5XX1hlczBjVUstbW9LeHY4THFMZEpqT0dScw?oc=5</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>46027.91841435185</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>EU sees opportunity for democratic transition in Venezuela, spokesperson says - The Mighty 790 KFGO</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 14:39:28 GMT</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPUDNPRHJ1LVBIY2lBekt3REYwRlRCZGw1SzhKUUZlLV9XbldKc014bFZqczgzMDV3WWgtMEhUOEdJYzR0MXVnN1o3UzdPVTA3ay1Cb3NMSlczcTc2V2ZqTXVyV21pMGtObGtsblg2Ry1NQ2RqN2lRLVFUaVZPVC1rMGdQSVZkMWdZNWVZSnhpS1VwdFJndzUwajdJa0ZFNkVLOXdZYnlweGk?oc=5</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>46027.61074074074</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>How farmers can lead the way in cleaning up social media - The Irish Independent</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 05:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOY09wWkVId1VIdlZwYkIxZTVycEsxSlpqUHBQTGEtd2xzQ1hiVExvSVNObzdiR012WTlXdzFnY0NEOGFjRmNkV1dsdXI0V0M5azkyWHdlaUt2M3czRk1uQ0xFZFd2bFBPMERtNGxTZzFBTFdkTW0tTDlwcTRQRWoteVh1NC00eDdGYzBfTG5WU3d3Y2xCMTVOcGYwMk14di1aSTZCalVzNmRlXzdDanRWQ29LQzFNVkE?oc=5</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>46028.22916666666</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Hungarian Security Chief Links Western Europe’s New Year’s Riots to Illegal Migration - The European Conservative</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 15:31:28 GMT</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNYVAwSVZTZjdPeURMeVFUU0NqTUlzSC1TWWNsaFJqM0ZMa04wTE8xMVU0TVFjU2d4VE9rOFJjd1ZNdDJ2bW9lalctVnVoMUxEREpmajJlRVotak9RSlRzMjZFaTdUU3E5bTJZd1R3VkxCUVQ3NTFiY0t5allhRFhxUVVpQjJhdk5MRGdYSEFWZ1UwWXF6NkhoVVlRYWxrZzRxekVuVmFOR2VKNmQxdl9wd1R6TVItQVFJRy04VVJFa2FKc0xSS0xoS29tSXJ2Q1pDaHp5Tw?oc=5</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>46027.64685185185</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Showdown in Brussels over competition policy is nearing - Financial Times</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 05:00:37 GMT</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5KRGxFUDB6X0hYYm5vMkRmR2I5Z2VzdkpaUjNZSzlUOUwtV2NWTk9uZnoySENOZTR3eDJVMlV1b2J6MGd2RTF0VTFhcTMzZm1ZVmE4bzF0RXJfQU0tR0x2NTUxcS1qOTR2ZWZXZm42dG4?oc=5</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>46028.20876157407</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Warnings of ISIS links ignored. The anatomy of the Bondi attacks - Michael West Media</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 18:05:36 GMT</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNS2dqLS1WZVBHN1IxUXlVeDBySE9qVk4wc0Q0V3d4cFBJSDEwNEhwS3RJUF9mMUdOSTJYUFZlWlM3bHpvdXhwOUZfYXFPUUhEenBtU0VqT09fVF9JdU1ZNFZoemQteWN4eVNHQmUyRW1HUzhpeEx4Nkd5a0ppX1Q3anBsWmhCRC05Z29tWHB3NEpMcDhfMlE?oc=5</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>46027.75388888889</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>What happened overnight? Police blotter report for Monday, January 5 - Newzjunky</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 21:42:45 GMT</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE51QThwY0xBRjN6VE1haFlKYTRSZ1NXNThZRGxLN0dWajI0eVBQMDVPdW1qTlJVZUF2c21sOVJ4cmMxWEZDR2F1bjlpel93cmFLbEZ6bWdoMUw3Rm4wNGRWb1haekNORm91dXpoUEh4eWM2QnZBQmZLUHE5aUpUZkk?oc=5</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>46027.9046875</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Local Town Searches Wertheim German Terms</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>("Wertheim" OR "Wurzburg" OR "Aschaffenburg") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR boycott)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Wurzburg vs Levice G1 – Preview &amp; Prediction (Jan. 06, 2026) - basketballsphere.com</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 17:39:51 GMT</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNM0Q0ejJPSzRnVm8yLXV1WExVY2ZOVGZwN2o0RldsWkozV0JSQ0k0WWd4RWRaQnc1LTRBSE5TVDNiVkczbzdHX1ZqLV9paDRtX0hwZFhVajhjTk1KMWNDcm9yZDFTVm1jUGFneTNhSWNCclU4V1l4bGRYX2xyVXBocGJWNGpidXhxTUl1dEx3?oc=5</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>46027.73600694445</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Village search Wertheim,</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>("Wertheim Village" OR Wertheim) AND (incident OR protest OR police OR security OR evacuation OR closure)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Europe and Trump’s National Security Strategy - Quincy Institute for Responsible Statecraft</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 22:21:36 GMT</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPV2FLejRoUS1qVHFUOGtXMkZhaW8yS2R4WjV4Rjd5VDRSY196ZDNRQUpSbmMyQ21Nb2oxMTF2NmNuZS1URUhGUFNhR2lNeFBoeExzRzlfTjNoczF6QlZfcjJ2WGl6bVV0QzE2c1A4OXR6bHhycVZIUEc4ZjVUZk1MSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>46027.93166666666</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
           <t>Ireland / Kildare Protest Groups - Social Media</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Former Kilkenny underage manager takes the reins with Kildare Hurling champions - Ireland Live</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Mon, 05 Jan 2026 11:12:50 GMT</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQRnJ1d2c4XzVoNzdlcVJhR3U2UVp1aG1DQkUwSlh6WDF2TUVxM2FlZ1cyZXg4eDBwaWR0d1VWTndMUHNFd0w5bUFWYnFjdVV0MG1wSEZVV3BDbF9ZMFBOakszekZCcm8xaGF3YkdLWENmTTBTYTNoTzJzM3VsVGtlS3dBTmcyT3pPd1hQLUJaTnRxZE5rRFVzMmpuQXJsNHcyN3NNSmxHQ050TzV3LS0xQ1pCdmdOc2p2Z3d3d3YwNWxzVFFBR0VxS2VTNTVhUHl1OHIybEZ3?oc=5</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>46027.46724537037</v>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>The latest LEINSTER LEADER is out now across Kildare - Ireland Live</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 05:37:27 GMT</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOR3pia2k3VGFTRUhxTTNEMGpuVkVUcUljamNHMGZpdkxLajJVTlk4UmNORHpjVFBHZlpUS1JOTVhGRHpIVkV4SHVoUnBueDFGQmxic1BQTXljT1VjeFd4VG9pYlpFNmY1M3MwSGM3ZG81TGMwQjN0dmgyOFd0cW1jZnM2UUpTYWtMczM3Y3A4ajNDclB2RVZFUUQwZWdPT25WcUJWY09xQ3I0elZnWHQ0?oc=5</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>46028.23434027778</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Vacancies lead to delay in Kildare road improvements - kildare-nationalist.ie</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 07:03:46 GMT</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNaXZGNmh5M21GVklVMFVCZF9MRFRyMDRUTlFLZmE2VmNfaHlYTGs0Mm0xZXFtcWlMZTZlbWk5cXhGMWJ0OUNvSVprQjNob2VYVFlFRVdnLVRZZ25PWl9HTEJtY01FS0tPTXdOZzJTLVNFbm40V0JIaFdQWHRoSV8xT2ZNU2lOUTRxSkw5Mkp3Wl93VjRFOXlQbnNiOWNJaUJOSGgtX21HbWw4VXF5?oc=5</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>46028.29428240741</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Louis Vuitton Opens a Soho “Hotel” to Celebrate 130 Years of Travel - Business Traveller</t>
+          <t>Demna drops his first Gucci campaign, plus more fashion news you missed - Dazed</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 14:07:35 GMT</t>
+          <t>Fri, 09 Jan 2026 18:36:00 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE05WnlCdVUxd3VWQ1R6aWlCR3gzTXY1YWd2SVpzWDN3RkVFbGZGRk5BWFlLMU9QYm9tRGxWc0dfazlURHg0anM2Wllpa0M5dGRsTlZjV25nLU43UWR6elRvRDBsQWJ5aHljY0k4X2xjN05oaDBwR3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOeXdrZnJ1cVZUb29zS1VZeVRoZ2Y3dWE3Q1g2UG16TXptME9UZWliSGhOQTNzWDlSSjF0YXd1a0RNVjBCZFBldmoxVm5KYzloNkxDQlp6eU8wa21pUVMwRjF1TDRUS3hHVk4wZXUxald3cG1qZTl3WG5Qb0l1X1ZReWhPdC1FMTFoRjZLQzNuYlJBY2w5VjZiSzctU0ptSUszSy1NV0wydTNab2thZ3M3enpfWWQwZVoxWjYwc3o2c28zQU1m?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46031.58859953703</v>
+        <v>46031.775</v>
       </c>
     </row>
     <row r="3">
@@ -515,24 +515,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Burberry Her Parfum makes travel retail debut - TRBusiness</t>
+          <t>Editors' Top Reads: News from ASOS, M&amp;S, Tommy Hilfiger and more... - TheIndustry.fashion</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 11:29:00 GMT</t>
+          <t>Fri, 09 Jan 2026 16:16:01 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQdjNBWndUUlJIZktGS3dZTkZ1Z1JweTJPeWsySE11UTdoRTBiOXh0b2dYUVlsS1JRYjhSZWVhUFY5RVl0WFJaX1BrNHZQajR6RUMtR0lxaGYza3pwUDJUdHc1MUlHN2t5TmpLZFdIZWFSZXUtS0lCUnllZkVhMEl2LUl5VS1VM2RRck1mYUZ2bXJXN3ZxSFVNTjdqSWVHakk4MjFpNXhKNkwxbVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVNBblJsS3lVa0Zoa3hhdVVldTF5R0tJOXpJRlVjWFZSZmJmVWRCQjFCMGl3aVNoYmNGdHRqLWZxTXRWUmVGQnE0QUtNQU05R1BXUjdPZUgteGc2elZtMUs4WEJxeGp6b1VUeF9ZS2ZPQ19HYWp5ZEh2NG1Kd2hIaWg4Um03MW1zOHNReDJQMUxTcll1YjFZ?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46031.47847222222</v>
+        <v>46031.67778935185</v>
       </c>
     </row>
     <row r="4">
@@ -548,24 +548,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Armani Group develops global joint venture with Symphony Global for Armani Hotels &amp; Resorts - FashionNetwork - The World's Fashion Business News</t>
+          <t>Dior and Moncler Help Shanghai Nurture Homegrown Creative Directors of Tomorrow - Yahoo News UK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 11:46:52 GMT</t>
+          <t>Fri, 09 Jan 2026 17:24:33 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNSm5tWE02cFBHZ2VYWGx0TVczUnhjUk56bzd3bVROcmQ3Rk5vbmpnRUNCdHRkanpKSktxakMzS0xwLWg3anlRNUFCSGtEdW9kSE9CQ3VkeGVpNkdCcGczVGlwdExQaWxFSjdOaWZNNjZWUDJFa3BGa3dWalo0YXZ5Z001eWR5bXVSMDdNQ1NZdG0xRU0tYTZiQnpETlVrUW04M2hVZzVhemQ5Ty1JZlY1eHZMdUQ2eUFvamI2NllNTThaNTlGV1dQd0RuSzRyWVRqUlp3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOaG8tdktBTDJMbWhoXzlfUEhSVGYxNmxrRFF5NFJhUWVMdk5RTklGZ3NyRTRrUHduSEN3YVlHWXIxZ3pkWGpZTTdqZkVjRkhKQ19yaVR6aGtLVzFIYXZRa3hTaGljVEs4RVF5bWY0THNmUWtJZG01b3JXbG1lbU15RQ?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46031.49087962963</v>
+        <v>46031.72538194444</v>
       </c>
     </row>
     <row r="5">
@@ -581,24 +581,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The wait’s over – Jonathan Anderson’s Dior arrives with a Selfridges pop-up - wallpaper.com</t>
+          <t>Gucci’s latest chapter turns up the rockstar energy - Rolling Stone UK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 08:34:46 GMT</t>
+          <t>Fri, 09 Jan 2026 16:50:00 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPYzVVTUFSQXBkZ1FLT2pEVEh4WEFWbVlwSk5KaVlQQ1pLdzhQVE5MWFJaQTFqR1pCWWlRSlZzUGVJR2JlZG51d1A3QURkX24yVzEzQVNaT1FFcnE5ZWpFd1l3M0JreFd3cndINFlnSmxNVkFmUzUzZHFZVEc3QU1zR2l4SnNMbFFY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBoRmJZV25xV01DMW14N1hLMW1kczNEbV8zbGZfbm53Wk1PTlpNcHlWellxTnprV3pJNFFDcHZtMTlTdlpYcFc1WGkyb0VobE9SRDdRWVY4LVRJVXZhR3lzdzFDbmQzS3kyRGdTTXh4dHduekpidF9mLS1R?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46031.35747685185</v>
+        <v>46031.70138888889</v>
       </c>
     </row>
     <row r="6">
@@ -614,24 +614,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tommy Hilfiger signs “first of its kind” sponsorship deal with Premier League club - Prolific North</t>
+          <t>Discover Jonathan Anderson’s Spring/Summer 2026 Collection for Dior - Galerie Magazine</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 10:16:52 GMT</t>
+          <t>Fri, 09 Jan 2026 16:44:35 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOR1lPNU8tbS1qdFRxUVlDZTkxNnRsTXdJSjN0cXk1dTZDTnlvSWZOd3N2UkMzOVByMHdXV2tQMlMxbkx6ZlA4anlXYlpVRnhXVFM5b1JDekg2VFRTcmwtLVdxTDMybmc5VThuanhPZW90VkFMbmYwWVZxNzRBZ3A5R0loei1YY1hkX2oxdWtUQXlCZ1ctaTNUZ1l0MnVxZmpmM085bGxMcFJFTEtWWHJIZkpCMG01T1JXUUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPUXVtRnMwb3pYRFJKQ3B6X0lwOEhOV0FySElqNTFlaDNhSTk0U1FSQlprV0JDT1pxQmotTGw4eU5NWDc3UDU0ZE9tYmd2RXkxTFNsVUZqRDVJcVdRWkxydk5SOFJFelBqWmNQTjNEMmR6Q3NuX005VzE1ZmJLMC15cGZmejd3OS1vcEZTdDZscFRvaWFEMXA5ZF91Zw?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46031.42837962963</v>
+        <v>46031.69762731482</v>
       </c>
     </row>
     <row r="7">
@@ -647,24 +647,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Madonna does her raunchy thing with Dolce &amp; Gabbana - More About Advertising</t>
+          <t>Gucci dials up the sex appeal as a new era takes shape - attitude.co.uk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 12:55:48 GMT</t>
+          <t>Fri, 09 Jan 2026 16:22:39 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQS2RtWTFUTmNQQkJ5TUp1cnBQeGMya0ltSzI2RzJPLTZNZHZsRllRcmcwMU12UERPLXRzQjcyZ2RqUHVHOXFTaG1YUWZhbERSSU5YSTJxSk1qWWNaME5nZFY3R3pDUG9sbGpaT0piazd6R0tJMU1NUXM5Q2lnTzBoMGhiSjk5enJoV3Y0WWtlZ1FZd2NKWEFNMVh3Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQNEF1dzlXNW0tR2prN1didzJocVdCODl3VVZrOEstVVV6WDhxLURZRFBJc0tVcHZidlUzSUp3WVpZZ3VmeG9pLVNHWHlwc21mNTkzd3N6WWdxdmxaejViN3U0OU1BRXQ3ZHFsNUpLb1RhMDczMi11cDgtQ09EWGlXcA?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46031.53875</v>
+        <v>46031.68239583333</v>
       </c>
     </row>
     <row r="8">
@@ -680,24 +680,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Renowned explorers showcase Burberry’s Gabardine collection - Hero Magazine</t>
+          <t>Alo Taps Former Dior, Miu Miu Executive as International CEO - WWD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 11:10:40 GMT</t>
+          <t>Sat, 10 Jan 2026 05:01:18 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNZVFIYVRkNExiUDRhOHZSRVNFVmh3YUJXTGpNdzNpeEtLNVFUZlhNQnhseGRxblhNaHFsMTI5X0o2ejNwQlJXUTNRdnNuLWUyZF9yRm1UbTN1RzRiQjY4enZNamtKUUhfc3QwM0pMNExwWE5OX3FNNERZNjNwNE9hVWtLYVBDS0hVbnRmTlJfUU1TWXpEY0VLdC1md3l2NVRo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQcUhCTHdoemRYUjJCT3o2bDlVVHNZTTZPSTZRazJHS3ktTjhtYmRsc294RUQwVkd5S2FIMGtfYks2MnpmZWFZNHNiTzl3cmdBV05fYkNfTTdWUjkwTDlLemVkdW50ZmxGNzdiMTl1ZWFxSUk1VW4xMFQtYVREeDRMY0ZGR1QyM1UtUTJkXzZBLVpIQm9kY1c5OWxsdTJZVTdJMTNIVGU0UGRjV3VOV2VjaWMtVmlEbGVvWWlJMURR?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46031.46574074074</v>
+        <v>46032.20923611111</v>
       </c>
     </row>
     <row r="9">
@@ -713,24 +713,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inside Gucci’s Research Lab, Where Materials of the Future Are Made - Vogue</t>
+          <t>Olivier Teboul named president of Parfums Christian Dior North America - FashionNetwork - The World's Fashion Business News</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 12:26:57 GMT</t>
+          <t>Fri, 09 Jan 2026 16:23:53 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNaHktVWxtNTZuTmFRd3BtZXowdTNuRzR0Q3ppeFpCQ1VtTkc2OXppcHZ6ajdqcENTaVdfcTd5SUFNdWxBWFhxaXZKdG5KS0I4NDhmNzVjZjM1aThjaXJMZ0tEQXA0RVhrVHVFQzMxcklQazEtdU5uLS1xdkJUWTVmaFlpV3l0WmIzMFNWR2txZHhUUU0zZkp4a1ZzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNcUxmVW95SmZJeU5WVFVkRFRiZ25vOWE3U2tvbHEtVWhxUUtRNVJmd1hNTXEtQ00zNlV3ZDVESWtBZi12U18yVTc2WlJPUC0xdV94dzM1SzVjc0F4ZC01RmUwRktCMVhPUWFiUEY4TEx5U2IzV3J5R3dsQV9xX0xzTG5RX2liNTczQ0trekNFNTZGUnllSlZ2d2ZqOWpxY1hQNUFqaVNUMzE1dHQza1pRcFkwT013NjUyUVE?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46031.51871527778</v>
+        <v>46031.68325231481</v>
       </c>
     </row>
     <row r="10">
@@ -746,24 +746,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'I Was Told From A Young Age I Was Wrong In Some Way': Now Anya Taylor-Joy Is Unapologetically Herself - ELLE</t>
+          <t>Armani Hotels &amp; Resorts to Expand Globally Through New 20-year Joint Venture - WWD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 13:13:50 GMT</t>
+          <t>Fri, 09 Jan 2026 15:30:07 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBMUW1lc3VDcmY4UzVVcFR1N2dqOFdYekRoOG9Idklfc1BwdWNSRndlbXVfRkZScDhVYTQyeUJ4OHZoazlmcHp6cnlZWUZrRE5XS3JTb0VBMVhHRFVFVFQ1OFNmTDNSbFg5X0JsX0oxQnNiaEd4VV9EQWIzVVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQeUp6VXU3U1JyRFZrYWxrMW15emFVdHZ4S1N3TGFEN2ZJS0lqaDlPRVJiN1R3dkQtY3pOcHppbjVDSE9VY0JXWTZvRVBrdm5RZzNqV29JejBLTWhLS0tyQnpuS2RhWEF4MUFDZEJnRTJLTEtmTW1tWjQ0ZjdUQ1pMQ3RRTGgwZTdCalhySm1rM3g4UG1oaXg2WGZ3bjlwN0pVTFBsNkhMcVczNHZrWkU3VFV0cWZRZmVfTlE?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46031.55127314815</v>
+        <v>46031.64591435185</v>
       </c>
     </row>
     <row r="11">
@@ -779,24 +779,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dior Beauty Introduces Cuir Saddle, a Modern Take on Leather Fragrance - A&amp;E Magazine</t>
+          <t>Hailey Bieber dazzles in glitzy Armani gown as she joins Demi Moore, Emily Blunt and Mindy Kaling at the 2026 WWD Style Awards - Daily Mail</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 09:55:57 GMT</t>
+          <t>Sat, 10 Jan 2026 03:54:00 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPMDUxa3RuOU9aZEdELUV4VU03aHlFdEhlN2hwZ1BhRGJLTG0wTkZQRlo0WkhEbGJnbVhZSWNleE8tdzRvV2Q3WmVYSUhKZ2pWODQ1UzRIeFk1SnM3Q3VFUGhGUDlFYkttWjRvcW14VFAwQVhOWDA5d25lRExYUUJyTlRoRUR2NFlSbFhMeko5VGlGNWV2dWlDa1hPZGVJQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPU3REOXlHM1hwLXU2RTlURkNTX1Qxc01vNzhIMlpVVkhvR1JlU0Y1MTVzaF9ETFRzbzJlTDJKX1l1Y2NmRkRlbFItd1UxRTBCVEljS0NqNmV1NHo4STVpemx1dEJnMWtaSFFDUzdxdS12d1J0Q21DdlhTMUhJeE0wTnFITVM1dnpEUTVlaVBIemEwQUVlN3Q0alZWbUs3RkVoWnpGLXh4aURISlYzOXBGSHUwMNIBuAFBVV95cUxPYU90NjhESUd4WnFoRkVESkxpTlQ1UnpSOS02YUtKRFp2bE9tb2lieFJoQTRLUnFrcHFyOXJxM3NaV0JxYWdTUzBYYi11WXJGcVlNZEhwejk1MC1Yb002MS0wbkhXcTBmRXZ6V2lIc2w1XzBRQ09SOHFqZVdOSlFWdkIyQ3Q3aGkxOTRYcVpRb3BHcFdUXzZQa3dNRlJubkdhQkVWOTdmZmowemptLXNHX1ZwYUdVcGlo?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46031.41385416667</v>
+        <v>46032.1625</v>
       </c>
     </row>
     <row r="12">
@@ -812,24 +812,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Valentino celebrates the lunar new year 2026 with a poetic new campaign #YearoftheHorse - senatus.net</t>
+          <t>France • French security contractor to Louis Vuitton and PSG lands in legal trouble - Intelligence Online</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 09:38:03 GMT</t>
+          <t>Fri, 09 Jan 2026 15:37:30 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOWnE1d3ZiYUdfSjA2NlJGek1ZYzVzQzlKY2t2S0dpM1VuSnZzM3lVRjh4RWhBblBDWUNLRjBGc0lOTXFYNDdqQm5saUNNemlTMUhSd0daR0RmMHhHb25GaTgzX3FKS21Ock90R29WR3FNck1fY1VkbjNOTmliRHd3LWlneVVBNlQ2cUJKRW5jZGdPc1RyYjlaSHhKT3lLX0NYYlpzbTZYWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQRVAzV3dNQ0hORzlRTllNMUFfeGYyTFlWaXZ1UVdULXQzSkhjajJtdWY3dWd2eXZzQ2dhUm9hME83WkczODNjN3Uyb21qNGhpOXpzY0RmQzBPOFhrNnFVTEx0bkhtdGZkd01tTldUR0syMk0wUGxPUDh6ZDNZLWc1VnU3bFVRMHduUUVjWXBOTE40V2xDSnFWbzBLR0lkaTd4WlF2MHVjRkQ5cTdhUkQ2djl4X0NyOG1fa2pvVzVwRUdkS29JWTdiOF9oQmcxTDNIdlBwbTROM2J1THRxUnZ5WUpB?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46031.40142361111</v>
+        <v>46031.65104166666</v>
       </c>
     </row>
     <row r="13">
@@ -845,24 +845,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Louis Vuitton doubles down on South Korea amid luxury market revival - KED Global</t>
+          <t>Louis Vuitton | The Architecture of the Monogram - Flaunt Magazine</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 13:23:00 GMT</t>
+          <t>Fri, 09 Jan 2026 20:40:23 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9KMlpZMFRLOXZqQjExT2NZbFhPWFJDeXR4U2dyX21yN2tmaDRmRWk5dzB0QTlfXy1wUUNhZ205cU40RGRfMGNHYnppaWdEbVg2dW9ob0ZzeTlnMlk4b2c2bndmaWhYNGFO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBoUHBLUHNqcXlTSUZnZlI1MVB2Q1BUQnhDb0pBSHZFNUJsQ0tmenByR0NfUXI2SmxBVkh0RW9PSHlkSURSeWllS1JtdlJGWDlXMFFXZXlSOXA2bUJLR3VvbXpQb2U3WVdQUmQzRV8wekZTRkhvWVVtaWdXMUhFS0E?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46031.55763888889</v>
+        <v>46031.86137731482</v>
       </c>
     </row>
     <row r="14">
@@ -878,24 +878,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>‘Gucci: La Famiglia’ asserts vision for next chapter - Luxury Daily</t>
+          <t>Gucci's Highly Anticipated La Famiglia Collection Has Finally Hit Stores - L'Officiel Philippines</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 10:01:33 GMT</t>
+          <t>Sat, 10 Jan 2026 02:41:42 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxONWhGY0JVRTZfWmxHOHQ5TTJuTUdCRmhVZjh1Q0xydDItQUtRdV9nMXd2MUpKcWpvNUpHMHdTT0V4YTdSeE4tdjlpOXBfWGg2MnhFX0ZQT0ppYldjd2w5Y2x0dlE4OHRYUXY5Vjc5dlRmZ1doVzZ2MFlVS0JpNnN5UkZ2Ulk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNdEZGOFpvOFhaMHdCMzUzc05id3EtWC13ZFRMRVFWT1JSczJkb0lmWVNQYjBvUUloTTNSSmY3MFBIX1RGb1Vyb1NMRU96REVhTE1ROFlvbm03NDlnWTV3X3BKSGZsZW9mWlNsNDRjYmYwaGYwY0VER1pVSWdBWUc3OVp1U0VvelZTZ3laWFQ3N1lVNlVYZllNY251dFRBS1BlOURYVnp2VmQ2WDRkNk1jc051bnZuVUxtZ2Z0VzVXQnRKTEN4cDJWdmZjMWJlODlLYnhDa2Y3YzVmbjdGVjA2WVRQOUtzaXdfWlFxTFZR?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46031.41774305556</v>
+        <v>46032.11229166666</v>
       </c>
     </row>
     <row r="15">
@@ -911,24 +911,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kate Hudson flashes her toned torso in a chic tailored look as newly-married Este Haim goes matching with her lookalike sisters at Louis Vuitton and W Magazine's star-studded dinner - Daily Mail</t>
+          <t>Here’s Why Ralph Lauren Is Not a Typical Apparel Stock - Trefis</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 10:49:06 GMT</t>
+          <t>Sat, 10 Jan 2026 00:08:24 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOX0E2OUVBcWdnbkQtekx2QTh2SlptUWNfdmlvMkxPa1ZLaEZXd0pWVy1rMlQ4NWhMNGJCRmVTOG95NjVJb19tVlVJRmtZTHFnZGRsZENnSXI3NmMtbUVNNm5VTnlWVEk0ZWlZcEpBQUFSNHVfZWEyOWVwR0wyMGk1OXpwU0tBZk1fakIzQ3o4TG9MUVBvdTFfSG5SeDhrRnMzM1MzcmVBUmZBWEdMLW12VXQ4ONIBuAFBVV95cUxNZDR5cGN0eDBZUnpZWl9wN1BHRU85RUZoNHhCX0VvLUxTNGhvaXFDRnNnRHZEVExOV2VHajkwUFQ5dTB4LTNzZkNLcWRqMEtTWE5GZTdVVEF6N1Zvdjg2dXo4UF9hMFBtSV9NUTg0dW43UlM1MHFsQWpmQU00MVVYUlpNTkRMWXdPWGZCRTg1dFkwbUZlZVFyLTNXR0d0ekgtdW9TTldUaFc1N2FrYXlWVmpsQUM1eXlT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNeW94Tk5ZcEpRWGVxazVXT25FZW14d0pXeWRGYzNMb3pWQ1dISmhfLTFoLU81RmloTFhvYXIyeXNYNnZLLXdUeElBd0V2M2Z1eGpjTjY3VkJDMjFDVl91WnQ4anRYazQxX1dSZ2JCRTQxbU1weWRMR2R4cVdYNVJ4TXdSYUVETzRQMmZzUFhPbGtnR2sta2o0ZHJ4aXZoQUEtWS1BMXg0djNnOU41YmUyVFVn?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46031.45076388889</v>
+        <v>46032.00583333334</v>
       </c>
     </row>
     <row r="16">
@@ -944,57 +944,57 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'Stylish' £35 B&amp;M furniture set looks 'so similar' to Homebase's £225 version - The Mirror</t>
+          <t>B&amp;M European Value Retail S.A.: How a Discounters’ Discounters Built the Hottest Store Format in B - AD HOC NEWS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 10:02:00 GMT</t>
+          <t>Sat, 10 Jan 2026 00:44:32 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQMDEwc2hpWk9NMjd4bk9maVk2RDBhdk1TMXljY0NaQlJGbm9kQVRDb2dKVlh3RTRmaEthell6cEhpQUIwbnVNVnQ1bVVYdUxueHk4MndkZ1NUY08tSFFJTENLalNRR3dRU3Z6N1FRSXZ2OHJnZ3BqQzJ3eGdvY1hOM0F1VE80RGo4ZmfSAY8BQVVfeXFMTU1MN1RROG9CLUtiNUNWdU9FbFh6V3l2MUc1ZEZjQkJHX1RQMXN6RzV0cFl6bHFsU0tVSU1ybG96RUExc3ByVFlqbDNQRjQ1dVIxRUxIMWstUWMtUFVIM2RITEVnbjczaTFvTDdmenRhY3FOY19WRVFXdjhsZHppLWFNYmk0YjVGY2M2Z3ZKeW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPZEJub0hoTTVRZF9VX3BaaUd3bXFJS21BNmtXZFdaSmVneHg5X1RfSXpNbzByTk1lVmFhTFR3QWFaUG5UUlUxLW05Y0FyX0ZtaVpCdlpadjJOTlY1azlRUTQxNnpVdDlfR2lrSkZ0TlpzX2RYMjVlcXJoU2xhTHJuNVJlY3JiX21oZ2sxOENYUjFIaTJoeF9Xbl9uSjh4anVzdzZhTjQtVDJxSFBqSG9rQUpaZm5mU1dHTjJxQkFJUFFIbXpsNUNj?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46031.41805555556</v>
+        <v>46032.03092592592</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DHL: How Packaging Supply Chains are Becoming Circular - Supply Chain Digital Magazine</t>
+          <t>M European Value Retail S.A. (Common Stock) (BMNU) stock compared to peers - Long Run Comfort Guide &amp; support options for steady strides - ulpravda.ru</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 10:00:45 GMT</t>
+          <t>Fri, 09 Jan 2026 17:19:53 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOV25lTjRMWjhoSFNIbVhOU2FySmdVOUtlUFBtTzhlYmFpZXJpZ0lSSG1DdVFJZnREY2RRSjByNk9uY2oyZnhERldHV0J3SERUbmEzY1RiYVNGSmFHSzdLYVl6S0RKUXl0dnpTUENLV0lFZ01qblR2NFNvWnFQWExpZDRfRlJTMVZ2RHZJdG90M1hrdmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPakZ1dDZPYVBCYVplQkJSTkV0a24tZGJ1NnVTZHhsVENHSC1Cb3phUHhCVTVmV2VvV2NIVnBrSjhFNUNhOFBwZzlGd0JRTDZ4NDlUbjIxdkZDLWdrbUE2Qlp0MzU2elNwSXlXUmlDNTRFbjV1bmhjX0NPMjBwdHpBSGVhaW5PVmJteklfb1NvRk4tN21Ya0RwbGsyOE5JVlM0X0FmVEdNcnpOMWwwOXpfd1FjX2g?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46031.4171875</v>
+        <v>46031.7221412037</v>
       </c>
     </row>
     <row r="18">
@@ -1010,24 +1010,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Amazon Pharmacy Expands Access to New Wegovy® Pill with Insurance and Cash-Pay Options - Yahoo Finance Singapore</t>
+          <t>FedEx driver does quick dance routine during delivery - Yahoo News UK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 14:05:00 GMT</t>
+          <t>Sat, 10 Jan 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNOUtxVkxvUkJFX1Zjd2NRY3pDOUhjMzJ4bXprck5jX29YcExoYmdKTlBSVHQ2anZ2X0FhUGJpUEZMNnRyaVlvV1QzVk93ek4tWmRYWS1QdUhWWVVZWHN1cU1vOTgyTGxnVzdsaVdrV3pFa1JYODVaQXB6VU5xQjFvMFVKLTlGRmpfaUVfU1hjYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBrQm5tdnFUazhuQXBYMlZmT3R3RVVsc0tUa3d5aE5qa2FwblE1T3ctcnJ4S2RyS3JTbEZac05Ic19KRm9hSENMbkFJLUtWWVlwalJ1cDVyejQyMTlMa1lmaWUwcUpPLWFzNHVTdFY2TDJUcERzcmcxd0VR?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46031.58680555555</v>
+        <v>46032.33333333334</v>
       </c>
     </row>
     <row r="19">
@@ -1043,24 +1043,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Delivery giant FedEx ends services in Brazil after 37 years, maintains international operations and supply chain, closes facilities, fulfills contracts and begins a 30-day transition with layoffs - CPG Click Petróleo e Gás</t>
+          <t>DHL to operate Waitrose’s first South West distribution centre - Logistics Manager</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 13:42:00 GMT</t>
+          <t>Fri, 09 Jan 2026 17:26:00 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNQzdjMjlnMzJoc0sxUjNJaldocXdlUmc2Ymd6REFiUkpLQnYwczV5MXBOZE9Ddm9QYTB2V2oxS2Q2S2xidjNmcGwzb2p5c1JJYlVPTnJOSlVNUGlWeG5jRkZaOEpwbmxOXzBoSUpmc3kxY1h6MWtEellPTEFfZGhVdjlWWl8xdlJmb1U0VHF2aXlvMVhwUTZmcFRFSU1XSVQta09nR1p1MWVLVi03MVBFeDc3Y0lsQkJJcThDN2NtQS1TUkVXSkVZN1JzYkwyY21ONksxMGxmcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOOVJfWnlVYlRXbHlQVUhlMk1ZQVU4RVlGb2xqdzhlaWY3ay0zeXQzQzFScG5VRmJvbTNrZ2xVMlJQbjVnTEFZVWVHalpndE9DM1dTaFNGaDc3MUxsNTN2STZObl9BQnRYbzRMWVYxdXlKbEdoSmdWZTZUc3dnTm91YVE4QlEzQ2lTY0ROc1JQZ2VtZk1TdmZvWDA4cw?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46031.57083333333</v>
+        <v>46031.72638888889</v>
       </c>
     </row>
     <row r="20">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>‘Wholly insufficient to address serious and ongoing problems’: Objectors raise concerns over delivery office car park plans - Suffolk News</t>
+          <t>What DHL Supply Chain has gained with its new returns network - Supply Chain Dive</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 11:54:00 GMT</t>
+          <t>Fri, 09 Jan 2026 16:17:28 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQTENjOFZqc3QzTFhnb3pmUWl3Rk56TVpIa19VZ0x5U3ZYUDcxejUwQjZBbTVfUS1sUjVNSVpBam9jS3ZjbVlzcGx1bkZmUEdjcnU3OC1xRFk2MkkzdWNURHZzMk9fQ0IzeFpxVi1FakkxLUU0SnJ0YnR1a1hic2l5aDEtUm1YTXRjLXFBU0tvb2FuUnplcmNtVnRoalZmNUhtT2ZoTWJfYlBWXzNncXFpMFVqdVJCMTJGc1NV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQTldBMndJRlhlMFRQdGl2WjFaY0VCM2FVcndiYTNCdWlvNkV1YTRCRXBhb0FHdElUTFo4OG4tdUl1TlM0UkFwMFl3cl9JRlcyM1hMMklScll1TnZIWHlXakZKSko4eVRVMUZoR1dwMG5PYW1EeGdKU3RFdXpiOVRHMFEteVNMX2ZULWwzbzEtV0M2UQ?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46031.49583333333</v>
+        <v>46031.6787962963</v>
       </c>
     </row>
     <row r="21">
@@ -1109,24 +1109,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Windows 'completely cleared' of condensation with 'fast working' £10 Amazon gadget - Wales Online</t>
+          <t>Amazon pharmacy to begin offering home delivery for Novo Nordisk’s Wegovy pill - Sherwood News</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 12:28:00 GMT</t>
+          <t>Fri, 09 Jan 2026 15:35:04 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPeWc2SWM3NS11REVZUl9iRUotaFJYeHpmbVE2cWhyeXlXR0NiWDN2VkRsQi1CTE5fTVlDTHFVeUNuSUZCUE1ORHlGVmZZSWtiX05pdVRwZ1p5WlJmcHFES2IxTjFwX1FQYmVCMkZXRTBsZlJkTHpFZDk0a0ZYbVRNSk9OdVhiSW94Q0ljTm5VS1VueW5HdUo3M0VyYkxGYXlDNnhz0gGoAUFVX3lxTE1OX1FWWXgzam04WmMwN3RvTVN1RFlDTmNYN1VmaFBJQjIwOVpPZENzZDN2VDJZQi1zNXl6X2V4NzdPMFhkX1BLYWh5cy01MElfNHFBMmtEYmJaV09JYWJTS2xheGdXSlRsWVNXY0dnV3BEMFo2Mk9uLURKUVJLblItUUh5dU0wQ2d4eTZsNDFpZFhqYWhvUjZzME5SRmdiNlhzLUZWNmx0Nw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNODd6WU1tbmR2REFXSExVQV9nelBLb01rVmRwMU9ldGlZVkVxZUEzMnFmdTRfa0NTQkFCZ1l2bUFRZmE2TF9hQmJMMzlqdjdiWHo2cmYxM0x6TzVOclM3MzMzaE9yWlBTNktXd3I4NU5hbEZWQ3c2SFZfenoxdnJaMFl0LVNZVWwzMkp4LXVaTDBGejcyZHE5aVpydDlRUURfdFdCSi1B?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46031.51944444444</v>
+        <v>46031.64935185185</v>
       </c>
     </row>
     <row r="22">
@@ -1142,24 +1142,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>How to still get up to $51 from the Amazon Prime settlement in 2025 - Yahoo Finance Singapore</t>
+          <t>Amazon’s Drone Delivery Paradox: Green Light in UK, Red Flag in Italy - DroneXL.co</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 13:01:21 GMT</t>
+          <t>Fri, 09 Jan 2026 21:37:24 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOTXNOMFRCVmt6aGVVUUx0Rzd2RmZ6RVAtZUw4dzctNU4yZm1VVVFCNVlsUUE4WnR6QWVpOS1DX0RVVXNSUlRQZjJOWmFrMFJOZ0NMVkFBbXFvc0dEa3pmYklQWGxBcFNlMHc2TDRfeWZ3U2k2MkJsYWRmUzFWV29rRi0zb0pWNW45?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5RbjBDeWZJdzdjcHJEdlRDUTNSTVd6UWdPUkxrVy05OFcwMVRsVllVRjl0Y1N4RnE5cHlodE9wZ3FDOExhR2FGTDI1Yl8zd1l5aFNlMDdyajY4LXA1SnBHMUI3Vzh3RWRYYTJqSXgwQ3dJNjA1TWVPcmpn?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46031.54260416667</v>
+        <v>46031.90097222223</v>
       </c>
     </row>
     <row r="23">
@@ -1175,24 +1175,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Amazon Has a 16-Drawer Plastic Organizer on Sale for $20 That’s Perfect for Decluttering - parade.com</t>
+          <t>FedEx Corp.: How a Legacy Logistics Giant Is Rebuilding the Next?Gen Delivery Machine - AD HOC NEWS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 13:02:00 GMT</t>
+          <t>Sat, 10 Jan 2026 06:46:02 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPV2Uzb2V4cVBKVEE0MzZ4RVppLWw1Z1R6Wk5xTXBWS2k0QV9sVkxXcmdrUEZacGZtZHQtTS1DTmVSQ2RwOFRQenFLRG9HdFFoRzN1S2pNQy1wOUFyOVBmbDRzbThKRVNSMmVFa1lsclhsTlFBUnpvZEpfTUZPTndCWHRsdGdnQk5HNVFGMGVSRnY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcnVxMkR5UkR4TDVjREVMUEM4QlNqSDRPcHJHU0ZORHF5dmhqRHpseWdEaVZCV285TDV4emRDUG41YmRfc20yRjRRZmRBVGhjQ0lNMFg4dUI1Smh2N3J2N3pKUHkzOFE4Qm5jWWlfYVlvTkdETFRTekZhNHlIRXhEd3J1dHBzSkpBMXJBMDJhLWVIcTNiYkIxWVdoeGZtOWlxeVNTOE1IMkk0bHE3bWQwMWQwNFBGUU40cmVDS09ISWlBbnM?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46031.54305555556</v>
+        <v>46032.28196759259</v>
       </c>
     </row>
     <row r="24">
@@ -1208,1641 +1208,4413 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DHL Wraps Up 1 MSF Facility in Pennsylvania - CommercialSearch</t>
+          <t>Connected Grocer Shopping Carts - Trend Hunter</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 12:48:29 GMT</t>
+          <t>Fri, 09 Jan 2026 14:41:53 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOdll3NDdidDNRR2RudGxxTEl5bXhuVzlMMWFhc0ZWZWx4VWE2SzB1OEctM1NaRThfWVoyRGxLTGlYUklKZjB6YU84Rm9pdk5qTllBVGdnT0ZYSWlJZXA5dVZKRXVYZGR1VUMwQV9fR0E3Yy1CUHdma0lpWGNqbmdLSHF6SDJDSkVmUGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE8wdi1WU2RnLUxjNWo5TFRTdk1Cd3hSOWF6M2xOejg3cnpYZUtaeHotbGtQbG55cTZjOTg3Um9jSFdzT3lWVTQ3QmplUkZ0WkhnUnhpSkhnVDh5c1d3a3E5TmJ4R29ETGVJN2JB0gFrQVVfeXFMTzB2LVZTZGctTGM1ajlMVFN2TUJ3eFI5YXozbE56ODdyelhlS1p4ei1sa1BsbnlxNmM5ODdSb2NIV3NPeVZVNDdCamVSRnRaSGdSeGlKSGdUOHlzV3drcTlOYnhHb0RMZUk3YkE?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46031.53366898148</v>
+        <v>46031.61241898148</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kentucky State University Campus Shooter Kills 1 Person, Another Critically Wounded - AOL.com</t>
+          <t>Amazon delivery center in Weatherford to bring faster delivery for rural communities - MSN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 09:35:51 GMT</t>
+          <t>Fri, 09 Jan 2026 22:01:46 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPNllmOTlWRkZtWWtPcWZ4VG9ieE1wdGJnTlhuYkg1US1QWUJJY214ODZfMVhKV0JKS1RkNnV5X051ZnhLSndLMlJjV1d3UzRQczB6Z2hqbnBBRlJWWHBRNjFRTjJXNHR5T2ZBdVJpVkFMSTRqb0xxUEtnalZoeDNEaExKY05CbVE1dDZwZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gJBVV95cUxOQjRhZUdVZ1F6akt3dzhFTFhacU53aVpYMkpfRU5MU2pBd2hvXzMyeHRyaUM2a0RJYW9CZVltSkNvWDdjMmF2bEN0Wlc2MFZkaGpJQ1lWUjF1SFR1M21pZ0V6V0hPcl9jOHRXM2E5N2lyR2xBTWVuT3VIdVp2NGFYT2VMSmk3cm5TV2dudUl6blBZRVNmb2JoSDRYcnloY1RtOXFtQjdfOXF0dy1sSE1PWmtCWmRYZ3VzaE1hS2RfajFxYjlGYXZlczVQR3p3SFowa1puQlZlYzhmOHI1cEJWTGNqVjlRZk9pRTNNbXp6LWVsdzlqanFaUy1UM3ROTTRXdGx5M3FhdkpYWG51WGZqNmNyLTdOVXRrYWNKeWJWdmc2b0x0VjN4MTRVQ1Z3OEY4ZTBiakpOM1I2YmFZUUhDajFyOUlQcEFyRDAtTEVkcE1OMVFPU2RqUXllUVBMbFd5V21vS3pHU2ZFUQ?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46031.39989583333</v>
+        <v>46031.91789351852</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bundesliga Matchday 16 Full Schedule: Kick-off Times, Key Fixtures, How to Watch - KnowInsiders</t>
+          <t>Last Call: $250 Amazon Prime Visa Bonus Ending Soon - CNBC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 12:57:22 GMT</t>
+          <t>Sat, 10 Jan 2026 06:19:56 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPai1UUXZ3dHBtOXExblhrNGEwaEVkYkpaZWVIekEtUXpib3hvc0VtMWh3WmFWemdfTDRaUDVUemtBTW1WaHQtM2JUOXFkbTIzNEhOdm5SMkVlTk5FckZ4VXFyNGhncmVSQkhoMU9VTmV4TS11WTd4aUdLb24zdzI2Wk5vdXh5bWtGbFZMOGpWYXRLWmZBcU9zMUswMkdPM0xoaHliUTV2dXFRdXNGM1ZVLTFMaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE81c2twamlkQlk4R1BXSzJCUXJOZW9hSHc4Z0xyWW1sdVZtQjNFZ2V1eFQ2WW5nR01QNU1LNE9reGlsV1k4S2Mxbl9zeWlreUI4YXpxTUxrWXJPMEczSVVMT3loQmozY0Rzdzk1bXZ6UElvTklEX2NBdjMzNWdocmM?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46031.53983796296</v>
+        <v>46032.26384259259</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Theft at North Carolina vape shop under investigation - WYFF News 4</t>
+          <t>DHL Express India Offers Festive Discounts on International Shipments - Machine Maker</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 13:54:00 GMT</t>
+          <t>Sat, 10 Jan 2026 04:14:05 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOa2Z1bjYya2dldWdZa0I3SWRqSVhKdFVhSjlWX3ZPcUwyMjZkZU13Yk1FQmpGZHRvR0dGNU5HUnN6THo4SmVjNzlkV1lrYW5ha1l6SmoxMDd6c2FBQW5kSkVXUFRYejhtU21LVnZQMUdJWHNDeksydjAxRDBsVVVhWW9sWGN6dDRXRlVjSWlkUjl2bDM0X1JR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOdUZvVG1yUGFvQ25VRHlLTE5va1B1R3dmRzVlYmp4T3JBMWR6ZGswMUptSXIzaER2SkE5NlMzM0p0bERZQUpNVjZNTFU1TURRTEkzVmVOMUJyaHdvejduWW95czZHTEZjSm4zOXNYbFZEOE1vZXhQWjY4VUI3QWxQLVhTSnlKRDU3X3Q4NlFidUpheGNVM0hRRm1uR09tU091YVZZQjN3?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46031.57916666667</v>
+        <v>46032.17644675926</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>The Biggest News in Loss Prevention: Jan. 3 – 9 - Loss Prevention Magazine</t>
+          <t>UPS to close or trim operations at 4 locations in ongoing network shakeup - Supply Chain Dive</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 11:36:01 GMT</t>
+          <t>Fri, 09 Jan 2026 22:17:29 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOZUtLc1pOeFJNTzUtWVotdDJicDBsb0tOeXRqSkdqcElPa25felJVVlBZbTFNSUM0Vlh4dnlsTUJqeXRqQkZOeE9aWFpIV0g0aXlxNjl4X25Zc3pqZjZSbUp5ZnBtUDR0b0RrYWN2T04tRnZxdXZqM1I5NV8yZHZIcUhBWXc2d2R5U3fSAYoBQVVfeXFMTmVLS3NaTnhSTU81LVlaLXQyYnAwbG9LTnl0akpHanBJT2tuX3pSVVZQWW0xTUlDNFZYeHZ5bE1Canl0akJGTnhPWlhaSFdINGl5cTY5eF9uWXN6amY2Um1KeWZwbVA0dG9Ea2Fjdk9OLUZ2cXV2ajNSOTVfMmR2SHFIQVl3NndkeVN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxON19LdDJPZ0JTWlhnSWxpNjJaYXprRXZEcVM2X3p2ZUxpOWZzMHNuYko5VHJxRmFFNzI1OThpeEZKX0UzUko4VEFtQVdWOEJ4Q29DTE5UNG5mUTRkZndGZ2RDTFQyXy1YRUpFTHpGLUhScHczcHQ1bVh1elJIR3BFdmZWOFVVTm8?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46031.48334490741</v>
+        <v>46031.92880787037</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dozens arrested, over $6K in stolen items recovered in holiday retail safety blitz - CityNews Kitchener</t>
+          <t>Amazon Rolling Out These Major Changes In 2026 - dailyvoice.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 09:07:15 GMT</t>
+          <t>Sat, 10 Jan 2026 04:02:26 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNTEItQ1M5NDUyR2ZoQmUwOHNJYVM4WVJFdG9zLW11aUczZVpJNWxNNmd3bjF5dGdtSmYxcTA1dTlYZGVTdW1GZFdGUXBWdnpMTEJpZnhuc1pkcEhtRW01WV82SVhUcnlrdDJ5SldGNXVmdlA1VHhwUHJ5amd6UUJ2UDdNYmNsMkx3dU9WdVFYYWdxN3NHOXRjcXlVVDNtajA3QkJfWmJOOVBDdUdaOE1tY1JkZ0x3b3NnSjZBRWUxVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQWU9YYmdnUkdnR3lPODlpcEwtekRIbWFRSVpoZ3AzWVV5VVZkRzduOGtYY2hHdHR3VjVuZGRiYzlsQXpEbTJmSkZ4aGQ2VEQ2ck8ydS1tU2V3VjkwOF9OUXFFR1N3YVAzSWI4dmpOSjVPQUh1eEdXMnMtTV9TY0dDdU1weUVEa0FJWDUwNFJObjczSFlW?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46031.38003472222</v>
+        <v>46032.16835648148</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cops in Chicago area recover $500,000 of stolen protein powder - Truckers News</t>
+          <t>USPS &amp; UPS Renew Delivery Deal for Ground Saver Packages - News and Statistics - IndexBox</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 10:30:01 GMT</t>
+          <t>Sat, 10 Jan 2026 00:32:00 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQaDVFT1YzQUx0RF85ZmFhUW4xNWdUeXh1SlNfRklVYWFRREVQOHlxZEN0R0IwYnJERUNGVEwxQWJBc3JOWTZycDJVWmZRYUp1bzE1NVREU29MR2RPUHZqaUJZNjM1UDNzUE1tZHhUbno1d2JiUXlJQzMxTHVyZ19WbE9nbGJ5UkJuTkZmNTN0bk5ybGVTUlY3cTluX1hJaUI3ZHhKUGdIU1FhSjYwdng4dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNYmNEM3hrd2FYLXh4V2Jua2dCSTVjNk50T1RxUlhLX0JwdGtaTVNGNTlhdnlHdWM1Ny1QU1JfbUgzSEJpaVNhZk1yd21KYnhYSXVMbXZrSHBwcFY3MV9EclFjeGM3WGJLYTZjeHU2U29nZDlLV2pPVm9iOVJtWTN3NkVTeDVaVE1reFNOMnBtS1RFSm9xakdQM0d6a3dRYUtj?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46031.43751157408</v>
+        <v>46032.02222222222</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Xabi Alonso insists Diego Simeone 'crossed the line' in explosive Vinicius Jr row - The Mirror</t>
+          <t>New attempted murder charges for suspect in Ellerbe Amazon driver shooting - WSOC TV</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 09:37:00 GMT</t>
+          <t>Fri, 09 Jan 2026 17:24:42 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQeVJzN21YMnBIeUN5eWhjWHY1LTJ6M24zWFFSamJDallTM0VZZU52Zm9FblRJY2gzQnNVU0FMNHhkdUg1Wm5xTHZVMHdJMEhyZktTR2xXcGRyeEY1c1BGMVU2UV9XUGRvMVhTSG1BQ0UxUlo5ME1ZQUpPdGMtLVFyaENrcG5wNWdtQm1hTGVfaUxLcGfSAZgBQVVfeXFMTXJfR1V0UVZIcktiWUVmU2NQZU9HQl9rMUJ1Ukg5YkIwbFA1RDlBbVVxdTR6NC14djk3ZG00ek0yMWh0WWFIN01vbHA4TXVxcFpMTWM0VnRMV0QyRHRXMzlpMHhIUnFwQ0hGTjM0SkRKNlU0cnkyQkhjQmlhWFRVNXJtZUdJLVg5UkpKUEFOcThFRXBiNU1CZkU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNS2p6QXZaMGJwajlWcXBObFhFSHlzWXpzajhoTnJjN3BLOXlOU21STmpFYkJqcG9aWkhWSUtiY0NTUmtYMHpycmFTb0ZsUlJsaDZBZENfb0dtck92eVRKTHIxTVlwenBkdnVRaVlpSGpyVnFiM3JoMnZtaC1uN3JQNUZoSjlxWndoaG9zdllGT2hjV3hoeWRha2FnVHR5LWVjN29XZkozRkQ0TTJwUWNiYUVQNU5OYnREdEsyTld6OUd1d2dOTy0xaNIB3AFBVV95cUxORjhFanJaRUdHaVpWQ3Y0LU5TdVY3bXRxTllyVE9fOTNza0t6YTR0cVZrZExQRGhSREVvZ1hrNmlweHR3cDNxOFlYWmQwQWMyTGlPNkYxeE5YODBnaDJoZFhGbDB3YUFIbkNuUXhpUmJNZnBuNl8zbnJqUjJCeVZTRkpYN3hDamxkN1R5d2lHRlJTa0Q1TkJUT0M4ajJJRFhQUHZLd1hLX2ZpYlNuTzlLVkpOQWZRUHBTWXdKdWNCTHMxSTB4dTlyc2RZNkszNXRPaVY2dGV3Tm44WXlk?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46031.40069444444</v>
+        <v>46031.72548611111</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Storm Goretti ‘weather bomb’ set to hit Spain: Affected areas and what to expect - Euro Weekly News</t>
+          <t>Amazon Mass Layoffs to Hit This Month - Newsweek</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 09:28:42 GMT</t>
+          <t>Fri, 09 Jan 2026 15:54:00 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQam4zdW9sZERGZXpPZ3FMM2hDN2FLSXF4TTBtY1FtUmZZYldMU0M2cHZxcnJXVEN4VHg1c0M2SlFWTW9kUlVoTHRWazhxaUt6OGJUQXc5VllNMHVTanV1SlBHTVhRWWxWVkJpd05acDNMc3YzVXpWek5LRWNVbnFzclJUZFBPbzJCYjl0NkZYT01vbVAtRTN3TnZ5VG82eFNfRW9IbFpyRkhBQ094TzBjbWl1a2x1ODA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE91bmkzNGFzanlJVGxnM1Bya2J1dnRQZERJMm9BU05aaU9QeTd0SDlVSU1iZGdqbFl2SlBpdWhoVVcxWnBCSVU2RVQ2cUpOZEtoWnJ5S2x0WVJsZEYyY1NnUHVRRVNHNTVfUndNdmpSX1dWaEw0N2tQVFBSUQ?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46031.39493055556</v>
+        <v>46031.6625</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Investigation under way after Portland shooting involving federal agents - Latest news from Azerbaijan</t>
+          <t>Tong Road Delivery Office to close - West Leeds Dispatch</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 13:16:34 GMT</t>
+          <t>Fri, 09 Jan 2026 16:45:34 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNMk9yUVBaWm1jSjRZNWUwV20zeVpFenR1c1BBQlQ4bUVqRlBfaGFMa2FndXNXWHcwanZHeFZTb1RsNUJoRjZuWDFwYU9wQmRDUUNTWTZkc3VOSlVCSHJqUGZYbVdKY1VKRHVBS1ZqNlA0MHhNbGFQeUFGRDNMbUdlcmlCN3dfN3d5a0laYWowWldqZlBWNzkwbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5GVkNoWFRPRnJLS3hUX29HWnZfTE5fYjMtMmVjdkhvWmg2MnZmMzVHMVFWcVlwOW1KLUN3VUxRTEFhV295MlpaekJhcl80cFpJektmUWl1bW01YmFabXA4d18yaUdxTkVUaXpIUlNPZnlwZXM?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46031.5531712963</v>
+        <v>46031.69831018519</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Freeman leads Syracuse against Pittsburgh after 27-point game - FOX Sports</t>
+          <t>Amazon to pay nearly $4M to DC in lawsuit over driver tips misuse - MSN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 09:43:56 GMT</t>
+          <t>Sat, 10 Jan 2026 02:16:17 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOdDVMQ25SMTJmYnlyVVMtUlJCN1dCSnVpbXhUSTZOY2lna2o4ZERDOFg5eUJXTFNYbUVSYmRoT1NOSTRTZVgyWENUTFotUU5fMFdBUWtpcjZYOVc5cjFDNnVlNENBUWczY2hDSFd6dU9ENW83TWdnOEF0UzEwcVJXWVk2WnFPYjFfNGRIMUw3Mk1oWVo4Q2ltT1I1N3luaXE1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygJBVV95cUxPMGFDQ1Ftd2N6Tml2ZXdtS0VHMHo3VXlwa1lDZktaSGt4WWtFX1FlZlN4TS1hR3ZKV3RKR24tTTlRd1Z3UXdTVGRVMzdQX1dDUlRsa1JWMXJGV3FFdF80dE9sUC1LMGIyS3FIME0yMktRbzItblJxbjBXNTFqZnh5MUVicms2NERSNVFjV01YS2laZWtaVFlVSnNkRlN6bXpqS01lV2RWT1ZJR1FURnBYMmFKdWh3MTN2b1RMenhyVU1CTl9TRkFYRmpvT2hma1FzY0JsalBfMndqVC1xQ2JXcEJJa25pQ25MTEdlbFh4aTNOUEJJT1FqalFVNTVqSGp0ZXE4VENqZzhFS3R5MVdiZzNUOXJzdXJ1N0dhZk9URkc5SkN1TmoyOVNzcWk4VUR1el9ZTUx3VUJuWkx6c29JdGhPQkkyY1hIREE?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46031.40550925926</v>
+        <v>46032.0946412037</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Florida State hosts NC State after Williams' 22-point game - FOX Sports</t>
+          <t>Major bank tells customers to ignore text from 'Royal Mail' for important reason - Birmingham Live</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 09:43:56 GMT</t>
+          <t>Fri, 09 Jan 2026 15:29:00 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNSE9MZ3U4M0N3cGVnSlRqdGMxdi0wYWxNS29DSF9vZFlwWTd6ZzNWZXQwc091TzB3N0FUVG80VG11S3daV19BRTRrY1lCQUxBczBrVUNpM0VIUGIwamRwRlpZQXJRTG5SS2VQcXRUcENrYjNPdUJXRFE1bUZla09LOWNieXBpay0wN0JVQ3BISGNMd09sYUxhejRCMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNQ0tDemV2ajVQVDFveEowSXA5MTkwc3E2OGZxNllIdU5XZ2hzNkpsVG1PbkZNX2NJdG1WMTFaRkJLTTZsaVhlMGVBTkFpMkZlOUVBU2gxYkN0UWx6RzJRVWVRbkVZeTVwdnVxMTVYZXRqc2x2d0V2Z0NiQXFRcXo0TUtWMVEzTjFiZHZUV0FJZzd1RVBs0gGUAUFVX3lxTE1DS0N6ZXZqNVBUMW94SjBJcDkxOTBzcTY4ZnE2WUh1TldnaHM2SmxUbU9uRk1fY0l0bVYxMVpGQktNNmxpWGUwZUFOQWkyRmU5RUFTaDFiQ3RRbHpHMlFVZVFuRVl5NXB2dXExNVhldGpzbHZ3RXZnQ2JBcVFxejRNS1YxUTNOMWJkdlRXQUlnN3VFUGw?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46031.40550925926</v>
+        <v>46031.64513888889</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Village Search Bicester and Kildare</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plans for 400 acre history-themed resort near Oxford - MSN</t>
+          <t>FedEx Boosts Holiday Shipping Convenience with Expanded FedEx Authorized ShipCenters Network - FedEx newsroom</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 12:13:43 GMT</t>
+          <t>Fri, 09 Jan 2026 15:58:21 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAJBVV95cUxPQWsyWS1oWlhoWXVCSnVVMlF6R2NfWm5tT2ZHclgyRjJ2bU5FWjl2LTN6WUd2VF9XNVpoVEpVeHJneVN0bUI5OHp4R2xGNmdpQS1DSUNvbnZjdHFlSDNpQzgzWUVibXQ2ZEYzYTVDNU9lYWNrN2lycFJQSFVaYUVid0JBVUNrZHJSODJwODNvSVJvVmpzLUJvVllOZHVJYkpweW1PX0dpajdxWkNMd0pRZVI0ZFlINVA2QXo3TFpmcDRWME5IeHpwWHlSQWNIenN0T0p3T09aSDR4SDZxcmNoVWt0b1RNQWd6MWhmYW1pWlcyRHNBVlFjQVpWRkNNaW5LZUJOdlFjOUgzc2hxZmFiOGttcGx3RGlraWo0RmRTUkh2eDZpMDRXRGdnbWRWTFVaVzB3ZUg0RDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPXzk2RmNXQ0dOSjFlWndpYXEzTk5TeTlxbUxXNEVrcWU0Sm9pb2VhX1VLRGV4NXdmUTEzODRnaS1uY3lvNGt4aGVKeDNIajFCdjQ3WlNjNkpTeW5zMEJLX2hfWmNZSV9EWnVPVXVrMzVOYi1jOWpoMGlDMnVYaDJ1ejIwcmxkV3M5Y1ZrUERNMlE0N29UdUVkaURySnRpc3BrUVRDbXFXUjJUblBHWTl5anlPM0FvelBfSHZz?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46031.50952546296</v>
+        <v>46031.66552083333</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Police update after man shot 'outside bar' in Bexleyheath - london-now.co.uk</t>
+          <t>New charges filed against Richmond County man accused of shooting at Amazon driver and son - Queen City News</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 12:29:51 GMT</t>
+          <t>Fri, 09 Jan 2026 17:41:36 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNemIxcEJza3RDZkx2OGZIUnhRTGZrMWFBTFJkci03U09qczFuaTdweFJPbHhmVDZvejhnX0pwbHBKaTliTy1fbS0xUU04QkJCWTE2Z0IxblhsYTZVTXFqWnA5QURNQk9mSTVTSVExdVV2cHhXZl9PRmJYLTgxSGNxRUgwY2Uzd01OTk13dkNIUnh5dHZkWUhHUzNGbXZNWXo4Wl9jTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOTkJUSGo3b1AxZVFCVjZDTUVtc3g4MjBiUHJzUC1pNVBoZFlpaU1wcTdTVFF1bGczeVVJXzAyWF9aSDFhRVZkbG1OQkRBV2c5dHJjbDNjeXdNQVMxUnZUdHY4aXhOUzBzM2p1ZFV4X01wWWlSQ1VWNThrOUtMSm0wNnU1T2ZOamhCeWpybFZYNGx5RkNmRGxpZWN1UGNFY3pES0Q0dDZHTWdlMXNNbEs0MXBYUjJrOWlVSHNrS3dsOGs3d1NNRERfUTB2VVRQcGswZDFPQnZGbjF4Y3lqX3Zmc3VHYjNrUE5xTkE?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46031.52072916667</v>
+        <v>46031.73722222223</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US immigration agents wound two people in Oregon shooting - london-now.co.uk</t>
+          <t>Amazon steals Walmart’s playbook with massive big-box store near Chicago - Cryptopolitan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 10:28:33 GMT</t>
+          <t>Sat, 10 Jan 2026 05:04:00 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxONnRxZEg5Sjc1XzZ1TlNPWDZPN3l5SGtuck51cmZKVm45MkpkVjhpdzhBSXdoWmNfcFJKQ3dwNGpTRHJHZW9US0d3RnFRWmNuSl92VzdXVjRTZTRacVBZOU50M1NmTUktN3pnRnFUUm5EbVVOdjBXTXJDYWNoM1pZY0U2ZlloNXJGaUhxY3Z2YXYtUk5vX0xMN3JOVGpMdUg3YkdOamFiVnZGVkU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQUkRfa050VXN3TkVGQS1DUEFkc2pCUDBSWmZ6WmJmb1Brc2swanRaRXhLOGN3Yjl6SHBNaXBuN2xSS0JSTGlsaWFZcTNENmlSOW8tRDlnVG93bk9kVjFzdGVuLWVXSnBMdmhpWHlZdzRSX1c3bC1FNWJqa2JRaS1wU3VHS3FCWTZ0YzBMc0hOUGQyODdwbFVyQmRJc0VPZjNtMEoteA?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46031.43649305555</v>
+        <v>46032.21111111111</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Two passengers suffer broken ankles as turbulence rocks BA flight to London - London Evening Standard</t>
+          <t>10 Amazon Prime Perks You’re Paying For But Probably Not Using - AOL.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 08:35:52 GMT</t>
+          <t>Fri, 09 Jan 2026 23:41:11 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOSm1oNzQwcUVDLS0tSWFoU1h6NEsydlcteHhiU1o5elBjM1psWDRaN0phVklmMUZESDhhTzJhYmVjXzZaUm9VemVFdEtBMUZjM2JBRGtQcmpuSWsxd1A2eG5HRW1lY2Y3QktCMHZ2U21sNS0yd2VlMHVEVnFrb1dpUUkwQ0FQdU15LVFHX294aFRQekJtNGRMU1hlbVQxbG1ya1dpblZTeUZBTjc4b1lLVlQxb1FfY2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1xRUljWVVQMDBoZFJMSWxRakZmbU52U1ZNVFNRWEZfZWdyLW9la25Ic3FUMHlRaTlZVW5BbElBMTNrUUV2b29ib05JRjlWN2MtQUQ5b1czazFuRFBCZDZrQ0t3UGI3YjFFUjJicmpuRWtRTlJYdlhTME1BeU8?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46031.35824074074</v>
+        <v>46031.98693287037</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bomb Hoax Conviction: 95 Calls, 12 Months, No Borders - Lawyer Monthly</t>
+          <t>Is Amazon Stock a Buy for 2026? - AOL.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 08:47:23 GMT</t>
+          <t>Fri, 09 Jan 2026 23:23:49 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQSFRFUXRJZ3p4Nm5NZWlMQUwyaXlzQzAyRHk0VHFBY2VuQzVTRHdNTlAyTWhrQUI4YzVIQkJrbDJMMGV3TWZjSmVIVzFxZHUwdXE1MzZnVGlsMU44bHRiclJ1Smx6RXh1WjA5LWRCcVBmMm1hNV85ZTJYOTc3RGxFMHI4bzZqWGRtaVZDRHJQbkVxR1Ru?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE40Z2JSZG1ob0JQbFFxa2t1ZjV1d2lQSmRxNzRCQ2tuemtNUHhpVUFRN1VmNjMwTzh5d3RiOG5RZ3piUDE1VU41NzVFR1o3NVBXd0QzWU10QVpaZlJnWEEyZVVTb1pMUGpPSUIzZzZJMzF3Wms?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46031.36623842592</v>
+        <v>46031.97487268518</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US immigration agency under srutiny after shooting: What is ICE ? - France 24</t>
+          <t>UPS vs. FedEx: The better long-term play? - MSN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 09:46:57 GMT</t>
+          <t>Fri, 09 Jan 2026 15:57:18 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNZ1NyNEs5YTM4X2szQ3g2bG0wdXVOSGZLNjFfdnZOR3l0R2d6ZGQ1T1hkT09ZZ0hjZllJMnh0NGNfT0RiUmZMZHBSRXR5SHJUWUdENVJ4clhvRlJTUG1USjVMQjJaMVY4QlNZOFpSUy1hcHpzUjBxOE83cWtSYnBOTmZ2OXBJc1FqTDhWdEM2YkFPSmdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQbVZUZXZnR2hJX012S3ZFSWxkdUlLTnNGdzlQWUI4TXRUSHJzNXA1Z2ZfRVdTUERfQm9RYkNRTkFrcTFSZUpWcGt6WVFsajN6SVM1NEZldThtVm90MllhRUctR1JHRFpDZDJldFhNUENNT21uWmNlZDIteUo0dl9EcHdQb0tBQW11ZWlmNklsRUhuOGhCSy16cmFFTkRuTHpqNllNYWNtQ0h6QmhTd0ZMeW1TSkU1Y0U?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46031.40760416666</v>
+        <v>46031.66479166667</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France Farmers DEFY Macron: Paris ‘Burns’ As Tractors Roll Into Capital, Parliament ‘STORMED’ - Times of India</t>
+          <t>Motorcyclist injured after crash with Amazon van in Sun Valley - NBC Los Angeles</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 10:59:05 GMT</t>
+          <t>Sat, 10 Jan 2026 02:58:12 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxNS1ZiMHhnUGRnOWJFRmNJMy10RnN6WlBqa28tWFVtMUV5ZTZ1aFBseUJmTUE2UnM1cFdabnhXOGMwb0FVQmgwV19QcHdOQ0JIN1lCcUZESENBSWpYa21EMS1IQUNCeHJPaURNVFp1Ti00UFBxYVczZHdTRlRmdkVNNmRLVDhWbTVtMFJiM05DZkc1UFIteGM4T0hnbjFtNVUwX3dfTjNXV0FUMU55eGFRTjlzWEwxMmlMS190YlFqcGlnYmJGZ1BDZkpsVGFQY2ozRUc3UFRyVFZSRzF4ek5SR0tGeXV2MTVHZEpXanhZakprYUxfMDFWY3ZET0jSAYICQVVfeXFMT1ZwUVlzbjZxSDg0WWlDalp2RlBmNl9MQUpwSVI3UmdMQjFMbTkzZDl1b3lZSU83QmhTb1gtSlM5RHU2WUdFZ1FTN1R6Yk5oS2I1dDNhWGtLalZBdWY1RTkxOGZ4NXlYYWRkVHV6dGh6M0VaNmIweWZQeTBSMXctbVpWclhyNjdmQndHVHRVQ2FSNVMtRWZzUVpzbi1FZ3lDUHdWSjhTS0RmVnJNUEhjU2JaYnM3UEY5cFBnOUU0djBYYXptdEJoMmFOQUMtVjRETDgyYXpSb2F1LXF0RzByQkU4dUVFX2VKWnN6Um5HUm9XWW5vM3RNVmpKbGtmNEpYWUVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPYnRUMVU5aUNYbjJYajhPeDJkazV4RnRaaW9RcHdrc3VTcDIxZHgtOUR1UG4tQ3o2V2p2eDdTMFZUWF9Uckk4NW5ITjZTOW1uWVVKY2tGcnRqOFhiTHhwYXYwLXcwQjliZjFlNEZ0ckFGRm5CY0lILXd6eklTZkZRS0NMNkp3aXBTQ1RLNVptSDZIa0FlaUVfVE5EeG4yeTlUVWZrQU5YWk56VmM0eUoxN3F4T085X180REHSAboBQVVfeXFMT2J0VDFVOWlDWG4yWGo4T3gyZGs1eEZ0WmlvUXB3a3N1U3AyMWR4LTlEdVBuLUN6Nldqdng3UzBWVFhfVHJJODVuSE42UzltbllVSmNrRnJ0ajhYYkx4cGF2MC13MEI5YmYxZTRGdHJBRkZuQmNJSC13enpJU2ZGUUtDTDZKd2lwU0NUSzVabUg2SGtBZWlFX1RORHhuMnk5VFVma0FOWFpOelZjNHlKMTdxeE9POV9fNERB?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46031.45769675926</v>
+        <v>46032.12375</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lily Collins shows off incredible designer shoe collection in BTS clip from Emily in Paris set - MSN</t>
+          <t>Amazon Formalizes Performance Reviews with New Accomplishment-Based Forte Process - scanx.trade</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 09:26:53 GMT</t>
+          <t>Fri, 09 Jan 2026 18:07:55 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOWWl4aWJ3eXg1SEZCNlNpMlBSdV9kRGpjd0VPOTJrNDBlbi12TW8wZGZydk94MmsxMnRIdXBkTUR2TXVVSHpWV21QS0tHcDF6QVl4bjZ3ZVNQZlFEbzFqdTVHRVV2am43NmFoaVJvQVhrYjRkSWY0ZWhPU2Q1ZjVQUHhNUmFKSTl3dlJmUGE2SjRHaGxLTmZfbDlVeHhaeVVNSUtSMzhFWDRmdDVDZTNzcngzU3RwNy16UERrR3Ewc05JV29DQ29VTE8yQ1BXbkZLV0dfNm8xeGtFQUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQMVQxUnN0RzN6OWJDWEg2WXdmSk5wY3VlekpEak1Vb29Mc1hwZUh4YUVkWTFkSC1CcW9vcTVuZXlJLTBFVHZ5b2hnVUczdVEwSXg1bXV3Vm1EZXEtckJtVHVEZDAzSVRlRHhSWHNOdWx1UlNwSDg2d1VodC1NRENEQmw3OWxJdFBnV3VtbGFkdl9uOENEY2E0ZEMxV2M2UzBQMHprdC1kRWN4em41cEIyMk5RTUZlalZWUEgzbUx2am9KSnlMLW54bXY1VjdXY2xD?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46031.39366898148</v>
+        <v>46031.75549768518</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Korean Air launches clay shooting team with Iwona as playing coach - CHOSUNBIZ - Chosunbiz</t>
+          <t>Amazon (AMZN) Deep Dive 2026: From the Everything Store to the Everything Engine - FinancialContent</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 08:56:00 GMT</t>
+          <t>Fri, 09 Jan 2026 16:05:00 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNaEh0SVNvaWNqOHl0R2JZU2FEMlhxZzNQMnZUT1BMM0czMVFfd1pkMXBwaGVpQTRER0dBM2Q5YXpDS1dQa1NndjhoYkRIVC02VGFzWkRYSE5PZVd3ZktzYlZUVDE0UUJONTlFVVZBeE9KNXRqV0Y5cFJvcVVqOXZ5NUhqckF5ekNOblVnNkhtX0pGVkJKZFHSAZYBQVVfeXFMTWhIdElTb2ljajh5dEdiWVNhRDJYcWczUDJ2VE9QTDNHMzFRX3daZDFwcGhlaUE0REdHQTNkOWF6Q0tXUGtTZ3Y4aGJESFQtNlRhc1pEWEhOT2VXd2ZLc2JWVFQxNFFCTjU5RVVWQXhPSjV0aldGOXBSb3FVajl2eTVIanJBeXpDTm5VZzZIbV9KRlZCSmRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNZ2FVSTVOQ1hzQ0VURGxaa2F2SXY5Q1lHQWdUWl9PY3lPNnpvb2RJTXFuU0VvVmhYVmhvMEdUNGMzQldHcXpnWDVMZ00yZzJ5Tm5EOXFvcEZWQUFralNlbG5XeE81YnE3TElCajd4ZDMwN1kwbkZuUU1pV2hRQ3FoN3pCNVd4bDFRMXBpU05LRmZlOTJLM21MWTlwME12cFMwdkEyUTBadG9GQUZ0cnpMWkNXOEdEYzUyV1lVUXJIQ1RIQWx1WHlBQTZzRjZyNGwwcTRBSnlNWkliOWtxSW1LT1VCMm4?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46031.37222222222</v>
+        <v>46031.67013888889</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Central Arkansas sets records in 85-29 win over Bellarmine - KTLO</t>
+          <t>FC Bayern against Olympiakos: All you need to know - FC Bayern Munich</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 11:25:00 GMT</t>
+          <t>Fri, 09 Jan 2026 19:15:00 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNd1BURmd5TXpfZms1TjVtOUJBbU9uU09VYi1NWU1EeEVaS1BvZTBrTEFqWTVDWHR5dVlfYWt2UnVTa1UwdEtrT0RuZXVJWlN4OG9LdmVPU05ZTWRHT0FWNUZveGQzb0JaZDNFaFVtemVxakREVUxYLUxIcDBwRlItamFaT2ZueWNVakpwLVNFVGRMR0xNNlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOaWQ0bEJCMVRzcUlITHlsd3pyUWxwZ05HczJUYU5YOWNLaHZuRkRwWEMzN0NKd0FPS1JSbEVnZXdmbG9EVi1DRGpIVDNrWUpzQU5Gb1VhTWVxSEFJUjJvYkhkaVRoNmhZNjNuWEpJekFoUGlTaVAzQURFMXl3UGVZa0lCWFJURnVFbmxlMEh6MEJSQ283UGd6MDVRZmY0VjFKY2FHeV9hZnFDd2tObEhhMENoN3BqQjlrV29WTGFITlg?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46031.47569444445</v>
+        <v>46031.80208333334</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Une teuf électro débarque à l'Institut du Monde Arabe ! - Le Bonbon</t>
+          <t>Hyderabad airport receives fresh bomb threats targeting three flights; all land safely - MSN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 09:11:44 GMT</t>
+          <t>Fri, 09 Jan 2026 23:51:46 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxONC1RcjNYYXB4QVJHOXNPbmlWWm9NcUVzdTUtVVR1bjNWcUlNSHBuZXFxQW1ZbW42emp6Q05Ha3pGQS1GeEluZEhZMkNHRkVpdjNLcVNaQ0FjREtya1FaaVFRUFBoUm5LUjJfZFJiSXpBbVFvb2FLcGZiRG5xd29aaE5MN21FY09MOXRyUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AJBVV95cUxNbTBaTEhqNGN2bGxYbGFLQUFfSk9pWFZOMWkyYWxKNVM0RnQ4NE13OUM3MC1leEtDQjhpMXkxNzg4NXdsczFXZk5lU3Q0VWpMTG5zeG5jMFRUUkxENnhJU1NSTnp6QlpEanptMEJ6UDdyTmppc0RwRkFBeEFCMldneTJ4cG8wNWRRRzI2X21tdE83LV85NU9LOEdySmJYMmlhT3haLVBGbThVX3pyNEhpN01OSHNJSExreDhaeHpKVmJZVGxONGxTMXVqbkQ4blBjQmNiS052UVVZWXZoUzFjc0Mxb2dtai1HeGRBNjJRWTA5V3VWRzZXaFZVREpBSy1oclBKbzhPSXhUY3lIa3drYzRMYnZDVXRYWnBYbGxNLXl3a1FFOXpCdWlFTnBDU2tjREdxMVZJRWpUZlVpTTZ5cXJETWlKZExyOWFCcHA3Qi1NZHo5eDE0eGx3QTRGaHRIVkRHaEhraUtHOHot?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46031.38314814815</v>
+        <v>46031.99428240741</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FIR Against National Shooting Coach After 17-Year-old Shooter Accuses Him of Sexual Assault - TheWire.in</t>
+          <t>See the full list of London flight cancellations caused by Storm Goretti - London Evening Standard</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 09:40:30 GMT</t>
+          <t>Fri, 09 Jan 2026 16:38:11 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOUEUzYlpxbm9nWjFDYlptYWszajh5OHlnSTZjd3ZWcUJLTjU5V09wZFFUaWY5SHBjQlVKSEU1NkNaNlFHWTA0d3BYRGNzTVBFWXdpelJQUHFjYjd1VVpEZHhaVGJRaTE4MThPTmYyREtLcWg2VGhCbTVMS2VFc3NuLUNKd0t6VEVIQmJGM0dhZnl1cGs5dHh3ZW5BemEzSzNYWm1LY2g3NnZhNFpEdzNzbURrSTA5Q2tnbXRoRXIwQ0JSMkFRcTI2ak5FYXA5U2lR0gHQAUFVX3lxTE5QRTNiWnFub2daMUNiWm1hazNqOHk4eWdJNmN3dlZxQktONTlXT3BkUVRpZjlIcGNCVUpIRTU2Q1o2UUdZMDR3cFhEY3NNUEVZd2l6UlBQcWNiN3VVWkRkeFpUYlFpMTgxOE9OZjJES0txaDZUaEJtNUxLZUVzc24tQ0p3S3pURUhCYkYzR2FmeXVwazl0eHdlbkF6YTNLM1habUtjaDc2dmE0WkR3M3NtRGtJMDlDa2dtdGhFcjBDQlIyQVFxMjZqTkVhcDlTaVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNNGFFdXNVV3JKc1JybVp4OVN5TjU0alpTMFdnbjBTRk1VUnJ4NGNxZkd2TDlMcXNBUEJPTHd5b1lieVVoY1dWd0lRb2NkTktBc183UVJhVEpqSjNJaVY1cHk4MGlXcFFrU0x4VDdYZmw2RWVmUmJjeGtLUVVBVmtCR0EzQ2RTQzJHU3QwNE1fZ2lEaWhiQzhJTHVEcjJhOXZlSlhiMDJLZWYwZlN0Z1RjZy1R?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46031.403125</v>
+        <v>46031.69318287037</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Luis Enrique: Man United prepare radical offer to secure PSG manager - The Peoples Person</t>
+          <t>Frankfurt share new year spoils with Dortmund in thrilling Bundesliga draw - bastillepost.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 13:00:00 GMT</t>
+          <t>Fri, 09 Jan 2026 21:57:29 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNTjF5VmZScFVyNWJuUDI4WFZZVUhMWkNsWjg5OVYxaXlCTUw5Mjdkc3FnS3RCNFIySHhER3FkWWZKM01BLU42TG1zM0Q0QXZIeFFGRjNxX21EZHJkREFqOTIwMmJDQ2Itc0ZJV2VZdmRXa1c5czYwRzdaQ3UydjN0MnM2WXJUUnZiM095RzdaRklBSUo1RTA1LWFtdEVBRWFLcTd6bTV4dHIweTlDLUhhY0E3dDVHS3lMSXlZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPVE11Y05KMUJ3cUhUaHJCM0RJdDMzLTNrZ2tfZ2NTRnA0Q1dlWVlXd0xRVGVoNlMxcnlreVpfUDBhdFU3S2poQUpVb20xbWpSLUhBNVdZbGxuZklwZHg5T0Rqd0R4QkZnZ2VsQjNMcDJCUUU4aHBpT2hmTUtKc29hTjVyMUJHNVViT1lzRERHTlpjOFBtTVBPSGlBZVJENUVUTnFtRS13SVdkcmpuNWRPcjg4dGoyMjZJanpkc1dMVGx4VC1G?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46031.54166666666</v>
+        <v>46031.91491898148</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sinner and Alcaraz express desire to play doubles together - Tennis Tonic</t>
+          <t>InvestigateTV+ Weekend: Examining the consequences of cargo theft - KMVT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 08:39:15 GMT</t>
+          <t>Fri, 09 Jan 2026 19:14:00 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNVDcxWFpnV3ZSVS1XSDVMejk5VnZmTUVmWm9nQjZzdjFpZVlDV2RqYVcyU0RlaDUwLTZ6MVR2ZGNLbUNKaEl2R0dXbjVRY0ZvNWdvZUFPaW9fbmdoSDd4UElxMjNxMV9iMnQzdVp4MHhDaHBheWhSeXoyYkZiSWlHRDNDbTlfRmRaQUhXbU0zcVdESWVoRjFKbV9vc1VLclNwa1FvNHF0Y1ZCQdIBqgFBVV95cUxNVDcxWFpnV3ZSVS1XSDVMejk5VnZmTUVmWm9nQjZzdjFpZVlDV2RqYVcyU0RlaDUwLTZ6MVR2ZGNLbUNKaEl2R0dXbjVRY0ZvNWdvZUFPaW9fbmdoSDd4UElxMjNxMV9iMnQzdVp4MHhDaHBheWhSeXoyYkZiSWlHRDNDbTlfRmRaQUhXbU0zcVdESWVoRjFKbV9vc1VLclNwa1FvNHF0Y1ZCQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQTllFUks5eDFMa05ySE5NalpaTlBmTWJSSVo1MG5CRVplX0pfNkRudTFnY1pKeFFpc1J2dDVoclJjY21YMEFjZzFuTW5yTDdTMW4zMU5uaHItUm5tbXJ1S0owYUZiMHdTMWtiamMwckVBdHhNNExxQ3hJUS1VODBtREtNVThoQ3g5NzB6QVVOTTFiQ2s?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46031.36059027778</v>
+        <v>46031.80138888889</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tempête Goretti : grosses perturbations dans les transports ce matin - Le Bonbon</t>
+          <t>Istanbul Joins Madrid-Barajas, Frankfurt, Josep Tarradellas Barcelona-El Prat, Munich, Rome Fiumicino and More European Airports Break Every Passenger Record in History, Everything You Need To Know About How Europe Tourism Shines While US Leav - Travel And Tour World</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 10:02:26 GMT</t>
+          <t>Fri, 09 Jan 2026 14:42:50 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPbXZlUTRESWY3aGY2MldYTG9ldXdibTZTZ0FnZUhjX1FCcjVCaWdYN1gxZlhzTUhlSUZmQmZwelhvRWJHb2MyM3o0bTk3cllFRk9ua2g2cEdXMU9zOVZCLW5IeXk2LTk2elE2bVRVdUVRODRIZXFDYnpOMlVIVUFtaEdB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxNNWhmRVlQRERQeTBXcl9DMmJtVi1ITm01YlJYZjlwNTBIV21sMklPNkZBaVdIbndyOUxiUHowSC1fMkN5VDRGTndRci11eWdZaGJGRDNjWU1KQm5FQW9fSnQ5V1BaeXprUDRYbmR3MnJVSEhpQnA1Z2hKYm1fRlBrU1BMT05yR1puc1VrQ1J0X3FtajZBblh5RXg3dUVXazlNaGJvX1pNc1cwYXd4MU5uM2VzOXZFNm9PRkhSLThEcl9zMmIzVENHdU5pNVFzNmpHT25DRUlrd3Y3VHhJaWEyUWdPbDFJSElTbFpwWFd3c0xxSFdQMC00Yl9icjFrNXB4b2syYzFsdzNVZ3pKNEcyQjVB?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46031.41835648148</v>
+        <v>46031.6130787037</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>What to know about biathlon at the Milan Cortina Winter Olympics - myMotherLode.com</t>
+          <t>Goal fest in Frankfurt: Eintracht and Borussia play out a thrilling draw - Zamin.uz</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 11:12:30 GMT</t>
+          <t>Sat, 10 Jan 2026 03:45:56 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNekhlSFVRYmE5OERzNGsyU0pFWm5VTlhQNUpaNkZROGEwbDNwWXdPQ29BWEt3SWpWQ2hxcC15VFBkd0o4RFV6My1ZVnFtdHgtQUo1ODNXY0M3M091MGZmMWxERk5yWkpJaUdLZ2lIQlp0RXRXT1NwRXctNXJ1Q0N0bXJhTlVqWDM5WjM3WlhCRnpzOTZSaXpFWDhZdVNRdmZiQ05jSGdfeGZraTVjTHBZVGUxeFVPYTlFR2tR0gHAAUFVX3lxTFBQaWpJR0dfa0NTT291dXNSOHJKXy0xTUJ5Z2V5UUdNYVBFZWtxNGM3aHJjVXFqTVJnZDFhdGU3aVNsajk1ZmdrWUthZFB6Y2RGelNIZE1GT20xa2txNVJEemMwb0lsMmVuUXg5c2F6RG1Vak1yMmxEUjFMOXdicG1CcldpVUczRUs1MGVQZFFVNzZpVmIyd1lvQkdCY2MwS3l1MEd3NF9NdmpWbVB5emlSalBoOE9sVUNQZGtVMWdhOQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOdDd2ZURZVnowcnJjOGJXSEdVY1ZSZEFvaXBOM2c1TlFkMDktUXVyc3BHSGtNYjBVNUpwUHR0cXg0b3pxVkFIZUZGQVQ3YWF5Z29lVWRLeXptazN1c3E5T083WFZoQk1XT01hOFRVb2h0ZnJscmYxRGpSamx5RXdwRGtGbUFDOG5UcTkzQWMtSlVvbUV0Mk93ejVUZFpKMnV0Y1dF?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46031.46701388889</v>
+        <v>46032.15689814815</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Panathinaikos bounces back with win over Virtus Bologna - TalkBasket.net</t>
+          <t>Football: German league returns with an eye-catching clash between Leverkusen and Stuttgart - The Hans India</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 08:50:38 GMT</t>
+          <t>Sat, 10 Jan 2026 00:45:27 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxON2tRd2owSHE5eEdSRF80ZDBsdEVzZnhOU3RlVEl6RW1HaGtzVmU2MGE1ajZXek5YeTVreU9MeVNDeDVGTHZrTFVTMmJiVUlnSHRKTnJBNFU0Z0JoUThzY0VmUjRJVGNOLUtfSXZfVDVnSEdxZkhjcDh4ZEVQei0tOWpaWXJFLUdPQ2drNHhIcVhFdDTSAZsBQVVfeXFMTmZ4WDBGekxKVkh4c3lZTkFlZ1l3WXM4dTZUZ2VOM0lkLWRqZ1FBMkxoaDFHUmpFeDg3dWxzSF8zdWlzLTFodGZOZzBTWF9Lb2kwQmFCcWl6NmVjZGkxcEhoR0RUMWtPZjZXRnlfX21MUEgtdDJ1X0pkM2JBUVFZU1NNbEtHMlFPVUh1dy0zalJjNzBQVWI3RXNJZms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQcF9POEhMWElmS25wdzU0OXJUZU5VeWhKd1BKb1FpVmtKN2thUEU3dGxCS0RvTHpfYjN2UkpiVWZoTTliZmVhcVBwd2tqSTh4SzAwUnI0QXp5RDFXQlNMWG1uTndfNmtjaHVnWkdmVjF3RWttQlNZbXFHd3J4ckZ3aEVYWllGMVRiZjZVRzNIU3hzMHZxeUxnTnBtUUE3WnlKbWppbjZYV243ZVFDYTJxTW9jUGtfdmNqUkRLQ01hRnNMTkdzS2k2S3RDVVU4b0ZIZFh6atIB1AFBVV95cUxQcF9POEhMWElmS25wdzU0OXJUZU5VeWhKd1BKb1FpVmtKN2thUEU3dGxCS0RvTHpfYjN2UkpiVWZoTTliZmVhcVBwd2tqSTh4SzAwUnI0QXp5RDFXQlNMWG1uTndfNmtjaHVnWkdmVjF3RWttQlNZbXFHd3J4ckZ3aEVYWllGMVRiZjZVRzNIU3hzMHZxeUxnTnBtUUE3WnlKbWppbjZYV243ZVFDYTJxTW9jUGtfdmNqUkRLQ01hRnNMTkdzS2k2S3RDVVU4b0ZIZFh6ag?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46031.36849537037</v>
+        <v>46032.0315625</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rafael Leão scores another important goal to earn Milan draw with Genoa [video] - portugoal.net</t>
+          <t>Grafton's 6-foot-8 senior Brody Lillemoen in rare company with 48-point performance - Grand Forks Herald</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 09:41:58 GMT</t>
+          <t>Fri, 09 Jan 2026 15:45:57 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPdlN6OUxjSTU4MXNXMlVMeTdCUEZLbkZBQi1Ka2FJaEs3R2F5d3MtWTNKbkFjSkRkR0tlQi1KdGRTU3dmbjE2d2J6NzFVLXFuVmxTdmtnMXVKbkEwejFPZnJERDdNN21LejhGbGpuU3VZdWpjdTRycl9zMUlMbmpZT0pFWnNHNy1WNjdMNlJVenYtMk9VV2pJVlhadzhmTGNrRVBVTXRKRjhTLVlGMW1RRlVhRUtVc0ZpX003OENuVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQVXpfMjdtclVjVi1xMEZpbWYyaVFyRjBvMi1SajVyM1AwaEhzTGlubjE0Z01yZVVLOVpYTHoxRDU4bzNGcWZqVlB6RUZfMVJab0JwVkxramtIaWZadU9NRXFyU05jb2NVbGhrXzMtRDI3bHZfcldpdlRhVEdTVXRIaEI3NElzMF9pMHZUbkdEN2ZuZmFpYklLWXVmbXFheGZXT1JxS040cGw3MmNDRVBfemVUS0JyNzZDVTNfWHhhcjBqOFV0amc?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>46031.40414351852</v>
+        <v>46031.65690972222</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>In the news today: Minneapolis shooting, Freeland’s resignation, December jobs data - CityNews Halifax</t>
+          <t>Photos show snow and ice hitting parts of Europe - The Daily Reflector</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 09:36:09 GMT</t>
+          <t>Sat, 10 Jan 2026 00:00:11 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQd1lEcFBLQUdaVmNYUUVWMVdSWEZlMFl4VGtKb3JlSW4tTmU5dE9WWEpKQ3NPWFJ4LWc0enJpb1RBRGduVGhKU2R4ZDk3UF9tVjlqcTdWMWhMNkJSdkFKUzhrUEJOTVFidjhhRGFQbEZPblZxT0l4XzVtYUZZSFRxVXlqOXlCc3I4dUNwcmJySmhXVWd4ZVpoTi1VMXMzZnRKTVhTQ0RtcUozUWFyTTBiX3JxamxJeUJOZXVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOWDIxb04xMVRiYWtpVGlRTDJyWVdONXZNMzU4NkU5UVpPcGs2VUlWWWVSdHpTSDJYWWVTREVZYVpLLXVqRHVPRGpKMUdGSUFsNVBOYndqY2p0WjhzU0szM3Vpb1g5M3E4Y0RGY2lITDNjbWFBZjU4QTY0Q0dQMVpRQU9IVGtrOGY0ak1nc0xjSXhjU1pKNWliWE10cWdiQjhqRmlSZVpTYnVvWmN5TGJiUVpVUnZZbFRJbFhHdF9fZkhLMTVrcXUzeld4R1BFQkVLQnRnWg?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>46031.40010416666</v>
+        <v>46032.00012731482</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>EU envoys provisionally approve signing of record Mercosur trade deal - Reuters</t>
+          <t>Ivory Coast's Yan Diomande unfazed by €100M transfer speculation - theScore.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 11:31:51 GMT</t>
+          <t>Fri, 09 Jan 2026 18:33:44 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOTl9OS0lmZTJFRkJ5TWs0SXVEOVlTOTRTNFhDbUtGM1U5Vk1VSTJCYUE2R2w0Qkt4am1HclNFLWRfb1BPbHluQmxIUWkyaW9acnJEQXpTTUhDTXBNbUU2ajdkWHUyajdCMUZoS01yT0FXRk8zWXgwOVpiYkVzWGZyTHVsSFh6ZUZTU0FNMjFRYmgwMkxYTkRVOHNjNXBTcGFPTEgwSEZXZ3dPLWZJYVVBdTdlQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE9ZSGw2WFZvQWtOSHNzVGlKX0hxUTJQNjJyUkxlaENoN19hbTlIMzFtZmt2LXZxQUEzQVhOQ0VCMzlaNEZrUXF0cDNmN184RldCNVFkOWRB0gFWQVVfeXFMT1lIbDZYVm9Ba05Ic3NUaUpfSHFRMlA2MnJSTGVoQ2g3X2FtOUgzMW1ma3YtdnFBQTNBWE5DRUIzOVo0RmtRcXRwM2Y3XzhGV0I1UWQ5ZEE?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>46031.48045138889</v>
+        <v>46031.77342592592</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>It is all-or-nothing for EU-Mercosur FTA in Brussels - MercoPress</t>
+          <t>Real Madrid receive a bomb offer, Florentino thinks about it, FC Barcelona want him too - madrid-barcelona.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 10:14:00 GMT</t>
+          <t>Fri, 09 Jan 2026 19:00:00 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPUk0ydGNsNXdNNmhlSlhwWnZNNDJCeTh3OHVJNDdQZzZCUkdtMS00WTdSRVVtUU56eFE0OV9LOGFsa2pNSGtjazNOMUFfaTFfVWRhZ2ROMGh5ME5BNHR5S3k2WlZvUHFMeDdiUEpDZUllS0dQR0ROS1J6V2J6UWt2aDNiRVlDWkw3YVZqVWZ6c0lJaTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQSFl4ZjlidUVwRUpCY3p6UE1QMmhNTTh4UEJSZC1GMkZUT0hOU1lCRUlFc01RWWNzdUtSZGMwVEVsSXJ2UkRwaVFqM1FtWGlNT2dsRE5YNExRSUVoTXg1SFl5UW0zdjN1eGlTeWpTUjJxaFoyLTdXaHhLUkFFT1VUTVJfYld5VVVyaHRPU0hOS2xYdDk5ZGdtZ2FKYzVNTXRhZ2JKVDNKbm5lZDlubmhkZ0E1ZmhEZnVLSE9nbUhram5WU194Z09YbS1hTlI0SEhtZnc?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>46031.42638888889</v>
+        <v>46031.79166666666</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Police officers who shot man dead before Christmas 'have not been suspended' - The Brussels Times</t>
+          <t>River Plate's Explosive Move: Denouncing Agent to FIFA Over Scarlato - footboom1.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 12:30:37 GMT</t>
+          <t>Sat, 10 Jan 2026 00:15:59 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQVHJVYm9xdlVmQk9KeXBPaW0wYl8yUnBNVXVTRS1hM0pzcENiTjFoTEE5a3lZbXhkV2NRcDFqYlAyeTdLT0hqWFQ2Uk1YbV85OFlXQmJwVk5SQTJIWmQ5ZnFwUXpnMi00aEc5SDdwUnpvWVRNaXZhMWRpN2FfdVNvN2lZc19PejJPNC1XMjZMRG83SnB6T19meGJ0VDNDNmF5MGhkaXdKTS1lNTdKZWk5WW91TEpZSWlDRllxTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQRll5YUE2V09ISkFRbVhRUkpaZVk3UndHdWtMYXlRVjVFVk5yemZjNUt6Y3ZIN2ZpdXJEN0prMWdrbzV5S2Q3eUVCelJ0QS1KQThwYTdxbDloMEMwdWVjY1ZnOWdJdHdFM2dVVkt5aXFCQVdFZ2J4WFc2cXRENl9FVFoyalJYaDdNcUVQTE5obHdxOU1yWXY2TG5ITGZHN3dqVGgxTGhTbk9oR2NCdk5ib1FHT3h5Z2NDdE9sZzZR?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>46031.52126157407</v>
+        <v>46032.01109953703</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>PETA Twitter search</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>peta (gucci OR dior OR armani OR lv OR valentino OR vuitton OR polo OR ralph OR klein OR hilfiger OR prada OR balenciaga OR goose OR burberry OR lvmh)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Polish school kids protest at teacher removing cross - Brussels Signal</t>
+          <t>Peta Jane Beauty: A Self-Tanning Brand By 'Dancing with the Stars' Alum - fashionista.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 10:18:40 GMT</t>
+          <t>Fri, 09 Jan 2026 16:00:00 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNTnlvUHdhWEUxVlFkMDQtaVFIVXZHc21wemJOSGMxN0ktc2pvSGlQUW0zSm1sLVdEXzVoTlpTNHA3NWs1NVBSMzNXcHYxcXdMdHhyV3pLV281SmdKZ2lVams5SDlSWFBLclpkNmI0dFdYdWgwd0VLTEJRQW5zeUVVVDJsSC1teGpVQ21pZnBZUlk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE8ydjJTa01GSDRiUlM2X1VKcDcycDhFT201SUozekRjWUFsYWQ4bE92WHFDYTMzUEw3R1RSUGFaMFdDSXhlTFBvOWFydnpxTWdjNURDRmRQOGczbFM0Ym9zYnByN1NINGVSb3ZZSm1hMmd1bW1pZmc?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>46031.42962962963</v>
+        <v>46031.66666666666</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>PETA Twitter search</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>peta (gucci OR dior OR armani OR lv OR valentino OR vuitton OR polo OR ralph OR klein OR hilfiger OR prada OR balenciaga OR goose OR burberry OR lvmh)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany says EU-Mercosur deal sends 'important signal' - RTE.ie</t>
+          <t>Kim Kardashian Steps Out In $7,500 Fur Coat After PETA Backlash - TheRichest</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 13:34:59 GMT</t>
+          <t>Fri, 09 Jan 2026 14:30:00 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE5xQjZ4dE16TkdhVVJkT3k2c3VreXpzWV96a2VyWWJHSWV3R0dRdXBDMVBIUVgtTkFyOF9VSDk3d1F6M3B1QUxiUlBBVWs4cl9oMVozdnFIS2VrSnJtZEU2X0R1R3dUVExIcDBwTXI5THNvNDM4U2thSjZBOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOeGtUMy1IMUFabWtOOW80YV9wWjhORjFaNHVPc01idzQ0VkI1TEZzSjJNWm5JVlhKcmN3c2t0WVBYOWVFNG9XQ1lvME45WDN2aTJ4Q0NXSXY2YnhpYmljY3U2ZzJlTnlaeUxjYjZQUnZiaDloTkw0R21JQVh1R29nZmNYZDRIbHVZRDVIN1d6Smh1eDAxaGZiRkJB?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>46031.56596064815</v>
+        <v>46031.60416666666</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kyiv Mayor urges evacuation to find warmth as infrastructure war escalates - Brussels Signal</t>
+          <t>Eco-warriors put people off going green, warns environment professor - The Telegraph</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 12:59:18 GMT</t>
+          <t>Fri, 09 Jan 2026 18:57:00 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPY2NjMnB2clFncGZlb0FwWlM0ZUdCdjFEbmpLeGl5blR3cTBiSXdwUExyLXRJd0Z2SVByX09yb3lqcGpfSU5oQ000TENvZHNVeW1nem5LQk9jejJCR3p6N3hYbnlNQ0hpcUw0cUEzdmRKZ0wtc01xekZ1UldnVDY4TWxtNDljWDU4c0xDSGpTUnI4c25Deno3X0NIaFRVX25uR2dIUkF1MUxVeTJ2TVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQc2Y0V0hVSnZGRmtSMFZJRmhvNGFPTS1FajFnOWp5Q2dIdV90SnRIUGNiTjNWSUlyZEtLaTZTbTZ5OENXRWVUUVZvd0JCOHRSTEMwSzN4THBGT1oyQVl3amozc1lFa1JkalZ4a01YWE1La1NfaFpXUU1ZMzBZMVU2ZW40dVdtaEZuVlRWQQ?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>46031.54118055556</v>
+        <v>46031.78958333333</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brussels jeweller kidnapped and forced to open safe - VRT</t>
+          <t>The Eco-Zealots Were Wrong Again - tippinsights</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 12:15:17 GMT</t>
+          <t>Fri, 09 Jan 2026 15:37:53 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPWGtwZHNqZEdnamZ6Zl9jY2Q4cXV3bjhtVDBuTXlaNjFrY1VVeGdlMWhrR3Q3Wkc0Ykl3NHNqMTRWQTZadHp4VGNyWnN6WllpOEs0bF9teTFPREYydURBY1VIVGRXd2puMTdDZWtSbXpXSXpNNnBOeWVGZ2VnMV9YMDFrc0pweHFYUGM3bkV2MmJCSHZCWGZF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1rSm5URHd0MkRqZFZ6cWdDcVJqQmo1eHZKLThWLVg4NDRtemRsZGJ4NTVuSi15RjEtQmpQY1JEeFd2R2lIM0pod09CREtRejFrZDdsRVJScXRnV215eC02NnpPU29fbzlQc0E?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>46031.51061342593</v>
+        <v>46031.65130787037</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Former Audi Brussels workers to get €7.5 million from EU - The Brussels Times</t>
+          <t>Skegness man charged and remanded for nine counts of shop theft - Lincolnshire Police</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 12:30:36 GMT</t>
+          <t>Fri, 09 Jan 2026 16:29:00 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNRUJiZjVVbnFVSTNVNHlKR05YNXhzZFpvNm5GVGxaYWRTeDRpU1g5NWVGQmFVX0RzM0VqTjgwRldJNmdXQkVBR05kaHRmNWxBamU3V3BPYkh4MkpUU3ZMMUlSWDRfQ195bGtxRVVwRThGdXJHV2dCNDBWV0RwS05aUmR1bHpCN0ZwaXFKT1MwN2FxeTh4Z1pXb1ZZa19sOUZ5NVhpUkxnUTd5SDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPY3BTcVFTX2pZWjZfd1N6RjREc01tVXdzRVN1ejNJaHowbWZndHdjdC1kSWxWdGJQRkxTVEE3RGdCVW1qajE0RVR2RTVMQVZSYnZKQWFTckJ0WmpwdFZKSWc5eHFmck1pYXFnSmRwaFVtOE1Vb1ZDSU5BX1pncUtHSlVzWGJFeElRYUdyQ0ZjMTU1cXo1eG9qX2RMLXBaTERoTFdqa3hCQ29yRmJMclU3akRUdlFVY3RKbE5QeG5KT1hGdw?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>46031.52125</v>
+        <v>46031.68680555555</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Reaction: Kilkenny voices say Mercosur vote 'devastating' for Irish farmers - Kilkenny People</t>
+          <t>Merseyside Hosts Landmark Conference Driving National Action on Town Centre Safety - merseyside.police.uk</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 12:39:14 GMT</t>
+          <t>Fri, 09 Jan 2026 15:16:00 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOdjFOYXN6amRST3A5S0hnci1UNk5CSEhhMzAxZVZjX1NZdFBXWjdpUjBUN2ZCbkJLR2dQUHJqeHN1M29IUVhJcl9uTGtDSlQ1elNUdG1VWWNQaFFTY3Jiby1nWUV2TlJvQVVHdzN6bnZKcVd3Mmc1U2VuVGpwTkc0ZndFMGk0ek1zUTFVaFhjcnpYclNTOE85MTEtRl9aSVg0OGhwaDAyQk1sQzZkbXowZ3NEa0dsUW4zSGhTSVFqZXBmd29zZ1k3SFczaTVMQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNdmJmWndYZTI1aTdidEJRZGZfN0FzWVJsN3JybGtfYlRwM3hVeTJscklVWHBoeTR2cWJCa1RDN0tTekVFOU9heUhkalRpU21KbnJGeEh3R2VISlZsNFRnaDFzUDRRdXIzU19IUjRXNndudzI5clhONXNxRWloT01memlGVG9SaHYya0tQXzU2OHdJaExPbGVnSHZNNlQ1VlNrRjY1X3ptaUN5bXlOV3ZiWlRmb21kWG1QcmpQLWdpNjlqM1FEcHRpSU5YVDZ0TlBXOWZZclNiZjRPS1pXOXpvOVVwLWhLS0h2ZVNV?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>46031.52724537037</v>
+        <v>46031.63611111111</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Goyal holds talks in Brussels on key issues of India–EU free trade pact - The Assam Tribune</t>
+          <t>Facewatch alerts to retailers more than double amid ‘industrial scale’ retail crime - housewareslive.net</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 10:44:19 GMT</t>
+          <t>Fri, 09 Jan 2026 16:05:00 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPTW9NcmF1Sk8xTjRIcjh3RUFxTmZhdkpWOURMdmIxd0t4VnEtd243Wm9fNzZtMEFjT2FkOTBnRzVudjJzckl6a2laSzR4NmdmeHRubE9VUHdkNTBSeXFCeW4zZlRtMDVLRzRMX09lcld0bW5oZjB2RlNtamZKLWVvbTF0Ym4zYndaeFk4bElhcnM0NlU0OWRfdFdBbU5nOHdnZ2FkNDNxQUNIM0dQMkJhUjB30gG3AUFVX3lxTE5TUU9JczRiM1pYZVgweFhpTHZfZ3p4cDBqS1NlREp4a1FqMWI1cU9WUDRvbGszS2NKdjFwanFteHFpZFIxODBVYVd6VER6MUlpNjQ4eXRkdjJvS21jWmhBbnBfcjRZUTZxeS1SR25UM2NaTGptWk83NzNmSlBXOEZoN29HVzZDUWhabkl6V1U1RjdNdXRaemEzV2ZHZm9Pa2VvNTMzaTRWbUF1TmdKMGZWMUhobEhCUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPaHJNTWJDMWgxY3pzY3lsTjRfYlpXdlpIdUI4bURkMXJuRjBFamkyUTl3dFI2U084NU9lNTFlUlZ2bDl6WHNQanFwb1pjUEVCa2RTZUFtdHlYcVRrQ2hVZ08tNm4yd3F3WUNBYUhlMnJTSWNqZVcyMFhnX29XYUszZWhvWFFRejlWOFZiRHlzN0xjNlV5MUFudHhsWFJCMjZ3TW9kRGxYcTFSUFNjVFE?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>46031.44744212963</v>
+        <v>46031.67013888889</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>£40,000 Zeekr 7GT squares up to Tesla Model 3 - EV Powered</t>
+          <t>'Retail crime is not unique to Clackmannanshire': Shoplifting rises since 2021 - Alloa Advertiser</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 09:50:59 GMT</t>
+          <t>Fri, 09 Jan 2026 16:45:09 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPNzBGbVhjNW9jX0xLeXUtQmhVcGxwdjRYcjEtOUQ0QzdhYmlDN1lYaWxHbEFIbWRhZEZCZlZpQTU1MmpQLXItNG1RMWdQdjZILXBaODhnX21FV3Zjekd6NHlBYVdQSEVhMlRrTnNWci1FMVMyOUw4UG9VVzNnaGY1NllzY1FNelhlWlhoM1dDZi01UlpaZ2RXb2Z0TjZiY1d6bnFNeUI1OWdrNkFj0gGsAUFVX3lxTE83MEZtWGM1b2NfTEt5dS1CaFVwbHB2NFhyMS05RDRDN2FiaUM3WVhpbEdsQUhtZGFkRkJmVmlBNTUyalAtci00bVExZ1B2NkgtcFo4OGdfbUVXdmN6R3o0eUFhV1BIRWEyVGtOc1ZyLUUxUzI5TDhQb1VXM2doZjU2WXNjUU16WGVaWGgzV0NmLTVSWlpnZFdvZnRONmJjV3pucU15QjU5Z2s2QWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNTHZyMmx0UGNvb0pTWDNVSGduY0tnajk3UzFGSllTVm5sYjBPZEwxMlBwVUZnNTMzRFdnbDJlNGI5UXdtTUE4U21oT0dQN0Qxd2xqOEhsek9lbkJyeVRJQWpFT3FHVWpqNjdqZ2dYNzZHZlNvd3dNQVp3X3BjcEFDZUZjUlpITE80d29mOGhQR3R4YmJBMUVLNQ?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>46031.4104050926</v>
+        <v>46031.69802083333</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Zeekr 7GT unveiled at Brussels show - CompleteCar.ie</t>
+          <t>Group wanted over alleged Yardley shop theft - The Solihull Observer</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 08:38:14 GMT</t>
+          <t>Fri, 09 Jan 2026 19:02:14 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQLWxPc2wxN3BjanJDTDFBTC10VUFfa0ZFRWFsd0puTmpySktEdGVyMEF4Nml5OTM4YlNHTTdBVDMxR0tvUEt0TGN2THkzTkFpTkVmREJ1Nmx4RjBVU1o0UWk0MUd3M0JXaDQ0RUZ3UWxTYV9xNVEtY1RwZzNwZnVjYkdnMEpkLWVHMTN1eXl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOSnRFb1ZSTFp2VXV0d0tScmNGbTRVeU15QVM5RFF4aThJWHFpZXNIY1ZrUHJuN21sWWQ3MFgtMl9wUUtBVU9pSktMZzJuUlZ3Ykc4TVF5ZjB3aHVvSldZRS1NaER3NkIzYnJnTnp2T3dqTHpjYndRS25tQ1o2bTBNcFlmR3FLQldP?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>46031.35988425926</v>
+        <v>46031.7932175926</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fire guts apartment in Schaerbeek, leaving building 'uninhabitable' - The Brussels Times</t>
+          <t>The few behind the many: How the Hutt Valley is fighting back against retail crime - ThePost.co.nz</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 12:30:36 GMT</t>
+          <t>Fri, 09 Jan 2026 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOeXJPTzg5UEIwb2ZyT1N5ZHR6TC1qNGhnSWxsQTFQemJ0RG50THJoWjhJaXk3dldlLWxRd1Y4YTVBREdYRHF6QmJmN1d4Y3RBXzdsR1p2NHNjYVQyNXVVVFZqMHJOZWprSW1YMlVNMkpzdGhqZzJQVzc2eDVfRzZUSHhZaFNWOU54ZmxFZ2FWSVpPQmJTUGhFWkVGX0dGRDE0S1J1dG9IdW84cTAtOGR2dQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPWkRZcDlpbWloN2tFOHcxN1EyNUJFT1lXem5uRzBFc25IQjM0NHpUS2s3YjdzM0pXSUd2d3VTY1V4OXI0a1cwRzVxTm9PSi1EZTVuWVFtVFlJV3BXU1cyazVfV2hlbDdjZzRzalhTSFhHdkx1QS1xN3FTUVFUbDhFMEFkOU5KZ0E5aEV6VXZEeHdSa01CUk5GVFVfZS1wU3VQRENWWXlnTzFjWTB6RlQ4?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>46031.52125</v>
+        <v>46031.625</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgian PM posts message of support for anti-government protesters in Iran - VRT</t>
+          <t>Toronto police to crack down on retail crime - TorontoToday.ca</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 10:43:16 GMT</t>
+          <t>Fri, 09 Jan 2026 18:30:59 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPU0Vqd2drVXdBRlYwUmxrcUV4NTBERGN2MkdXazdpVHItZ0JtelB0eEVUeHhqWWVjdlRmSDJMUW85UVBqOGhLMlJQbmVpamJSUVRzX0xNcWV1ODBsaGRRcDE4aW4tWWdzeGJQN1pqaDdGTUxfcFBUd0NXYl95T25EaG01MFFlaV92NnRKMlNZM2tPRDNDU0pOUHBBY25zbExuZ09Fcjc1YXE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPNUFwbDdkX3laTWVENW0xVTZPcXdpQ080cTRtR05udFo0cDdON2prUkRWVTNwcF9hVUJzcFFNNGQ1ZlZMTWIwNUhpdGw3alBaT2dJRVkxY3R6TmFWNzlVWF9TYW84c1ZkZnBtSFYtRkR4OG12RldiaTBxUmZTRURQVjBVUFJHN0tiRERDR0FxN0RvSDhKbkdwbjFMUGlaRmdyeXFzUU9QaTlZUQ?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>46031.44671296296</v>
+        <v>46031.77151620371</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>French opposition parties seek to topple government over Mercosur - The Straits Times</t>
+          <t>Theft at North Carolina vape shop under investigation - WYFF News 4</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 09:51:36 GMT</t>
+          <t>Fri, 09 Jan 2026 17:58:00 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPQUc4OXUtZ1lZcFgtUmRTZmRvT1hVdjhUc243UzdpbUpLT1NmS2J5MmpHaWI0amhoX1pRNXJlQmNlVk5oMUkzWWlkekhyZDVaZjJLQkpaZE1Pam0wQXh0c0hpZ0xFa1ZTY0dLYVFmUEg0V1RWMWNvcndweFUzS3U0VXZOZUR1cG1aci1xal83MzZ1Rk9NbjV2cWM5eV9ZRE5FdUhDQUJBZGw0Nkt0a1BzSDI5ekpSdHdaZmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOa2Z1bjYya2dldWdZa0I3SWRqSVhKdFVhSjlWX3ZPcUwyMjZkZU13Yk1FQmpGZHRvR0dGNU5HUnN6THo4SmVjNzlkV1lrYW5ha1l6SmoxMDd6c2FBQW5kSkVXUFRYejhtU21LVnZQMUdJWHNDeksydjAxRDBsVVVhWW9sWGN6dDRXRlVjSWlkUjl2bDM0X1JR?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>46031.41083333334</v>
+        <v>46031.74861111111</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>What happened overnight? Police blotter report for Friday, January 9 - Newzjunky</t>
+          <t>Unity RCMP looking for man after seven businesses report break-ins - 650 CKOM</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 12:00:30 GMT</t>
+          <t>Sat, 10 Jan 2026 00:49:00 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE03Si0wTmxqUGxJY0NlU3VaQWlsdzY2TWFFRDJEODJRakkyQjJaWmNOVkxMclRuSmk2N2wzMXc5ZW8zUnVOcndERmRJUHg4NlVGWnFURDRVTlAxeFFib1BvQjBGUkVoQW5mUXd2LUtLaU9DY1dXYjhGOUIycDExMVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPaXlKa2c2SGtvc3lqdkdNOGhrRzJqYnVhTHpxUVRReFdjYTdqY2NuTGxYaFdrcVZRUXlOaTl1elJ6SzBDWE01YTJlUjRhdFRUUWQ4OUpQZW1YQy1zU2Q3aHI5bGFtRG8tOE1ad0h0NFc5cE5VS0hCYU12Tm91QzdXVUl5VXh4TnhuWWhMajZDa2sxdkhudlp4RURJVFRtNkNU?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>46031.50034722222</v>
+        <v>46032.03402777778</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Local Town Searches Wertheim German Terms</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>("Wertheim" OR "Wurzburg" OR "Aschaffenburg") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR boycott)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>The meeting that gave Albanese the inquiry green light - The Australian</t>
+          <t>Suspected thief arrested after running into path of chief constable - MSN</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 10:55:25 GMT</t>
+          <t>Sat, 10 Jan 2026 00:47:33 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxQRDRzbk5LeW5Ud2RyUFhJcU8wa09PekJEN2NyTjhfdXdROF9tNDdGZ0ZZdXo0S2RPZEVJU1AxSmV3amx6WUpSRWxzREN0eWxuRTN3dFBlYndIYXVtbTU5Q2VpNFdVZ3JZVVdpUHhDYXg5YU5RaDVmT0JmcFZjZExqRi1ISlJVZUp0RS1QMV9iekJUMEo0ZFY5WkR0Ti1MeXVEYUtEU2gzTUZrMC1rUGJBSmtuREs2d3pVVGFmS3N5aXg5N1BqbmlvVmFISFJsMjEzRGRqVDh3c3ZOeFc1YUFtVE1TWU1hT3FsemVBblUtbDk4a3dGUkEtYVBSRXE0NDVTYlB5d0I4bTlVaEJORzROZGh30gGXAkFVX3lxTE4tdG90c2k4QUVmb1B3REs2MmlYczk1SmluZGIza2ZYdzgzS1prMnlUOTlwVGlJdmFtYTV4Ym5fSFVKWkkwZktVLUctUTFrdXphSGFGdWdmcXFCX2tCLWxzXzV1Ty1Pc3NOdTJjQjRXQnFUSm9LU1RtNzRCa0FiQVR4aTJ2ZjZlWnAyTEwxZUhLRWFtVzk5dW5OaVBvU0Jqcm9xZUVVd0FGMW1DVV9ZRklFNU9uRGdlbE5VaVlXc2hVM3lDTVV6c0dmS2JvblhsNGRXSEctQnFrQ212c2pqeUJ4YkhVM3JTZEFOd3Bza24zRXhDOS1nQS1yRUJmUUNjdFM1THN0RTFTYUg4MTZsWDdRRzlYemdxRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQalFZZFVWRVllRVRpSVNVNkduU3kxSGlmbURPc2N1N3N6bmhTR0ZNcjJsX1VBZ1F5NFlBYXV4dEtUaWZiYzJwVGEyb2x5SDllekp5WDVKcGVETGNzZFJ2eS1wdkxpSk5rMkE2UVlxX0ROOHg4UUtrQ3lUd3FjZ0dWNkpfeWY4dk1XM1pMMEZqM3V4ZUR0T0NlNmNLVGU4Rms1QWRmaVV1dXREc1RvMTZ3bm9yU3Z5eWVH?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>46031.45515046296</v>
+        <v>46032.03302083333</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Man whose body was found after plane crashed into reservoir is named by police - Ireland Live</t>
+          <t>Ketamine classification calls as gangs target high street economy - Liverpool Echo</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 12:28:33 GMT</t>
+          <t>Fri, 09 Jan 2026 18:34:00 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOYmdaYTZ1R05PNFVZaUJvcm13WEFmQ0tMalZtTDBEMHVkZnVfd0tpOV9vcUk2U0E3ZTRIS3RpSGowaEk2b2VuR0JjX1pnTl9SUUJWUm94NHBMMnFDT2F0UXFLZUZ0aFQ4WVNRSnNfeEgxS2dkdDBZRks4TGJHQmlCYktMTWYyd1kyYU1nSlRySGRzTDlScElBQXg5UW5SOHpyb0RMMjB4SDlMZG1tQW5ncjVzNmozVkI1VzlRRlgxLVZFR0ZoT2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQX1M2SUtGVllvd290Vi1mR2lsaVZkdFptS0htenhHbjFqRUo3eGRBOGNnWWFHNHBoM2N3T1VmcWJwWUxaUjdua1NlSk9QSG81MUZ2RUxNdWZLZXBnbXN2SzI0MVZKZm1TdTc4a3R3X1FyS2xBbGVCelJBeTlDOG9FQlVyTmg4NHBGSTgxTnhQYzA5Q3lFcDBiNzFJc1IybVgySG9uMnhlcGI5bS1qWC1HNUFB?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>46031.51982638889</v>
+        <v>46031.77361111111</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Tulsa police arrest duo accused of $1,800 Old Navy theft; stolen goods recovered - KTUL</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 17:34:12 GMT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxQQjRyNDlLcWdtbE5qZGRSeDJ0QkcxTUxORlIzb2RMOTZOUUZiQjZzLUVBWXBHT25xMm5mSUpnS1FCejA2VGNQWXhkRzZ1T3ZwdUZZaW9LTTVPYlZiQjU4eEVrSFZtTGd0YjJjdXdGVXhRMGV2VjJCa2RmdXN4NGRUcTFWVE9GdmJoYndBcUY5X2Rmc2hHYldBdk51Ti1VeWg4bUxQR1picDN4Q0JDUXZHdEJxTHR5c2xPM0dhSk52eVZRVE9WcnlVc1c5STNsVkhCOGVLN0RwVmlNSjJyS21oajlwZXAyMWhfQjZfWnRnNlp4WjhSWlNpTDhiQlZaR1BGZWF1bU1iRDRZYWFxVjJNeXJLRTNXazdYcjRiNVdzSks?oc=5</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46031.73208333334</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Japan's Fast Retailing names Francesco Risso as GU creative director - Fibre2Fashion</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 15:28:53 GMT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQRWF6MlVnNnE0N2JNdkZUN0stU050NHNMV2lNWnZNelg2N2ZZcG5IYXdGci1aNzBFcGdjSkNCRGVhYU1RUTNRS2VPUHBLYXZ2X1ppSzdURXNhMEx2azZIdTE4dzE3VXpUbjJfaGVmS0J1UFN4Wmk0MlVQY3FjNmhPOXJuNXZwM2YzRk01LXdRX28xRm5jTHJQcTlNSFVWM3d5eDRMM0k5dzZ2VEEwZkNvQVJRNmNWckY3M1A1cWFRSFdpaDJLUHBaSVlPb3YtSlAwU2JOTkFZUWx0YXU4cjdha19OWElNNm8?oc=5</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46031.64505787037</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Shoplifting, other store theft suspects face Ga. racketeering charges - WRDW</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 19:57:00 GMT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQV3hYOFhDZXg5cm5FSUFydXRyNXRZYjNPR181OUZPNXNySDU2c1p1Z3NPSDdhTzF3bF85ZmZKTW4wUEJJMnozVVJqMEhoQ2JoZDUzX180OHg3RUFMYTlIX3BTZmkxbGJMbXZCYW1MWjFScmNqVmdoemE5WkZTeHhlZG12TEFhRHU1dUc5RDlQd3E2eGVMVHFXWlp4VmNmcF9DOVh0OTB2czI5eDhmNzFqTy1iSEcyd9IBtgFBVV95cUxQV3hYOFhDZXg5cm5FSUFydXRyNXRZYjNPR181OUZPNXNySDU2c1p1Z3NPSDdhTzF3bF85ZmZKTW4wUEJJMnozVVJqMEhoQ2JoZDUzX180OHg3RUFMYTlIX3BTZmkxbGJMbXZCYW1MWjFScmNqVmdoemE5WkZTeHhlZG12TEFhRHU1dUc5RDlQd3E2eGVMVHFXWlp4VmNmcF9DOVh0OTB2czI5eDhmNzFqTy1iSEcydw?oc=5</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46031.83125</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Saskatoon police retail theft operation sees 30 arrests, 42 charges in December - Prince Albert Daily Herald</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 16:23:48 GMT</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTVRtSGlicmZBY2lWeDhRY0pEYmNKLWpuQTFLdm1fb2RzLW9na083bkJSOUhDN2g3TzNzMFc5R0VDRDd5dXJ3NG52U2gtcHhyUjAtTDBpckVOb2p2ZHpiYUtucHB5S0c0ZjJxSzU1NFVSQjV1OW03ZTRnX2ZtaUtibUYwVW1id3RjTGpjMUp4UEFuRUluVWZWcHVoS0VyeVVDQmdvbw?oc=5</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46031.68319444444</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2 Women arrested for Grand Larceny at Old Navy store - 102.3 KRMG</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 22:14:54 GMT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQdDJaWXMxdXE0cFdNVl9LamxmRzdMZEloWk9HQjRxaFFGWnZCQ0N4c0NmclZja0tmNGJVQklHbzIwckt3eUN1d2ctWDJTMnR4bUVxRnd2Qm9Ha1hCQUg3N1lPaU11Y2QyT1dndThMbG50NkxQZEVJY3NySHlMQVhvQjNYc1NkdDRH?oc=5</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>46031.92701388889</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Sopore Police Arrest Accused in Bakery Shop Theft Case; Stolen Cash Recovered - Gulistan News Tv</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 14:58:06 GMT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNbEJXaE1Qbjdqc2hzclBSMFF2U3VvdFBHRmFmOS01N2ZzQXhxZU5NeHN5QlFtU0pOai1qejVmUVdTc2ZmTGthV0xKS2tMOUhMaU5KN3AySHlmSWs4WURRYlBlMkNMczUtd2lfejAzeVpJTTBjMERMYUNKQ0g0R216UVdiRGQ2RTgyMXo5QnRQanIxbzdCVnVQalExYXE4SUdTcTRXVUZ2Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>46031.62368055555</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Law Enforcement Agencies Conduct Retail Theft Operation in Rancho Cucamonga - crimevoice.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 18:03:37 GMT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOXzBXamFGMkVxdkt4dzBvVU5pTGg5T3IwQ2dvWG43NXZTVUNWU1lFQ1Z3S244bkp0M1hJQklBeG9pZ3Q1aEUyc0FWeUVDbUlOUlRBZVhGcTVDZ2gxOF9wM0Z6SU43YTI4WEt0dFloZ2c3SFNiN0c4R2g4Y2ZjWG1WcVhvMFdqcng0SEZFTW16cmFsVTZ3eUdMWUxNMnZQeEliczQwc3dfcWZYWEV3VldzQ1N1Ni0?oc=5</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>46031.75251157407</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Deadly explosion collapses part of Madrid apartment building - Euro Weekly News</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 17:15:38 GMT</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPbU5WQUxOVVo5NkxmVWZlWXl6cjVPd3htdUp4c0xoVDNyZk5UMTMzLWZSTmhMTjdnSS1OaWh3Rl93SFJXcFpuWUZva20xdUlRR2FjRHNrU0hFTzBCdUg3NVF2cEJ0aWd5cElPYUZzUHJpLUM3bktreGV5WUVXX21KRklEU3hiTUdtNG0wb1JhSmp1Zm02U1EwT2pfNGluZENt?oc=5</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>46031.71918981482</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Barcelona Make Transfer Decision on Marcus Rashford After 26 Games - SPORTbible</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 20:17:35 GMT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQMUNxbWR5YTdNenlfTklrLTRqaHc2bjRkVGNWbEQ5dHNKcUFERVlIWjdRZ2o0R2NiMlNjX1lpVHNod2lxSmlVUG5QNkw1RHhJeHdfR091SF8wR1B1eUtDSVVkV0lqN0NyX2VMaXFtSWwtZVY0Tl9tM2xMQVN3Wl92Zkx3SmFKWHlzNDBDYVVQZDhKNG9MZlVPNDBHRGJzZ21uSHBWTmlZSlVBUXgyT2wtSzRTVnR0bnlGV1FHaVdkOTRreHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>46031.84554398148</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Inside The Shooting Locations Of 'People We Meet On Vacation' - Travel and Leisure Asia</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Sat, 10 Jan 2026 05:34:13 GMT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxONDZrSHFmdEUyVEJiU1A2aG1vdjlFdkZNQmg2cnVrT3dfSnlPYUhtbWFJRTJualc5dEFxSTJoM0ItN0JUOWlkbWlQak9LMm9DN2JOUlZrRWVNUmNHRDNULXBZQlJ5U21PdTNxS0xzSVRNUFNtcko1aWNtaXh0WWdxcjQ4dUlsQ0U3WFdlcW56V0hWSU1PZmJqNVVtMlNId3FQLWFCMjZWVkNaYmNhNTF2RVNlVzVOY3NHejNoSUgzVnA2Q2l1UVVBclRlMDhyMWfSAc8BQVVfeXFMTjQ2a0hxZnRFMlRCYlNQNmhtb3Y5RXZGTUJoNnJ1a093X0p5T2FIbW1hSUUybmpXOXRBcUkyaDNCLTdCVDlpZG1pUGpPSzJvQzdiTlJWa0VlTVJjR0QzVC1wWUJSeVNtT3UzcUtMc0lUTVBTbXJKNWljbWl4dFlncXI0OHVJbENFN1hXZXFueldIVklNT2ZiajVVbTJTSHdxUC1hQjI2VlZDWmJjYTUxdkVTZVc1TmNzR3ozaElIM1ZwNkNpdVFVQXJUZTA4cjFn?oc=5</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46032.23209490741</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Fabrizio Romano Transfer News: Maresca to Man Utd TRUTH, Vinicius Jr BOMB, Guehi CONFIDENCE - footballtransfers.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Sat, 10 Jan 2026 06:52:00 GMT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxPb0J5Zl91YWpSemgxMFFoRUhiQUR6N0pIa0taM3J2WnhXYXhLN0dzM2pRTFR5Z1l4bzh2VGl2V1JZUDQ0NmZkVmNCRXZ4WVR4YnYwSWJjZGVjcks5bnM2REVyMU5IbmFySlZfQi1Sc1ljNVpQVFh4Ymhjbkk3eE05a3R3OTNkN3RWcGYwd1hSUkc4dmd0TGw1eDRoQVJwV2gyZjY2M3E3bWRFWjBPMkEyQ0RXeWk4bUMzTWtXRG5YeHVaZjlJaVhKdkVCcm1sQjk5dHE4a21pWS1EczBmUW43N2FHaWRsVFNhU2kxbk9KSTBRUUtGaHZQVHN1TjRXSExZYlltYk55Q0t3Tmg5MDdxZmVtU3N6cVJ1VThzSWlOT1BOQm5EdXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46032.28611111111</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Atlético Madrid 1-2 Real Madrid: Player ratings - MSN</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 23:46:49 GMT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPQkZxNXAwWFEyUnYzOWxpajFGeHpyUHEtMm9ydm1WX2lUN29JZm5nZThTTG8yNkduT0lFZy1OZUhQSTFSNTVJN09TSEY3T3czSEUyeFF5OXpxQktVTHhNQXBsaGdJbXc2VHRUWXNsZXNWUTI1YVBxUzFMcWFLa3lnSlV5Y1YtRkVmZ1U0dGplZ0N0NmowT09KMUhpWHlUOVNleUtDVEt3?oc=5</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46031.99084490741</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Doubts About Rüdiger's Participation Against Atlético Madrid - ysscores.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 14:53:49 GMT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQeUFYVnhfZDZNeXNIenNEVTB1OURaVU1BbTVXNjZvb0h4SE9ndVdCS2hOcTZ3M1RvSlBNUTNWeHFrZE5TeDc4UmRna1lDQ3hrWkU1S2U0ODRjbnp2SGsxbjdDZVgtWmFTcUcxWEQyaFhUZHltcmZlSm1ndHJqUHltUXRHdEtLUGxqVDF3emNSME9IV2tFMExyY3NqOGh1X1F4YlJ0NTNTOFZpaG80bmx4VnNn?oc=5</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>46031.62070601852</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Why did the explosion in Carabanchel originate? Hypotheses about the gas leak - La Voz de Ibiza</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 21:32:59 GMT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOZHpWYjBnTkZBbXY1N1MtdU81NVp0Y0dVbmRQMmJkNmJURkpFMmhkMHk3eHFRX3A1ZEFRTHdXQUxzQ1pmWlJMZXNoSjVkdHAwOVNTdjcyOEt4cUJ0TVVHUjJmeUwyek5nakRfYVp1ejlEQWJRNHh4X0VFOV93VTNnMTdnejRuQy1CX0VYaURBbDZraUdGclByM1docjI5emVyLS0wUnVfVG1iQWpEaXBfRy1YcFI5WTUxWHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46031.89790509259</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>One of Tottenham's best players delighted by chance to join Barcelona - Football FanCast</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 17:40:00 GMT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQbmo3Y0N1T3ROLV9JRGp0Tl9EX0ZHSWMyUWVmNXBjdFYweU1KSVJ2M1JUSzVQRGsyQzlsWWtvb2RNS210cnVLeFl1bW9ISGYtV25ReTJhRS1ocXY1MW9HNGJXdF94dU1GbzBIYkM2THU0TEZIVW1XMW1YRXV5dndvTjhWY0ZfS1A4YmpWTExXcUFTQVotYVJpQnpzQmJwcUl1NWZVcA?oc=5</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46031.73611111111</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>What we know about the fatal ICE shooting in Minneapolis - Star Tribune</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 20:13:08 GMT</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNdmxpUUFOVmcxVWdFOHIxbWJPZ19JTl9CbnQ3dFRfZFotaTU2QzJHR0x4LW9hbkZCZm9zQUhLVjE3V01wVjZqM2tBSjE5S2toanJGSV9OZFdFMC1tNzAzSXhtVldOSThXS3BqVXpmMElpak9nMHRZSTZpMGpMTm9NUFNTOV94YlFDVTJVUm50NHFvVGNhaTU0ampVODZMRW0teno5ems4cXdGaGtmd2JxaTNR?oc=5</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>46031.84245370371</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Agent pushes Dragusin toward Roma after agent remarks spark Tottenham backlash - CHOSUNBIZ - Chosunbiz</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Sat, 10 Jan 2026 03:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1YWi1hQTR4RmJjcXB2QUJKakFLT2tRZ0tyaklnZ2RzRWY3RldKNW80MUw5aVVRM0tUakJnM0dyLWlzSklYcmZDUzVrcWs5WDMxdDNLWHpEOVpHMk9RQVhFUk9kbDJrV1lUNjRMZDZpbEY5YmxfQ28wcG1aWk9fR2fSAZMBQVVfeXFMT3JmZ2ZBRVBFcmFZODlXa1hTY2NZcWlSb0wzZFZCYktoYWNQVk1JREVLcHhONEpBWWtYNUV2bThXWVpLMFdHcXI4bnNCdEZpUjNXQTRpM3lrR3haMEtTQ0dVUGRuc3p5RnpYU0ZVVEVzY19oMTU2X0RYMVhpSDhJd1RHRVljLURyNjNlb2tKMDkzWWF3?oc=5</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46032.12986111111</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Atletico Madrid escalate war of words after heated spat between Vinicius Jr. and Diego Simeone: ‘That’s a classic' | Football News - Hindustan Times</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Sat, 10 Jan 2026 06:42:54 GMT</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNMFlHZGZORXBLTnBQOXdCWG4zWVdXcmhGendpMkE5andScm5SQzh1WHZOTncwVFg5QWdWcHdTc1Z2VklKUVZ5WlBiTjhzUU5WTS1wWTZHdERiMGxBSWhsaERBR1p3di1DMm83bmFZVjlvRVA0Nkx3QThrQVdsVnhCc3NRN2F4dkt0dXhfZVdpUTdHV0tUTEl3S284QmhTXzFUbmlkNTVLR3l4YkpsRW8ySGx6ZW1KRWE1aHBJa0JLV0ZxYk40TmtBV2RWTEwwdVFyaUtrY1o4WVdkdHZYTFJpMHI4b2pwM0Z5WUZCNEZEVEFPWFlrSWlYVGN1NWk2S0xDZ1Q1LXlKa2szd9IBjwJBVV95cUxPa1N0N3hIaVpMZElhekFsaFZDQl9kaTg0WEdaQ2NmMmJqbGlzVF93R1VsWGFUUFNMYjNObTlSVGRWbkVVMi1SaGRFRGpzTjYxaWFaTjU2Nmlqa2RIYzNwWnpPdVVXYzY0eXJXVjRkY1F6T1BReXVGWnI4LWU5S0FHWWpERUhvZlNfazZsUlROOEVRU0dDVDZPeGwwcHA0VUtzRTFwcFJYZzB5bEU0cEl4MnRMRmE2NlN1QmhOaWJmbEluQXh4ZnFJRXdXelF3YVppZklJbjB1cXRzLW11QmZzQzM1MnpZWTI4dlhFSkRBQWhRemtPTHV2N3FLUkwxTnl6VHdlTTlNZFhLLXZwY3BR?oc=5</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>46032.27979166667</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>New Madrid County deputy in custody for hindering prosecution - First Alert 4</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Sat, 10 Jan 2026 00:22:46 GMT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNZWFvNlBMYTJwaWdhOGNqcDVCYXNxcFdvd1BVUUg0TnVmaEw4MnRIN2hPSVhBTlRqRE4zUnNQOUh3dVVzbFQybmpDcHBRZWhsV2Vyc2VqeUpaWENHM3REYUZ0dzBvWE5QVDlBVGFDVjlLSVpJZ05fREJaRVduWC02RU41dUxHWGR5aTFDU2JOREIwOWxPZWpEcEtjTktmakQ3UlE?oc=5</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>46032.01581018518</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>High-speed shootout: one car opens fire on another on the main road in Vila-seca - Diari ARA</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 20:08:22 GMT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQanJEcWJZSGstQmRBWXJvYmRNZmdpenZmZmx6clZqak9VRGlhOWUyU0pJNDlGRVYxVkp3OXZZOGhhVEptUGFBZGVJLWNvQWZjZGJsdVpuSXlnMmZnMW9VRk0wX0xzMU1NSXFzQmJLdFJ1VmZjUjBUR29Fcjl4Sy1yRHVlRzFwbmRHUENTNnFPZmVDQUhpZ3QwVWZ4OUp6TmpjUXFVUmZEMm5SelJhdXpHdEVIMm01Z9IBuwFBVV95cUxOTlI0NWVYc0dTTmxXQlNERXN5aUVwck41VjZ5QVE5WkpwTGl0UWNZN1R3Y2tnYmh4WjJmWkQxSnpNejFaMUtIVFd3OGdZM0d5ajRyNWRWNWdkRUk1OWhjVGdaSUdMbTlGQkFKS2JMRFVtWk5mLUk3U1hYcDc0TUxaWXQ1aXlXak5lVEIyNktKUGxwM1ZUT1U3TlJaZS1EN2FmOXRFMzRvaHFzZUJVVWxfQndwSGJQRkl2VE4w?oc=5</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>46031.83914351852</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>'People We Meet on Vacation' Is Full Of Vintage Fashion - The Zoe Report</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 15:18:29 GMT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1CU25YSjlwX0g2SVhmUk1OOERQekJKcVJSam53cVd3VzVXalJLM1FOcFRBY3ZpcFV4d1J5dXQwUl94QzBUN19pLWJmWndwNXFCYi1WdlZLOElEajRQaTgyWHBqUGNZY1Z1bWFYT3RFdnc0Q2lLdndRb1pIdEM?oc=5</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>46031.63783564815</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Barcelona secure future of 15-year-old eonderkid Ebrima Tunkara - Tribuna.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 21:31:20 GMT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQZmhsdjhKRElDNnB2X2w3bzdjTW1VRzhxS2Y3LVBELXF3TnhRWFcxOXV5X21OUkRzOEw2MlJZbTFTbm52blZOeGRybk5FNklkRmlGZlpkVGM3UmhCbUwxU2pUZE9kUjhDdE1BOERjMkZfdlF5U3paSVIwSlU3aEE4ZnRQYTdPR2lQYTJhRy1qazZJbnZWRWlOaTRnZUNiNVZOQUU4LXlwRXHSAagBQVVfeXFMUGZobHY4SkRJQzZwdl9sN283Y01tVUc4cUtmNy1QRC1xd054UVhXMTl1eV9tTlJEczhMNjJSWW0xU25udm5WTnhkcm5ORTZJZEZpRmZaZFRjN1JoQm1MMVNqVGRPZFI4Q3RNQThEYzJGX3ZReVN6WklSMEpVN2hBOGZ0UGE3T0dpUGEyYUctams2SW52VkVpTmk0Z2VDYjVWTkFFOC15cEVx?oc=5</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>46031.89675925926</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Timberwolves coach Finch gives his opinion on ICE shooting of Renee Good - Diario AS</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 17:25:41 GMT</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQUnJCdzlkZW9CZzRtM0dKYm5xbUpGM0s3bGFoWEhnLWdXanRzS1loV3o3MXp5azRscmtPbmFvX001SFJoMl9NTy1zZ0xId3dwbU5UTmZqcXA1amVWVGw5ekFRejZteVBqOGZQd3dObzZJaEt0cGttZUNhakRhZUpyenJCZkhBT2xpaUtWdnNyN1MyRGZydnJJa2VPczVWZl9vaTZtRnFHaUJ0SmJ6Y0pmcGJHT2VlbHdmM1FsStIBvAFBVV95cUxQUnJCdzlkZW9CZzRtM0dKYm5xbUpGM0s3bGFoWEhnLWdXanRzS1loV3o3MXp5azRscmtPbmFvX001SFJoMl9NTy1zZ0xId3dwbU5UTmZqcXA1amVWVGw5ekFRejZteVBqOGZQd3dObzZJaEt0cGttZUNhakRhZUpyenJCZkhBT2xpaUtWdnNyN1MyRGZydnJJa2VPczVWZl9vaTZtRnFHaUJ0SmJ6Y0pmcGJHT2VlbHdmM1FsSg?oc=5</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>46031.72616898148</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Mbappé and the science behind his speed: how he reaches 38 km/h - Pasión Fútbol</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 16:59:52 GMT</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQOUhvQnIwbi1rRzAySkthdnRzZkVxanlIaEFteHNZbmNPTFpXT2RVZkpBNHM4dXUtbG05VTdud1JHcFZUV19pVURjWGtpODVjOFpzRmdaUXhmaDZ4TndLbkhzaC1Da2pqTEFLWWxXaU5QZzJMTDJXazRIRDdSRmdhVG9fM1pIZjBVb2xrU0RRZHFjajJjZlJBUlpHUFVwaWx3N204Tm82azJXa013cHl4SDhRd0NlOVFK0gG4AUFVX3lxTFA5SG9CcjBuLWtHMDJKS2F2dHNmRXFqeUhoQW14c1luY09MWldPZFVmSkE0czh1dS1sbTlVN253UkdwVlRXX2lVRGNYa2k4NWM4WnNGZ1pReGZoNnhOd0tuSHNoLUNrampMQUtZbFdpTlBnMkxMMldrNEhEN1JGZ2FUb18zWkhmMFVvbGtTRFFkcWNqMmNmUkFSWkdQVXBpbHc3bThObzZrMldrTXdweXhIOFF3Q2U5UUo?oc=5</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>46031.70824074074</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Vorcaro nega ao STF ter contratado influenciadores contra BC - lnginnorthernbc.ca</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Sat, 10 Jan 2026 02:03:21 GMT</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNUHh0RXJnbG1MOFFMbHliVS1RUW9CSDI1ZkpqWXpmMHRjLWluS2tKbGJ4VmFESHZZemt4OFc1dzZmdkxwRk1yTVhBdTFmR0hDUTZPQ0hlbGtod3hJNFY5c3ZPVEFJUmlnRFN5X1VJTDJCcFZCUEdoVjhpRmU0S0d0WVNTSUY1enpIUklkUUxHbXUyd0dEMW9FQjFxZWNrdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>46032.08565972222</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Rapper Kali mentioned his beloved daughter, strong words: Since I have a child, I am more and more aware... - lnginnorthernbc.ca</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Sat, 10 Jan 2026 03:31:19 GMT</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQQ3FqY2x3dlZCVWhtTGVzY1JlODJlS0lsY2YwSWRzZ0g2Y3h5MTNpUkZiNTFIeWRWWThxQmMwdy1mYThOX29ZNXRoSm5OXzdmN0RIQkU0TFJmRjJ6R1VpaVI5ODJxeTdkVTVRWWE3UjQ4Yi1wVjh0ZUp1bE1vLTc2VjF1R3FESkt4YkZfX0kxMk5ESlhuYml3RjJ6TG4zaW42NThBTHRabm5XdGFIZjA4NzhESUJFNjgxZEpPUzFOeWNXTzJGSzJKQ0VEUVhlVHJvazBlUEg4SQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>46032.14674768518</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Lamine Yamal’s Absence Due to Stomach Virus Ahead of Spanish Super Cup Semifinal - SSBCrack News</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 19:56:40 GMT</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNckZjZkE1WW9wNThjb0NFZVdGcWM0aHk5NnBNTmoyYW1VN0RQMF9rcnRzWXE0VUZDVjM2QTNxcWotZnE1QmZicFFDYm9kWDNRUFdyOUFibWN6aFJnZTNqWENjd19ZcWR5d0JvMXBMa1ozRDBnTU81eWJpb3owWktJY1ZYbkhyTEF2REZvVFdIMTl3UXhtSVBKeHA5am1ENkhJMkVQQWh5NVVyUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>46031.83101851852</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, Spanish   language</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomba" OR "amenaza de bomba"  OR "explosión" OR "paquete sospechoso" OR "paquete desatendido" OR "explosivos" OR "explosiva" OR "tiroteo"  OR "puñalada")</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Al menos una persona fallecida y nueve heridas tras una explosión en una vivienda en Carabanchel - Libertad Digital</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 16:23:40 GMT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNYXN3UXdqeWd6a1JFR0R3Njd6b1ZFZ3Y4eXhwWEtVM1MteGpLdEpYd1FqY3lNLUpZS21MbDlQWHJPcWhkdERLM2FjcmlxY1QwMm1jUm4yR2V3bFpjMjc2TlVqZENjMURuMXhHRFljdnZkMktHZEQzVG1LSnVKdnpnOTl2dW5LWl81M0FHZ2NxS3NXZGw5ekRIR29fRDNBcFpYRnFkdnZGQllhOFJaTEVkWUFrR0hLX2NvbGQyYmZtc3JQS01hb2pCaUpJcVVBNzRzQlpWVXlrUlJrSGdvN3lWLS1uZXMyYXJzeFlLNdIB9wFBVV95cUxOaVdhNV96TjN0bEQ0Tlptd2x5YzExa3BYWU9DRGtEZGhONVFtNXBHYWMzVUMwNFNxS2ozaE1iMmZZM2J1X2x5dXl5M2V4V1ZXV24tX0lLeHFRNXppM2t6bEdRcFJQRWZ6V1V0LTBZbFdwclB5TWo4a3RySDQ0d1UtVS1oOUhtQ1YtbmFwNzdLQnNNR2d0RkgxUTJES3I5Q2JLWU8wZU1zY0JZQ08ybktWMDlYMGpXdnhZY3lzNG5RMU9BZW9qRGNtZXRuS0xKX0VXT0M0SjZYcmVXb2lLMF8yaXNwUjczMzB3LUNEbk1oN1M4dWZwOWFB?oc=5</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>46031.68310185185</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, Spanish   language</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomba" OR "amenaza de bomba"  OR "explosión" OR "paquete sospechoso" OR "paquete desatendido" OR "explosivos" OR "explosiva" OR "tiroteo"  OR "puñalada")</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Respiro para los conductores: la gasolina y el diésel caen a precios de hace años - Libertad Digital</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 16:24:20 GMT</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPNGlEX1NrQTZsaURjTmE2Mm9YazZkdnNpNl9HRS1KdlJkdU1rVTJqbE04WDhPUUlKVEIxTkFJbVFSNkRBMndJYjZlMDFDYkFuUkxHd3JvRS1UWUlnUnZGTjJnRm1OeGRhMUdISDN1RWtNVmZ6SWJyYzloYWN0aFhEcEFwT2hrRHptWkw1ZDB6TjRJM1d1RVVrVjVXeXpSM3VHMjZZQ2xybDhSb3JrVy1pZS1DeTNyYU9haDF1TnhEZzlBRExqLV9rRjFrdDZmMy1aM2FxYzV2MC1OVGRYeDRLYUxRNXRIdXUt?oc=5</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>46031.68356481481</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Village Search Bicester and Kildare</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Winter in Bicester: Making the most of shorter days and longer nights - Bicester Advertiser</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 23:08:06 GMT</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNRjdLbk1MeEk1NEdyTUNiOXFlTDRZT1hxdmF4dUZQQkdzY0Y0OW1rT1RNNjNBWS1sWUNGSXFmaGRFdEszalg1bnBtVTlzMzNQNDNyTVJnUzAyOG9HbWZKYjhXTzRvZWJJQ0tMdm5aUElZRGNSZWRHTS05M2wwd0RZTUZVZElXZ3otRTZnUmpBc3JuRG9oNEJxLXlYTF9qSUZf?oc=5</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>46031.96395833333</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>New York man jailed for hoax bomb calls to London venues - BBC</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 15:37:48 GMT</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxORDlIR0pPS2EtbFppU3RjZG9VNTZIemFOWEM3SGdGTlpyeDJwcGk4V0dfd082bFdaNnc4b0FTMkdSMFlvWWdWcGRYN1VaT1BuR0Y2Q0lIckMxQUhEckdVbXNkOEJsdlYwSVh2emZpczh4WWVUc2p4YXQ3eUZFSkIzbGR30gFfQVVfeXFMUFNWVzI4bHctUU84Ti1yOVFSc2ZFZHF3b2hCaVVRU2hHa0pfU1d4UGhhQVY1NVhzQmpmV1h0NEdrSmVWb3RGbW5ZT0M5TWJGMFQxNzgxOEJOU1lKSG80U1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>46031.65125</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026 film and high-end TV productions shooting in the UK and Ireland: latest updates - Screen Daily</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 19:21:44 GMT</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQZmNMRTBhWHdsbFo0WHUtenBKUWJ0Z09LVVBuTjVUb1R6dnYyV0UwSEluX01NUXJuVzhuVlZCTUlHanpOQ0hpT1p4N2xGSnIyaEg3eGRKQ3BZVlJWT0hPREU4dmd2azc2VGVhQVl2emFKVmpENnNrT3BJNGVDY2xlNDVSUV95dzdPcHFtOHhqcG9WbUdYYU9odjhUTHp2b0dzMTZ6Yzh4U1VGNVVfeVl5RmQ1eDJpLU91MHlMUS1kZlZNNng3LTE1VHNIb1o?oc=5</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>46031.80675925926</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Police issue condition update of man in his 20s fighting for life after stabbing - london-now.co.uk</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 17:34:22 GMT</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOSWl2dzNDMFpaY3VTRXNIYkFfdXJ3V3FJZVJPTDZwdmw2SEI3X0lPdlZxNVZ5c0R0aVlXcHJEeTVKbXNoc3E4WmpacmVZTFJPY0dlZzE4Nzl3bjZfb21IeHdGV0EtYWJidHJlYWJ3ajZJUlRUMzYwa184TGswbW1EQWZYSklBb0NkQ2V4cmM1UEQyV0g2QzVSag?oc=5</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>46031.73219907407</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Two men charged after triple stabbing which left victim fighting for life - london-now.co.uk</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 17:09:35 GMT</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQcmZVcTc3aTAxdlVKWnpOa3RsdDc1WkhSYjZmWkw2WW40Z0dVZWZ3LXUzVy1lZjFmSmVWSFlHbnJDUFUzdWFObjN4MEdxcGVndlg3eWt4Nm5adWZoalpJSERZcmFjSndmZzRhbW10SGszbnlfQXRXSnhReTRIRGQ3WmhGazBsSEdBRkhLeUx3VmNHdi1BWDFWMk1TN0FTeW83M2FqUjM0Ykw?oc=5</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>46031.71498842593</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Second man arrested after shooting in Bexleyheath - AOL.com</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Sat, 10 Jan 2026 03:43:42 GMT</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPZHFuSDNqc2NuelFUQmRmbW1TS2dtckMzQjREOTJneGNtdDJkSFZoV1pwTDVkMkU5QnVmWld0WDVtLWJGNk1Vam5aMHhwRENybVF4LVppNTBXZXhmWDZwdDdicDBraWpjeWxsUlhvQ1F0TWV5d0NwYnpZMVo1cGoxYVNDMEw1RGo1Yl95aw?oc=5</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>46032.15534722222</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>'Miracle we weren't killed', says student after Finglas home petrol bomb attack - The Irish Sun</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 19:25:55 GMT</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNZmhCamJsVk4wT0RpMmJfV3JoNkRoVzhHeGZEY1RUbnFZOWtBV25tN0RvbGVkT1BRb2RzVjNnOTQ3WTVoaGYwUVpzaWpUUUpSWU41LVEtMzVlQWVSd095RU13R00wNG1QZVFSdGFXUzk2eWkzcGI0LXhwV3lNdlVLVUo2WXMyWlY4VmppZlJ6bVA0MXpC?oc=5</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>46031.80966435185</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Four in hospital after sheltered housing fire in Chiswick - BBC</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 21:34:34 GMT</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE1zVUFpVE5jc094WUhyZ051MXNHYS1iVEg3OFhHbHFZd1FBTy1LOHdWOUozWWtndDJDN3RhUEU2cU9CWGZZS2xCV2EwYm1HZVJza1V3U24yaE5BNEJCWEdR0gFfQVVfeXFMTXNVQWlUTmNzT3hZSHJnTnUxc0dhLWJUSDc4WEdscVl3UUFPLUs4d1Y5SjNZa2d0MkM3dGFQRTZxT0JYZllLbEJXYTBibUdlUnNrVXdTbjJoTkE0QkJYR1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>46031.89900462963</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Samurai sword wielding stabber pleads guilty after Oxford incident - Oxford Mail</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Sat, 10 Jan 2026 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNXzZxM3NfUDZtc1Q2UGZvM04tYVJTZm9tU1o3Qjktb3UwRklzdGhmRE02WTh1emE0TWYteDVpbExuUXZWTWRUOW54MnBlaWh2U3FJd3pkN0dPQm93aDFaMmtfTVdpN0J5RkdCZDlEenE2OHVNNFZ6UHRKeGp5SmRCa0dIUVQxUmVEbFBRNTE2V0N3a1FIeG5rMGx4SXRWUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>46032.20833333334</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Wrongly released sex prisoner Brahim Kaddour-Cherif admits crimes - BBC</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 18:05:48 GMT</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQZVlHOXlzd21xRUFkODlSbTFmMlFYaFlzbE9MLXlsWlVrTDlITVFmelRzSFhYTmVZSEt0bkZZQzdOa25iR1YtLUVQUXU5REMzZm4yS2xyWmY4aUoyN2IwMmw2cHkyZ2thM05rbmNBZE5GdTJJTmJjRVBhQ2dJODBwQWVB0gFfQVVfeXFMUDZkMW51N2VGR3Vxdk5OZFRqSEJ4V0xmdFBXRDlOMkNfQzVWTm9QRVA4QUxrS3FLU0pYUWlzZVp2dHNEdkN0VGd4TlVYZENPeFRxVHNhOGJPUDRoV0huUmM?oc=5</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>46031.75402777778</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Swindon cordon lifted as 'suspected explosive' item is a replica - BBC</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 18:43:17 GMT</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBQTkZiUjJPQ2JlT1htYXczcUFTSVlJeGs0ZjBodGZTcjhXZTZUUlBTaVhkaUV3WkhIUFNlcTRXSFBEMWxvb2FVNWR0OHMyeDhWTHJLdVVQVVhUd9IBX0FVX3lxTE1zamY1U3NJZHhkZmdmaS1LSmpVQkdQRFVPX0xPU3VmSjZDQjhlcDAzNW8zX2VqNGlHcVl1d3FaTEk0Z3hDdHF3TWlqdktHaDhGNjdUbDBLa3ltNnpETHc0?oc=5</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>46031.78005787037</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ex-Chelsea employee spared jail after £200k fraud - BBC</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 18:54:06 GMT</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQdDZBMzNHUHR5Q0lRUG02ZUEtYmpEN19xblVfM3FGQUFrLTh2czhpV3RGY184VVY1bm1MSVE5LUM2bGVZWmcwZ2pwQUJyRl9CRjFRMEJ6T3NTeV95QW5oVTRkR1dNWUh5UXlfR3NDdDNTSnhEWVVySXpVWG9MazJZcU1ZNkhqaHQ0bUtZSDk5YnVrMWFXLUVhZlozQ3JpYnVMQk8tOWktTFRNWmRMUzMzSmlJLUFLSlVxNDE1ZUtWblA3QWxyRU4wbzJTb0lZX3pjMnFRLXdxTDVVQTBpa0U4bEJ30gFfQVVfeXFMTVlwbjZXNTBSZVdmVTdtV05ZaDBwaXJ3OW9oNmgyMkF4dEN6cndoRUhVeHVEYXV3YmdTZmVLVE9jS2ZubjZQN1pFMi1CSUJaTjB0UjB2aVlaZEJ4RFFrelk?oc=5</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>46031.78756944444</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Surge in Londoners falling in icy weather as fury mounts over ungritted pavements - London Evening Standard</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 16:10:05 GMT</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPYUIzMnFUUnQtLTlGOUNWclZjWW95YWdEWnVSU1NVcUloaU5aOXYtd05zb2VreFd0MDlEbU9CZzVrSU1ZREQ3R0NoVng1ODJycmdPTU9hU3VSSWxWaVZBWEtsckpkdjVDbVBHQlRZM1paeUIzR2kzU1R1Q3EtTzUwd3BuNTB3MXptTXFtWVZlNVFodWNSc2tCbWgzRi1tUUhXdHlRS3c3Q2o?oc=5</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>46031.67366898148</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>The Traitors sees explosive row in the turret and fourth contestant murdered - London Evening Standard</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 21:46:53 GMT</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQb3d3ZWt4aUh2amI0RU5VNXVmZjdaN29RQ1NHQW1UM05aOGZ3WkNBQ2JTUDhJMEVndS01UGVTOXlZT2JpWjZrVkR1WUY1d2Iwdmt0WkgwT0dNNHdjaGd6Wk8xX29Ob0ppWTJZNTBtYXNJQkxRZWlaUlBqMVNTV2RvQ2F1VTc4alVFNlRQVTU1NVJta3BHNVltY1dFMA?oc=5</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>46031.90755787037</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Police rule out terrorism in UK train stabbing attack, after two British-born suspects arrested - MSN</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Sat, 10 Jan 2026 03:13:36 GMT</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wJBVV95cUxNdG1ocnVuVlBmaHZvTThNemM4bUR5Ui13Nm8xZHl3blFQTVoxT3M2VkFIdU1mamlHZHJGTmNfenpXVzhkLVBHeGEyby01NVRzLTBwNTAya1BRS1hkZTY1bXRoeW1QY0gtQ2drSHhxaWlPeXczRFQ3UUhfNWVZalZBQkIwZ002WDB2b19VNXlid25CYkFEdFpGZHM0eTdQdzRHZ2t0MV9mb0JOWTBVOF9YMF9idFA1RWJwbW9vaTBfcHVGMC1jT3IxSndkTUJBb3dCODk1RkpWMGh4QTdVZ3Rkc1ZqMHZXbHNTMlZMcXZaUklTX0pial9iQjlyamlWRWVDZDdRcVp1Vkp1bE9GcnpQQV9lZFQ3Zm1MX1N0bFVhZmktQVVIRUdzcmYwM09mdUdHcWQ5MG1KOE16c0o5UGtQRk1HSTJ2M3hDZ2E3RHQwM0tmZ0lvTWpYa2V4SmJWWEg2XzB5R0xDaw?oc=5</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>46032.13444444445</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Rabbi Andrea London to retire from Beth Emet after 25 years - Evanston RoundTable</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 17:31:26 GMT</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOR0ZfcUlNQW9XREJVUFg0bVQwcjJqNDBZdGRqRGgxNm56aWVGNnU0REtfTTlDeDZ3eXQ5N0pUTkNDcUFWSEVSOVdkSFZ4NDE1NjBZWUR6VmRiMFlkRGJSZHBsWHk5MklDdkYwYXRmVGFvNnlwazEyVi1rQmJ5ZHVwRlhJeDlYMTVhZkFwYUktaVF0Y2ZzU3ZTQUhyUlc4QUNGVmgzdA?oc=5</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>46031.73016203703</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Fundraiser for family who 'lost everything' in Finglas arson attack raises over €60,000 - Dublin Live</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 15:30:43 GMT</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxObTFmN3VLd0ZQTGVoN0xKd2haTHlmTWRlTG5FalZHM3Yxa0hvRWRXM3ZYSXBSNUpDclZSUkRMNkM0U0hmUmxHYWVTbUNiVUVGaW5ycFU2LWtsLTRiZEcyeDJIMkVHWTNnQ3hxUlQ4dUxDelhGek9oRDFMT2hnM2F5bXVOTl95MU5ZbkF0Y0J3aUQ0UG_SAZgBQVVfeXFMTUhzR0VYd0hUM2Y5OWQ1YndmNkM2LVNIRGlvWXBDOVdUVW5mTUdqRDJoemcxaWpLZkctSzhweXc0VlRCbHRNaXg0YW43b1lBSGNEdHdSSHBvQXgwUm0zRVQ5bDhVOGUwUkhFQlBJQ24yY2JDTUxJZjVQOE5jR0dhUS1ENlBLYWlWOXdnWWxJMThYVzJXZkg1aU0?oc=5</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>46031.64633101852</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Tri-Valley Protesters Honor Renee Good Killed In ICE Shooting, Demand Investigation: Report - Patch</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 18:08:46 GMT</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQR1BBTzlLZEpyRlBQTjlnTEN0NnYtX2EzMHI0dlduLWZkWFdfZDZVX3RmdFZubXlnclhURjNVYlRPNmFQbURVZGFCWnNTT3BQcVA4QU93TklEaHhCVUJNakk4bkY2S1NPM196R3pSb3FrZGZrbDdDcHhqaVRpbFp0dGd5bGFCZ00tRVc2TUxZVWVESmNNVVB3SzlFdUg2UXBIQlBvOGJ0VXVIdVBfV19neC16Ykx3VGfSAdcBQVVfeXFMUEdONmJjSGtjT1FYQW8wb3E1emNCOVQ2bm9NZEdiRmFPeXdmTDZIYzV5TzBnYlJvcXg4RVhWTGljZnk0YmU0WFpRbHZ3cFJtMGI4ZEZIY3N3MS1IelE3cTRsQVBVU3pqbm9xU291NlM5RTRTNWlPeFVlN2JPOGprOGRQRUhvQ0lvdzE3VG8wMzJXbEV5OE5TMjREdE5FdmxVRDhNYVpxS0NsX091c2NyY0gxM3FzdzFvNUdCLXlmOC1McTgtYnhKbzF6aVhPTEMxOHhYa3d0LTg?oc=5</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>46031.75608796296</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Four charged after shots fired in McDonald’s parking lot in Sydney, N.S. - CTV News</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 15:55:44 GMT</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNNExnWklyZmpGRnhhdEpOR3Fpd0xjRmY5N3JmblRlZjVOeTVaV2ZOM1VqbmdSZ2pYeHZPN3M3dDkwY3lsRlp6N1ZUUTdXSTU4NWEwdHZMbjFrUGJvaU5tTFp6bTVaZHEyeHY4NzJUd0N6RHJpZHdqN0QtQzRTUHFRbGVPV1BHYUdaQkdFZmlVRFQxMTV1ZG5xOE9OWEJsdVRjUVptZHZ0c2t4MHhISUNQNzljc29PNXVWaUMycURn?oc=5</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>46031.66370370371</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Where Was Primate Filmed? All Shooting Locations - The Cinemaholic</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Sat, 10 Jan 2026 03:28:47 GMT</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBxMG43YTZaVUhZSlYxTGRoeFo5eDJhcDhzbHVDa2dEOXVIUkxuYWhDbkJTWG9Ic1pTLVZBSzFtN3g0SUJNWkRlMDZaU3QwdU5Xd04wdVBSLUtwTFYx?oc=5</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>46032.14498842593</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Where Was Greenland 2 Migration Filmed? All Shooting Locations - The Cinemaholic</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Sat, 10 Jan 2026 03:28:45 GMT</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5SeXprRE1BckZTcVlXaTczY1ZBelpFbnlhbXE2YldSdDlMS2NaaTlSS1VsTHdpSUhRWHpzWTBaZFZMOXhMNUxaSXo4NjBSYmdWM0xkS2dnaDlZQnpzNFJsX1lnd012MDdRdFpBajJMUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>46032.14496527778</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Anger over Minneapolis shooting probe fuels protests - Le Monde.fr</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Sat, 10 Jan 2026 01:24:27 GMT</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQQmFzZVBXR2oycW9mTURwNURsN1o3TE1wQ0hMaVM0TnVQbUJfcEk2enJsazA3MGtwNThOazM5Uk9uemcxTkg1dnowNllYd1VJam9tamp1SUNGZGYxNGZkZDlCYVNsa1FVQ3ZET1hMTmxGRDRrRWRzUVJPQzYySmVLNWRrNkJjdWl4Y0EtQ3FJYVJVNDlJSW10Yl83UGRyX3JPWC1qQUplcUMtMk1oVFF4OW5DV1NwTzhaVmQ2dFN4Q2hXd1Ni?oc=5</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>46032.05864583333</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Russia fires nuclear-capable Oreshnik after receiving security guarantees plan for Ukraine. But its warhead less effective than standard bomb - Euromaidan Press</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 18:01:30 GMT</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAJBVV95cUxNczA2U2Uza19hLXFCMnRjcktnSDBwZDJBZFE4Q0UySHRncEcwM2hValQ4N0c3YklvZlJuSmJyTzRSbTJKN2FUQUdmY1BkZHBVTFpVY1dnZXhDNFdOV3ZsbnRBZ0UyRWNhaEJ6OEdkYlpXTzgyWmJaMHJnNXhfR1ZtdlN1ZHEyWU1yZDkwWW5MM2ZMSHJtSDFNRnBORTBVQ2gyTXdQMGcyU2ZmV2NoRDFQa2tSb3N6dHkyWmt4ZXZqUHBhOVVJalJQTjNwa0FwOFh6U1paYUhkYUlacHd5eTQ3OGNzUjczbkdXcXNJZDNHVVlqYmhjN3NDV0FoSFE3VXdnOXYxbl94Z0hZX0YwTnZPTEFkRWhFLWRu?oc=5</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>46031.75104166667</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Ukraine war latest: Moscow launches major attack on Ukraine - as Qatari embassy hit by drone - Sky News</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 15:47:08 GMT</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNkJ3aEU4VFdLZnU3YWlid1NUcmYzQzY0MWVhaHlSRm41OG1WcUJvQmVsSWtmT056OHVRazE0YVRkcHJrQlJCNmtwNFdxOFVpNHpFRzFWNHJOd1ZTcVVLb1RLb0liY3l6dG9ORC0ySTl4b2xxelg4Zm9XTGN4Zi1zUlRLTFRKYjZtT2dLaGgxanoyS0hlaWZsTWkzSnBuaDM4U0x5WQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>46031.65773148148</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Gamecocks Back Home Saturday, Face No. 18/20 Georgia - University of South Carolina Athletics</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 20:16:45 GMT</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNaHFqaENBNnMzTmxjVlRaX2t1MDYtMzhCTmpxeFZvLTlpaVhjY2thelhpeVBvQlFtdkhOU0FZVDI5QWxEczVPTHFzbHg5X2VKcmJvWDdYSFlxU2o0cmhTRDVjZWhYVk82cmZ3UlJxNk92NmZhdVk2R05OXzBsQjd3SnZVX0pZSlUyQi14ODJESHI1aWVtYlY2bTl3OA?oc=5</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>46031.84496527778</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Groom in Viral $59 Million Paris Wedding Pleads Guilty, Given Probation for 7 Years - People.com</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 20:36:44 GMT</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPdUROWFJScjJfelJiWTBtbm9Kd1NBSm1VMm14MjQ5VzFCUVVPQkxEU2lINlFLSTZrZHdfSktNR3RRSVF5X2h2Q0xheDNCemJ6WFdVSlNoXzc5aXRxb2VMWmhuMjdYTnNGWGM0SDZsTVpBQ0dWY0Nod1hpcnVSZV9ITFh4bUVxX0tjbVliNnNqbmZZRTE1UXZMWW9mZ2lUV01iblNjaG85bW1YRUNBcEwzbldn?oc=5</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>46031.85884259259</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Video: New video of immigration officer shooting of Renee Nicole Macklin Good - The Globe and Mail</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 21:39:34 GMT</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONkJDdV9zQVNXWlFNU3QzdExrQ0pLZlpHb3pXYXpOU3hPOFc0blFYNFZ2Yk9LT2xEUUN6UDhqLTE0R0ZpR0FrdndIR0c0eU9ZMVhQNVdYM1dCaXpNcTdfc2RMUjI4czRDbHJodTVJeWtaRDRZekxLTDg4TWVfUk5lSXpXZkRIeHpRM2Nrdl8yVlBFNW5NUWNMUC1WQVVwRFg2NlJ3emhlMjhJSmkwaVlzWmZGOUt3UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>46031.90247685185</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Bomb threat to Guv: Kolkata Police detain one person - lokmattimes.com</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Sat, 10 Jan 2026 05:23:14 GMT</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPYkNpNVpBaEtmM2pNc1plVUZzc2s2YlFLa3o1QzlSSTh1dlhBcFpUTlBtOUo4UDItQkdaYjl1ZmlaalYyT1VrUWgyTjhRSWdnN2J2NjAtOEpyeWVIUTI3d2hCd2o1UkRicWhwOGhpak12NEZOMVIwNVhCV1RnTktvNVZvaGJkZndDUG5JY1NRbmsxWTDSAZgBQVVfeXFMTTlYNXJfQlBUeW92c0xncHNQX3FPRjR2UFB5Q1dsR0FWc1ZkVU5zdGtpMWRraWZ3QjFBTk9DRXBQYnFVWGlsdmZtNXZSU2Y1S1lUd1RHZDBWWFdBYkN1SUVjTzlWdXktMXk2VWllLVdXU3NMOHpISk5yZ2k2a3o2R3pMVEJQOWxscXEyaHVYMjlUYmFvdG4yOUU?oc=5</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>46032.22446759259</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Brownsboro’s Miller erupts for 30 points in Nelson win - KLTV.com</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 19:58:11 GMT</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPdW45WVlvNDJWNFlyWElMRVJYQWNKMkRxVHlsb0U4cllMRGItNG5YN0VFdzg1R0VqQW1YXzk3TllUdlV5VWljTksyRjJpTk5XUGJoT3pEdEw1emJQVGh5N1k3QUl6TTFvb20zZzg2TzlYWWhtT1pFelpwNEFvWWJ5T3hWZEJ3YkxsQkZOMTZzZEt4bWFhTmtnQkZ30gGaAUFVX3lxTE91bjlZWW80MlY0WXJYSUxFUlhBY0oyRHFUeWxvRThyWUxEYi00blg3RUV3ODVHRWpBbVhfOTdOWVR2VXlVaWNOSzJGMmlOTldQYmhPekR0TDV6YlBUaHk3WTdBSXpNMW9vbTNnODZPOVhZaG1PWkV6WnA0QW9ZYnlPeFZkQndiTGxCRk4xNnNkS3htYWFOa2dCRnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>46031.83207175926</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Woman indicted in shooting death of girlfriend - KATC</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 21:30:13 GMT</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOa1ZHNktiTTluM3BtYUpxWkRMMVF2VTU1WnFLcmxfNkpvSENCaG9WYy1JdURIeHFUUFFZVTR4M05wSEZ5aXh0MFNtNmZuTHpSNTR2dmMxb2NQZUY4dUUzNFA5T2VyTDlUUVdLbUJiaTVNcFdLVnZtN1YwX0lMTHNzSVdNWXUwWTZQSDZvag?oc=5</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>46031.8959837963</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Iran’s exiled crown prince rises as a figure in protests, decades after leaving his homeland - WHEC.com</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 14:23:21 GMT</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPelFuVU0zQlNsQWZpQlFtZzFLMHVKV3FfNVZWQ3gxNEhfWWtpRG1acThWYTE2QTNWc0JFT1hneENBLV9xdXozVlQtcVpEMVFHRjh0WndIRDd5czVCV3RrdmpzT3hPY3F1SlV0TnRqYVN5RVJKaW5jdkJjWWxaaHc0S1RtVFl1cUZ0YTRxdzBIcUpEckJVRnV2bXpETkVOa0hRX1I1S2dORXNPUGY4N3FJZXhYdDY3MFJJMkZnSjBaRFg1Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>46031.59954861111</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Where weekend 'ICE Out' protests are planned across California - The Desert Sun</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 22:40:00 GMT</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOTFZXU2xwRVROUTZjU1lONTlEcm9IUkZ1M1FGR21xaVcyeE0wSWhUaWhRUW56a1RSdlJMNHRMN05mLUUzVWtJcUg2QlVyam9VekZJNm5qbnJUNUN0Rmk5SWxEaGlNUmJVRlBQMkxYZ1FYS3Jmb2M4OXM0U1FFOVlYZ2h5LVc5RXFOQW5ZUzNLZk9sT1RGYmdGZjVRdXpHVHgtZG0ySVg3TkpMNV85eVRtVlZOUnA?oc=5</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>46031.94444444445</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Three-vehicle crash involving logging truck closes Route 26 in West Paris for hours - WABI</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 17:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQb2V1SG9sR3RpbnJ0bENUeWhIdEJyWWRXNTVvNUZTQjdVcWp1RFJhZWVCYlpxRGg1bW1RVDNsdXQtR095RTF4ZTNhM2NsbDdFSlFsbDFJMW92UTdrNm9veGd2QnRjZ3F2R2xJTUhReUhnSHJjVXkxLVBwNTVvbFVGMjg3LV9QSlBqZmxwWHIwazgwbUJRN3dFRWJZbDVzTWg5ZmZQRWZneHJFTGdVWWo4clBZMlUtOExpdHhxMkpwUlrSAcABQVVfeXFMUG9ldUhvbEd0aW5ydGxDVHloSHRCcllkVzU1bzVGU0I3VXFqdURSYWVlQmJacURoNW1tUVQzbHV0LUdPeUUxeGUzYTNjbGw3RUpRbGwxSTFvdlE3azZvb3hndkJ0Y2dxdkdsSU1IUXlIZ0hyY1V5MS1QcDU1b2xVRjI4Ny1fUEpQamZscFhyMGs4MG1CUTd3RUViWWw1c01oOWZmUEVmZ3hyRUxnVVlqOHJQWTJVLThMaXR4cTJKcFJa?oc=5</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>46031.72569444445</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Mike White’s The White Lotus Season 4 reveals its hotel location in France: Here’s what we know so far - Soap Central</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Sat, 10 Jan 2026 07:04:38 GMT</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQbndlWTd1bS1QTDRtemQxWjJVbkdqaVpwa0hWVUllV1VXVUFRSVdRQW0yQnJITTFIUXMtQ05jWGstbjJYb1lzVGxoUUx5YWdTUGFaU1pYdzEtWmV1ejR2Z0JtbTJVazZpWTVDUHpfSnE5dE80Q0JuRjA2cExiSWloTjRLR3V5aWxHVFNGU1ZxMkZPX09MbDB1RC1MaU5EQWswYkZ1eG9aQ1FES0stMndFSVA1LWZ5LS1y?oc=5</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>46032.29488425926</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Road trip en Ontario: voici 11 lieux de tournage de la série Heated Rivalry à ajouter à votre itinéraire - Silo 57</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQaEFSeHkwdU90d2s5akg1TlNRcmVLVkFwY0Vjb0dvNldJWnJCMmx6ZVY5dmF6aEl6V2M4WmpScVV3MlVMM2JLUGg2cy1JTWFIM045R3pBRXlFQnlMZVNnVDR2LWI4NnJJQzM4Qnc5TENpNnJxQmZMRjA1ZkNWeWpzck1pLVBfVG5LMExiWUFqal9nREVJSXhxYXBKZGFyLXB4cHlMVzhBOWpXQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>46031.79166666666</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Video: Canada’s women’s hockey team eyes Milan with confidence despite setbacks - The Globe and Mail</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Sat, 10 Jan 2026 03:16:32 GMT</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNVTRrc2xtRk9tNHltWkFUZGpaUm04QW9adFRSemRCSVJkX1RvdzlYWU9WNXVuRTBoc0pVcXI1QVlVZWZHS1hwRzFvOTd4VGgtRnd2cE5ybWZPQVVaMFl0Tnpvb2ZzMmttaTcwRENjT2Nwc3l1ZG9mLUhtMTZmazBUTUw0MGRLS3J3N082c1lzd2V2OTc4dzctUktvdUR6WUVOTEJtSkZLamR6cC1OZmlJcHFwTUZYVEk?oc=5</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>46032.13648148148</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>What to know about biathlon at the Milan Cortina Winter Olympics - Times-Standard</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 19:26:52 GMT</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE01QjhFOFp4NFFOMzE4VUpocFNONzZRUnlOb1kyckE5eFhtRDVhTkVxT2NzblZMU2g2RHRyb1k2bmt5UWZBMUVuNGRrdTdqbW1jOE9DSVZuZUZGb0t6bm5GVmxNS0xnYm1GbmpR?oc=5</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>46031.81032407407</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Florida bobsledder chasing gold in 2026 Milan Cortina Winter Olympics - NBC 6 South Florida</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 22:14:47 GMT</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOLThOOWRFU3ItTkk3RUJsVk5SZE5WX2M4ellxOUtwOXVheDJtMGdTcjBTVnROQVhPQ2ZmTXYtQ2h5b2lGRk5Ia1NYQkVjbFhDUUlGUnJ2X3FXTFFoZ1BBU2RYRFFxVXJ4Z0U0V0lYU0t4NG1fOE5vV0Z5bVlpeG5mNmN2VXF0UmxrcXFaU3AxbTdDQlUxczE4TEwwdHhuREFUVlNXaUtnVF9OSXcwWG1MMU1HVkQ1SzhZU1AtWtIBxAFBVV95cUxOUmE0OUo0NFZfYUU4OU9fY1BmMnBLVXotYVVUTV9rRzJnejB0cUZuQUtyQjdCWlEtQjNlMm4yT3VqaFdRM1JQcUdRVC1wSFAtRTNnRGJGdmVJU2EteTF5MnFhcFRORkxWWVFuZ1pWMW9xMERWYlQ5UGM0X0h5QWNyemlJYlFzc21pUXppTlVnNmMwc0NCV3d5ZVl4OWlndnVDLXR3Yi0tSjRrRFNqbm52WHpoN3YtLUtTd3NlN2tSWXJEUElD?oc=5</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>46031.92693287037</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Man charged with Hartlepool man's murder after Brussels arrest - BBC</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 20:48:45 GMT</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9ieUR5RUVleGx5NDV2MC1wS0hDSDg4MU9aUmF5RWpjcGZTV2o4NUhYeEpOYmN0anROWWlzOTVXQ05Ca2Z1dEltZERaMmNCb2pycGJUMXBFMy1VZEJ10gFiQVVfeXFMTkFIRWhPN3RGQ3pUU3JJYzRmRlhYUnNvWER4WEFtanVUSnNUZEozR01WellEN3NaM1I2U2hhR3JUWWRkNjV1NDV3c0M1eW9nWmlZN2ZjV1I3VW81WDhmbFllWmc?oc=5</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>46031.8671875</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>EU states back record South America trade accord after 25 years - Reuters</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 17:43:21 GMT</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOTl9OS0lmZTJFRkJ5TWs0SXVEOVlTOTRTNFhDbUtGM1U5Vk1VSTJCYUE2R2w0Qkt4am1HclNFLWRfb1BPbHluQmxIUWkyaW9acnJEQXpTTUhDTXBNbUU2ajdkWHUyajdCMUZoS01yT0FXRk8zWXgwOVpiYkVzWGZyTHVsSFh6ZUZTU0FNMjFRYmgwMkxYTkRVOHNjNXBTcGFPTEgwSEZXZ3dPLWZJYVVBdTdlQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>46031.7384375</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Iranian regime ‘doomed’ says resistance group as hundreds protest in Brussels - Brussels Signal</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 16:03:29 GMT</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQcXBhZERacE5KQ1R0Mk43RURNblRXYmhQdk9qcWpQeHZ6RlY1bTFraW00NG9oM0ZseDZIWHNLRE9pTzRWQXh3SFMtYUVQZGdpWlpacmM1bk10S0lwVmdIWXkyN3FsQkxISjVraGpkLXd4WF9IM3dxbEF0OWpVMjhmREI1Yk44S1dDSXQ4Q1Rob0JZMHdvTlg3UTJtSWgxZXhJMnNrSVRvX3pPVzNRWW5R?oc=5</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>46031.66908564815</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Sweden arrests man suspected of spying for Russia - RBC-Ukraine</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Sat, 10 Jan 2026 05:22:00 GMT</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNSlI3ZEhnZlhJN0VaRW1VdDFScGMyeWpFQ0N2dUxwcFZFeElXSk1FMjdMVGh3VjF2aU50V3BwUml1RTlJZ3M3R0lzR3lTamNlaFlYY0s4RGNINWtodGZ5MEFfUjcybE1LTE50VTBFNktaWVlYalZ0MUlybFU0c3dpYTMyblh1T0k0U0lod2tMd29mOWs4?oc=5</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>46032.22361111111</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>EU member states confirm approval of signing EU-Mercosur trade agreement - Reuters</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 16:49:39 GMT</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOTldUWlpKY3dmWjRKRXpRdFo2NHNhSWdpdVB5LUZ1dlVyYVdGUnU5aUZwYnJDVGI4VUhtb3BWV0U2aVBfZ1RXMW1CMUowTGV5eUdSNF9KX3VDNEZFQ09WTnUyRXllazR1YTE4NVBuMUZ5b29CajMzWkt4RktOVHgzSVpoR2tNbndLdm02Y3Vvd2ZWeldGRHAzSnplbFZJdWdqZnBua050OHV1cXFEeGEwT2ZQWVg?oc=5</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>46031.70114583334</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>New Year’s Unrest Stokes Anger over Unchecked Immigration into Europe from Muslim Countries - Middle East Forum</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 16:40:33 GMT</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPcmhXeFJUOWRBZzVrX1FELWRBcDE2NHF6NmEzd3Vsb2lCaklnTlU4RkZiekUwOEV5cVdOZXVjQnhkbTRoV0IzSUNGRkt1NUQtVGp5d2pLOU1PZjJNNHZ2WHJpWk5TbFRrRWxMd3V2TFZlRy13T0JzUGtSN2hQRmJvRmRUX3VLam9oOXRRdjRBSzlORnNWV1YwTEkwZjAxRkdkV01GLUwzaWVhNlNKQnl0NW83T1N3Z2FxNlloc2ZXN29KaUdFbkNSaThHXzd6bXNm?oc=5</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="2" t="n">
+        <v>46031.69482638889</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Man charged in connection with 2019 murder as hunt continues for further suspect - Teesside Live</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 17:13:00 GMT</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNWlgyMldfdXZBNUl0dlgxcjlXdDRGdmI3WmprOHRyQ2M5eEVEMU5GU2c4TmNLdnVsX3JFelNZLWxqbUs0TllNNWNBSF94elVYMnZodExPSXhCT1RJX0hwUkNhSExObndhTzE5aW9JdFAwV1dRUDhSejhIOFVrTkhyN05iVWoteXBsbFg5Y0VGN283ZTdPX2RKTzZIVFM?oc=5</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>46031.71736111111</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Former Audi Brussels workers to get €7.5 million from EU - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 19:00:29 GMT</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOSmFXakR1Q2JZMldmOHBzNHRYZEt6TmpCcXJUeUJDdTE3aTFzNjRueDFLbHBDc0xuZkZMVlpGQldJdW1Jd292cHY5RkJkR1lTV1hDVDQwWlp1cWpTOVlhemdvczg4YTRNOVpPN3RsN0ZielJrdHRPbHZfZ0Vfckh6Mk5uUE1wRG95azhlWmhSd3hnUUMxN3pFenBPekhzUEJ6?oc=5</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="2" t="n">
+        <v>46031.79200231482</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Look: Have you seen these men? Police want to speak to suspects on CCTV footage after robbery in Dudley - Express &amp; Star</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 15:23:45 GMT</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNbU5obEx1TFBYVzNFdmwwSEp6clk2X3VselJKZFlnSktXRHZPYjNTM0FkRUpqMWFuN21pT1Jlc2oyOTBqdmEtLUZmYnZKUU1QYkU4UkRlZjZ4NW9FQVh2OHhTUlVTbVVyeFBFNnF3TTFtNmlaT2RtenVRZTN5STJSUG1JXzdFR2RsMjZkeWluVlN0TWlyNGpFeDdIQjRzeDU2bXlPMVdpTnZsUVlzNmFTSFh5RHBPT2xFRTk4dFBEek1VVmYtMFNhZzFnUnRtcUwzUE9EZTV3SVpDZUtKc1ZtTHlJYw?oc=5</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>46031.64149305555</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>EU joins Swiss National Memorial for Crans Montana fire victims - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 18:58:29 GMT</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOYVRVeTNLRDBjbXdLWmJpT183VkVFQmJiZndhTkxOTDFuSlJwUW1RaU1EU0oyWHZOeGw2MHlCbG9NMk9YZjNTUG51Q3Z0M0lvZEt0czNGUkY0UFJzeG9QN2hQTG5xMURWNEtmU1R4TmFZVi1WOWhCUlFUM3hZNVh6b1d0bm80TVZBX3h6elRLSG45TEJ5UWNTVXNlRlBBNXVSQzdJa0V3aVhPYmFfdDg0QXJPRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>46031.79061342592</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Mercosur ‘unbalanced and flawed’ - Copa Cogeca - Agriland</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQWU5xbUlzLThTRnZtel9SZ0RaVXQzNVJfVmhNTVdDbVNmNTUxRzlpcXB4N1M0TU9wSzJJNlpXZ1FiVFFQWTFKckVMNUZ2MGxmd1NRR0JGaU1QYk8yTEFlTy1VeHhianhNY3BuM0RSYmNkb0ZYS3o3QjU3SWVhb3ZBOS1KZW5RU0k?oc=5</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>46031.79166666666</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Major traffic disruption expected ahead of Mercosur protest as gardai tell public to do two things - Irish Mirror</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 16:30:54 GMT</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQcW83Z2VPSzc3OTA2ZTJwaGctdW56bkFxMlpWcWlGVW1WWVJ5eGRLMGxORzNWdkVrY2V5TV9GUy1QNkpRRWxva0VKOXAwUUdGREFNeWV6eEtHcW1PZ25tUlA3dzZteDk2MFV5NmxzR1I1YUxuNWZWSmw1TGRKdDRJMThXYWU1R2JfN2JkQUtVbnB5X3U1bWfSAZsBQVVfeXFMTk1vSXVDR0RhQnJhN0JVQ0RNaExNVHFlU3phbXVYYmNXVHdxMWQxc2VuenY1bHlzNjY1WU9yMVhVZEpURHhjU1VSYS1ub0sxbUJjYWlZTVFzajFPODcyVzFqenFPR0x6RjNjT3FvNjRWRmFCMXA4OEUyMDJKeHl1aHZVRXp1c3FQcWllcXpoRDZ4R2VpNWpUR1M0ZjQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="2" t="n">
+        <v>46031.688125</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>EU countries override France to greenlight Mercosur trade deal - Bangladesh Sangbad Sangstha (BSS)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Sat, 10 Jan 2026 03:10:15 GMT</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9PbmcyaE5IVXhsQTdoSGEzc3hxSGtDa0ZxUVJXSDBZR29rQ3ZkeUJGTE5pNVExMUhzWHRvTXNHT0J6bXFvVVd3cllRbWhMaDZf?oc=5</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>46032.13211805555</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Village search Wertheim,</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>("Wertheim Village" OR Wertheim) AND (incident OR protest OR police OR security OR evacuation OR closure)</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>As a stubborn PM dug in, one Jewish leader had his ear - The Sydney Morning Herald</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOTnRXeHdYLTR0Yi1EVHYxN0ZCRjJGczYzRzRJNjRDbTRzVGN6ZFAxOWRfQkxDSGpvTTBDR2h6VzFrMlJidHd1Yjh1Sng1RHFOUWV5c0hGUDl2SDQ0LTBWUWVvT2VNNFdTVlpDdmJrU1ZXd21aZWxOTHJoMzgtVk8zMDE1c2luTG1EM0Z1aUZsSU91aE9XTlkzNjVNd2FiOHIzcUIxeVpUZk11YzdHTXhDTXVGZVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" s="2" t="n">
+        <v>46031.75</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
           <t>Ireland / Kildare Protest Groups - Social Media</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Plans submitted for €25m residential development in Kildare Town - Ireland Live</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Fri, 09 Jan 2026 12:38:10 GMT</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQSHVJaF9lYWpnaElweEh2cThaUzA0WVpVdGJnRi1ZSmdoemdYemtmVzhqeTk4U3gxM2Z5Z1JkYi1ibkJOdDd4N2p5RHZjOVU0OUhqZ1Z3ajNvWUxSV0xnV0dDcjl0YUJuMUZrSlFsNFQweEM0aTBwNDUtMnFlZUlkZHhwYk9iWUY2TkFmXzQtZ3lHbFR5bXU4Z3hlRlNaMmVlcldHYXplbXE0Y3NLS3JJTFZnektsekV5T013QzRR?oc=5</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>46031.52650462963</v>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Man in Kildare court for allegedly taking a packet of crisps - Ireland Live</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 19:38:25 GMT</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQU0dQazBuZ25OYTRWajNOWTVzRTFfOFZvdlZwNHVYcjZoaTVoLWdheUN1ZUF4ZTFXb1Flb2pYaHp6RzJsSVFMa0tnWGtQTVBVWHBpTlhZWm9VLTlBTDBlOGRCNVdJQ213VHhna1VJX1Z3RXUyMW8yd1AzR0RhX3BrbmdQOHplcDRJc0txYkoxU2tTeGh4MHB6aG1xdlVvYVR5bnRMbnp2Vnlwa01ENmhsYXpSdmZzeFBVREE?oc=5</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>46031.81834490741</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Post-mortems completed on Dublin father and son - Kildare Now</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 18:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOZjVFU0FBN24tbHZ6YWxad0tRMGVHZVppYVlITjhJUWoya1puc2NhUy1wRmJrVW5LWWpOZzZnSW1tbEZCUlYxdDAzZFJZc3lBZmpPU3FoR0RwLXhCZTVOWDNOSXpST3hwNGxiN3FfVFZ1bmRfZ25JVmUwbGJKMWJGbW56Q1dpdUlPLU9fWGlkYkZ4MGdlMC03SjVGd2Y5X3B3c1Z6RFZmQTVkZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="2" t="n">
+        <v>46031.75347222222</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>TD calls for Minister for Education to intervene in Kildare school closure - Leinster Leader</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 17:31:42 GMT</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPbUZQZDBjbkRRdjJyaEQ2SmVscnRoRTFSRS1OUHdPczNEZGZMOElUT0duU0lpMmhhMTNQem9ZTHF2MGV4aEE3Wl8tcWdzamhCUnFldllTMnFWY1QwaHVUc0g0ai0zeXgwY2RpVTR2c3M5anFTVjMyRHVKUUhqTWlqV25wQVFnWkJOYkFodmxTdnoteWU0akVCTXphSGlUeVdwYkpQR0hfbHVLY3RRalZBZ0tWY1dDdDEtc3BYMjkzTnlscy1OWWZySHFWTFJOUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" s="2" t="n">
+        <v>46031.73034722222</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Kildare's Ruby Boland called into Ireland U16s for double header in Portugal - Ireland Live</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 20:45:16 GMT</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOV2R2MkFEeGlJSzZfVTIwOWtLc3FDZDFmYVhQM0tHUlZ6bGY1ZnlxUHZOSUs3TVJNWW8zMDhDbV9YTl82b09UVVVNNWRRUDJfWU1jQTlzYWtETnFOZUFRVmVRMTFBVGVJejU3SHlORGZqV3RnMkVreWRrUV84RHU0TXo0bWY5dV93SVZHMHdKYzk3VHl1ZHppMVFlcjlYV1NKYnY1WGR0VXZzNTh5YXk4RnBYR3NQVkk4SHBsd3JQb1o1U1VBR09ueU9kOWRaYTNw?oc=5</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" s="2" t="n">
+        <v>46031.86476851852</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>We Got Our Hands On The Most Talked About Bag Of The Season - Does It Live Up To The Hype? - Grazia Daily UK</t>
+          <t>Where luxury meets ASMR: Burberry - The Times</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 09:57:01 GMT</t>
+          <t>Wed, 14 Jan 2026 04:05:00 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNdEpCcnRqS1ltajFPZnpka3JMRzNiSVJfMjczNkdVODVQZy1VNWdWNVFyNTRHeHV3V3ZuVElDRVlPN2wzYzJFb2p0Rk8tMVVaY2VXbE9pQnV2YkJEbDJuUXBkVUNSai1LM3Bsc01FemNQNHlBWDhCMUFyb0I3VlFJRmJ0YlE4dDlqQV9r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwNBVV95cUxNeTlzZnBfbm1HWDNzM1dGWTVvMzRwWFNQQ1hKZ0dDbDFLZFpvNFpQM1UwQ3RXTU9YR1hqd1pHTFItX2pXQWNmLUtMQm1Ob1NoV3FsMndSZ2Zuekp4aHZjUkdHNjlHWS1mZW1PVTRxMURIS21XUWRkN3Q2SnhERElXYUhWTk1YVzZjUWc2RmZ0U3p4bG9hbHN2NER5UXZHT0R1SUhJYVNBZ3JQSi16anJiUzdIT1dJTDBKZXQ2cTU0SmFyMW5nYWJsVzBsOGZHZTN6MkJXV3FwQmRvSllFT3ZHMEhPRGIyQUQxOTNUTHMwYkR5V3NBOVVyUFBUS1o2dG9KeGFpWXdYMy1leS1JYVJJRG1fczFXRVM2Wm9vMHlFdll0YV95WTZiaWswVDlZSTYyXzMxLVpBU2Rfb3FWc3pmcjFkTDFsZUx5a0g2MWtleXBROWpjdjBrT0hJOWxEeWRpMW1fY2h4RnlaX0FTQTFQQXpUOEhLQk9fNGxIMktYNmQ4UjdTdUNkZkRFLTU3MEdZZjFOQTU4R2NKODRVYko3elNXZ053TlE1RlQ0a2xLUQ?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46035.41459490741</v>
+        <v>46036.17013888889</v>
       </c>
     </row>
     <row r="3">
@@ -515,24 +515,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Louis Vuitton Refreshes Seoul Flagship - Retail &amp; Leisure International</t>
+          <t>Inside Louis Vuitton’s Sanlitun Flagship in Beijing [PHOTOS] - WWD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 10:56:54 GMT</t>
+          <t>Wed, 14 Jan 2026 05:05:43 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5LdHR0Ykt2NWthaG1qNWV6Zmd3Z25tOEg3MjY0ekh4WWdYQ2VIeGdkdWFCR01ZZjg3ZENnNGJZanZDNWZmb2Vwb3dyS0h4cTc3ajA4QUJVa3E4SnJsRVk5bmRLd3lyLXV5NDlvOHVyUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxORFRncGtwRGM4WFlCQzFET29aTVkwMEVzMHNkYzZyUklhSFAwZjZmbEdyMms5ejZlcjlITkhfV29UOGNwaVV3Z25NV3FRa25JRlAzaGhpelZoYWdjVUpieHBJUGItREJJdzhnUkpEZlFidDhkUDVjcHhvcU9RcEc2bDdoeFhZNWR5amtCVUE0azZWYUtIQkxWaGVvYXF5bkFnbzhwdDBNVQ?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46035.45618055556</v>
+        <v>46036.21230324074</v>
       </c>
     </row>
     <row r="4">
@@ -548,24 +548,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Louis Vuitton Kicks off the 10 Years-Celebration and Renewal of its Partnership with UNICEF by Unveiling a Limited Gold edition of the Silver Lockit Pendant - en.worldtempus.com</t>
+          <t>Jorge Lorenzo says Valentino Rossi once saw Marc Marquez as his MotoGP ‘successor’ - motogpnews.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 09:04:11 GMT</t>
+          <t>Wed, 14 Jan 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxORHZjeEFFOHQ2d1o3YkFBQjFpTGlQaFhPcXZEcHdfSFd2WHVKV05mTXRIWmU3a3E1Y2JicUZqal9VTU5xSktqcWdoeXJzSEVCVjhWRGJQQVFMV1ZoSWFNbXVqa3QyRFE3aFIyU05LZnU5VjV1Y3l1NmdxVnZOZ19KQWhFbkI2RTF3UjF3N3dOLXhVeHRiOTBIOG9WUHY3VVd6RWJnWFRCZkU3NFRLU1NORG9kbTREMzdIRjZZdGQ2cmpqdzFKVExYWF9XcDItVTN2ekFhdzZ4X2VvTTNCcDRSaDVFYTQxaEZRODhDNzh3TEJYYW5XV0w5QmdiRUhSak0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQU2FUTVdMaXNZUnRwd00tWlRTem50OXFqdTZ1LThlMFZsS1pIVk5oa0lia2I3elBCVWlocW5Uc1Z6aGdNT1ZNMl9va0VsUU1neENqVFo5NmhrRzRwWW42Wkh2UWhabmNpbWZQVXdtd1poVVZsQ2xKQnZsNExzVlo3YkdkZ0ZaNENfVDJlanE4aS1PN1F4TzJoMnhPdGJiRkFtWUdzalpBTUJQdlJZSkdQSGlkTGlWUjBkQnMw?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46035.3779050926</v>
+        <v>46036.29166666666</v>
       </c>
     </row>
     <row r="5">
@@ -581,24 +581,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CFDA, Ralph Lauren launch funds for US fashion manufacturing - Just Style</t>
+          <t>Louis Vuitton celebrates 130 Years of the Monogram - trillmag.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 11:43:46 GMT</t>
+          <t>Tue, 13 Jan 2026 23:09:24 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPTVRlME5xaGt5SHhwdVVNSkpNRUd2dVBqVTNKNFpOVEFrWmFERVBTRlFPRDZaUVlWOVRMa2xnVUFyX1FScERBc2x2UjZZSGhTX0lxZ3poaDFPUDdDZGJ4RGh0MHFIQ0NqYzdvQ1RjMTZ4VGhXUVppY0lwVThhTEdNUlBMNjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPdGUtSW1VVGozM2tyRG1kMWVYOTVDMjhjZWR1cEZtMjhIYjJBTUppTXFqaFpVdER4Vnc5ZnRBVFpWTXhBNnFtamZKdWVlNFA3TkxNUVJDcUtaNHpNRzZmNFUtUzdwNnJhUERNd0MtY005RldjT1VHZ1hXeUVnaE05NG80aFFsV3VSTGtsZWdrMTNTRzg1el9wV1BzUQ?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46035.48872685185</v>
+        <v>46035.96486111111</v>
       </c>
     </row>
     <row r="6">
@@ -614,24 +614,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Josh O’Connor Is the Newest Ambassador for Dior - Vogue Philippines</t>
+          <t>Valentino Beauty exits South Korea amid intensifying competition - Global Cosmetics News</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 11:25:11 GMT</t>
+          <t>Wed, 14 Jan 2026 06:02:09 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBaUGF0bHM1N2RFVTUzRXVEeURpekVha1VYWk9pejVlLWVKWHdTVUlzMG90R3J6b0xTUlh1LWk2S2wwU2d0d0ZNN2lYUWdxRUVNVzhaZ2RPZWk2MWZxcWJLUlVZUnk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQYThxbVZGdzAycVhOQWotZ0tlLVhrd1gyX0JwNEsxdnNZTkhOZEtyU1FMNUdNX0E2YXI2NGJlZzN1QURiZGEzbHk3TFNTbEhKVk5mZ3phMDdtZWJJN21vUDd5c2kyZHFGUVI1NzQ2MV9VRWNkQmZua2V4ZEJvdUVwVW8xSzBNQW1kV2c0VkNBQndCSUY1dHhEbDBPVWlvTW1ZMHBj?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46035.47582175926</v>
+        <v>46036.25149305556</v>
       </c>
     </row>
     <row r="7">
@@ -647,24 +647,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Debuts, homecomings and relocations: everything to know about FW26 Menswear - Hero Magazine</t>
+          <t>Louis Vuitton Kicks off the 10 Years-Celebration and Renewal of its Partnership with UNICEF by Unveiling a Limited Gold edition of the Silver Lockit Pendant - en.worldtempus.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 10:24:26 GMT</t>
+          <t>Tue, 13 Jan 2026 16:00:00 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNazhWbVJzcWZORThTWnJ2N3JnclBXalZzSmdpVk5ISl9JbmZRM1MwU3Zrc0VCaXpkRlZmb05hcVFRblVVWU5NZGlSSXR5TGg3VGpWSEhoanVHUEkwQW44b29qbEx6eFFwU0lmS2dwY1JNbWZyN2QtTE43TlJGdjFtcV9DelR0UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxORHZjeEFFOHQ2d1o3YkFBQjFpTGlQaFhPcXZEcHdfSFd2WHVKV05mTXRIWmU3a3E1Y2JicUZqal9VTU5xSktqcWdoeXJzSEVCVjhWRGJQQVFMV1ZoSWFNbXVqa3QyRFE3aFIyU05LZnU5VjV1Y3l1NmdxVnZOZ19KQWhFbkI2RTF3UjF3N3dOLXhVeHRiOTBIOG9WUHY3VVd6RWJnWFRCZkU3NFRLU1NORG9kbTREMzdIRjZZdGQ2cmpqdzFKVExYWF9XcDItVTN2ekFhdzZ4X2VvTTNCcDRSaDVFYTQxaEZRODhDNzh3TEJYYW5XV0w5QmdiRUhSak0?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46035.43363425926</v>
+        <v>46035.66666666666</v>
       </c>
     </row>
     <row r="8">
@@ -680,24 +680,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fondation Louis Vuitton Explores Calder’s “Fourth Dimension” of Motion - parametric-architecture.com</t>
+          <t>Day two at NRF’s big show: Ralph Lauren and Sephora talk AI and taking risks - Inside Retail Asia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 11:41:14 GMT</t>
+          <t>Wed, 14 Jan 2026 03:43:43 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPTWpyUlV1NmsxckpnTWFLMWFlVnhmTXVVSVhmbHhRSmVPUm4ycWRiUmVUaVJwalk5TVY3aE9iU2JwWkpVVVJ1MFFNNHdOWEdNZU4xRzFoYjRWUU9Felk2d3dNbFFVQ0lIdHE3R19UVVphOXFSMk1XUDV0Qklrd2ZSSg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOYk85SUpiUVAxZ3lQbno3Szdua2cyOFhpTU1vclBvQy1pVElMa183c2lRRnVEY2c2ejJKWVdZZ1NzektMRWhkQ09EdzJrMXFuVW5yb0hzWDJmSzM1TGlNLXBodXlELWZ0RW9mMUVWdDNKMjRNenhIbW9aQ1Y0SHhrVTNmTFBnMG1RcVM1am5FUG5rVl9IRFktY3QzYk9wbzhFQXdhTzFBRy00QjdwTW1ha0N3?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46035.48696759259</v>
+        <v>46036.1553587963</v>
       </c>
     </row>
     <row r="9">
@@ -713,24 +713,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkish actress Hande Ercel sparks debate with love rumors, luxury Cartier watch - Türkiye Today</t>
+          <t>Valentino Beauty Taps Visual Artists to Reimagine Its Iconic Perfume Bottle - hypebae.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 11:43:43 GMT</t>
+          <t>Wed, 14 Jan 2026 07:12:54 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRmx3dmtvV0cxU3VEbjNsa0pqRFdsMzJoRVlLVl9yWXR5VUQ0eGJsOHg0ZS1vcU9WcVpzb0NzWjROb1JPRnE1V3djSldlb0xZUW93X3BYNTBWODlvOFBraWhFQVJnU1lQRjh2SXBkb3FMUkNNV0ZYU3BjdzN6T0cxSWl3YVh2aXE5eVY3ZmVyT0NLdkwwWFl1MjBDU1FwMjMzSjQyMmhNWjRPclNIOC1YckdoRnNRMFIwaGNpbmxTbW53QzBHNXFiY3lR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOdGZfOVV3Y0syZEViTHI0c2RMdU5rRllCVFF3R20yaFE5cmUyY3l5QWRQV2FIYmpqSTdSWVRfMVlIZVEwdFZ0Z252anR5b3VkX0NfbjNEYjdhVnJodk9mdVhhYlc5TVBXeU5BbzIxNGxpbjVKMmd2clRESGIyM3gxamRRamxfa25ZWFgxaXpEbmVNcDVSeHJXRlliMkcyQjhoU2pLTkJR?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46035.48869212963</v>
+        <v>46036.300625</v>
       </c>
     </row>
     <row r="10">
@@ -746,1212 +746,4050 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How Inviting Consumers to ‘Ask Ralph’ Deepens Their Connection to the Ralph Lauren Brand - Retail TouchPoints</t>
+          <t>9 fine jewellery watches blurring craft boundaries - WatchPro USA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 13:35:00 GMT</t>
+          <t>Wed, 14 Jan 2026 07:47:11 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQdTJOczR3a1dOVUg0NlZzckM2N2thM2JUaF90d1piaGZodHdLOGg3MUFMc3Ria200ZEplUmczOWtnOG84VWpFQmotTGNJMEpWejg2WkRtU2NVUmN5WlV5WFplT1pLWGFmZ3VoUXV4S05HdkZ5VFN5SzVrZHdXWTRwbFRwV2QtWkZlbG9aRVJ0bmtpZ3QtQzdsdkROT19scHBkOUQzRUVpME9oa2ctMWlDa0FaZjh6X2lFTDdtSUxLRGFsMWY1Wi1vbkpFaVo3Tjg0U1lJbEtqUnBYZ1lnZjNEeA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE01NjVVaXkyRjRlT1pscVRITTZ0RzRDT2dEX2U0WWNRcjdVTVBuTkt0bWhlajh3STd4bllKNTFyQklQelp1ak9Vd2NMLWE0UW5feFhZNWlHRk1nT1AxNk1fMVhBNEJQVzVUMFFXS29GMFZLd0s4LVFXUWk2RzA?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46035.56597222222</v>
+        <v>46036.32443287037</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Value Retail</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B&amp;M European Value Retail SA Unsponsored ADR (OTCMKTS:BMRRY) Short Interest Update - MarketBeat</t>
+          <t>I'm a beauty editor and this is the only feel-good perfume I'm wearing right now - Glamour UK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 13:01:41 GMT</t>
+          <t>Tue, 13 Jan 2026 14:28:17 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPRzZqYzJJeGg5UGplV3ZIQXcyWFBTVmVFNk5lZUdwVnZpamxZRXl3UGhFVjdTZzdmaG1rSWY4OGdLT25iUl9JaGROcmNoM183RmVTM29mYUNhOGpGRGI2dkF4SGx5SklFVDBSRkRLY2JqUk1Vc1c2U1h5NDdxMVBVRXFJanh6OGdBQjhSOGI1UU1OUGtXX2hpbDBwUnIzdXUzWkRRSTJNcjlRUjdkdUQyOHJvbk14NXJHam9MdjYyS2R5bEttR0FwQUVxV2k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQQ0xGQi12b3NWbmdIaFhWbjlpQ3l2bDBRdXJJalladUxuX1ZhbkYzNXRURjRIN2RIUE4zTl9FZzkzSE9sQWZNTUtoeEJNU0xITUNlVlpDamZQb3pYakNYbUgwZDRtS2NRTHNXbXllNmw0akNJSnA5d0VULXpMNUFNcmJiSktSNGE5aEVj?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46035.54283564815</v>
+        <v>46035.60297453704</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Value Retail</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Temu’s UAE growth points to rise in value retail - Arabian Gulf Business Insight | AGBI</t>
+          <t>Giorgio Armani Corp. Taps Matteo Mascazzini as Chief Executive Officer - WWD</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 08:36:12 GMT</t>
+          <t>Wed, 14 Jan 2026 05:03:00 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQU1Bza3ZSV0lPRnNFMkh1dVhRQlVyeXlkTEllTmMtdmMwYzA2TnFkZkpJMFBLc29uelhrR2xfM3E4bXNRTHZxZkd0d3ZORGhMUndOMTFreUJyUXdBZGluNzVKcU85SUEwUjNvU1FmMnRRV0M1Z3FWRlQ0cWo0OWFzLUJ1RmJ2TE56eThNNGlGR2c1cTBBUVRiWg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPQlVPbzVrZ3lwb1EwY205WWt4NElWYVpXdXFJLXExU1VRMHMwUm1lcXBrRm1TeWgtZTM1TmRvcEg2RGQ0RXpTZjVPUko2RU9rblVzbmJ4Vmw0alhtNHdMb0RZWnRoTTVSQ0VCaGU3NmUxUjg3NVRxdWc0dmJLUnRHdkRaTW5GOTlZYWxkQlB6VVBmOWZHTEU1SDRqWnRDU2JQUTl6dEx1b1BUMVZxM19lQmF5dnhHLTJpbGJZcnFQQjh5NFhvLTRF?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46035.35847222222</v>
+        <v>46036.21041666667</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amazon starts drone flights in ‘next step’ for UK delivery service - The Independent</t>
+          <t>The Perfume Shop does it again with big Christmas sales as Dior, Carolina Herrera, Chanel top the charts - FashionNetwork - The World's Fashion Business News</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 09:51:00 GMT</t>
+          <t>Tue, 13 Jan 2026 16:04:14 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNSVlZOExrTkxsM3owS1Q3SnpOWUJCeGxxbUJsWUZkQjZTM1I0UWc0NHF5VVh6VjY3NVdjdEVEdjJJYWxacFhZakNMek1lenU3N2lERkZtQ2t4emItLUljRDVFZmN5c2s1XzZNWWVaajNVUFZaNkFLekdVSU5RNkxtLXVwbG43M3BrTUZzVi1sNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQNTFPWHZxb082REx1eGpscWx5bWpKaUtOWUpBczBRVUNZZVNGZG95M1NsbHNYUTJKZExkWmNJMzVkQ0dtNG5Cbmk5QzR1Y3BVS0hRS0wwYUNzSVNsSXNoSXpsSzFGWEZMLUFNS1NaN0V6ekpWdlc1U2RlZW9EYzF2SVpzR2JSSUZYZHZlcVEwOVdKdi1Zc0NvQW5MRTVkMGRSamJxdTBQWGp2Y2ZKRkxPZmk0ZWxIbVg1VjFPRnJFQmhqQzhMd0p4d0RKR0hxX1loaURXekFFWHl6RDhkNDVnUXVLcHY?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46035.41041666667</v>
+        <v>46035.66960648148</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amazon delivery driver gets shot at for pulling into wrong driveway, NC cops say - Charlotte Observer</t>
+          <t>Score free makeup at the Armani Beauty pop-up at The Grove this week - Time Out Worldwide</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 12:18:32 GMT</t>
+          <t>Tue, 13 Jan 2026 23:49:28 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9kM3U5cU15UnBmR3JhZWVyaUl3R181WUV2cWMxR0ItMHFhRmZqUG1rVmU5cF8zLS1KVzJmTGVOT1prSU1XRW1GRGI3Sm1hNGNWZ3ZVbVNLMnJXU3BqODE5bks4MGowcEpkUHkwcjdrQ0ptUzItRDYxNnlYYjjSAXxBVV95cUxPdmhwWC1rV3ExSUhpajdDTWlpZzFoTmktcXU1VzNwRUFGXzZDMlRfYXBVOGdROU1faVc3OVRtRjZ6QTNvS1RGVGdzR2I4MFVua1dVamJSLWl5N2FCeWhxSFpKa2V0emNBcEIyc3Z4cjVKS2xNUTV4REtDanVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOTV8wTkNfRm90Rmh6VjRHVllQbXdQeFd1Z212d2gtRW8yOTRtbzFXOGoyeE5uSS1zYU9UeXVzT1NmeWtJSnZRLWQxMUhqUWdNa29YSHJDdno5ZE1ROUJpNmczYlp4V25DcEg0Q1J6c21zaGQ5Q29idlJyRUlNbW5IUnBpNkxNRXpZYUN5ZmQ4MzlNeDFkcWR0b0xpeTFaNkt2MUo3YlNDV0lqc2dESTR1cGkzLWt3bEE?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46035.51287037037</v>
+        <v>46035.99268518519</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Animal Crossing: New Horizons - Amazon Is Offering Release-Day Delivery For Switch 2 Edition - GameSpot</t>
+          <t>We Dive Deeper Into Cartier’s New Greco-Roman High Jewellery Collection - Harper's Bazaar Arabia</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 09:30:47 GMT</t>
+          <t>Wed, 14 Jan 2026 07:00:31 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNaXNJYXQwZHd5RC1jZnBfRjZPcG9tVnZscGxwRVJHS24xV1VsanpqeFRmMmVyUUQ4bjNxcHRiZFoyc1RUZmxLSWJXWnV4U2t1NkQyUDVSNmhTR1B5Y0h0MWF2LWc1NU40VW9TQ2o1LTkwRTdDdXpkOGo2YlNGYmZCOF9BYnQ2VnpGQXh4dU1fbkw0bFoyY1lhZnhidzRHcXpTR3VtdGIwRTBvUjlnOV9FeUZnLXVlX0hFOTBjWXVWdzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPYzdyS0xfWjRwcmU1NTdSYmtDRklOdUwzUGs5Ry1taDVpOGp6aVdyZHNOb0RMU1NvRENHV1VEOEU0RGl5VWJINlF6amxMNFBYMWNNaHkyY0xDSk1CSTBKUUhnOXF0WEF6ZlNhbWd2UE5KczJQSGlyb2hXQ1k3ek1YVVJJWFQ1ZXJ4OXc?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46035.39637731481</v>
+        <v>46036.29202546296</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How Many Packages Does An Amazon Driver In Sioux Falls Deliver In One Day? - 97.3 KKRC</t>
+          <t>Valentino Livramento out for two months with a hamstring injury - OneFootball</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 12:36:09 GMT</t>
+          <t>Tue, 13 Jan 2026 17:32:16 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE5MR056NEt4dXhqU1ZrNURCdHBfakVCRWFiOS1IRnYyc0Uyb2lRUFRDS0JISkpIOVIwajFBMWpEYXRiZEJEOVQ4bEtSWFNyR3dULVJzeWFjd1pUN3ZUU2l1dnBVRW5OSlctYVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNUU54ZHBzSkdFdVVGT1RJOEtac1V3UVFZekhoWDVBa3c4TVpaNTlpNXNWOE5IZEVKYm8xeUh3ZE4yWDQxLTdUNHFoZFV1eDdUYjhVTkpuNjRPbnV6Yk43MG95dXIzaU8yUExFcTFsRVZMZlFzTUFNZXRqQ0t0RkE1TzljNjFFMGdZNnRoWmtZaWxXWk9Vb3dBNG5YLTdEWjN5dElkc3J2TQ?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46035.52510416666</v>
+        <v>46035.73074074074</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Walmart takes on Amazon: Extends air delivery service to 40 million Americans - Geo News</t>
+          <t>Drug dealer caught in Tunbridge Wells had 'block of cocaine' in Louis Vuitton bag at Sevenoaks home - Kent Live</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 08:43:00 GMT</t>
+          <t>Tue, 13 Jan 2026 14:56:25 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNZVdCUGVBTTk0d1RkYU9MRlZ2TjBrTXRPbXA3VGNxRGNNR2hRRFg0UTJoVlpVTGV5aVhFdm11dTI1VGVsandEeUZGMGFMVHM3dzkxZTNtVklLQXpNWGdhSFlobW1JQUlfQjc5Yk5CSExicTJtWS1OTEZRY2RudXg0SGNxM2JEYWR5RWhmdTJRRjJpRnc1YlJOaUxFWVVDRG4zWHpxd0Q2WTB5S25OSGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOVnNNM0xLRG5XalFPQUFZdXZ1YkxmakR1dFBDTkJnZnVCeWd2NW8tRFBaMll2NVB6UjBpOENCMzVGQk5UWWpsX1Y3dVpfS0d4aGc4dVgzQlVxNS1aOXFQOVA3aExQU2tTVjJWLWFZTlp0U2owdVNoWHVzZVc0Z0dSSmptcjlTN2JzcGdyRUZkdTZESmZPeG84?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46035.36319444444</v>
+        <v>46035.62251157407</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How Amazon Sellers Can Reduce Fulfillment Costs Without Slowing Delivery - ABC Money</t>
+          <t>Josh O'Connor Is Dior Men's Newest Global Ambassador - L'OFFICIEL HOMME Singapore</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 14:01:07 GMT</t>
+          <t>Wed, 14 Jan 2026 04:01:42 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOcl9FalVURlJvMzlYQUFJMDVVb0JadXE0akNuVkd4bDAzLWtzVTg3ZUZzbENsUHlkSkdnd0dKLVJXQmo1MFhGUzMzN3JEVnl2bUVIUWZmemFNUXg1bURSYUp1OUY0Y0RSWWZObGl3WXE0LUR5aktYb1VKTWZzenZtZjJxWnlIY0ZqOTJqWUFrOHVvck4weXVBaVlTV3RrZ2lKWTBuN2pNLWVHN0Iz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOaGZHOGotODBKX01qbnB2aUF3YlhwemZJZHlpdGtObTRKZmpSM0FJektYbGQ3U01sS1c1S1htZkVxWlQ5VjNrZDdlQko2V3dSWXdlZkdJemxJZjBEOFpZdjNaQl82OGFNUUVqZ09MTUtfQ09PYmM1TXMtS2w1MXFsd05RSGRaN0ItMVNqSWdQZlNFbnZKZkhMNk96NUdxWmxnMEFFVw?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46035.5841087963</v>
+        <v>46036.16784722222</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>High Level City searches Belgium French language</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>("brussels" OR "Maastricht" OR "Antwerp" ) AND ("Bombe" OR "alerte à la bombe" OR "explosif" OR "colis sans surveillance" OR  "explosion" OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark at a glance - Anadolu Ajansı</t>
+          <t>Discount gucci bloom fragrance review Best Sale Gucci Bloom Perfume Review The Smell Longevity More - scienze-naturali.it</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 10:15:49 GMT</t>
+          <t>Wed, 14 Jan 2026 07:08:23 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5KNW9rYUp0cnhYV2dLTU1RS3pTOUhSbjdsOWFxOGFDaU1FNEVjR2dCRzNDSDdHQ3BTdnREb3pINklEZzVGUC1WTUg1eURJWVJDMjRhQ2hneVJ2RUJfR2V5YWVLTmY5YjBsWk9kaEltTVZKQTQ4OHNOQWs1dXhSX0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE5iWFhkaG9tZHQ0LUl5aUMySHJvRDRGTm93OXJVeWc0X0ExR3Zqalh0SWpGSmdESXIyTi1keEpqMENvajdGZFBDUWVpX2JlNEhWWDZMZ1kwbHZVNzFlb3FjbkdLRXJPQzVN?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46035.42765046296</v>
+        <v>46036.29748842592</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Local Town Searches  Maasmechelen Dutch Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND ("Boycot" OR "Boycotten" OR "Protest" OR "Bom" OR "bommelding" OR "onbeheerd pakket" OR "verdacht pakket" OR "explosieven" OR "explosie" OR "explosief" OR "schieten" OR "schietincident" OR "steken" OR "bommetje" OR "bomba" OR "Geknalt" OR "liquidatie" ) -geoffroy</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hundreds of tractors roll into Paris as farmers protest EU-Mercosur trade deal - Modern Ghana</t>
+          <t>Amazon begins UK drone delivery trials, Darlington chosen for first rollout - Maritime Gateway</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 10:52:00 GMT</t>
+          <t>Wed, 14 Jan 2026 02:31:24 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQUUZzTVZqYzBod1R4d0NtLWhNREl3bXlJamNUalBBdGZ5SjZLS0dPT2tBSnpUbWtyWEVEOVZCcng2UWpFTlZhU1NDcmVzcnp6Tk9leTFxYkd6MXlsWWJqWk5ScFFRdkxVcXpVNXZZWFB3Tmxtc3FSXzdhWXlqWkZKTS05dEpaVmlYYjREcTFSNjVsd204SEg40gGXAUFVX3lxTFBRRnNNVmpjMGh3VHh3Q20taE1ESXdteUlqY1RqUEF0ZnlKNktLR09Pa0FKelRta3JYRUQ5VkJyeDZRakVOVmFTU0NyZXNyenpOT2V5MXFiR3oxeWxZYmpaTlJwUVF2TFVxelU1dllYUHdObG1zcVJfN2FZeWpaRkpNLTl0SlpWaVhiNERxMVI2NWx3bThISDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQay1YdWxuUmdwd2ZFMGNMMmtDQTRYNnNjX1I4WjNGYnZkb0t0bjdvT0FJM2lTMk1CYlUyZDdidEVyc19xT000UFdvbDRIYlhJNk9JbWFSVGpTV0FpODVrVFA1VngtTzZ5QmgtTWZQLWVKN2lHMy1WSlI0bUFmMkxTVThWelVITGJ0dFhocEpPUW5MVXA2NlVsMkNJSk5iaTY2V1U0VzRYZjBFNUk?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46035.45277777778</v>
+        <v>46036.10513888889</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wolfsburg director calls defeat to Bayern Munich a complete collapse - Bavarian Football Works</t>
+          <t>Amazon Day lets Prime subscribers choose a specific delivery day - BetaNews</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 12:30:00 GMT</t>
+          <t>Wed, 14 Jan 2026 03:59:37 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNQmlVUVY0YkZTbWJrM2hIMkZZajBHaU9WMWlwZDZkQUZfZi1ocU42elR0M25yODFKUmt5SndYWVZSMHluc0xuRUNqbWp6SkJGY0c5NFVEeHVLbkY2SmJJbURXNkxLOW8xSldqV1NpVnE0Q3A3U3A2NF9KWG1iR1pIc3hiTzZzMmt0MFZBYUJYcVJza0FZa3MzWDZuR2t2MzNLTDJiRXlrMW1RNFE2Zjh3UmM1NVNMMWJWMWhjaDdKMGpBakJCZFFxRGZMZVFnRTRTYkdkOVdTal92a3BVdTdLZi16WVRTRms1LXQyeXlQLUtYYlVBM0FBOGtCM1ZhZ1FXMVNBVXp3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTFBLWllqNDQwNFdDdzZvYndmTnlIOUlSYlZvcUdMQVpvbXBIcFRKbjc5aTRiQW1YU1NGYWF3MTFQUGVuc1RqOU9HOHc3QzR1SnpMWWc?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46035.52083333334</v>
+        <v>46036.16640046296</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Winter safety campaign sees dedicated police patrols target crime and ASB - North Yorkshire Police</t>
+          <t>Streaming device deal: Save $20 on the Amazon Fire TV Stick 4K Max - Mashable</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 12:17:00 GMT</t>
+          <t>Tue, 13 Jan 2026 21:59:21 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxNeV85ZGF3aE53WXhvRE1iVnpTaWFMa2tISjIwZV9pOFhockNLWmNROFpDVEpDajg4dDZ3YVFtRnBISzc0dGJncU1FOWlmVUZCSmY5RGZwVFNzMGNBTEh0ZjVIY2RFMkNJbFUwME9MM3I0Mzc3SjBjSmVQODBPZHhldURzTnBhTDM1MmRZblRLWlRFS3FuSVlKQzd2blBvazd0aHkzYmdMOVlLSk51cTZQa2NMdUk3SnlvYkNZaU5fMHBYZXV2T19MMXJtQUc3ZjlvSDJEVnFlMk9naFA5X09NYUJSajNzbm9pMmY3azFVbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBZNzZjamxGYzNYRlVfRktlSFItSjR2LVJVb2h3a2RfMWpXUGp4MExLZHQweWI1NEVlTHd6d0JrVVVFd1Z2Y0N1TDBZaE9Ma05lTkNWSVpJQTBpN0M4dUdUTjEzSklPRmMyeThTeHRNS0g2Qjh1QmRR?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46035.51180555556</v>
+        <v>46035.91621527778</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nearly 100 arrests made in crackdown on festive crime and disorder - The York Press</t>
+          <t>Armed men break into Stamford home, assault residents after posing as Amazon delivery drivers: PD - WTNH.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 12:34:54 GMT</t>
+          <t>Tue, 13 Jan 2026 22:18:12 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPWEctUm96TW5wa1g5NzB2YWJPOERITjlTdlNTaFBrY0xvRlY2dW8zd1JoVlF3cjF1ZDdRc044T2VqbWpOSUlYcWk2SzV1dDl1dWd4bE1pNEVmZzZtVV8yU3pDb3FOUjlGTkFjY3JKdXMyZTl6WmZKdFFvUUd1dTMwRUJRYVZZSGF6eDRRcmhxWS00dWpY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQNlc3SFJuZ0tGNFg1N1VuSUl1Tl9la3B2VTFlMk1XRDNUeG1yTmJfeDZPSHF0VkFiNzZHWkp5ajFvV3VnV1kwYm1fVWRQMTlGM2w3TG1wakZiQ3JzOVJyWmhMdjZwQ3Y4TDJ0TjE1cUZCUWgyR1JqdkgwWWhtc2tlTDJDRTNOQ3lYazNqc1F5MW1HZW95NTZjenVyVko5di1MbmZtemRtcnh1LWVVS0tsTm9wNU1ZQTg5NWZxSWJrdF9zVE96VWhURlBRemdyUUkyQ0dnT3FrZWo3bmE40gHiAUFVX3lxTFBzclF0THF2QzR3LXBPelZRa3hUM3VoMmREcE56Q0RJWmc2cnBBU3BCdkRTamdQUENWa3JHeEVGa09xbm5INkszN1hZN0xZT051cG5OMXU1VlNwbXJSQ3Atd19KeW85ZEZKNmdMUlRuWEZpRnZmZllfNE5VYThrM3NOU0lzcE9HVjE0LWd3OGVISHU3eW5ZU1lEWW5hMVJ6N2RkWUJ1RGtsYUlrZjMtcTdvUTBzS0o3ZE12ZHp2QmtnT0toYy1KNHhacUloUGNxY3UwcHoxb0VZWXQ1djc2NDFuZmc?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46035.52423611111</v>
+        <v>46035.92930555555</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mbappé's Hypocritical Tribute to Fired Alonso - 조선일보</t>
+          <t>Amazon boosts delivery in North East region with new freighter flights - BusinessLine</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 10:32:58 GMT</t>
+          <t>Wed, 14 Jan 2026 01:24:49 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSzFUVWcyamlLTUpTanZ6T05rX2dpZmRqWTlveU5hYlE3bFNxS1dpUXFoT1NTR055NFI3WFFoLXR3RGk3T3NyUDAzWk1ETTFfZkdOaWFLUUdBVDF6ZkVCRF92c05oNm1LbFpkWVM1U01nUC1QQWxGM0lxNHhVbFpWQ3ZLc0dvUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOb1lMYjBTNmZGNGg4dVNTbVpoNDFVTkhTNHRUUE9VNUpHY1B2VG5aRXNHcWtjNWJlVlozZlNxUk9kNGdjV0pocFdzbi0zbWJDejlDSFhpcjBiRXJCUUFYUFFpMTl3YnFpUTBpSE9KRFZWaHFJLTh6NVRpdkwxaTlkY3hhU0VnWTU3Tm9TNUUxWU01eHlBNkltTmJTUm5OWUU2b29sbUpMUGRkWHBVSlgzMmVnSWl2NFBlZlBxZ2dBOVI4RkdtaE5kTHNIaGJFMG1OVG5GeDNBX1dIUDJyakHSAeQBQVVfeXFMT0tLTXZENk13alY0SWRhd1Y0Q3d1c0gzQmVoYlpZVEZ3NlhaN0R6YWJqR2otOFhBQWlPclo4RTZiZTZIR3ZzS29IeTMzS0Uxai1ORU9TN3FodUg1cDJCYlVzSF92dHh6MG1rODNEdDRGcEJobnZSeGdSSTBlcEpIdHJvN1UySTNxY0RFdE02Rk4xaU56THZKTms4LTZmSkpOOEl4M1o2UVZEdEI5bFV1NVo0N004YUpOS0o0STA2cDd4S2hqWkZ3cEc4bFZna2hwVEUzZTFJa19CTVN4d2kydnE5Nmc3?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46035.43956018519</v>
+        <v>46036.05890046297</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Xabi Alonso's Short-Lived Real Madrid Coaching Stint: Challenges and Farewells - Devdiscourse</t>
+          <t>Delivery giants face share loss, Amazon threat, leading BNP Paribas to downgrade FedEx and UPS (FDX) - Seeking Alpha</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 12:09:20 GMT</t>
+          <t>Tue, 13 Jan 2026 17:48:34 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPUjNYNjNfVnNmOS1VN282OUdXZ0RFMmpyNE9aR0VLWGZYNU1DYjhfUkZ5US01VF92eFNNdGVLVVg5dURJeFZYSjZXM3JudUttZFdLSklmQ01pWXZ1a0RkQTBUSEFRUlRYWEFGVDl2Sjd3M1dzdGxaWmdEQlFHdzhMNUhsdWNGRGxkazBWa24yV1NaMGg2Vzh4d1R0bmlYZjZVb1dNNlJ1a1ZCQW8wX3d1S2pwMTFzQzlhczZVYUFoUXgtWkt6bnhvcTRoZGhhdzI5d0lfMtIB1AFBVV95cUxPUjNYNjNfVnNmOS1VN282OUdXZ0RFMmpyNE9aR0VLWGZYNU1DYjhfUkZ5US01VF92eFNNdGVLVVg5dURJeFZYSjZXM3JudUttZFdLSklmQ01pWXZ1a0RkQTBUSEFRUlRYWEFGVDl2Sjd3M1dzdGxaWmdEQlFHdzhMNUhsdWNGRGxkazBWa24yV1NaMGg2Vzh4d1R0bmlYZjZVb1dNNlJ1a1ZCQW8wX3d1S2pwMTFzQzlhczZVYUFoUXgtWkt6bnhvcTRoZGhhdzI5d0lfMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOSnJsVnpObnBldzJoUHVHT0VXSHJpMXRTS1RySG42TVdJRzRqcWpkVHRYR3VCLUpocndWY3Vjb1BJSXF1RVh3VkttZXBlZEJYNDhvWHQwUXlXdEZKTWpxdDlYQ0UzYjJSYmxVdWpoeVplUVdpcThmWlVOUUZmX3l3RFhXcG5vdW5ocTZGTWhNZWREc0N3U3EyTThxdkJrT1NocV96aEY5WjBvLWY5ZmVScmhfTEU0X3poME1sSTE0WmdINVd6Y28ybkV3?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46035.50648148148</v>
+        <v>46035.74206018518</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hansi Flick saved my career — Raphinha pays tribute to Barcelona boss - Pulse Sports Nigeria</t>
+          <t>Walmart makes bold move to challenge Amazon for customers - thestreet.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 11:58:09 GMT</t>
+          <t>Tue, 13 Jan 2026 19:47:00 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNSmtSdGlSdWRMNDN1Q3JpSE1wbktXaEdKbkVMZXIwal9Va0ZKX0VWQ2JCNGpZbzlBSGYxZ3dveVh1TmNfVG1Zek5yUnQ0NVQ1eEswMmFVNlBlcWF5Mm0zZnQ5RUJ1RnliVWxwX1lxM1huVDRkeGV2TnAyUk5fZDA1T2NlTzJKQ3Q5cXVqLTY0Z0tPeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQMGhwWGx6cWVGdzkyRE9nRWdLUWVQR3VjbkNlMGx1X1Rub0lTd2ExMjlnNmoteFp4WG01b291SmI2cmNuSVlCa1NzVHRUTk1lb00xRk1ZanFGS0M0bjRXejltZGM0dkRCaUs4ZGFZeFNDcGdMYXFBVHMzcnQyUWNFUktyTUtNTnp4a2QxX09DcS1DbnhJ?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46035.49871527778</v>
+        <v>46035.82430555556</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Simon Jordan insists Sheffield Wednesday is a HUGE OPPORTUNITY for potential buyers! - talkSPORT</t>
+          <t>‘Valid Crashout’: Amazon Driver Clocks In. When He Sees His Route, He’s Ready to Quit on the Spot - MotorBiscuit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 11:20:07 GMT</t>
+          <t>Wed, 14 Jan 2026 02:01:15 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQQU9WVHF5OWhMMjJEVUFHODZJcDJNdmNRR0xVb3F6YU9zTGgxU1hTaGwtUWZMcEhnZUgyRzhQX1VmNXpfNU1EUnhoVWhDM082Qll2T183OUItb08xY3lXTDZWNjM0OUFoR1VtN2ZLODJYQjdDVUdEQzJ4UlZGZTlhTFk4eUE3Q1Y3bXZtcjRzLXJqRmZfQkFlV3lJRlhITC0xbVZnQ1RCYml5OTB4SXBGU3BhVF9LblgybnBmbkZQeWZXVlNYNHVUSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE82NmNaN19iX01QVzBaT0RRMU92MDhFalNhQjJhcXBZYk5pa2tXTzJKdGNiUWEteWhFM1hLT3RqWElUdXhKZEYzM0Uxc1hRb3B4SExvSVUwRnZkUl9LcVFxTUR1QWxMVkZ2bFpGSXQzQW50UQ?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46035.47230324074</v>
+        <v>46036.08420138889</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vinicius Jr makes final Real Madrid transfer decision - footballtransfers.com</t>
+          <t>Berli Jucker Logistics and DHL Supply Chain Form Joint Venture to Elevate Healthcare Logistics in Thailand - DHL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 08:31:00 GMT</t>
+          <t>Tue, 13 Jan 2026 22:33:09 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNckJHZHA3VFV4NnNUVTFwTjJKR2JoN3Fub1VOakFiSElqNHdHRXFKWV9pZ210NzVsVjBaQjNYZ0JfY2dnVjFPM1FEaU14bzgwcFBnWXdpa09IVER4SkNzWFUyRVVveTdZY2pDQ0F3eGRLTWxCRFJnWUlRTGlBUkh2eWZpOTBuYzlFblgwMmNyNllVUEdXRDQwdzdONjBYU2xBNTU5Qld5TWQ1dFpfRExiY0JKeXBBdXcyN2FqU21fZTlRbGRLejZUNGFKQjIydXJ5Z0tSYUxJNXRKTlBtdVF5WjRYcmVaYkNSdXFyTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOYTFBcGJwRWZELWZiNDNLYURIYnNXUHAwdFVER0lTUEZEdVhPOUQ1a3BQc2x5d1ZjTGJFUTRPb1FFV1J2bktQSXloVlRIcGw2T09mUXJ1U0h6OXNDOFM4TjRlQ19qbzEyUWUzQ3ZCYlQ2R1djQ2pySTc0UlozcC1xR3JKa1lleVlDUnIwdUtSTHhLa3VqODR2QjNHVVdrR1dKZEh1TEtvQlVBdmNDRmdaM0o5TnJLOGxKVHdxUW4tVHhJRTN5MUZOZ3ZMZGNUVGYxMV9iRnpTbURVazFERVUtMjhfV1htbl9tcVprakp0Vl9wVE9yWXktbWNaNA?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46035.35486111111</v>
+        <v>46035.9396875</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Guti points to the signing Real Madrid need: 'It would be a bomb' - madrid-barcelona.com</t>
+          <t>You Can Now Tip Your Amazon Delivery Driver for Christmas – at No Extra Cost - AOL.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 11:45:00 GMT</t>
+          <t>Tue, 13 Jan 2026 17:44:58 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNR0ozdE9lSzJkSDJvck5tZGFwelpVYnNKQmhHWHFoLVBudU9wUlBQbENKUmkzYzVxSnNJUExack05anZkMGp0T0tsQXhWTjgwWEotNUhCTVlYQndIeWZDTm5BV1dlWG1mdHh2WUkzemVCWU5xR1NQWVJaeEdWWjQ4U0x4b1JVdTR2MExYVk1reWhuUnJrRExrSm12UkRsZklXTThhMThfcTZvVFRrMThVaHBiZldQWkI2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE8zRmpzQkY1LUpwSWlrdWpPUm9PZ2dRREdRdklMdkpzTDA4WGxfSUpWaU5SaUswaE1xODNnaU53V1BnTzlrcnppUTY0UTdJOWVqQndVTURvSVJaZlpIU3FkNDZBMzdFNGF0ZzNteDNjaFR0V1pWSjV2SklDSXYybUU?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46035.48958333334</v>
+        <v>46035.73956018518</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bombshell! Alfredo Relaño announces that Florentino wants to bring back José Mourinho (62) - madrid-barcelona.com</t>
+          <t>UPS in 2025, and How It's Shaping Up for 2026 - The Globe and Mail</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 10:00:00 GMT</t>
+          <t>Tue, 13 Jan 2026 20:44:50 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPVWNEQlpsSkNiS0l5X29wQkZZcjJNaE1zVWpBZVFpVEp3cUlFQ2hoOXdFTzEza2xKV2k2T2lTZ1dxYlhzcFF2UmFQQktUYXozVUUzeXBrWkdJMnF0VHZIb2NzX3lIZnZhalFuaHVPZ2hMdmNoamEwWHdMWXdZUUotSTd5SGhnMXpYTjMwZVV6eW9vTFJDTXctcVFqWXZzWmhuWXFYYUtxQ3h6ODNENXJwTjVaUnJZSkdrbWVGWXFQVXVPQ2Iz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQQzNsRThMNlNpbzBGOUQ1b3k2YXJ3aEw4RVhmN09sdl85c3FDZVNoMDI2WHdiajZ6UU1QRnlVNUhDRDJ0Uko0LWxoa2p1aEVtRm9ndy0wY2Qwblo4UC1MNTg3eXowOThnMVZxTnFRbFF4RTN2aVg3bmoxd09OOVpDVVRDVy1kX0w3MHkzT1pyTm80ajhWNVdWcVV6RWg3aFk4XzQ3VkZBQ2NkY01uN0VMTmFST2oxZFpTZXI3bEM1MnBGZVBjRlBnQ3RfWQ?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46035.41666666666</v>
+        <v>46035.86446759259</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LIVE updates after boy, 18, dies in stabbing near high street - london-now.co.uk</t>
+          <t>Lagos steps ups drive for safe blood supply - The Nation Newspaper</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 11:35:29 GMT</t>
+          <t>Wed, 14 Jan 2026 01:48:59 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPNlRSczdjcWxQM2Zfa21rRmdObzlyZVJGb005LUctRS1fOG5CTllaVldQYTM3Ykd0U1U3TFRBUmxWbEU2Sk8wQV9OcHRvVFZ3X1FHSzJnNDBiQW95SnM1VTBCQ2tjUnRnajRtVkp3RTZsMmpGclV4U2txd3RhSjlPQTdoTEdWa0pDVTR6Y0k1ZVRaUHgtZTBoZUg0aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1FQ0tpVFg3NUswcFNKTGt1RHRtZXlTcXRCTVdVcUFnYUNuWXp6TGJSRWJrV1BidkN5NHA1NHh3NjlJZExqNmhrZC1YdmVkQ3hjMXhMOGY5OXkzaUVoYzJxenVIeFNYTGhYSHZYclJoQVViMFpfcWFobWFWSy14VDjSAYQBQVVfeXFMTXV4OHQ5Nkk0SklwbGplUjN4N2FvejlLZFRuYzgxcF9HNFVoR3A1OHdhQy1ObE5KQ2oxajhaM2E0dTVnQ19NbXhfTjdKTjJjMDRKMGt0cDRRNGI4ZnJxUDRyTXV4UWpfa0tvbndIcGZKcGpGeW15WldQSGNRXzRkdFU3Szdz?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46035.48297453704</v>
+        <v>46036.07568287037</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bomb delivered by local to police station detonated - GB News</t>
+          <t>FedEx expands parcel pickup and drop-off network in Poland through Żabka partnership - Parcel and Postal Technology International</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 11:31:32 GMT</t>
+          <t>Tue, 13 Jan 2026 15:10:59 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5TRU9ITGVXanJfRHNfNWFxcTB0Q01fSjZOeFYxaVkxUjFjZzBZOTZqbVB1QnJXaDNtVWtmejJlcC1TQnZhOUVWWnVVMng3cjB3S3JEMm4yRGk0alBvNDR4c2pUSjRBS3NMLTNCeHFxNW5mVXZOTjRoRFJvMnFrMmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxNbFhoVkhleVVfRkR5R2ZQV1ZOcGJqYXNCZUFQQVV4cnNWdm9XS3VxSEljZlUwakZjeS1HVk5mUklVSE53d2pqMTJmQ1QxY3Vna0JGcE5WUXc3V1lxOGF5ckd6Nk5naDRueHoyUndLS1Jhb19fQm9SdmVUQnQ3TG5jLVRFTkdoMHJsU0MySHljQVpBeXc2T1VhNzVzODlSNEVPb0pfYXltWWlzeTFuSEJVLU8zMlBWT2pWVHpTRDE4VmV6V2UwdlZVZFhCcjJBSnplcVVRdGRkc1B4RjVuX1hnTTlDQXduSEN5OUlQNFVhUXhqUW5p?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46035.48023148148</v>
+        <v>46035.63262731482</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Former soldier who threw petrol bombs at police station jailed - Oxford Mail</t>
+          <t>Mixed messaging after reports of Amazon delays in the Channel Islands | ITV News - ITVX</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 12:20:15 GMT</t>
+          <t>Tue, 13 Jan 2026 18:26:52 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxON01pU2FuMDFsNEhwQzJETncwbzhLVU5LLXJOMXZmWW1xMmtoN2lDdUE0RXotZTlvRUpJNXVyV3UtUHYwV1RfM3M1TFJkNDgtclM0cVBGTDFYUktyNHM1cHpIMVNHTEh1Y25uNXR3X0xOZjVobEl1Qm1ack9rT1NfeVBnSzJ2UlNpOU1WOUF6M2dxaWdPdHM5S3dIcTYyamZKQkhFTmRTcGJjUU8t?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQUkVnUVJaSHZSVUxhUU1YaDk1OV94bGlpWDdicHAtREdUNThIYzUzWHVBWE5XMnFxbmQ3V2hQSlRhQ3d2TlR5MUdpUjBsTVZMVXJwaTBtMktrNVhiQlBDUFVyZGlObkJQVHkyVlFXVktNV1RLZHFmRTFjdTVmUVlBcjJZVTBtTjNhZGhqaFQwNjVzU1JGcUpmM0x5ekxHUXllZUVlOU1yaGU0M2VXUDBtRzMtQQ?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46035.5140625</v>
+        <v>46035.76865740741</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>talkSPORT hosts apologises for dropping F-bomb during passionate plea to Arsena - talkSPORT</t>
+          <t>UPS sees $10B loss in container industry - The Manila Times</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 11:59:17 GMT</t>
+          <t>Tue, 13 Jan 2026 16:07:00 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNaHZiTXI1R3MxLWNwT2thQlBXcVhhd1RfZ2ltSm1ZUmo1ejFuN1hpUXRZSFZZQTE1Mmg2UTV5T3NWbmRvOHRRZ2p6alZrMmdPQ3o1ZHhLMDVkNVRCUFVVeTVtcUl1ZGhuRE0xWUQxT0ppdTZTSVp5Z0FGVnB2bEk1aWJVN19KMzZzZkFJeFFDM242TUZJa0tpRVAyZWJ4SVctbC00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQRkdHMkowZGJQWS01MWoxVVd5X3d2R25GTHduZ0Jkajd3YnNkMDZmOTdQY1RuaFRQNV9LRGRwSzlYdXhBYjRPR18wZ2tMUTcySEotRVFaS2t5NWpMaFd5QXFVWkRFSjMyRWZmejVzWHJpYi1WNGFVVzJJbkpRblZ2b1I3VTJtMy1QaC0xa2oyNjRhX2FQN3Zzc1lndk02SzQxZzdvb3RMQdIBrAFBVV95cUxOZUZuUTFkazVCelBYLWRMMENvb3BJV2JKYUZ3SGJuNWg4OGRxQzV6QUd3aU0yR09icjBlMlBqSG9kM0Fkc1J0MXJaSHNoM0l1cUhUU1pEX25VUlR3NTdwaTExRGJyMW5VOWFDTmh1NE5OTWl1N1NCdXljT3hmcTRmeTZObFJsWkxJOWdlRWdQaUluUDgycjQxNkp3VmtkVllqRC1sUXZRZ1VmV0ZH?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46035.49950231481</v>
+        <v>46035.67152777778</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Michael Jackson's explosive paternity scandal linked to Marlon Brando - Geo News</t>
+          <t>After shooting star shock: Frankfurt stumble through 15 nightmare minutes - Yahoo Sports</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 13:26:00 GMT</t>
+          <t>Tue, 13 Jan 2026 18:23:00 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPcTBBMUQ1NEZQUWJPVk9hYk9TSW5PUXdTUVF5emtNNFFEeTdCaE5ZbW5Lck1QZ2RSUmpkbWpDMW1xNWJSSHRLUFgwU1c3T1NYVllSZmpsamVRZW1ROG56VXN0RXR5Uk40eTM1VnlQTHA4Njc3YTl5YXVPd1FWVTVpNEtiY1oxUklMeDRjY3JYWmIwZXhCeVZNeHNabG96dllvUF9n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOdXVaTzVlSG1RejlYTVljSHNBMGs3am5IdWFqa0R5Um9odTZUeVZoSTFyblI3b0FYa2hrb01HTGpGcGRnSm1kUFl1SG1SY0lBdmFqaThhclJwMzN6Z0Y4aXFXRTVjek1iZzI2UGhNOUNVS1JEV1lhU0tpc1lhb1IzdEJpRHJMd1dYT3ZJbmZuaw?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46035.55972222222</v>
+        <v>46035.76597222222</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Capello criticises Pulisic after Fiorentina match: ‘Only Ronaldo did things like thatʼ - Tribuna.com</t>
+          <t>Germany charges two Ukrainians over alleged Russian-ordered parcel bomb plot - kurdistan24.net</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 09:42:04 GMT</t>
+          <t>Tue, 13 Jan 2026 16:15:00 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUk04MVBvSXRRcGlvbWZuTnZhN1lEUjg5STBDOUFtRmNtMFR3YXdxUm80NWhOV19kNkpaNTZFbkdNdUUxTFpPNVJ6UjhrY2dWb29OMzdqXzctTTdsMlotR3laMjRSMndZZE43cEpQYkVXdTdvU1dsTVJBalVlTTBVRXIzVnRkQ1NQVHB5VWZ5LTlqTmR5WE95Sm95Y24zNE1BRW1XYnphRktwU2Nka29FWVBsMktzNVV3MENaZzBpRXZkNkIxNlHSAcYBQVVfeXFMTVJNODFQb0l0UXBpb21mbk52YTdZRFI4OUkwQzlBbUZjbTBUd2F3cVJvNDVoTldfZDZKWjU2RW5HTXVFMUxaTzVSelI4a2NnVm9vTjM3al83LU03bDJaLUd5WjI0UjJ3WWRON3BKUGJFV3U3b1NXbE1SQWpVZU0wVUVyM1Z0ZENTUFRweVVmeS05ak5keVhPeUpveWNuMzRNQUVtV2J6YUZLcFNjZGtvRVlQbDJLczVVdzBDWmcwaUV2ZDZCMTZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE1PYTJVMWRsLVMtMmpqRjl0TkZIdVJXWnZYR3JRbG1qbTUxSUhLbUwxZU5pd2lnWEFtYjgtYVRLSmNTX1o0akl3dDhDRFRpRnpOMTh4VHJn?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46035.40421296296</v>
+        <v>46035.67708333334</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No. 0 Iowa State visits Peterson and Kansas - FOX Sports</t>
+          <t>Harry Kane talks unselfish assist in Bayern Munich blowout - Bavarian Football Works</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 09:43:33 GMT</t>
+          <t>Tue, 13 Jan 2026 21:30:00 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOcXptUlFXeHpSa1pQME54OUE2Z3pUVnhVdGJHb1Y1TVBmSXBSU3JRMDlzdDFpTHI1V0M3bzBfM1J6UWNTaXNDVkJkcW5VajllUS1qeGxtVUJXMjVLUU9iaDFtajFRbzVyOFdGRGNjaEdHSXlZWXFyb043YU9veE1DdnRZdzVwMFNM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPNnpfYkR6VkdMXy1rcy1TdkU1dFM3Z3ZTUW5wYWlnMWJ2WlFzUmQyWWJfV29rZUJTNmZGWEowWkJSZ0tzd0NRZ29ueG9hWF9ZeHRMdWRRb0pXQVhENTctNmt2ZGxWY1lqZzU4Q1o4UHh4OVVDQTB1a3JHZHVsTVktaWxlMzhRd3JVQ0pjU3FsdUNnUVNiY0VrVF9VMlJkMkJKdHdOOFFjSnV6TnRVYzNnV2tpUkp1NmltWnI1WV96eXhsOWYzWUd2dXNyZmJ1NF83Sm9rTE84Um5uY010bEtBQTgxREdQMVZ5WHR5ZkV4bzJoUXM?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46035.40524305555</v>
+        <v>46035.89583333334</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>How will climate change reshape the Winter Olympics? The list of possible host sites is shrinking - CityNews Toronto</t>
+          <t>Raheem Sterling offered Chelsea lifeline as Liam Rosenior reveals plans to speak to 'outstanding' winger over 'bomb squad' demotion - Goal.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 12:29:00 GMT</t>
+          <t>Wed, 14 Jan 2026 07:57:07 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNZS11MTE4cVNjRG9KRjV2RmVnRGh5eDY5UHpmaGg0c0lPWHNiSE5fbnp0N1d6cVJkVFdyY0p5Tm9SY3ZXR2IyVkp3UWpIVUt6WHY5ZVNyRzRLYm1BQjdjVnRaYUJMaGtFelhBQnBoRUszbXVReVRObGlhTDZGVFU0T3FCanFRWFVMQ2ZVcTJvOTRHR1ptNENDUHdWYUpUeHR1akhURkFMQm1uNlpNUm5KdFFJbWc5QnJsNVVEX0Z6SEQ0cTI2TzY4NVZWUlpBWk9lNnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOdFVrNC1mdEFnQjZPRnA5NlNmWkh2NjNiREhCRFNXUWFoamZzLW5uOXJLbnlrWWNiYjVScWJacDBvN0tDdUcySVU2MUlvMGNmTUZINEJLUExPRV9GQ1hrSHppaFJOSFpCVXQtQUdiaHFwamtYc3JVQWpZMUxSRWEyanM2R2l1X2VmTVI4N0RSNHBSQ3psN2dDeUR1aGhSYXQzYjhHS2xyeWk3dWlPTEFabWIwMk5ReWZmN3Q1YzdmVmZBcFNVUzN5SWxEOW83NUxHTl9FZWhMT1M0ejBzaUxN?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46035.52013888889</v>
+        <v>46036.33133101852</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>The Netherlands to propose new sanctions package against Iran - Euronews.com</t>
+          <t>Nartey's breakthrough goal gives Stuttgart a 3-2 win over Frankfurt in thriller - The Killeen Daily Herald</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 12:53:58 GMT</t>
+          <t>Wed, 14 Jan 2026 01:37:04 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNMWxoakVvTU1qbjlieF83WW9EWXpnWFpvRkFBV0tSdGdnNDBKZkZlWTlnV3hIWVNOaFE2VW5kRTFmRHdrZHlhVzc0YkFDZ25XbXp1bGJveDBzbjY3UjZlVzJzd2czTC13cGx0ZHFIUVU3bVNnbnl5OFN1cENvbk15c1A1a2hPdkZ5ZjBvZ2ozeDUxZUhwUlprdzlId2tDdjNoZDRiekdBcWlabm5QSUQzTzlrM1hVclBlYlVERnEwaVNzWXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxObXZ0YWNRQXQwRWdVVmtLamVNcTdYdGFhWlZRVlNVSFlWWTE3M1oxcy1ZRDhhaVlUZXYzT2ViRHNHM1pfX29ULURvbFZCUG5QMmZrUXVDTjcwRm5TcFNpQWxvWGY3enZYUG4wZ25MU3h6dExxTTlnSFBJQ3ZsbDFVX0hsLVJIcHcyX3Jpc1BZQWVXSEY1VjBvd01rNWtQVG5uT21LYllkNG16X3ljS3pUMlVqT1BlYVd6dmxZbFM4bi1ubzluUFFCT05YZlRuYmFmSHlINkhzdU1ybTFMbmNqbENxalZsSGNtcmRMeEpkOEUtZW10?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46035.53747685185</v>
+        <v>46036.0674074074</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Crime boss sentenced to 12 years in prison for drugs and weapons offences - belganewsagency.eu</t>
+          <t>To Catch A Cheater - Marcus &amp; Emily: He Thought She Was Cheating… But the T - JAM'N 107.5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 12:00:00 GMT</t>
+          <t>Tue, 13 Jan 2026 16:24:01 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPaXBra3JFLXlvUHhmSGJZMHNROWNFR0MxZENUWFBMQTdJQ2Y0Zm8xcGpQVGM5NmdYTkxnbnBlQldGal9DQkI2NEY1LXMtalR1S3F0UHdIYzYxMV9FVWNMWEpicGdCcXR0LTdYb2tTQkFfNzRDei1waUs1RzdsZUxMTG1scjV5MlJ5b3JqeUJsaHZJREk0ZjNVdGstYXFwSHdDWU1FeVZZaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNTmUwS3lsYW85QTllYlQ5eVd3X3J4bk8yZmppZGczbDdCcE9Sd253a0hqMllFbVZiYW10U0s1aXF5WXpwN2lWSkwtZ2w0djZINEl5ZXpDWi0wMHZ3cGtWN1l1TGkwZUdQUWJuUHlkbHk5aFZfWHViYjNMSWxOX0VPNDM0bFZudWlLakRibnJjWklEdEl4V1dNb1J6NWpTODBxOVd5dkh3d3NfOVV0bjAyQmY0SUNVX3ZlWUVTQXdEOHZnbnJzMlAzbTVmT2lKcG9ZckgydVJYYUhBNHJkUEw1cg?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46035.5</v>
+        <v>46035.6833449074</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Polish Government attempts to prepare population for nuclear and chemical attacks - Brussels Signal</t>
+          <t>Popular 'repair café' for broken items returns to Powys town - Border Counties Advertizer</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 11:02:07 GMT</t>
+          <t>Wed, 14 Jan 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPQkI5TGlmclF6dzQ4N2pQVzZoSm1KTE1keHUtVVR0SDFQRlM2dTZIbTBuV1o5Y0NRQmRRc09JbWtjV2lBSzd1T1pRakhRUUxzbVFGWFpWLUJkTGxTOUZPaE51R2RmeTd6R2xsYjROdXhvYlgteTZDTG5IWTQwckJZcEhqY0QwVko4blhuUGhwcEpHZng3VC1ja21jQnV4em1zM2NJeUlnTXJ2M2x2ZTlSc2FtNHJpRGs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOeS16bzRKRXdIX3B6Smx6WklVZjlnTk9YdG5uczlKNWdRdHk1VHZ0V040N0xuV0NtbnFpQkIwcXZGSnBMZk1pQmw5MXBzbk0yeUQwNFdmRGxiRXFaUG1KbmVTVXJycXpYT2pydEh0dVQzVmsydGJmUmxDNWY5ekhRUlp3RllqakJjRkNzd01DTXFiWFcxUnhZ?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46035.45980324074</v>
+        <v>46036.20833333334</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hungary to Pursue Legal Action If EU Approves Mercosur Trade Agreement, Says Minister - Hungary Today</t>
+          <t>Animal testing to be designated Key Infrastructure - Freedom News -</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 09:12:19 GMT</t>
+          <t>Tue, 13 Jan 2026 16:01:47 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNZ1c5dHpqcW1aaVM1MUM2ZEtDYUVUQVhlOHdCTlR4OElWMUd0bFNlMzFWQ3gyS253SllQdTV3alVPRVdKbG9MUEJkN0ZGOU1KUmtoM1M2bUJNWGV1aUR1a0t0V1pmLXp5cTVDdTBKakZrNDM4eEZFTlBRa0ttMGFPQlgzUHlqODF0cXZWR19tYUxxNktkdW9NMTJlWms0dmloSm5nM0VCdEl1cjJJdlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNWGtVbUdhZ196WHZyZ3gtMjVrbm12TFNiVmpTVmR4aWRsVXV1T0pBT3FlS2x4aHIwV1U3c0lLaUlRXzdicHVidGF0RXZPWFBGQ29OdldwOVFELXkwT24wR0VneWtYbzAzVGZRR0ZadU1KSnhySkxzcXVEWDNGYnN1ajUwUmVEWjc1YkpXZm5kVG1SQzg?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46035.38355324074</v>
+        <v>46035.6679050926</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Algerian President calls on nationals abroad in ‘precarious’ situations to return - Brussels Signal</t>
+          <t>Santos Tour Down Under sponsorship faces growing scrutiny - Australasian Leisure Management Magazine</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 11:41:03 GMT</t>
+          <t>Wed, 14 Jan 2026 01:02:45 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPUHNUTHRtVldyZ05hNlUxcWJoYUNlc29nX0hnR3RBTElCaWl3TERIZTI2VHBxZGtfT0ExNmJNT2hVcXR6UGhsVlVTZmxFVjMyQU1RMzk2eXgyS2hUV2VhcVNfR2RxSS0ybGxsenBPXzBscnlfU0s1cHVmb256eFBzc2hqLVhLTlY1WWl1djl1SXJuVG1tZV9sczNSQTRRaDBtZUQ5N3Nzc2JwYWRfS3Q5ekR6OGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZFA4OE8wOUJnMk1vOGdPZ2wwbjhJbmNoYnVTaks4dEV3a3hUSkxDSVdJWVBxelZndjdndTd1X2lyRmNrVU1rR1pvZXpuOGEwcVpVVzRZN3NoSk9CbEF4TDF2U25PUmRqMGdvZlg2ejduVzItenBYbUtnZXhtYzZkVzFyVy1ETm5aTVZleXFrbWJpdGYtRzZj?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46035.48684027778</v>
+        <v>46036.04357638889</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Antwerp’s AZ Monica hospital hit by cyber attack - belganewsagency.eu</t>
+          <t>Man charged with shop theft and having a blade in Sutton Coldfield - Express &amp; Star</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 12:50:00 GMT</t>
+          <t>Wed, 14 Jan 2026 07:48:04 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNZi1yOE94ckdabTdpWVZwZzVSMngxNTdsODZQNFZudkNHYndqRnZEcm5henBnWHVCRjA1Y3VneW1VbGhqeXY0OF9GdUFxaXJLQTJ4MDRwYnJoVVFBX1AzRzRtdVk3SVFaWEZZdlVfLVNkTDc5T0lBRmpYbVRnaHBiNGY1MzE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOLTQ0VGFqbmJKazloc3BnUHRTQm1ZWVlPMTl4SE5ZVDAwWUZvazNVdjZNMUxrc1BsOTBhOUtTOVRiT0hYY2Y4ckNXMTA0cUZRVlZ5WUs2bmQ1T3VDSHhNc09WYWN0dEF3TXZ5NWw1OWhPdW90RXpVRGR2c3pITDlFNE1Wdk96dzFxX1ltN1Q5T255RjgwMUNDVW1HYmljcTc3bXdIbXY1d0tpZkViS21sRFZ5VnE?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46035.53472222222</v>
+        <v>46036.3250462963</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tehran faces rising int’l pressure amid deadly protest crackdown - Hürriyet Daily News</t>
+          <t>Organized retail crime investigations up 31x since Governor Newsom took office - California State Portal | CA.gov</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 08:33:06 GMT</t>
+          <t>Tue, 13 Jan 2026 18:39:03 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQeVM2SGJLNmMzYXNUMGZtR0tmZWM5bzdEejFpMUE5NEJFVk1yOHplQ05oM3VqbXpKTVdEaC1UZDM4d21ETU1ZN1otUlY5aDhhbzJPMXZ5QjJ4TzZ1VENTWG85NXlmQUhYWEQ1bGUyYjRPYzlnZ0gyTjcwNnZTWFlQMWNkNVdEQ2QyV1FrODVabzV3TTQ0elZDN0o1b0NrREpTaExYRlg5Y0lZNFkt0gGsAUFVX3lxTFB5UzZIYks2YzNhc1QwZm1HS2ZlYzlvN0R6MWkxQTk0QkVWTXI4emVDTmgzdWptekpNV0RoLVRkMzh3bURNTVk3Wi1SVjloOGFvMk8xdnlCMnhPNnVUQ1NYbzk1eWZBSFhYRDVsZTJiNE9jOWdnSDJONzA2dlNYWVAxY2Q1V0RDZDJXUWs4NVpvNXdNNDR6VkM3SjVvQ2tESlNoTFhGWDljSVk0WS0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNcV9Ld1NvMWFUZnVFRkxJNk9MOHVxcUtnR2pVQW93cmVvZG5ISmQ3SHlHLWNIY0Y3MmxfcTVTZmdyYzU1dnEwY19hUDM3Rmt1UjlQaGx0aUxOMUY5dEJNbWtfeklYbFUyeDN5M0N4QkExc3RvWk5HblpUZlU3QUpKSkhXTVFuUkQ5SXVGMEpLMl9IWmhKb19Pek1lRU9EcC0wTE1iMVJXbnRsWEpFSUp0WWFGMA?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46035.35631944444</v>
+        <v>46035.77711805556</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Nearly $17M in retail theft items recovered in 2025, governor’s office says - FOX40</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 23:33:24 GMT</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPRlpEd2tueW4wNnZtRk82d3NMY2dGTFhadkN1d1pLWGJfSmc4VVdQWWZZOUFQb0p4UmpUVTdlS202QklqS3d0RmlacVluTGx3RzBWWlVkcGE5SENPekc5d0JfQmlDV01rNVRwVDFsSVR5LUpkX1gyb1V1Z01ldDNZWjVnbXpqZ3lhUnpoNkRNbmozc1RSc1liMGNtbGpiVlJ0RjZwb0JsM1dKY0lPOWdkMkh6cVI4U3M4VVHSAb8BQVVfeXFMUEd3OTgtTTA5b0lLb05iX0FVVkdySkswYzV2djVEblp0LV9FOFlzb1RBVWc0UnFFNHZmM1huZjNaaHJ5elFxUzk1dzh5VXo2QmZTdUdacXFPeXNjNENPZTM1OWdacjljSXpRdFdDWTRFY3c3bEY1M3B3MF93YUxpTm90X3E1Vi1ydXlmc1NPT0hPSVg2alF2NGwydzA3WXd6aGRvU0JTV2ROcVRkNTVPMkpVMmNkYllhU3lQcG56NGc?oc=5</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>46035.98152777777</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Retail Crime Unit 2025 Report Card - windsoriteDOTca News</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 16:50:16 GMT</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiRkFVX3lxTE93TWZyaU14bkd0VjRCcS1ZZldnX1FLWG1pcldBTjhfaGU0dUtOSk5xSVM1Qnp4dHpLbFBKdUNVaEJNUmVEUVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46035.70157407408</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Retail industry reacts to Scottish Budget - Scottish Grocer &amp; Convenience Retailer</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 07:33:13 GMT</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQTUJ3c0xXaVhzbzJXeTItS19lWUdpb3VPZi02eTVTb3ZCNE9wM0xWTDh1MEdBMTRqenRMVTBxTEtlYmI5cTMwM3o1cENJN3RXZGpPWF9jY0g4NmtKNTN3RDB4SG5xT0RYaEpxaFZVQTJKWjBMQUJ6MDI1MTRfVU1vd3ZXSUppQkRZX0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>46036.31473379629</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Crackdown on shopliftin­g as suspects taken to court faster - PressReader</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 00:54:43 GMT</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE80SmNiaGNZMGt4eGdsZTBVVFl2eGdzMVJYaDR0bUZJSHRSc3hQV0o1WnRaaldKaXAySzVqU2FwZXJrcl9iSWt4bmRUeHFoWHh1S1ItUXRVV3EzVGtXUHZQT1VGcXI2eHE5cG1pT3BMQUNSbFpnVDFiemhmRFJlZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46036.03799768518</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>5 things police officers need to know about flash mob shoplifting - Police1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 14:37:35 GMT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxObzNQeDA2Z0RER1gxdGtjTVFXUUNlT3hwMXNFc3J1cWE0dl9jVTdsdl8xZG0wbG9vc3o0MzVfR1dCak00dUxxTmJfdTdPWEFNLVB5TVYtcmpTVzhzY0RUNDJyM0U2NGN3bkFheFlEZ0NfMjZMTDZDSW9yeXk2MTZVR2RpTXJwU2NDckZHTTRPTHdiMnBBQXNETlN5bXdtd2VyTTEtelJn?oc=5</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>46035.60943287037</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Disruption on trams at Wolverhampton after early accident - Express &amp; Star</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 08:01:09 GMT</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOWjRMdktnbjRwMXd1UmxGY2RTR0NTLUlLcV85WEs3a2RwSHVPejIwVjJSLWpBTFM4S1ZPSnV0UjZ6dllDNjg2aTBUYkhnbmFIQ2tXNGpLQU9FTzBsUm5LZHdkZ3lqblNuYnBlV01yZElsdjRsOWpRcDFpRE1seEFqU3JWOU92Unl6cGFSdHQwUC1Nay1fdUs1cXJ5SzdKWFFQTjhqaUZHamM?oc=5</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>46036.33413194444</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AAR applauds Judiciary Committee passage of CORCA - American Journal of Transportation</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 21:33:00 GMT</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPT2JCOGwzZGtMcEpyZkFUcE5OUkgtd3VpeXg2ejlrME1VXzNMVTRMQlVSTFdtbmpCLU9RV21ub2FNbzNmcmlsMTdkN3RqRTZoSFVhWUExX2Z5UWc4ZWc2SkRRdldqSHYyZUhsbjlLTG90anh5dEVjU3VqM0dONWVObQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>46035.89791666667</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Leeds city centre unveiled as the nation's shoplifting capital - Leeds Live</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 14:42:26 GMT</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQMnFuT2Z5UFNnMDVlaDZ4ZjNXZ3FQYXh3c3lCTmdCeS1Oa1JXUlRwWWYwUzRPdktfSGpEU0NrTlRtbmMydjJSQ0ZrMDlvcHVVbVNzbTIxLXFvU3huc21NX0xmS1h0M2gtRHo2Q2ZheHFIeHpDcy1UdWpPUEw1eUt1WEQtTE5RWEtQT3lMbS1NNTdpd9IBlwFBVV95cUxQN3RUWXBJaW9wbGlJX2xvcTdqSGk3eHVNTl9mOHF5aGdPc25xUkxmWU1kek5CQnJhRURuREoxTXY3T1FxYTFZZlRzNHJPTkRPeGRHQng1bGQwLW1lNXhzSFZHUTVHNFZ4V0ZWVnlXYm1SVlFtR1l0WFpBVndycm5qdExxUTNRMkIxM0ZlWVRIVmtLX2k1c3lV?oc=5</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>46035.61280092593</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Jude Bellingham Issues Furious Statement After Xabi Alonso’s Real Madrid Exit - SPORTbible</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 21:06:36 GMT</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOY3JDOFIyNUhMZTE2Mk1rblpMWk9qVFFDd3VyUTVFY0tqVG93ck83d0JicmRMN21XSGJ3TmlVSHFkd2x2c00yRnFvaE1CLTFWXzlTSzFBQkFMMUZ1X3M2ZDdWSzJBTXZHSmhZVU9FWFhidTRxRUx3X0ZlRTdaRVZWcXdmTEJ3OUtPSzRFWDQzdE9CZ0VHMkFGYU1lLXRMYjB6SEFHNFpaVlI4R01zcTBvQ0V6WFczM2I2ZkdYSVpQVWFfUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>46035.87958333334</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>'I didn't know I was coaching a nursery' - Xabi Alonso's explosive row with Real Madrid stars before dramatic exit - The Sun</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 17:06:00 GMT</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPbTZxRUtocGdKaTB3MXdRUTdmVWY0UG1BMkowV1BrcEVvWG10c0IwVUxzUmlON0UyVHl2QnM0T0VEaW5IQ1dCMFE4Ti1BWW1iOTdFVUtjRFRxeFdqY2ctdmtDNi1WODJjUUhVWGFmYVBRdnpPOE84S18tZ1dZQWpUZmlfc2hSQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46035.7125</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Barcelona player ratings vs Real Madrid: Relentless Raphinha fires La Liga leaders to Spanish Super Cup glory as Lamine Yamal &amp; Pedri also dazzle in breathless final - MSN</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 00:47:43 GMT</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugJBVV95cUxQR3Fxc1lMbnEyWENqUk5YbVI2dnRHbUJ6enJWTWhoLThXeHB4SjFwVHRaald0bDFvS2dlMzVqR3dpRmFTSnlhZHJxN3lKeW5icWo2dE5GX2x5Q0VyaUhYcktOemc5clZWcTRueUljQXQxeDVSai1xYVRUWHhUOFpCZzVZckpDRkVEY0tkdnc5b0x1dldTNFNFb3lrUVRSRVZKbDRnal9JeXl0cnRPYUFRcUhHRi1hOG9jbjUzeVBiNzQwS1FKSC1POTZKTzVUajRXbkNfUkdwS2h4TzM0aUV0QWp5MDJVZHBLaGNUX3kzcXhpSmFhM01adktaWUtVUkdiOUdITU5wMXVDQ3VkclUwMDFiVnRkZWx1RDNHUG9LYS1hNzQySjJjWENJY1VUR3dhMjRkSmRISG1qZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46036.03313657407</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Copa del Rey: Griezmann guides Atletico Madrid into quarterfinals; Sociedad, Bilbao also progress - Sportstar</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 03:59:44 GMT</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOaEZCUFNUZGs3RlVISGpLYm1hajNoWnZTUlZGM0NWRldVYlhVTkI0NUYxYUVGeEdNM3VwcEZWYkxFckFXc3pWQ3R5MDhfaWJTNm9ndk5XakRkbVVWSzhrQTd1ZXFpZjBuWXJ3bTFQWWxyamQxNjMxLTVBNmFBZkRvVVdIQWRSTU9FY2U5eXB6MmVMRjlkdG8wMGpaVW1oQ3VzUjc4N3RDYWNVN0VoTDV6YnJzUDZXbVVsY1l4Y2tCbGlUeS1XU3pIN1J3OTRDLTN0WV9RSXJZTmJncHVyS1RKeGxJdmtSSWdDYjFwLVM4SkRtUdIB-AFBVV95cUxNSjZySzhRMWxVQThTTlJ3SE0zcHN2TzJIRDdFd0dTY3pDZjRUWHlMdTdqZTA5X0RpX0NfYWdfRlV4RTV4QnJwRnZhQzA4ZHAzdnpLU056dzZZdDlNTUw4c1Zmbi1rODl0a3VMVHRVYnV2Q1JHM1U0ZEcwcC14VjZHWWtIN2VPN1J2b0NzYjVlZGdpNGQ5VjRjR19NMENtVklYN2FFSm93bExleVVyV21aRnVBbU1tMmFOd1ZPTklaclVOdVJ5anVFc21uVjZMZ2xNNUlRN05LQUUxNlZEYkFzM2pISlRzQ2hTc0x3OThLd1ROeVNELWpqdQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46036.16648148148</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>‘I am a Mourinhista’ — New Real Madrid boss eager to emulate Portuguese legend - Pulse Sports Nigeria</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 00:54:24 GMT</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQRURkRlp3dEtoUEJQZC1lWlgxR253a1dfZ0dUTDR2N09WZVFuNEd4LUF2TEEyYm1tVGU0NjhkLXdadVROUG9aQmwyOTkwa3diZzdlSFFWbGRIajFnS21vb1M2NTA2SV9VQ2xNbHNZajI1YVREMFF6NjZyQmhQRi1BZVlLUGh3TTBGaGxNVmV3MHluMjA4WXJvR0dyVEtfTEpNMGRpMDlNcWdjUmxSTDZaMGh4UmRrVWtaUWtDOWFiX0M5T2stQnBUOVR3enJlMTlNWkE?oc=5</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>46036.03777777778</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Portugal defender João Cancelo returns to Barcelona on loan from Al-Hilal - The Courier of Montgomery County</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 03:25:04 GMT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPN1JhSkdxWmhKU1FSOUZEU1FTYmNDMkFSejBQQU1PUjZuc2lYSDFJLTVCQ2k2UXVZbndaVXhacEJ6UHRiVnJQTTlnSllIWmtIdGV2TVVFRjVpVXFETzlHNzQ2Q2NMS2lNN3RGQzF1aTZKV2IzQkVUenZYMURFRnNadGxoQ3VjVEVtWGlybldwVHJkTVk3Q3FTXy1vb0JjazVfSFE?oc=5</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>46036.14240740741</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Real Madrid Dismisses Alonso Amid Mbappé Defiance - 조선일보</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 16:19:22 GMT</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOOF9MWHdPZ0lmMzhvS1F5RERKamdfcE56OV81bl9lZmlkTmE2RXVUMFk5MVlOdV9ENGxVMnV2c0dmV2VXQU1DazJ2NGxEU2xubXFNWlVOZFlxT1pyc05qY2I5ZURJbnhfYWlvcVlmeXVqRE1ZRkFtVnV4TERkTVpJQjZoRzVYdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46035.68011574074</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>A video circulating online shows a Michigan man shouting, “We executed one of you yesterday” at an anti-ICE protest in Minneapolis — the day after a mother of three was fatally shot in the head by an immigration agent in Minnesota. - Facebook</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 17:59:55 GMT</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPbnE4a1gyLXV2VW9jaDhTajVGa3lxbkJTTVlTWlh5d0lRT3RyakhaMkxUNFZ5ZDZwbS00eG5xa0t2VzlTaDMxOUh6RTJDZi1HUnlWSWlQMmthMXpzN0pWbktQN0ZybTRka3I2YkJQVGtsR1R0eWVCUVFpbUxLQ1pLQ0d5MmZfQVJib2REVDRKX0NTcVVQOEVKOW9GNHU0RVVCb3hmaTVnVUIzTHQ3R2hmQ3hjMkhWVVRSamhHck96VExCYnBCMm5Ja0gxRXVPQ2lpQWVWRzRWU0hXS3gzMDBN?oc=5</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46035.74994212963</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Former UFC champion slams Real Madrid for sacking Alonso - Pulse Sports Nigeria</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 00:09:33 GMT</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPekdqaGRGZ2ZwMDNlTWxVaS1lODRGRkxTSjVORzBLaUpHR1BJRzdsWEZhclZxQzRKTVdUSHNkR01uZzEzN3ZiWjl2OVhXakktMzBWX3hZcjIyalFyX3k1QTJ1ek5uSzFqekV4S3dKTm9ULWRpdmVJRWZfWWR6TWFxdkhITDc1T09CQnBFOGc0Y1paV0dLaU05UE9ya3lOUDVLYV9NWkVLbndQaC1TWUNDUHVRWHRNTXZGX3c?oc=5</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>46036.00663194444</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Barcelona beats Real Madrid again to win Spanish Super Cup final in Saudi Arabia Clasico - MSN</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 18:29:58 GMT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPMVZZWkpDNTNxNkJPSExfZ2Rla2Z5UjVRWkZOTzhad0dYV0lnLW5OanNVUm1NTk53T0FnUl91LTY5ZjRIbVN6cENfZlpzcWZUOUFqbk10VXJBbVh5SXhrZzdLbFhJQkZsczlGV3ZpZXlrT0s4TXlIM0VCU2FocVc1TnVVRkRGZUdIQ1lfVVdILXpuVUtxQ0wxeVNnTXpoX2k0OXJ0VFBBRzN0cFBPX2E1NlI3UFFaMTRFSVQ4bXVaWUlvNmtQNHc5UjZZelk?oc=5</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46035.77081018518</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Marcelo agrees new five-year Real Madrid contr - beIN SPORTS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 18:41:29 GMT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOWG56WFV2ejZpSlpMQ2RncTlPVlRONkdnVWVHdzVZQlRGMEl4V1BWTDVncnhxb1luZlRxT01ZOEQ3WFZncWNoTkFvby12RWZLMXNBQjFnLWszSHdIaHAyUkxySzVvRjJhVXpXdnZ6VHFka0xaZ2FjLUpDWmktdkJ2ZDBKSU55WDhSRlB3dC01dDhyeE9aVmZ5S1k1ZnFOVDAxUTB2VmtnckdSMmhqT1ZRYVpQMWhrU01UTW1Kd0tYZUhHQmNjVkhF?oc=5</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46035.77880787037</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Real Madrid's Official Squad for the Spanish Super Cup - ysscores.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 18:09:31 GMT</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPRWlwUnNySnIyRDcweHc4RlF6bGdMMTFUMk52dDBNUkFOMWdjSGUxeXJyd0U1Wl9ibERNaURpQ1RNdUg0ZE55YzNYc04xZV9YQUdBZEx4bElvalFjekZuMFl1ZFRPM0pXUjhxQUcyYmREOFBQVXNGV2QwYzFYcUV6X1BUS19Vdmp1OUpnZHd0RTRBVzEtZ0xnNUlUbHA?oc=5</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>46035.7566087963</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Liverpool explode into lead to sign world-class €120m Salah heir as star reveals: 'I want to play at Anfield' - MSN</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 17:16:48 GMT</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwJBVV95cUxQalJDa0VfOENpYXoxX0lFdVJ6VW95cTVPenNLLXh3Y2dldVB5M0pYQ1c5d1Y4VVB5N2RNZ2x3WV9CeUpRZ2taT2d4M09rWkUwVTVXYms0WUZlbHpXU192ajdDRVB6SnhPSXhfVWxNYnVvZmpjVGpuVG9kakQzalNhX2xEUGVncW5KM254NDdIVFVZalA2YnlDbFZEbTc3czZoLWpWTU9zVzBoT1hVQXJXbjlldkFxb3Utc2NOdVhEYkJYa3R6NmlZNDlNNUk2Wlo0RXp1RnI4QkdVRUU2NHAzWW02aEtWV0M4LTNiYzJfN2hUU1pNcldHYkw4TFQ3SDg3VUlYSjRtRDFqMExMNFhrclNtclRmWXpQbUJtNjNUWE4xZS1GNHlKNndJem0tbkoybExEc0QyZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>46035.72</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Barcelona unearth hot Japanese talent currently setting La Masia alight - Tribuna.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 19:19:00 GMT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOaXVUNmthNjVHclNFUUxDZS1QWGIxSEFYLW1lazJsdFROU09SaEw5TEJwek55ZDhELVdNaDRkdWxxU0ktY1JBaDhiMHVoUjI2elRucmh4RU0tbFhYNUVWWFlHQjZWQzEzbFR3NXo0YXlYQkVxMkxKLV9IaXQ4cHVzTmJZU3pKRlNxWDEtR2lCQ0FvVEw1WHVZa3BaYl9TOWhLN1lFejJZcS0zSUJ2Y1E2MFQ3cjU4Z9IBtgFBVV95cUxOaXVUNmthNjVHclNFUUxDZS1QWGIxSEFYLW1lazJsdFROU09SaEw5TEJwek55ZDhELVdNaDRkdWxxU0ktY1JBaDhiMHVoUjI2elRucmh4RU0tbFhYNUVWWFlHQjZWQzEzbFR3NXo0YXlYQkVxMkxKLV9IaXQ4cHVzTmJZU3pKRlNxWDEtR2lCQ0FvVEw1WHVZa3BaYl9TOWhLN1lFejJZcS0zSUJ2Y1E2MFQ3cjU4Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46035.80486111111</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Marcus Rashford delivers Man United farewell message at Barcelona unveiling - MSN</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 22:53:30 GMT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwNBVV95cUxQQmNIRlJ3NDIzXzBTOV9BNTZxcXRGa2o4aDFFZDN4cHZPUzVWR3d0UDlpNm9odXFYOS1FQmxxb0ZUcHI1NHBvSHREZzg1SUZVN2pFLXBRNHdSUnBMVm42d05PNGE2d011bk42dXVXOHNjdXBObHpMV2xtRnNaZWtUc1dpRFhYU29EOVZDVFNtYUFKbzdHb1p4OHVUR0tiT1dWTTA5VWpGSUowN3E0UDZPY25uZ0x6V0lxMkNsZnl6alloWE4wX0RQaHBJbVlIb2t0NkgxRFh5aklOSlhva0hWbk5DQnZDY2dBMENqQi1INnRiaXZwcThMdUtPSTlDYVZtUmNWRzBTUXVPemlyVTctbDl2Y1NHb1Fma0plVkRZMUJtRXM1am1pQXBtR05yRkVQN1hQdHgzTVd0Z0NqRmZIVDh1eGVtb1NuSU9OTEFvWC0xbWxxa210UlZVbUhONWFzWFkzLVU5bDhXTlEwSDlibnBnMlFkMUcwV0w4VExweElqZVo0eHhFZ2VHQkpKbnlxeDRZMk9POA?oc=5</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46035.95381944445</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Massive explosion next to major Argentina airport sees flights cancelled as 22 rushed to hospital - MSN</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 18:27:41 GMT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9AJBVV95cUxNcUpyNmRKX2YzWVZOd2g1cHRRRGgtVGhlMFJTQ25wT3h3M05YRjVrcjNPVTJRT0FDakFrSkRDNEE0MEZqV0l1d1V6ZkQ2a0Nla0tHRW5nc1cyMDZxS1I0UHlMMWNISUR4RUJ6V0NCcFNFVGk4OUNFb2VGa0lzMzA3VTVxV012eUU4NTFfblpTYURkRmR4bVhXd2hLVjY4T3JlY2N6ZmttY25pV2xJX3k4ampZeEw4NEVpMXZwVDlMRFBYRmU4cXQ1RmZ4bDJhOXlhZlRlaFMwZE1wNC1TNk9YY0R6QkZNODFfSS0zT1hEbTJTcnV5UXJMU3QyNzEweEt0ajc2ZHdIUDhXajVYYnd3YURUMVA1ZWF4VzVGTnVERjdLR1h1ZURCcGNBODNJSmFseFl2Nkx3RUdDT3R3bHpiNkdSMDhfaVdRbF9QMFlhQUF1TXNkM3RlaDdrZjRLejN6LXBQUUhBbWVweF8wdkpWXzUyOEk?oc=5</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>46035.76922453703</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Fordham Rams vs Saint Louis Billikens Prediction, 1/14/2026 College Basketball Picks, Best Bets &amp; Odds - Doc's Sports</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 23:41:52 GMT</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQZVhYRVFXVlZkS2ZRMnd1dFdwbmxjU2JjZkdPOEdMX2g4TE1FbFF1QWM1RDExdVZjaW1LSHJMVklVRTV3Z2VtZWpNUWlJZDNvMG44THRZWkZMYkM1cDhNV21FSmxBMzZGTmgzQjBYVjBQR3dENkxZejZDNnhxLUVNREZ1bTJxSDFZcWIxUlN5clRWNDRFYmJ2ekttNjcxRzVfY3ZPUHFzMVFYdkZVdlFEVGZHOUdPMVZEZjlXLXQ5Qk9vMF92MWlMNWFiUUNWQkdQQTYwQWdZX194WW9xb1JHbEpaelhKZWdfTG5DU3pKQnBocXVsbVc4ZFBsZWotZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46035.98740740741</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Siro López delivers a shock, Florentino already has Arbeloa's replacement ready: 'they have given me a name' - madrid-barcelona.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQYzk5ODV2VzBSQS1ndEc2elZRSEM3LTF4ejI1aGcySWV5MHk4dXU2ZzhlZE1lMUd6bm80dmJLME5XRkdRLXE3OVAzMlZtOWt4dUtZYy16V2dhejdDWFk3SFdIbVltUFFqTzhQMkRvYjZTTFBFNWM3Mm1qWTJlX1dZc0hncDdBbTB0dEI3YXlRdC1kSjZuWVZfR0hfLXNKY0tLNDRJSGg5aFRpVFdHVUhlR2otYzhqRnlxaDF1X1p0OUtzdFBJS3VGelRXT2l1T2RlbWUtT3lhZHQxZ0hfQXFOQ2o0MHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>46035.66666666666</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Chelsea’s £300m La Liga transfer bomb may have element of truth given Romano quotes - chelsea.news</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 15:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPVUNvWWNZcXAwS1JyOXlKbFA1S2FiMFBLd1o4LXhCRDhEaE9RN1h6WGk1NEFBRGxTTEtscktLOUI3VHFIaENpOXJRR3NJY2V5ZmlFQTdfWWpRNWV4VEc5TFdrdmpyejNzU3AwclJuRjZhVjhpUVVETV8xd0R2REFCbVFn0gGCAUFVX3lxTE9VQ29ZY1lxcDBLUnI5eUpsUDVLYWIwUEt3WjgteEJEOERoT1E3WHpYaTU0QUFEbFNMS2xyS0s5QjdUcUhoQ2k5clFHc0ljZXlmaUVBN19ZalE1ZXhURzlMV2t2anJ6M3NTcDByUm5GNmFWOGlRVURNXzF3RHZEQUJtUWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>46035.64583333334</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Gambling loss of $20,000 leads to bomb threat at Harrah’s Lake Tahoe Casino - Tribuna.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 17:38:00 GMT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOd1ZfcHZqRGlnaG53eXJzbjdoeC0yZ0R2M0lUZlpSaWQyN2ZPeW9rYm1VSFJScTc1UGNIb21vd2tmdXlTbTNHNUhFcF9lMUZXVVlLYmhxeHZ6QVlWQWJfd3ZiXzBwM3FWOXJUR0lZbDZBXzJLdTR4b1prQ0tkRWIwbC1ua3NxQ2J6X3JXY3hNc3l0anZjYmtnb2FDODNMb3ZscGh1My1VN2RfX1dsSmNHRExQeTI3djlrU0Rj0gHAAUFVX3lxTFBMVDBWdUZDMWpLSGNVNE15VDh0eUpPelVaNVF5Q2pNY183U1hUdmtJYmdIZ2RuR0RtS1VvUDkxX213a19paTZwZUhxREY3WHhPMWl5aVg0dEU2aUVET3hlUGIzeDgtZWZVUWpHcUNjQmtneVo0eThHc3JERkZLakpSNVBXdVZPLU13QW9FZWJtQjJJbHdyTWdhS1dYeHlHM2lyNmdwcWJaUERKQ0tZRE4xQ01MZzY0R1N4eTBSOTVGaQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46035.73472222222</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Cadillac reveals stunning special-edition livery for explosive F1 debut in Barcelona - motorcyclesports.net</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 22:41:15 GMT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQcG5uRWtTOUgxUFJhUkNEVDZ5TXEzWndIT0dGVXpTZk93enNLdVREM21vQXBSSEhzVTFObUNqNDRHYkhOT0w3R21oVWh4ZlpDT0JsdERmTExTX0Y5ZmljVE5XVGEzUGNSbFU0Q3BtOUhFcWZ2YVVEcHdlaUo1d2l2cVZzUUdLRHVtb0JNUldGQk51UzU2TWdGd2pQanpaNUxWLVc1U1lyLXJ1M0lCTy0zMURvdWZ6X0RjQ0ZVUUxXT1lnZ19z?oc=5</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46035.9453125</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Yamal breaks the internet: the record that puts him above Messi, Ronaldo and Mbappé - Pasión Fútbol</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 16:05:32 GMT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPZlZGNjdZMmdVRy1HZ3I1SkRYX1QwNXdWN1VhdEVPZUpROXNzWU4zcWdKQ2NwUW5IMzlYTm84amc2c3c1ZDg5Y2JtOUtXQTVDaHc4c0VXQ0lPUTRhUFRLX25CY2pFSm9rdnpPSzh2eGVOa0dRMzBzRGdvN3JiQnplX0V2dXpNQTFLclhqZmg0djVBM05rb21KZEpSNGoweExKbVFMZkU1RHJ3UzdMa2w1WVlZQTZDWi14MnZ3bkNJNkdGRmM2R1FYVVhoRGlOOHdlWFJv0gHTAUFVX3lxTE9mVkY2N1kyZ1VHLUdncjVKRFhfVDA1d1Y3VWF0RU9lSlE5c3NZTjNxZ0pDY3BRbkgzOVhObzhqZzZzdzVkODljYm05S1dBNUNodzhzRVdDSU9RNGFQVEtfbkJjakVKb2t2ek9LOHZ4ZU5rR1EzMHNEZ283cmJCemVfRXZ1ek1BMUtyWGpmaDR2NUEzTmtvbUpkSlI0ajB4TEptUUxmRTVEcndTN0xrbDVZWVlBNkNaLXgydnduQ0k2R0ZGYzZHUVhVWGhEaU44d2VYUm8?oc=5</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46035.67050925926</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, Spanish   language</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomba" OR "amenaza de bomba"  OR "explosión" OR "paquete sospechoso" OR "paquete desatendido" OR "explosivos" OR "explosiva" OR "tiroteo"  OR "puñalada")</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Bomba de £300m de Chelsea hacia LaLiga podría ser cierta, según Romano - OneFootball</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 15:38:31 GMT</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQdnpnaXBtNVlvdnVUY2xhVEY1VWd6X1c2c0hZWVJJVTBBeHd5RlZTczFzb3BxNUlZdEVWNGNmQWhwU1RLMXd6Q0p0ZXQ0V2Y1ZENtdWRTa1A0cVdfZ3RzSnVxS1NTV1lNZ0Mta05CSkFkRWp3NVdQcnd0LW4zVXRweENLdmtmbkxLbmUyVzZXcVJ1cG5sdS1WdjdxX3VoWnpvanBjdmdxaWFOLTJHQlE?oc=5</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46035.65174768519</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, Spanish   language</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomba" OR "amenaza de bomba"  OR "explosión" OR "paquete sospechoso" OR "paquete desatendido" OR "explosivos" OR "explosiva" OR "tiroteo"  OR "puñalada")</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>La enorme decepción de Xabi Alonso: los motivos y el principal culpable de su despido - Libertad Digital</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 16:48:40 GMT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNZ0NrVWlqZVFjYndhTEpqQnlrMnlsZXNmN0hEMXdVLXlxVVBvZDBCVkxpVzhnbmhSczllVm9HUm9FS2gtZFFGd2JqVy1xTmlkZ1lkNFNfMmpKa0xFMWVBWkVrdkVibHlrVWVXeV9laGJ0VUhvMTdCWXNta3lvYTNNcU81R3JUeWg3OUZhVGVFS25Vay1ONVhfNGR0dUVnOVZGLWg3enFsQUZiMW1Rak1YXzZ5WmNyUkZXdlB6YXZiZXR1cVZp?oc=5</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>46035.70046296297</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, Spanish   language</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomba" OR "amenaza de bomba"  OR "explosión" OR "paquete sospechoso" OR "paquete desatendido" OR "explosivos" OR "explosiva" OR "tiroteo"  OR "puñalada")</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Barcelona's STAR signing for next summer is already being negotiated - Fichajes.net</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 18:20:00 GMT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPenhYbUZzRmFrX19Jd09NZm5ZYWg0cVNGdk1hTzRya0JvSHJ1eG1ybWxvQVJ5ZjBqQjF5VWpVVjhmbTZlXy13TURNRU1pOUpiWXlNcllPS0dkY0lRN2RpM1EydXV0dVZZR1ltODh0VC1xX2dZdU9USER6UUtuOHFKNVZHNEtHSjBQR0o5UGRYR0dVMXEwai1mUWNyckhrTVZoSi11ZGttMXNxZ1JHZUR4UmdxZjc?oc=5</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>46035.76388888889</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Hounslow Council Leader responds to fatal stabbing in Feltham - London Borough of Hounslow</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 16:55:36 GMT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPc1BmQWoxcDhzYl9RNFFIZGVVT3Rib28wenpQTTlxcDFyVllLdWNUU2hWTl9GSThUU1RWWEQ2bzh6Y2UyZ25zQWRySHNpY3ZrblMwQncteHZJcWVkNXU1ckZkTEZaZHFuWndKN1RIa0pOOS1ZNldJZjBBREFrSjlrU2g4WU1sODdGM2dNRVJJelBiQ0twT1EtVGZzeXdiSjFtcnBDVktSaE5hc1Iy?oc=5</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>46035.70527777778</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026 film and high-end TV productions shooting in the UK and Ireland: latest updates - Screen Daily</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 16:05:16 GMT</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQZmNMRTBhWHdsbFo0WHUtenBKUWJ0Z09LVVBuTjVUb1R6dnYyV0UwSEluX01NUXJuVzhuVlZCTUlHanpOQ0hpT1p4N2xGSnIyaEg3eGRKQ3BZVlJWT0hPREU4dmd2azc2VGVhQVl2emFKVmpENnNrT3BJNGVDY2xlNDVSUV95dzdPcHFtOHhqcG9WbUdYYU9odjhUTHp2b0dzMTZ6Yzh4U1VGNVVfeVl5RmQ1eDJpLU91MHlMUS1kZlZNNng3LTE1VHNIb1o?oc=5</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>46035.67032407408</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ex-Oxford Center worker says key safety item was abandoned years before hyperbaric chamber explosion - ClickOnDetroit | WDIV Local 4</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 22:47:51 GMT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNTmdQbnBYaXRyNk4xVjFSZV9lRUE5bWJOSjNYRmVUTkcxM05UZktXZXYtUDZIVlRzdkRsRFB4Z2lmT1NlRDFUaXJHZ21vOU5jQXdROFZBT3FmZndqc09STzBKYVJpYU5qUkhMRDJkY1hoZWNHak1uWE1NN0g2ODNvSnRxVzZ6RDJ3bDhoR0d0YWxzTW14dXR4aEZVaFhLRHZzeVpsMnViZUFwb25UTjVUY0xXbnU1X21vR2g0bXJsUXdYbUI3RDZHOWFJR2F0dkd4TUREWmgtakFHM3RtdGp4X3otT1FVenJMMU9wYkZJOS1sZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>46035.94989583334</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Witness denies knowing accused after earlier guilty plea in shooting trial - London Free Press</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 23:13:18 GMT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxORnV3OVlRbFNkMWR2NmViRVhRY2pkOWZRYkphRHVhdEczR0t5dFN4QzJ4OXVWY3ptb1RsX19hR1NZMlhVcjNKcU9UYS1fdkw3M3gxNUlrU0lqSWZ1eUVuNnp4Vi1lbHFzNlM1X3JOZVE3U0FFVkF1ZXRXVDQ0cFFKcnI1Ui1sQWxaZGVzMEVOdGdnb0JBb1FxOF9NR0xkQlhmZ2gxX2FtaHM2RllpWVdn?oc=5</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46035.96756944444</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Hollyoaks star 'films final scenes' after 20 years with explosive exit promised - Dublin Live</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 22:28:49 GMT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNVWNPdF9JVGt6X3V6VERiTHd5c3NlSkUzcE5wTHRlME1MTTdzUkNjYXZfWUhMXzV4SlV5ZkRmS1c4WlpMYlZqZ0tzWHNkTTJaMUNlWWhjNW1lMGlVSTJ1VWx5YlFXaDdiVzVuWW0wMFNWbE9rODRGOWp2NTJTYlNEeFNVcjZLUXNtSi00VjFaMmJoZ213NF9ZYkpKaG9XZU01am9YNjItTEpEZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46035.93667824074</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Oxford Economics Debunks AI Layoff Myths in Explosive 2026 Report - OpenTools</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 15:45:33 GMT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNMHJ5QkNQaHh0eFJmSlR4cHhPZjlGaW8wejN1cWtvQWZHRC1ZU0VURnhpMWpEZ29DWlJFeFczZFFMZWxmWExfY2hrNUZzdmY1UVExSzA0dVVKVndjS09uY1lNb1pUNV9PRDRPUGZlVGkyZTgxRU9xcUJ3UkJKc1RRUkpzbEJwZEFaM1lBcWRBU21vZWdXaUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46035.65663194445</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Newport man's big heart opened the door to near-fatal Jan. 2 stabbing, but says will not let attack "ruin me" - Lincoln Chronicle</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 01:26:29 GMT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1PdmMyR0NheURUemtnelpUV1hyVm5YLUdOVWZkUXhGRHB0bnI4V0RLODJrTDYtcEE0NHlnNEZaRTVvZXI4d2J2ZWM5R3J0UXIwdXVtRFBpYUQ4MjBPR21HME5NNy01THY2QXljRWJ6ak42bm1pWVZBQmVqcEQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>46036.06005787037</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Pair jailed after sickening knife and boiling water attack - Sunderland Echo</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 15:52:00 GMT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTGh6cnJ2bS1KQUdFQXhYa1l0V3JvMk9SeElvQmo1ZWVhazZXT3VvMmxLQVhHazlUS29ZZDgzMkx2b3RSaEs2dThONXhaUkdnNlNvTVV4WTZFMzVuWWpRNkNWRkU3ZWpXWTd3RFRvMXpaTjFRWENKUkZnQ2g2YjBRVzNqd3FISGowNk4wVUpnUFk1b0Q0Q2hKNVh3dVk4T0pHNzNEeXFmX3pWaUNW?oc=5</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46035.66111111111</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Police investigating after woman killed in North County shooting - KMOV</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 15:12:00 GMT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPN3RnQjFGVE8wOUJGdmUzYVlURmdWSDZBZ3U5dDVnaXNGOTM3emhkUi0yMHFVRlY0aERSMFdZa1JXVUtNZmlHdlRvTmdyVnZFWmJZVGtyV0tyOUN5NDVjQTlkNWc0MHdoQzN3bjJHTEhrMUZ6R2dIVGY4M0dWOFU2TEwwQmxSRmVPNW1RelE3Vm9tT1kySms4QXRlVURfTUh5?oc=5</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46035.63333333333</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Marine Le Pen's appeal trial opens in Paris, with far-right leader's 2027 presidential bid at stake - The Detroit News</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 18:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQc04zcmpNSE43UnRDXzI1cDZyRkJFdHdZaHMtU3FNb1hBQzc2Yl9UdUh6LWRsUmJfRlpvSjI1QmNRVjlVQktoMWxVbXVTZnNWX3VIS0pVaTdLNXE5eVEybkxaNTlsN0tweGpmSWJ3ZVJfa1gtNi1sSy11dGVYckt1NTVzR2JoQVNvXzdueGtCeHlXZXk4ZVdNazhZVHdhZ0VUazA3aGV5Nk5FVE91U3ZkYlVwNnRHRV9EWVJpQXJzRGpZY0VJMXJ3cUU4YjdMQ2g2UkNEd1oxRHZDbnF5MTBKX3dKYVpuVldIWkZfWkludVZmd0VhZnFQSA?oc=5</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>46035.78125</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Gamecocks Face Road Test at No. 17/17 Arkansas Wednesday - University of South Carolina Athletics</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 16:12:53 GMT</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNVUlQRkJOYklXajFGeFRRV1E2dVFQSmdTY3c0RXhUQTBackM0UGwyaE1qN3g3THJua2ZVNkdNd3d0TUViZmgxc1kzcUc5VncwTS10OGZieGNhT3NkQ0NRMHk5VHdOME1DQ3RIdS1ua2lCVnNpUmtndnMwQXJwR01UNUh2dVhkc2VmWFo0dG1MTHl1NENIQWRfMElpNE1NVTg?oc=5</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46035.67561342593</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Stepfather suspected of shooting stepson to death, Logan County Sheriff’s Office reports - River Valley Democrat-Gazette</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 15:18:00 GMT</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQeThYbS03VElRZ0pFbXJhOGdhUHE5NlFjcXc3WklkU1g5YU1sclhadi1JWmktNlNtYktzOW1vczRETFUxTVFDck15Z2JGa0VzQ2Z4OVJ1c0ktY3NHRkdhZXFIa19aaWFzR1hFS3BQSDQxTXFyQmlwVk9ReWNJLVpVUUd5VVRSNW40RHBYRlJIRVdlMjNTdGNneFRXRjhOMl9iVEZ4Q0F2ay02enpq?oc=5</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>46035.6375</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Brownsboro’s Miller scores 18 points in Nelson win over Texas Wesleyan - KLTV.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 15:48:14 GMT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOOW40NXdMTUFSdHV5ZG1ZWDFGWnZSbVA0dWh4SDUwdUw3eXVLWkJZUEs0UnR2dVFPLVJUODZ4VFM2Z2VhOWFGZkgzcDNEdHBrZVRTM2J3Rmd4U3hlMklmLVBGbG1YWjNWc0NER2VJdTJheHE3RmpIeVFRWUF5czVoZUY5N0J4OGlYWXI1QmxOV0xONzlJMFZ6MXJKMGN0M3dPcThtcjNFbC1JckNGVmFLZ1pHQlLSAbQBQVVfeXFMTjluNDV3TE1BUnR1eWRtWVgxRlp2Um1QNHVoeEg1MHVMN3l1S1pCWVBLNFJ0dnVRTy1SVDg2eFRTNmdlYTlhRmZIM3AzRHRwa2VUUzNid0ZneFN4ZTJJZi1QRmxtWFozVnNDREdlSXUyYXhxN0ZqSHlRUVlBeXM1aGVGOTdCeDhpWFlyNUJsTldMTjc5STBWejFySjBjdDN3T3E4bXIzRWwtSXJDRlZhS2daR0JS?oc=5</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>46035.65849537037</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ultra Play OTT Celebrates 100 Years of Legendary Filmmaker Shakti Samanta with a Curated Festival of 32 Classics - ANI News</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 05:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQNEhseDA2UHFfNExCRUdFMWlyeGhNNXU0a05OS2J3M190TnMtMXNPR0h5cUNmSTBnYkQ0bkZOMGdVWFJ5YzA2NHlJekJWTHBETDU3YklFejZmZnpscDV1c1lIT0daTTJkTkNLdWtPS19GdlJjeTNmZnJVRnNiUXY3MXZMX05uVEcwQnI5TEVCa3J1ZGJTanhQRTEydlRJczF6dnlTZ1ZsN0hJZ3VrQlNFRmcxc2JmN3NaZmNHamRyVmZEeFBOU3JCZDJZOXIxSGktUzM1N0EyRjQ1encwYlJpTW1Ecno0S1pCa29pX1dfdGtmT3RNMURwMTljUDA2d9IB_gFBVV95cUxQNEhseDA2UHFfNExCRUdFMWlyeGhNNXU0a05OS2J3M190TnMtMXNPR0h5cUNmSTBnYkQ0bkZOMGdVWFJ5YzA2NHlJekJWTHBETDU3YklFejZmZnpscDV1c1lIT0daTTJkTkNLdWtPS19GdlJjeTNmZnJVRnNiUXY3MXZMX05uVEcwQnI5TEVCa3J1ZGJTanhQRTEydlRJczF6dnlTZ1ZsN0hJZ3VrQlNFRmcxc2JmN3NaZmNHamRyVmZEeFBOU3JCZDJZOXIxSGktUzM1N0EyRjQ1encwYlJpTW1Ecno0S1pCa29pX1dfdGtmT3RNMURwMTljUDA2dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>46036.225</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>20-year-old gas station clerk charged after shooting customer, High Point police say - WXII</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 22:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPbjc1UlpsT1Q2RWRxUS1zLXhycGVOcndPWjVUZ0lnZTlDTkFxNHdSaFFIUVp1YU9fOEYtN2hNXzZ4UjNWbEhSSmpLQkVZX09NZWxlUWp5QUpmX3RZbkJvYk9TaUpJSDd6UzVUY0JFMXVmckZqdEp5eE90V2lpVDhuV1dRVFZlYXFkV2VRSkhmR0tPdTBnTFNuekNR?oc=5</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>46035.93263888889</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Police Investigate Homicide Of Adult Female - RiverBender.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 15:46:00 GMT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE5zclRJb2F1bmpvNVM5UGhISU5iS0ZVYmF1ZzNxRWFuUkxXU1NMLXU4SXdqbXctRG1BU1RfQjFYMjN6UkNGeEdKQ2xyVmFWemI4cnhYQXJQSmhvMVFET3lJa0czaXNtMnM?oc=5</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>46035.65694444445</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Sports shooters Ban Hyo-jin and Yang Ji-in rely on mindset for results ahead of Asian Games - Korea JoongAng Daily</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 02:54:51 GMT</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxOWEFqdkRlMmF2VThXMWJEVmJPU2hCTWJMQXJBeE1OeVhabDZnZDZLUWRsU2dwbDdsVFg0Mi1ma0Z1V083a0dqUkFuVnBVb0k3ZWtnRExaYmhoZER2ZUNmMTRRSmhjQWIzb1pVakk1WVJuVFNkTFZNbkxxaFdZdGdiTjVlY0YzUTVqZzg0aVBKTXNwWVFQY1lUMXkxcVhEeXVJVFgzeThTSk9EcDlzUER5SzJHQ0RsNnBfdEZsbHhKUTVQa0ZEUDZWZGF2WEhFNFVxdTFqeFM5UDN6MV9BNlMwMzZUWDJPM0VidEVCZUU3NlNrdkszc1ZuRFhB?oc=5</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>46036.12142361111</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Small Candles of Resistance Art - Tempo.co English</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 07:04:52 GMT</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5BcTBlYTEtNWhRU0FUamhhdEJxa3FBTkV4MlJYdnVEZFVGYTFBb3RZRnd5MEd3THBYNnl5dGlWSkRPYWliX0RKUE54Zi15c3lQUlpoQWx4bDZ3dC1UZmF4WUgxNWZCeGhUVHM4eThqR2otZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>46036.2950462963</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Global K-pop group BTS (Bangtan Boys) is expected to generate more than 1 billion dollars (about 1.4.. - 매일경제</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 01:07:44 GMT</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE8yZWVkVU5rM2R1RW85TllfZGZlRlRIR1B4V1FLY0h0b0d6VEhsVXd3YlJ1Uzg2Rm42SzgwcUpYb09ZRGI3eXYyZ3JqeGJiOHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>46036.04703703704</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>La saison 4 de The White Lotus aura lieu dans un château du sud de la France - Le Bonbon</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 18:32:29 GMT</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOS0I3c2ljU0ZGWUY3U19HN1hVdmZNclRrRGFqNHNIbjg1a3V6NlBTNGFSWjhDeTA0dWxYaXlmM2VJMEp6ZHNoc1FfellXQXBveWpGdjV3YnVxVFhHNUdBcHRMUmlmcHlCSmtId1NOTWRFNC02MEM4WVQ0dW5qMXRCa1kzaTY1d2NrX1FGU3RFWng4Mk1OYjFyVHlmdTI?oc=5</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>46035.77255787037</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>'Aggressive' Kansas hands No. 2 Iowa St. 1st loss - ESPN Philippines</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 05:15:52 GMT</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOS2h2MXFweGF3NkhTLXQxOWVvemRSNHRoUWdnNXlzMVpEbFRQcW5HWkRtQmpKNjZZVGN6RTJhaUppM2Z6YXUyanYwXzZkMThFeVQ1TGo0UjVGcm1zQVhiVklPTWJkMlJMNEROWjJwUklURk83djBCU1pkb3RDblBWUC1Ba2lzVVQ1YlNVaFREVlY2WjdqcUFqUXhJT1BzWkVLOFJ1eDA0WGlvY3VLNjB2TEpuVFIzcWxuQWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>46036.21935185185</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>After Retiring 4 Years Ago, Figure Skater Alysa Liu Is Shooting for the 2026 Winter Olympics - AOL.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 03:19:21 GMT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBqS3JLNnpNZzR5bloyVlBmd1JxSk5XRm1uY1RPYnBSeVFzNXRmM19hYjJBaTFHbmk4SlJPTHp1NGNVQWd5aVdoVzBiWno3cXVMcC11OUhOUHE4azhDSnE5M0xIZlhKQTBsRmtDZFl6S0JqZVdyOUxFMDBmUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>46036.1384375</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>No. 2 Iowa State visits Kansas after Peterson's 23-point showing - FOX Sports</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 19:23:34 GMT</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOUU1hUGd5eVE2azJnVFJZMXptWkVTZWU2ME44c0xDVGhPYnB5YXBONE9kYjJSbjlyRUNpRHVuM19jUUk2OFJyX0xWc0tkeG1XOXM2NjRINkRZVUtQaXlUWG15LUFZc1VHR2FhcGg0ak5sTmlvakpXLU50WFA3OGZocnprTExfaFJ6NXFjZDNNZVRsLWU1MzhndnBKZHlzNVZ0X2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>46035.80803240741</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>How will climate change reshape Winter Olympics? List of possible host sites shrinking - NBC Los Angeles</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 15:14:28 GMT</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQZFdDc21PQkJVdlNUQ0tPQlZvaW5aNWROS2FtcDhjMVBieEstdk94dVlVNER5Ymx0Q3dybkZVSmc1TC15OTRma0xHbnRMQUlzNGJ2Y2djTzFIa3lHbkNTdmZqVDQ3cVZMZVk2cnBRVU1VZVNZMEktM2YyM0czdFhSVU4zMExNNkY3LW13dTh3QzR1cG5sak5SVWVxbEdpS3ZTM09CQnBNdFNlSE1VQzd1bjBCLWFVOGkwZFZIbDlPSl9JZ9IBygFBVV95cUxQOFp3TC05QmJTSU9qZjZCSXZ3UjV6VWVOWkZfRUcyb2dXZ19HbUxFN2RDZTRyNEpaa2x1ZmoxZ1JFd0I3Q19GZmFmU3M5cFhzanVEdno2ZVROc1BnQThCRkFvYk9EaUgzUUFTeTZaRlFZVVZZUTl6ckdETm1hVkJBZVdQNFE0aGhFb0xtYURBM01hS2J3aDdxNjFTZmRuSFotTGMxTzlrS2VuY0tGeW8yT1hYelNsM0VLNkJjVnh6X2VWV2dxTV9BZ1Z3?oc=5</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>46035.63504629629</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>5 telling stats from Iowa State basketball's loss to Kansas - The Des Moines Register</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 04:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxPbVA1UmZ1QUVQT2h2VUlvSmNaUUFiTTV5cFd2WTBjMk10X19OenhSMm9JNTBzS3VFU3lmTjhia1JtWVJ0SzJ5Vjl0NTgySXVXV0IxMDFxd1dQU0dqWXNROG0tUm1XQmlPRWFoRHNQd1B6MVpmX3hwejE3OGZrT0gxMFpLdU5Qdnl6bVNRRXFUazJoSTFiMzkwYlZqSXpjMHZMMHVZeHZxc2Ztc2gtMkgxQ1loVzBLNEhQV2RMN3RabUdSeXl5R3VCRklkb0c0OXUwVTJpajhQc0dSMmdkTWJKODBhUUo3dVRJeC1JSW96ZXE?oc=5</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>46036.18472222222</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Trump’s Iranian protester aid: Letters to the Editor — Jan. 14, 2026 - New York Post</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 22:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPOVl3bDg3cVAzMzhnWW13T1h3c3YwYk53ODIxYXkyU2liRGU2ZGE3cmY0cFNJYkd5Zi16MWxPaVpOZHZNTkt4TFVFYjZ6WmljcEFfSXNScjh6Wmx3NTNYbVNMX2dtX1BNcmY1bUNLTUJDa0k4UWZ6MF9tVnFaV0pEQw?oc=5</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>46035.94513888889</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>IIHF President Luc Tardif drops a bomb about the NHL at the 2030 Olympics - HockeyFeed</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 00:48:17 GMT</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxObWhvNm1td2pJSnBNaXRJODN2eGgwVVZEZGpzVTdhM0xTQTRiVmxDbTljanZqb01NZG5LZFlDbmJRNk1STXJKakNHWFBKV0xhWVNiS0RoMXpZazlKbWk1VUo0dEFrWElRNTNjc1g0X0ROZnQzMEYyU3lmYmE5RHpyTlVxRE50eEZrNzBOT1hrV3VxaDdNTXpkNUNtOEp3a3JzLTUxX0ljVG1ldVFXbFE?oc=5</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>46036.03353009259</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Signs from Füllkrug and zonal issues: Tactical analysis of Fiorentina 1-1 AC Milan - SempreMilan</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 17:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9rUDNEd3NXelRKdUtEbTJ2Tld5WXhjV1J5SXdYRWdqWXlXRXdsZWRpVnprNWxRYkY5WjNpLVFKQWJOQlhtZTBacnd4NXYtUU5TeENVVEE5TUJ0eVNHMGVIeDIyMThTd3pwX3dNUm55X0N5a1nSAXhBVV95cUxOZm11OGEyd1ltR19uc3BFNXRFSEVYUTl6Y1dLVGRKekN2bGxwLS1RTmdrNG5mN0FIV2ZiTWpNekN4RXFpQ0twVjZkUGFmd2FjSXVnRUUtZWhIQVRCYlJ0ZnpBdk1PYTNPUjNvNGtOamUwTm9rQ3YzRGg?oc=5</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>46035.72916666666</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Village Search Fidenza</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>( "Fidenza Village" OR "Fidenzavillage" OR "#fidenzavillage" )</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>I saldi ti fanno risparmiare, ma se sfrutti queste due offerte a Fidenza Village fai anche tanti punti extra - The Flight Club</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 17:03:10 GMT</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNb0xpbmdFRzlYQ2p6MlJHZ2ZraVA5d29HZHdIeVRFaHBSMDY2cmdvT25zQzh2UjhnS01ibFNWVzFoSWtBSXZYakhQQVhDOXZQTUlqSVpSbGQzd1J5dWdkWEpPb1MxOFI2NENNbmEtSThqdHRWVmlXdk95RExvYUJBNnhtQk1iT2IyWndZ0gGLAUFVX3lxTE1vTGluZ0VHOVhDanoyUkdnZmtpUDl3b0dkd0h5VEVocFIwNjZyZ29PbnNDOHZSOGdLTWJsU1ZXMWhJa0FJdlhqSFBBWEM5dlBNSWpJWlJsZDN3Unl1Z2RYSk9vUzE4UjY0Q01uYS1JOGp0dFZWaVd2T3lETG9hQkE2eG1CTWJPYjJad1k?oc=5</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>46035.71053240741</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>EU summons Iran's ambassador in Brussels over protest crackdown - Euractiv</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 19:07:28 GMT</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPY3VyUXNHa2dKSXVTMFFzU3QzTlN5czUxQWdsVWo0ZmNuMnBhREpWaUN0c0kzM3ZxT0Jhd3k3UGI1WFpJcndRQ1RuTWwtMmNOdi0tRVdFLWZFUjNxbUpxZWdWMnpCd3pkRTJrY0phUDJrLUM4NDlNWE9HU2VLV3hOUS1ya203eE5WMlc2TUFHWE1EendJeE1ETg?oc=5</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>46035.79685185185</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Brussels Weighs IRGC Terrorist Designation As Sanctions Debate Intensifies - Radio Free Europe/Radio Liberty</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 15:51:22 GMT</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE1hQjNiRDRhc2xRRTFrdVVGMm8taVZseF9XazBHUmNXNFR4VktTX2RiQm9uQ0dUa0w1NDZPbkVvM29tdWhLUEVlOUc2eXFPUdIBUEFVX3lxTE44MTFzQkhIdFFxQ2tBb192QmlJUGFDR1Rhbzl3REdnRGVoYXh2NEFUekV2VHprVzhHQVhid2ZzVlFESlF0LTgwXzFBY29tUGVu?oc=5</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>46035.6606712963</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Man in court accused of 2019 Hartlepool shooting murder - BBC</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 16:10:48 GMT</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE40cXVfdkdyS3lOaUFZY09TLXkzZ19uT09seEViblFFMnJfNmR1eFQ5ekNxbzR5NlJkOWVfZUxTLTNOOE0xUTR1TjV1dEd3ZlloYnowQWFhVlBpQdIBX0FVX3lxTE1oYVF0S2FudEoyUW5FS3YwWl80Q1FBUjRHTGR5ZXhwVU9FNjVtRmlrbmZxRkRhQk4zV1A3Y2xwUlJmUHdoYV8xMkFLQ2xaUVBTQ25md215TzlwVWJsT0k0?oc=5</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>46035.67416666666</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Eurostar alerts business travellers after technical issues at Brussels-Midi cause cascading delays - VisaHQ</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 23:37:30 GMT</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQeGhRRzRYUnZoM09QdXBMekZLRG1zc0REUWg0LVUxaUVyaDVKaUdpVGJnV1FvSU5GLTJ5b2lHWlJLcllFYmE5NHBkNXVkS2NubDNoWmVEX2xpWDJOTjJnY09kVElfb0tseGFpcmE2a1h3YWx3TmJaMFYwdFcyeFZlTXB5MlByeWxZeGZtSXNuSkJ6T25MMFpyN1dFZ0RQMG5WTU9nNWZsamxXOHp3NHFvTUVaN3d1WFlmdWpnNzcyd2ZFUzJXSzZVSzViNTduUFp6clQ0NGRRUHM?oc=5</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>46035.984375</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>What to do if your mobile phone is stolen in Brussels - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 05:16:32 GMT</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPZlNYSnB2d21XQjd3WGpXOXY3cEYzVk9ETmY2TGVveDU5RVdHbTRQMWZHanAtekQyZHpLb3RUdjlUc2doOW5RbzJTN1RrN0ZXMFdNaXFpUGxBUjc2RThxLTA3d2hEWHpuLU5GZ3E4Z29ISXB6V0hsUzhxMzBCeVR2Q3ZJSHJvTGZKR3RIMVNFa2Vray1uMWE1ekRtQUpicFhVXzhTbDBrQmw4TDVaS2s1UUZKZDU5blE?oc=5</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>46036.21981481482</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Poland faces millions in EU fines as president vetoes tech bill - politico.eu</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 15:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNNlJqcExMZk9iZlY5U0tiZERpZmJGTVNpSGt2MHFkbU51UlRFQ0E1LVBIdzEwSWJ1OVhraVplMENKZjg4bnVrX3NJaVZFLTlpTmdSNWM1TkQxcVZaM0Vvb3g0c3FXbkRkX0dVU2RaN2ZQanpUNW5WTEg2c1h5bVFDUjFXWWMySGs0R2k0dk9HcG8?oc=5</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>46035.63541666666</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Discontinued police project cost Belgium €75.8 million, says Interior Minister - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 18:16:29 GMT</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxObUU3MTBKVUJNZlRELVN5eExCTHBDZjFaX3Fhdnh2dlZ2WFVMM2daR05RX2NQeHFJWFJQcUJycTRUajFkYmQ0cloxc3FNREFJN3ZHR0ZtXy1TMUU0azZFei0weDhyaE9lSkJCZUZNaHBWdXJ3ZVVyT25LcTc1U1BCd1NFWnZFYkJYWFRHbnFjcENSeTUyZHcyX0g0UWRCcnRhZWpIbUZRc09SSGN3MlJDR09hakstQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>46035.76144675926</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Antwerp mailing new property tax bills after finding mistakes - WWNY</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 19:31:00 GMT</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOSlhyUVpLVFREc1JrYkw0ZzB2djVydnpPMHpSSTNCdG1xemhSd3RzQzNvb2pfWktqSHNIU2pER25BQVdzN1E2NTI2Q3N2U19waGhBX3NkVVBwallRWmhpaHZmVE1ydTdFQ2w1cFg2ZXd3R0NJTzFITWtSWWUwQmVXSWN1ZzhXdGlyeUtEU3JoekdhM3ZmT3J0ZTAxWHPSAbABQVVfeXFMTXBpbWd3MWVuRkszLUNVZGx1OEJNakVOdHpBTi12Q3RqODh6NjhWaDdDRkVQbEs4UkgyZWFibHo2U0oxV0RJaFR0V1c4MjBvVnNkMkVKaW0xMzVKY2hCS2x6ZGVEd2h6NHp4NGR4ZmZzTDNCeFJwcVk2dFRIV281bGdaTTJwVUNWRHlZYUxSYUE1WjhGeF9pRFdFS3BERW5qNW14ZC16Mlk5cEpYV2g2ZEw?oc=5</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>46035.81319444445</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Belgian farmers allow Egyptian Strawberry trucks at Ostend - Brussels Morning</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 16:08:42 GMT</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOTjREbHdxRHBfODVBR2tiOVFVNnJiYjBGZTBGU0ZyZGZncWw1Qy16V1o4WUQtM2w0d2NRbWZEQ181b3k4ZU40ajU0akFXNTBqNTIzdVpBSmpxdTFtalBxblhPQ2I0UGxlNXZLSkxOTW1KNWN2RXBpSTZVY0steEtERk9acmhYNXhRZ2FpekYwUmlEMDJsNngxOA?oc=5</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>46035.67270833333</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Jihadist convicted of attempted terrorist murders in Antwerp City Centre - VRT</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 15:12:30 GMT</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQR080OFZpYWVvRHpKblpzYURtXzFvU2pwNHZyZ3NSa3U2MHZUNW1VYllOZE1xa0oxWFdVU3BVdjh3LTZsZVBkXzIwQXBCNFZOa200UldVVDRLNkJ2SzFyTTFDamsxVUZub3NUZGlCeFFHWTV6TlpQUTFwOVE1RG9EcHgtbmNxUUpLd21HbXV6SENZWmtRb3p4dTBDNlBHMGJiYjRsazBBTzQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>46035.63368055555</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Bulgarian farmers from three industry organizations join a pan-European protest ᐉ News from Fakti.bg - Bulgaria - fakti.bg</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 04:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPVE1oN25scjNkZFlRYWxQZXZFTVVtNHozWlR4dXhSQV9LdWM4OXpTYl9jTFRPU3VjU01aZFpUUEpTLThYYXpMQk8tY0FBM01sMlR3bGtTQ2p2LTFJeGJZTDh4Y3ZCcFBOQUV3RzkxWE1NR0NybFRmMTFlZ2lQcHdoNkNKVnVsZ1RPYWVMNXd3VkFUOTlNMm1mRVluR1l3MXp1UzR4OUhWMGxwRU8xa0thSEM1RWhjYms?oc=5</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>46036.20763888889</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>What happened overnight? Police blotter report for Tuesday, January 13 - Newzjunky</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 17:25:37 GMT</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPd0RGdWU1LVh1OVNJRXlKaFlBa3BwY3dDcWVtaVFWTTFRS1V6UGoyRWJfTVV3bkxhcDZhZ0NqbmJCRDh2bnN4M3pTaGpTdXdubVRjbERRRXhwcVkxSzNJN2VSZzI2a3VPTDVEUnJaMFhCNm1pNlpkM1lLTGJwWFdvRWpB?oc=5</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>46035.72612268518</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>EU biometric Entry/Exit System goes live at more Belgian crossings, prompting queue warnings - VisaHQ</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 23:42:12 GMT</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNOXlva3lwOC0zN2pHVW90QnFmRTdNYS1paHRKQU9rRktYTTdwX3dXUzRjQ3dPNU9hUC1wQ1ZkNlpzdUhRQ21JMVpGbDRBMTEwYUFhZzFYSEd6MF8yUC11eHZVelhpSDdlV1NOc0dXZm1BR3pCRFd3Yl9sVGE0MUJCS3NjVW5CbzFlN1RUOHFNSktJdGhEdHBwOGdZQzctZVZGRFhobmRJUWdXNGlkYUd0cGhNWDhYQnlpTlZBYWYwd0s4ZXUwTlpiS2kwWTlEdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>46035.98763888889</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ACLED Regional Overview Europe &amp; Central Asia: January 2026 - ReliefWeb</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 03:18:12 GMT</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQZzJyMnUtclczNHBZTnp0M1Nab3RGZmNsWVNDQ0ozSGJUcXlhQUxVUFhmQzNxd0xKM2tvbUdJQ2lXTU85RmM5bmtFTm94TFl6c3k3ZEJOMmVvN0RKWDNmSEE0TEdfR0p3NEI2dTNzQV9WYWNVb016MUt2Y1VMN1RfRnpySC1oczQ5NklvTnhIQ0I5alhaNU1OSw?oc=5</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>46036.13763888889</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Brussels Motor Show – all the best new EVs - EV Powered</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 15:22:30 GMT</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE50ZGZpNFpQclVLUEdrZHM0b1N1SVhZTnBwV1NadjhxTlRhYnlyVk9LS3VCd2EzcmliN2lGS3pQeFVkYUFnN3JkczBWZVVrSktDOThuaHRCSkhLN3lCUnJ3b2pnbWV3MUJ3b2V6N1Z1TnFpTXFmbFVwRUt30gGCAUFVX3lxTE1hQUUxQVdRYmFVa0F6cS1KRXR4RFVEdm5jSEtqS1hTSVpXMHBqQ2VUWmhNWEJhNjhOcVdvNm51dkxscUhIbXpOOU9fRmRZbWt5VHU4UmZkb1F3dVpvQm4yM2ZIWGt5LWJnR2p4b2xyb0lOS2ZDVHN0NTc3Q3NzcHAzTmc?oc=5</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>46035.640625</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Greenlanders, Danes hit the White House with little left to offer - Euractiv</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 05:03:45 GMT</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQMHUxcjZfNkI0MjFmOERjbGpRLWZIb1hOdHZOR1BROENFYnZtUUk1dHVrQ1BzcXF6Sk1hSEU2ak15QWc2WWdLVlBUNkRMZVlyRTNWSmlmT0JoV3RoZlU2blFyY0RtTHBZaW03OTJDcVhjeVBVZHBsR3hiVW5IYUVOTjB6Yl9iM2JYTWZ3eEQteVJHOTln?oc=5</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>46036.2109375</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>AZ Monica hospital in Belgium shuts down servers after cyberattack - Security Affairs</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 23:47:50 GMT</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQenRKd3dhb2VzM212VWp6ODI1bmVNNXZ6aE5CMENMNHJWWWhlQW1lS2Z5Nm1tWmRRekdOVTMteG45RGw5VURLZ21ReTRfRDc0MG5weENrR1V1bVFzaHhNRUp6WExsSl9mRHRhdXUwRVVzOG5rUXJfb2tZbU41UnNzN0M3czdqZTNoUVJhZWU3ejh0RFB4bkZESkh6bEMtRTljelpQUWdWSVJ5RnNTOHlSQ0FyLVdEZjM4TU40bll3RdIBvwFBVV95cUxQenRKd3dhb2VzM212VWp6ODI1bmVNNXZ6aE5CMENMNHJWWWhlQW1lS2Z5Nm1tWmRRekdOVTMteG45RGw5VURLZ21ReTRfRDc0MG5weENrR1V1bVFzaHhNRUp6WExsSl9mRHRhdXUwRVVzOG5rUXJfb2tZbU41UnNzN0M3czdqZTNoUVJhZWU3ejh0RFB4bkZESkh6bEMtRTljelpQUWdWSVJ5RnNTOHlSQ0FyLVdEZjM4TU40bll3RQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>46035.99155092592</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Iran's protesters call on US, Israel, who must heed call - The Jerusalem Post</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 14:31:02 GMT</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE5vYnRaeGNwNlpZdEdZek9GUUpfV3VKeVJvUFZmUmNwOFFDeDFBby03TWlLUlF3TWJ3RE02eURHSlo0WWRiWnpNb1BLN3h4XzJwWGI4amZ2SQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>46035.60488425926</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Germany Buys American Drones for Submarine Hunting While Brussels Debates European Alternatives - DroneXL.co</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 18:45:07 GMT</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE13NTU5eGJsMllnak1fZVpCcUNkeW5JNG5kTnNYR1RzYmFmTndELWM5M2NkX2dGTzRfMFJOQmhYTkJmRXlON0VzeVotVThObEo0WDJFaFc0QjJVeTN5NlllNURWSFRZM2JBUGFOU0hrdGJ2V2haSF9aMkVOR0I?oc=5</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>46035.78133101852</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Iran Opposition Rally Sparks Strong Pressure in Milan 2026 - Brussels Morning</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 18:35:19 GMT</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9SYl9TVjdlX1lfMWlxdDBRWUpHWWNqTUF4QXpzZ0NJTlgxVzFncV9ETGJOX3IyWVlOTXlKTjlRMXhjTklaVnYxUWdNNy1SbnhJTzZ1TFZZSnJrTmJfMERQM3g1a1hFYVd4dENaVURXcHFyNTAxaWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>46035.77452546296</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>General practitioners on strike refuse to meet with the health minister on the sidelines of their Parisian demonstration on Saturday. - surfcoastnews.com.au</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 19:02:15 GMT</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTFBZYkZBRC1sdnhIejR0TTVmNjBSbWgyamFRMFZEeDYxSlVGemJqTklTNFlQQkRhU0VWOW1mRmdveVFzbF9jV1FySDlTYTNaVkU5bFlMbA?oc=5</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>46035.79322916667</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Local Town Searches  Maasmechelen Dutch Terms</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR boycott)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Fuming French farmers camp out in Paris despite government pledges - Shelby News</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 19:39:32 GMT</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOVFZZNWMzMXhJWDJCWkIwbEhZWE1ueXBXN0xpaEQ0ODdEQldqRElRZnhlNzBVajJsZ0RMWnFndWNSZUZzVnVQalN5c21lemZtSDB5TWwzbkwzNVBOWmtHTmpPckdVcWdzTWJJci1WOGtDV2w5RHltd3VfWTFYeVZCWS0wVE9JcmhNREtTcExGb0VZNnItYUlQRmtrVjdEaVRqUW5ZZnhDWlN5NWlMaWttRG9rZmI1aHdRbWZYLXg5MXl0TGY4bndZcC02U0xIdE13eFRGdmp4VVUyb0NaTkFqVG52SnBjaVBZZzZnaVBn?oc=5</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>46035.81912037037</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Village search Wertheim,</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>("Wertheim Village" OR Wertheim) AND (incident OR protest OR police OR security OR evacuation OR closure)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>'Just get rid of it': Jewish body warns against religious text 'loophole' - Australian Broadcasting Corporation</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 07:18:45 GMT</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPbVZkNzYtOGtMTGdFbnltUFlYWHRGTUJuQ0dUOXBFMTBaTzNFTmRHSVFCLUFvODhFMTl2aTdpU1N5cmdWN09UU1ZIWENCVERiaDY0NlRtclVEa2EwSjlTdjFkX0hqT3lZZk1EZ2dDZ0gyRTY1RWpKMXVXSTY5RnBiTEpRdjhQWG1MNFJnOUFhb2piMmpQTC1OemMtWGxtbWlZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>46036.3046875</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
           <t>Ireland / Kildare Protest Groups - Social Media</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Sports First Aid information event to take place on Kildare border - Ireland Live</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Tue, 13 Jan 2026 09:35:39 GMT</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOQkYzX3JpbG9nLW4tZ2hNaFhXX25ZVlBid3dJRG0zNlhfTVhiWmp0UTdxMlI3cmwwMDA5TTJraEw2SWs0T3FhWkQ5Wi04YXZTV05xLU1HWVQwejNlbnBOWVFKZ2prZXlUQjV1WGNWUTNUOUYxdTE4ejdYWVlDSXpJYnRBU2JRVUEwQjV5U2VNbVFPMUpzU1RrQ1FIcUtQc1YxMkp6Zk5ySGE3T0dmaEJYT1ZjUEkxSVBiTEtEYnpYQ0k3Zw?oc=5</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>46035.39975694445</v>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Man dies following road crash which also claimed life of pregnant woman - kildare-nationalist.ie</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 03:12:37 GMT</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOdUdmaE1ZNUp0ekxJbzIxYmk5MEZkQm9qbnZTZngwMjl6Y3hreTY0RU8ySnBxUFE0YWVybG8wN2R3UUNxQkE0TWlvUWtQQjRNc1VqblR2N1pBMno4UkJ5cldYWFBjektmTHhldUZDc0EzOGZnY0ItaVg0VFVXa09TYVd4ZEtWQTRLdlVhS0s1NHNOamtzRFlUUHY5enQwUF9IMXlETTlYU3RiLWdubGh2STFTTndzRm1kazRwc3Z4NEVSb3BtSXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>46036.13376157408</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>BREAKING: Man arrested in connection to 2024 criminal damage by fire incidents in Kildare - Ireland Live</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 15:34:43 GMT</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNeG1KanZ0bUJfaWNzdS1pTHMyTWlDOGhOdWNYWlJSelg0Nzk4ZE5YcUgzb2NhR1A1a1BfOHBLT0xXcGxhaXhBQXVuR0FDRy1OSXIwQ254dUtZdmZUaFlveDQ4SEIyNEtoMEJfRjVaMUdYYjZnUkwySnF1b09mbzhhemxRZXVCUXVHTDU1S1FWcnpOaE04dTVHbklaUVZaZ3FMWDk4REZFT3ZNRVF5V2VxTWdmcnd1RFg3dGdmOXhPNlI1ek5hZEdpcW5BM3JUY2g0Ml90eWxKUFNjbjZGbXIw?oc=5</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>46035.64910879629</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Louis Vuitton unveils architectural and culinary landmark in Beijing - FashionNetwork.com</t>
+          <t>Cartier Owner Richemont’s Sales Beat Expectations in Holiday Quarter - Bloomberg.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 10:45:00 GMT</t>
+          <t>Thu, 15 Jan 2026 07:15:00 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPMUczMi00Nm9MbWZWaE1CNjhKTlhRVWdycmlocFIyWFE0Um9VVGstMWFpQ1dta1RkYkJfWFBRSVNITnJTTS1VOUlnemZnaVFjWENKc0RCMTZIclhaOGdrc0Z3ZGRxdVppbTdNMExyc2hvLWdYTjZ6cENKZkxPTTRBbF9GR0pqSXNFU0JhR0pDMzZKcFFjbDY4UzZmSU1tbTZMWFdtaXRqTE12bjRlS2g0UVNOSEFsUmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQVXoyRHhBMVpvNnI4bmZ4RGFJODk2ejY3eWJhSTB6bDV3QzB2clp4Mm8wb1A3aTZzWkF4QllkZlhlT0ROai1YelI1M0FKcGlUaU5ETHpyWmRQbG9kYUZiZ0xBOW96QlE1clVCUThZZ1lZWDFxSW92a1lIcHozR3BSR3VjQjR6MVdPRzdUdmR1cllFOEgzMzQ5RFhnX0tJOFE1eDNJSHhHMVhIU3Z3bmJsZg?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46036.44791666666</v>
+        <v>46037.30208333334</v>
       </c>
     </row>
     <row r="3">
@@ -515,24 +515,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>What the Burberry Comeback Tells Us About the Luxury Market and Pricing Strategies - businessfocusmagazine.com</t>
+          <t>Giorgio Armani Corporation appoints Matteo Mascazzini CEO for the Americas - FashionNetwork.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 12:03:06 GMT</t>
+          <t>Wed, 14 Jan 2026 16:30:56 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPY0dwN2h4a1M3dVFRYXo3QjUtamV6S2pkZTJXLVVtbWRveHE4YjZnbXl1V1VSLVFHeXIySlNBc0hxN1Q3UVdtN3N3YVFaUlZWVkQxN0RNRlY0ZXJsdVh3Y0VIejlZUXUzLWFKWVUwRDQ2bnBuZXlMMVlEaUtGWVAyMnNsTU1qc2RNYU1KZFpDczNpbElzU2w4cnRFOFFxUUY1WGxKdTVkV3NSSWhwVXFxeVROQXlrQUx0ZzdUSG1ocjNaZkczNlhB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNcm1oQmtEalhieUlRbEJpaVdYbEdqYzd5Z3R0Z2lGSW1JVU80OXFIdnE2LWMwemUwdFlMQXVMMk01TU9XUUtkLWwtdnN3b3QwMmwyMzVGVHFieGFvT3pvcGQ4c0pJQUoxeXVDVUxrb0ZFUEFOUlNWUG9YbXZxYkpGMXMzU0JHQ3Vwa3UxNmNoWWlsdTMtV1czeDl1dXVzSExKLTFFd1VyR3I2ZFRGaHQ5dnJ0Q0p2c01wVl9kWHZZUQ?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46036.50215277778</v>
+        <v>46036.68814814815</v>
       </c>
     </row>
     <row r="4">
@@ -548,24 +548,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Louis Vuitton Goes Hard with its Latest Flagship Store in Beijing - PAUSE Online</t>
+          <t>Chanel, Gucci and... Rosen-X? The Brands Topping Saks’ Creditor List - The Business of Fashion</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 12:18:25 GMT</t>
+          <t>Thu, 15 Jan 2026 05:27:00 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQOW5nRnZiMzEwM0pCR3hwWWxGZkhiMGIwd3BlS1Y2M0I3V0I2cWFXNW0wNTJyZlJLZ0ZLVW5vRWpLbXYwTU9GYzJVY1dfWW9DTnNtSEJlWFkySFJVV0pCVl85dEZtNlpaU0VIWTU0WlEzeEdyX3lTWE1ONEsybUI2ZVFoN05Td0x2N0VhUmZIVUNnT3hVRGhLSkNwVW9Fdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQNl9NRS1NRzlVZzlSRm42Sm1OU1d0SEt4bjFCMXdUc0ZnejcyNHJldTl4SlFFZDlQamFXOF84bUEyTGdncVpPR2RKR2NNeUJzVFMyUXhZX041aDRlcjV4TktNUTlpeDJXUUIwbnMwSnhaLWRidVNYZmltOEFZUVVuYlozMzA4eWZnX21pRFMwM2N2ZGdNYjZOaklIRUVwemppT1pyYU55d1FMQTdZZUtUajJXbw?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46036.51278935185</v>
+        <v>46037.22708333333</v>
       </c>
     </row>
     <row r="5">
@@ -581,24 +581,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The $1,000 Gucci T-Shirt Problem - ADWEEK</t>
+          <t>Armani partners for hotel expansion - Hotel Investment Today</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 11:00:00 GMT</t>
+          <t>Wed, 14 Jan 2026 16:01:48 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBpSXptWW9hWGp6am04UU1MVXpVSGpiRmYweVZUd0JyZVZfQURXLURGZlExTzBoZ2E2QV9vVWk2RXVFeEt1RmxWMTRhcDVOaS1zSnRjQ0dtX0tHczZiSWFqODF5Yl8zWFJ1MnVFOXZkdWY5UFVtM2V4YkpR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPSkljZ1ZPUFgwR0gyV2ZITWpIVjVhaFZCTEN1MnBjZzhfZkRVbUNzaEYwaktwNExVMmlGMklvZTU4LTZtc0kyUXZaV0hmbHFWU2w5OWVoQ2x4bncweHJWR19GVGRndzJmQzlaQXEwWm41X1BOTm9YMld6eG1oamZUTnNud3dUSnpRRUEtNUVkaldDckktMXc?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46036.45833333334</v>
+        <v>46036.66791666667</v>
       </c>
     </row>
     <row r="6">
@@ -614,24 +614,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>I Saw Mbappé In Jonathan Anderson's First Dior Campaign, Through David Sims' Very Expensive Lens - Our Culture Mag</t>
+          <t>Rose Byrne Suits Up in Armani Privé - WWD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 10:00:23 GMT</t>
+          <t>Wed, 14 Jan 2026 15:56:15 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNSldJWE5MTEl3VnRqOXp5Y1RodFRCZHFVTEdFNEItSTdaQzZoQ1dNeU9BdEpmZTExel8taF9kR0FTemMtd1FnT1YycUVVWjctdDdIcm1HZkpTOVdneVNicTJTc2d3TVVsLXNZWGhQWDk3c0ZucFY5N1RBakIyYXNFdnRyelM3b1VRTjNhbUFUbjI1MnEzeXJyLVM0dS03RDdVNmtlQ2ZoS3AzZkh5QmwtdzhvejB4cFBzVk1nY1J6dU51dU1RV0d4WHY0UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNSTVQc0h3RU9aa1Z0YTZZT202ak9DU1RqUTY4eGxXYldxa3ZmZUNJSzdOTnc3LVkwRUFHdTRvbFlKa3lneVd0OE1uV1R5d0ROTzQ2Um5PRUJFVTU5U25mcmFza2NCay1Zamo0eEFXV3p5My1zNEJHd1c1T0w2YU5LN2FoQ3RCN2VEZ2stSWxILUUwejJ1QXBkdi1xN1d0cktLUWF4OFpLaGpIZi0xcG5Z?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46036.41693287037</v>
+        <v>46036.6640625</v>
       </c>
     </row>
     <row r="7">
@@ -647,24 +647,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Valentino Simoni unveiled as new signing for Gimnasia de Mendoza - OneFootball</t>
+          <t>Chanel and Gucci owner tops creditor list as bankruptcy tests trade credit exposure - Insurance Business</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 13:06:32 GMT</t>
+          <t>Wed, 14 Jan 2026 16:58:02 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQLXFaSjR2WG83aVBIUUpsQXFfd1hQYWw0QkljbFNQQ3pOaGxTTmNacERZYU4xUlNqbnRaQXE5djQySzlFM3psZGF5Rk1YWlZUMHBpcFVHbGFFVjc2cGxkTFVxZ2JwYVQ0RzJjN2M1M3F5RmJTdU9QWVhXUXlLUzhMN2RoZXE5RVB0QUxCeWREN1JGWUxZQnMtckJucmNQcExRM2d3dlo5N18?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxNYTc1djVOOEVTelRacEFqRlViZ1BYUG45T0t2ZG1oSUFFLXB0SGltbE1JazJPNHNDeElKWTZiZ3BvYXhfTHluWl95OURzS2RNRDktMU1NMzRQM3dycGZxVE42dFJaSnlYclRTMVNlcmJldjhKMTlsWkNKMkl6OGwzdEw5YWpSV1M4ZGtiWS1RSmdOVTdSVnh5X2VRUlVyWUcwSGZOREFKM0VFS25TNFY3LUJZcE52ZGJ0ZVlrWkUzRXdBSUdaTnpJWjZkQVRTQXlBdEF4YmZmSG5QbC1ldkVxMWhRYjV5NDVQeWc?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46036.54620370371</v>
+        <v>46036.7069675926</v>
       </c>
     </row>
     <row r="8">
@@ -680,24 +680,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Alessandra Facchinetti at Gucci: The Creative Director Everyone Forgot - nssmag.com</t>
+          <t>‘Dracula’ Goes Designer: Dior’s Latest Collection Pays Homage to Classic Literature - The Hollywood Reporter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 09:57:25 GMT</t>
+          <t>Thu, 15 Jan 2026 00:03:38 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBfYlc3Y0hGdlBMcWdSdUxYeVU4cEUxQ3NrcFl6SmdreWRvUlgtcHJZbm5TdXhYd180U1BiT0NZVjRFTlA4WGFKX0Rpd1J6R2dKUFlaTmNMQ0JKcjBxZW5JSDFCMGVpRFZ0aXI3QmhzY2tKNWpZb1REY2ZpNmE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQWUJPZjdJVGdKRGdyUEQ1WHJ1T1VQQWJtbDFib016eFlxRi1ZYjk1dUpmclJBUnhPSGtqaXhvNmR6RWFEUGJ4UE9famNhUEJEMm5UUGE4N2NoLW5hbDc4Z20xVjd5UnpNYWo3T0dlSGVlQW13Wm11X0VPQ3Jhc3BIS1ZiNlc1Ui1BcUQxZ2xBLXRaUUxxQkg2dENNUlNmbWM5dUkyeFdDOHZ0eksyYU1oem0teGlhajAxM2lIVUJnNA?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46036.41487268519</v>
+        <v>46037.00252314815</v>
       </c>
     </row>
     <row r="9">
@@ -713,24 +713,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dior’s Beauty Products Feel as Luxe as They Look - Allure</t>
+          <t>Calvin Klein's £17 'perfect for spring' perfume 'lifts my mood when I spray it' - Manchester Evening News</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 13:00:00 GMT</t>
+          <t>Wed, 14 Jan 2026 18:12:00 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9RaVZYU08zRm85UVpkYkJRQ2FtN2RZUEdUQzVianI5VWVBNUk2S25tMDZHOG50a2p0YVRva3dxZlhWeTlDdmFzSVZ3X2RRU2NoUTdoR0dTdjB5Z1pOVXVENGFISTM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPam16aC1maWEzaFN4c184Y2VuUEtwbTZoeTNsLUhzRl9lVy1mSXMydnBHOVR4U1M4ZmpBdWpzVkx6WU5EQVdCdU93a0RuZ2h5dlBWeUhmYmdOOWw5M3RRM0dJVmFHSVJ3cU5QZGg0bFIxVF80WjY3N3l4cEE2dmNTSGdIQVRxMHdGQ2tRY1UzV1RDY3NBY25YYjZHeFZreTjSAaQBQVVfeXFMTWg4d0ZRMFc1UWlkc0wwZ3ZxR1NVbmRreGxKb2tpYXNmemVxbmFrWTlmZEJQbmN1TFNZVWtOQlJuTUZIUWVtcGNLNTZLdnFtaWx0bEpKMm1oMy1PdlBldTdnNlZkQWlPRFhOX3NuQUhpdHpQcm1tbVRTS0JfS2tmZHl2ZWZ0N0E3Ukg2QkVNN2xuMUJzbmtiZUlVdG9zUkNjWm1KbXE?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46036.54166666666</v>
+        <v>46036.75833333333</v>
       </c>
     </row>
     <row r="10">
@@ -746,1278 +746,4380 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Valentino Rossi reacts to his VR46 team not winning a single MotoGP race in 2025 - motogpnews.com</t>
+          <t>Valentino Rossi and VR46 have already made a mistake that will cost them Pedro Acosta - motogpnews.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 12:00:00 GMT</t>
+          <t>Thu, 15 Jan 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPOGhoMVJVRXNZd1dDRm5teXVkN2hrcDdYNWxrdDRQOFNMSHZpR3IxNDRZblBmNm9tRS1heU8yc284eHRSRmw5Mm9KZmdwb1FyN2lGY2N3TlhoUDRKNkQzLUJKYUNFbVN3cnRwYTBZOHc4MWdLZDJVMUpCTnZjMTZ4TTNKWDlLMEdiZkxEMFNTUV9xYk1KTnYxUExOS2tjOThhdkhYNWo3bzdtSWNLZTZxWV9IQVV4MnRydW5B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPU0g1LWUtSmYtOXNiN0hLZmdQZG5EZDdCQkZza3l0OVpiNVRHdDhYUHFfSGwybDJwakY0Z0xfZU83azRla21ZUnlfOGZKTEhtc0VvYnNUSncwajRhS0kzTy1aYXBTNWlJdGo5eHI2M2I3U1RhVGFtbEhXNUg4cG50UTA2Y2hzRV9keTVSSWlsYkdwamxseDRROGFGMXhuWHUxQlI4cTF3SHVPSnFOZFFyN3ljWGhQQzVSdnBOTXZxdHlOUQ?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46036.5</v>
+        <v>46037.33333333334</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Value Retail</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Zacks Research Upgrades B&amp;M European Value Retail (OTCMKTS:BMRRY) to "Hold" - MarketBeat</t>
+          <t>Dakota Johnson Does Elegant Makeup Best—9 Products I Know She Uses - Who What Wear</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 13:16:20 GMT</t>
+          <t>Thu, 15 Jan 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPamZsVU5IUXRGZlhrcnA0WEdia3NOaGkydWR6alZ1TzRFLWtCRnRxVDJhZXlxSjlJQkdwNTloZTZaSldCa0NiREc0ZWxyWGptWkNhLWZRazR4ZlJURW1mQXVNREdldmpyT2h1aDdzalJPTkhNWWo0NFpISWJIcElUeGllMHRFWjc4eDBCY191Zy1tWF8yd3AyenpOWWY5UG5HejZoN0xYZEhvS2NhcXdCVEZUQU1oY3lWd3BBR252R2U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5CbXk2SThjdC1xd3RIUmNiUzlXZ1BIeURCQmZZdGw2ZUJXN2pKSTdOVnQ0elphVDlCOTNSVjdwQWxEQW01Nk1NSTN1NWY3b0lJQ2YtMjNHZURJQXZLLUM2Vmt2OUpIVnVMZ2pEUGtzc2xCdkVUR1RDX1JqaUc?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46036.55300925926</v>
+        <v>46037.29166666666</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amazon to launch Prime Air drone beauty delivery in the UK - Cosmetics Business</t>
+          <t>In conversation with JISOO on fashion, personal growth and New Year optimism - RUSSH</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 11:37:15 GMT</t>
+          <t>Thu, 15 Jan 2026 05:05:51 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE13UW9NbmF3S3BocEhDcFdYX3QzcDFWeDc0ZTdqbS1CNldjRUtFdmYtZk4xaXN3YkhJSG50MG9yTFRRV1ZnMmVFMGJmUEZDa1NQbWxqUUdKS0lHUlhJYnFVZ1F1VVF1bkNvZm9TUDFQZWowcUJHV0Q3M3BrNGdoR1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFAtSTBlbzRqWGFGNjc5ZWtoTDVhVVgxZEVDRm1ub01NdDRXejhwSDVzTW9OeG5YQ2RqZkR6dGRZSXJYRXdVYWFjV1ctMEJZR0YxelJ3a1BJSEhfYXdBVE5HZXdtQ3p5Tzd5a2FoNkNjSlJVRDJlbE5jSGhnRQ?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46036.48420138889</v>
+        <v>46037.21239583333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The London postcodes affected by Royal Mail delivery disruption today - london-now.co.uk</t>
+          <t>Why Best Buy thinks the future of retail media still lives in the store - The Drum</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 10:55:42 GMT</t>
+          <t>Wed, 14 Jan 2026 17:15:00 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNSnZOdG4xb2RkM3VuUmE5Y2p4Q2w3NFBHVmNGdXd0NFlRTnphdG82dmpwMmJkdlgzSkJ3MFluOW8wTFU5LUE5SWJSODhrVl9KYkVxUHdzQzBGX0JsZGxqRVAyMHpjNFlkcXhTa2k1MFFXY3BuNDYycTZmLXAtN1BESTdhRDZ2MzJZdzRxZzJrY0lhcUxh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPazRJTkdNSy1sOFZxT25jZzh5OUV5eUlBNXh1MExuZ3psRV9XREJxRXN1MnZPekFJTXRqOHBfLWg1Wko2QU0wQk1meVMxcDdTMFYtckU2ZzAzYUJiT3NfQkdLSjhCLWJHbTJDTTUzYUpEY0NsX0hRLXZ6cHdLeWpBcFdLNzNJTktkdXMzUy1IMGRxTDV2a0R5bzdSSHIyYlBZckE?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46036.45534722223</v>
+        <v>46036.71875</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Berli Jucker Logistics and DHL Supply Chain form joint venture to elevate healthcare logistics in Thailand - Payload Asia</t>
+          <t>Dior: Dior Unveils Women’s Ready‑to‑Wear Fall 2026 Collection - Luxferity</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 10:15:03 GMT</t>
+          <t>Wed, 14 Jan 2026 17:57:12 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPaV90UW14ODM5TVJqWnh4dG9KNF9PcWowWThrZkdiN3BjdVJVaXhtT1RSRU53MkNUYmtZNk1CcGdFV01YMlpfMFpIeGxKR0pVU2NaZnFFa3VEVXlVZXNaNDh4dGJkZ2F5NmJNY2I5blROb0xlVzJzRG14QkRoZS01NVV3RUZzY3NFU0pjdGh2bGRKemJWdTBPRFFPaHQwSHByaW9wSjQydkwyV1QyWVc3RjRiMDlEZFFrUHY5OWR4bURDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNOTNSazltNU9hQV8tR1VCMWZFZE9YMm95U0VuZzRHOE5PM3NnMEp4LWlaTHVMd3NHUkE2QmxZNXVRbEhOOXZxUy1WaS1iUFJLWHJ3SUhuc2tNdzltVDVMNURFeUlFbWZ3YlpIRGhkX2taQk9wUWRCSV9vWXBuZDJuSHJ0aWV2SE43S1BiSkd3?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46036.42711805556</v>
+        <v>46036.74805555555</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amazon Seeks Vendor Price Cuts Amid Tariff Uncertainty - Silicon UK</t>
+          <t>Gucci’s La Famiglia Is Now Available to Shop - Haute Living</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 10:00:36 GMT</t>
+          <t>Wed, 14 Jan 2026 21:23:53 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOTVc2dzN1c1pkWVRRNDEyQ0F5TnRVeE42X0hWZ2dQNzZFenVyd0tIbTdTNDhMUW40R3p3ekRWT3BKVFZIcVdZa0s4bTJaaV9aR3VuVC1tQ2VtZXZ4UmpSdzBJWUZjVlcwMXUwZGQ2RVV6OGFXWGx0M0wxRVdKVjJJU2NlZkdLZXfSAYcBQVVfeXFMTk1XNnczdXNaZFlUUTQxMkNBeU50VXhONl9IVmdnUDc2RXp1cndLSG03UzQ4TFFuNEd6d3pEVk9wSlRWSHFXWWtLOG0yWmlfWkd1blQtbUNlbWV2eFJqUncwSVlGY1ZXMDF1MGRkNkVVejhhV1hsdDNMMUVXSlYySVNjZWZHS2V3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1jS3dCTkZmR1pXWnhZV3ROZTFnMmN2Y1I1Y20yOWMwT3o2ZjBlMGR0MUNrMTAxS0xKTzBRMUU5WUQ4N3ZZWUs5UUdFcE5sUW9xZTdYX19XT2hZQjNQRVFqSlhCanhVTXBrUnNKSUhtWnhXN3dqNWtIZEhSN3Q?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46036.41708333333</v>
+        <v>46036.89158564815</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Another explosive Mane v Salah episode on the cards - Sowetan</t>
+          <t>Dior’s Book Tote Gets More Bookish - V Magazine</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 10:35:44 GMT</t>
+          <t>Wed, 14 Jan 2026 14:42:32 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOTDV4SlpQQXpVbG1GQVR6VkhzNkxnMHV4NjZ2Um1yVWZ4VzgyZlV3d0NzR1o5TlI4MEtoYU1Jdl9zOGFhUG1mQmdrQTdBYVpDcmR2aWcxck9OU1pnVXhXWkc4VEw2R3ZUYUgwM0pvZE1nN21FQXhWeG9ELWJxSHJleWg5RkV6cEpvdElHenB4YVlyS29Nc0l3QkFyMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE01OVB5MnVaZFRUNTZadUVVYVBzMEE2QlIxLVZzbTJKeHNqeUZBMTZBTXBPV25jeEotaklxbVJFVnFSM0Nsa2g2WFZIck5iUjhiZUJMSXdreGtVV0lvVW41YkJQcmxSa01BcFhyYkNud1o2dw?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46036.44148148148</v>
+        <v>46036.61287037037</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>The defendant, who cut his aunt's throat and burned her with cologne, attributed the crime to forbidden love: They guided me. - Haberler</t>
+          <t>Cheer on Team USA During the 2026 Winter Olympics In Designer Collabs: Skims, Ralph Lauren, J.Crew &amp; More - E! News</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 12:44:01 GMT</t>
+          <t>Thu, 15 Jan 2026 01:30:00 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQYVBjTVlRUXpZRkUxeVY1VUZuMWlRV3c1R3M2NlhPeVhEWTBRRmZEcUhJc0VlNldlSUd6VFhkLXhCbHBERm5JN1U2YU1vZFJBWnhHWHQ3WkZ1cF9ZWFhUdUJCTi11VHR2WG1oNmxTOF9FU0NHUkJOLWZVbzY3RDlETkZxMncycjB4bjVj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNWXhyaTljQUhmMFBsQ2JMdzFGOElzTFVtamdzQWJpZTNnenNNT2I4REJ2ZXZHLS1CbXFBUEFfbGJ2VDktWTh3RzF1YWhGNmNtbTBva0xNcU5aTE1OQlRsSVJrQl9LREJsdkZrT0lMdnZ6TlJGalhLWEZ2RWFsc3p2UlVtOHRuWVJvTFZIMS1vSUx3S2ZGVHBWbHdoRzJSdkVPdkRTaW5fYw?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46036.53056712963</v>
+        <v>46037.0625</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bayern vs Panathinaikos prediction and betting tips 15 January 2026 - Dailysports</t>
+          <t>How Ralph Lauren is using AI to scale luxury service without losing heritage - ClickZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 13:14:54 GMT</t>
+          <t>Wed, 14 Jan 2026 17:39:59 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPNWlxUF9vQmlqdnBjOWRwOUgzdmNlZVJhS3VhaVRTd0xLYzBVNnljM2NwV1ZjSDR0aUk3TjJrVm80VDVkVktxREdaTDVHV003bmFmSGRydk1rbFpnNWFuQXkyd0tLRGpHWUF5MmQ3cWMtUkxjQWw0UGNLUlRRMDNRTFNXTV8xM0UyTjRpMkU2SW81aEpEMnlfU2pnOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPS2t0RjNNNTlfdjZIcTdwX0J4MWVNb3BRVmRGNFcxbzk0MENzVkNKeWJXVk1MV3VuR3VlM0VMMGpCYzJka0V2aVZRcThiT09KSFFEVUsxdi1MVm9wdnM0LXY4YkZyUmZhVjQwRWU0bkFYLWxhdXZUUWdVYmpVQ1g5VmcxOGg1M3RMVlUxc0dPck5oSDAwc0o0WmZENTZCODVpX3QwY3ZNTEZkSmc?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46036.55201388889</v>
+        <v>46036.73609953704</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CALLING ALL TOWNS: are you up for £3m? - Punchline-Gloucester.com</t>
+          <t>A Discerning Watch Collector’s Guide to Cartier - Sharp Magazine</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 11:28:18 GMT</t>
+          <t>Wed, 14 Jan 2026 21:14:38 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPSlQ1Tlh5LW11NkQ3VGtCa2tzZHdReXhFWThaUWxzbm5NVk1uYmpqR1lTcm5pSDU4a2tXSll1TW1IenZYd2NMSDJnWjFyeGZSMmFTdUhCQVMzYnpiWVo3OUY2Ym9IeldoZkxWSkNaT1ltZV9FOXNucDlNeDlfTXdMS1RuVXFtU0hkaGNoRzlfb0JvX25Qc0xhekxpNm9udHU2UERvaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9jUEY5dEctTFAzTzVmVFh1SnZkYlYwcl9feHVKbk9rbWJiQ1lubjdMYkRtM3YxRWJpOFctWUpwcmdubDF2YUxqNVAya1JERy1YYWNJdlFsSlZ5Rmt3Zk11WkZDSURzWjBSVlIxNXJiSUs5ZnBhTGZGVWJRWnN1bUE?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46036.47798611111</v>
+        <v>46036.88516203704</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Retail crime now a five-minute reality for Victorians - ragtrader.com.au</t>
+          <t>B&amp;M European Value Retail (OTCMKTS:BMRRY) Sees Strong Trading Volume - Should You Buy? - MarketBeat</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 09:46:54 GMT</t>
+          <t>Wed, 14 Jan 2026 17:35:43 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPNVhKcUhKajM5c28zNkFvRV8tWEZRQXN1NHNIOVZ3TkNrWjFhRDlSQzl2d1lXMFVtTUE4dEdvTUtreF9BRTJiNXBjR1dqVncwbGw5amluRkRCdDZKZVdRdUdhaElRVXVjd3NGRDl3R0UxVlhnOEtpLTc2UzVZcm5yRWdnNHBUV3NQUEFYN1RmYVY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQVHhNVEFZOFZGWWZUWi1JLWpISmMxMTNfcF9yWEF6SGJJM2JUdXhlQmNwUjY5bllQRWRiRVhGRWx2TVdEM0RvOE9uV1VaUnNqZXQtOXVBMk8tdVhHZllYclJlemxQN3NtdnhnUENuQ3UtWUM4S3puYnVBMlZHaDZOa3VHNk53cVVFcWVWZ3FOTVl4S3pZWU9nbmxCc3NtZTNQMTFuWi1LVWRaMFN0N0FSTDNuZjg3bjFwVHhRTnZrWUk3dXVoVmxud3pZVjFpQQ?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46036.40756944445</v>
+        <v>46036.73313657408</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Flock Safety Showcases Role in California Organized Retail Crime Crackdown - TipRanks</t>
+          <t>For 8 years in a row, UPS leads the way in on-time delivery during the holiday season - UPS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 09:36:25 GMT</t>
+          <t>Thu, 15 Jan 2026 01:39:45 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPbEQyS1paMkVadkZTZXpTcVg4TEJHeG9zWjJUTGdCYjhDUkNYWEJJNVVvZDJRcklSZ2I2Ul9JekR3MWp6ZVdVdEt6aVBnZ05LQ1A0VTlKVVo3a2hwSmZIc3RPYUQ4dEZlRmdIanRsVlQ2X1paclFpb2J1Ti04UFNrZDlQVmF4MGp6Z3dMVm4wSFlwcXJSQldPOE14YU50c2x3MXcyZHlIcUZMNWNqUng5UVMwdWwtY3pLSVVMaVJzRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNYy1xQ2N3aXFka1g2Z3dpeXRrWlAwc3ZZQy1TR1IxaHdJcnNad3lVOVlLOE1JS2lxZlJtOTZoZUFMVklyX0FTUFhfVVhmcUlWNi1vVmVmUUNwc2RmZjdMS1JnN1NWbTVKdTlUZlJiVzBybXRwUElwQ3RCZ0I5YTYxRmd6TkVrVU8tV3VkZHgzQU53ZVZzaHFrOG9tWUdoS3VycTdMY0l4aEdSNHJzNlhOczRVUVdoSGtrUWE2c29QNmxTZw?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46036.40028935186</v>
+        <v>46037.06927083333</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scottish Budget 2026: 15% Business rates relief for retailers - Better Retailing</t>
+          <t>Armed men break into Stamford home, assault residents after posing as Amazon delivery drivers: PD - WTNH.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 12:13:38 GMT</t>
+          <t>Thu, 15 Jan 2026 02:44:54 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPZ1pfX1RkTEhRWlMtTW96aUZuek9JV0xtemhhM1dRZDBmeVYxMkFERzRBdDRFQVZDM0Ita1BsT2o2cWhLVi1UUkVSSEVvVlM5S1o0WjVQUHNDRTdFTjRjb1hIYjNoakZydmc5ck9mM3ZVOFF6eWlGdzdfVFFybkVnbWJTbW94ajc1STcwTXFRb19RdFJreUxJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQNlc3SFJuZ0tGNFg1N1VuSUl1Tl9la3B2VTFlMk1XRDNUeG1yTmJfeDZPSHF0VkFiNzZHWkp5ajFvV3VnV1kwYm1fVWRQMTlGM2w3TG1wakZiQ3JzOVJyWmhMdjZwQ3Y4TDJ0TjE1cUZCUWgyR1JqdkgwWWhtc2tlTDJDRTNOQ3lYazNqc1F5MW1HZW95NTZjenVyVko5di1MbmZtemRtcnh1LWVVS0tsTm9wNU1ZQTg5NWZxSWJrdF9zVE96VWhURlBRemdyUUkyQ0dnT3FrZWo3bmE40gHiAUFVX3lxTFBzclF0THF2QzR3LXBPelZRa3hUM3VoMmREcE56Q0RJWmc2cnBBU3BCdkRTamdQUENWa3JHeEVGa09xbm5INkszN1hZN0xZT051cG5OMXU1VlNwbXJSQ3Atd19KeW85ZEZKNmdMUlRuWEZpRnZmZllfNE5VYThrM3NOU0lzcE9HVjE0LWd3OGVISHU3eW5ZU1lEWW5hMVJ6N2RkWUJ1RGtsYUlrZjMtcTdvUTBzS0o3ZE12ZHp2QmtnT0toYy1KNHhacUloUGNxY3UwcHoxb0VZWXQ1djc2NDFuZmc?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46036.50946759259</v>
+        <v>46037.11451388889</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New map shows London's shoplifting hotspots as police boss says retailers should 'do more' - My London</t>
+          <t>Amazon customer fights for reimbursement after delivery truck damages fence - Global News</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 10:50:04 GMT</t>
+          <t>Thu, 15 Jan 2026 04:10:46 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNeEw3WlFHLWhEbS1FSHc4ZHRXM2JQRkZyR0tHaXRXTkgxSUNoUlNFdUpLcmQyaWtITUd1a1pJTEt5V1NGOHZ3TDZ2STJhY1U3bllob1FaOWx1R0xJd0RsYmhZNkxsYldhMWNYbW9DSHBnNHkxVF9aMktHVzkwQmZmZ3dTOTVPVEN1bUY2UFFhSlRBT2vSAZMBQVVfeXFMTXhMN1pRRy1oRG0tRUh3OGR0VzNiUEZGckdLR2l0V05IMUlDaFJTRXVKS3JkMmlrSE1HdWtaSUxLeVdTRjh2d0w2dkkyYWNVN25ZaG9RWjlsdUdMSXdEbGJoWTZMbGJXYTFjWG1vQ0hwZzR5MVRfWjJLR1c5MEJmZmd3Uzk1T1RDdW1GNlBRYUpUQU9r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOZnNfQll1ZmxDZmZJZlBlejM3VkJaRTR2aVFuRWp4TFNOZUNkOHRTcXg5akZycjRFS2F6R1hEN2dNSjBNZkYwVkxFQ0lIVkhIMXNOdk5ZaVg1SnVfaTUxRklPaURiZ1dPeldidHIwc1FtWFVUWThCLVRNWG5BR1JNUkktX21UZ19ET3NNQ1hCZDlRbmZ5aWxkTl9TTG1oRTFuMDY2cQ?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46036.45143518518</v>
+        <v>46037.17414351852</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Barcelona player ratings vs Real Madrid: Relentless Raphinha fires La Liga leaders to Spanish Super Cup glory as Lamine Yamal &amp; Pedri also dazzle in breathless final - MSN</t>
+          <t>Amazon tests out game-changing new technology in 'next step' for deliveries - The Mirror</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 09:21:24 GMT</t>
+          <t>Wed, 14 Jan 2026 18:10:00 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgJBVV95cUxQTWs4ZEl4a3ZoelhPVDdkQU5MTGpkbTJhQ3AzVTRoQXBSQ0Jrd2ZJWUVrbi1obVgyTUpfSExQMWJOS250a0dBbGI2TUtfbnRqWk1IMXZOanBSbTFwd3g4UjdicHJFUFhwc2tXT1dLTFdQWWJzNnpBekVHaXlfTnBLWEdBcHZpZWxfVnhvVWppUm55OW9FaTRCbHBBMnRLOWNuVmlrYVBFRDV5QVBpazNpNURyZ05aTkRRX1R6UC1lMExkbGc4TkdQcC02OENFSzB4a3V5d1lrSnY3MHhCbUFIQjhTeDh0MGNvNWlWM0VYN09jaW54Wjc1WkNnRXlsNGhoSW16UWd1S2JrMkcxU2d5UXlVVzJicVFCYVZZRVpRQUNNckJUUUFJZnFsRk9WMVFhZENaY2VB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQVGNGcTJyM3RGNGJqRDh0eGRCSW1IakY4Mlg1QzBSSzE1WG1pWWkxNG8tYnk0eVduOXl6cFJHTE5RQWNNMVZkTS1Qa0tOZVVEMTdUSWhZRlVUb1pkS0Z5Q3BFS216YTBUYUt4YnBiekw1MU1XNU1UR0tYa0JoMndTc0ZPMNIBiAFBVV95cUxPenJacUp1ZTdmRWF0V1BGSGZKM0p4S0hSVHFnajlGY25nY2ZaM01VUFBicmpRWDJYYlJMeUhNOUFzaHZuOFpxdnNoZlVQd1VPeVZqZENlZk5Kb3hYNGVWc0o5dkZlWFpHMzNZaEprNzItdTFUZUVvQ01HTF9YbnlPMW1jWEQ4TWJq?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46036.38986111111</v>
+        <v>46036.75694444445</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Real Madrid are looking at £86m Arsenal star to solve their attacking issue - Yardbarker</t>
+          <t>Amazon Prime members are being automatically upgraded to Alexa+. Here's how to opt out. - CT Insider</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 11:54:05 GMT</t>
+          <t>Wed, 14 Jan 2026 18:11:23 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNMVFnakxqX0F6WGRNNXZkSnRKaVBKandyUmNNR0ZuWTZ6b1hBekJUbUR0d091MVhlelZaVmljZWdRQXpfRFEwN0tlMjJHMmZNZXd4SHJiaFhpRU1reDBRb3NvRFluSllfYW1pd20xZ2RpeE9yMktXTTJxTkk3Y1J5Tzl2b2N5bkZSNWg1R3UtSThldlhxQXdtTjVBUlQ4ajMxN1p3OVhuS1NKQlBDQmNCSm5mSDZidjNOVWd3LVZsckJianVOUG5nWVgtaUgzSDV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPRFpIbVEyUU4xNmw4SW11OWh6Yl9sTTNQQ0FwWFUtUXU0N1pZZUt5Vl9qN2tGYjZQLVF0bDBueEdJWUZlVXo2TWI1ak5DTm5mZG92bnNLWTV2SlowR2VKUnlONW96dFlYNkUyTjBfYjAyNkhKMVk0cWFGQWNHbHJHOUo1YnY2dnpaWTlv?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46036.4958912037</v>
+        <v>46036.75790509259</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jurgen Klopp Denies Real Madrid Link After Xabi Alonso Exit - News Ghana</t>
+          <t>Fake Amazon workers rob Connecticut home, getaway car stopped by road construction - CBS News</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 11:39:02 GMT</t>
+          <t>Wed, 14 Jan 2026 21:23:00 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNcmpHWlpvclFFcXlPUTV1NVNxWVg3QlNxSWpERFBDeUhURFROVzctdEZScTJObEpVRGt6M1NpTDgtOGxkcUJHUjRBbkVMeVBfd3dfU1AxMDBmR3dORzJFSjZnOGVxeWIwbDZldVQtQzFXVXlJS2N0d2w1dVBrWU1vajJOYVctTlNlSG5Xc29LdWxEb2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNaFpqdjlOMFBVcXdpQl92WUFsY0VodXdXNC1JZGdoVHdERVV1MHZuZDJ2T0hSUjF6VzlZX0FoMTk2WUFucFNFVk1nYWtJV0V1YXVhS3d4cU9id2cyVzA3V2Z2ZF9ld0dDMDdXR05QZmRrN1RNX1A1RVVKc242N3RxdV9LeEgzN1RnUUlJZGF3?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46036.48543981482</v>
+        <v>46036.89097222222</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Barcelona beats Real Madrid again to win Spanish Super Cup final in Saudi Arabia Clasico - MSN</t>
+          <t>Amazon announces Memphis’ first same-day delivery station - Action News 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 09:52:52 GMT</t>
+          <t>Wed, 14 Jan 2026 16:55:00 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wJBVV95cUxQXzcxenEybXJnRFdYU211SzVjek1NeFpQY3FBRUY0M3NVMXI5TTRCajhHYVNBdktBR0ExTFdHbUtxZXQ1ZHI0UkdOeWk5Ty1yNXN0dlRMaXNJTzM2M04xUnBRbTBtYjFsYTlKUkdJZ0k0X0FaemVoWjR2UkEwaTl6QXBXWXFGZ1daR2tocmJSZElqLWhHdThjbXRaa3ZlWVNkTlV0VDQxZ0thd2Z2SU1aOUVXckZiQ2hCZ3VQV1MwOV95aDFfMGJ6MmppaERMRFR6b2JUYXJ5NnNOOGl0RFFsYXFYYkhLcUIxcjN5cnYzLUxpRFo1dUl4S0pBNDZfQVZqMlY0Z3BQSGVnTVh5SzZ0Wk14Ml9xTnMwd1pETmM4SVZVVVpJWjlrZGJVREZUYmxhUEx4ZGlOc0RfYzBZcTJpV050bHJoQnp4aVppTUFwbE1ZNVVtLUFoY1ctazNqQlo5ZVZr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxONnN1UlcxWUtWNU1oa0xyd3M4Zjd0RDczdTNyNGZ4WmhTTm4zSVhuaEZ2YmRQTW9QQnBWSGpiVnBsS3B3S2hBZlRXeDZOUDRqZ1RFYlA4UWJhYTVJZ1NESXNuc29YQUdfb2tfN1BLSzA5TDBlTmN4Mno5ZDUzdlZaSWVxdmNnVlV0WkpzRENMUUIySjduX2J4UzlRVEw?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46036.41171296296</v>
+        <v>46036.70486111111</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Luka Modric scores long-range wondergoal to help Real Madrid beat Girona 2-0 and draw level with Barcelona at the top of LaLiga - MSN</t>
+          <t>Berli Jucker Logistics and DHL Supply Chain form joint venture to elevate healthcare logistics in Thailand - Maritime Fairtrade</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 10:52:51 GMT</t>
+          <t>Wed, 14 Jan 2026 14:36:53 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinANBVV95cUxNWUdCS1JaM3pNZ2txelNhRmpaVDFTY2EtTTFGTkl3d2hGZjJxNEZxY3JDbUxNYmNQQW1NQ1hZZHJKV2pSQ056UWtQX3d5aVY3U0J4RnJKYm5jS1dUQXJaYzZteVJ0WVpQaUhEVGZxN3UzSzNqSlk1bUhnczIwTC1FWURSWWdOZWRMR19Fcm1VU3ZnT0QwN0hMU29jUWo4T2lvSGNOQmlOTmxnMkQ4RWNsQ0pmd09Hb2d2dU1GcFBTVm1weGVkazlMYjVGandDZENXbF9tbkswR0lCVWJsMkZGMTMtbGxYcy1FVm9hUENocEdWVE9qV0twemVTeUpaTW1mSDZOMUVCOUFoVVc2S3lWalhJR2NTeTdkSXlOSW5oUFNzSzlHQWlBQnJ3cHFVTnJOMzY5T1lFN0tGNTFvX1ppVTFmTEZSbHpiOVRpaXZxanZ0aERIQ0dHY1RjVDN2VXdDSHhMTmRSZGp6NE8tU004OVJVUUs0REZpUUtCTnU2MmY2N2R0VC1OUFg3aWNIa2xOblNrcXY3NUhFeXJZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPN0Itd2ZKY28tTEFRYTVJUDV3QnR5ZzNhZWdla0V6R0RDWUpzeldtcFBadk1KU0JsY1dhbTdwWmExMGZBUlBFNU81OWlKUzhoX2hlLW1QTnBSaDhIZkxqdThYS0FLZ1J2a2VobTZkU3hJS19IWi1BN0NDLW5HT3JJRWtUN1U4blFIa0htWC1CVTRoY25SWW1aOXdtQklMYVcyM3BBakNxMVo3NTJqdUpoaWxlMmVjZEFrdWNRQnUxN0xaVy1JXzMxbDdfTW44dk1oRmxN?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46036.45336805555</v>
+        <v>46036.60894675926</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>'I didn’t know I was coming to coach a nursery!' - Xabi Alonso scolded Real Madrid players in 'cry of desperation' due to tactical struggles in training - Goal.com</t>
+          <t>Royal Mail tests parcel lockers to strengthen last mile logistics - Transportation and Logistics International</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 11:44:44 GMT</t>
+          <t>Wed, 14 Jan 2026 15:05:08 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOWUxjTWhjUXd2YVdUSGNCZ2xrWkZlYVRUaUk1bjUwVG4wdUc1Uy1QbC1LNGg4Z3dsa0hhZGlDTk5COVJKc0x3dldmeVZ6Tll4VU50U3VtaUk2UFhvSnJTQld2aldiNmpyeXhUcnp5R3ppVU80cnl0WHJHMG9GZUlLYUtNNUtpV25yMk1rbnZ0V3l1UzZTRkpSc1JQaXk2SGRlOXVtUUhSQjF6RHp0bWdiVEdpTHd5aUdnNll5WURnZTEwNlAweDVCV2R2R2xPSDM0Y0YydzhjMXNENHN3b2RxYQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPSFpJNVVic3c3MUJRdTJBRnNybGVITENnYjhwYmtwYm9yWXNOdDFiMmZmd2RwOUVVLTUyVkpPRkY1SXVncUR2Y2w5eUUyc1FlY0VTMEpUWk93RktQb3BWNkJaX0FxMXYtMlN2WGt5NHQ1R2oxb1BBUl8yVjBuT25hYl9HWEdXOXU4SnFSUmRpVWs2Y1F3WjBaTTlNQQ?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46036.48939814815</v>
+        <v>46036.62856481481</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rosenior vows talks with Chelsea's 'bomb squad' duo - Tribuna.com</t>
+          <t>Reverse logistics shifts from cost center to competitive differentiator, DHL data shows - Parcel and Postal Technology International</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 09:34:15 GMT</t>
+          <t>Wed, 14 Jan 2026 15:50:19 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPSjZKUkNfanFEVzFCa3l4ek12SmN4Y3NVTjJZaFItWklsMUk5OUdKN0VIX3hkSmg1Vms3SlhBUmF3TE5mdVVka19QQjBlZng4RHBQQVBWMWJoYlR1aU00bk5jZDNKeVFPRF9femoyS29qQTBQeDY5Q1U1YTBXR2x1NFVnRGFfR01ldW5lX1F5Vmpod9IBlwFBVV95cUxOM0Y1RHRJWDhIX3lJMHRlMWhLX0JZVWxPQUZVMTQ4bWpSRlhCNHI1alUtSU9ranZ5aFdOZjBQZGZsTkZzbHphMlV2WjFuUy0yTFVRanR2N0RzcUY5VnhkX2JEalhpbnUyRGxtMjR0eVE5aG44S0lISUs3VHZCUTdEd25nY0lfWVdyNmt4OE01dUZxRlBpRDVZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxONFdyMXVRaENsV21UOGxtN0V2RUp0YmNLMmJSQWJVWVpQQmdBcEJ6a2FfWVkzWjg5RTlQTGlTV1RMOF9LZ1BYbk5wNXFBZFNjTk01MndMWW80ZWZucnNjSllENHJYa3UtdjdWWlFtYk14NDhOdEZoY3JHNzdQLUVpUFJCSXVZTkZUaGJsZGhuMmRXeUZRLTA0WkR3WWpvdFVYamlKVlptdjZWWC1KX0VmbXc5Wk5HaVNkbWdsRzE0ZncwOXRyQkxTTDJFZ3hwN0VvQVJZWTZVeld1Z3JpZ0lrQlhmRVk3VEdTZEZFOFFtRC0?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46036.39878472222</v>
+        <v>46036.65994212963</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BELLINGHAM EXPLODES: “LOAD OF SH*T” – England Star Slams Real Madrid Exit Rumors - CrunchSports</t>
+          <t>How Amazon is going small to make a big difference - Amazon Sustainability</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 12:15:49 GMT</t>
+          <t>Wed, 14 Jan 2026 23:59:27 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNQ2ZsNndzRWV6Vm1LT1NaQXZ2dkppdGZ3NkNTYzlkNUlUdG14RzV3U0FuaVU4MHplMkwwdzI2em5GbXBpQ29DUjBrWFNRalRSd2dtWm9qLUR4YkpvNUdJWGdBc3R2YlU4NXlEVGY1ZjM5anJJX2ZCejFQa09lMjFJcTRlbVBlZno1YWdaajZidHJfZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPNVpzLU1zWkF3RzhFRzhXWlRlQ3FvZGZzZ2RaNUJaenNvZjhyanV3akpqbDBGVkZTVHo3dzJBSHpUNDAtNG9SeFA5V3BDblotM1dfTXNoZHVyTkpiZlRGSERfLU0zbFljakZrdDVIczlEU2oydndtTWJoSWFWN05FbDl3dHFTRVZLSllBZ01tcHplY2laeVBrTjJUNzVPdw?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46036.5109837963</v>
+        <v>46036.99961805555</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Three arrested after 18-year-old stabbed | ITV News - ITVX</t>
+          <t>BatteryTrader Replacement Battery Pack For APC Smart-UPS 1500 (SUA1500 Models) - 4x 12V 7Ah VRLA AGM Batteries - umlconnector.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 10:34:46 GMT</t>
+          <t>Thu, 15 Jan 2026 03:29:43 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNbkRyRjBNaURTc1p0Y3Z2UXpPN0hGOGpHSWRRYk1KTkJLZTM3d3EtMmdjdDlfeUZmcTBDbGpXbmR4cm5fcjJfUnJrQmV6ZXlZVHljVDlHTElyTGhCSVdWaGxhNzZSdjI4MDFBRmF2a2o0WUpGYmtoZFk0UkVnbXYwekdEWFVCRlpGMERvdTIzOE16dGRRZHpBcFgtQzNZcVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQRy1QV3czZUVQREZ5Z1Z5bDk1ZnVaOGlTNllVVWxkTHlYX1FHSDlvRVUxamo4Y2pyMVQtNkxDdnUtYl9ydE5SN19QQ1Q0X3lsWTNBaDlQT0Z1bHlnamV5MnlvWHJxTWlKb3dzQzBfanlrandvemEwMHg3OGpnVmM4WGZMU08yY0d4RWhkRHVhc01LSC1TRENFaXJMcFFsQQ?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46036.44081018519</v>
+        <v>46037.14563657407</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ULEZ camera destroyed by 'powerful bomb' that sent shrapnel into child's bedroom - The Mirror</t>
+          <t>Amazon testing out humanoid delivery robots that will ‘spring out’ of vans: report - MSN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 10:12:00 GMT</t>
+          <t>Thu, 15 Jan 2026 00:07:31 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQN281VFo3WWZ2TkMxc2RYcDNxSWJLSDhoakJfN0xBLXhXVzRJTFhuVm1vSllkeXVwc3VjTTZVbUo3UkMyd1VRUFBfRkNBREdqYmFuN1pFN0MxTmFPRHRzWjRWQ1lZWm1NcGZTU2FQcklNd0x4eEp4VENfYUdBLTdweHNsVTVQSGNva0HSAY8BQVVfeXFMTVQyZURXU0lscmFHYk12UGlZcDlJV3R6NDNzdFVicF9HQ0RadDdNY2dDRmdJanZUYTBXb0Exb0lacWliZ1hDcVo5cGliazYyRkwxUlhNMnNMVmRxUkxJMXZ0cHgwdHRqZHVUWkRVX3BPRWRuQUQ4SDJISE9Qc0NwY1EzOE9RNmh4TnVGQTFHUGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wJBVV95cUxNSURBOS12VU0welAzdjNnLThtZGpiVGxxSU1WR0w4bUtjTWFiMW11Z3U4MS1RcllvOTA3V0hORDROZVJLWjZYVDFlODRzdXo0ZHVhcEhEeGZUcEhOWEptQW5IaUxFcGN3aHMwQnFaZ3l3MkppU1hMTGI1Q0F6N2RfaWxRT1BvNU8ya0lKdU9nSmFMZ2xEMi16Y2lLMnp0WmJkM1BQTVBic29fWGs1X1pjbUxid01vYWpzQTNKRnZqY0tOUlJMQVZKN3dQMl9RNFRHRnNNS3o3eE1oZFFCQ0UzeDBBejA3QWY0R3VBLVhjcklVZlZKVmtTQ3ZUTFRVMlFkY2ZPQnZxMDh0SFFGYjJvLWJ5Q2ZVclZobnI2SlhweWdiR2ZJamtpZENVR29pZnJCNXVpOUU4X2NSS1ZfdjVSWWgwT0NWR3E5NVVBTzU0YnBUWnd6cklxZm9wSS1pT2RJVF9J?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46036.425</v>
+        <v>46037.00521990741</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Man arrested on suspicion of murder over Tadgh Farrell house fire - Dublin Live</t>
+          <t>Proliferation of parcel delivery surcharges drives up shipping rates - FreightWaves</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 12:34:28 GMT</t>
+          <t>Wed, 14 Jan 2026 19:52:07 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNY0VVNjdxVWZMZUtYdy1SalROZ09JZ3hES0pfMzk4RF9sWHYwMHJGRjViSGNpY3lTRDV5eVNYamdoNUJxVW1PMWFmcHJYcGZzRE82amZIUGw2eEMwS0FCSGFjeXZHVGdmME1ZUWpzeEluSlNwZWxZdDRXd2xTbk50WUJwblLSAYQBQVVfeXFMTWNFVTY3cVVmTGVLWHctUmpUTmdPSWd4REtKXzM5OERfbFh2MDByRkY1YkhjaWN5U0Q1eXlTWGpnaDVCcVVtTzFhZnByWHBmc0RPNmpmSFBsNnhDMEtBQkhhY3l2R1RnZjBNWVFqc3hJbkpTcGVsWXQ0V3dsU25OdFlCcG5S?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOV1FpVlRDalZPM3h6T0xfbUVKODhRT2JlQmxBdkF6UmpsYzlGeTZwTWItbWJyRWtkUUdrQnltUnAtZnNtbGhIWGV0ZUxZYnpaRERrRkN1UkZZa3lPLWJkR2tLRlJNbm5rNVlLSzJxZlFocnVfZzlRNFBaSURTNW14aE1rcWZsUGdQaHQtdlE5TWthZTRmcVctTHh4U2Q5cERQU19uaQ?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46036.52393518519</v>
+        <v>46036.8278587963</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pictures of the Day | January 13, 2026 - Reuters</t>
+          <t>Stamford police warn residents after home invasion involving men disguised as Amazon workers - The Register Citizen</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 10:19:36 GMT</t>
+          <t>Thu, 15 Jan 2026 00:56:09 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5LNzRIYjZfa3FoZnRoNXNZMDhsYkZFUDdQSXF0ckR4ODVFWHRkazdGUDFMVi1WRFF3WTVjMHdObTZfN0Ffei1xZk5uMmhPcWtlYkdtc0RXa3FQRHlOem9pOGhONzlKa1hCazFJSnVqM3hJRkUxNTZnVDVPelNUUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQYXdfc3lNb3RXYWR3UUVrWkFSM0h3UFlyNEpjbGZTOURmYzl2QzFibWlza0NUY1VrOEIxMnVka1VUX3FRMnNtb0Z0elM1SjAxZHlnaGxnYWROejJtcEJsNzUtYWtyTFR6VzJZUVI2ODBaUFAyMXVyVWpXd0NnOTNrV2gwbC1pclpHZ2NmMkZTN18zUDh1YlV5eHdjSlo5dnNrZnNmWE13?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46036.43027777778</v>
+        <v>46037.03899305555</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Stepfather, 68, suspected of shooting 38-year-old stepson to death, Logan County Sheriff’s Office reports - Northwest Arkansas Democrat-Gazette</t>
+          <t>UPS surges with 97.2 percent on-time delivery in December 2025 - Traders Union</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 09:25:00 GMT</t>
+          <t>Wed, 14 Jan 2026 19:00:23 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOVjdMMUVOZURsWlplZWRNOEo5dlhZNy1UTmVwODVzWmE3NEoyMHF4d0FyLUVUQ2xOWm1NUVZ5QnB6OENvVV83LV83UXI3T0RIa0pLNjYwalUtc3d1ZlVEVEt4ajZ6OVZrZzdNeHpEOUpsSGplM2ZsN1MzNm9rQjBOX2IwZjEyWk45VGNQdXhqZmdiVUNpekE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQS09oblFEQ2M1WTVfMk1GVnVDOVJOM2ZEcS0zVHFJUlFYbVlmNmV4Q3g0Z2RmYjJJVk1nYTNWZm5kRVZHaVF0WlgwQW5xclhmVWQ4aGlNNXJWb0JyZGExd3ItdFZERFJjWnVyMXBKbU5QdVBBYTc4VGtOTWdjdlQxNkV3bw?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46036.39236111111</v>
+        <v>46036.79193287037</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Middle Tennessee visits Louisiana Tech after Bradley's 31-point showing - ESPN</t>
+          <t>‘Amazon owes me a gift card': Man rescues stranded delivery truck in the snow, but what he used to tow it is surprising - We Got This Covered</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 09:46:00 GMT</t>
+          <t>Wed, 14 Jan 2026 21:11:00 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBZWG9CQ2NGN3c4VVdqdkxZLUJtenNqSm41a0F4WVhWODZZMzRGX2s5QzdINGJXYjltVTgwQ3FNRmh2WEduVEVSNlF2VGtyMFhnWFJrY1l3X2N2SG5FT185SEE4R0V1QWZwbmlIbE9qMkFPaXdD?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNeUh0ekNfbkhEYTF2VVI5dm00OEZ2c0dKMmZZMlNtUG1KOFRTcmxRekNic1VFSU92bU5qeHI1eUdIOTdVcFRPS2Z0bHZxNmdqV0RXeDRVenkzUGdBVVkzTEpHa0owb3E5SHlYU2hqdVhBZDdBeGwyYTh3TjNZSWJoZFFaclk3T2NueE8yVXFFQmF2VkVCbjlaTnRiN3pPbWJmbVJyUnk2VGo5N3dIN0U2Z1RadkRQM1o2eFhxbGs3S2drb3dFeEFfVmdBTDJ0RmxjYXBuZ1pDanJQYjN6TndPTWdlUkg?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46036.40694444445</v>
+        <v>46036.88263888889</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>High Level City searches Belgium French language</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("brussels" OR "Maastricht" OR "Antwerp" ) AND ("Bombe" OR "alerte à la bombe" OR "explosif" OR "colis sans surveillance" OR  "explosion" OR "colis suspect" OR "tournage" OR "poignarder")</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>'Explosive rows', 17-year age gap &amp; her friends' fears… rocky start to Idris Elba's 3rd marriage that made Sabrina 'cry' - The Irish Sun</t>
+          <t>Another bombshell from Brussels/ After farmers, EU suspends funds for Albania's digital agenda - Pamfleti</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 10:56:21 GMT</t>
+          <t>Wed, 14 Jan 2026 17:46:00 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxObWxINjRYampXaWdNd3ZrOFh4YzhvS0hCVVV2bnMxYU5IRUo3ZDJ1cnhOT3NyUkpfMUtOeTlHT1R2YTE1dFlySFIwVi1aMTl2Tms0alp3T2UxWGQ0NmxXMjBkSzQ2dGZaRmFEZUoxSjBkVTRQVnpENWZ3LXQ2aVpvOU80eF8zN3hJSmJUaWxrMUc5WVBk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNc0QteG1kQUFtQjJ2OE9UYTNaRnJJbGVkMU1lQWdpa2pMZUUwbllyR2ExTzI1QUNDZHFuRnRCSW0zYTJUY3VDeHRjRzhLRTVxZjZoaGJHQlVocVhnZXJNMmlUZmplbUh0aklsR2pfLXduRWtTQ0tTVXNOcFNfWG5ZaFJUajd4bTBUQ3NhTHpQQjY3dGFSeUpVLS1Tb01JQi1PVGtld05JZHdwQUJJb21KQktISVRBUTla?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46036.45579861111</v>
+        <v>46036.74027777778</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Daily Briefing: How fast could the US acquire Greenland? - USA Today</t>
+          <t>Bayern Munich’s Lennart Karl, Wisdom Mike, and…Vincent Kompany all late for team bus - Bavarian Football Works</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 11:49:00 GMT</t>
+          <t>Wed, 14 Jan 2026 23:30:00 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOTVRva2FPZW5UbG9ibW1fVXhkRnk1RG0ySU1hek9sSmNZZE1mNkNYcnN0SzJBY1NPRlRReHVlWEd0cXFscTB0TXhBdTBDTGFzZnVySVp0SExFVUotM0hUa0hWdG1VbElUcW5jUjZLRjUxazBmbDlTcjhDNE50R3lseV81a2tzS181OTl0aXNnRDB1dDVrNTRiOTREaDFORndJSjhYdmtjV3J1UUtCTmFKenFKWDQzVUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOY2luckFxSnBiVVpJbDB0T1lFSUItZ001X0NDa01aTWZVQXZpcWxITi1Dcm1zU05xZ3dLMWFPTWNqX181Y1BnV3Rhd2M5Y0E1VTRoeGx5TzhPMjVsc3pWSHpQUDdBOGIwWERtNkR1MUo0Z0h3Vlh3d0pvOXVfc19MZmZpeGk5cWUtdWdOeWpzWXFZX2Exekx4ODE1R1VHc2RHZTUwSmRjVDJMM2NWSGZ4Rmx2TUh2NThwZGpaTzRMUzBHWFRDVXUxM01fejJuQkcyTjcyTzI1a3k?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46036.49236111111</v>
+        <v>46036.97916666666</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brussels unveils plan to fill up Ukraine’s war chest with billions to spend on weapons - politico.eu</t>
+          <t>FC Köln vs. Bayern Munich: Live Match Details, Odds, Predictions, Viewing Guide - filmogaz.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 14:04:00 GMT</t>
+          <t>Wed, 14 Jan 2026 19:54:03 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOdWVFZF80YWQ4WHlnZXVLRGRQR0Z0QjQ4WjRCVjlYdXY2eU1nRTBMT1c2blpIWndDODJKOTQ4c2JFUUhJaTRtaHBIaC1tRzBzY0g0eFA3Zmd0QnFQUUJZUG9HZXRJSXo3QURPQjBqWDlISnk2Z3N4RmdUdDhORXFvQklRTm55NFdnQU9wb2pBMGJtUVA0MWpIcS1UQW5XUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiRkFVX3lxTE1uclJ6dkJ3Rk1HMG1XdEVrbjJhT3NmYjc3cmp3ZV9vdi04dHhhTXk5OEVxY25oSC1UeGhnd0lyS2ZHa0paZEE?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46036.58611111111</v>
+        <v>46036.82920138889</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SNP Government boost spending on 'pretend' embassies while Police Scotland and Fire Service miss out in Budget - Scottish Daily Express</t>
+          <t>The top photos of the day by AP's photojournalists - Seattlepi.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 12:03:00 GMT</t>
+          <t>Wed, 14 Jan 2026 21:04:00 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQN3RoMzcyb3o0M1ZtZkxSWFI4MW5TckFrbFMyM3RuVFNxeS02dFRPN01vS0VxY19FMGNzdTBUeldCREtvSWdfVEtzZVVWRXJPckxYQlJ0aHl1dnpoaVJ5cDdoWWZjNHktT1ZJNGdOaUxmN2JvYVVDMG9hZWd0SjRSOEVFNlFIYjl6ZG5yaHdWMnFMbFZncGtyaWZCQXhsZUtG0gGmAUFVX3lxTE9tRGxHbC1sdm03X1AzXzdZNTNiM2JTaXVRNEV4bm4zRmNCM3hZb1E5YXBqYmdXdUtLLU5YbWMzeUJ6bERyS1E5RU5lOExpX2RBUlVUTzZjVjcwQVluSUs5SHA5YU9VNFBYTjRQQ1VmNm1sc09Sa1hzU2tkc25rMUd2RjNiY1Fndldna25EMFU3OGVSZTBJTDZaTXJxSFhCRTFXSXh2ZUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNRE1jQ0dILXYtZktNLWpCN3Z0SVhDcm5UWjJVa0RUZkZaYnVmbUlLQXp5MksxYWY4Vno4bmJNYXE2dEVWSzczbkFxc09UcEdIVjhKTnZYaElvVTZDT25JY2M1MGpLMk1LZklBdlMxOWg4Znp1TjZnVHZ6WlcydmpHVllBRl9hazdYenJocGoxUmprOGItNGc?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46036.50208333333</v>
+        <v>46036.87777777778</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Apple App Store Policy Critical Test 2026 - Brussels Morning</t>
+          <t>Dortmund outclass Bremen to tighten grip on second spot - Kuwait Times</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 14:10:22 GMT</t>
+          <t>Wed, 14 Jan 2026 17:54:00 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1lN2d5elB2U004eTQtZUk4aUlkUmtfQ2hIQkhNSVhkVl80aHBQTG10UnJNMGRfS2VHUEpfVU9jZ0RaM2tUVFFkaW1lVVhJbEtzS1d0VzdscjNGc0lWdngtSE9kNmtfRGdVcU9KZnNoRFlZeVBIQkI0WmVEdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPLTRMeTFENEF3eElvVXJCTWI1Ni1TTVZpSk5fcFdFc0sxb3Z1RklaXzdSNWhwekx1QmxLV2JfWFluUkpscWhCRVpBeUcxVUI0MU1Zd3dUYUFpdXk0WF90ejlVbHJfSmMtRGVjNU1oSHJnLWVWay1GM211UDh4elRodHotUENjNzRLc1U0eTkwSDZDdm1BRmItUUJ3M3hjOWZXVHQ4dE5fREs1ckZVTm1aWEpka9IBswFBVV95cUxPLTRMeTFENEF3eElvVXJCTWI1Ni1TTVZpSk5fcFdFc0sxb3Z1RklaXzdSNWhwekx1QmxLV2JfWFluUkpscWhCRVpBeUcxVUI0MU1Zd3dUYUFpdXk0WF90ejlVbHJfSmMtRGVjNU1oSHJnLWVWay1GM211UDh4elRodHotUENjNzRLc1U0eTkwSDZDdm1BRmItUUJ3M3hjOWZXVHQ4dE5fREs1ckZVTm1aWEpkaw?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46036.5905324074</v>
+        <v>46036.74583333333</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Strikes cost Brussels Airport 275,000 passengers last year - VRT</t>
+          <t>Mayank Marwah becomes U’khand’s 1st ISSF A-Licensed Coach - Garhwal Post</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 09:10:01 GMT</t>
+          <t>Wed, 14 Jan 2026 14:47:51 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNd0ZvaHNwOXhyRDhRQVRJc3NjUkliNWJKN3dRLW1FT2drU2tFODktU1pFckVJTTNLY2k4ZVhwVWZGNlpYRVFibnBRaktJcnpaNnZOZWlrM1FjRDhCdGhtQ1ZWZ2dVNVJlcFd0WlZyc3RhYk5hZWhiSHZuaElMTTBTeGZLQ1JsNEI5VEx0Z3RaOV9PckFzX1g3TlM0VDJlZW1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQY1hSMnpyUlNJY3M2aDEwTHVxQno4M0ZsSjRSdUZWVFdodllaYmI5Z19xaGNkWHlLRHg0NU81MERDWUNPbllYZVFCR1FuU0VfcHljQ09OUFlCUHVVY0ppdTVtajZLOGZSS3hRRDJpQ0VyZEktQmZUbVdiS0FTLWlES3lBbTZBUQ?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46036.38195601852</v>
+        <v>46036.6165625</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Local Town Searches Wertheim German Terms</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Wertheim" OR "Wurzburg" OR "Aschaffenburg") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR boycott)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Quoting religious texts could be exempted from new hate speech laws - 9News.com.au</t>
+          <t>Endlessly Shooting Oddcore’s Unique Characters Captivates Players - filmogaz.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 08:31:15 GMT</t>
+          <t>Wed, 14 Jan 2026 22:54:51 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNZFJoLXdZcy1zbnpsSVJJam1CNDFiZ0h3dFFmbm82OVpVSmkxcjI3d0JQd1pmVjkxQmMyeG50QjJLSzdRd1N4ZUdCZ1BLdzRhMmF4Yy1fc1FXN2JWZ1dqUGs2V083UVpOYndCa3FEb2NGMTQ2WE5WUkx6RjZiNVdTb3pBXzlXQ0ZKeXRrUVRWT3N2anJlUEFTMmt6ZU5JYXNScmsyX1dzbGM0RmctcVZpSnFYT0l0djN5NGM4SWE1SHVHMXlPN29DV3J0MC1IVGplR2lnSnZCTFA4VWE0VXc3RTdwaDNNNDVKOC1oS3hn0gF4QVVfeXFMTzFVVERPYV9lRHFkV09XSGVuVkhtUmFuUkdwVVM3UElNNTdsVjA2S0hzMU5vbWF0c013dVZqME0yMDh2WGxOZnJGV3NyRkZubkFreVllelVqWlZxYTdfVnRkczVpMUhXSFRLdHo1ZTVNMHlRTlVWbUNL?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiRkFVX3lxTFBzUnk1SjZqUGtDS3BfdXdNWGI2dC16V3UtVURvS3ItcXRKZFBfTVZmNl9wTG9KTTB1aFBxRUx3M001LXloY2c?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46036.35503472222</v>
+        <v>46036.95475694445</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irish police investigating 200 reports of Grok child abuse material - Kildare Now</t>
+          <t>Chief Keef Safe in Chicago Amidst Unfounded Shooting Rumors - filmogaz.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 14:05:00 GMT</t>
+          <t>Wed, 14 Jan 2026 22:05:20 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPOVZSbGFLOUt1NGhLb0tDcTJFUmo4ckJnX1VJYmZuREFoWTdjRGRYaHhnNDAzcVZtRmh4Q05PZS1QcXRWZFNGTFpSd01VRFZMdVloUWJWNWxoYUdnODdiZGd5LUNnTDVRdTc4UHE5SzdEWmVMRTJmVXBOZVBxUXdHeTZTbFlFM1VNcG9FZFUycnJJSFlOclhlSEVpM25mclVBdm10Sk1pNmRyZXhua0JXeUpKSThsNTZKUEZzNFpmQkUwcUc5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiRkFVX3lxTE0yTHJub2xpQ29TVy1HNTdRbGtPVlRjdU02b0VhajhMaXVpZjlrVHVxbDBfZXNfREZEVGVGN3huZk11MGVzWFE?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46036.58680555555</v>
+        <v>46036.92037037037</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Protest in Dublin as Palestine Action hunger striker in UK prison passes 70 days - The Journal</t>
+          <t>Bayern Munich join Arsenal, Barcelona in race to sign Yan Diomande - TheHardTackle.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 11:37:00 GMT</t>
+          <t>Wed, 14 Jan 2026 20:35:49 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1faERBVGZwbkc5MU0tYWd1aEdMcjVEWk9CNkRLUjhoUjhiTHJ5eDNZZjhCRHh4eXBGQ1ZOU3ZtR3MxSXNaYU9nd0VzeEhwSFpiaEVibzVNb0RfNXpFWTgxV0VIcHVoeDJ1MFpHYXQzcTNBSC1uRlRKMlNQbG5YVmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPTzhNLWdzMEdwbUcxZE0zY0ZMTW52NGFjS3RUQm1OSjhBMlA4YndFVW5wNzNCT29iN3dwd2RQbTFKaXFvQU4zcmc4TFQ4T2lRSXFtYTN1LU1UTDBNOVE2ajgtblEtQVpFbEdtZUp4OHRRdzl0UEhKUy1NOGlwcElwN05SWUtaYi02Y3Qwd0FNVWxIWEQ3UkFyaTgtd09BWkFZUHZOem9GS01uNnBQY0o2bi1Kb01tNjN1?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46036.48402777778</v>
+        <v>46036.85820601852</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>Local Town Searches Wertheim German Terms</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>( "Wertheim" OR "Wurzburg" OR "Aschaffenburg") AND ("protest" OR "protestieren" OR "boykottieren" OR "Boykott" OR "Bombe" OR "Bombendrohung" OR "verdächtiges Paket" OR "unbeaufsichtigtes Paket" OR "explosion"  OR "Sprengstoffe" OR "Schießen" OR "Stechend" OR "Messerstecherei")</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Garda harassment case involving anti-immigrant activist Derek Blighe is adjourned - kildare-nationalist.ie</t>
+          <t>‘Most significant’ uprising for freedom - The Australian Jewish News</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 13:46:55 GMT</t>
+          <t>Wed, 14 Jan 2026 22:50:07 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNY1hoVEdtX3d5VmNBU2t5bmF4OTdjM1BlbU82YmltNkduUVdKY2trUnFDZjlWQ1hJRlh6a1V4M0J4b0Q4d2hCWGpwYmJzTHVyeTFIZ2Q2WG1hUzhmZ0E2ZkZhMXFYRVlOalkyZVl3MUM1dkp2N21NSXFxOU04djl6eFd6R3J1QjQtUGdtU3lSV1c3TG1JbHlhRS02U1d4RFFCTHNCMXBnd0FLZlEwaGdaVUcya0l2bmlxUzJRZlVYRi1tNVlLR2lsOVRjZkVOdlF4UHZV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNblk4YkRzS1Mtb01HRUxTVHpBUDdMSThSc1Iya2M1OERlSkxoTGJtN0ZKbUh1dTF2Q0NCdm5ZWWl4WERjTVdMUHJYaG5BSlg5RVAzRVlKb3pFd1BDdWs3R29sYTdNM0xiQ1hBYmhVQUpyVTFaaEgxenNydGdURnBsTdIBhgFBVV95cUxOUGVsNDRubWZac01PMWttZEloY2NoOG9EbG9FUU1ubTFXT0lRd2ZydXJDSC04bmg2dnJIajd2SXZFSlpacmpiRUdOa0hQTGxRc0pKb2xwajhFUnBDRS01dEhPdXpMenpBeHF4RFA1SXc1bVFpRzBOcmxCZERpM0kyMUZWNjdJUQ?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46036.57424768519</v>
+        <v>46036.95146990741</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>PETA Twitter search</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>peta (gucci OR dior OR armani OR lv OR valentino OR vuitton OR polo OR ralph OR klein OR hilfiger OR prada OR balenciaga OR goose OR burberry OR lvmh)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Carden Circus Beastwagon in Town With Old, Disabled Elephant in Tow—Fuming Activists Set to Protest - PETA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 18:07:50 GMT</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPQkhtNWdBQ3lkTXpKRGtUNXFsN2Y1VWFWTUFpVnZtM2NVZmtBUHR6UXg1VS1zcXVfQzNPWmxZWEwydlZ1NkVOWmpBZkY1M3V3MktDS19JMXJ1elFkb09iOThORkdGLWNJeVFVOXVrRXpkNnRLS1hkQVBPeU9WekRUT2NKQlpjajd1UEpTWWZEOFMzWmtxa1hjd1pVRUFGdlZsejJvc1lGdENEdFJJNGFDVHYtbXpFck9ac0dyV28wMkVaLXBTMlZTR0Z6NElLNi1KaXU0eHptZ0V1Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>46036.75543981481</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PETA Twitter search</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>peta (gucci OR dior OR armani OR lv OR valentino OR vuitton OR polo OR ralph OR klein OR hilfiger OR prada OR balenciaga OR goose OR burberry OR lvmh)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>‘Photographer IN Residence’ Launches One-Man Operation to Capture Small-Town Life - PetaPixel</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 14:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQelRHcGgyNktxWm05aFo3TGpEODhVSTVRY0dSNzB0U1BJX0FzUV9INmZMTGlKbG0wMXEtY256MGltVWlXSE5HUklaYmY2R0dQVTl3UHRaUmtIRzlKZ215TXBtSlBhVEo0OV91VV9Jc1JVbXNHQXJGczBKb3hSSllLd0NDbVJleGMzVUstcWU2SFVBUHEzbjN0MzRLZ1NUOG1PR0pnRlF1UFJvQVJUZ1gzR1ZTNA?oc=5</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46036.62430555555</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>XR and JSO Broad search</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>"Extinction Rebellion"</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Extinction Rebellion event to address air pollution in Winchester - Hampshire Chronicle</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPRlVEOWZzbDdqWUFmUzdhNk1vbGZZLXFfcXdSd1FEQ2s0N2hNUElhbDB3d1ZwWElNclVGNVEwMThOa0RQeWg4cC1HdFNnd1V0dFpUVU1reERMVml3cE4xeXNmVkVwbDdRYmRWNzBkWWlOYVlIUDdIRFhEM3ZDcEFFUlJ1RjVENGFndUJaU3ZUMUJ0VXY5VU1yT2VSWk1QSmZCLXdocDJMMDY3d0FvSlE?oc=5</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>46037.20833333334</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>XR and JSO Broad search</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>"Extinction Rebellion"</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MPs vote to restrict protests outside animal testing labs and research centres - Manchester Evening News</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 18:33:00 GMT</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOTFdpWFNWUU5pLWZvM0xGUTN0d2VWdjdGTlRSS2Q4VHo1bmFJNm5xQkNJenlNVjBkRzVXSkQ5WEY5eE1oRWRLWmlMcFNSMmhBOVk4Z1JSZlJzcEdYbGhvQjRndHhnaVRhcE1iOFJ5QTRLd0I3VXd2NUZYQUhRby1vREVaXzVESGxiS1h5TTU5SWFReXZpSkZ2RTM0SFpfRC1NWERMOVJsYndJaU01bkZqVlp2TFdPVWfSAbcBQVVfeXFMTkxXaVhTVlFOaS1mbzNMRlEzdHdlVnY3Rk5UUktkOFR6NW5hSTZucUJDSXp5TVYwZEc1V0pEOVhGOXhNaEVkS1ppTHBTUjJoQTlZOGdSUmZSc3BHWGxob0I0Z3R4Z2lUYXBNYjhSeUE0S3dCN1V3djVGWEFIUW8tb0RFWl81REhsYktYeU01OUlhUXl2aUpGdkUzNEhaX0QtTVhETDlSbGJ3SWlNNW5GalZadkxXT1Vn?oc=5</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>46036.77291666667</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>OPINION: Retail crime demands tough responses - Better Retailing</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 17:00:01 GMT</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1KbEdQbjdGRzQweHJyaTBuYkxkRkNPLUcyUUp1SF84bUZ2aTJBTmpZbFhyT1ROMm5JQi0xblYxcWg2c2h0R1FxTWFLaU9Ebk02NTFfMWxqdHhza01FZ1dJNzF2NmJaS1VibFlSNExmNWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>46036.70834490741</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Retail Crime Unit reporting strong 2025 results - AM 800</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 15:38:10 GMT</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQd1o2eTBuNVU1cmxkV1pYVnVKQ2lya2p4Q2NOYzFxX2NMZEdST0lXUXVncThXa0l6aFFaRjk1dmRmaklxdFZiSmZMbTVaaU04ajdFRnFhakVnWUJLWHNmZlBJU3ByYkxzX1RGYTZfUnloanRWRVZpbUxCZ2NhSnJSMDVYR29jdXR3STBJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>46036.65150462963</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Toronto Police are offering $2,000 rewards for info on shoplifters but you'll have to act fast - Narcity</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 23:07:10 GMT</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOOFlIclluTVFyR044UDVrTHN4VDB5QlNUaTVJaEFvTG1SSzhVNTZicVJwbG5hQkliMnJBZ3V3bkdybnZHc0pWOU1zZVA3d2hCVjlsY0JPNjBHRHBWS2lid0dYb3pSaGtaUndBV3pSUHlTbzFSdkhlTnBZaG82V3h1LWxyaEo2bEZYY2ZmTGtDdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>46036.96331018519</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>California Recovers $17 Million in Stolen Goods as Governor Newsom's - Hoodline</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 20:23:52 GMT</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOX3VsanYzZGJKcmJBMjMyNFhiYjh3SUZ0dHZKZzBfLVQ2RUt6ZXlTWTExYUZva296eklPLVpZN3JYMU9XUEFDdUszOFVMZS1oZ25jYXotSVdfZXVsa2pKUHFlOWFfYkFqOTJ3cXJ3ZEQyWXdNNzdDVjREanJ3VExseTVZYW4ybElzQmpsdFVFZWNEN1hRakVFR0dXQmJzc2dQRkRfYmJJZ1VrWG1RbDhyb1dLR2FweTF2eW1YTU9wTEJTSUFUTXgwVk5KeXFGSDFZYUprT3J5T2ZjS3Jma1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46036.84990740741</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Worst shoplifting hotspots in Cornwall MAPPED - Cornwall Live</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 06:05:48 GMT</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOVmI5SlNxSUs2cG0yR0V6RVgzbjdIbi1UaUwxcTcwa2pnS2gyLWM1VEVuR0VJcW03aWhRWndLdXFsS3kwbWRfQklZNDJvRFQ4eHFVR2RuY0hRZ3NoVUswYzFSTi1EWWY0U211WHlvTzY5bThBRkk0WWhOUTRNemVreC1kTDVGZ2R4SEZrTktFeHVBM3RHOWROUzRSM2pGczhrUFFWaGJB0gGmAUFVX3lxTE5WYjlKU3FJSzZwbTJHRXpFWDNuN0huLVRpTDFxNzBramdLaDItYzVURW5HRUlxbTdpaFFad0t1cWxLeTBtZF9CSVk0Mm9EVDh4cVVHZG5jSFFnc2hVSzBjMVJOLURZZjRTbXVYeW9PNjltOEFGSTRZaE5RNE16ZWt4LWRMNUZnZHhIRmtOS0V4dUEzdEc5ZE5TNFIzakZzOGtQUVZoYkE?oc=5</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46037.25402777778</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Crime gangs target Christmas shoppers and deliveries – with one offence every minute - MSN</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 03:11:06 GMT</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6gJBVV95cUxOUm9oM2xycWNaMnAwTHE5aUZYX3VmY0xleFR0ZGpzQzl6NllDRHV0cFBKSmV5TzFRc2R3bjdQYzVacFlxcm5EdG54OFB3Q1RSbDVuU0gzckpmcFE3V0Y2Z2xNVmRaSFpoYlRROENKeEpyR1hnenlEcU9YS1oxNUVPY0hodlZ1UE1EcmtyWlNOYXg0bHNpdmhybGZSTnYtT1k3b05MVDhHZVFuRktISmwxZ1NCeUY4dUw1Tlo4cDV3TG5jSzZLSjc1VzBKcmM1NGRtNnNYMWtDeTNCUWh3MVVCX2lQY0pIM3J1aG92WmJkb1dpTXQtbGtadk1SbVVIb3dvMkdOYmN6OWdmZFRLMi1YbVhwWmtuUlVsd2xNem5xRnFEQ2g1UlhzcExPRGpIMzg1TkYydVJ6bUdMenRxblU2UlVWdzVldjhJRE95cG1uNTRIek91T0xPNWw2b3RVZFk0Rm91WEQyMXd3dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46037.13270833333</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Jude Bellingham Issues Furious Statement After Xabi Alonso’s Real Madrid Exit - SPORTbible</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 22:24:29 GMT</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOY3JDOFIyNUhMZTE2Mk1rblpMWk9qVFFDd3VyUTVFY0tqVG93ck83d0JicmRMN21XSGJ3TmlVSHFkd2x2c00yRnFvaE1CLTFWXzlTSzFBQkFMMUZ1X3M2ZDdWSzJBTXZHSmhZVU9FWFhidTRxRUx3X0ZlRTdaRVZWcXdmTEJ3OUtPSzRFWDQzdE9CZ0VHMkFGYU1lLXRMYjB6SEFHNFpaVlI4R01zcTBvQ0V6WFczM2I2ZkdYSVpQVWFfUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>46036.93366898148</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Real Madrid knocked out of Spanish Cup by second tier minnows two days after parting company with Xabi Alonso - The Sun</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 23:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPTW9IYmNDWURYUHQ3MU5zalVaQWZoS0ZFNXhzMTgyT2F5Szh3N0xIczN3TFpDdEFpeDJoWXhIZ2t4VnJqc2cxMWhEWmlkdU5EUTlIaFJqaVR0dlhOaElxWUxZakN4dW91U2MtQjZtclZMcjBkTkRzV2Iwd1Jzajl6Q1ptU2VRalZ1UW0wM1A1X2I0UXV5RWVHNGZkWGc?oc=5</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>46036.975</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Woody Allen’s Next Film Has $14M Budget and Will Shoot This Spring With a “High-Profile” English-Language Cast - World of Reel</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 04:18:40 GMT</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9HT0pLclJlVjFEUW1MQW1ReHhVLWxQSlNxaGtLRVk3SXZEZk5OSWdPWDN1QTZ0RVJpUm5LNVdLeDR6WTQ0ekVTVUtuR2IyakNCcVpkZm5EQlE2R1Zu?oc=5</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46037.17962962963</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>18-year-old Lovro Chelfi catching Flick’s eye after stellar Juvenil A run - Tribuna.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 17:15:49 GMT</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPNW9pVGVyazdPRGVfWXJHYXVxOENTYVBBdi1BRm04eURPNm1vakdnMGxzV0czRTNFbW03Ylp6VEM3bkpUdjVjN2J1TGQ4R01NbmNSQ3oydmcyS1NvZUVfRzhDdlZJMVJ3ejkwLTRhN0FVSmxBNDNZcnFTR0JzNXk5WFZXOWFnVnZEcTRmRF8yU2VId0JJVW94aUUyb0ZoLWZkNjR4aUx1dzNsQkNKSklvZFgydUnSAbQBQVVfeXFMTzVvaVRlcms3T0RlX1lyR2F1cThDU2FQQXYtQUZtOHlETzZtb2pHZzBsc1dHM0UzRW1tN2JaelRDN25KVHY1YzdidUxkOEdNTW5jUkN6MnZnMktTb2VFX0c4Q3ZWSTFSd3o5MC00YTdBVUpsQTQzWXJxU0dCczV5OVhWVzlhZ1Z2RHE0ZkRfMlNlSHdCSVVveGlFMm9GaC1mZDY0eGlMdXczbEJDSkpJb2RYMnVJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46036.71931712963</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Zlatan Ibrahimovic's son joins Ajax: Explosive transfer reignites 20-year feud - FootballTransfers.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 16:27:00 GMT</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxObzl1Sl9Yc3RtM3lBdkJWdnljWl9pNmxWeTd2UEdWQUFkVzEwVWZDVEpqN3F5bmZjVWU5MDR1MTZ1ZEdpYnJKVE9MZktMYVVPdEtlY29HWXVSTUVxV1N0YjhkeDk3Ump5U0QxaXkzN1UtNUU1cjFZdWtWQW9WWWsta1dJSHNjNWtzOFBGb09hWmE4N0k0R3dUS0J1d3U5TlphMkJsTXZRdlJXSTBtRGxUdDZwUzNrQlpMMzJ1MnVVQTQwZ3pJbWRKakhIUFg2dk85?oc=5</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>46036.68541666667</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Albacete vs Real Madrid: Los Blancos kicked out of Copa del Rey by 2nd division side - Pulse Sports Nigeria</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 22:22:10 GMT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOT2JJVEVMVkJFWk1RNVNHanlMSVVDeG01UTlJbXFzV1RrdTUtWFNhYmgzNG9JSUhjTkVrTFpFMnh1YVc1bHlMbDgtWWxPVUZQTkNkMVZFbnAtWGpfOEhBOV91NF93UHA2YVQ2Q2xuNkhlck1FcUxiUGJLcUd5RHprcTVsU3BDMjlnTngyU1VTeXAycmRWVVMwQURTVm0yel9KWklLemJoZFFTTmdRTmt2UHhXR0w4YUtlSzh2d3c4VEw4MktLYXRUWkxvOWI0NXhoMmVSdkM2N1JOeWttX1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46036.93206018519</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Rayados want Antoine Griezmann as their new star signing after failure with Sergio Ramos - MARCA</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 16:40:20 GMT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPcGFxVFBvUkFQVkpKdXVQakJxUWY2Y0RwNmxZNGh5RGlld2FLb09wQWl1TGd6XzM3U0NRcWRjQ1AxY3QtNEU1Uk5IOVFWQ3pkU1ZpM0d1S1dzWE9xbFNMdTM4d2UxeHNrU3dPVlhXaUcxSlBmd1NRdGsybHhfSXFiRTRRdzZsWUJzSEHSAYoBQVVfeXFMT3BhcVRQb1JBUFZKSnV1UGpCcVFmNmNEcDZsWTRoeURpZXdhS29PcEFpdUxnel8zN1NDUXFkY0NQMWN0LTRFNVJOSDlRVkN6ZFNWaTNHdUtXc1hPcWxTTHUzOHdlMXhza1N3T1ZYV2lHMUpQZndTUXRrMmx4X0lxYkU0UXc2bFlCc0hB?oc=5</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46036.69467592592</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Police: Third person arrested in New Mexico shooting that killed 3, injured 15 - MSN</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 17:40:53 GMT</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AJBVV95cUxPQ3lDanB0RlI1aWFuWEF4YkJma2hrVHRwMXRUVGJZWmEyV2lILXM5MDdWY3JsVWsyNF9mY3FLVXpKX0ZjREhhMGYzQmZBX1ZGZU9FVWpGYzExbk01RUR4ZWdLdDlpM2FiZHhHLVhjVk1ZLWNNRHBEZFoyN0J3MjE0SEZWZzdxQmtVVzBwVkxsaUhxeWVfNk1sXzQzZFltNGVmakp3aHRvc3ZTMGZfQWVoUEN4RUVSaGNwYVE5Z1RsYWtlLUhxcDA1dmdTMEd5UTFIQldVNVJPOXVwVl9icjZiVjhXN3VaN1M1c3RvRm80TFZSUWktOHcyN2hUbFFYRTBwYzNLZm1pamFUQXRsS0xSd2U3M1ozMmlVcWNTbXlRenQxeENTMlhuRE5tVFBKM3pjUElNRXVJS2JaS3pEUlhhY3JoUURucWNYQWc5TVZidlZDcDZfQzJNR1l0cUw3OThN?oc=5</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>46036.73672453704</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Man United and Marcus Rashford must avoid awkward transfer chat despite U-turn hope - Manchester Evening News</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNQ1F2WmNybWJTVUhobzAxTllNcXZoTnkzZi05TF9JRC1veFhfbFRzQzJLUEhkTXQ0dVdjbzVCVE5wNTV4b0VacTVMd0ZrLTRtUV9PRVdQQjV4QURkcGJNOUY0YUU2Vzk2TUNUUEJuQVV5c09yUnV4QWxWcTJCV1dvakU5NGNYWmpYTlFvcWRERUJLcnpISHFaVlItb1RVTzcydGtwSnBqRHoza0JDMWxmTEhkZVB1SmlUNVBrX2FJQUYwZ1B4Ni1sTmxqb0Y3dVBFVXpwOXQxTdIBwwFBVV95cUxPZXdYYVVtS1VoeXhNUmFHVS1hSXhFOWRVSDBmSkVDR2t2ZzNfTklFT09ZclZhWF83SF8zTnVOUk5YeTVpY3pBQ0d2RGpveWx2ZVQ4ay0zdzJrNExCMTB4OHJzOUFUMk9mOVJWcG5pWlVIX0ZYaVZwNi1IcjVXOEhiVmJKR3RlaFg0ZmNMM21vQjgxTGJkSjJ3Z210OFZpSVBaSTVMbjg0Z2JtWmFNanNQWFZtaVpmOXQxQ1UzU081Z3FnLUU?oc=5</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>46036.625</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ex-Real Madrid &amp; Brazil player Robinho's appeal to overturn nine-year prison sentence for rape rejected after majority vote - Yahoo Sports Australia</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 17:29:58 GMT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE81SDZ3d0hiOUFGSTR3Vzd1OE5MZjh2Z212TTBsMEFROXFnMm9Mam41c1duYjlVZS1fNVN4RVh2NzVycURDbjBJaElTMHJOZkU4TTA3aThDVmtNSHZ0WnlWX1dYb3c4ODJnZEZSRlhTeW01Nng4V0QzeWVNVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46036.72914351852</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Inside Marcus Rashford's incredible new life in Barcelona: Man United star is in his 'happy place' - MSN</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 05:11:53 GMT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxOSUZ5am4xYV9ial9MT0xRZktRanNEWUxvUzFaYTNvSkVNWG5nTHl1ekFhV3lpZmc1WUFGR09FVmNhMERHTkJhd1JKbnpYMnNQaDVrVm9yMDhQdFhSNFJFQ1U0VXFwelB0dDVHekpCbm5xaldZN3AzaDE5MkdfZi1ORGhZOElmejdZN2xZYmdtbDFCUUx0TWFZUDU0ektqR2V6VktscjR5MzhsSEJwUWNaWTNKblZHLXpBOVJ6UnhKQms1M2RqU2Z0Rlp1eHVYWFFZRm5FclY2ZW80SHI0bUZMb19nUjRFRldBMU9ydEd5ZnVpRERSNWZsVFQ0SkNzUFlIZWZWV01yZ29PMGZBY3R0NnR5MW5QRzcwZTloTUlQbmMxOEVPeUkyeVB4clg2N3FSaXZ5TERBWVc5RmhfVDhDcXhvWk9DOXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46037.21658564815</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Clippers take on the Raptors, aim for 4th straight victory - FOX Sports</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 07:03:44 GMT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQTW4wYkhrbXFBYzFDRVFsQllnckgtQ2FJcTBNNFZrV2tvb1IxcUxyajlPS0JybFREVXZnaTBWb3Vub1N3WW5weFdHUzlkTDRtOEEyenNDSG1jVHV3azNTOWdlRjRHSGNRZlQySzNKUEJLN0VNSERnRDVoS1p3LXlfaVdGQ0w4S0FoajVXWjZjSlNkRVdUbVZQa3RGTEY?oc=5</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>46037.29425925926</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Basket rumors - Sportando</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 03:21:01 GMT</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE1nRUpHMFZGTzN4aEZ1QWJIUEpBbWpXbWVsd0FtQ1RNVTRVTDVVNS1UMlp6SVZ1cldzb05aN2FPY3RxUGgyWDVDeTVqNmJGUjhJSDA4RGxDUWRhWlBwYVZ2c3hYRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46037.13959490741</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Punjab News: Ludhiana Court, Moga School Evacuated After Bomb Threats - Free Press Journal</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 16:34:27 GMT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOSmdIUTBsRXhrY3RjTGItX1kxNmo5TDBVQWhYYVhNWVZxb3B5MmRfV0pOZHFIZnRYdDNxZkF6YXdXMy0wa3ZuZmhhdmplSkxYUzU2b2ExY2VPR284X3pncDQzZ1dYZ1VNMEVVSWpYSWRGNFNrLS1sVTNqaWZDRWFGQTdiSlBPbWhjaS1qVUdDbC0yQU5UWmdyOU41RDZneFBTMWFCeFdweXjSAa4BQVVfeXFMTjBiU0xqUHhkMlU1SUppUm1NVXQtckZNQ0s3SklMbUtlMWI1VzlITFlHREZITmRZWG9kSTRnckd1VDA0allJdnoyTGFuUGRZYWxlUHRneDdvX2l6NjdNVUs2WHpxNjRFdC0za3BuOEZIekJoSlA3TG81cHZTMTh2MWtEV1lpV2lyeUdtQU5oS1hfTkQtQ09hd1g3Nm1NYkhaS2Z4a0pzdEZBNE82N3dR?oc=5</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>46036.69059027778</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Xabi Alonso’s “nursery” outburst revealed as Real Madrid dressing room turned against him - Nogomania</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 14:51:18 GMT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPQ1o0Ri1QSlgwbnBmR1BYaVB0QWg3Z0xwaHVTZm1reWluS0dEVWFXdXlVbG9JY2drbzBDcTFJRkgyWTJfQ2lGZjN3RlVScWwwcXc4Q2RMZUtJbmhJejZ1cldwdXJFbmo1N0JFZW5QNDlVNmU3MGNUaXExOC1iY2ZCemlmN2xPLXJVbWVCMTBkMWJSMVNER3gwUnhSVDFRamNGek41Vy1rNTBsLTVrNE04WTE1czU0ODQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>46036.61895833333</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Civil War Erupts Among Traitors in Explosive Episodes of The Traitors - SSBCrack News</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 20:41:12 GMT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNUE9lSGk2YzB3cDlCc3lPeEo2d2tubU5oNjJLRmh3aktRVjgxT2ZTYjlwNG55X0J4LU9yd2d5VEdEY19Qc0QxY0NxN0Q1LXVMTGIwd1BWQjZ2aWR4ZzdJdzE3TFdDX01UMGlpSjEtZUNHYURPWWdmRTFuNy0xeEE3c1VhcklzdlhoOTh1Y05LLU9lNUZaNmZEc2lSNk4?oc=5</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46036.86194444444</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, Spanish   language</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomba" OR "amenaza de bomba"  OR "explosión" OR "paquete sospechoso" OR "paquete desatendido" OR "explosivos" OR "explosiva" OR "tiroteo"  OR "puñalada")</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>¡Bombazo en México! El club de la Liga MX que quiere fichar a Griezmann: "La oferta le agrada bastante" - DIEZ.HN</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 16:11:56 GMT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNNTVXbzZtNzRTTGIwdlVncVhJT0FRaVdrMTBfOFlWRXQtNnNoanQ4VjVaYWItZW54aHE5RFB5dFpGTEVITWZDUnJuQ0UycWFfVEdrdFpNdlJMZUdZQl9PSHFDc3JDUjZfWjBXNTdId0JCUzYyVTBpU3Rva0tzWlFpVFEzSmpqdEN3cHlkRkxHbWRuVnlId245Yzc4WWw2RVVYZnFuUHRuTWY2V0VWaWZ4c0NB?oc=5</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46036.6749537037</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Maliki Sharma named as teenage Feltham street stabbing victim - BBC</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 21:41:01 GMT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFA0Y01hYVF5TUhEeG10b2JhUTdxRUowcHhwYmZaenVoNnlrUV9lam1WRnRLTTRqT2xwUWdQZmFuSWtndFp5M0dFakZwSEhLZ054b0pXWXlwMDJXQdIBX0FVX3lxTE5nVVVHV0VmdU13QkVWbzVEUHRsNWJYU3NWSFRiR0FtUzQxdUZoY1lvS3Z5ODN0UHpwSWhJTmFidDVTQm5FbThhcWExUHpqckxtQXYxN2Y0Uzd5SEZISm1z?oc=5</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46036.9034837963</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Teen stabbing victim named in west London - Rayo</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 05:22:37 GMT</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBNVVVlTTJtLWx3TkZwYzZBcVlaVXhrN0Vxa3ZjcGJDUlRLOHREZkZCeXRtSy1VU2RPZkphVmcwVXBOWnFBU0NpSXRxRTZfSm1Sd2hYeWFRbjg1empWSllWVHdKV2RMa1V6eUlIdTU5T0JsY3dWcW02eVdweVNyajQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46037.22403935185</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Sophie Turner says shooting new series in London felt 'invasive' and close to home - Yahoo News UK</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQZ1AyV2JWeU1FTGVLRWVlUWl3bF9uLU41b1hjVUNtRmpvclFieTdEQnlRZ3V2bjlyNW9ubjZYNVlNbWI4c1phM08tSTlobGJoRk5OZkZHZDAwaTZ6ZV9ZUUpKMEpxbzdFOENYM0VrWnFqVlNKTVA2YlZLVWRyaVNsQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>46037.20833333334</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026 film and high-end TV productions shooting in the UK and Ireland: latest updates - Screen Daily</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 19:29:05 GMT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQZmNMRTBhWHdsbFo0WHUtenBKUWJ0Z09LVVBuTjVUb1R6dnYyV0UwSEluX01NUXJuVzhuVlZCTUlHanpOQ0hpT1p4N2xGSnIyaEg3eGRKQ3BZVlJWT0hPREU4dmd2azc2VGVhQVl2emFKVmpENnNrT3BJNGVDY2xlNDVSUV95dzdPcHFtOHhqcG9WbUdYYU9odjhUTHp2b0dzMTZ6Yzh4U1VGNVVfeVl5RmQ1eDJpLU91MHlMUS1kZlZNNng3LTE1VHNIb1o?oc=5</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>46036.81186342592</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Girlfriend recounts victim’s final moments after east-end stabbing - London Free Press</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 19:22:23 GMT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNaHpSdk5YVkNwZEVMdHVabUpMSDRUVFRmWUk5VDNnNVctWTFBTVNYcXpBNXF6THlRdVZqeTBrTUhVRlRkYXJUREtqcV9tTVhGNkhpTzVqVWFhemcwWGREanlTUUJyeDRBeWozR0J2QzJUS1BQSVVnRXlnNXdITnkyY05JMElDNXJucDRkNUFzbzVTZlZscnRoTEZ0V09TWklMYmJJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>46036.80721064815</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Woman dies in police-involved shooting in Burnaby neighbourhood - Global News</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 18:42:54 GMT</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQRDBDTHdtcVFkUzdlaHlETDVBMkxuOXZkbUpDSFBfMklRWFpRNG9ab082QmVCakNWYkowQ3M2alEyamZUUkRKOXlKT29Zc1JvZC11cS1PS1M4VkFrTEpPQm5jY3dwVjgwSFZTaHJhbk1jUFEzNUg2Y2wwcnJpMkw3cDlrRGNNM0RyMlhqSnl3?oc=5</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>46036.77979166667</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>One person dead and independent investigators called out to Burnaby - Vancouver Sun</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 17:05:15 GMT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9rX296cnY4YXhtdnBPRnIwZWJKT0dDNkZDVUZwT0p6S01LVmRxSjBXd3JiYXotNktJdEhPbElZT3ZrOHZJWmZEMkpnSlcwUnVvbkZrMEtmNmE0c3VZWU9hRFBYakxVRTFfcFNnNlRqWDZ4NDM4eUZVRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>46036.71197916667</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Phone search histories examined at Richmond Row shooting trial - London Free Press</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 22:53:44 GMT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQeWhsQmpJS05YQ2dReUNPOWxwdFNHRDVHc1FOdVF1YUdPaWJpWEFVZU5nc3d5SmRrLWNZbjVfZFRwNFBkN2RERHYzMWZlbUdaZTB1Y3JMN1J4U0QyamRIUTd4aXBXcHNyT2hscHloQkZCblBNZHFYYVhvbloyNEpGLVpWNHFyN3llNGl0S1JtZU0xVkhUb2l2dHZFUThvQ00?oc=5</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46036.95398148148</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Renee Good’s family hires same law firm used by George Floyd’s family to investigate ICE shooting - WWBT</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 20:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPeFhsOWVJU3B6S0JEVEIzZnZEX25ZSFlQSnBOU1pOOEVXYU9ZNUhfY0hPZ0lDZHVhTFZiN2JHRTR4OFFNbzI2TkhsQTh5Vy1iQmN0QllabGpsUy1naUY3WUJnUW05LWctU0haVHdHS0RjTi03UTViZktaa2ZKakxUNU1JNEdEeC1fWWhkaE13eWl0WWVPSE9zd3N2VmtPaHRXZEFHdGE4aWFpeGtvT0NfY2ZRbm96TXduSUZNNEFiV2Z5b0hEczVkd0RISlJCUdIB4gFBVV95cUxQaDlJQzRTSnBnTkloSmpuRWt6T1l0TndYeUt2Nzc3Y05EMzBuZ29UY3h3RUNmUXUxbHhWbmFLVVg0M2gzcHlYcUhMczUzNzRndEhETXd2cWRfNWZtdVhlSnY2bzI4dFMycU8wc2VHZ2N5THVyQUtHX1JITmRWX0hwcTF0N3FJdVN5NzhUdXJ0eHp3cy1jTl9QRk1PWHEwZ013YkJwWF9BTTgzR25hdlFvNzNyQ190UjNUaGxqRTNvV3VOWFAySzFxeEJkVjNuUV8wMmxfdV9ZYS1pcWtQa3k1S2F3?oc=5</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46036.86458333334</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Federal lawsuit accuses London of censorship, targeting independent journalist - FOX 56 News</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 14:52:37 GMT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPWHU4aVdVQXY2Z0FKdl9ZdVFDN3B0dm56ck1USHZfUlpmQWxHekRjNVVzQjVZVXVKSWNTZmMtWjYxbXVoYjRvc2J2ZUxOSFE5aktaYjY2TzhPbzZ2N0JnakN4VHdBZnA0b1RILVBBNzMzYWlYd2dJWjRoOVMya2hMWENPZDNSVy1GM2dTUkZZc19RcEk4bi1Vdm53eUlWemM4OXJVcE5HbDhmUEc2ejdkeVZ0TmdBeGVUdWfSAboBQVVfeXFMT1h1OGlXVUF2NmdBSnZfWXVRQzdwdHZuenJNVEh2X1JaZkFsR3pEYzVVc0I1WVV1SkljU2ZjLVo2MW11aGI0b3NidmVMTkhROWpLWmI2Nk84T282djdCZ2pDeFR3QWZwNG9USC1QQTczM2FpWHdnSVo0aDlTMmtoTFhDT2QzUlctRjNnU1JGWXNfUXBJOG4tVXZud3lJVnpjODlyVXBOR2w4ZlBHNno3ZHlWdE5nQXhlVHVn?oc=5</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46036.61987268519</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Yves Saint Laurent Beauté Pop-Up: An Immersive Experience at a Famous Paris Club - Sortir à Paris</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 19:42:22 GMT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxNNTkzVFg1TjIxRTMxSDNNcHJsLW94djlrMkxLcndXZWNSSlQ2NU1rTklCRkxnZFZhbnltY2diUVVRTE11LVhTU2NLOFdYRG1Dd19kVTBERkhFTm5ESDV3THBnU29FVjFjX1d2M0drN1ZmaVFqNkd5ejNvclhnakhUS1VaSzB1WU9KS0MxQjA5NWNVV1JfMXNHcHAwVElpOTdvcW5WTnVaQjhkMDQ5NGE1bXlpUk5fNVNBQWg0amZWbUpIcnliWTA0dTRCRFVFcnBmWUVzb3NSbHczcEtQalFpRWFuQnVTRDFpNEdqN1dTRWpLX0oxSmpwbFg5bklHTkl2d3Fqcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>46036.82108796296</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>How “Emily in Paris” season 5 pays tribute to assistant director who died during filming - AOL.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 00:59:04 GMT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1kQmVXYktpdXlBdnR1d3QybDAwSDJad2FUQXFzaTRJWDFWVTZKUXZDd3plMWtMUFRsMW1oeTNIQzVKMXo4ckVwZ0YzblBHbVVnQVlnQTlxR3JEOVBpZmlvUlV6LVYxZTJ5QUdZRzdBSnVoMzBIVi1QdQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46037.04101851852</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Faces of American Jihad 2025 – And Into 2026: Backgrounds, Allegiances, And Targets - MEMRI | Middle East Media Research Institute</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 17:34:01 GMT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPMVlLeWhiVlFBV1I4WGVxd2tJaHVpaEJudDNJWEVzdVJKQ2w0THFwUDFRVEhGWUJLdFRyUk9EcDllNWRZZGE4N1I0aUJQMGpLQ0pxNWhUSW5tVE9FdlpodFloX3djUll3MXdoQkxTaGhERTNtdGFoUDlLY2lKUXdZRU1TZjFJRGtqTDJ4QWx1a1NIbFY1OTRtY0FiZXNZSUg3VXJ0WGtORkxabTlKMHVn?oc=5</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46036.73195601852</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>When Sharmila Tagore Wanted To Wear A Bikini In 1960s: "She Knew She Had A Fabulous Figure" - NDTV</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 05:40:01 GMT</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQcTdHa0Q0QmNGcXMzOUVFcWxTX1JrcEczSEFyS2Y4aVlJSHA0MDd5WVZ2Ujk4Zy1DdHRqZm1iYUpzQzhiaGY0d0o4SW1HVm1RUXlscXhoV3RlSElpMlBrYTFCS0lGLVgyV2FMVFJFS0I2NXA0LVhKZWltM21yeFdmQzFSZko3RFlnajV2bnl0TEZJOGNCS0k1Um1jajFKbjZSTEFJb2hmbmd3dk5QTmlOTVBEWF9ZUFhndFkyU0xjSVUyVjJYNzdnQzZkd09md2g2RkJFSdIB1AFBVV95cUxQcTdHa0Q0QmNGcXMzOUVFcWxTX1JrcEczSEFyS2Y4aVlJSHA0MDd5WVZ2Ujk4Zy1DdHRqZm1iYUpzQzhiaGY0d0o4SW1HVm1RUXlscXhoV3RlSElpMlBrYTFCS0lGLVgyV2FMVFJFS0I2NXA0LVhKZWltM21yeFdmQzFSZko3RFlnajV2bnl0TEZJOGNCS0k1Um1jajFKbjZSTEFJb2hmbmd3dk5QTmlOTVBEWF9ZUFhndFkyU0xjSVUyVjJYNzdnQzZkd09md2g2RkJFSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>46037.23612268519</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>'Bridgerton' premieres in Paris promising 'Cinderella with a twist' - NonStop Local Billings</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 21:26:03 GMT</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPSTVMNEdRMDBpbVY2d0QxOHJFRHJxeUx4LUh6RUJzRUxUcW9tX0gwQ09DRmRfRFF0dDhNTURQMC0wMmN3aXpUZl9uZ2VIVHV1X2xlWlp1VFQ4dFNFSHcxb0Z3QkhIRnoyS1otMGJDLXVhRlVOM3NPWnhWRHFvc2pMYnZBSWxURVN3d1NTdS1yZXRIYnA3QlpqTFkydWlFblNRTFlSWVk3d2lRQVpVRUp1LUdSWkUtZWJ1SHdkcmUxVGJvNXJiaF9uOTNBWFA1cjJWVVNlZW92bjk4OUhXUXozVzB6dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46036.89309027778</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Seven Pakistani police officers killed in targeted bomb attack - The Straits Times</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 23:58:56 GMT</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQY29lVHVwUHgzSWl6Z2hpamVBVmVuRFBDeWNFUzN4blNyY1VLU1dJai1obXNUNDBQb2hJdnpKV05tTm43TlhYODlUZmozNkNzSXRwVlFnMGlEQVphVnBOMFdzQUlkRGtRQ3FmY1FrWUloQmJFNUQtTTlOTktvODFlZmRyU1g1bFJRX0lwbDBpTUxJeDVRWDdhWUxTbENydjZHWUhrTFY1VHQ3bk0?oc=5</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>46036.99925925926</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Shooting involving federal law enforcement reported in Minneapolis; two in hospital, including federal officer - KTTC</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 02:16:00 GMT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQWi1VcUtrYkxReFlDMS1TVjNQX3RidzhWRTFzclFpM3ZLaVFXTkxDdmxvbDlOSGZkNzMybFljOXIzeDl1OFVVdjRua0ZCQXkwVjYxVzhfeHB4T2hDdHdMWHpMVzJoOGd5dXV2WDFwcWhQbHpvMUZuUWI5RzA1MmlNZUZzUTZhS3VXNmNEaWU0MGJ3RjZObGVxelVLX2E?oc=5</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>46037.09444444445</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>EOS gym coming to southwest Fort Worth amid explosive growth - MSN</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 06:02:15 GMT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAJBVV95cUxOVDlYajd6WTJUbENVSGQ4VERsbkwwWGJCU3RybDFGaVlrcXdtclFGRWk3YTh2QzJwLUZ0bjBkb0ZKRWVqMlpCQ3lpWUZZYTltX3VBUHNwYkRKaHNoVHJ2czhhSndjYUpyTkgwdEJ2ODdzcUd6R2FBNzFvSnR1YWVRNWR5UWJucVhWZmNxbDltc1RnUGpvNlUyNmRPYUJFckRUS0tpNTUwRW9jdDkwZ1EzT0k4YjFPbS05X19FRXpSVThuTXl0c19HenhYYVlTRVVNekZMUTljX0M5ZktReTZiaVJNREJmT3lMTlRiQmdfaXVHeTlOelBkRTB6YmM4bEpTcnNQbFA3WThpYlVnR3M3X1BVdEpCSDA5d2I2X0dKRGtoU0l6bjRKd0lGLURjTGpST2owLTB4YVpKY0FBVnY3UXVwbHZ0dVhhdFVnYw?oc=5</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>46037.2515625</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>What to know as the Louvre's ticket price goes up by 45% - San Antonio Express-News</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 18:35:57 GMT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPdGtfcnBabjhoYmIzbFlYQXV4V3ptY2duUUdQYVh5Qy1FaFZpSnBxa25aUUlQaGJKSHFqZG5tR280b3BneUp6YTRVb1plcGJtOEtJODhOT3ZTTFh6WWc3RW5RaEctSHhiUHctSkNDbUE3VkMwZWJ3MVVaOTdDUWg0OEFmVU9CZzZXclN0QmNkS2hNMm5KS29MczZYYUluOXZTdmVaYUVUYldIcGpDckE?oc=5</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>46036.77496527778</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>G-DRAGON Headlines K-SPARK Malaysia 2026 Festival - 조선일보</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 01:56:46 GMT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQMVFPMlVEQmVwMm5yQUdTbVp2a0ZlRG9aY2VKZjdraEFieVI3NVJqSEtmSnRycXlmLWt3cTFiNjE3bXkweHNMdEVTejJ4X2RmUGloVXhnR1Fjalp5bUJEOGlLQjhLejIxVUx3bHE0ZDhJR2EzaVhwRkJaWlNteXhnc0pZME1qcm56TDQtMUJR?oc=5</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>46037.08108796296</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ICE officer involved in Renee Good’s death suffers internal bleeding, reports say - KXII</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 21:50:19 GMT</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQckw4TEFBdXpjTi1Ub0pkR3hLVmNOS2dkOWNSaW1UMEZLaGFyRE9YRmRjWXF0RVdEd3JNQ3FRcUNWNk5ZYVpXa21pQXE4MFhhX0pFRDR6cWptN2pON3dEd0JmOU92OVJBdTNNcEJKSy0xRmppRWw4N2lMRkI5NG1rTjQwWmxRaFBRcG1JLUgxLThIYUE4YVRuUjA2RHZ6WDBmVmFvY3VhR0hPaVhjSmJkSkFfa0RUaHVJRnRlY0NQcXJEUdIBwgFBVV95cUxQckw4TEFBdXpjTi1Ub0pkR3hLVmNOS2dkOWNSaW1UMEZLaGFyRE9YRmRjWXF0RVdEd3JNQ3FRcUNWNk5ZYVpXa21pQXE4MFhhX0pFRDR6cWptN2pON3dEd0JmOU92OVJBdTNNcEJKSy0xRmppRWw4N2lMRkI5NG1rTjQwWmxRaFBRcG1JLUgxLThIYUE4YVRuUjA2RHZ6WDBmVmFvY3VhR0hPaVhjSmJkSkFfa0RUaHVJRnRlY0NQcXJEUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>46036.90994212963</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Los Angeles County moves to create 'ICE-Free Zones.' What does it do? - USA Today</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 18:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOSnRFSjh2Q2h6dXowNzFMWVNYYzR4amV3aHZndnpqaTRwcEtLbEY3elpXUDVYN2ZSenhxNEUwTDI4eTc5N0hqbFRXQW9PR0NtcjRFT3k5TFczOEZXQ0tOYUF0Tlo0bWhOcXZhQnh0RnB6MWlLNGQtMV9xTEVQTFd1ZEcyajdKQmh4TExTZ0xFdWlYSllJMzVKUVlKbGJoSlYwZlA1dU05TC1kVjQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>46036.79097222222</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>South Carolina MBB blown out by No. 17 Arkansas. What we learned - Charlotte Observer</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 03:57:27 GMT</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE0zSmRNWGg4bkYxZHhIYTNFMkZIUXI4ZGQ5aEJVMU8zY3VZM3VPdDQ2ZzJtUnJIN3dweVIzYXlqZ0ZLVFRWUkRhMjg3Qmg0UDFKR3hDaUliaS1RSEhiTm1QT0hnOGhWOTZFanhRNVUtRktSRnIyXzNOem5B0gF6QVVfeXFMTTNKZE1YaDhuRjFkeEhhM0UyRkhRcjhkZDloQlUxTzNjdVkzdU90NDZnMm1Sckg3d3B5UjNheWpnRktUVFZSRGEyODdCaDRQMUpHeENpSWJpLVFISGJObVBPSGc4aFY5NkVqeFE1VS1GS1JGcjJfM056bkE?oc=5</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>46037.16489583333</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>St. Louis County Police Investigate Fatal Shooting on Av De Paris Drive - Hoodline</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 15:15:53 GMT</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNRHdrNXFWc1NIRG1SMFZ0bmdJUzNickxRQ09FQVNCNlBwdEQ2Z1dpNFVjNENRSGZLZTVEVm1WRlE3TDlROU1jQTNmY2FIVmdXY0RVYmw5MjJoMmxzWlRqWW5iSmNYMUJOSzdrMDZWd1BoOHUwcUc5N0VxSVNNM2tSTXNtNTBZUzdiSE1pTjVVdlYyZnk2alA5M0lJVE5hZDBMcXk0dGUxeWpkb0I2aWhPOFNTWDE5aENv?oc=5</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>46036.6360300926</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Trump calls Minnesota ICE shooting 'sad to see on both sides' - The Straits Times</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 01:15:53 GMT</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNS2NpOGJHVmRtZmphLXFHM0RlZ0J5LXdoTXpoTjNpZ0pnV0VRN0tJQU9NNTIzYzRCcVB5WlZ2cERoNV9ROEZkUUZ4T3hnbkFhN1JNR0hORzBsOElDTjhSMDhYNnRYUnpzbFlNaGZIbm91TUlMOVp6MktLWEpRRGNxenFEWUJIY2JBUFB5SVpMck92M2F6LURRZ2JR?oc=5</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>46037.05269675926</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>After Retiring 4 Years Ago, Figure Skater Alysa Liu Is Shooting for the 2026 Winter Olympics - AOL.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 06:01:41 GMT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBqS3JLNnpNZzR5bloyVlBmd1JxSk5XRm1uY1RPYnBSeVFzNXRmM19hYjJBaTFHbmk4SlJPTHp1NGNVQWd5aVdoVzBiWno3cXVMcC11OUhOUHE4azhDSnE5M0xIZlhKQTBsRmtDZFl6S0JqZVdyOUxFMDBmUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>46037.25116898148</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Trump envoy says Gaza is entering second phase of ceasefire plan - MyNorthwest.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 16:59:22 GMT</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOMEpDYlN3MHVKd2RxUlJBcGs5MWJGVk1CZ0lwREZCb2dDRGdYZTNjalhSMmRYR3pYVzRfS0dKX1k0ZDRDbXI2cDduOGtYc0pwWnc4UGh4SkN0dVV3Z1FTNUdLeXlCUDBnRFJPcWZpZTZXYUhSS1JsbFMwRmwyQndCVU1KdlBPeU94OGFDZ0l0OUl4VWpRNVl0SThtUTZCbzMta2hONEE0NjA?oc=5</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>46036.70789351852</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Weirdest Sports in Olympics - Go2Tutors</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 15:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE90UFNVc0pHY0Rxb044VGF3ak9JYmdNb0pLOThwMmM1Z0NxT0t1MjJTc0FOTzRYb2ZiZ3FTeGQxWnZHVEg4WFB0WXN1MnJkUFhvNkhwc3VIWGowNkVCaV9J?oc=5</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>46036.63194444445</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Lens Challenges PSG in Ligue 1 Title Race - footboom1.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 06:01:14 GMT</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQVHQxOXJkajdESHQ3S1duOC04YU9JV1l6NlZEU0lyYUNzcGx0RjRfUGNQd2VLbHB2azFMQnJtdU9CcXBTWkRyV3A5Y3JOSmlnTkFCS1BpMEh2MXhSVXd6RlZGUTZpV1NOcnhSUlQ4azBaU3U4MlpQUWFKY0UwNDRkbVNJNkJsZW1KVVRfVUt4U0daNDdmLTI1MFFMQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>46037.25085648148</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Memorial plans announced for lone survivor of 2024 shooting after unexpected passing - KSLTV.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 05:13:07 GMT</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPSmQ2V2hVRi1EbVN1ZDg2Zkswai1ud0Rpbk5FdkgxMm1oemprT3RDcDcydkozRlZZM0dQcW5yRngxdDJGa05YVlRqTDRwTFhWdlZ6ckpnT2VyYzBSb3lIRm16MkRRMjNIdXBES3V0SkZOSGRnM2xhclNVUDN2bFI5UlB6dnRyNFFscEFjVGcxN3JQYkw3T0tGaDFhYzlDMjNkOFFsRHFwMko3RVR3QVpaZkZucGdONk5NY0dZV0Nn?oc=5</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>46037.21744212963</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Red Star is coming to Milan, "We want to protect our court" - Olimpia Milano</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 17:04:37 GMT</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPZ3k0WUU4YW1mOFdaSTBjSWM5NWZOR2tqVW51cGVtbkl4MFE5UDNNTm9tSWE1UTFrWkhYUnk0SGxIbnEtcUpXZERPR0xrSnBmckYxdkRYNFJCNDVLZlc4a0M0UFBrd0RlQ2F1dVg2dlFqemhuQnI0R094em0tMlJ2UVUySWtpWEZIelBGTjNpbmpmdVJY?oc=5</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>46036.71153935185</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>His service did not end, it changed uniforms. Josh Sweeney’s journey eyes 2026 Winter Olympics - KTVB</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 17:34:00 GMT</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOX2ZxTjlhVFpmWTQ5Rko3MG1EOVNUdWMtZ2RaTVNkdnV5a3N3bmpCaTVCRnlsSlBLMW8xSTZtYkpaR09SU2N0alp2cG9VYVYzMGVzSzRhMG9weUFUTmZ1cGpBbTNVSXBLMW9WZnA2SmJMNDRaa3JVdWhFVUpsVG51cExFV2RfbjdSNU5ZYmI3clp4MFJsM0hhb0JKaWdEYTd0Y3NuUFZDOE16ak9ETlU4ZVJtV0NVN19UbGZJb205WkQyUjM4V0NmV1FKZTZwRVJPV2t2bkxNM2YzZGVPMHZqcmZnRUtPRWdiN0lEYmc5NGs?oc=5</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>46036.73194444444</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Greenland biathlete pursues Olympic dream while anxious about ‘terrrifying’ threats to her homeland - WJBF</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 14:27:49 GMT</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQRzh2eDZrNDIwUTdPNDVvTVh6b0JXTDRoQWRJaXpacFppX0c3MEtUai1tblMyS3lydmcwd3cwenNJVXg1NFl4eFNZWG1nVUtIMHZxeGxHVVBocU9mdWo0ZXJ3Z09KOE5JQWR4S2dSS2IyUUt0ZnZjZnhYSnFreGxac21IcGgtLXAzOVA0dzhVM0NYN21RaEZSbUFUcklvRnZJQ3lNaEkwR0dQM09QOW5qdEhpVzNNMmJ5bERjeWRXSlh6Y0x6WU9pX2xmelZiN19JN0xXVnRJNmFrTHfSAdsBQVVfeXFMUEc4dng2azQyMFE3TzQ1b01Yem9CV0w0aEFkSWl6WnBaaV9HNzBLVGotbW5TMkt5cnZnMHd3MHpzSVV4NTRZeHhTWVhtZ1VLSDB2cXhsR1VQaHFPZnVqNGVyd2dPSjhOSUFkeEtnUktiMlFLdGZ2Y2Z4WEpxa3hsWnNtSHBoLS1wMzlQNHc4VTNDWDdtUWhGUm1BVHJJb0Z2SUN5TWhJMEdHUDNPUDluanRIaVczTTJieWxEY3lkV0pYemNMellPaV9sZnpWYjdfSTdMV1Z0STZha0x3?oc=5</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>46036.60265046296</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Man with gang ties arrested in connection with double killing in Salt Lake church parking lot - KSLTV.com</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 15:50:42 GMT</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNbFZfZGJIVkxWNmhKazc0VGJkaHBfbVMzT2pST09VS0RESHd1RjJBRmVPYWY4aXoyTGRKZ0owbHZmWlNvejkwMm5UbXNKV0lyTlh1UFNaOWFUYnZzeEU5cGFtb29ETU5OcEIzSGtsUzJpTEV4NnVOS2lrU3pNM09DbVBYWDRhdkdtUmt4TW9PWGR6WFZ3MDNHQXhWT1F5eDNFSWFZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>46036.66020833333</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Letter from Brussels: A Chill Wind Blows from Trump’s America - Balkan Insight</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 07:10:48 GMT</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNWm1iVGxrSmV4czN4X1Q2Wm9VOXc2bHNhTEZ0WGNiQVlXWHZNRG8tYlR2M3Z0ZFg3TzFickltaUMzb0dFTjYweS1hU25xVnFMMVUzNV9XMjYyOFduTm8yU2xybUJkS2otWFZpdXlZNHZmNjJaNEZEYXRFSUgxNWNvaVI0bl9Eak1KSkZEeVhZZnZFZXJzVE9mNXhsTk15QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>46037.29916666666</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>France farmers protest against low incomes and EU-Mercosur trade deal - Jurist.org</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 21:20:16 GMT</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPNTFYVmJaeTIza0tGTG94aFVFRkIzM3NQVTVJY0xNeUNqQl9zY2tBOU5TSXN2d3pVam9PRHdOOVdKMzJtNnZXcjc1YzNYalhqaGMwOE5ZRk1LaVZhZmQ3dFdlMGMwakFQR1JsRVVlMUp2TDZLSGthYzRFcnl1MEtrdTdGWnAzNXRYNXhkRmRQaVY4OGNkT2h2Q2w1VldINFBwSUFRV3dLYzktUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>46036.88907407408</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Brussels police officer injured in arrest of suspected gang thief - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 19:09:31 GMT</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOUTFmV3Nya0NsVTJUb1JjUGxfM3A3V1FxS2w5dWdfQnpNQ29FTTZDRjYxUllqNU56RTB1SGIwczRWaVROYkZxUlNfWDZLdFJFUnM0ZjZEc3M5VXFqTHRYWG9jWGFXb0JYUmhzdGl5OXhrUFJoY3FVcEZzaEhWMkVLcXVLZTQwZGhaZXJ4dGpFZDBLXy1pcDRuTzJjU3VGNVRfNUVpM1RR?oc=5</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>46036.79827546296</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Cyprus Police Deploy Schengen-Linked Tablets to Speed Up Border Checks - VisaHQ</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 23:14:02 GMT</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNaUM1QUo2UjVGQkw3UDBYRkJCTVZRZ3NFaTlla29wcDl6eVBvWGpYVU5ZNUVLNUo4bkxUYWZIRlhDQmE2amhjYnhtN3dpeXVRX2lhZWtoWEhRMlhrbGVUdlVTdk5VT3lvVHpFY3diYTB0ZklUR1o0Q0gxeWxEZXR5S19ObF91WUEyRVJ4S2wwSzN3R1dxUEtiazFQSUR0ZUFMbzNaNnQxTUNsMzkwbkczN01RVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>46036.96807870371</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Extra funding approved for ANPR cameras in West Flanders - Brussels Morning</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 17:52:21 GMT</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNb3N1dzlYZTg1U3JKTzVxMDF6OUdWT243Wm5XNFBERkNZbmtTNS1UNEVmeU0xOVZ5ZmREemJVcWFjVGpzUUlBSkRnV05fNk5SRHhhQmVvZF95aWpuMEFFdFdCTGNvNEVlYTFlMW00cWN6RDV4N0RWWV9MVHJIOE0zSEFMUFZaLVFKQ1dqNEJKSzE4S1dMb2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>46036.7446875</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Huge rise in informal talks about work resumption for long-term sick - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 23:20:25 GMT</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQM0JqdXFTS2NGdFM1RWJINGJhNzE3NzkxY09EY3JiU2d5TDFRRzVrc1VxRXZyX0ZDUGxmVlkyMm5CMGQtdE9hY1A4cWV1aGlSUkxlci1IWk9oZGItUXdoY2FDNVh1anFOdWNWU05VZUFTUmN4bDg0Y1JRcUtaUFYwX3NPcTRqR195ZjJVYjE1R0dkZHFyUjEzanJlQkRQWFNSRy1RR3kzZ2Ewdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>46036.97251157407</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Brussels Weighs IRGC Terrorist Designation As Sanctions Debate Intensifies - NewsGram</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 20:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOU1lvdWdMUWVyWE5MX3BYbU5kUGFDLVp0QmhjNWJqNDNEWVlZeURiVDhHSFhZWERJS3ViLUJyVU5Ca0tva201ZWY4cUYyZUQxOGNLRzk0RDF5Y1hQRUtfeXQtLWhscm1rUFFGOUU2dGhXREdZNFB3bUpsY3E0QkpOeXVmRWpRTjBzZFFOTdIBmgFBVV95cUxNa2Zmdk1naUJoa1FDQ3hTZEN1ZEZJeUNPcEJhV1NkYzRCV2ZtU2lXWGQtNHRlVVUxVThqSnViLUZNU3RsSHUwaWxDc3ZPVGpqVU9tTDg0Z25NSXlxLTdtdXRXR0UtS3FPaXhDVjl3ZHlhYm03Z1N5RW4wTXZNeGNkcGZJRjc1YU5DYXhINUdtYVdPRUg4QUMzZE5R?oc=5</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>46036.85416666666</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Maastricht City Councillor arrested on terrorism charge; Tied to Atlanta KLM incident - NL Times</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 18:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNV1RPTGJnWVQ5d0NkVmRUcU51ejJxamRIN29QeWxHWkVqTDBYLUR1Ujg3aFBOTkFrUDhWY25EYjl3WGZkU09LQjJualNOeDdPMnBqWVJ1a1pZamIwTlE5NFJBZXRHd05UWWM4R1B6UGJ4STgxTXZtM0d2TnVBY294TFFHQWFhMzRSX1NMVUFlX2FTdGtJXy1OdERGeEYtdjF6ZlVhYkRmbnU4OWZz?oc=5</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>46036.77083333334</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Tienen shelter animals terrified by fireworks during a former protest - Brussels Morning</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 15:42:08 GMT</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPOFhtbUE3dFpiYUJGbklSQ3hqLXFJMk40a0dSU202OWZ6SmhJejh1VE9fR1dkMVBWTlZ6cWFLY2dVUVctbk9xb1ljZk82VlFDeDBwSVB3TGNEUlJieVlIb0ROT0RyZ0Z0cmpMcTFfaG1OU2x6VTh6eGN5cTE2RjVYTnJaY2JpRXhETDMwQWtZVEFGMjF0Z20yVXU3dV9BM2NkRGtrQWw1NA?oc=5</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>46036.65425925926</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>4 Men arrested in Hainaut after Uccle Machete kidnapping incident - Brussels Morning</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 15:08:10 GMT</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNM1FUbXhMRVlVZEFZYkk4cmQzd3pHWFJ2TFd1QVZ3bnA4WUtqUmVJNnYtcTl4Q2d0TlBEb2dCTnNRLVNPX2xheE5xNGozNE9xaENXUmwxRENCZkVrTDY5cFhtY1F5VkJFV1oyXzB5LV9ycmtsYUdENWQzVS1tLXR1M3JYenowbkh0R2YwaWxIS0lMa0M2Y0htT092YUVRMVN4Zmc?oc=5</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>46036.6306712963</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Molenbeek metro station to shut early tonight due to Morocco match - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 22:30:11 GMT</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNWmpMa2JicnZKZGVtTTktbV9xOEVmaU1ZeGZGaTF4RDM2a25IcWI0bkxYZE5tWm9WS3NubFVET1Qwa2tPdFA5V0pYUkh3ZEVmZ3Awbk9jVXVyWG8tcXZKZUF3TmNhQnlTcVFxdnlTa1hvZjNLS2Q4YjNQdXZ2SlFTY1MzMnNzTDJ4UHQtSkxkdEFxbnZFQ2lMNTNtcjRfUHZsU0p5X3ZRcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>46036.93762731482</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>All checks and balances are under political attack, warns Belgian rights league - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 01:53:12 GMT</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQWkZUU3JTeGlVRGJHX1U2QjdIS3o3ZW1HaGRkVVJzUzBjVzhDZ1BJb3BobUpqX3ZEdmlUZEpqanZiOUFld1V6VVZvb05mZWxQMWFiMDBFQjdhZTlrcW5uUVZyX280dmRDdUVoUUxCOVlTdGdidDBJaEFFS0doWk1obU1KZ0pZam5FYkF2bnBOV0p1dnU0SHp1TGQzRTRBWWtuU09CeU9GOFFrRHlYT09xakhMU3Z3Y2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>46037.07861111111</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>5th luxury car stolen in 2 months in Spoorkin police zone Pollinkhove - Brussels Morning</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 17:27:04 GMT</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNTW54Z1dYVjV1THBET2QyOFRQa0xYWW4taHptaExRek9KaWVFVVc0SVIyZXdRMlZ4Y3kwWVhub2w0UjlWR2QyOWNab3daeC0yT3VHNkU4b1pHQ3BHdG5qNTNFVVZmWk5oMHhyMWU1WVhMTEpxQzhfNWZKWGowMGZOVHI0RzZ1QWVLT1JKMkFCYmxfczhOcEZNN2xLMjg5bTJDVjRzRldJaw?oc=5</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>46036.72712962963</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>BRUSSELS IGNORES THEIR DEMANDS: Truck drivers from Serbia and BiH announced a blockade of all border crossings with Schengen countries! - Serbiantimes.info</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 15:06:31 GMT</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxOWl9ub1BxUDZCdUdOUC1lZ1dzT0ZULUxfcmJNOEFnRVgtV0FUTkh3aFpvQ3M2cWJYZE15SThhUXNtNTJBdjFkNU5uNUpLWGFNLXAtdk10NnpnR3d3REp3SmZYb1dEWV9QbS01NEx3WE1iVXZyVV80N1UwSVRKTURiZmstcE9VLUtGQ1lIUVJJdnhfVlU5TGNQVWN4bThlTEVJMUVhUzFGYmM3OXVJSDN1VU1fRDRxSHpYVEUxbVUtUkdvaFlSb3E2TTRQbEx6TXpFbFdiRkNXcG9pbGhRUmpTcWpfWjFLaURXc1hJSFk4SUJOcHA4aWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>46036.62952546297</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>India’s election system sets global benchmark, Telangana CEO tells EU officials in Brussels - The Hans India</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 02:56:44 GMT</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNUFVzR1N2WlVxTFhjdkZVNXdKeTVGc0U3YU1HbHhYLU9hQU1GNXgtWEdsRWNUd2pVbkpCWEcta3YtTWgtTWlfdm1paHhyeXVucXdqRzVIUHY3NWxOX05KbGFzOGlsMXluNXdtS2ZVcXYyWmdqeGhvTVEzWGpDSXl2VWppWk82VWVTX2ZaaEZfNUpxWHN6WjItSmZsTFlfMWpxOGNMdEdOajVhNUNZZUtZRjhGVnVJS251OEEyMjBBMTQyWTlZb0VQa0ppdEhDY0hJTFHSAdcBQVVfeXFMUFBwRTN0RkdHLVB5Z3BrY3NCRkdaeXJEZUdUbFkyM3lGSWZmY05Vc1ZlMngydjRMbWxHcUs2R1hZRlFKRTVmOXZ4eF9YMlkzd1F0ZE5xYi1XRzVDUmh3M0lJbFp3REdPa3ljYkROc1BTZFpTenNVMnBDcTJMQmtvY1dlekJfSXZ3X2pLVE5rTVplcDJiMjZPSGNUblVQUEhTVy1HUGtSMFlIb1BTX0VwX1BxREd2THRHa2lXbFhRSlJHZFhBMEp3dV92d1oyMWpXTVU1NVFUTjA?oc=5</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>46037.12273148148</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Thieves Target Wrong Victim in Cryptocurrency Home Invasion - Live Bitcoin News</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 22:00:07 GMT</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOLTJCNlBGcWw3X1U0ck5VMjFRZXliRkpEbTg5X3FnQlZFTGc3YkVKRXc1SDQ5R3RGc0RpY05LSEk2aTEyZy1TcllZWVZwZ1NHQ0tYZXlxNVY5MFc3SW9HemNObUliUVYwR29qeEloZElBamgzWHpRcFYySS00bUNLUjZ0X2lDaVJxTDBKVUMyTTJMWGxLTW9j?oc=5</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>46036.91674768519</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>What happened overnight? Police blotter report for Wednesday, January 14 - Newzjunky</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 15:00:39 GMT</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPLUFsTlBnN1RVeXE4X1ZsRWFOV05UVkpNd3I1S19YVHkyVzhjbXJYZmwxNUZJN3lyX2NibUh1bGJLUGJMdWRkdC1zRU9xaUhDQkUwZThuM0lXR1ZUVHM2Mzl4RFFRNnJRRnNqQzhFM0thTnVueXBZRmlVRFJlYzdPeEF1X1U?oc=5</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>46036.62545138889</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>France Bars 10 UK Far-Right Activists Under Public-Order Powers - VisaHQ</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 23:14:03 GMT</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQTm9KZEtkbDFWYVFVVlJVNk1GYjBnakdEQXcwekF6eVV3UlF0akFJVkhIWGlpSWZhZnRpUG5vQ2Jla0Y1dXhuTlEtOHJ1ZW1jYVVsVzU1eFRHak9ncnJKOWRQU3A2MGtNREhPX0J6bmhaZk9NRXlkTmJ3LUZPbGo2dVhFU3JVbzVZRXdOalhfSWJVekdQWUlEQktmVzNMSnJvY0hXcGFIWGtNQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>46036.96809027778</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Eight years in prison for raping his stepdaughter - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 01:21:04 GMT</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNdVQ0SldYZ0xkM2U5TE5QVEdqWlo3Nk9BZEdJQVhPN3NDMkVqUzJfaU9Mc0ptSERaRDZEQzlRNnZWUUFvOUJRVWlzaGxwQU9SYk1vdXJZMEd5bE1GMXM1d3BPZldZTjBjUzZMb2Q1RnRwYUY4RFpxMnN3T2tsWFNvSTc3Y2pPNGExX2prOHRIb0M?oc=5</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>46037.05629629629</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>French gov't survives no-confidence votes in National Assembly - Xinhua</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 17:56:15 GMT</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9Yek1BbFZKMVZHSE5hS2d4bTVaNjFVTnBGcVFoVzRIOTZ1OVlrQkwwYU1mQzEwSDkyd3FTUGd3b0NrOFpSdzREb3ZubTQ2MVZYSTIyQzhTbnJFd0l6c0hKZ3hFRVhfS29PeGstUk9fLUNwMUphZTdBU05VMWI?oc=5</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>46036.74739583334</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>IFA to join Mercosur protest in Strasbourg 14 January 2026 Free - Irish Farmers Journal</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 16:30:54 GMT</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNdHJ5bC1XVTRMdnVlbVdETnduRTZvT213REdBSzJ1cUNQMzZrcldTU1NfbVM2MHZCMmotakZETU5BN0ZQMHlaMnNHcWp1OGZvdTV0ZHV5Y3RfbUFFU0JWc3pZbkpObjNkWUFjLW5YQ0JTbWFfalk4R1B0T2xvclBWRjdKSEJGTDBZYWN6UTVnSTVaa25oWUZlNg?oc=5</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>46036.688125</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Genk converts roadside verges to protected status, reducing waste - Brussels Morning</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 18:07:47 GMT</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUXZpalFhSjlpRzUwa3pfQzFCSDRsemhXZmJTTEJFNEwwVEZqRFFkcmd4S3RGY2drTzhoUDd1U21MZzN4MkJhamZEODJXRWw4Mmp1Z29vYWlpZm9xN0ZHYlpBeUljREtLYUFMbk9zbFRQaTY3a3AtUlJvdWc2dWpMY2RLZjd4MjJIZHZ1WXR3S0lGZTV3RmlKME0tY0tmWnow?oc=5</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>46036.75540509259</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Beachcomber discovers a WWII German Gas Mask at Lombardsijde beach - Brussels Morning</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 15:58:36 GMT</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdVktSjhCWnRXSWFoTk5qa2YtNFJ4dUN0Z0VJVDE1Y3V2MFA4ejRVZ0lrTDE4dk94Q0RpdTdkMk56QWx4NFJsX0lHV1BNcU9VaXV0MUdHTThQMlV3X2IwLU12NF9DUVZDaEo0ZHZ2U2VJdHdPSnAyTzNOQWY2VU9sVndaY0JTTUQ5dTdLdkxXSjVSODZuUURNcDlyRFFWN1ZjR21N?oc=5</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>46036.66569444445</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Long-Awaited EU-Mercosur Trade Pact Set For Signing - Channels Television</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 06:49:42 GMT</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPdU1KTkRVdE9aR3VYQ3hpMHRqSS1qMEdLRGJjQ0tYSHAwc29HTll1a3ZqY0EyRHdXcXFEUmVwQ3VYLUF2RjRVLUV5SXFUY2E1SlBINW1pY2tvVUpDNVB1REJyWHZGRkpmYmQyTllNdUxKcHltcllINWF6VExYZGRuWjF1TkhXeEREbzlhMlRaSmF2bTMt0gGXAkFVX3lxTE1jRE5UdW95VGxHWTl2NUdVdW9iZlQ4bnhOcWQ4ckFfTG9EYlF2VW1XY1lnT2liNnl2T3RvUGtBdW1Vc1VrNmpaRy1XTG5NWW1BVkgxazBjcUpGWkFMWFNkSGE5bHdpd3JBWlhYT2NoVnBrUnN4QXhNZG9HNVdSYi00QWRhTjZmOEdQaWk0WEREeERMSjhIcWhtSU5JWm04R042REFYV0tIdzRRUGZwZm5seFVSNl93aWNFbDNjZmtzUGxFcHQzTXEzVEJnQ21tMzdYM1RkbHN6V2VvSV9GUTk1S3VZTHlTeUdOU05tb25GRUtFd3RDT0picDRiMjVjM0I2TjdzeGtJX1BBbDZuTnVIUUdHQlBiNA?oc=5</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>46037.28451388889</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>EU says Ukraine to spend bulk of $135b loan on military needs - The Straits Times</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 15:11:36 GMT</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQZXFtTlJ1aU4yZl8zSkNsbWlWRFd6Y3RELThvM213Nkd3ekk4N3BGeDFHWWdDR1hPc1pHQTFrSnF6S3VkdVBqOTJkMUJyNE45U2NzZUpEbDk0Y1RaUnRCMU1IQ3RZQTV6S2VMZUpmcklZTG1pZnpfc2dyY1A3aXNYZjVrOGNtQmNPWmdXY1NidGgxellsd2x5bkVnSnN3c21VemthNQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>46036.63305555555</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>EU olive oil import checks rare or ‘non-existent’, says watchdog - The Straits Times</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 18:12:33 GMT</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPYmFyeGFRUExmT2kzU2JXQi0zNnEybzU0aTF1SlRSUzBOcEtRZkpTTEhFaUtpZUkzZ0JpY1RfMUt2TlNCaHdLV01jdWFHVGhBd0dyVTJKazVtOFVYbFFSM0dqX3VTTTVZaGpESFlDajlFY212Rkd0ZUhfaGgycU4wUWNQbjhPSWZENTVLbFViVE9xU1FUWFM4ZlVlTXNhOC1YMkgxcTVR?oc=5</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>46036.75871527778</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Leuven student Venue HdR launches silent disco solution for music regulation - Brussels Morning</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 15:50:54 GMT</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNOVJKZ0pZRXp3RmdZU1N2MmxSSGk0Qkp3dnJIeGV2THFleWVSMlZvSGZ5YUx6bDRzMjRQdjNnWHhRLVpQTmpUZDVvc1h3cDVXTmVtb2kxMTZGSEEzQkNOR01HMzN4b19QaUhmbjE0NHZ2SVFWY0pRMnJTcjVhbk1UWHJ6QS1Eb3Q3a1N5THJ1Vm5HRFI5ekh6eTFPZ1BpM2pmU1U2V0twdmtwQ3N5ZnhtRA?oc=5</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>46036.66034722222</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>CHAOS AFTER THE SERBIAN NEW YEAR CELEBRATION IN CACAK: Police identified 11 people who threw objects at Ana Bekuta! - Serbiantimes.info</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 15:13:20 GMT</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOcXdXTVU2MzRydjFKemhFRnJYSUp1ejlvWUUxUENLd2MwRWhTa25aVmJ2VmpVUk1YSEhvWWt1SW4yZ2Q5ZkhpYi14MWVJd2gtTHdwcTFMMnowcEJXS2FEQjNDUFRDUEd2SU5qaE5Xb05kSkk1NXZ5bWlTNFE3cFhrU1Y4SGNJeW5GaWdWQVRmLXlaUGZPdGk3dzJVTkFUbTFtVHBtTGFyaGhJTnpCLWdaYzk4enhuSEZsRVllN3ZwQ2E2eGFsVE1TTjc5OC1Ia0J6ZTBoQzdvQ0V0UDQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>46036.63425925926</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Bhim Army demands Rs 50 lakh for Dr Lavanya who died by suicide - The Hans India</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 03:02:12 GMT</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxONnhrMzJEanhYMjFBeDVKNHU3aTVySm56QkpnS0EtLThRQ0trbWp4MzRhMXFRUEM0Szhibkg2QkM3RjdWeXU5Snk3NE1aN3pGUGxNXy11aFg2U19FQkdybUlSeGFia0dLdVY2WC1Ebkpyb1FDOFluYnBrY29FRk9mS0tjelVSYUdWZVJQSVZwWkhSb3U2aURJWUxWR3ptOGo2Yk02RFdSdURtanNMZVRvdzB5bjjSAbQBQVVfeXFMTjZ4azMyRGp4WDIxQXg1SjR1N2k1ckpuekJKZ0tBLS04UUNLa21qeDM0YTFxUVBDNEs4Ym5INkJDN0Y3Vnl1OUp5NzRNWjd6RlBsTV8tdWhYNlNfRUJHcm1JUnhhYmtHS3VWNlgtRG5Kcm9RQzhZbmJwa2NvRUZPZktLY3pVUmFHVmVSUElWcFpIUm91NmlESVlMVkd6bThqNmJNNkRXUnVEbWpzTGVUb3cweW44?oc=5</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>46037.12652777778</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Local Town Searches Wertheim German Terms</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>("Wertheim" OR "Wurzburg" OR "Aschaffenburg") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR boycott)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Peak Jewish group urges co-operation on hate speech laws - Australian Broadcasting Corporation</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 06:48:30 GMT</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNWmZnNmtRbzlJX0lFSk5wbl80anVfV2hZRHFKal9raUJIZEItUVdHVUdjREtUN2FBME45Z2xIV2NkRFRLeElvLTI2ZEEzYnVNS0VZWWVyeTJEQU9oTDJDNzA0ZGEzcURzT2dmUWpuc3Z0Zl80cU1LOHNWZXVmNkZMZFFfN0ZVMjByaWF3UEFIdEJ1TkRRLW1HUHdCQ1o5eVJHY1Bxdmk3a2RUaVRq?oc=5</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>46037.28368055556</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Local Town Searches Wertheim German Terms</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>("Wertheim" OR "Wurzburg" OR "Aschaffenburg") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR boycott)</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Greens want concessions to support government’s hate speech laws - AFR</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 05:40:00 GMT</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQaTVJeVlsSmZDeGdvQjZ6SlFSSEp2OURzZHBkOVNOUElaRjJGc3NfR21ycTIyT0VydWxJS3dDU056SWdlQmlQaFNvWGZSd3k3eTNyNHFRQ3VVcERqaTJNdXhHNjlTZ1A4Mm5qLWh6eHd6WG1UaURELWYzam9BZ1BNNW11WVpjZmhGV0tCdkFXRERsRUJ0T255QV9ta01PRE9ESGplVk1qSV9pVDNmamstM0FzTzJOeGM?oc=5</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>46037.23611111111</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
           <t>Ireland / Kildare Protest Groups - Social Media</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Kildare's O'Byrne Cup final with Westmeath to be broadcast live on TG4 - Ireland Live</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Wed, 14 Jan 2026 10:38:08 GMT</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQUjdqaC0yazExbV82RFliVU9yVmU0Qzd5M3Zaa0tyUUx6cmRGbDdLYmtRY3pic2dkdXFUWjBmWVpXNUNJeUxQeVdXSmJORHl4ZDdPbkxZWlgwWGUwcHB1RVNpNThuUnRMSmhwWW5UcGZEeTlpMC1TUUdDNlNaVTl1TE5vZzR4RUNkdk45UHdLdWFjcWp2d1JmLVZJdmg0SFdGeWFhajdUNjJLcl83OWE2aHJvY0pyT0plbXQ2d2FkRzdCcW9wb0VZ?oc=5</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>46036.44314814815</v>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Disgust at badger hunting as horrific photos appear online - kildare-nationalist.ie</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 19:11:56 GMT</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVWcwVHk5bHJabzVtREktQXk5ZU9zU3A4Snlla1RUc0V1eW5lel9zNUMtWWVzSXlnckt6b2hSRmphYi04SDJBTnM3SUdnT0x6bzdiTkZsWncwTWdmS3Yxck5nQ2wxNWNQamdjYU1CcWN0emJWZ2haV3dLSGVDY3RzNXowM0dVWlcxLW5IMlI1TTY5MXo3bkQzWGJORXRablI2cmtEWFBFY0FPMzYtMDllanNfYw?oc=5</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>46036.7999537037</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Plans for new gym for Kildare GAA club - Ireland Live</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 15:38:54 GMT</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOeDZqd2E0UWdLRnB5aW9LajdpbTZkRkN3Z2k4SE03SWJrZzVkLVpjSmR4VVZnYy1nYkt1OEFHQkRMRmdZODVHel9EaVlxNjIxWGtTaEpmbGR4cHNrQThHSWFqc1c5YTAzc085UnRoOVVIWFUzTjBtLXVFejlDSzFfT3IzUThUWnJHc201Y2hFVE0xazFnUlhsLTRZYzc?oc=5</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>46036.65201388889</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Murder investigation launched following death of man in Coleraine - kildare-nationalist.ie</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 23:01:57 GMT</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQS2dGaU9Sb1dwa2g1NlJOcDRRb2RaOE9vaVlOZVRnUVo1R0g3Q3AxdENXNGZJV2t1R1JXTUsydkhFZzhFUWJFYzNlb0RKa0R4RklqYXVuaEJFVjJ2Sll4NGQyNlFZUkxFRTRpdTI3d0g3Q0Y4QVZ6VlAtbzN1eFNrUjc4eXFhUVpuYVNZdVM2TEEwQ0VqY0RKV2lJbVhkWFJNX2FmbmxfdDgzUE5HV2w3Z29SMWRKYWhJb3MtUExn?oc=5</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>46036.9596875</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Stocks to watch next week: Netflix, Intel, Burberry, JD Wetherspoon and JD Sports - Yahoo Finance UK</t>
+          <t>Teyana Taylor Pops in Purple Burberry Trenchcoat in New York City - WWD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 13:18:28 GMT</t>
+          <t>Fri, 16 Jan 2026 18:21:40 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPSWZ0OS04ZTk4ZmNMOGlIS2Y4Nl9Sb1lVOHo3WHZXWFR5UnpFdkdMMGhDZHVDSWI1MUR6RGM5RFBDSk1RSjgteDV5eXl6aXdsREU5TUhUNmQwTDJCb3NMVVY5cWEyTEhNRVN1NF9RUkRVeTJBTHpfOFBpUEVFaVp5M2tQOEF6Q1p0VmpOVUROT1NpQmZmWFZGd0dWb3p5Wnh3TmNuTTY0MDVIamwwR1pzbWRn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPOFZkWWJHbmZ3UWp1WFJocXByd25TakVnRm55YXpCZlRZQS1rdE80N29YREFSMFBUTEplZzZKZklNN3dhZFp1NWktWXlLT3JycXFkdWJWZDdPXzJfclBybGdMcVgzZVRxd3VIWmtoOGR5TGlNTjRNOFpnUkdrNUNwMnFYdlFzTy01cHgxMzVEUFVqbTJXR1ZSblJwSmRGRUt4Z3l5RQ?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46038.55449074074</v>
+        <v>46038.7650462963</v>
       </c>
     </row>
     <row r="3">
@@ -515,24 +515,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cartier owner Richemont delivers double-digit growth as jewellery remains resilient - TheIndustry.fashion</t>
+          <t>Milano Moda Uomo: Ralph Lauren, the coolest classicism - FashionNetwork - The World's Fashion Business News</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:46:22 GMT</t>
+          <t>Fri, 16 Jan 2026 19:12:23 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOZEJfODR5cDZ0U2Qzbll6bWtscENLdnpBUTZURXlWblVBYkUxcjRZanVoWDBxaWNBNmNsck1MQnNMNTdydFBGcjlTWkxlVUFsdUZibE1tRHcxVUNnZHAzNDBrQUgxaERuZnlCSzBfeTZuRFRReUh6aVVXU0Y1VkpQSEgyZ1ZuVmw5TjZBRFRHX2xLdE5pNHFUTFIwX3dnRTJDel9rcGpuTEtkZ1MwS2s4NjVUaEhFWUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOUU5xN1AzQlQxdjE2TzFXZWdCdmczOUJSNDR3NHNFTTd5OVZVTzZfYlRDVlJTUlljTFhPbnRHZU82RW96V2tHUkhiS3g3R2ZQc0t1SjJ1THJFX0NwMHdPUlg0WWpud043REFHbUFHaVFqYUowZkRmc0E0cWt6ZzZjdFJ1cDZwVkk4Z2VwRVhnbkctdzRoUDNzWTZ2WDA3ZkFFUWc?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46038.40719907408</v>
+        <v>46038.8002662037</v>
       </c>
     </row>
     <row r="4">
@@ -548,24 +548,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Disgusting Sisters Return with Warped Electronic-Pop Anthem ‘Calvin Klein’ - Indie is not a genre</t>
+          <t>Louis Vuitton Goes Big With New Four-Storey Beijing Flagship - 10 Magazine</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 14:08:25 GMT</t>
+          <t>Fri, 16 Jan 2026 15:58:34 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNQ2d1ZGJDVFVCMXpMaHZ6NGdwMXVFUjhVZ3dJbE04YWoxeVRPdnFTNF9leS1pUnM5a3hnV1Y3UEQ3TUJsdzQ5TGJkdzkyV3BPYlg5NVhPQldUc3VfMHI4Z3pORUYyNUpPM1NlRTNNSWEtUnl4c25WWFdFNlpCb2t3X2JNRVotMnJmT1ROMTM1dlA4NGxiSm5mbng2MUJudFVGalplbFZGRXZDdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9tT0JkUzlIUDZxbDlIRlcwdm9WOTMwaWJEX09jZC1SeUlNNGVCODY3QWF0Y1VBOC1OeW9JN3NQaENHeXEtRzd5LXQzbnZ0SFJMV3FlU2xCTTdQRFJrcHh6ZWNIekM?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46038.58917824074</v>
+        <v>46038.66567129629</v>
       </c>
     </row>
     <row r="5">
@@ -581,24 +581,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Valentino Rossi identifies Bagnaia, Martin as MotoGP 2026 unknowns - Crash.net</t>
+          <t>The Glow Was Real at Armani Beauty’s Luminous Silk Celebration in Los Angeles - Vogue</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:33:14 GMT</t>
+          <t>Fri, 16 Jan 2026 17:22:25 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQUW9ZaVd5d2VwY2xVVHU3dWJ6Sjg5bVUxUUl3WmVWajBHMjZrMGtfUGEzSG5uandVVTBDcUd5eHQ4VF9ETGJkWFhOLVNKYktBcThSSjA2V00yRzlzN05hcVl6Q0ZYMlZ4REhkdTV2ZHZab2xEdldycG5nS0ZzT09fbHMycDd5bExGTk5pZDJkQ3VjOUFkcDdyd0Z1LWdoQ0FOejR3N0dZOXRCRFE4aW02bThHaWo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQV19QTlV2NUNabXVKRUUwRndjMnFlcjNkdTU5TnlEWUNhdWk4dUk4OEk5YU9ZOGFpeG41b1B5Z1BHZk4tRC1McDczSktOQ0tLVldIV1VCdlFlRGZvTE9ZcEJiZDg1U0hlYURSNlNZaWZNWWVIZjdtUURyR2dVNV85M1dYRQ?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46038.48141203704</v>
+        <v>46038.72390046297</v>
       </c>
     </row>
     <row r="6">
@@ -614,24 +614,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>This is when luxury brand Burberry provides an update for investors - Yorkshire Post</t>
+          <t>Ralph Lauren front row draws celebrities to Milan show - The Independent</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 13:47:00 GMT</t>
+          <t>Fri, 16 Jan 2026 19:16:00 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNenBCQlYyNlVocGFqQmJnTlNyNnlsVmI2RWFOWF9RbWkwQ3UtM3NrbzBYMVgwaTVLUWk5alREal9zd2dicEllUElsMU1sOGpUcTVyWjJsLUR4WlZZTXQ5RVQwWTNYMFQ4X05KVDVwM1RFR2VfeV9lN1FXdEFDUVpsQmVrZFVrQWNIOXFaVEdPTXR2bDVNTHV3dy1YeUFQMmRpN0tDY3BQbnBGM3BGbmMxM3FBbFU2dVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOX1BucGMyLXlyRVVOa2xadTVsMkZscnA1QVB0RXJFQUdBVG80RG1mbGZ1TE02c3dyREFWQ1FJY0VnWERNYnRaTHk4LW5xQXdjejNRTUlMMjNBSHRYQkhlRlhoUW9wVm16bnl1NWdKdGFjWkVCQWZFS01rYXljbEtfYUtUY3NQeDI2cF9CWTVSYm5fU2RXQ01NRWUxd0QtS2toZkFlSEhKRWxkdWlybW5lRThB?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46038.57430555556</v>
+        <v>46038.80277777778</v>
       </c>
     </row>
     <row r="7">
@@ -647,24 +647,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Upgrade your beauty routine with Dior Addict’s new lip oils and perfumes - Tatler Asia</t>
+          <t>Disgusting Sisters Twist Romance on New Single ‘Calvin Klein’ - famemagazine.co.uk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 12:24:02 GMT</t>
+          <t>Fri, 16 Jan 2026 15:47:45 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNWkhHWEd3cXE2WnphYXB4U3ozVzFUQmh0aHVlcDFhMWIxa0Q4ZHJCeThUaUFORVpJRkZYMzFHc2huVDl5YzJhRm11UTdDb0V6QVJXMGJQdzdpbUtjWXVfY3p1Z2hHTkxDVjRyZXZ2VE9NYjMyU2p1STVtVm4za1MzbDdvOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUmY5c09ZLTNZbjVRS25YaWpvZTk2ZkJxdTVQLTJpbzhBcnp4bkRNT3lZd2xRTWZZeTVsWS1sRnppdXBjbURoMzFMVG05eVBNNDZFbmloVnlFR3VhdkFleTdMam9adjFMQ3ZibkpsTGpId2wzek1rVUQwMGZfUFhINEMwMmJFMVRKM0VCeklRRVJUTDBQWnc?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46038.51668981482</v>
+        <v>46038.65815972222</v>
       </c>
     </row>
     <row r="8">
@@ -680,24 +680,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>News, Valentino Rossi accuses Graziano's companion of stealing €200,000 - GPone.com</t>
+          <t>Louis Vuitton | SS26 Travels Through Feeling - Flaunt Magazine</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 13:12:10 GMT</t>
+          <t>Sat, 17 Jan 2026 02:08:24 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPWk1sai1DcE1xM01YRmtvUFNIN3JJalNHOXA1aXVFMm1RRkUyb0c0VXV3VEFQX2dYRjdZcTFaYkpiRFR1cC1NM1JBTmxMWC1obXFOOTROWlFTeW0yOVo5SHZMMmJVcWg3S1FNbGxMdmt4VmRZcnRLMUs4TE56Nkl1dnJtQkdKUWlkYkVYYVdReHl5eXllYkVsb1RoVjhoUm1LR3BCME5IZE1FbkVXcm53?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1JYVhBalZwMWtCSlYzTlpNUEIzX2t4S1VTR2pDdG80dlBfS0ZkbUpuYzE0Mzc5QmVzRGFzNHRFdmN2SjBwUkhTR2JJZkhVVnRxczhVQ1ZsREY3eGY5MHJEQnlLOFo3R0drRGc?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46038.55011574074</v>
+        <v>46039.08916666666</v>
       </c>
     </row>
     <row r="9">
@@ -713,24 +713,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Emaar’s Alabbar and Armani reboot hotel partnership - Arabian Gulf Business Insight | AGBI</t>
+          <t>Armani Reformulated Its Most Popular Foundation — But Why? - Refinery29</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 08:58:54 GMT</t>
+          <t>Fri, 16 Jan 2026 17:51:00 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOQThHU05ZN21GVjFUQklQVUtCcTlIa2J2d3phR1pRRUFZTW1DOWNqVXo2SkRWMWI4VUE3V3A3X3diWHRWS3RvOVU3NTJPYUpTdWNFUUEwU0RfVFBwWWRhVUFqWHdmQTVQYjZNeDZDOWZnQVFyYWE0blh2UWRiUzNXNW5pTmlRcGFrXzJybGFOd2NzY0lkRUdCMUE5aElIM1hCLUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1ra1FSUVlMZmVqekpjVlRuaHNwTzV3Tmg2NE5BLVc4OURjS04tZUpjV1l1VGlHTURMeXFOelBNeWhsNlhNOXBNNi1LRjRBZ0tJS29obS1pZlVYOU5QWG85Nmh5NjEwOGdSMWNtbU91TjB5VEhxR1RfX1ZnMA?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46038.37423611111</v>
+        <v>46038.74375</v>
       </c>
     </row>
     <row r="10">
@@ -746,24 +746,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Precious Fibers in Paris - Interior Furniture Design Magazine</t>
+          <t>Saffron Vadher Brings Us Along To The Launch Of Dior Cuir Saddle - 10 Magazine</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:00:22 GMT</t>
+          <t>Fri, 16 Jan 2026 17:28:34 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9IMXlORUxGR010Z3phcWdTWi16b1RfYWtvbG85ZTRyVWlWZDJ0VWhuT09LZXo2aXJ6TF9TTUQyYWpOaFhMY2wyUVROa254NlFjUXJ3cEpvYW9XYk9veHJ0dUN0MDgtNm8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBMOXJyd1BxeDA1V25iTWZkc2ZyT0lwVXBrMjYyQXZGQXlfS1ZFcHdKNW5uLU1wSUM3SGtIMDlDZmw1YTJOVUVNbE9janlrM3kyZDVGWW5oSHdVRUN2eEw4QXFaY0tJSXd1TWJhdm5RaWgwa01VclZhag?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46038.4169212963</v>
+        <v>46038.72817129629</v>
       </c>
     </row>
     <row r="11">
@@ -779,24 +779,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finn Bennett In Gucci La Famiglia At Berlin Premiere - Luxferity</t>
+          <t>Why Armani Beauty Is Relaunching Its Hero Product After 25 Years - Vogue</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:27:48 GMT</t>
+          <t>Fri, 16 Jan 2026 17:42:26 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxONXh2ZnJlMkJreHVsQ2pSU3ljaDNIU053aTloQUNNZDlTQU9NY1ZhRktGcFdYRUxLWlZ3bG1NNzFJZWVJRHZHb0tMVEZaUDNPSTlkMUpaNER0eDFTV0dhelphLVc3R0V2TE5pRFExTWFNNGJLcHFlSENia0pQbXhGeVpFc0NqSlV4QUtRcktn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOYVJ4R0hudWhadEhnOFhiMlF2eDg4Yk0xQ1BPSWdhbHk0cTg4YVVkUVdfcENVU1FJdzV5NjcycGhyYkdPUVYxenJsLU1Ma0JFWTRvUlhfVXlPMEwtOU9uUXd4QVpBczJ5OFloZTF6QU1VM0s0WkE2WjdLcy1CQ1phMHNwV0tKeGFtTzYydjhKbnc0UXhvSWc?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46038.43597222222</v>
+        <v>46038.73780092593</v>
       </c>
     </row>
     <row r="12">
@@ -812,24 +812,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ralph Lauren Corporation appoints Cesar Conde to board of directors - FashionUnited</t>
+          <t>Louis Vuitton Toasts the Men’s Spring 2026 Collection With Fai Khadra and More at Exclusive Cocktail Party - WWD</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 08:58:25 GMT</t>
+          <t>Fri, 16 Jan 2026 18:19:55 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPT1FxYjJPOFhPQVZXaF9nVXpsMzlNUExFQk52Q21SQ2RfdXN5R1EyRDNvSnVlTlBGaUVkN1JQbF9IR3FJZ09sNVROMVVyNjZycGpkaGQzcWZmZ2xfQW5JZ1dvam1ick9OcEV0a2lRSE0xTkZqZHcxQi1Hcmx3WFUyYVd4b21IQXVXZFl4N0tvclVMakFueW9oTU94R05KbmtPX2lhZ19yclQ1cWsxcWRKdFpxdnJJWGl1Q1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOMkI5Qi0tTmtSdGhPMHdTaGpHYk42LXgzaE1oR3lzLUhvZHg5M1cwQ0ZDVVNHOFlOR0xvQnhOanYyS3FYMUdnZWJwNjMzcGRGVklJaEZ6RGJEb21JdUhlQ1NLSVJ6SUR2VGsxLVlKMHg1N3NhOWRkd1FLX01VTHY3cmh1aWNrTllTTmxnVWJkUkNrOUZJWnRuX1VCN0tUUURqdHY5T1dmWTFWMkNKeEk5Q0x4MU8?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46038.37390046296</v>
+        <v>46038.76383101852</v>
       </c>
     </row>
     <row r="13">
@@ -845,24 +845,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jennifer Connelly Leads Louis Vuitton Spring Summer 2026 Campaign - dscene magazine</t>
+          <t>Dakota Fanning, François Arnaud, and More at the Armani Beauty VIP Party [PHOTOS] - WWD</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:51:32 GMT</t>
+          <t>Fri, 16 Jan 2026 16:52:30 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxORGF5WjZRR1ExSXB1MVlLUVAzY2VYOFhxQ3UtSkJlVmRXVEV4SUlHSnplVVVFMHRvUXVFQ3dSQnY3bWdRUlJIZkZpSFJzOHNnWGozMklNV08xemxLUzQ2dXRlMHZtbkJFWTFmMlROa3IzMmxYX2tTSVBMVklyeTZtT21YOTJlSURSTFU4Z1YxLVJDNTlsWXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPbUFTY0wyQURPbTQzaG9uVUN6VnROQXBCbklSbmYteUhQV3ZMT0tSODRUVXNsQXBHZlozcFpSaW1jQ0U4TXhFQmJ3SXNKS2FyQTVoR0VEek1id21TcGxkTEpuYWJGX1hlY0JUTTV6eUhEYzB3UHFlOE1NcTNSQ2dackNGT1ZfTkUybHAwS2RLNXBKQzBkN3BVNDFzMkIwZFNkMnRYYk9BdUk0eXpXOUpJUC1qU0syeHRkbnc?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46038.41078703704</v>
+        <v>46038.703125</v>
       </c>
     </row>
     <row r="14">
@@ -878,189 +878,189 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chalamet’s Cartier love helps brand revival - Business Post</t>
+          <t>Olivia Dean: ‘I feel the most myself I’ve ever felt’ - Dazed</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:53:37 GMT</t>
+          <t>Fri, 16 Jan 2026 16:31:00 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOZi1EVUdGN2I4RWpkaVpic0poREJqUnFXQ2sweTVkTkpxc1p5bTBCeDduR1RiWi1NYlh5WkVDWUI5OUJRZzlpMElTTXZEbHVXTkJDSTliN3VXNWllOTUxQWNYbktuWkpobXk5cExNOU14OXZfc2RnbTlnS1dCbVFnUkN6ZVNoMkN6?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQNF9TUUNsWHdObU53d1B4OGMtdUNzSkVqdHN0TTJNNnZBdy1SWFVTOHFjZDI2WUJyakFfS21hQm1rd2xFZFItcGdEWU80THotcHJJR2FROTdOMWFXeEgtNWF3YTkxYk5HX3E2S3RxY1N6RE81SThfVVVaUU94TXpnSXdUbnJ6c3BaWmdMVjhWWXM3SmpZSl9pMXFlWW81QkFNdkE?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46038.45390046296</v>
+        <v>46038.68819444445</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Royal Mail explains delivery issue timeline after Aberdeen parcels sent to Livingston in wake of snow chaos - Press and Journal</t>
+          <t>Go Backstage at Zegna, Dolce &amp; Gabbana, and Giorgio Armani at the Fall 2026 Menswear Shows in Milan - Vogue</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 13:10:41 GMT</t>
+          <t>Fri, 16 Jan 2026 17:56:41 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPZ0ozT2xSdzNZeEdHVmg5MUg0RUVIY1FhTGJkMkJmVkFrMi1kbDFSZjFOY0Q3WjNiVlctS0xPdEFYUjRTSHhNSk9mZ3V1RFRvNEpJUTFUM1pCNi1iMXFvak0zWGlvekhFcUhrMVR4VnRYN1ZsNE9EYUpuOUNlRy1pSW82Nkc0UXVwY3dQMmt6RVF5TnBoYWdVTW5McHVZQmhqYTU5dk5HcHhtb09DcjFIbTJRMDltLWd6dGFGaUV3OTlXS1pIZFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOMDNZbENlZWJZcDhwZUp6TEwyWmFxeUR6bkVoTm10T3JnNFhUSmhVNm1qQWRNWW5ycHhJMVBYVlJVaVNvWHViQzFrSDRIQllMQlc0NlpmR19UeGpVaDNPZ05KcUdEbnNuZEFVanl6N2hPRjRZVUZ1azM3X0xyblRwdlRnTG5HMFQ0bG5ra3R3?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46038.54908564815</v>
+        <v>46038.74769675926</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amazon Locks In Copper Supply as AI Power Demand Grows - TradingView — Track All Markets</t>
+          <t>Fashion Week: Free exhibition displays 126 haute couture pieces by Dior in an opulent Parisian palace - Sortir à Paris</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:11:32 GMT</t>
+          <t>Fri, 16 Jan 2026 16:35:08 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPaEtUQ19KdTlsRkJxYlFqdjdCYkZmdDgzZUFQTzJrMDRTZ2FIUEcxcU84TkZwWTdaSTEzSDlQVnhDbDRuRVgxQXg3MmZWMlU5ejcxT3pQaWpFZExZcFNaV0dOdlk3M0N6UVJZaldpOWNTMDhnOFNvUzZfRnJOQ3VXRHZGYTNQRExyaFFad3dfM1hkMlRzanlMVjAybG5JZUtTajB5bmlHdGhpOHRHbEowUXJvRkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxPa25xelh5X05tS1RYM0ltdUgtdjNwZlB4RVVOUGF5SzdZQjlDd1ZRTDE1cDJoLVlvTW5UVE1tUGdTRGRMbzFZaVcyN3R0emFwTHZTamRkWWxOVFd1dTVGaDVBMDFCWHhVd1ZSUkhlOWJJQTNtNHU1UEo0Ynl5dEE3c1NfbEJBQnRqUWhEMDlnTmVDRG9VVDk0MTdGVWNZRjZMTUR1VGczQWRuZmNrcVVsbjFiaHN0OEtrNlRmWS02XzlJaWtUdEZRdTNKYjk2dTdMdkZwaUtIRXEyR0dKd3hwWEdGbTdNa3QxODBGVVdNb1NmUGlHaFdMNjIxYjl3OEFZTzU1X1ZDdVNBZw?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46038.46634259259</v>
+        <v>46038.69106481481</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Special delivery: FedEx preps its freight business for a major spinoff - Seeking Alpha</t>
+          <t>Valentino infiltrates skateboarding with Vans - HIGHXTAR.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 13:32:09 GMT</t>
+          <t>Fri, 16 Jan 2026 14:44:24 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOV1RFbmUxOFY1bnpxVkxGTkxoZ2czRDJ6Q0dlZ1lBbGlrV1NUb2YyWDRnd1M4aWVqMXhCVi1LU0pnODhxREVDcHNiNm00aEk3elVhY0pIRHpwRUl4ZXNRSmo1bUZqQ2VRdjVleTZpSlZ3N05zVGdiX3NZLWNlOUJzT1RlTEE1ZTAtMkdrdXdLbEJSanJ3MlM2S1RCdXVTaDdOVzZTNXJlVEhVVDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE9WNWQ0N1lWU3l5SU5MMHdFVkE3ZXNxWkt4Z2UtX3V4VlZGbHJsRVUtcXJiOGZFN0RBVFl2cU9lQlhpLWg0Zk0tbG9RbUlmcHYzc1Axd3J2dkxVZzNuZnNZbXB0RTVlQzZZMVV0RjVVdXpFRVpoUmdwUkd3?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46038.56399305556</v>
+        <v>46038.61416666667</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FedEx adds 17 electric trucks to last-mile fleet in Japan - electrive.com</t>
+          <t>Vans and Valentino Garavani Drop Six New Styles in Their Second Collaboration - WWD</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 08:37:38 GMT</t>
+          <t>Fri, 16 Jan 2026 16:39:07 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNWWZvMnB5ZGk4SkpKU2VJc1FmVUt0RmFsd0ZCclprckN4Rzd6M2VseHZlMktza0NyMDdralp2REpsdE5OWmY5N0ROMU9nbFlDcHJsZ1A2NnlNejdEM0tZZWhsQ2tYUXhPU2FwYU0xYXJ0ckxWZzVwbkdqbjF1dzZ1a0RwekNybUFvVVR3ZGlwSWI1M1Ruajc0Tndzdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQUXJBMjlLZTdyLVAxTThnbFpGbmZwQmxxT1FRejVfQU5HLVcwTUNZQndQUjdTQ1MwM1NhVWN0SWNDR2xjX21UeHVZLUFVYlBhdGU0TWJxNEUtS2lpZVRaYVhQQUV1bzVBcS1CSTVnWmpxSnJpaWhZZXFCRVhLUGJHMDl1VGF4Y0VQVVR5VHE1XzR3Slp6ekJZRTVlS3ZfZjJnMzJQcUhR?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46038.35946759259</v>
+        <v>46038.69383101852</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DHL leases 3.5 lakh sq ft of warehousing space near Chennai for ₹77 lakh monthly rent | Real Estate News - Hindustan Times</t>
+          <t>'Compact' B&amp;M £25 dehumidifier dries clothes, stops mould and banishes odours - The Mirror</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:48:12 GMT</t>
+          <t>Sat, 17 Jan 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPcDBCRUdTUDBQQ1MzSG81dlg1NlFpdVBDbGFOa2dBemxDRWVmZVFWamhicjVtZXNGZEs0MkVOdE82XzRnb0psWHI0QmwwWGZPSXNhQi1vQnZFaExyQmdkdEZQZHhRaVgwSDVTOG1HdFF1YzhIa3F2QmlXa0czVDMxVnBPSVJoZ2Rzc2tLMHNSSGNZRG1IbkVrRlE5X25jc0gyRVVOT1ctT3hGQkplUGtpcUFRa1JmMXZ5dV96Zk1uSUp6QnVOcG5TQWM1OFFOY2hlVFZrNDhSQlRSWDFOTDRWX2xyVnVaUFB4UG9z0gHrAUFVX3lxTE9wMEJFR1NQMFBDUzNIbzV2WDU2UWl1UENsYU5rZ0F6bENFZWZlUVZqaGJyNW1lc0ZkSzQyRU50TzZfNGdvSmxYcjRCbDBYZk9Jc2FCLW9CdkVoTHJCZ2R0RlBkeFFpWDBINVM4bUd0UXVjOEhrcXZCaVdrRzNUMzFWcE9JUmhnZHNza0swc1JIY1lEbUhuRWtGUTlfbmNzSDJFVU5PVy1PeEZCSmVQa2lxQVFrUmYxdnl1X3pmTW5JSnpCdU5wblNBYzU4UU5jaGVUVms0OFJCVFJYMU5MNFZfbHJWdVpQUHhQb3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNTlJYaWlTQXF3dVN1N2xpY1B0dDhkOTVMSG5HU1pYcHpsLVJBUVBWOHJnWi1OLUNJemVneDNTTVFKc3MzNkxkM3Z3c01QSnN6X0FCd2didEkyTm5QVXJIeXhQUUtKSHZaX1oyeGh6OVJRN1BoLWt6aXRWYnB1RXU2bDRLVEJiZDhKaUlVLTlVeGfSAZYBQVVfeXFMUHl4WHlBaW9VRG9PYVcwd3h0aS1WTUxKS2pVOUNkandwMlRrSmRSYVhiQWJZS1NNSzdLN1lTamFmUVljYXdrMG9vX1l0Vm9oVGNoaWM3dTBVbTBnVS1KZ0Z3Y1hnbktZX2xqX0pGZHNiQ2VhVlFzUlh3eUlSRWY5VXdnQkJXVEVwTHZZR1NkSFhHRTY0MWlB?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46038.49180555555</v>
+        <v>46039.20833333334</v>
       </c>
     </row>
     <row r="20">
@@ -1076,1179 +1076,3918 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'I'm Going to Get You Fired!': Texas Judge Caught on Video Screaming at Black Amazon Drivers — Then His Son Allegedly Spits and Calls Them Slurs - Atlanta Black Star</t>
+          <t>Bournemouth MP takes Evri 'concerns' to parliament - Bournemouth Echo</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:35:16 GMT</t>
+          <t>Sat, 17 Jan 2026 00:00:00 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOQ3Q3bDhnUEdHRklhU1ItbHloam9LVzhDb3JpSTR4cWx0QjQ4VGk4OFpOT0gxeHIxTl9obThvTFFrLXBtN3BucURKWm15WmtRZjNneXhPR2hoTnlUUkVDQUtKVDRWQTR6cVRLX29JSGFPV2pBLWlJakhaSjA3MjVDZ2RtTjF4OG0tMHpSTGFjRzZaSWh6ZFJMTXpaVjV1SDV6VFJ2Nw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQUFBGYnZpMUNITTR6VUlSeW1uS0hHRGN1dXJEd3h3RnZrczhSeGN1TFByNC1Ndm9Kd0FTWlZ3Mk1UdFhiVDl6UGs0aFRJalZTRWt2czVBUENnYXY0clV3Z2RDSlBKLTM4MURWY3lNYzRCZzNaeFFNeF9pVW9RWVJtbll5NzQwTEF0eXFFMFFUdTJSbkl5dUtRT2JB?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46038.48282407408</v>
+        <v>46039</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>High Level City searches Belgium French language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>("brussels" OR "Maastricht" OR "Antwerp" ) AND ("Bombe" OR "alerte à la bombe" OR "explosif" OR "colis sans surveillance" OR  "explosion" OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Laughing gas canisters cause furnace explosions in Belgium - Brussels Morning</t>
+          <t>UPS revamps US sales team, makes layoffs - Supply Chain Dive</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 14:15:09 GMT</t>
+          <t>Fri, 16 Jan 2026 16:16:48 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPNlVQVkR5S2RrUk1QYUkyc1ViT25OWEkwWHFjdjZXRURjMGJvM25sNlNZOS1abS1PcVBlbkhFeWdFb1Zyd3dsOWtJelBuRFkzSEZ5QjhZdXlITDAtN0FWQzZPY3NHUEtxcXBFdVduQ1dvb3o4aGVqTHFXVzZ0b1FTUkZmOUJpenViUEd5eDRkU1FtZ0l5Yko4aA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNRkpmbHl1UjRqQzJDNHE3cVRKVTRqbFVuVXQ2Vmt0amxwTmYxTHplNVZYTUFzdVFmZWdvcUhTakR6ZmRlUnRlamVQWTZMdXZrRWZQOG0tT2lZWmJIdG56dEt2N1d5cllYRFlIeExkUEhuQVZCdUR5SDAtNDd0cEM4U1hha2R1d21ZaVE?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46038.59385416667</v>
+        <v>46038.67833333334</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Frank to Make Decision on Summer Signing’s Tottenham Future - Vital Football</t>
+          <t>Special delivery: FedEx preps its freight business for a major spinoff - MSN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 08:30:00 GMT</t>
+          <t>Fri, 16 Jan 2026 15:22:05 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPNkxWYkdPYS1IX19MVmZYZ2lLNS1aSlpuUW5RQ19kRFd5cmdUMjhKTFFDOWhGQ21kRjYxS2dhZHRTWGNZUy12bS1KbjRlME1Sd090YW82R0ZQQlAza0lMOVc4XzdvTjU3VnM5bE4teXFmS21UdDFNM1VhYm1ibUlmYlBkOWVFQjJvMzVGMlBLM1I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNWmQzQ2xOSHFMcXhGRS1fVzQ5bjZOUFFRdmZ3cTI2eGZpend6NENqVEZmeWlBam1HWU5NYnF0WGxmRjhZcjBMVk1POGNCbURybTNXSzRPaDRUVWhPUFdHdEpKM3dIb0FfelgwMDlMcjZEVTM5bDJTQWlyRVg0LTBDMFdrNEQ5aUNtb1p3VDVuT2dfRW1waTVadHhWQ1BIcklTV0h4eFBIaUp1NlBpSG1XN1VLMjFoOTFWLVNj?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46038.35416666666</v>
+        <v>46038.64033564815</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Afghan man goes on trial over deadly Munich car-ramming - Free Malaysia Today</t>
+          <t>Amazon more than triples wildfire relief supply stock - Chain Store Age</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:31:15 GMT</t>
+          <t>Fri, 16 Jan 2026 16:02:59 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOeWJVZ0lNdzhyWl9TcUstRmZ6U3hmUXpJRTVxR3l0Ykd1SzdmZU5lRDM5T195RW9fLU1LX0ZxcHpHemtlMGhrWVpWZzBPbDNUWUtyTUNaaXlKbFVCSEJYUHFyemF1RkpFUzZyOGVBdHJEdHlyVGd1M0UwTGJWODhMeWlMUnNYemI4ZXdlekQ4QVZMT1d6c1NYZVRGVkRNNE5NWjdhLUVWRTNCdjZGalJNY29rZkFZdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5TTHpINmhRUFNobEJUVy1RaFNleWtuLWpPUVhfSjh1M3p6ZmQyQkhuLTVSal8wcGlCY2xTSHg1NXNHQkVFRWxiWFh6ekVsTHp3NWlvLTVBajRYdjROSDA5enZ2elFKZ1ZacDlWOFhGNVBMbGdDRUJvUGl3QWVuQzA?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46038.43836805555</v>
+        <v>46038.66873842593</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>The transfer video is explosive! Kasımpaşa announced Cenk Tosun. - Haberler</t>
+          <t>Orange County files lawsuit over Amazon warehouse PILOT veto - Times Herald-Record</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 13:27:48 GMT</t>
+          <t>Fri, 16 Jan 2026 22:17:00 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBwRjQwZk1tLV9BaGZaenY0YmxoMDBCY3FOd3NqS29yQ1JwQWpOQTJBN0QxSjQ0S0RJZ0RfV1JkZlliOWY1Vk9DYUJHSVZ1WlNuc01VNDZlX3Z4V2FKdnRPM2xXQUJ0ZzVFbHN1UlBlTHBPY2RMWHdhaG05OWhZOE0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPWmhOa2VlZWNiVkkzajRNZGNDcENjNTRLMHRUWUkzRjBTUjAyeEptckFRS1BjYlRWUmtNSDdRY2xqa1V5Yk1qa19WMUtjNFI0blZRRzNDSmZHX0hUSW94QzdtRWt0Zm0zMmxSa1pQODRCaVFfd1c5MHJyOTdianhJcjczQmJnckZjWUlyN01UbEdPaWpGczc3aTd2OHlEVDJUbm9jeGdnZUlRZVhSRmlHQ3dJOWpMNk5oOW5IOGFmVUhwaXNoVWNQd2RNX0lOcVJJX1g5R0tEejlfOGdMQ19mVWdSYWxQQzQ?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46038.56097222222</v>
+        <v>46038.92847222222</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Three woman charged following thefts in Manchester city centre - Greater Manchester Police</t>
+          <t>DHL Supply Chain leases 3.5 lakh sq ft warehousing space in Chennai - The Economic Times</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:19:00 GMT</t>
+          <t>Fri, 16 Jan 2026 19:19:53 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNcVdEbnE4SGMzb1JaZDJ1aGxRaXR5YlFCaG9DSDY0NnZCVlA4MnM0clY1ekhSU2d5c3REZGFSMHQ1UDdzbUhnYXlROUtGbUY2dnNEQ3NZSjJPXzJ4aXNrT2xhRnRTdXVUcGluaS1aeWxyZGU5azBGWjg4YUx4amhJSkhjRnVCVVFwZ1NjOFQtSV9YZnJHNUJPWUF2S1laMHJ2eEhFWkJrUk1rX1N3bnZyNXFfd1c5bFN5amlsXzdpYUc0VmdmUE9lblV1X1gza2N6NFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOUGd0UG5ERUhFVEhsZ3NjLThoZWlMQXBVQTdmT19JSzRTTHQ3UXNYdS0tOWhfaG1iTFJmMi1BTk1uTDBYdHZqcHVTdkczMGVlWmstbkF4ZVV2aGR1aHg0bFZSQ1RlSVczSzIxXy1uUkhaZDIzaldFZHdxQkZSWGx1YjNaX0hTT0xqbm5LYV9xTU1ZMVBUeHJGUmRDWFhmczhaOHIya1llSk4zMFJtaU1VOFZJN3F3eldGQmdERzR0bkpJRzFYQTV5X09XT0FKTzF4YllNY3l0bUpnSjJoZ3NGUkY5dXB0SUFHOFJEYlNZdE5NRVnSAfgBQVVfeXFMTW9Fek5BZEtuc3RSNjQ4M2NXcU5OcF9RYlZWNy1URWpMRS1FNmhGd1ZzWlU5b0MycmFoaVFNX1NYT05xdV9lODNjaDNvNnpncjNSOGVVb01ISXNudlFMTGVZeW1KMXNXSEtfSExyb25qa05OeTBZR29ORXJNemp2VzNvUm5vRm56N2U0cDBfNGNXak9iTU95TW9tYjhMcnpYTjZ3N3Y5NmJIN21xWlk4Z0s0Q2hGVXJvNk5Dakk5azR6ZzhFdUdCYkVKV1M2aW5ScFlyN2NXM3ZZTTNudzdQaWt3S3NkMW9LMUNGQkJYcFJJelpHLTBXanI?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46038.42986111111</v>
+        <v>46038.80547453704</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fed urges Welsh government to fund £6,500 CCTV grant - Better Retailing</t>
+          <t>Amazon Adds Fresh Groceries To Same-Day Delivery: What To Know - MSN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:46:58 GMT</t>
+          <t>Fri, 16 Jan 2026 14:43:50 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPbXplci15NlQ5T3JzbzdJN05jazhta0VETHdCWC02Yk5RSXBrd011UEtjQ2l4UkNMVXhtOGhhcXZmcDVoZ2lsQUF1OVNobEdZOXlKbzdzNmxCTHRIczJFX2xFNndTc3VkZkdETHViVjJwN18xRlpWZUhCRDE5R243SGhtQzA4UG9sb3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAJBVV95cUxQejVQVkFyQzBuS1pCWmxMdHBzQVlhV0c0bUJqb2lydlVNUEVnNFVoSWlJMWtLOS1FaFBWV3ZQbzdQYk1BcnJnVzFJUXpnSUY4Sk5VWmU2ay1mOU5KbzdLZldiNnFkVDFLZHlseDBoNzA5WmFwZ3ExQ3F0WXExRVBGNTh1dldpX0NDYk1CYW1zNlhDd3FTNEdtRnIxb2Z3cmlyakNWMUs5dmlzT19tYkx6ZU9lcm8wUDB3ZjgwN3hRRk5mUEROTmxqVkg0ZWtQalpHQklUV0MzOGhTTTdfTVhDOG96S1RRV1Q0NGJyRzFmZ2owZTg5S1dSTWxKVUdDQlpwdWxuTm5lbDFqNnpLUENkNDRDR21XVVU1OGJZQjdVdVZnYThJWDUta3Jhd3ZoZ203M0xFYUVlemU2ZktucE9uUG0wbjY5UFJMZVR3Yg?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46038.49094907408</v>
+        <v>46038.61377314815</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>More than 50 arrests as police ramp up undercover shoplifting patrols - Welwyn Hatfield Times</t>
+          <t>Jefferson Parish welcomes Louisiana's first Amazon same-day delivery site - MSN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:58:52 GMT</t>
+          <t>Fri, 16 Jan 2026 15:54:30 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNRnFDMkp5VzdwQUhHc2M5OTQ5VFZoYmRUOXBRaXhRQWx5Q25EUkFhRXQ5aG9TNGhmcldQUUMyUXRndDRNUUFYOWMwWE1CNzZsc1pWUEpVNWVJa1Q0bm9SYkZ0WW1LT05yQzNHdkw4ZnRGTzVsVzBBa1ZvODBhLTJGQkhLN3JGNlJLMm1SNnBOcHlFZVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AJBVV95cUxOa3RPaXRLV2tPTk9mUExDR3l0TF9zbFRacmxCZzBlMXM0aXNPUVBPaUJiMVlqS3JrTVUwRktDTFU1VnNLRGh3bnVSVE9ySG9oendZWDJtcmh1VHA4YkF6NEF5eXFJRjFjT3NPU19Zd01CUW5sS3hXVXlMYmw4bGRVcWJkWFJMeEZhZHYzSlRNOFNmRG9uN1pUVk1hU3dlNFo2TlRvUHFNYTJCZnd5aklKOHdOMkdfYloxOHJqb25WaXp2ZjZOSGxFaW9hb3Z6Nm11TG8wYm5XUHpuczkxNGtSLUpIdmF3dFI5ZGVwaElyZDZKYWwzV25xNExpZ2NObWFPNkp5MVJtUWMtajFJVkJRZGJmU3JpSlJSZzAtTDZJUnB2dDJEUmFIcjU3ZFBYZ0pGUkpEQnVXOXgxd25admZkbTJSTGk5OWNGQ1dOX2RCeFc?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46038.4575462963</v>
+        <v>46038.66284722222</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Police appeal after car damaged on Christmas morning in York - Yahoo News UK</t>
+          <t>Amazon Business: The Perfect One-Stop Shop for Procurement - Procurement Magazine</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:44:02 GMT</t>
+          <t>Fri, 16 Jan 2026 15:21:46 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPLWhxVDdDSl8yWEExNXloN3hpY01va1B1N1R3MjBqN1V3MlVReG4tTjhobWJJbnBEcHJRZlR0WEZIcHZjR2tGV2Jja0w2T0h3ZWNxRmcxQ285eTR2RkNYY2tLOHVuLUotTGViN2wza09peENsZTE4dWtxS1J3VUxDU1NB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9kSGVzYlE1eE9QTjVxS0gybWFMNjZiTTl0Qmx3d0N5ODc2TDJZMGlfTGtUNTdWNEpuc1FZOWJQQU1iR1FHSVctMk5NMmZvZDJPMTE2VEptank5TGhBaThFSjhmck9KLVdwa0NKaFh3V2hzS1dKTl9BS00ycFB1Zw?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46038.44724537037</v>
+        <v>46038.64011574074</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Police divers comb through South London park lake searching for fatal stabbing clues - MyLondon</t>
+          <t>Royal Mail apologises for delays in 25 areas - check to see if you are affected - MSN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 13:24:54 GMT</t>
+          <t>Sat, 17 Jan 2026 01:12:42 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPaXdHWENoXzB4bjNlbXZFdDlJWl9BRzQ2bzZLYUp1ZUxTa0l0S24yMUVKSmVjbVFQdHhHVVVRWFhLdHM2QVdKc0hOX25IdnNRTC14LWxBTFFKT2VuTWRmdlBDZllYejJ6YlBjb1IyXzVCdERQTl9QNXZrdHBma3BqSk5yeWtCaU1yR2M5ZUh1U2RRVUNUOVNOUllTMUhDeXPSAaQBQVVfeXFMTjduVmNPYTNfcDctZjMwVjllNEl5ekk4VXBWS1JJdHVxdFViY2pFSk9EMDJsOUxTTGY4ZGVmbEZwdVZDcUd6ZDZDT0JQX0JvWnc2cmV2b1BaVnMtTjEtdTA5bFdBMXFXVGNyMEJ1b3F0NTNXQTVQSzJqeVdKNlJoOEZkYngwNTA0T3loby1nTFgwdmN3dVgzeE1vOXozU3Z3Umt5b2I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wJBVV95cUxPdjd1b2lBbmFMam1xWW5kMVpsSzVMWnFsOGNYV1NMSXE4bkFxblNadDBEam1PUUJ3QjNoNFBhd1FSc2hiS0NlQzlhMlAyMEpIRHI0eTIybWEtSzR4X0daQjRTaWJISFJrSW9hbEJrVmtDYWtPN3FaNmNhclg5d0w5djlKZzFkbEJJR203ZUg1M04teUppb3hDVXJ0N0pFT08zRGVpU2d3TVMxenRXdmZzdXlXTGNTNzBjQ2ZUc0pMNmdoZ0ljU2J0eF9UdHNEUHViUTg2WmVhNkZmRWpENnE5dmJrTUM2NVZwZXpCb0hiMl9uN1k5Tnc1UGtYdDh0NHJNV0NOMW85YVZ4REw1WnRDUUdraWVMWXBXSmpYYnRNY2QtTVFud0ZEa045Z2ZzN05OR1VCQ050UVpJQXN2YnhmaWYyLUtIY255MnpnRF80NFI0SThpaExiVDREdGxfdENRRWk2cG1BVjJhUEtCQXZMekJqVnBpa2JpYkJPZll3RQ?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46038.55895833333</v>
+        <v>46039.05048611111</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Second man charged with attempted murder after shooting in Bexleyheath - london-now.co.uk</t>
+          <t>News | Singapore REIT acquires DHL distribution center near Columbus, Ohio - CoStar</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 13:24:00 GMT</t>
+          <t>Fri, 16 Jan 2026 19:54:29 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQUl9pOXBDN2hyaFQ5UEdNVkpXSzZiSlJTSkFwME5wM05fNzRkRmE4R3NCVDk5ZWxTRFZteVR6dnp0bVppeDhVNnlZaDNXYVhiNERiWGdZejZWR1hITl9VVUxoUFhzUllYMWFIUmpUV210RWRiQWtWUWFzTzVxQ3JKeGh6N0FocHV4NTBHdVRWZEgtMUp3c2ExMER1MkJfZzNrOWRUT1hMb3ROZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNdGRuMW95U04tUjIzQlZxbUIzRURyUXJzSURIVUNiT2twZHk2TUZNcm9NOHdKenFMQVZCcjF4aVZPSVJLSy1Qc1puTEVhSm9CSllFN3RUb1JnMTJYem91V0FaQ2xaei1ZaWZVcW9UcUtoUzhCOGdqOHI1cmYxN1NMWVNITXJPMDFRT1JVNUM5UFlVU0taMThBTDJVMVdjd052MjdJREcybVo2VFk?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46038.55833333333</v>
+        <v>46038.82950231482</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bomb squad descends on residential street after 'explosives' threat - Essex Live</t>
+          <t>FedEx just days away from service interruption that will hit customers for 24-hours - The US Sun</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:15:38 GMT</t>
+          <t>Fri, 16 Jan 2026 22:20:45 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNMHYyc3FhTUh3MG0wamUtSi04QlNDaFctT3dHNlJrdVV1SHkwckliNDlsdldxM3hnX0dRNkpUS1RxdGpCM1dadU1RZ1R4c2RkQjZ6WHo5dWx0Z0lkMG1yc3YtUlJYRmkyVGdSeGk4eFQ0T2JYZk1xbHZKRUxpa3JxcVpsY0RTVFJ0MnQzbk1CRlIxdzlE0gGaAUFVX3lxTE1zR0xjazJ5QWx4Y3pqMlFhU05hSkRWdXhMQ2pSYlpnREkxMjYydGRRdENhbU9uZUE0YUNtTGhmdjRXRlY1WXpQYjFhb2E4eDhJdTZGTzN4M1VTU1FtbFhFcjdNbUE4NUdtMEFSSUZQcHA2SktFd3hFYnBVdHhIczJHVEIwdjU4TXd2eFlub2dyd29kZG9jOTZKdVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNUml1cVo3dGF2MHR4amo5Mm16YldsWnFMT0ltTkplbTlCVm9xZ3kyTVdTUXZIZXRVTlFZd0l5M3g4RnBSYmp6Z2pqNFh5N2xjNUZ6UHdqSUlhaG5mUm5Gc2toNmxvaVgwZElyQ0JoazZTVTZaalhPOWVSRjNfSTh3Ym93VUc5bTl0T0hoQ29nc0ZVUVhkZHc?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46038.38585648148</v>
+        <v>46038.93107638889</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jury shown video footage of fatal shooting of George Nkencho at inquest - BreakingNews.ie</t>
+          <t>‘A horrible act’: Amazon bans driver accused of stealing California family’s cat - MSN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 13:34:36 GMT</t>
+          <t>Sat, 17 Jan 2026 04:16:05 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVjRSZHFXcU9YUmxMRjQ2U3Nyd3ZDZURQLURBRVpUMW03aTFGbnVFREtpb0FKTzF3QkQxN3BPTk1Qd253LXBkTU5Wb2hOTnE5NGFDcnJnUTVHdVVETjdHdWZ6NFNiaTZhS3JYRllxR0Z4OThGWHFMemtpNVJ1TUF6bVJSWWtPUWFCRVdkRGR5NGFyQ1oxS2tKNFFmTEVuNFFWOEVUTnJ1M0FOekJrZTNjLVpGRVk4SXJ5VVFRSw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gJBVV95cUxQTUktT19FOUJaTk8teUZyNlJKX0xxQWFnanZjdWZSTVptWndsZmlwM2ItZWttOHhuN0plM2Z6ei1FajNnMnBYdDViZ1l3eURDYjVGa3dxejN3ZmdEZ3hHZGp4cVVDc2Q1aXFIaXh6MXVfVWhfYWhEZF9BdkFGc3MzcVFTYjJidUVVeGh1dmMzOU85bHcyVEdjNUJvZE9CLU1YUV9jWUZSdnVOdXNiaGZGTE43RVNjanlrcHJzRFBpM19qa21ObTR2a1AzbzJUVmpTTjNqaFRWVUMxQjZGdWk1WFV2TEZYckJSTDNka05ZUnlTSXQzUDNRcy1acHJjYTh0N2NxSHA5dTR3YjFLQlZsbjJ1X0RWSDlNUjFHcnZ0ZFJVYm9uempaT2Z0TlEtYTZRMl9EeFhOOXl1ZGJFdjk1T29jdjJiUmlSTHE0WElFbGZNeElRbVJKYzF3?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46038.56569444444</v>
+        <v>46039.17783564814</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Police search Beckenham park after man stabbed to death on New Year's Eve - london-now.co.uk</t>
+          <t>‘I forgive her’: Officer reflects on being assaulted by delivery driver at Vanderbilt University - WSMV</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:55:16 GMT</t>
+          <t>Sat, 17 Jan 2026 00:48:00 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOeFE1d3pIQVd3UVl1RzNETWR0MFFRUUNiWVlObW40SWNFYnZBbXV5ZEFwbUZmY1lxTm4yMWZITWh2U041bXctQ09LakphOU5mNDJUT1dNUldfY3RLMEROTE9xR001Y2xSTFo1OUszQWJwaERITmVzNTFvb0pxV0J6ZzRJX3pPSFBiTjdSNXdwcUlUbDNMY3ZpUmpmQUQxZkwxME45dk1SQ3Q0dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPWW9EYzFfU3Z2WG03WVRBaDd3VGdDUnNDUXprNHlSc25LU0RXLXpnWmJHdmMxVXJqUzY2ZkQ3U1FCOW0zVzd2cWlmUk5xMHBOdU5WNGl6LURRdVFEdGZ3a0c1TUFYWUhzYlBVSEg4Z0NPXzcwMUFKaVdZZFl1b0NzNHFQX01JbmZUMmdKOWcwM19ZOEpMWW9tQVRkZG5aZFRObU00TUVzNzU0S2NLa09COWNxZDdIV055UUhZUdIB0AFBVV95cUxQNWNZd0tCTFZUT1hSMlI1OGdtUFRyczZGd2JTRkRuNWk4U2hqdlhVQlJDb2xydzB0R1pPaFRrbEZUZHdQcFMwVEp3b1F2QzE1MHJXZklsMXpwNU5ZTUE3TnN2b2pVNGdkdjZmVF9qR0JjZU94UnBRSm5BSHFjd0d6Qkkwbkp2TXFCTlZoZXFuNHpyUmtkZkxvYUt5Q2dMRlIyQWJVSmVFelNBUExNUVdneDM4ZFB6cHNsakFycTNaeEFXSmVCbDZOYXAwclRjMGRX?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46038.41337962963</v>
+        <v>46039.03333333333</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Maliki Sharma's family pay tribute to 'lovely' boy - BBC</t>
+          <t>DHL Packstation: Why Everyone in Germany Is Obsessed With These Yellow Parcel Lockers - AD HOC NEWS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 08:49:40 GMT</t>
+          <t>Fri, 16 Jan 2026 15:34:14 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFAzMVJCSzJCWFFmcHpTS2RuUGpjNDZramRiWXJvZkNZNUdqZHRPcjdPcDlQa1Q2d2o3SUhYTmp1NGVRdGloQTVvZ0RqX05sWjNDTzZSTHNsRTNiU24z0gFiQVVfeXFMUDF6ZGxKRkhvcF9yX2htMFp1ZmI0V1g0aXh2NjhDdGtwSzM5SFlhcUJEZm81U3EwUU02dE90aUcxd1p1ZzVEVWZWQ2d4ZkxrbVdURXdmazRSYXk1cktRY3FQTkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOQjY1Z0YxMFIxWVdnTGNwTkZJbmFHUklVYzFKLVVaTjlMMjJBZjROVHo5ejRoM0RYRWttd0tSQkliRTM4Yk1JSlJ0cXl1ZHZ4MGI5SFNWMC1pSFEzN0V6ZW10aFdfVWZqbHlsY3pFNE9GZnlWQmNOM291Vk5vZUt3WlVUcXh5M0xqS1FTT0s0S0lLLW53X3JXdnNIOUNjcFNnWkRlNVhtRzdLSmpBd2lCRUVzVlBHQ0RBRTJ4ZlJ3SXo?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46038.36782407408</v>
+        <v>46038.64877314815</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norwegian Court Convicts Islamist in Oslo Pride Shooting - Devdiscourse</t>
+          <t>Salem Lakes, WI, Firefighter Hurt at Fire Reported by Amazon Delivery Person - firehouse.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:40:47 GMT</t>
+          <t>Fri, 16 Jan 2026 16:08:58 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQVlFjNjNoQ05yM2ZsWUZ4YWlVNW0tMlJrWDdGbGVSMTVwaFo4SHVoem1JTW9rU0lkZVotMFNlOVRmbVdhZTRreDJOT2VBbGUxT05rRnNVS29ScnhtSGd0Y3FvRUFQSm9KbmlCcjVzX2lEam5kdGZpUEgwVnhJWmlwQmdzU0ZSUWdPa05ycnUwSE9aVFlXekRfc2tfNWF2cG94Q1FKSDFRUVJ3eUtYd1NDV1FZVEY1QdIBtgFBVV95cUxQVlFjNjNoQ05yM2ZsWUZ4YWlVNW0tMlJrWDdGbGVSMTVwaFo4SHVoem1JTW9rU0lkZVotMFNlOVRmbVdhZTRreDJOT2VBbGUxT05rRnNVS29ScnhtSGd0Y3FvRUFQSm9KbmlCcjVzX2lEam5kdGZpUEgwVnhJWmlwQmdzU0ZSUWdPa05ycnUwSE9aVFlXekRfc2tfNWF2cG94Q1FKSDFRUVJ3eUtYd1NDV1FZVEY1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOYWY1Q2tZbHJKTzlLUEttOEgxZjRnYmZVTmhoM0tfYUVGMkp6WkxHMVIxeVg4OGtkTEhkcVFteVNlVnVhVlJxTE5QdV9tRFJSZktfZHNMcjNvbnJNdWJkM0VTcFJMUmY2bHA3SXJHVVN3TGZHX3FOejhOdnJXcEtoTzhRTDJmcVYzZ3J1OG81WlM3RldYSDQzOE41czVrRFFXcnpCM0paVUJyajJQc19nT25DZw?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46038.48665509259</v>
+        <v>46038.67289351852</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SPECIALIST TEAMS CALLED IN Explosive scare ends in arrest in Romford - UK News in Pictures</t>
+          <t>Blinkit Drops Delivery Charges in Select Markets as Q-Commerce Race Heats Up - outlookbusiness.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 08:31:00 GMT</t>
+          <t>Sat, 17 Jan 2026 06:26:15 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPYUxCT1dzdDRKbFNGYnpLQmR5dEZPa3M1Tl9iTWZKNzZQeFdPY0pRbjNjbVRZaWV2dFJQQ0dmM1RyR1FQNGFLVk1jSnVPSGFLSWp1UVptOFV4clFhTURnbXVKRVllYWlaT0M0THdMZU90WVkwNWlhNEN3TmhWSDVPRnhYVWxiZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPd0NjdmkyckdtY0g4UDJHNE9lTlBfSmlZOFNyckx1U2RiUFc3YVlDXzNwc2owanJBRzRLeEYtTXZ1cUdaSFlHUldyNW81ZnhCU1ppam9sTmlSc2ZCUGI1UE9iYlNLcDlKWFJxSlFmSkNXT3hVdFJkQnh6a3VhbUNnWUhobkR2cjlWSW9YY2xkdGlBdnlFYXdhTm5KNGFGYjg5N25tbnVIdmFiTVJiSlBscWJLbVVzTHpCUU1IcWFrSGwtLUxNTjBv0gHUAUFVX3lxTE1pOUFnWTFQSi1YNTBnZzdLR3Q2YTh1Wk0yZGlNQjdpei1SMnVfdGNDM1IzUy10N3RldUt0SUJYYUR5UlhLRVI3dTc5bTNmMHJoOGFBMjZ4V1dUQ3dDbWVSeTREZ29nZWotNFB3YVFUWjhOQzU4dTE0c201SERWWVJsZm85VFZkektHZU1VUWcyNmFIeUZDRUUzbWxKMmc1aTRialBkSGlQX0xBTDFaQ3R1NGdfb0xmMlp5ZlJ3NjhOS09EUmZ1Si1vd2lpZ1JIMTJOaVlS?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46038.35486111111</v>
+        <v>46039.26822916666</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>'SO AWKWARD, IT'S TERRIBLE' "Bridgerton" star Yerin Ha candidly shared her experience after shooting steamy scenes for the show's upcoming fourth season. "So awkward, it's terrible. . . But when you have an actor that you trust like Luke, it's really quite ea - facebook.com</t>
+          <t>'Why Are You Here?': Amazon Worker Turns Tables on Karen 'Policing' His Every Move as He Delivered Packages to Residential Building - Atlanta Black Star</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 08:50:19 GMT</t>
+          <t>Fri, 16 Jan 2026 22:00:00 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNV1lZTHNXdXk1c1FvQ1hOVjJMYUJRWnZSV293TUhDMDJxRjJNNzVxYjM2dVBHVFNSUXVTcnIxc1dxd2c5TlVCV2tYSDhWb1l4b21GdFZCNkYzQzZrd1RYd25OY0hhYV9aNWVqTmx0bWljeFllRURSNVR6LURoUVg4dnExZFlZVktD?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNUThRRjNDdkEzSUducEpnRVZzNXM1bE1aT2dxUVRyaS1ySWg5djJTX0QxUEZqa1g2QncyemIydkhpMC15eFREbDk4Y1FoSzZsaXR5YjB4YUQ3V3FIX2ZteEdIVzU5NURFenoxNTlYdDZoZjFqSy1hUlBqT1NqSlBLY3RaaS10X09xNHRrUGpnaEIxVGpiRTl5R3hvNVM1cjJ0MUE?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46038.36827546296</v>
+        <v>46038.91666666666</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Paris R-II Schools closed Friday due to Illness - KOMU 8</t>
+          <t>Bomb Threat On Flight! Bahrain-Hyderabad Flight Diverted To Mumbai - MSN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 12:15:00 GMT</t>
+          <t>Sat, 17 Jan 2026 05:07:15 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQODVJWWpFV1FrQ2ZvM1puMUJvWU1RM2tDN0lfeXplS3BvSEJSOUM1TU93SzdRcFlZTG12eGgzdVo3eWVzM1VzVDB4bTlEejF5WTY5ZlJnOEdKbmszRlhGSjdVeERfSHltb3R4RU04TzJjbllHNU1ILVBZZkw5TmdyTnhwdUNtY0Z0bUhUZFU0bGphREdYS0ZlTW9tbnVfbnBhaGhTZjA1ZHFxODBLTEJ5N2laWVpucUI2UWNUNG1R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygJBVV95cUxOQkxlS0VuV0dXVno1NGtTSkM2bk1hNDI4Sl9ROFBicFJvbXVaYVFMbEVVMlQyc2dvdFAxVENhZU9Tdk4xMXkzNGpQR0k4UXgxVG9wSlBVcGdqVjMwVFB3NUIyNFdpOW91NC03Z0MtRFRsY056ZHUzRjRYbmdjQk44M1d0M3AzamJvcTBKM1ZNOVdMdDBndzdoZ3hSSWhUUlFnTFRtZ3RaejE4cldSZnVabVUtZ2Ztbm16ZW10cDF6TmdCRERuVkgwb19OUHk2aGhUSl9adVFleTZzbjVCcWpfYXl6R2RqOUVWWGNSM0F0VXJPSGgzOUxGeE93RWhCTHB2Wk5icEszVG5FcmdzZG04dzk0bGJzalVmM2ZoVy1jVm5yU080UDU2M3E1UGMwS3F6eUt4RDA4OVNuWWI0bVNuRXRwY1NZNWJNQ2c?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46038.51041666666</v>
+        <v>46039.21336805556</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>‘Nobody likes you’: The frostiest feuds set to be reignited this Open - The Cairns Post</t>
+          <t>Eintracht Frankfurt and Werder Bremen share six-goal thriller - The Joplin Globe</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:11:57 GMT</t>
+          <t>Fri, 16 Jan 2026 23:03:10 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNUWY2bnpvQ0NfRXZXR2dFYzJUMU15NHlaeGlON1AwbDE5UTM5ZjF1Q2pzU2QxdmNyYVlTUW9CU3M0a3RHSDJ5M201TTFDWFBDMnV3Sy1KcmtMS0dlN3pSM01QUGtHUHBNTjI0bTkzU01tR2pVWV9TaHZjSFpqX2puNmc1T01tSS1PeVppS2h2TUxRbWZOcUMwS3pfWFEwd2lpMzRiY3VRQWN5d05RZGo1bHZGVUV5UDFpMGRxVEhFY0hZNUZLYzhwMjJLT3VXUzV3Wm5fTTBZZFpNbHpGV2VtbXlQbDItbjlmamdsM2V3cU5CUXZ6RmZvaEJDV21ucUxkM3dpUEFNNi1EYjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOb0NFZmpoZUlYWGRSZWFtamQzSENldllaQl9JU3dUSXZaQlE4bkZ4WDNwU1YtajJ1QU1YQWl0S1VyTE1wMk53dFRWLUlKdVRZdm9MY2RqcUp6OXJZaDJ0NkFYNUlBenVhaGJUa3A1dGVIdXBlVnhfZ3JQcDJTTjE2cTM0T2Zkalg0c2t5Sm56aUtfbzZTOUJXM1ltTGo2MDRyOUFSUVRibGRlLWxJYm56ZDFEX2FNU1B1MjNvWlpjdkpucmtwYXNnQ3JfRURLZUN2eFdzWWR5ajBmR2c0LTZKc0ZybUgzOE83dW50cXdLRnlfSFVx?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46038.46663194444</v>
+        <v>46038.96053240741</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sophie Turner is Lara Croft: 'Tomb Raider' production starts with 1st look - Philstar.com</t>
+          <t>Knauff snatches late draw for stuttering Frankfurt at Bremen - NST Online</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:26:00 GMT</t>
+          <t>Fri, 16 Jan 2026 22:49:00 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPTXR6UWcwdWlkeW1FOFZPdHdKU0JJaFlTdG5EdTN1SXM5YXBDemgyb2ttaGZBeHh4YWFRZHZfT1VTc2NDN1RMVDZkTHhmRkdGUU1aSV9TYzdwMTN1ZzRrZGF4eVdrYjRoMTFGWjBNbmdtVGZzU25faFdxcTNWcEt1eFFUM0Rha0VHLUZYUUZkUTNoT0xhb0UxU05HbEpKdzN6N3FLczV5LVRkMzhuS0V2dEgzVjdGbUJQd3YxVXN4Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE1pOExUazJEVjBDMHV6R0NIS2t5WkQwUWc4X3BvaXNrUTlNU01SUk1iN2FOQXNyemZjcngtNUdrZG1UM09mcHRaWEJwOXRlMXBkYnBUUg?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46038.39305555556</v>
+        <v>46038.95069444444</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ukraine war latest: UK position 'of destructive nature', says Russia - but Moscow hails 'step forward' in Europe - Sky News</t>
+          <t>Report: Bayern Munich join race for Chelsea January target, potential deal could be worth €66m - chelsea.news</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:17:22 GMT</t>
+          <t>Fri, 16 Jan 2026 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNd3lrMnZaNWpsN3NaM05XaFF4dmY1cE5JSGlCWXRnN01ubnphclRNc1l2eWZPdDc5bURZcmg4dEllaWhhbWdZTVBjd1dZUWl0aW0tS1dkMmxrV0JtZHdFNFJIR1JNZ1VlcDBBeWJUdjA5ZW5vN3d0d0l0c1RqNEc3Nmg5NUM4ZkNRTmdLOU1EYU9lS0lCNzBybWQ4TzhEU1dEaEVYcE5RcTJ5S3AwV3IwS1N5ZWFqb0k2QXZiQTZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1uRGZNc2kxN0ZIckNNcWVXajdwUXFESm9nYmx0WlRsRjJPNUNHVktYdlBhSEJzU0dzTkdYak4xQ1hQeU85aUxEMFVMQWRQbV94ajhJSDVfOVMxSFQ0dHY3QXAzcm5SRDc3QnBZUWluQ3M0UHJqZnZheHhKbkNTZ9IBgwFBVV95cUxQRTBCdksyQTRPa0Z6MGk0TzNUamNjRWMxLVdacUdsM0VSV28wTUdrVllBazNXbjc2NnpaQmwxNmVET2p0Xzhxcm5aZkVKOEZjdjVfYjI5MjJyT3hlVG9WS3Nmdlk2Y1lrLW13b3Z3dzktSUNmLVhYY0NTSzc5QmppRkhrOA?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46038.38706018519</v>
+        <v>46038.625</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Miller and Cincinnati host No. 2 Iowa State - FOX Sports</t>
+          <t>Surrey's shoplifting capital revealed by data as retail crime continues to spiral - Surrey Live</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:43:36 GMT</t>
+          <t>Sat, 17 Jan 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQUU1MbDdCdzNMalBrQVZDVE03NEN2dEFyMlhpYXA2NEVzRkZfbW1FdkRhdWZwQkFwMmJjSUEzTFU4T2ZCWG52eTU1cGpQT3RkV3ZEaTRrSFZIV0hzOUhLUEJfamJTd0puMVBTSDE3OHR3RmV6d1F4QzVRNEFTTG9xbkFQN0cwN2ZK?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPejRadEQtbFpXLXdxSjE3TWozb0dCTzNfZTRCSC1tQXBPdElKSk55WkdNZ2FBemFGMDhqR194NjdfM3l5VW1DMUlmVTlyZEZGZ3FBUzVjYWFKck5jMjRrRHF0ZW9rUnhXaTVURTFOdDQwdDFlQzNhOFJadlgtSm4zb3lsRUd4R01sak54VkJUckNjc00tTFlKa25EQdIBoAFBVV95cUxPWWFVMWpXaTQ4cC0tUmJlaW5wNDFJcUhzMjVwVl9MWmFBZGZsdWdGUWk3X2s1M2pNdFdEVkVsNWxmejhJdlpNNGRHSEVycXhUbFVod3FOMnk3eWZBbW52eFFJOEVUaVQxQldubFlrbHdFYUdaNXREMWthamc4cVZwRmp5LWpOZE5xT3U5anFEUmpCVE0zVEg4SzVxbzhfRVYx?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46038.40527777778</v>
+        <v>46039.29166666666</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Crvena Zvezda rallies in fourth to claim win over Milan - TalkBasket.net</t>
+          <t>Calls for CCTV grant to be introduced in Wales amid retail crime concerns - Yahoo News UK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:12:29 GMT</t>
+          <t>Fri, 16 Jan 2026 23:30:00 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOUGc0U21jckFkQUhFeWl3S0NQQWZWVnE5cGRueTd2bTBpNzNmV0lGNEt1MXd3TlFPanZiT3J2VUpNQVZab244YUJpc1czbWx4YXM5YmZ1YzBYdEZVczNUZlFQYlBmeGlxdDcxY3psOEh2dkNpUmZNZi1fM2R5RDVUNDBPcFd0VG9LQU00S3FqRHBkSTTSAZsBQVVfeXFMTVd0QzA1UFhERFozcndjdFNjS3pETDAwZ3IwN0RPdm9yZWRwTVhCYVl3N3k4Y1ozbnJVNWIyNnJCdml1M2c1TEtYZHdEckp1c1U5dFN1ME9qeENpRGlfUXhrVG81UkF1dTFGODB4SEk2WnFIRXU3OEFLRUhuZllLOXQ2Q3A1OUJnRmpxWHJwbDV4eWUzODR4WWoySm8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBELUxZMkpxMm5IN0hDb254eC02c1ZyRzZTc1RBQlQ0SlFrTXgtRG5zeEJqdVRfemFBTXZFc1BFRjIwZ0J4TjdnYkpFWEhtQW5lbzdBYWtlNGZGLXdZRHFPSC03aU5mcmRpZnowUVlQUElHLVQ4X1VqSTJESmt2LXM?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46038.38366898148</v>
+        <v>46038.97916666666</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Maccabi outlasts Zalgiris in thriller - TalkBasket.net</t>
+          <t>Fed meets West Midlands PCC to discuss retail crime - Better Retailing</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:06:41 GMT</t>
+          <t>Fri, 16 Jan 2026 15:27:21 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNSGVydm9UX2doMmJyeUIwWFVlSER1MTNLZ2pRcDVRNWhQOUVpdllZcUpzbXhrU2QzZ0lKTDExSFhWNUxhQV9wQlBpdDZSaHIySm5CRUhnSVdjZ25aSHp0TG4tdWhONFhjcHZsQUdhOXhBX1lLbzJIc2ZFd3JEeXVHNjVxcGlGYlN0Uk9oV2NRRdIBjwFBVV95cUxNSGVydm9UX2doMmJyeUIwWFVlSER1MTNLZ2pRcDVRNWhQOUVpdllZcUpzbXhrU2QzZ0lKTDExSFhWNUxhQV9wQlBpdDZSaHIySm5CRUhnSVdjZ25aSHp0TG4tdWhONFhjcHZsQUdhOXhBX1lLbzJIc2ZFd3JEeXVHNjVxcGlGYlN0Uk9oV2NRRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNQXdnY2hlVXNJS3VmdUI3UlBrM1pJQmZoZ3JTLU9aaVdaUmNodHpiOUVSVVJZWGxzdGtRc0sxRmhfdVZPQm96SmtHeEl5R2NYbV80NmlmZ29YSEFwVDJ2OWtoanBuVi1qT0ZzWGY5RDh1RzJpMFFXRFRQOFFCekdHcGJDWHdBYWdBcEdnag?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46038.3796412037</v>
+        <v>46038.64399305556</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>What happens next in EU-Mercosur trade deal saga? - Reuters</t>
+          <t>Three men charged with theft offences as police continue to tackle retail crime across Dudley - Express &amp; Star</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:56:53 GMT</t>
+          <t>Fri, 16 Jan 2026 15:31:06 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNVkNXYlhnUEdQdnRfaEhGTjJHQTJuUzJLX2szUVJYM2hPa0FBS2s2QmNCUDFPc2hfcEttLVZNT3pKVTlNbGw5NndYNVZCZXJCeHR6NndPM2tDaUdtaERXeG5jNDFIUXAzeWdodzdacTFGc0gwcXNVYTh2alB5SlVIMnpwaHhjS0pFWE41ZFJqSUNfNTIxOUFQNlRGZG9nV1h5dVMxMk5uS1RBTXpJbU8teg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPdWd0T01LUFVnRDRkTjhNRjZHODAzV3BNZ2R6UmFMNFk0UmU0VW0tN2FGdUZMTDVYdHhXQWJVaGZtVkREUDBsTVhpTldwYU5xREE4Y1psV0M4ZFNiSzJpYzNEb0kxMWJIeDVRemx6aGpKWHpIVnMtYUFvZW5TQ1JJcEpMSmVkNU00dlpVVGkyNXJnNllDcS1sU3loRHJyS1FfLUNzYnFNUFpQLW5QYkZhRUlwMDRxM0x5Szl2RU9HN1VMdjdCUmxicVdNN1lXNW0yMFFkU082QlljSVpLbzNyYQ?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46038.49783564815</v>
+        <v>46038.64659722222</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Foreign Minister Reacts to Stabbing in Germany, Blames Migration - Hungary Today</t>
+          <t>‘A real deterrent’: Police pleased with response to retail beat team - ThePost.co.nz</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 08:31:21 GMT</t>
+          <t>Fri, 16 Jan 2026 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQT1lJLUpMUkROeXZFLVR3S1FqdHFvLU5rQ3RYQmU0WmtfbWJkakEzWG00alhCZFMweWVxYUR1MGw0Z0JvVmpkSVE0ei1DYVJvQkVxUTNUODRQNXE1RFZpa0Npb2JBYWVIUnVSUUFSQjZ5RnNvN29RamZPdVg5VjlsU3BBUXd6VUlDSWJmZXRSRDBtZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQWlE5VG9yVkcwUi1fQlgxdmUtT3hSeEdVN2lZVDBzQVY2eFFGcHJKWldqZDRZZGU1dDlUNGtfUDFWdnQtYzMxVUNyb1Y0WjhmeFQxdE50VFhDeXBSV0VOaXVVWklJZkEwRVNVeXotR1ZWbjRYb0poZjNkbENLVHBtc0xyMUVTb0M0b3RiOFNiYks0cHBFMS0tbzU2ekNsUExrMDlMdzVnUFFTeF9ObkE?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46038.35510416667</v>
+        <v>46038.625</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Romanian Murder Suspect Tracked and Arrested in Bali - Jakarta Globe</t>
+          <t>Jewellery shop theft accused escapes from police station - Times of India</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 13:25:00 GMT</t>
+          <t>Fri, 16 Jan 2026 20:04:00 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNbWkxd3VzclJ0MUtPdi1OMTN6ZzRuekp5Tjg0NUFneUJIRy1RQ3Z3TldqTnlyXzVNRGs5RjVSNUExTWlCbnRVZVZFdzFlVFJyRFBwZVJrRm53aVBTOGJ0Tlh6TU5lNjNBLWdqNGhkaUpmbzloY2pDTXFHMV9FNjNoNGJNdkdQRmlW?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOVHhNUGVOSlRBTDdYTjhCZ1RxMWNXekRZRi00RGZSVy1GQ0EyZW5sWjdtdzdPMGVEMWdxZGlvTEhIdmJfWEVvLUNpbUVraUc1X2RWTy1VSUJZcGtVMWlWbW8zallwS1ZaUXExVnpFdGNUZGdfbUM0WXNqcjZjRkR5OTc2ZjJZMV9oQV9KeVFSY09pRUZvektIakxaajQ0QjhRa2ZVLThUQkNNWlpEUVFBSkk0UzFmdDdfRld0VjZmZDNSN2w3SnlicWNn0gHPAUFVX3lxTE5VcWtWRTlJVTlHbWFZR2hNZkhkVlJJR1ZFRWJzREU2OTZETUxIMEZoWTFVMWZKOUpCNzFzQldmcU1DazVTYm1jX2oyTWZpS3FhMlV5OXJ4VWktMzNGYloyTHM3MmpQR0ZIdWxBaW5kei1OR29TeW5sTTdaQWtHekpSazkzNDl1Z0dUTUl3T2ZWVjZEdTE2U3ZzWTBGenJiZGVlTksteUN4M3A2Qk13SDZYTjJ6bUZMeEQzWEF3T3RqMGlfLUpQOUMzLTRDY3pISQ?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46038.55902777778</v>
+        <v>46038.83611111111</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Circumcision could be ‘child abuse’ if done wrong, UK prosectors warn after deaths - South African Jewish Report</t>
+          <t>Man banned from ASDA, TESCO &amp; ALDI stores across Lancashire - Lancashire Constabulary</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:26:48 GMT</t>
+          <t>Fri, 16 Jan 2026 16:15:55 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQOW1ocmtLNFByVGdmVVBnWUsxUlBDSG1RUU1WNFJEUkQxWDlkVFp5cmpOSHNGNmEyTjl3N2RfNzlPXzZoaER2ejZQeWt5ZWJuMXFMSTBFUmR0MEhWeHFHWEF5OGZhMGtmNmpRaGVEYVhXWFhxY0tiN2h1WXhxNTN6WWhPRGJ1X0xUbTNSUkxHcGVTSjExelplZzJkQ1A0cDlWYTU1S2IwNWdMOFHSAasBQVVfeXFMUDltaHJrSzRQclRnZlVQZ1lLMVJQQ0htUVFNVjRSRFJEMVg5ZFRaeXJqTkhzRjZhMk45dzdkXzc5T182aGhEdno2UHlreWVibjFxTEkwRVJkdDBIVnhxR1hBeThmYTBrZjZqUWhlRGFYV1hYcWNLYjdodVl4cTUzelloT0RidV9MVG0zUlJMR3BlU0oxMXpaZWcyZENQNHA5VmE1NUtiMDVnTDhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONVNnMkUzNGhsbmcxdDV0S0lRcW1LUlN5UTl4YlhoZVR3TDZFa3dxbVlRbnVMQkExRENzbzY1WWtfSEFxY2tQbDlkQk5QSllDc2JpWERzdmxCRjJXQ3R4ak1QeTJBbi1CSFhWNzZUS1M2MHFvSTVGZ1ByVHlMYWl3bm04QW1LQ3hIdUhONlZweTBJR1RGYlppVEI5TmQ5STlsUUNLUGFUNnBSZXJmN3c?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46038.47694444445</v>
+        <v>46038.67771990741</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hundreds suspended after drug screening at Antwerp port - belganewsagency.eu</t>
+          <t>Grays: Shoplifter admits 11 thefts - Essex Police</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:00:00 GMT</t>
+          <t>Fri, 16 Jan 2026 16:40:00 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPYlhud0VLQkdvUy1rcHpKN3dQTFVqR0VKYlJvU3JVMjBNV2ZlQ2hEWmNmU1JGMVg1bGU5SG9FRENnNFNRaU9Tcm5XSUFhV21uaDFiNG1pcnhvdTJxY2ExU2YwOUhsV2I4OTVfYzZkVXdUMC1iYkZkSkp3ZmJnU3B1TTdKR3ZtWUkxR2FTNXotYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNblFFVktUWmNrd1JjLUNPaUNKUlRyazdUSThVT2JFM3hVcm9acHRMVUEzSm1iZ1FnNTJTNlVZcGpuUENxeG00LW1HcVVLRGM4Wk1OTUFGUlFsNU5pTEV1SU11LWNfaVd1YU41d0FyMmRDaVp0ZWUyREFYSEFoRklnX1N3X1A4ajMxM3FBNUViLUJJalNuLXRZVk9ESFo?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46038.41666666666</v>
+        <v>46038.69444444445</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Voer en Dijle Police Zone Opens Modern Facility in Tervuren - Brussels Morning</t>
+          <t>‘Precious’ family heirloom snatched from 98-year-old woman in cruel distraction theft - GB News</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 12:20:49 GMT</t>
+          <t>Fri, 16 Jan 2026 20:43:44 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPYTJmNGdqMUdSWWRNT0wyTkp4N3o4MmJaam9YUmtQUHNKZTVnSENBdlE2ZXFZYktIRGR0c21wcjZGTFBoM0otQVZ5YmlmS29ULTFhS28wX3VUMlByNGNWTmVKb0pWWWVqb1lLRjRaZWVUOS1sbFVBWTdjaERwNXZ0VUYyWml2OHJ5cWlsYVBYUGJIdzFJMUcybVJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPTkhIY2pFUkJqc0lITFdDc2p2ZlRYNkdfZkNiNlR0X2JZcjh6eUpKZHJoOWJGcWZ3cmpZREV3YnBWRTVNOG1INXhXXzhhTjBTenFydF9BYVRlbjFfTG9kN1Z4OFpwa1RCZUR3MjM1RG84b3ctbXA4LWVSMTJqTGswejhpeFpjODlPMy00OVdSTQ?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46038.51445601852</v>
+        <v>46038.8637037037</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>What happened overnight? Police blotter report for Friday, January 16 - Newzjunky</t>
+          <t>North East career crook who already owes £9k to courts stole '20 sandwiches' from Greggs - Chronicle Live</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 12:00:37 GMT</t>
+          <t>Sat, 17 Jan 2026 00:31:00 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNOGN6MUFmZkNKNnBzMHRvaTNoeU5YaWVDakFJUng0dzNKbC1mU3U5UnFmQTZTZy1rYTdpVXp2Rzd6R2lIbVFDZzNSOFk5R0NPbjNpYXJnUlJSYjNpVFVMRDNPb1BUY2Y0ZzdkV0IxWDVWbmFkaG84TkQzU3NSZ3NiMQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOdExYanBQNGptRnhYMUZ3ZWdkVFdHVjctRkVXRUJiR2x1ai12bXBRQmtJOGFvbWx3U1F3SDRxTEFabm8xZVFFNG1XZDljOXVRaDhpV1BybUpNVVpOcHJMRDBRSkJ1YlJqR1pRYi1fbHNzclZiNjltWmVEOHU1S1YzWC1vVjN1Tl90akFsUW5FdFFmcV9rSGktWNIBmAFBVV95cUxOdExYanBQNGptRnhYMUZ3ZWdkVFdHVjctRkVXRUJiR2x1ai12bXBRQmtJOGFvbWx3U1F3SDRxTEFabm8xZVFFNG1XZDljOXVRaDhpV1BybUpNVVpOcHJMRDBRSkJ1YlJqR1pRYi1fbHNzclZiNjltWmVEOHU1S1YzWC1vVjN1Tl90akFsUW5FdFFmcV9rSGktWA?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46038.50042824074</v>
+        <v>46039.02152777778</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Two-vehicle crash shuts main Lymington road - Advertiser and Times</t>
+          <t>Police probe incident at Essex butchers shop amid 'daily problems with thefts' - Southend Echo</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:26:00 GMT</t>
+          <t>Fri, 16 Jan 2026 20:05:24 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPY09pU24zYjFlZTJGcU94SUQ0bVFjaVlyV3dpek80TVFMdDQ1QjRVMG1aN0xnUDd4c1NtR3dyR0JGOVpLVWpWNUIzdUJqRHowc0gyZzczYjVlYkY3ZTcxcXhZT0tPeC1yQ3Z6VU9MblhzOXNPelRVZktSLXpoQmJYZUVLSFJBRUZtcC1sYTZNUTg1QkQ2S0xMZlNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNSlgwNVl1d0hwX1BUSnlMQkdmWUktODB1UW1fX3BjM0ViSXhBRWVOLTFReFVoeXloMWlZRHpvYTUtWENpaUZYRHB4aldlcUdsNFM4OVptcWtHZTVlUXZpYlBWVVJVZ2pwWU5GT0F6a3Q2bWk1VXBsRmZTWnhEY1ZVX1VsV3ZJVHdvcmZwOGxTVk1NZ1dZRVo5azNhY1U?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46038.43472222222</v>
+        <v>46038.83708333333</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Murder probe into Coleraine man’s death continues as police granted extension - kildare-nationalist.ie</t>
+          <t>Las Vegas Retail Theft Rises: Organized Shoplifting Up 11% as Police Target Crime Rings - Country Herald</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 14:02:51 GMT</t>
+          <t>Fri, 16 Jan 2026 18:10:58 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPWjZNZDVUYWEydWlvdW90X19fMnhLcWpXNXZsMGlEbjNMU1djRUl5WHlCMksyTlZUa0lQQllSbkNSdHBjYjNad1Z3SE1Gb0FwOTc1WUJOOU16VVFCRHNBNmVqd2sxeGU0NzRfQ0sxZndDWDY1RzB6ellvTlJZTGliQkN3YnJ1a1N3Mmhjd1NOZVRTeXRFUHVsNS1JUDVFVEJmelY4ZFFLdmxOYU1hc3lYTnJ3Y285eHNSZmwzajU2RzNScDl4SUdIa2VERW4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQTXRlWnVCb1BzOFE0WFB4MHNyNnQ3NXBVa0VYUVlfTi1mMGxPcmNGVUxJemZrUHB0YnJlNTI3TmJ4WXh3a05qbmwza0JpRkhXN2xmNUp6dk1lTVZjcUl6VTgtVEd1WnBoOEJXR2J4QlpRcVAxSWNYWTlvQTZ2cXlhQU1pTUxEWGVCLUEwXzg5dGUtc2pncnRkSkx5Yzh6MjR5bUpHdTNoMGJqUkUxRC1ueDdnX1p4R0NX?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>46038.5853125</v>
+        <v>46038.75761574074</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brian Flanagan names Kildare team for O'Byrne Cup final tonight - Ireland Live</t>
+          <t>Bomb WiFi threat forces emergency landing for Barcelona flight - Murcia Today - News</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:34:11 GMT</t>
+          <t>Fri, 16 Jan 2026 16:48:09 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxORVdVUndrdnZ6LXluLUk1VnlVckJZQi1NTTVQcF9QdklaTEpfUExNSG9VMk16NERQUXl1RjBRRzlrMldHQUliZFF6a2w4SlFMa3ltYnlmbENqVkozSEsxamE1OGlyWndTU0R3RGhmdkk4TnpnSmdCdVg1OVlKeHJGRTZ5RFhzSklZSjFteFBWeEJUMFdOa2FfRC1haThzbXJlaHg1RTJZWUc2ejd2Nl84SDJUbzhRdWdTTUQ5M253?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNVHRsOE1oTVdtOEdKcU9JbDRJQ1pBVm5vSlgxZmJnYmdLTElaazVxZG9GbjVTUWI0RmhfaEZXTXVlNWZJWm5aOW9iV3h3aEtHckRuSmdrS1dyX2ljZ0xlcGRDdGxJcWdlWFJHM1NxUnUwWU5nbjFkYmVPa1U5R09LSEFDdFVwOTJ3Z3lOT2ZwSC1qcEtFMjlqRHFhM2xKMkRHMmkyT1dKQ05SQXVmUl8ybFp2NUhOQVliTzdlUm1B?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>46038.39873842592</v>
+        <v>46038.70010416667</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Live Coverage: Real Madrid vs. Barcelona in 2025/26 Euroleague - filmogaz.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 20:58:54 GMT</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiRkFVX3lxTFBMZ282cko1NkdRLUcweXZRUG14OHJYR2ZoSy1vbjRabGhZOWtPTWlQalJ5aUtuRDRXSnhDSl9GS3dTOUJuUUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46038.87423611111</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Passenger jet is surrounded by cops at Barcelona airport amid 'on board threat' alert - MSN</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 06:23:25 GMT</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3gJBVV95cUxOSXY4UnMtU0hUb1M0YWV5bjZNX3VuMnY3OTloTVJlNFk4YmQ2RTd0X2ZKTks0TUJOLTdZM2JJa3ZUaGpBS0R1U2xENXAxeDU0NzQwTTNZZlhQRDY2ZENDUWZRWU9kWU5RN19pSUVLeDFiSkVTU2I1bDhhNFZ0cnEzNFJHelVacWRwdHNoTTBjMDVmRmhMemVYUFdJLVJTTlJLbDEtWF9ZYmpnRjlHZDJSM05zc3M0aGI4Z0R2OUJINmxHUXdqdUhUbUcybWg5VDQwZXNwYk5ERm9SN0gtLWJxa0dMbFp6eDBnb3lmY2N4OVMwR1BPV09Wc3BUVVVaLXkyRkg0eURad3cwSEkxLXMzT3pWajMwMGtic29aaTkwVUlIQnNnbDctWXp3OWgtTGZxV25tLW5Nb0RFR3VSYkNpNnVHN3l5T2pBSU5zVDN4TGVhdE1VRGUwOUlhYkFJdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46039.26626157408</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Spain and Portugal Ignite Tourism Explosion in 2026, Outshining All of Europe with Record-Breaking Growth! - Travel And Tour World</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 06:52:38 GMT</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPT0ZlSWYyYk9uYTFPVW4zSWtrWl9meWZpX2p4MDVOZWJiNlo3ZmgtdTBqWGpnTkJzeURpNU5ic1BDalcyRVd5X1M0U3kzckFNRTl2M0liVXlWZ3UwZzV3cWoxYmptRFR3a3haczM5ZWpNTG1GT1pPZ0swOGNRX1Nvd1VXZUkyUUVhNXI1SmRtSF9qbGU4TGtLZlZmbFJJUHlzRHhON3NwVW05eTVvYzZEeUtqUFR4d19aVk9sNno1TnVWTlhXc21YejlmaXc1Q1ZxVlp1eVZGTURjUzd1dHpTcmVrR1IzRjF0?oc=5</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46039.28655092593</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Xavi Pascual's Barça does not repeat the miracle - Diari ARA</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 21:34:29 GMT</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQZFlkSWVIY01mUG9nTkNEN0Itbk9QdUxkTGRVVlY0d0JTV0xvS0xiSUg3ekFueHJTODhuY3Vael9Semxkc0FJUGpmWkRHTVp0WnViUmhIUnZjOEFlYnNkTmVjYm91UTRfOW5TZl9UeDRPRHRINFh2VzhYZUFieU94WHA2eWIxY2fSAYwBQVVfeXFMT29VeGJ6c3kyR0o1Q2plS1I2QjZQYnJKRXFXTnpRTVFwdW9fTGNYZlYwQTBwRDgzMkM2VzJYRkZTNzB5VUpKTWU3eUFIWjYxd3Y4ZU9Xd3BBbS1MTjUzMmE0eTdON3l6ZG00ZFZ4N2Y0V2ktM2oxRU1zQ3pLVlZoZFBMVjhBeXhxTGtNNy0?oc=5</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>46038.89894675926</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>For two nights only, Barcelona will be lit up by the thousand drones of the DroneArt Show: information and tickets - Barcelona Secreta</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 16:30:56 GMT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPT1F2TXBObGw2T3Z1bi1RUmR4YnFNLVZSV2RveU03MkQ5QnFqbFl2dmtsSlpwRjNLdzItXzlwckF1M21sbnEwcXJRbmp1YkZZY3lvVnNUTWVPUzNlLXpoNU5PMlphaVE3WGh4TnBpZnRvaUx0TVp2aUZaN3lHeWJ5OERaNA?oc=5</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>46038.68814814815</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Real Madrid plotting ‘bombshell’ Man City coup amid Jurgen Klopp rumours - The Transfer Tavern</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 15:06:34 GMT</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQTHNpWE90MGcxYVFPSjVNTGYtMXBRdGIwdkMtcUQzT28yeVluWkNlSHg5MWNTUzR4Y0lteHFsdTRfQ01QVUR2cy1sdi1YWVlNV2xPTlE5UXVaNkVJQVBCWTV6R0Nna1VScXF1QkVpb1E4S3F5NUlKRHpjNkpkSVBHLTNoZF9ZUGtpUVBmYlE4bVUzdUh3ZTlyUjBYTTVNcHdZN1ZibUhoUEZVd0pTUFV2X1dR?oc=5</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46038.62956018518</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Barcelona’s Big Mistake by Not Signing Luis Díaz: The Best Signing of the Summer - beIN SPORTS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 17:58:33 GMT</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPeWhnbmc0Nk9BMm1WeGQyY2d2ZWlIeTlscXBJeUFLQ0s5T2JrMVdTVkRKTmUtakZnRG1yWWxzQ25PSk9vOENjSXRpdzh6OFp2TDRrQ1BuN3JXZDJGcnhJQkx5aWd1Q3JyUnB0MnRBaGd2SHNpZkRoeXBvaDhPWEdoRV9Nd0N5ZlE3bXFzaUJUVzNuNEV5OERjODFxWGUweDl6eEZwckRmdjlNVzZTbVJ3SWNOaUtJNjB4Q1RLZTJDVTZqTXpGbmIzMjB0N25FaDZsV1dRNlBxQU9PZVpHdV9XVTQ4eWNzREt3c09v?oc=5</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46038.74899305555</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Spain records 60 % fall in irregular migrant arrivals in first fortnight of 2026 - VisaHQ</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 23:02:26 GMT</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNcXEzUzVvNGtzUEtxT0dzSWEzMk1aVVhVRVpOa0kwRFJCTEE0NHpKUzZpUzVURTlPWTlpRnRzdU4zaHkyNFBNX0lwVVdHT1Bkb0FDZFRXWjE1bUVVRWxlazFZSlFqSHJ6cV9HVkFVOG5sV2FrUEk0WGJKVXpLc0tzRkZpUV9aVmt1SGJIcm1KWW0ybTJScWdfNHlWclJMYm9jODA5UHFkeHM5dlhtNDNRUEdlTVEwYzNxcTVYR3VR?oc=5</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>46038.96002314815</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>EuroLeague CEO criticizes NBA's ambitious European plan as a 'bit of a broken record' - ClickOnDetroit | WDIV Local 4</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 05:10:33 GMT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNeGN3SF9IUklxQ2VOeWRSbXZMeFhtR0lHV0RmcUdCbG5KTVZ4dFFieW55b2JMT3pGS1VVQ0VTb2hBemFhSV9YMmdBelFRMEw1M081Y2VTVEFPRFdVdWoxTjNKMUx4MlMwV1E4cXZja1V2LUVWeVdFaDFEVl9WaFJwUTZLWURGblhKWU44MHBtblV1LVd5LWYtQWhObEtSU1NnOXYzUGVVNE9Ga3IzbFAyMS1hcy1nSkh2bTZYaE1lSElkYTVVbXhmV1pDWUs?oc=5</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46039.21565972222</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Dembele scores stunning goal for PSG in crucial Ligue 1 clash with Lille - spotted - Tribuna.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 20:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNUzlsblQyTEZkSExzc0tXemgyMm9iVmMxNFhjVXlITFFLTklwQmRSUkdhRTlfUHVYQXlKTVZRbW0wMmhCNks3VGw4MlVzaTVZZEoxalBFT0pLZWZtWks1azhlUGtibUR1bnZWYUJ0R1NONEFuM0hZejdFamRZQTEtbjc3b1RRM0VSdHFqSDE3WENkN0V3cS13ZXp30gGaAUFVX3lxTE1TOWxuVDJMRmRITHNzS1d6aDIyb2JWYzE0WGNVeUhMUUtOSXBCZFJSR2FFOV9QdVhBeUpNVlFtbTAyaEI2SzdUbDgyVXNpNVlkSjFqUEVPSktlZm1aSzVrOGVQa2JtRHVudlZhQnRHU040QW4zSFl6N0VqZFlBMS1uNzdvVFEzRVJ0cWpIMTdYQ2Q3RXdxLXdlenc?oc=5</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46038.87152777778</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Greta Thunberg Flotilla Incident: Drone Strike Or Self-Inflicted Misfired Flare In Tunisian Port? - AOL.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 19:59:45 GMT</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNNWFGZU13NE5wVTl3a3RCRTU3b3h2VWw1b0VIMTJCTGFYTjZJVU5Pa19rSnlmTnZULWRXU3QzUXlLV3ZrOGVyeEJoRkk0TWRheFMwQmRhNWpoWDRVLVllNndnVGJ4UExkRnhCd3hhVmtWSWdzRlFfd3FwMnBuUzh1M1d3SEs?oc=5</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>46038.83315972222</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Klay Thompson could join Luka Dončić and LeBron James with the Lakers if he secures a Mavericks buyout - Mundo Deportivo</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 15:24:34 GMT</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxNNkNjYURJQzhvU2tqOHE5UjZYTzc2MTgxTzhuZVF6T0dGRHRlSVkzbXk3aFduRmlGQ0wwXzN6QzJheVNXRnFpdjNKNVczeGR4S3BJQi1EMjVDVTE1Ti1hWmJRTWR2TGZnaFNVeXl3aW1ob1B0VVBQOTAtSGNJTFJBYUNWUWNwR01jTkt3MlZWdElvQURFNGN5dEhPWnd0c25XREdRMVJMdEdITDlEVVVlYmdzNE5zUHFmRWh0UmtDVDZSQjZYczc4NE9Vd3RYNEpiTUFiV2I0NzFDa2k2LXNMeXdDb00wVG9QbU5IdDgwSVQtbTByQ3l2bGtNNmXSAfwBQVVfeXFMTTZDY2FESUM4b1NrajhxOVI2WE83NjE4MU84bmVRek9HRkR0ZUlZM215N2hXbkZpRkNMMF8zekMyYXlTV0ZxaXYzSjVXM3hkeEtwSUItRDI1Q1UxNU4tYVpiUU1kdkxmZ2hTVXl5d2ltaG9QdFVQUDkwLUhjSUxSQWFDVlFjcEdNY05LdzJWVnRJb0FERTRjeXRIT1p3dHNuV0RHUTFSTHRHSEw5RFVVZWJnczROc1BxZkVodFJrQ1Q2UkI2WHM3ODRPVXd0WDRKYk1BYldiNDcxQ2tpNi1zTHl3Q29NMFRvUG1OSHQ4MElULW0wckN5dmxrTTZl?oc=5</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>46038.64206018519</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Bombshell! Shock exit at Barcelona: Dro Fernández (18) leaves for €6M, he has already told Hansi Flick - madrid-barcelona.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 16:48:00 GMT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxPZ0RZdVAzVER1ank5MVF3N05ZN1dkVU5GREVOMDNjWnZjbFhmdGJOV1c2RUQ4dTR1UnR6TkhXMXdwUjAzZFJXMVFXelU1Z1gzZHB1NzItN1dSZm9nVjQwVWdUU21icW1pNHAyRXJBZzFmMlo4QmY5b3lxTmpMVTRPZ21OLWN4dTZvaDRIUk84c1A3cmRtaVlRaEtmTWRoNUxGWlR0dXRJWUpheWh4Q0Q2OFR6ajB5SUtPeEY5c1JMR2ZCMnF2b3p3V2hfd283Y1BraThGQ2I3SjdUTE5FR3ZCWTVPWDM5RXRob0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46038.7</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Julio Iglesias accused of human trafficking in explosive claims - capetown.today</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 17:40:13 GMT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOVzU1ZTFIbE1Ic0N6X2t3T1lMVTY1eno2WGZQMm9TeXN6b29DRGpxQXY4aGFLSW9mMXRHRXVRc1pwVE1iU1dhazc4SVZfaEdwb3M1RVZRY2o3LXBQTDRUaEl3LU5WMFZuOVIxa2w2RHZtMDlyT0JHQjJld3RKQ3c0eW9fYldiU0RKUndDaXI3RFJ6QnBtaUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46038.73626157407</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>FC Barcelona, Valencia book Copa del Rey qtr-final spots - The New Nation</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 18:02:00 GMT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE90ekY0TmNYX3FFQ1pEUU9oTWhUTjNPM3Y5MzQ5SGxiT3YtOHp4UGRWMjZJdjR2TkNsbllpTmQ1enR3QXB3OFBmcmhZTmJRNGpr?oc=5</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>46038.75138888889</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Mbappe takes a stand: refusing Real Madrid return until fully fit after knee injury - motorcyclesports.net</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 01:13:32 GMT</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPa0ZHOG8xMVpDU2EtdVMwd002SUdXM3JCTFBMTzhrYzZsVGNDVFNSaDdRcVRXSUdJX1VxaHBZVnQ4RGN3TWV5a0hLZ2lvMm5CX3VCdDFtNzdXTy1mSFBCY3J0RzBYdWM0RWtRMVhmcnVvMVNqWGZySUdFbnE5UUNvT01aVW1JWG1YNFZzMHo3bWdURmI4dV9uNlNWejgtN0QzVFYwWFlMa3F3TFM4azRBWlJSNWdrSWY5N3pn?oc=5</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46039.05106481481</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, Spanish   language</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomba" OR "amenaza de bomba"  OR "explosión" OR "paquete sospechoso" OR "paquete desatendido" OR "explosivos" OR "explosiva" OR "tiroteo"  OR "puñalada")</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Real Madrid celebra regreso de Mbappé, pero arrastra siete bajas para enfrentar a Levante - DIEZ.HN</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 22:49:00 GMT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNeHpuejdLLVRIekxmRGNGcmoyRFpkeHYwdW5NNV9xTEhSLVpMTUpsRE1tR3NSNGpiMVZMTV84cWFGUW5GSl82LWNVSWdIYUNuOHNudXhSS0E3blVvX2FMZ0o1T0xYcDQ1X1M4ZDI5UE5YUlNfdXhxWXZ1RzFESDhuSGVsZFJpeEhSVWNxbDdlVVBXLVpYQmRMdUIyb3I5Vm8tSXN1akxaNmJITi1nTFZBM2pwSmUwYjN4RUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>46038.95069444444</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, Spanish   language</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomba" OR "amenaza de bomba"  OR "explosión" OR "paquete sospechoso" OR "paquete desatendido" OR "explosivos" OR "explosiva" OR "tiroteo"  OR "puñalada")</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>¡Duro golpe! Se reunió con Flick y le confirma que abandona el Barcelona: "La decepción más grande" - DIEZ.HN</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 21:09:39 GMT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNdDhmLXcxNURkSjM1Q0I3bkNUM3V2RmpyLWlnVVBIQXVPQlU5RWFJbTl6Ml9KbnlGQ1B1ZUI5TUZlYnpDX3dRU3hNUnBFcHBHV3ZBVERYVlZMZ2NydHBETWNfWFFJUkpaZTNVTmZVMGlzRkZTVFREN3NaSWhYTHdEeTZicTNFMC16MTNrVkdPUXFEaGN6NWZxYW4tclpVUHhYbV9GbUwwTXFpOHV5dGpaZzRMeFlWVDlFbzktcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>46038.88170138889</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Village Search Bicester and Kildare</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ralph Lauren clothing brand shuts children’s store in Kildare Village - The Irish Independent</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 05:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZkdWbWNPOTNOam9VYTVkZ0FHUHZnc21LZjdLcmxxODFJU2FfY1JpcHZKSF8zbkRrdlZ0dmt0OHhmR0tRUUFaRXVBSVlzUUJkUHRMc2NxOV9yYzRjeXpaU1hLVHc2M3dzNmFyb3ZxQzB4eEN0UTFmLWpxUWpJcmc4VFF5Z1hBdG5pUGFXN3BkSENDdUgxZkhFcTBSX1cwQ2Jqd3UyaFIyWGJiSnlsRlYteG95ZkpUY3RMVUtEVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46039.22916666666</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Six dead after fires, crashes and stabbing in tragic five days across London - london-now.co.uk</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 19:13:21 GMT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNaWMzNk1JUTk5eVhnTW15RlRlcUJCYTdSYWFmZ2VfeUJoVGV3bjFlc3F4UWVvTi1DdE1HMEhFZC1LS3pYcm42SnUwUTVHSHpOY0llbWdLbnIyamh3c2FGd2NPVHFjZl9DT19tdmtyY0tDMFVSLXZCM21ISE1hZXZVNnVHekxUOHNza2tSRFlka3RFa2NQN2ZaRXdTbm9FVWtMcWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46038.8009375</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026 film and high-end TV productions shooting in the UK and Ireland: latest updates - Screen Daily</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 19:21:50 GMT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQZmNMRTBhWHdsbFo0WHUtenBKUWJ0Z09LVVBuTjVUb1R6dnYyV0UwSEluX01NUXJuVzhuVlZCTUlHanpOQ0hpT1p4N2xGSnIyaEg3eGRKQ3BZVlJWT0hPREU4dmd2azc2VGVhQVl2emFKVmpENnNrT3BJNGVDY2xlNDVSUV95dzdPcHFtOHhqcG9WbUdYYU9odjhUTHp2b0dzMTZ6Yzh4U1VGNVVfeVl5RmQ1eDJpLU91MHlMUS1kZlZNNng3LTE1VHNIb1o?oc=5</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46038.8068287037</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Snow Could Hit London Again This Month As An 'Arctic Blast' Is Predicted To Head For The UK - Secret London</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 16:43:45 GMT</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFBNSVduUlZkUWRJVU5XeTl0RkNHU09rcW02MEE4LWEzTWx5ZGpyc25Fdk1vYmFHX1B0SDc0ODMzRVA2S1pKVlQzM1VQSVV3UEhRV2NBUGlR?oc=5</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46038.69704861111</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Toronto men sentenced for 2023 shootout in London alley - London Free Press</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 19:57:15 GMT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPajdzOVBxcTd3RjJQV1dkSzlFcERNa05tZnVrTWdQaUpKenA5VE56QVVPNEJiS0lFTldGY0xPSjRaNHNCRTljOFV4eFdvTldqOExqTnNPTTFvd09pUThrcGxFSk56RUlTZUlmbUVqRGJjd3NwVWZ3amlMV1lMNU1BUHB6NDI3bENDaG83eFctRGwtckJQV0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>46038.83142361111</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Man charged with 2nd-degree murder in London's first homicide of 2026 - CBC</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 19:12:46 GMT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQSmJETWtiUEZWNl9fbDllRjlBNXdnSzR1dnUzTENMZDFhRWtmLWFvWmNzNEtFaTVSblI2dllLa3RqcDAxY283aWZMNEpwTEp1THhDN0lHR21mMFJSOW5HSXZmTVA0Y2h3MFFvZTAtMm5rVHlmbTNpV2hmMXNWSC1tUUdxb3RyeEFtWGMza21RUHpyOVpCTlFxdzRjZGRqamplRkpWZlBYVlZkUHV4UEFmU2JzTU5XcDhn?oc=5</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>46038.8005324074</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Man rushed to hospital after robber attacked him with knife on major West London street - MyLondon</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 14:47:21 GMT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOTnZ2bmJqbkdwZ254MnFWTGh3bnl4UWxSUG9tX21qZWVSOXBHa2xpS3p1X3NWNkN5S0xvRXVfM0xuamxseFdOZGpKYzh2ckdaUHV0Y0hUN09yUDNSN1pGVV9xdm5wMDAwdUhna09nMmNPX1Vhbjd0WEl1Y0pKX004Nm9DVm83Zk9EdUlUbW8tU2p5QTjSAZgBQVVfeXFMTS1uSnBpT1dRVGpKS2tlQ0ZmVFYwZDM4SnU0UWJGUmtSejI4S1dVLWtiaWRXcUhlVDBlaVVQNVkzOHY5UWRCeXZhSEVwdVFUMFdtQ1p2S0t1dHJ0ZF9OQkR5RFBWQVlZei1FYW96eXVpZ1FUZ3JuRFl0SmoteDdrZTlfSTJMaUU3U0Z5M29tS29qc2pKclo0Qko?oc=5</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>46038.61621527778</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BRPD: 1 dead in Thursday shooting off Scenic Highway - WBRZ</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 19:52:18 GMT</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPQ2g2Zjc0T2E0N3kzSUpPZUs5Y3QwSm5NdGxYcU94RHlCbVVOS0RiUEZ2THc3VE9pSnBiYmJ1dmdheDdHcU8zLUlNWkJkeFB1WEx4Uzl2cDdlWWZKQ0VBY1JYTGx1VkR2dDlGZ091U0g1U2pUbzNkUnliMXBxUFd1dnd1cnM?oc=5</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>46038.82798611111</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Norway jails Pak man for 30 years - The Express Tribune</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 03:17:43 GMT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBHQUdYYWpCMGVXYlBwZGVVbkJyM3ltaFFXczV0Sy1RQ3FjclBzSjN5QUl3Q1BlWHJaQ0lMM1F2ZFA5dEVTOGNyUG80bHRnZGhsV2hCU2xxeTBHN2wyY0VrVk9CalB2TS1xWmJ1LW9TQ2NLUjhscDNmS2FB0gGCAUFVX3lxTE9oME9nOEFUNllEaHRfMGxnWUtEVUtEa1cwd2hsUG9EejZlQzJqZFBQM1N2bEFTaTJ6RGhHSjB0OXRTQW1hTE5ldEljTW5QLW1mQV9TV1I2STNJSE1heFFfalhFSkdObHdnUEMxMTVxVGxiS3dfX3pYMXk3MUs3QXZtcUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>46039.13730324074</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Norwegian Court Sentences Arfan Bhatti Over Deadly Pride Shooting - Devdiscourse</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 18:35:54 GMT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOT2pUZHFYLVZaZFJnZHFZazRsZ2NOVUxoaHFBbUJQZnFIdUFuVzMxRVEzVTcyaGxBcmFKYWtjbDlYQzlya0ZnT24wSDlQSjhXUzRiMGIzS3lZVm84ZFo4NGRUaDhKS2RrNGxXNjF3eDNuRS1GblVvcU5IM3NOZ0l2R25paUppd1licFVFaXYzamRvdVFTZUs4MTJ2a0pTcFRkWVVYLWZpRzQ3WHBBUW5hRV9MTzlCQkxSNHREVUJ2TmZ4UdIBwgFBVV95cUxOT2pUZHFYLVZaZFJnZHFZazRsZ2NOVUxoaHFBbUJQZnFIdUFuVzMxRVEzVTcyaGxBcmFKYWtjbDlYQzlya0ZnT24wSDlQSjhXUzRiMGIzS3lZVm84ZFo4NGRUaDhKS2RrNGxXNjF3eDNuRS1GblVvcU5IM3NOZ0l2R25paUppd1licFVFaXYzamRvdVFTZUs4MTJ2a0pTcFRkWVVYLWZpRzQ3WHBBUW5hRV9MTzlCQkxSNHREVUJ2TmZ4UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46038.77493055556</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>UK teenager who praised Southport murderer jailed for possessing Al-Qaeda manual - Arab News</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 16:22:47 GMT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE1xTlpBVHdhclp1LWtralMtanVPT0Q2OHV5WWVOUVJKVmdaR2o5NEpjR3FQVzFTTktncEhVaDg1UUhsMXZpQzQwam9lWE1Tb09NOVBz?oc=5</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46038.68248842593</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Husband jailed for stabbing his wife to death and grooming their child - Yorkshire Live</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 15:58:00 GMT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQOVMzRjRxNGlBR0NZRjVlZWpfOUJia3JNcVY0eFFfQkd6UnFnMjA0RTdNV3NpbmJlVExrdXlCTll2T21rcG5kc2dLU1pkSFZnSFNVNk5VcHBQMEQ4LWxuSUVLc0pzX1JTUWMwaElDTUtMRWZDTkhvTkQzRmVzcElsUEN2cWtaRl9EdXlkSV8wTkhLVlRLS1dnSNIBngFBVV95cUxPN2F1dUJVS1FfQ04yemQ4S0F2M2VGalZyZktDYjhxVmJmT1lrWkhvVUlSc0YteHNCdUhiVm9QVVpCTkRac3BfQnZlQXV4M196U2VUQW1wWHJBUDZ5M3RiTlloMUUwWVNLNk4ydGtVSUtKekhUVS1WY2pPSXpMb3BIbEN5WE1UNHRvOFpGWFpIcUtKZjZDeldGRGphal9ZQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46038.66527777778</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>London market dubbed 'awful' as visitors notice 1 major change - MyLondon</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 14:59:31 GMT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNUEdoVlVLS1c5bWV5NXdlUnJ2Q2YwM0FtWUFiR1BrR1lqZ0FQS1NuQ1UxQ0puTENXZU1JM3JQTTlRVWZLdS1Fd3E4Y3VfekZlamN2TzlqMElIdU9uN04yQ3BGVnMyOXhCRmVYMl9uRUNnYTgtR3E5NEtfZm1RWGpGQlZPM1I4Uk1QcEl3Nkk1YXN3T0haYk5sYVR2d2x2Z9IBngFBVV95cUxNUEdoVlVLS1c5bWV5NXdlUnJ2Q2YwM0FtWUFiR1BrR1lqZ0FQS1NuQ1UxQ0puTENXZU1JM3JQTTlRVWZLdS1Fd3E4Y3VfekZlamN2TzlqMElIdU9uN04yQ3BGVnMyOXhCRmVYMl9uRUNnYTgtR3E5NEtfZm1RWGpGQlZPM1I4Uk1QcEl3Nkk1YXN3T0haYk5sYVR2d2x2Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>46038.62466435185</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Brother of George Nkencho saw him being shot - inquest - RTE.ie</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9hZ1ZzWG10cVR1RFd4Ymd4SlJxRnJ5QUJoSzNEd3hER3VyMk9Bd2lKU0JURF9jNk5NOGdBb0d5bl9idU9jLVFWLXpFOWU3WmdXOENueGhXcGFpYmNNaHBaZk1nUWlYYnladnNSR3dmVFpDbHBOX2tRbVZNX19KUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46038.75</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>West London Horror: Eight-Year-Old Girl Shot Repeatedly on Her Birthday by Man Dressed as Deliveroo Driver - inkl</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 15:31:29 GMT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNUE93Y3dycWZfNzY1d2Rrc0F3QmNDLWpaWWYwUmZPSEdWOVhTWkhrSVlFZkpPQ1pOM215RUNtc2I5NGZsMVhlN29CcFg2UURmcy1fSV9WcUlJMG40T0FCWmkzc3NyTjJITjZoekZzTzNpN2ROdkhpaUdWX2ZRTWQzb05GMTJnSjN4aDNLYzZLdGxTenZYOC0zWm9UWGgwa0NPZmNDWnNJX0x4X3F5dzQ3djQ2d0puaWZvN0pfaEhDUVhJN1d5NWh5MktiZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46038.64686342593</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Gardaí ‘shut down’ mental health warnings before George Nkencho was shot, inquest hears - BreakingNews.ie</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 18:24:59 GMT</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPQnZ1YWpDQWVIbExOSjlXeVV3YTl1S2FuOV9BWXVoU3hoT0Z3VUpwWks0Wk5kTGx2NnBaUjVEbkV0Tmpkek0tSmFtZGxMVjlrdmNrMC1RblM5Ui1mVEk4T09Rd0VSbDJMOWM2bnN0MVpWZHkzN1lIWjlnUC0yWjF2TEpicnVVaFRfbWs5bmZBNEJwM3Y5b3pXeERZLXFSWGFqT2U3Vlo4X3JqbWpRRTNUMjNTdnA2a0gxV1hyMi1tT2ppaFJxbVd1MWtzZk5pQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>46038.76734953704</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>‘Kissing Is the Easy Part’: Asher Angel &amp; Paris Berelc Star In First Look Photos From New Tubi Movie - Just Jared</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 04:54:38 GMT</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOYVhfN3BPWVROYkE5a2pwakhTVklnTHV3QjZMTlFDUDRnemcxclVpelhKcW9FUklld2VnSnZCb3VKRm0ybTA4VjJpNXNZMldUWGtaRnVFalc5TFNJeldSMHJVWVA2ZkNPZ1FiblBDQVVLZVR6TWpFZEFHNXAxcXNGMWJXd2JOVDNqcU54LTctMHpJemQ5dnRoZWFUNUY1UDlPWENvY0xNa1RwbXYxMklLUnBHMFFtVWtKX29tVVlabEFXc3cyQVVQblIzdFZWQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46039.20460648148</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Gamecocks Remain on Road at Auburn Saturday - University of South Carolina Athletics</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 18:25:17 GMT</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOWkQ0dVlsdzVqamdEeWgzMXVyY2JXRXBaYWljUkhfTzlXTlhKLU5qeWVHSnl6ZFBiSEF4aVo3OGhzbDVfYV92U3JaS19NQVFGUzMwSmxXb3VWYVJZdEk0M3ZfN1F6dk1JUEdoWjZVc2MyTVI2Mldtd3V3SEtSWUVIenY0bUd5bC1TQjhNYS00TlZHQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>46038.76755787037</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>‘The White Lotus’ Season 4 Casts Steve Coogan and Caleb Jonte Edwards - TheWrap</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 23:41:15 GMT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQbEt3MG4zWm93a0pOYWFUM2o0eHVIM2h1bTRWY1FkN0dnV1h5UWNHRkR3SWxLUDV4SnVlYWVHQnFQcEtlN3dMYjV1STJybXNQQW1vSVVrNVc5QWpFbjhuSVFYVmQzZHZ4a2wwcVhOSjFoVGJoYno2RVRvYjBfczFobE5jNUZMaC1FenF5akVheUZMWm9jOTF3NjZlNklmaUE4Q1RFeXpJMnFPeDNNdU15cENLcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>46038.98697916666</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Gas station clerk charged after shooting and killing customer, High Point police say - WXII</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 04:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPbjc1UlpsT1Q2RWRxUS1zLXhycGVOcndPWjVUZ0lnZTlDTkFxNHdSaFFIUVp1YU9fOEYtN2hNXzZ4UjNWbEhSSmpLQkVZX09NZWxlUWp5QUpmX3RZbkJvYk9TaUpJSDd6UzVUY0JFMXVmckZqdEp5eE90V2lpVDhuV1dRVFZlYXFkV2VRSkhmR0tPdTBnTFNuekNR?oc=5</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>46039.18472222222</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Mental evaluation requested for Jefferson City man charged in wife's stabbing death - KOMU 8</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 21:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxOd01jSl9pYXFyRVQzMW1WRW0teG8ycnJ3U3hKWmt0OW5heUp4aGxOaTc3NGVBVklVbUpHVjVpRTdkMXN6TktJTFZnYUJpa2RVcHJaSWl0WjA3b3Ytc2JLLXNUNUdPbDBSV2xWdUk0bkFBS0xZNVRoLU0zUUpxNmktY0J6WGdzdHNvSTNteFUzb25hdU9kLU1FUmxzU2d0MGtsN3BBUnN4bXliZmxkOXB6SXQtT2dPT00yMEYwNEY3M0t4SWJQbnVZdjR4cE1lOWRYOWxYZ3pmVGpxUExzbGRxeVlUaERYSXAwMWo0cUFRTmV1dGktbi1XNEpyVGZ2VTEwWGQtRtIBigJBVV95cUxOYlRhTDh1WnlsekQwTVNZM2Zwcy1nVlE2bElBWUNURmNSR2JKNXJ5LTYyNkFveXBOMTFDYjNnb3BiQm5kRUJVX3I2MlB6Q1h1ZTFyaXM4Unh2ek9KT1RfWEpSbmw1OUpIQnRuWVhXR1dncDM2TlNNY002X2pFMjFQLTlnZjV3LVNDRzhON3BJWE1jUm1FZXBnUEI2MHZ6bUJrSHFpRW55NnpkSHJYZUg1bGtWTi13a2sxd3kzcExqX19ZaGFLdGtDVDlGd0UwUmd6WkZrX1JYMExsRW5XNnVzWnNXa0tyVlJ2M1JuZ3JKeGh2X290dTJyWHBJc0RhdFMyd19YSUpTYXR5QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>46038.88541666666</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Qantas joins Emirates, United Airlines, and Air France in shaping the Future of Long-Haul Travel—How France and Japan Are Reaping Explosive Tourism Growth! - Travel And Tour World</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 03:51:29 GMT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAJBVV95cUxNeHVJeWhRU29QWkJSVndUWmdtODZ4bmhKV0dKMzdYaDBDVTN5eTNnbFdUWkVndm8xQVNJX0V3SGo1MFlVYzFaTm5EeGRtVzd6YU92c0MyR0szUkJfWG5makxpUXVqa0JaSS02ZVkxN0JuNDhfUjJsbGZZblpwWHVpbFZ6d3NLc0JZQ0tJR3pDNERlOE9pXzNobklTUUhBS0w1c1ZIbHR5cy1XX201T2RNZHZiRXZrQ2RyV2NEZ0ZRbEV0ZG1CMkZQcnlfVmhHSTNzUFZpQmJDTHZ0V3dNcUZjWVV6Y05WbTUwbDZKX3RfVzJqRGRGMHU3cGFvZVpzbGkwWEM1UnJvQzh5SldVVlVGY3l2OWpDOEVTTDVTV2dEVTNSZGc1a1BnXw?oc=5</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>46039.16075231481</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Groom in Viral $59 Million Paris Wedding, Who Was Facing Possible 99 Years, Pleads Guilty, Given Probation for 7 Years - AOL.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 20:07:11 GMT</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5OSEo3V2J5NWROMHBfRlFyeTJVT1I0VWRwNHZNTkNPcW5nX3FTbTFFa2F3S0liOVBQeFpRSDhuTktpMnlFUm9WSDcyZkxQTjRwWHlKa0NuMktlOXpsVXRwYWlpdWFMR3UtQ200YWFEVGNCVndMYnJ0emZ0cEY?oc=5</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>46038.83832175926</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Paris England Game Report: @ South Carolina School for the Deaf &amp; Blind - MaxPreps.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 18:49:51 GMT</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNTFoSVZuQXNXRzZHTlN4WTZLZTM0UXljTHNMTXlFb2hpVndCU3BrRmVVcUdVZ2tvUXdpWXoxU1M5cGJva2xBcjBjdlpvRV9qZFNqeDlGSUxjdzdfb3Izd3FCNWpIQWwtTHlyakNPQVc4TDBtZ3l1YzhBY0NCREhmVHNHVl84aWdJVnZUNHFQWTNqcnlzaDlyMWp5cGFmVHQwYWsxOTR6R21uLUNaTnFTX290SkhfaEtNbTZXdElaN1pGNndMWHZsRmljRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>46038.78461805556</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Federal gun reforms ignite fear among shooters - Glen Innes Examiner</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 01:28:47 GMT</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOX1FYVkVZRWZqTEtlWHNVRFUwWFowamNOOUZHNEpLNlk2bEFTSTVyMVI2M2xfVEdsVWV6Q1M4SGlHcXBkenh1NkZ0T3AxSHR3bTZEc3JKdEdYT2pwdzJCQmRHelZPbDUzVHhKUmJYa1J0alRKMlcwWDlVQUEwVk92b2tDNU8zQVBiUW1wLXk3ME9TNWFhVnJsSUFaZVJHOXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>46039.06165509259</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Wildlife Officials Seek Tips After Golden Eagle Shot In South Dakota - National Enquirer</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 14:54:40 GMT</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNRDB2dVdiZU45bENzeUwxV2Q3VG5TU3hwYWtTRUJZSU1LWThxNWtONFNQOVIzNUVCdGcxSEQ0LVZMU1p3N2Rod1pmOFZ1ejctVUZ0SEphaVJqeFBwM2t2a0tpNVNFSlREc3NZX25lbTRHcmhaTk4wXzI1cUluaWdTa2NNTVZzWWRsazlKUGZ5NFNiQ2tTbV9hMTdXQTkzYkE?oc=5</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>46038.6212962963</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>French youth speak out against Trump’s illegal invasion of Venezuela - World Socialist Web Site</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 06:29:06 GMT</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE5Ic2NUUEVPREdQcnVzSi1VQ00xV3ROVWZJYXBWVEJCYjc1VFRNS1VVVlAtZzA3QzhxazE2ekFXRDB3aUpwZWZoZFNZbmotX0lrZWppMTlQR001Z0dRcFB4RFc4UEd4X09o?oc=5</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>46039.27020833334</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>'Magical' Dembele brace fires Paris Saint-Germain top in France - NST Online</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 22:54:00 GMT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTFAtVTRqSFh4c1ZRY1h4dzFDQmNHUy14NWZOX2FNNWJkWWlfeUMzNEdTS1U4RldkTW9vYlJEZzBIa2dpU1g0NV8tektoc3FwUzRSM1o4Wg?oc=5</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>46038.95416666667</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Couple Allegedly Forced Kids To Fight In ‘Fight Nights’, Locked Them In Chicken Pen - National Enquirer</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 14:54:21 GMT</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOTmpDcXBBSzUtbkVNeFdQNE1pZTdJSXBBamZ5eWQ3VFdUWGhianctVWFFdzJvZklOYzBzbS1ueFBNd2J3blRzdGJLVDV1bURRalVnYUYyLXcwdURXLVdZRndxbXZ3aFEwYUN1RWN6aUlfZDE5ZU0yUFRwdUhRWEhNaTBlbml6R3IxSmR3SV9hekJjVmtYZ2NsRHVwSUxnOWZxZHF4WmZnNmpYRndmeHdj?oc=5</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>46038.62107638889</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Police Seek Suspect In Christmas Arson Fire At Cinnaholic Bakery - National Enquirer</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 14:54:16 GMT</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNQk5UOXgxYUVhbUhNNHFNWjd2NmtWWXdlYkEzUndlME9vVVRnLTAxWGJkWjVneE9fRndoeGtXbWJSZnhSZWZQQ3hHRGRSQ0dIQlRQVnNBNmNRV1djV1hOYUdHSnRlWUFhdnU0b3kzcGdtQmlXVFl5aEQ2N0ZTYi1yS1RqbVdodW9XUFRVQnBwRE1Lbld3Z3BsdFFB?oc=5</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>46038.62101851852</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Lee Pace, Matt Smith, &amp; More Sit Front Row at Zegna Fashion Show in Milan - Just Jared</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 18:03:46 GMT</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNRWJ2eVYtaGtFRGs4LXdRamZrYjZqWmcxYmVLQlhPNXBDRmJFNDFwVlV0anB1WUs2a3JHaDd0TjF2WW0wcUpaakZQb2dUbGsxcS1lN2FseE9QdERydkF2VE5nQVNBWjlnSTBjOWNOd0gzeWExdE1FS1lMTkRpdXMwN1FfanBGSXdKNmJ5aU5JNGJGeXRxQjNBc1kzanZlNVJTQ1RSaWxqSXBzR00?oc=5</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>46038.75261574074</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Christian Pulisic benched as Milan extends 19-game Serie A unbeaten run: Massimiliano Allegri reveals the k... - World Soccer Talk</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 18:50:05 GMT</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogJBVV95cUxOQXJWNHlNdGRjWHlwbUhHcXhXZ21LakNNZnFGZFBtZk5PRTFfT3lBbzRMQ3RWUEMtVEQ1MG40SHJGNzFEdlc3WnhERjc0QTlFaEtvV25jM3hmSHVHLXNVUHoweFROOTBkR2QxOGhSVUszT09mX2F3OXRZRnNQdV9qTlgzRXZRVUc1SWpnZEJ1aU9hNWRsU09lMlFPX3QxVkFySGtaaGV1QnY4NVk2T1RYMWJLcDF5UGo3OGZOM2V4eXYyNjE3YlhJVFp4d1UycG5ERGxQajNhNWprTmhLZm9SX1p2ejdHdEVpV0lUSkg5b2tHcklpYk9QVkJHeVhqeTB1Z3BMQmY5bV9nOUM5S09qNy1SX0tBczZwNWFrUHluX2s1UdIBpwJBVV95cUxOdzZvd3puREI1NHFBT1otRFFUdVdLbXhwQ1M2ZVRZUmpFUWlHeFZNNkZDb2h6a0VvSl85UGRUaTBqeWcxeHBiTS1uN041NmYxWlFzbkMzY0ZMTjFiY2pJQjVzX2M0UVl6RXRaaVFZQ0RCbm1kNVdEdlhSd2dpZThuMEpVRmZ6enBGczhuT3BOQTVQVzBuVkRCaWNadnZwZ2FWQTVUZkdmTkNlaWd6SDRiQnZBdjE0WkxRZXktemJxU1poMERUWFN0VktwWjlfSFdPemRZUkFFODBVdDdubDltZ01QRHhTN3BidzJ0YkRVTUl2Q2dSUEFKQXZfc1VDTV82Yjg4QlZaQ05seHVqcmxJZmZPbk1hVWVnOUpFRnhVZkk1M05pcC1V?oc=5</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>46038.7847800926</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Killer gets 40 years in Ivy City Hotel stabbing - NBC4 Washington</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 00:49:34 GMT</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQeEFyMEl5SXlrX2o1NExvQlVUd2xWMmhtQUlqUXRKajB0Z2J4SEdpaERyUFR3M0NEMHZDcGFLbkJYdU5vc0pJamJQcWJkNVd5V0hBRktnYnZrRVJ3NmRPT24wMjhiSmpid0otMEZOOE1zX1ppZHVLVTd5SC1ELW9yOU9mSUJ5clpDRGFzc2FDWdIBlwFBVV95cUxOTkt2QmJNMDh2bnJwRUV2ZlFmT0NwMDdlZ21XNEtEc2gwQ1BjemJybVowaGkyYml1LU1zN04xMGc0d0hnS19DekdfWDlTVWZheVRSaW5BQWgwSG9wX3ZtVEotd1JRLUxVdGk0WmItdDZmd1Z6Zmk2cTczZFBud0luU0o2WjU1WUFEOG9rb295YkpfZUp5aDRj?oc=5</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>46039.0344212963</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Monroe County Region high school basketball roundup Jan. 16 - Monroe Evening News</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 02:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQa3djYWMwZE9MakJYaTdwdUpNc3VuV3hMT1VIY3VsaEx6a21yX1pQcnVVdkU4RTY0RURhWkt4ZnlyVm1DZlhDajVFci1ueDl3djlXWldmdWZGeUhGa0c2NnNSRm1CSEd3dWl2Q3JWWnRHeXhGY1FkQXBpaWhoa1JkZ0hjLXBHNzkwcjhXR3JKc0c1cU1HLTZWX1hzMlhnSE9iZmM2c09kWDRIU1AxTlp1T244eTZSYmhPUm5TckxRZXpQRDJyVFd6clkwaUtYZmktQjlyZzRRSWROYjJVam1MTGI5eW83S0paeFAw?oc=5</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>46039.11458333334</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>RABIOT IS THE MVP FROM COMO v AC MILAN - Yahoo Sports Canada</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 17:37:30 GMT</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE56azBCTzZ0RTI0ODBiSF9RSXEyZUJlZE11SUtDRGNsTERsOXJjc0c2LW9LaDNwQlZZTmN0dC04YVRpN3ZOcFpUb1BfVlpkSTF3MjY0aWd4RHo2ZHNSVFJoZ0ZMMUJjbmt1OHNmdC1CWGU2REtjU1U4?oc=5</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>46038.734375</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ducks’ Leo Carlsson out 3-5 weeks with thigh injury, threatening OIympic availability - Long Beach Press-Telegram</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 05:00:32 GMT</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNMVljaXl4Z1k1Rm94Ym9VX2Y3eFhGZkZocFhxZEFQNm9GX0JOZEUtc1BVeUU1M21nWDE1VDNQZFNQNV84ZlRHeFVLMkcyRHVwMFB5UEVGVzJrYlh0MWlFb3FvU3F3bmZxS01hMEpmZmdaSTZGdHlLQ3pXZ1hnMXV3T044NUtEeFBZdFF5RFp5cW41YnRCakhwSW11ZFpuYjlaUnNGWEZIcXdKc3hjUXV1VWJ5QW4zVVY0QVJXX012S2RGcDQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>46039.20870370371</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Isaiah Goodwin Game Report: @ Harpeth - MaxPreps.com</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 21:02:59 GMT</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPOTh2ZDBvZDVSMDFQSm9ScGVRQkN3aFRFMmNlV09ITXE4Y2xnRmdXSl8zQ1Y2VVJweU9hbUlGY2FIM2dlWW90RHZSQkNHeDlReXEtbmIxNXg0RE42UUsxZEJlR3ZiS01tM0RjSlp3SGNCbVZaQk8tbURERlF5R2hFdkM4ZzQtREdvMnljb0VaX3BZUGtmV0VqRXE2Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>46038.87707175926</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Heated Rivalry’s Hudson Williams Makes Runway Debut, Opens Dsquared2 at Milan Fashion Week (Photos) - Just Jared</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 20:07:05 GMT</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPd1kwOVVDZE1vTEtYcmhYaElMQ0VyX3hnODZNdi1uUUlkUGhWSXE5UXAzWlREV0o1bTlrVWo5UUtmek9JeWRoM29RTC1LM1piQjRSYmd2Slk0dEpHV1ZNbWpUQlVkRXlPcy1SWFFHazkySmNLbUM3R3BidEo4eDE1YWZnbkk3VW9KUkdQOXhjMzdEX0NKSlF2blZYak85d1RVM3ZDN3pveE8xZ2VMdWVfLW1jbDFIZ1JqOWY4Q2puMERQa1p1b0ZVOVRyblpIUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>46038.83825231482</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Tourism Kamloops joins playful online spat with Ottawa, Montreal over Heated Rivalry star - Castanet</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 21:36:00 GMT</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9KRF9MWFNGYWlTSE1LM0xrdm9XYld6bkEyVXQ2MjljcGNGT1RNSlU3eWd6SFlTTEdmcjJRUnNHN1pSNFI4MjVZTUlWdE81azgyZU1Qcm04Z2RUSDFKWW1rckQ4M1RpaWR1Tmc?oc=5</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>46038.9</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ducati’s explosive 2027 plan revealed: Marquez and Acosta set to dominate MotoGP! - motorcyclesports.net</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 15:34:05 GMT</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOaTdaYk4wOWt0SFZIMEdscGlNUVVULVRzSm1WeWs0NWtiblJ0cmtiU2RzSThSTTEyeUp0bk5zb2pYelRkN1d1cWFTMm5sNkY2Q3Vua3lkNWhORW9ubjlDbm9Pc3hjdFpRUmVkR05wS0xMMTd6RUdBdjBtM1BvZmIyVHRyMU9SWmhkcmRxU1JleHFlS2dSRm45OHVnTDNJMkxJUm5FdjEwR0NSckktYjJ0RlZlbmRTdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>46038.64866898148</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>French farmers wrongly accuse Brussels of betrayal. Macron’s complicity could help the far right to victory - The Guardian</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 05:02:00 GMT</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOelBoSC1uYXI0UF9CV2VLZGtpWWRrdWhtRnRLblNMS01BMmFYRDBRdkpMbFdqYTZucm5kcXA5WnNHZ0JuQTRkNkZDZUtkNEE0Z2V4WDFsekNkT0pOTGRacnZpWFRCdGVQdzIyMHVlaVl4LWZGQjZjWE5KX0YwQjA4alRJNGF5cTdSMTY4Q1gxTzB4MHlCMkE4Y0JRQmVsR3U0OFlsSUU1eG9PSENObUNkaU5EcUw1YUJVcWRfU1Z5R3o2Y3NkcnNQcFBGOWtTcFBGYlpnVl85cDF4WmljUllGVUpTTTRnY01oWXlhRzY5WGo?oc=5</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>46039.20972222222</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Brussels-West zone inaugurates renovated police station - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 00:14:41 GMT</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQSXpMOEthY1h6cnl2ZGczcWVoejlUOE5odEpyOVdSa3FvYWVGMkFKT0treERSa0JLWjVoNm5kVlR5blFEWDE4WnYwVm5GRS1sT2FickcwMURoMWZjeV9SYk1ZQlpqM05jMUFLVmd3V0d4blhGNjA3MnJqNHNtMkd3ODBmT1dZTnJMWnFGRUNpa0RlNG1jVk1zM2dldXRSdW14UEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>46039.01019675926</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Farmers’ blockade at Brussels Airport snarls cargo operations and international supply chains - VisaHQ</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 23:02:24 GMT</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPcTlGNVlwS2tGalJaSU10VUM2RUpRMDJoVjFNYmtfLXFuUE9jcGlobnJ0TW92cU1KY3RvcEhCTFhOU3Z6WkV4MmZ3dmJmcS1TNlRDVnRPNHMwSk1laG9xLURuTE1CODhYcnZocWpWMVVQR3VBenlRNWNLalUtSDQ5ZmlPM19oYkQtQmlGUTBxa25OMm5iS3Jfb1pETjJSa0ptV3l2ejhPYjBBQU0tMVhXUlg3S0o4OUhSNFAtTktHWEJ5VFVGdVMxN3FkclhsRy1D?oc=5</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>46038.96</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Kidnapping in Brussels: Four suspects charged after high-speed chase - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 00:11:15 GMT</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNaE5QQXhBUkFqWUczajFzczdpdkJxM3lTNTNTaXphWko1eVdZRFhEWFlkTmsxRTl2ck05bVJ3UXQ2d2RMVjBIdGE1eVRmM0RXdjZkSzZ4elZmZEZ1Vi0tLVp3ay03azdJX0t5R2lzSUIwNzUyZXRvU3UwUW1QXzlWNGt0ckdhb204bzB1RXNvOVF1S2RrYjloYUNBR21pWTE2UXhTYWNJZlY?oc=5</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>46039.0078125</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Farmers extend Brucargo blockade in protest of Mercosur and broader agricultural policies - Aviation24.be</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 16:05:18 GMT</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPWW1HaGdRcENtS2g5YlhjU2lLNUptQ1NKbXdDNnBwY1hqSldCWUxjSWhtOUhyNl9jVUlxNHMwcTM3NmJvTGJfNmtEWGF4b0N5eGd4ejJUWFQ2OVo3TVcwWWQ4VEc2cmRGWGIxU28tSnZ3WGk5Sl9wZjZGMVhJWldTWlpGWW14WUt0NnRIZExVYm1WNE9JYmQ2WF9hLVVncXUxbXl1eF9SQm5kMDZrSzVXNHg4VjlJNXRHUTdKcVo5WW9QeFFMbURGbE81SF8zSVBieTZQSjdwcUdRZHdwbDdvRmVsM2hyUDhXZThr?oc=5</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>46038.67034722222</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Massive Athlone rally says ‘No to Mercosur’ - Westmeath Independent</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 16:26:27 GMT</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNZ0JUT0M3US03NzBHNGhKd0hIaDNMRDgwRnkwendJTW1aeWQ3TUpXVEJ1TUhYdGE1cmhISFpGWjVrVTRhRmNSYTBSTnM4bGZxQVZtTWVWRVQ4cTNGN3dVNlUyQnlBX0lPTVNqREYwMTNSUm42VEhvbEoxMjJwN0h1ZndKUjJ3UUJ0QTM3YTBJODRYOEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>46038.68503472222</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Drop in the number of Belgian police sniffer dog teams - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 00:06:01 GMT</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPNDNDRmRCei05cDRMSEJzZXF0MVZrRlRURXRhWXlRVURBMUtIRFV5b1VUUWJVNEVia3BVczlYQnk1UU9zVGwxRTlDbkZjemQ3OFNPNWE1b09WM0ZCREM3Z3lnMlF3S2xiblZyaFQwSDlHUjNCeHNFV3pOOWxFcFN4V1ROSFA0eGVWV3JwNEZDaWFkdF8wbGYw?oc=5</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>46039.00417824074</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ghent takes step back from using Israeli surveillance technologies - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 00:16:47 GMT</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQcmZMSjREVjlobTZ4RmllN0QzZ0twaFFObkcxOXh6Z2RhVHFGSmtZZlhIa08wQ19FdDZSdm9kTjFCWGJMSnd4VVJBSW1LajFYbzJTT054akJjNl92Vk1OQ1p6Vl90bFJEVm52QWYzQWZwSDZBcUlKNUxfYmhMb2pYU0JfNUJYcGIzdzRoN3RVT0lUaTlkLXhrNFdHMklab0Z6T2FCZ0w2dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>46039.0116550926</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Hundreds of Port of Antwerp workers suspended for failing drug tests - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 06:05:46 GMT</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPaU1FVlM2NlBMdHFIQUcxWFVqcU5PVUhRS0hrZ1pjOENPOEt4Q3R2NTFMalJqZGIzTXVxXy1sZC1oVG90VkljV3JybVpNVFRET3hmLTNWdmFNRzhRUmRlUG53TzlpaTNfbDFoZWxtY0ZUWU5LcTRMSlNnS0ZEb2ZEc21IMk53NE55Z3c5dHJZZWR1TWI5YXBRdzdka1NIQkxxYjJ3VmI0aFMzcnZCRDRJSzNqSVo5UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>46039.25400462963</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Belgium's brand new justice department system runs aground - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 21:20:54 GMT</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOQkZoejUyY0lZTzBibVloMDZ5eEdCS3pLYTc0b3NXZkt1SURmbFdncXNCejd2RXVnZkx0MkF5UEdCamJGbmxfZTBmRlFDVC1pWXgwSU1pS3RqOGxFMHRYeWlHS2tRMHN1SFNuQXJXRVpfZUtZeGpPOVhVRmRTRTJNU1pGcld3V3dJTFJJWnBWeGwwVTUzZlFDUkRsNDIwZ0xLd2wzQWl3?oc=5</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>46038.88951388889</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Drug baron found with mobile phone in Bruges prison cell - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 16:56:48 GMT</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOM1FLbTVLaUhabm5xOEdUYUlHSVB0UzdkM0syeEpLS21yb2tPS2VSMjNxV3hSYVdtSTJ2SHltM2JGYzJzUURFMTlhWUhjTTdtWXZYZTBGVFpFOFVqODE5MmxaS0lVUzNqUkxyVzY3ZFpfTEVGcXgwRFU0RUpaZHBRTGhTSzBDMy1fNVpMcHNVX0pESVBEb29zYlF3?oc=5</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>46038.70611111111</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>UK union leader caught fraternising with ‘anti-fascist’ Russians in occupied Ukraine - Brussels Signal</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 17:53:22 GMT</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNSmZGVTM5ejVKZnFadDJ2NmxXQkVaaE4yVEMwbFFfUGlPSjVRN1Z5QURxc21yNDNBaGRpTHYwVy15Z192eGdlX1Q1c1pFdzFtRzd6ODZZWXY0Y1c1SXBxSkQwWFFHV25kaHhiM2lWTkItVEhNWWYxY0lXcWY3ZTRkeXMtLWFIajQyNjY1R29ZUlBRWFNsTTAtNmxCZDhsN01ETGlMbEF1YVo1RldUdi16LVQxRTllRlI2?oc=5</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>46038.74539351852</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>At least 15 Belgian victims of video game which forces minors to undress - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 16:52:30 GMT</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNalZ3T0oyWTVVVklsal81b3pSa25tSEFJSkxYVEljMnlaenZSWVBETEgzeURYNnhndndTbFloZE5HS29PTDk1U2F4QUFpUTBQVmFjckNuTlJYR2dsNHVKRWJtV0cwakRacUkyZ2pvb3VPTjFnOWRiZ0M3MWVvYTRDWDY1bkN6UlRYVVhkcDVFYUdXLXZqXy1tcUt6SmstcENYNUJyZTBTelZ3LTZpWTZ3?oc=5</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>46038.703125</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>European Commission Ukraine 2026 Bold Shift - Brussels Morning</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 20:15:37 GMT</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE13Qjg4LTdRRllvalVSaG5hcU5qMjdtUWV2YzFTMzhOYk51eEZkQWlqWkFUV1lxb0lORVZvZUp5dEVTUl8zeXFHTk03dmdMYnRiMm9TMmpSRTJYQnN4OFBSVDY5VTlvdVM0d3JWVGRLS1I2eDUxbEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>46038.84417824074</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Palestine Protests UK 2026 London Amid Middle East Crisis UN - Brussels Morning</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 16:28:17 GMT</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE5KTHF6MWZUSXlqd3ZtOE5TaGpNN0ZhV0VSc2VfNzktckx0dEJYdjlGSzYwZTJ3ZDg4Z1JtYTROdzkwbzhFZkJiSjBaU2N0Qm5TQk14dzhhT2NDeWFJV25RSnhpazN5VzBUV3lMZ2hB?oc=5</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>46038.68630787037</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Spectrum College Beringen cancels 100-day celebration due to vandalism - Brussels Morning</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 14:44:43 GMT</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNzN6V01Qb0l5UnkxR2NQci0tdkRQQU1HZ3dRTzZsai00OXVURl95WjU0TUtkUUdlRVI3ZWp6MV82bHpvOGNjQnh1Z3hvbWU0ei1KSmI5MFhQQk9hUjN0NG1nVlZiLWVCV2g4U2V2VEF5NnhaQ015cHlOUEVwc0pXRVl3LWItS1J3dkFlbDdYSF9QNXZKbXVjT0YxeWlOVm0yMmNCX3czNlY?oc=5</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>46038.61438657407</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>STUDENTS AHEAD OF PROTEST ANNOUNCE: We Will Show the First Fruits of the Movement and Plans for Liberating Institutions! - Serbiantimes.info</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 21:39:45 GMT</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNeWlIZ05LRnc4S1dvNHA4V0ljVEZCYnVQb19RNUtWclV5T3hqeFU5cHVNdURXWGFCYWt1S09SNHdNQmRqU0lyZ1B1VHlCcnl3S3FLZ1lSZWVQZHUwSXE1TzVmYVdqR1l5UTBCY0Vjd19VLUFJM0lBaG5JNzI2bWMtdjdzSkZYTnlCbDJKbk9FSjBhbENuNklZRWhJMUN2bUtQNGtheGFnZERvVVg4cXUxTGV2ZGZyRGhIbDlRdGc5ckw0V3V4VlZyMTB1Y3lUYmNqQXhySEhRUXFCNzFRWDhQUEVB?oc=5</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>46038.90260416667</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Fire in Hasselt prison cell prompting prosecutor’s investigation - Brussels Morning</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 14:35:05 GMT</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPOVN6ZHEyS2cwNkdHbkNpeklRZndpejdfYUpCeHdlbXgweWdQLVNLRkJ3cXUwRVdfclpjX1kwMy1ROTJwN3NpZGFfSUxCZDJiTWgweTNpa25hdFZadHB6V1Uza1g2d0VnVVR5YTd3VmRXa2U2M05yX2N3Q0d4OGQxdEM2WWl1V1ZkVzI5SWRwUnFuaHN6ME1oZ1JQMEtZNnM?oc=5</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>46038.60769675926</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>BRUTAL MURDER OF ŽIVKO BAKIĆ: Former Footballer and Drug Boss Liquidated in a Forest Near Belgrade! - Serbiantimes.info</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 21:39:46 GMT</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNb010Y0FjaEwydnlYaHItMkhGV2tmNWlKT1Q4RzA2XzZ2VldHQWY5NHhyUGZWc25uZS1uUTRWdURKWlpKWnUxa0RoYnU5QzdrWUI4Q1JNQUdla2dwTk5fVUNrMFA3MzM4QTk3RlF4elVGWTV6VDZ6eXc2cWtQMzFuM3BQR1VmTjREMmxhQ0g1YlVpVlNIenRDWTJSTXJPSVlIeUpzUkVuVDlzZVV0S2tNTDBvVG1RM3FiTmVkV2NMZUxUU1FCNFE?oc=5</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>46038.90261574074</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>European Farmers Protest EU-Mercosur Trade Deal as Leaders Advance Pact Despite Agricultural Opposition - Dakota News Network</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 17:14:06 GMT</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPTGNsT2xnWmJuMy1SYnJNeXNidVE0UmpSWExJS2kzSWItVzZaU1JLWnhPTzItSlJYOE1vV05hY3V0aC04NVRXdy10QURJak1oQ0JvbWZQdWFscWRmcXdTQlEtM3lnUnJ3b1o5Ymlqb1VKTVVwTEh1OWdNUWswdDM0cVBCT0hTSkNiVFdGLVNxZGlCOFJPcGZ0UGVoRWJTY0tEcFNKVGRtQmxmT0U2c1NLUEtISmd2MTU1ZVQ2TXhZcjA4U1cxelNTNk5qY0dlazhRczVlUDJ0NnR0QkJCZmtvNExlbmlCV0ZvVTdn0gHrAUFVX3lxTE9MY2xPbGdaYm4zLVJick15c2J1UTRSalJYTElLaTNJYi1XNlpTUktaeE9PMi1KUlg4TW9XTmFjdXRoLTg1VFd3LXRBRElqTWhDQm9tZlB1YWxxZGZxd1NCUS0zeWdScndvWjliaWpvVUpNVXBMSHU5Z01RazB0MzRxUEJPSFNKQ2JUV0YtU3FkaUI4Uk9wZnRQZWhFYlNjS0RwU0pUZG1CbGZPRTZzU0tQS0hKZ3YxNTVlVDZNeFlyMDhTVzF6U1M2TmpjR2VrOFFzNWVQMnQ2dHRCQkJma280TGVuaUJXRm9VN2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>46038.718125</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>TRAGEDY ON THE MILOŠ VELIKI HIGHWAY: Unprecedented Chain Collision, One Person Killed! (VIDEO) - Serbiantimes.info</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 16:38:16 GMT</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNMGdFWmNGRVhhVi1ZQTlDbkg3elJXa0ljTTVtZ1FYNnRib0FIeTJQeXMtalFvUWx2NUpwMVVGQkZaRWxCVDFRT2lGUkJYaFJFTVoyb0pYUVg5TXFuQmhtdG5ZVnpjZHByemJPQlNaMjcydGlyMmlyVnBlZGJvWUhMVmdoY1NjOE50SUl2SThuUGY1ZVNORWoxSWlIdTVBSmQ5ekVLb3gwRzN1QVhPelJNcTBheEJQUVdVcE9n?oc=5</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>46038.69324074074</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>The Brussels Reckoning: EU Launches High-Stakes Systemic Risk Probes into X and Meta as AI Act Enforcement Hits Full Gear - FinancialContent</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 20:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxPb1VtUFNVOTA3N0ZqVzJlb3lPYmpreF9pRUtuejBEb0JWNF84SzR1VTFaVlFmV0ozNnFJb2t4TURDelJCYXFBOUt4OVpHQ2JnNVdZUk4taTk2ZERlVHNWTzdOOENKcktPcTlLYS1CT19hdGxqUW1heklnUk5TSWs1eVdlMlNiTTJmaXV5SVIxd3ZTMzR4eFhocTJNWjZCMW1YOEhoRTdUWUI2YXhCU1JYZFZRYldpNzFHbzBseXVQb2ZtVnVuQ0RuZFNOTlNLemwtRDJfTW5NdnFVSUFJMFdXMHY2ZDQzNXdXb05EN082cExja2h6M0p0aE9xc1VIeU9TNzZHUXliNUdNUGpyMXZuSTdKNWctNXdxU1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>46038.83819444444</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>EU Denies Plotting Regime Change in Iran Amid Growing Protests - The Eastern Herald</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 15:17:14 GMT</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPcmtiOTlQcEhWeGxSOXhaV2xDWjZOMVVUU2pGUWZQMTRIa0pxa1RoSlpnV1ZlV3NOemwzclp6VFoyYlJsaXdYRkRwam9HNG40ZmxGTVIyRW5OUER6SFVYejVnc3JHS2h3RVJNVExXQ1RISFM2R2NFZXJTVkgyaDBVdzgxQ2tMaE1SdFMxTGN3?oc=5</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>46038.6369675926</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Local Town Searches Wertheim German Terms</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>("Wertheim" OR "Wurzburg" OR "Aschaffenburg") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR boycott)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Bamberg vs Wurzburg – Preview &amp; Prediction (Jan. 17, 2026) - basketballsphere.com</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 18:18:03 GMT</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNQ0VmUXB3LXY3ZEtJV3N5NzFwX2pMYk9PbVVTZmdrTWhfNk5ndEFPNXdIRkl4N04xMjRnajJhbkhhV2Z3M2RkNGxJSk9SZWp2UHlzSmdiYUswUzFwN3Z4UTU0UF9aOUcyNURRcVJuSjNDQU1aeVgtTWxKdDNWQmtoY29vOHpZeUZ6a3BF?oc=5</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>46038.76253472222</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
           <t>Ireland / Kildare Protest Groups - Social Media</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Kildare gardaí investigating alleged burglary in Naas - Ireland Live</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Fri, 16 Jan 2026 10:06:15 GMT</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOUndUTDZ1eUhhV0d5V0ItRE9DcDROblE2dzFNRXg0VmcxTHRoenRPSVJZSEJzd1diVGJMd0tvTGR6TzBzaDFUTDdMTkJ0NXdkUFFoUjRPbVRUd2hNMmZaNGozZWNoeFdPYkpqVmZwc0RjT0tSRWJqa0ozUGVoR2o4Nk0yQXdRS25zbURNeTAwc3hRNjFJUXFNQU9GOVJPODZGektkQXp0UHB2cHFqNzZacWFB?oc=5</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>46038.42100694445</v>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Almost 40 bags of rubbish collected in Wrexham communities clean-up - Leader Live</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPOXdIMGJEX1kxWTV1dmhKNWY3RGdJUTJnc3lnQUpUZ1MwaGhnbXVha0N6Y2diTXJ5QURfcGFjbHVsY2s1azlBRnM3c1JuNVVsem5UYnNfbzh4UWRFandlN3R6UWFnV2JjR1h0Ny1vOEp1SXdjT0FLc1huNVdTbWUxczJhQkRHaUNMcU5Xc2M3MEdiQXhNQ1JZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>46039.29166666666</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Elderly man dies in Co Armagh road collision - kildare-nationalist.ie</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 19:33:46 GMT</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQYTlKaXZadWM3SWJ0eWxtdThINEliYmpXaV9lNjk3X0ZuaWExUmhkaXQ4TnBLS05WdEM1a21vLTlneGkxdGMyekl3TGdHMFdOVE1weEJjT1E4MUlxNkFpZDF4TDlNeDZmTllNNXBqal9FaE9VNFhtV1ctYU9mQld6NjhhV2l2OEFlclVKUWhxVk5FSDA1eGU2OEVWdmI4WDdtLXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>46038.81511574074</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ralph Lauren: Menswear AW26 - 10 Magazine</t>
+          <t>Burberry banks on Britannia staying cool to boost sales - This is Money</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 11:08:41 GMT</t>
+          <t>Sat, 17 Jan 2026 21:50:06 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9WeV9aa1ZENFVFbjBqckt5d01NaWxseV9QX0FGSTctb3VnYXl4T2E0bWc2WHB5d1VtekFoVVQ3czItcTdmUDJQNmNqMnhnci1Qb3BjUWNHbWdWNmMzR3p3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPbmNoSVhkdlI2djVmS1g4MFpva0VidkJyT0lDUFRpYzhZUFJuektCYS1odDI0M0lrOUpHY0hUZTZCdVVFZGlTRVk5RVJPRVhROVRScTdmYVQ4aFJwNkZITUZ3UE4ydElxSGZNdHNnTS1XWkQwZXRyQkdGN2hKcHg3T3RaZzN4RFNyN0dFSGtfeFBuZm5KVWdiRzVRWmdGLTItOHhrb0JUMWlUc1o3b2dRRTFudlFVUdIBuwFBVV95cUxPZ09ybmNmM0Q5R1VhMGM0N2V0RGV5R3NuNFVJQ1ZtUzNDYkROcDltUk12bTFqaU4zM25Na3JCamZKNC01SlBmd3dxVmo2cFZGS1g2NS04SXhELVBqbnlacnMzemI3UElGTWpJMTRwVGZXaXlTQ3E2MlRsXzEzUjBXV3hhMEV3ZVh2SVpvQmp6ZFhtekpaT25aVU1yYUNhNnVTcVNkak1oWXNDQTM2MEkwLVBMWDVUQWVXdFZn?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46039.46436342593</v>
+        <v>46039.90979166667</v>
       </c>
     </row>
     <row r="3">
@@ -515,24 +515,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dolce &amp; Gabbana Fall 2026 Menswear Collection - Vogue</t>
+          <t>Reggiani names the rider who never won a title but had more 'talent' than Rossi - motogpnews.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 11:30:07 GMT</t>
+          <t>Sun, 18 Jan 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5XaUhqRVRGSVd0RkJIakxEYTlzNjRsckQ2TEZyVVlBMlIyOXpzUUpFSTZFMmxHbjY0MzVrOV8xWVNmejJqRTUxUGFMQWNtOEd0RTFpcFpadWVLRTRWNWRDU01PcEhSbW9OODViMFVVNHlVT1JudE1r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPWmdMQWpmVmJCWW9nZE1relEzNmlCaTJQQUo5UkVlNTExNEpjN3FLY0gwVFVHcDl4TFBFMmRCa2lZWEJVdnA4TXVReUx1ZFNiQ3EzN19OZXhTRWtmZ21scXRSREI4aFJwYThxU255RjF6d0NfWGp2bVNsTVZmS3VOTmJQVmh3eHE1OVVEQUlGbWlqNkFTZVpURDJoV195V1dweWNNRW0tUTFVQXdoZWVMeWY2bW1wbV9ZZXFhU05xVXJoUlJ3cDZ3QlFNVVJCbDVl?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46039.47924768519</v>
+        <v>46040.29166666666</v>
       </c>
     </row>
     <row r="4">
@@ -548,24 +548,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Men's Fashion Week autumn-winter 2026: See the latest looks from Paris and Milan - The Telegraph</t>
+          <t>Dolce &amp; Gabbana Fall 2026 Menswear Collection - Vogue</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 13:40:00 GMT</t>
+          <t>Sat, 17 Jan 2026 20:54:02 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQVWZoQ0pGcmNPNDZnU2tXc2llb3laM284ZnZSX05mQWl6VTRTV1VvNEJscklqYmhzaTB2MHFCdzNSeEN6Z2Rfc0xIcmNDSTBlSUstdV9WQ09Ec1lJdV80Y0YyX0dWbFZLQkEtVFlZRmtOdm9vbzdvcXcwZklLSTFMaHV5UHExTTJVeW0wX0N1YTZ5ZmwtQ09B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5XaUhqRVRGSVd0RkJIakxEYTlzNjRsckQ2TEZyVVlBMlIyOXpzUUpFSTZFMmxHbjY0MzVrOV8xWVNmejJqRTUxUGFMQWNtOEd0RTFpcFpadWVLRTRWNWRDU01PcEhSbW9OODViMFVVNHlVT1JudE1r?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46039.56944444445</v>
+        <v>46039.87085648148</v>
       </c>
     </row>
     <row r="5">
@@ -581,1113 +581,3720 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ashton Kutcher Says Tom Ford Fired Him from a Gucci Campaign Because He Looked 'Too Fat' in a Speedo at 178 Lbs. - People.com</t>
+          <t>What’s the Thing Only Ralph Lauren Can Bring? - The New York Times</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 11:00:00 GMT</t>
+          <t>Sat, 17 Jan 2026 17:00:03 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNdVdTdzRYb1NHd2FQbU9EUlBhVGZSOEtkUU02U0hqT1B6OUNkSVVXWV83dnZpeEkyUDZINU8tY3VLUlYxeTlRZnA3NmtJeDVXQVo3UTZmMzdPZHVTb3Vta2oyYk9jbXNnakZBakY5S0UzbGROVk9GeGk2TjZFcnE1eDhBZU91a3JD?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE81R212N0VKZGxvYVhtS1owTWZCUU1DaFl4WlY0MlVydGJhR0oxVkV6TXF5X0cxeTE3MXpLNE1pakVadElVT3lmUE9SanZBUUpvaFJQMURwSzhOcVB4ZXVYVTYtODQyc21qUVk4bGE1ckVLYlZKNm5mTQ?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46039.45833333334</v>
+        <v>46039.70836805556</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Here are Amazon’s smart delivery glasses that guide drivers and scan packages - MSN</t>
+          <t>Dolce &amp; Gabbana Autumn/Winter 2026 Is A Love Letter To Modern Masculinity - L'Officiel Philippines</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 10:08:46 GMT</t>
+          <t>Sun, 18 Jan 2026 04:49:32 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgNBVV95cUxOc0c3T0hPSXBXVm9uZlIydC1CT0NyajNIb01Td3hjR0w2N0FPT0FXUjFtdUVQeVJ5UW43OE5iUlhQNUVDVlpKRzNRb0l2LXVTaWRhQTRON2ZPSkFJa1JQUkoxTExpNHZwcHFLTGN4a3FvWHdwUjU4b2JTU1RxRHNJUlFxODFiOUNpLWNxZjZONDIxMVhUSmpzbm5ZbjdJWDVKcGhLby1aZUJDZ2swcVI4SmcxcVhRRHFDS3Z5ZXg0bGpOM2VWc3VqNElzYkQyd1JEbUxpT1BpMV9VTnl2d19HZ0o5RjF4d1FSOXNIMTg3VjBrc1JMRnVzY2hEa2JuZzlSdk45bmVvSHpXcXVza1pSM2lnR3JDQTVjMC16UGFtSWNleVFxbGVrWUlTQkxpbUV6SVZCZjc3NDJZS1dnY3JraFNHN0RQb0g3MUVKRmZOT3RkaXFkTEtxTWhHV25sUXJWQk5hdG5XQm9mN1J2eFBCY1lFRnpOQldmeDM1MnAxdTVlMDZ1amQ2dmExTkJBbThiaVNIdTF5X21PbzdmRG11TVl0Tndsck9TSXJjX2EyYTJXRzc4RGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPMkxDa1VUMTJNa3dPMEI3c09QVExHQkdYc2pFYjR2OHdfSERmZklkc1QzbmE0TGFxWlNXbjZORHFnY0U4amN6b2pWR24weHZzV2ozZjY5dzk4OVc3U1BzaWM3NnEwZno5WlA4QUREQUhfMHM5ZHRVaUdMM1lFaldMVzlSMkU4b01VdTdHdUZwdUQ5UFNLcEdfTl9iQmVnMTJzT0xnenhSWWpVQQ?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46039.42275462963</v>
+        <v>46040.20106481481</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amazon Secures Critical Copper Supply Amid Strategic Pivot - AD HOC NEWS</t>
+          <t>Nobody's Child's check trousers look like Claudia Winkleman's Burberry pair - Liverpool Echo</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 11:36:04 GMT</t>
+          <t>Sat, 17 Jan 2026 14:49:00 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQRWxQR0pLZUNuSEpFd3MtcDN3M2FOQWRJTEFEc21MdFBCUDM3WVFrQV91UC1Wc2RrSE1XZERRazFJTUtYcFo5dkFwZjdrTXI5MlM3RzFkQnIwQVRGMXZQNkI3M0lVZE15WGIweE4yVW9OTGFrTEF6QTk1SFJWY1VzcUxiM2tpWVppT1RiaXQwamFLZ0JOQm5GdXBnS0t3azFHREZ6dmIzbVpncEduMGN2bTFIc2V6dmJu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNREtEVTVJX0xFSGI0RzAxM0lwT2M0Y1hfTzhCa1BuSVJMNGl1WEpsOC05U1VLVDlidVFZOFJFT29reGtNdGgzbkx2LUFLd0pDNnN3SGVtZUtPMUNxZ3VleWFQWjByRWpnTG9zbDlRNTJLdGp5MU1wTDBQNVdBeVRNaWg1RWdwLVUzWEpEejFudXV2VGZYMEg5Q9IBngFBVV95cUxPeUY5MUk3REtwWktDbUJrdWYwSmJfZ3lPX3hma0gtZEVPREliWDY3emluZklRbGdwRHI5Z2cwb2dBMkhwX3FURHJJemlmODV5SGx4enpjSmYyRUNxemR5azRFT0FfSzUtX0VHcnNKVlhtME81WVV1ekFKanNnWlJITDZtRzFCMEpTWk1nVURmc3U5N2pvVGFHdFliVnNGdw?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46039.48337962963</v>
+        <v>46039.61736111111</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Are banks, post offices, UPS, FedEx open on MLK Day 2026? Do we get mail? - MSN</t>
+          <t>I Sent My Friend a Link to Dee Hilfiger's Chic QVC Collection - Homes and Gardens</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 12:21:51 GMT</t>
+          <t>Sat, 17 Jan 2026 17:30:00 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPY2pheDRwYmtmZnY3Wko2a2tZX3hPQmsxbGtmV1MxTV9zRlNtTS1MTTRMemIyQW1Lbkl2MmxZdE1PS3RWWERjeHRvVWZEOEFBdVZfZG4xQ1NtTjQ5WkNmdl9KQXlHdk1oNmloX0trR2I4VlZwMnFTZUZxM0tjamxLSm1Hek1mcFk1Q0VTXzJFTTJBMnItRThsMlU3RV83bjVtRnZYOTlibks5NnNpT0NGS0hERFNCTy1VaEZVZXlmVmM1OF9QNjhBNk5JWHhkc1dzaTg0aFJuVUI2WU4tQ0RieGFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQaGo4c3o4dlc2TW9OYW9GN01uN1RNTU5rR1puWDNCN2ZGUkZKbDd0TEZ1TU5FUFJ3aE5ieE05TzEyWEdXR2FGVUhPcjFzc3N1bG9JSzgwLUFjVDVjVXFEOXhSUnRxMzM3MEU2em4ta0NhUXlHMnJSVmM1SFlja1FYZVZSa2p0RTdFNlE?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46039.51517361111</v>
+        <v>46039.72916666666</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BP accused of ‘insidious’ influence on UK education through Science Museum links - PressReader</t>
+          <t>“This Isn’t a One-Off’: Inside the Ralph Lauren Men’s Show with CEO Patrice Louvet - Vogue</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 09:07:19 GMT</t>
+          <t>Sat, 17 Jan 2026 16:07:59 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1nY09mRFF3dnBvcmhTSFBQalZ2aTdHVWpJMEZxajVZSFJlRE41NGMwbTJ0QkwyZjlGQjNEVnFDeWxPdy05V1kzYUNUejlrX003Q3hXRmltVzlwa21MSk1WU3JCRWVJWG5yQm9USkdNZ3ZXVTR3ek1lcEVYakdsQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNNG9TTjdtbzg0X05BV21icHpWSE04aTNRY1k0VGh1eEoxM2hRX2Q4V3lZUVdIWlg3d1p1dzFycjF3ZDlxMnJERHNlTnVWVFlNdkFsRTBPbkVXYXBVZmhIcDU5YXlGSmFjMThtNG0xWmhqRzBFTTRGdkxBNnVtRVZVQ3MzS2wzU1FaSkFaOVplSXdkV1d1bzhsc01rM2o2MzVCM1h0ejJncjg3dEU?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46039.38008101852</v>
+        <v>46039.67221064815</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Athenea Delivers Justice, Prepares Madrid for the Super Derby Challenge - filmogaz.com</t>
+          <t>Valentino Rossi’s VR46 plan could now deny Francesco Bagnaia one ‘safety net’ for 2027 - motogpnews.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 13:52:34 GMT</t>
+          <t>Sat, 17 Jan 2026 19:00:00 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiRkFVX3lxTFBXeEtfN3BsVFdHalhZODhrcjBkRVlsMUVDWDRUajJ0WExzOVhWV3hqZ0FJWjZ1UE4zYjJOR3ZHSlVoNW9IaEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPWlZjQUNkcUpXMDRQTktuNHRWOGR3VHhUUjhTbTlicmFIMWxCc1RNUm9BekVHZDlWNV93S2EyQ3dobGMybXZ3d3FObHlWX2tVUkhrNGVCZ2dOTUNnTE52bVZoT1pOS0hYdi1JOElueHBOSmJvdmFZemw2eXBVYkFtSERjS0FvQmJNY3hybklaY3kwZU1KXzV3YzhLb25lQWtPZDFzRFRWYV9fUXdHTGUyXzEzX3U2SThrd2tBSm4zZw?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46039.5781712963</v>
+        <v>46039.79166666666</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MotoGP, Paolo Campinoti, "Marc Marquez refused Pramac, Ducati broke their word with Martin... and history changed": explosive revelations about the 2025 transfer! - Paddock GP</t>
+          <t>News, Valentino Rossi: "I'm worried about Graziano, it's like I no longer have a father." - GPone.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 11:23:56 GMT</t>
+          <t>Sat, 17 Jan 2026 17:48:47 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxQQjFlQWpKUE02bVBOcm1RQnBDVy1ia0p3ekFKX3NfNnJ3ajRKOXhWOWs4S1o1c1JtckZPaWg5WldoMm5uclJORm9tV3ZfbHRKWldRV1dUTzN4RTBCQjFWeEExbGJJWmU3d0JPYVlMeTROU2pGazF5b1JHZGdQR1BNbFh6VHBsLVNJTW4zWHBnMlduUkoxMGJWMlhNU2lXT21pN290MTFuYUhmc2xhWHNpSTFOUGlRQTdxejREMk9EUWRxY1pxdGdMQ09rbUs4cjJjWVVIdkdnajRQd2ZfYTlVSHZDYW5xVWthTmVKTGtOUDIyaTd0NWdObThuZXFLSTRkWlBSc1RvNUI2em1ibEQ3dU9RdW90eERyU1RZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPNG9GR18yRW04Y2dqODZwSzE4TTJYbVBqWWNSSFFtcnpHY2hzTFdDeHZUUDY3a3k5cUZlUWxVRHN3bGl4bk95TURwOFQ1QnhKYnVsZ3ZGeVo2MklLcmhrdktfX08tQ1ZLY1RPWDRleW9qdWRWS3dlc1N5Z2RUd200WXRnNW1RbEkwb2c1T0ZiQ3JTNndfQWI1MUhyTW9LaW1yTDFYeVRPcEEwbi1wa1E0NVE0eExqUm1fS0xXdndXdw?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46039.47495370371</v>
+        <v>46039.74221064815</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Passenger jet is escorted by warplanes and makes emergency landing in Barcelona - MSN</t>
+          <t>Polo Ralph Lauren Finally Met Ralph Lauren Purple Label &amp; It Was Incredible - Highsnobiety</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 10:34:13 GMT</t>
+          <t>Sat, 17 Jan 2026 15:19:00 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQMi1fTVd6c2RVQ0tFMGpzZk0yaUpFSG5xNmliUV9MNzBINEk3LTJfOXZJLWtuYUxwZnI3VHhaZW1adHM0YnF4S3ZJM1JDT25BMHVmOU9jbURrX3habk1sdER4V1FJVlpaTjNWVHBrbjh5cXliRnVBLUI3OXZZOU1OVVFJSFpFdDZ2d2dWaThmVUdlR3E3ZGNHc2xiN1NaQ0w0ckJZMmJINnRPbkU2aGF2aU9ZamplZWZURXNBNXQ2VnRTeGNQd2lpaktCZDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBDS3pzTEc5VWQyMVRVLUFmR0ZaQmY0ZkJMUHlfRXdrN1FvSXNzTVlnRWppcGZfLWtUUml4WldISF9mQnZtWktlR0NDNDR3YVJLZzV0d09UTE1nc2dQVVEtZXZ0bG8?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46039.44042824074</v>
+        <v>46039.63819444444</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Marcus Rashford told harsh reality of life at Barcelona – 'Probably not a place for him' - Manchester Evening News</t>
+          <t>Cartier Opens New Boutique in Somerset Collection - Hour Detroit Magazine</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 10:35:00 GMT</t>
+          <t>Sun, 18 Jan 2026 03:24:15 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNSGpWWlJoZDlVS2FJZnpKSC1ST0dxRTU3eEQ1enVyY0otRVVsQnppd1ZJTXVWd0hYLVBkazJTd1VKWGNwXzVqb2ZyRGF6RVV3RVFxcWdEMmRoOHU5NHJyRFBUcEtYM3ZaU0NNZHNCeHgtNVhxcVkxVk9iRjM2dEJkZDZhQ19ySmNWNjJfSTJUTFJKRmJTbU5uQmhmRFQwdFYtRklQcnk3S2l5TFc2RWF2TGFMREJFSXoyUVHSAboBQVVfeXFMTUhqVlpSaGQ5VUthSWZ6SkgtUk9HcUU1N3hENXp1cmNKLUVVbEJ6aXdWSU11VndIWC1QZGsyU3dVSlhjcF81am9mckRhekVVd0VRcXFnRDJkaDh1OTRyckRQVHBLWDN2WlNDTWRzQnh4LTVYcXFZMVZPYkYzNnRCZGQ2YUNfckpjVjYyX0kyVExSSkZiU21ObkJoZkRUMHRWLUZJUHJ5N0tpeUxXNkVhdkxhTERCRUl6MlFR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPd1hZVGFjLTctQTZlVzlWU0NkQ2NwY0VmZ2pHckFKWjR5OTFKbjA2SDRVY1pfT0JXOEVxR3E3TDhPS2tHTWdjLVpyMlM2Wi04LUZVMVE1ODRXUVE2UHNsTlZXS1Jab0tUNVUtazAxbnUtUjlESDFjZjUtZ0k0VVJFeFV3ckR3bFhTOGViSl9n?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46039.44097222222</v>
+        <v>46040.14184027778</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What triggers panic attacks at 10,000 meters - russpain.com</t>
+          <t>Ralph Lauren Reigns Supreme at Milan Fashion Week with Youthful Appeal - filmogaz.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 09:32:27 GMT</t>
+          <t>Sun, 18 Jan 2026 02:04:26 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPYWphR0dobEJZQlREaXQ2NXB3a3loaUtPVVBicHViNndCeW1jVVhCb0lqTWFaOEpOckVlbEdUVWFtMDM5ZllwaV9HV2ItUzlpYk1nblRnMlYzMEF2aS02YWhVMWRkM0JiZXo2cG1XQXZINUxiQmxvSXQxblNoWmZTZVVzYllieGdBZUY0R2gyb3pIbVR0TzdhdFItTkItdHBUU0hvekhXUXdJZzBFc2lXWFJoS29TUU10WHplQw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiRkFVX3lxTFBQOFA1RFFFNVcwUFkxQ2NjcVpIM3l0SFVIQjk5Um9OekhqMnROcDBFbGx2WUladDd6S0o4SkdjNUpYRHhEYUE?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46039.39753472222</v>
+        <v>46040.08641203704</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Brand search Google News and X (can't have 2 "And" terms in twitter searches) - BOYCOTT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("boycott")</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'Best to part ways': Hamann asks Liverpool to get rid of Salah over explosive comments - Tribuna.com</t>
+          <t>Ashton Kutcher claims Gucci once fired him for being ‘too fat’ - Page Six</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 09:57:00 GMT</t>
+          <t>Sat, 17 Jan 2026 19:22:00 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPQm5QaVNQdU01eE1GeURsMVN6cGZkZHFRVGhuekVYeHNVZEJPX3NWMUNTTDJ1aVdzbHMxWEhoVEMwTnlnTnpFNWFKUm0teXhSVF95YU5hR0YyaUZrcWcyQjBVbnJsSlRDQ2lBUUVJVk1kZV9EMW43dldmdkhBMm9EUklDNTEzVzZyZ3FQTFB4aXROVnlsUE5ua29RdmJzVy00dVFFM3U1anFCdEQySnJObUxSTWRzYmJqYWI0azFBalXSAcYBQVVfeXFMTWlLc3phc29uc2c4V19teVNCTlpmakFLc2pyakt6QTBaQl8xNzAtQWdNS0RXUXBPc282SmtUZVk4VXg1RVM4TzZOOEpzQUZGT2U3RnZtMEo3bVZ3S3FfZnF4akowMlp3TGMxSU5fR1RQbmFJS05QeTNLdHM0aUJIZnAzczBkZGFmcUdOZVNoQVZ3STlocFp5Y2pCZTFUQUZoRWdMSkJ6NC1sWEN1VTlXX0J4TUQ4Nk54VHljMFJiZ0FsY082a1ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNUFA2bW9mX1ZqWk9ycUx3SW82OWF0d1ZiU2FyOXhGSzlhQzN1Y2pCSWtHRkRjU3BraGhtTVp1UjEzX2RmcUxSVzNULWhfZXpKNHBSRTR3N0E3cHdHakptbEt6cUNFQjFEb0tiSWpNX2hWVzZlZndQbkxmUUxRT0VPSTJ4ZnRnY0wwenhWejRQUVJNeTdwVEpnRUVXUmF6VUNtM2dDeg?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46039.41458333333</v>
+        <v>46039.80694444444</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Filipino-Spanish booter Dro Fernandez set to leave Barcelona for PSG - FASTBREAK.com.ph</t>
+          <t>London charity welcomes £5,000 from local delivery station - London Post</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 11:33:17 GMT</t>
+          <t>Sat, 17 Jan 2026 18:25:36 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPaHJSNE8yZGlRRVZxOHBWZWNwYnI1U3Rnb0VKanFBcFRUZUlBdzlwS3h2a0tZeVQxaFFUZW43Z3RLWUN4Rll3dEJoVkhSNEVCbUl2YWdROEVjQUxDSXhqUmlRRjBBSkozaWg4RW84Z1B6djB0YlU4b3VLUEswTkw2bXBNTmtXSHZnSTVlVi1QT3JRNkJYZjluYkg2RXRNWXdtYjRHeWFRc0RzMXhrNmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPWUtYcmJsbUlMeUNYWVAtTU5DVzlLaFVMaFlZYmVlV1VwV3c3dkozMFhRa2hVbk1vaF92a2ZkOXhheENtN21TQlpxM3MxTGNucTkyTEZ0SlFsOENrck1MOW1IdDZZQzN4aDBrSXQyaWNPQm9XaEQ5QzJlbDdES21mUGk0M2lseW9mNlVn?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46039.48144675926</v>
+        <v>46039.76777777778</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Village Search Bicester and Kildare</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What the Papers Say: Row over parking fees at Stillorgan Village; Porsche deliveries slump - Business Post</t>
+          <t>Amazon delivery delay fears grow as union threatens walkout over 'Victorian disease' outbreak at warehouse - GB News</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 12:25:16 GMT</t>
+          <t>Sat, 17 Jan 2026 14:48:44 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPVVNnZFNkeVE3TWJpUHBwSWVZelVCVjdMRnFOTDVQZXpubTA2S2xNczRKVGk1R1ZMZ00yUW90WDk0TDFSVDk0QUFyallQUFVzV3MwbTBJWmRIbzNUQTkyWHhuY28tUDVKVzBLb2dnTG1JTXJub1FWaGZRWTZ5WFZtUTZOV2ZyQVRHS3hzNWhBbGFhdHd5RU81SlRlMHh5QXdrems3dEd5eS1JaXdsWjBTQUF3YVhsZFhqZUk3ZnFOQlZKNGNCMnhSWjVmVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1SUG5wZGY4Y1AtNVBrODVwZEtuX01PN0t4c0JEd3dxbkhFM1VxODlJVkdVUnp1UnFibXpDaklBYjR2b3Vydk13NXFFeDl2T1NDcWtQcV9oV09kWkpTRWRCVFNVOHBNelUyR3FNWHZJamhaaXhkZHc?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46039.51754629629</v>
+        <v>46039.61717592592</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Secretary-General on UN at 80: Humanity strongest when we stand as one - Unric</t>
+          <t>UPS in 2025, and how it's shaping up for 2026 - MSN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 14:00:09 GMT</t>
+          <t>Sun, 18 Jan 2026 07:21:30 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOdHN0VUFvN191bEIzR1F4dmVseW5WOWNpZGwzYkx3RXhkWUplanA1YzhjRUhCblBmbXc4VU93dkdlYklYZEJ2YWxxWmRZeTVUTDJVOWdmSm9zTFBtOWppWnQ3UUNLODV0WnJrOWxqZnhDYjdtUGRhN1RTSmZjMndHS19GZ05ydnRBd3FFSkxzaHdRTjJOVHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AJBVV95cUxNZTBMOVJkajRHMERCeDdtaU1ydW9YMXM1Q1NobnA5N3I5a3ZVSFRmRjdYNXpTeHBJaVFVMWw2eHNCcVlOeVg3X0pzem8yM0otWW9LUzlkNGFnd0RQMnVINVhEcjQ3azFYOS1fSXpQWnRyOElnd1NYQlUtaFBENmZwLU8tS2pUaHEycm9SVDJUdFlCTHlQU2Ixd3VDaGhLVENTSmtGdHFzU0toWTQwTm83aWY3S3ZGcFZ6Z2NlTmZFd241Zlgwdmd6YkR1dWM5amphMHkzMzIzS1U1NC0wY0xRY3p5RDdrRFpkb3F2Q0NFYW83cmpuVGItNHpvdGo4UGJQQjhjVDZteTdIcU9vcjg2QU5ELTB1ampjMVJKdHc1TTBiclBid1QyenA1dExfSzVkNXhzem5zdFdMOEwzeXZldzhDSEtOdVdfZ25LZkdYRGJBNlFKVG5QNA?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46039.5834375</v>
+        <v>46040.30659722222</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Young London criminal banned from entering an English city for 7 years after 'frightening' attack - MyLondon</t>
+          <t>Amazon testing drone flights in UK ahead of 2026 air delivery launch - The Star</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 12:45:12 GMT</t>
+          <t>Sun, 18 Jan 2026 01:03:22 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOb01vV25SQW1yUTBUcWdNYXlQUGVJUW53NVlEWERRcHhGTkw5VkhoNWZENTltRXlORlh4Qk1BaUM3eVJBSXBCYnNMNlM4RFpPTWM0YTltdThDbVR1bW5WVzZ3QWFBWklnOVpoS255LU44ZGhhNHBkSHh6TTV2c2xFZk56a1BJd3NHSVUwb0t0SXkzR0xjYlVMb1MxeUh1dTNF0gGgAUFVX3lxTE5vTW9XblJBbXJRMFRxZ01heVBQZUlRbnc1WURYRFFweEZOTDlWSGg1ZkQ1OW1FeU5GWHhCTUFpQzd5UkFJcEJic0w2UzhEWk9NYzRhOW11OENtVHVtblZXNndBYUFaSWc5WmhLbnktTjhkaGE0cGRIeHpNNXZzbEVmTnprUEl3c0dJVTBvS3RJeTNHTGNiVUxvUzF5SHV1M0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQeUp5YjRlT0Zmd1hkM1lublA1akp1V3R2bUZURHpyQm5VUFNTbVpMOHA2M2d1dEpVLS1tcVRYdU02cG1WYnk4SkI0eXZ4VnBlNnUyTGtuRFhoVjBmak40Rkh1aThmd01UVVZ2WXJtZ1F2dU14MUZKaHp0U09SUnRfUWdkN3dZWmR3MDBFLVJOazJhSnZ0b2tDRzh6RXFscW5JS3VlOXNxVU9MZUQzR0ppaFF6LVg3OXRrSWxFR2FB?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46039.53138888889</v>
+        <v>46040.04400462963</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Karen McDonald accused of misconduct in historic Crumbley prosecutions - Detroit Free Press</t>
+          <t>Firefighters Extinguish Amazon Delivery Van Fire in York County’s Dare Community - Williamsburg Yorktown Daily</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 12:20:00 GMT</t>
+          <t>Sun, 18 Jan 2026 06:33:28 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxPWnhpSHhaa1ljQ1cxREtOMUNaVDdwNlEzd2tIY3J5bkVUS25xb1Yyc1NsVzNYc3hCanlWdk1kYlJJWXNHVmduMExLbTRNNlVwaWcxbHlybWlZQmhiZkxxbERweWRfRlBOSEVJcG0zZFAyT2ZlTGlTWm42QU5md0J5TWZpZEFjaFkzSmZKc0NLMm1IcDI1M3I0cmpXMjlLTUdPQWx1QVBRRmxMWjhCeVQ4Y3ZDR2R0TnFucWZELUtxSVIzUWdjcWRDcldkZTV2YzJISUJSWndZeERFcXVoMkdWRWl0cFNsMDkzTXBWTlNXZnlXUHhLSjlLb2FyZnhOT1h6SHN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNV0NGa2tqejhyYXB6N2VsbGdVZ3NpZW9OXzlJZ3JWMjdyYzlNZHlaUl9fN2lBSWhndlF1NVFwSUFibWw3TGY4My1IODVaWFlvYlhZbnJuMDJFTDlLLXlmU01qUlpWSVRxWk1OSGdHcHBpcmttTFpKb3ZQVFFjbUg3dGsxVXhtVGJGWjVvZEcteUMwUEpjZy0tRDF0a1dyazU2U09mcEczLTJteVI3bnZKLXhERUVId0phSk5yZF8tdElyU0E?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46039.51388888889</v>
+        <v>46040.27324074074</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yung Joc to headline Mobile event to ‘bury’ violence after teen shooting - AL.com</t>
+          <t>MLK Day 2026: What’s open on Jan. 19? Banks, UPS, mail delivery, stock markets, stores, malls, supermarkets - NJ.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 12:00:00 GMT</t>
+          <t>Sat, 17 Jan 2026 21:03:00 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNOHpoXzhtbDI3aWZyZ09Zb2VOeUp3THRZc2VPRTJNZFFNTnVYRFFhY2JDOGZJWHB3MTI5QlVPS01VazNkNFVPX1ljUG82TExrVmF4eWdqVWx3bzMzU2tvemJBdG1BbnlyVTlvRVdKb0JPcVpFMUdFRlhuRWw4OFJja2p2RE92T2hsakZsRXEyVV9GWVVQS1hSY3JGRFNIVnZmREZIZWtmd01SOHNOSG92ei1QTEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQcUJIM1pHNWxTSTF0RGE0aDRmQTlNbWlueWlaRmRCZFFJQUlBbUp1c2NWNXJ4V280TkRUeWJuSHhFWm9Lb2tVZVg3eHBVOHFyaHdOWFF0RjRGcHlnd1Fxdjg3RWVDQk00QURuUXVXa2lCblRQRHUxajZOTXY5dHdfNjdFWnNBQzJXS3AtU21aTW0zRUJqcWZfNDB6UUREYjdvUjJLZEgwSTY0eHpBMDNNQnZ2Wmtwd0hrV1BTc0xDYTdZSHpUWkhqY3ctSUJrTlpFbUFqMtIB6AFBVV95cUxOb0xsVmxEbzhESDhHcGthY1RPcXJsT09XOG0tWC1Xb3BYNFhxZ09vX0JjcU5ycDdieUdhR2FXRzZyMTVMWmlDNUdQYVhubUFHdDJuckFHZWRKcU5BVUtpUG9NT05wbzlTVlFhWk5KY2VSSHRvSDBaVW80NU50eGF1cmFEeUFVZVU4a09sUUV6SmF2bXZsakk0Q1pVQk1qd2pDdE9PVHJwQXBtQjUxRlNfNWFyQmJwbFc3QUI1UWl0dkZwYUZQQnpVN3dnYS15bzhlN3VERG1nZzlFYllBLUhVcE5KT09yQWVX?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46039.5</v>
+        <v>46039.87708333333</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Where is A Knight of the Seven Kingdoms Filmed? All Shooting Locations - The Cinemaholic</t>
+          <t>Online shopper warning as FedEx hikes shipping charges — some items have $50 fee - The US Sun</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 11:29:27 GMT</t>
+          <t>Sat, 17 Jan 2026 21:01:13 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFB2Yy00a2ZkVWh2b0RsU094UjhfUC1qSU1OLVd3dWxkcjVkeUp2YUNvcklobENuN2NhQWhucGpKUlFpYUwyMTYxMlNGYXVpYllQMHAtZWIwX25NQ1RDUTBXSXJFamI0V3hXeHRPcjBoXzBrUTE4Q2Z2LUJIVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQcmE4STRRdy1SM3ZuWDdvUzd1aVdiWTJUdElwdUktbXZmX2p0MWk0eERmQzB0T2JxNVExYXBLeGo3QTBqbnN0LVVydTVkQ1Y1OW5xM19UWjdMNHVtdEVJdDlMZzNCc2gwd3pGeDVLZEdHZlRnUmVpOW9yVDM0c3NVc0RodFp2TGN2dUpiRGNVUGs?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46039.47878472223</v>
+        <v>46039.87584490741</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Grizzlies Coach Announces Ja Morant Decision Amid Trade Rumors - EssentiallySports</t>
+          <t>Here's Why United Parcel Service Stock Is a Buy Before Jan. 27 - The Globe and Mail</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 13:22:00 GMT</t>
+          <t>Sat, 17 Jan 2026 20:53:21 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNZWRaU21HRTR0dFkzU24xTVJTd0xyMEMzZ2pLUU9mdDJQOTBpazVNNTBFby1Sb1FpQkRaek54Tjh4RkgwTU1wZjhPMGl5WVN2MkwwcEtvYksxYlJGR0M2bkFjQlFsSWo5ZmFsRmRoQmh5Y3djN1BxNjhwU0d6bmJFb09kZDROOXNKZ3lwNDVOOGdNYWNqazJqUU9PdzdGZ1hMOEFBZWMzeTYyZWdiTVJTSk1sX2xPNUdYUHlPSkhwMWQyZE85eldRUGttVjU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOSnJqVXh3TWFZTHZtenFYRXNVdEZzNmhFaHYyMEVzMmdWRWtDRjhHc1VLVnVhR192ME9VYWx4eTc0R3poWGFkSzFFSnNXZFpSZ0tzcDE3QnJkZjBTQnVSZEdhVWQtYnpCUk0wbmQwUDVWTkM1UXFSTHd2X1VkVW5DMlNYa3RkZjdlbzh6VFJuQmYzOEFKbXEzcXJ2RERHMGtHbVpjaEJtbEQwend0cUNXQWViWFNZZ3VyTFpZUVMzakpzaVUxSzlVZTRMWF9COEQ2LXNnRlBBbUV3OHZXbVEtOU5R?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46039.55694444444</v>
+        <v>46039.87038194444</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rick Barry : The Explosive Genius and the Impossible Free Throw - Paris Basketball</t>
+          <t>Chinese Sports Sunglasses Manufacturers Accelerate Delivery Timelines for E-Commerce Sellers - The Asheville Citizen Times</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 12:25:54 GMT</t>
+          <t>Sat, 17 Jan 2026 22:54:49 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPUnZDRGtQTlRlMFZDNjItdTc4Um5XOFlmcHM1VDJGNDRqcEZmcTRvLW1ycUg1SS14eWk4Q2w1SzI3TTRtT1Bjb2RMeWZ1bmJzLThpV2N4U0g1TUI0bFhDOUF1aEQtbXBDWGFkakhucUVhVjlOeFZPclBicFhUUThIaFdkSHdnckZmdlRQang2WFk1UHhzMWVZUmVnMDBPN1BiZzQ3RGx0LWp6RTY1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNNU5HWEwtOUFPUi0zcHRwY1VqSDRkbVhSYWFsTXBoNFpLOXNGX3ZpWmxtU0l4WTcyQ3RZTnZoSmdsa09iSFZFVTI3X0JObG5KMHVKVzY3OVZWUDlscVlDbG5WQkNtWGw2a2haUEJuTXAya2JZakF5TXFoUm1pZlJEVmhxbkp4REM0QUp4QnNwLTB0RjY2VUVOOXFQTFZvcFBwQ1BGVVJWMGVuWHhwdjFwLXREWHVWeXlOSkg2QXJ1ZDNxcnhUN2k3SGpsV2xCMGV6V2ZQdk5oMURQcVh3QTJtOVIwUQ?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46039.51798611111</v>
+        <v>46039.95473379629</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>“An unbeatable detective drama”: Astrid: Murder in Paris is the "original" crime series for wannabe sleuths - Good Housekeeping</t>
+          <t>Woman pleads with Amazon driver to return cat, claims he was caught on camera stealing pet during delivery - MSN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 10:01:31 GMT</t>
+          <t>Sat, 17 Jan 2026 21:57:22 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQTFVwY05lX0hhd1J1V2Q5SW9TX1VDTnJvX0xZNkxQNTM4YVhJSUt1Y2NkQ0YtVzBMd0d6Vm9uY3JhYVpLaWtjVjFTWVN6SE96ZnhHNTAxWWlUdndUN1dHcURtcmpESHUwd0ZsZlFQTVBTZnpqRUI4djktNGp4bDJTRnhuRXdKTHIta2pzc3hmMFFTT0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwNBVV95cUxQQXRWS21MREJ6MnJKT0xHVTV4QXdYdzVzZUhVMzhZSVJKMDI0QU9mal9xOXJhTGxubEZmNGM3N0ZnY21VeHRFNm9tUVJCR2VFRDhnaE9ULXhmcHFDUzNBQ1VLWWhtWmE3WmUxODE0V0piVk5XMmx3V2Z3bzhuQ2dadnZ6Uk51MTBIdHdyR1M0TkliczVzRkNMX09ZdFNoc0VxTzhsRDk4NFk4V1VaZXBhVnh1ekV4aUg0ZTFxZ1p5cXRLZk51VWR1ZHQ4a1BSa2hBNmdHTWU5dkFFM3FSYk5xV2RzbEVFazk3ZjJBdnN5cnB5U2FMVkRMbDk3LUxlRzF3RWd1MFNtUThkRGZOZ3Fvazc0NnE1aDhhZ3FVajBIclhIS0l3azFhZVlFZVVGODQ0T05wUWpnYWlUcXpqekt2UXN1Zy1RNlB4ZFhIM1o2RHVMbGJrUHRwZ2FQdXVuVEIzWjdlTktYT0tqV0kyU2RFZXJPNjduellyYlc2cXdzVThESWp0dkJyY1E3OVpLanhfdUEzckhfVEFhRWM?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46039.4177199074</v>
+        <v>46039.91483796296</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fabio Capello and the Inter-Milan Scudetto battle: ‘The two coaches are intriguing. Chivu and Allegri are different but they have one thing in common!’ - Tribuna.com</t>
+          <t>Court Orders Amazon India To Refund Faulty TV; Refuses To Consider It As 'Intermediary' - Trak.in</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 10:47:10 GMT</t>
+          <t>Sun, 18 Jan 2026 04:30:00 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPd25mZmhEclRJME45bll2STFMVnFicldwN09XQzBaTUEzUjRJbldmWm1NRXJHZGhVb2hUY0g4aWJrc08yUnY4bzZhSmFOYmZaOXhTMk1oT212eXUwMFR2cXBwTkRrVkJhcC0xZFNqbl96dzgzTU03MnVZRWFid3JCcmJleV9vYndXQXhQWEN2RWd0ZWtfNHRuVy0wSDNUZmVzX2o2aHc2bk9Kc3BqYlBkSHZlNmdRY0RNZjZVNGRFckNfcGtZaGkwStIBzgFBVV95cUxPckdrTWVzTVJCWG00bWo3LWRsWWRxWEJTdkF2dEpGU3RjUEVERllBODk0OXgzWkYyaHhOdF9YWXNvcXF0cTNTUHZVSl9WX3lxMU1HanByckRVZHpUWVpKY3BYVXIxTjcyMHlJM2Vpa2d6Z014U2FFTWVzeF83Rl9JVEZ6RmRlUWhVQXE1NzFPbFZ6eDR4VVI0X2J2YVM2dFUxc1huX1pPdWozcHZjSFk4M0xvaFlrR25sWFpvcnh6alkwd1BITmhobVl5c3NkZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxON1ZQcG5vSUM4SUt4OXhoa25UUG9YSVUzMzRaUTBiV3JNZExhUG5RbHY0MWktU0s0MkUtNDQzRHF2R3dOdkY4T1dkXzVFOXlaRk1oTk5ReTVCbU9uSmpVR05ldzNpSnhUdkFZRTVKUFRBZ0R6STdHTl94cXA4Mmx2Zkx3TWRPaHgzc1JveEctN1dfc2tIR1dXU2ZncFFVMzNNSE5UVGlLdVdrSGFCWXc?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46039.4494212963</v>
+        <v>46040.1875</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Udinese vs Inter Milan, Serie A 2025–26 Free Live Streaming Online: How To Watch Italian League Football - LatestLY</t>
+          <t>Royal Mail launches investigation after undelivered letters found along Ballymena river walk - Love Ballymena</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 09:01:52 GMT</t>
+          <t>Sun, 18 Jan 2026 01:07:07 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwJBVV95cUxQbkJNMlBTWU0taVJsSlZTLVg3OXFOdFNsdDBVemNHTXFQcnJDT3B5QlV2UjhYQU15MXZzNS01NGpYdkNUdDJIQl9EYjA1aFBpdVJkcWxvdWZfc0ttS0xPS2pmUC1sRjdrdktRMDdxck9RVE5zUldabVdfbm40MmZCcGxRUF9mUndzS0Z2RWZBTmowUzgyUnk0Z0NCMUZONTV5NG5vck94RExKdmlHWi1tVEUxMFRpa25fZTBob2hpQ3pfek9HNTVCSTBYd3hPTVhqbTFEMmRxaTR6TWFDTUtrZnNYTzJFd0tnZVdtaEZqT1kzWEJRQTNGSmI2c3lvczhsbVJXRVIwVm9LYjVhdFpOd2l2YlNjYzdrNEVRRUp0N2ExbHBUb2p2NnVhenBKTFNRVkdjU3hvONIBvAJBVV95cUxNNG0zTWI5SmNCelBkTGlvWXhnRFVLQjVKUUdVLW0yN0tvbkRPOWs5ckI4WWlMZV93M3JLaHdKYlFEV3o1SWtkdlplWWFjb0hFc3gtckhXQlBPLURwTXFGNHFwdjJNWFQ5RG00QUkwUFVOMDJLYk1aTDk4YXNvUDY5NUJnT3IyamZJbmdfUXNLVTFMTUZVdjI4X2lhLTVIVVNxSjdYOUdKUnVaT0tUdjh6ZDRCaWk4U3ZMRHM5Q2JvbF9yNWZaSV92VnVzS2t5LU0zSmlKZVZWTVpSMlNuaVdDMllEcVprcDkwNVFTVzc3VUxnUkQydEpoMWNkLTl1MEgtQXQ0SnJYRDlwaGZPZkgyNi1XdVZER2RENmJvVzk0cXlXdGxOZjJQc1VlQ0JFUlVFQjllMERyM20waVBh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQUWhCVjhVT1ZMTXFYYU9ZVFVDMXc2V0JzQVc3Vy1KMncwdEdUbkdCc3NhcUlwMHRVX2MxN1hJRDNBb1hYYV9DS2FEdTlqeF9yNDlQNjBrTms2dW1xTHNOeE9fRnhUVTlHMl9aVWd5YWJFRkZNYWZwU2NNTk5fQzFmbGdRNElER0VLTDVMbGxUM0w2TTU1WHlIU2c5QTBMeFl6WXkxZHlJVGwtazg3R0doSnlSQWtiRXBXYS1fNy1rVm9XMGNJMWJhMzVR?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46039.37629629629</v>
+        <v>46040.0466087963</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>French farmers wrongly accuse Brussels of betrayal. Macron’s complicity could help the far right to victory - The Guardian</t>
+          <t>FedEx Expands EV Fleet in Japan with 17 Electric Trucks - Electric Cars Report</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 11:19:00 GMT</t>
+          <t>Sun, 18 Jan 2026 07:51:59 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOelBoSC1uYXI0UF9CV2VLZGtpWWRrdWhtRnRLblNMS01BMmFYRDBRdkpMbFdqYTZucm5kcXA5WnNHZ0JuQTRkNkZDZUtkNEE0Z2V4WDFsekNkT0pOTGRacnZpWFRCdGVQdzIyMHVlaVl4LWZGQjZjWE5KX0YwQjA4alRJNGF5cTdSMTY4Q1gxTzB4MHlCMkE4Y0JRQmVsR3U0OFlsSUU1eG9PSENObUNkaU5EcUw1YUJVcWRfU1Z5R3o2Y3NkcnNQcFBGOWtTcFBGYlpnVl85cDF4WmljUllGVUpTTTRnY01oWXlhRzY5WGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOdjlCZGRQYlRUeWlCRmtTQzE2ZnE5Y0t2NUFNMnpEdWo5ZWdWOGluazAtWVRQZU11dkwwNG9oUU5lSG1MZlVPX2Rxc1l1NHZDM2dUaDJEd0VKRlJXdEVfa1RsZjlZTzRkVFpxVjFidURITUMta1FlNlVQbjB4UTFQZkx6MVd2blVUWGpNMnQyVmNtRkxKbFZZYzZrcw?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46039.47152777778</v>
+        <v>46040.32776620371</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Police intervention prevents an illegal drift meeting in the Voeren - Brussels Morning</t>
+          <t>Gunnison Copper partners with Rio Tinto to supply AWS data centers - ICYMI - Proactive Investors</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 13:00:16 GMT</t>
+          <t>Sat, 17 Jan 2026 19:00:00 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNaUROaTU1RjZEVkJQVGp0c1FSRTRnZHpEV0E4Q2NxNGRUaDR3cWNlODkzZm1kNi1mcEpYTldpX1lOSGlkMk5TcE5XNlZqMGZJc05Jb2FGX3hIY3BXRWFWRWc4SmQ3TE9JRW9Bd1c0TE16NFlObDJTb2dLcmRORXVVUm9XR1ZJZVRJSUFWZ00xSkpuaENIVmk1ajg5akFzUE9GaVo1Qw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPaExreTV6ZnI5a1BhbENFMG1oRVNyUTlfVGhOVWZTRUVFY2xXeVR2UGUwekVzS3ZQclJYMjAydldVa05BQ1NkSjRzaVc2cE5ZTXFzV29nakZGSW5CZWlHMERDWUU0SEltM1drZjBZVksxQ2pjdnZzOVcxVUphUUd5NzZnaHZMc1NtOWJRZWtzQkowcjBjVFppcG5CeFIwQTNtM0VSeGxZdGQ2bWhBSzU3RWZxeFZCR0lpLWRvVGY1amJpR243Sm5kR05YMXYwRnpwOE9VRmZqUklpNzhOVmc?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46039.54185185185</v>
+        <v>46039.79166666666</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Police uncover large cannabis plantation with 550 plants in Kasterlee - Brussels Morning</t>
+          <t>Swiggy, Eternal under pressure amid Amazon's quick commerce expansion says Macquarie — check downside - MSN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 14:07:49 GMT</t>
+          <t>Sat, 17 Jan 2026 22:34:48 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNZWRwN3ZRdEl4SmpPTExrWEFKdnBvbHN5bkYzVVgzbjZoMEdTZEljdnVORmxyY09RMXlRbzljcWpFMWtGbFRERW8zXzQ0Nkk1Szg5elpWVlIyOHZzRzgyMlpfU3AyeHRTVEt1Zm9RX1VPLUEzTVFXeUI4UlBrSmJTR0RYanZDSGQ3Q2ZkQkxMdW14NkV2MjdXazJjdWM4N0RUVS1tSkxMRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gJBVV95cUxQS0lCZkg3cFRoMmhWaTh1SmdwZWtNTldjTU1xZGlGa0VwZkVlTkI0SUJrUWt5NXp4LWdSMXMwdm9FSXJLMXJramdIeTBQLXdBTmM1NmhjYXFEYVJnLU5XekJhSTFRMmQzLXAySjRRRHM0YUJHaFlwdUpacS1fZUNuZGxmSDkzVVJURHMydTAtY2Q5QXM3SnlBVkJhNVhHR1JYMUlhZkxtVk5SUmplQ0hGTzhTb0xGN1JOVTAyMjJLMnRIV19VenVzOEpmMm5aaVVrSjdvU0stVzNKNGNfY3pTZ3pjQVZ4dC1PS1VQZVo1Q3VfYngwWVkzdzBmT3Bfa2VoejhiT1hHRFZ4ME5RTnNwaTQ1aGRZM1llYlpnZDJIMUZiaFl3TkticVc4enV6eU9ucjV6SWtlc093bXExS0ZjZlUzRm5WLXpMTWxJVTFzeUdTZ2ZXUDR1OUNnRDVVVXA5N0Y1VUY3SGI0QjBoT0lJeDJwLU9DQQ?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46039.58876157407</v>
+        <v>46039.94083333333</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romanian Murder Suspect Located and Arrested in Bali - The Bali Times</t>
+          <t>Amazon under fire over alleged fraud scheme worth hundreds of millions: “Trojan horse” - AOL.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 11:31:09 GMT</t>
+          <t>Sat, 17 Jan 2026 16:08:08 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOZWxDUWd3eEFCUGUxcFJENE03VjZDNTNMcXFrclEwd2M0Y1AwS2huQ21oX0pDRFNrb093QXdBV3REZ282Q0NLYnhYYWxHa0o5R3BpZmhtRllPeWZBTXVFY0I0QzFEODVYZU1UZExNX1VCTWhsLTQya3F6cVNHNDlIRGc0VWp3Z3hIanF3SVRQRGZHel9FVlVZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPa3kwSkU4N3Brbzg0M1pld0N0el9GNHp4U1BaM1pSczYtUmlRb01zSXRMWDZLcGpTV2dXS1NMR2UtbnRiUFNFYW1DYjRIQ2Y3OGFXSE9CZXl4THJ0RUVWYnF6NVh0a3loNmtXSjB6X2ZqbzVJMGhMT0xiM2FuZjZZYw?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46039.47996527778</v>
+        <v>46039.67231481482</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Carma police station relocates from Genk city centre to Zwartberg - Brussels Morning</t>
+          <t>The Ministry of Communications continues to assess the possibility of terminating state support for the delivery of press in the Russian language - Inbox.lv</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 13:36:15 GMT</t>
+          <t>Sat, 17 Jan 2026 17:23:26 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeVFDTFRYdmxMLVpxbXQwRmNHOGg0QTVMWXlqWmtISC0zd0Q5TUpqcEFPalY1WkpUWGpfWExwaUdpdllMNmd5VjJYZnFsclk4Y3JpYWx2OXBzWUlISGxrWmtVRFNGQjM0bG9URk8tTzZ5bnVqTGgyb1M5bHhPUGhMRENHQ1pyUHdmQ2dQdnEzQnljeHZIbnRtWm12dUZUb3EzNHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxNZVVVUGpwaWVTaGRtQzc4cUVyV01yVHgwUEIwcWpKTjZOQUYyeHlsZnlsRkdVcmJYZ0otODU1eGx0V1pyQWJtVXBMUW4xNnhCdDhZM2xuN1gtWXc0THlieUwxT0RsZkNkX1MxRVJCU2tDNjkyNWdISHprSXRBZjkwX1pLSTJacHdYOVlEM0JyendsTi1YcXl1b09uakdCaWwwbml0N0pNRGV1cEowMkdHNkRkUlloWXIzbVFLeWJRZDBDdEZhRnJVU1BZdGcwUkI3dkJuUnV4aHpWbTh2dy1VX3hXRENQeGNUdW1XeFZYR29vTXJzbUNFSTNZOENFa3IzTS1sUm0tSW1vUWhKVngwb2NqbUZCZw?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46039.56684027778</v>
+        <v>46039.72460648148</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Antwerp white march held for Firdaous, killed by gunfire - Brussels Morning</t>
+          <t>Grovetown package theft report reflects broader trend of empty iPhone deliveries - The Augusta Press</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 13:07:34 GMT</t>
+          <t>Sat, 17 Jan 2026 15:34:51 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPLUt1RTUzcFZnY01kN3ZNcmNtUjF3NDZnSHBMbUlKOE9kR3gxLVJDSVA0T2t2NTFxdGlHZU9lNF9pbFA3SUlHQ190M0pVbFFMNkNuVUpZb2JVb2hySkU5T3hlclFHRTdBUE9aRXFCVjJIX28xRVZxRWRIOW55eHJnMTBkUEl6bWF6ZnRqUVo3ZGF3dkg3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPQjFBck9NOTdTUGVhd1JlRHVEM2N0REc3ZUJKdXBXTjgxa1l0Mm01QXVtUTI1cG4yQ1ItU0lFMUMzdHE0eTdjamFLRGNSU3JGZl84WXpVckNBQlk5RHM4N0s4YlRYMUJ4czZlT3l1VUtTRGlPU1VKZnc5N1cyZmFwYzI1SjNxdU5JZHExQ0VEaVp1SW9UNHlYa3haTXdSVVlJNWQzQnBYSzFILUUyVmc?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46039.5469212963</v>
+        <v>46039.64920138889</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Police helicopter deployed in search near Bierbeek - Brussels Morning</t>
+          <t>Man receives Nokia phone delivery 16 years after ordering them - Dexerto</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 11:51:11 GMT</t>
+          <t>Sat, 17 Jan 2026 23:00:57 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxONkxQS0ItdVNRUXlLUzJEYk9BcTQ3VEpiV01oLTMzMVJyNHZrSWFuX0ZiNjRLSXlYSWhxRlE2dklJdG5yMVJBdFlvQzZ0SnhLczZIVjlHYXdFSXJybGZXdms0YnZ6LXMwZHBqWFhsSWp4RGdMaVM0Vi1FVjZhVzdDMWg1R0hMMWJ6NDVIU2pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOb1JJN0J0WndDTXlQNEduY281RHFmOHU1VXAzaDJwUmNLaVVkRXQyejBhMTcxaHZPUXdFLXplRlRqMklYbHdMR2MtSWNuSGpwcUpQZGhTclJFMW5YZXFlZlJYVnhpYTVRdV9ROThSTWhRV0MxOVNKLWJPTnQ3RUhBMllWSGhLamx3YWg5YzZpeXBpWnJkU2pmbGZ4TlR0dHp6UVFYS0Jmd3dYa0JwSlE?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46039.49387731482</v>
+        <v>46039.95899305555</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>E.U., spurred by Trump, to sign mega free-trade deal with South America - The Washington Post</t>
+          <t>Okaloosa County Mugshots: A Window Into The County's Criminal Underworld - sohh.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 11:31:43 GMT</t>
+          <t>Sat, 17 Jan 2026 19:17:24 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQRVI1SW1SUVpHckViLS1jc3RhSzJlVHppcWdtX1pzbVdQN3YzQk54Ym5FT1dTMTFpdnM5TTFIYkFUSHFyV1d2cW9pcGVWQ0ViUjdOQVZZREZyUlc0ODB6OTVXR0FYZElBRlRsMWtFQjVsU05YRV9kWFpvcThhbm5FNDFDQkQ0bWVCdXo2Y2RB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNc0lOSWU0YlRIbnRfaUR1aVg2TzcyRWFpRnpJT0dRUWw4OGJkUWtFRDVDRlViSlZBLXBUMTlEckJBX2RXWE5RVXNVbUladmkxMURVRVFWUDdxVlBKMzJQX1FEVnBoeHhBNWNFMnVRZWMyWGtzQ3RYYmV1NFVmZVlqbG4tdUNmUTRDd0M1NjI4UlNPX0lCM0FN?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46039.4803587963</v>
+        <v>46039.80375</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boom opens new neighbourhood park with residents’ collaboration - Brussels Morning</t>
+          <t>Five Observations from Bayern Munich’s crushing 5-1 win over RB Leipzig - Bavarian Football Works</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 12:45:27 GMT</t>
+          <t>Sun, 18 Jan 2026 02:00:00 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNdWZIcG42Y0J4MkpRRG1ja19pT0Z0MHMwWjZ1ZGZlYV9rOFBPb0VraFVsTVNBb0NaVkZZNEpBV19LdWJJX2x3dldaU1djTDhvelRKdGNpRGRaWWpQNG5SblhmeXd3VmYtRS1kdUg4VWJPWU9xbnhOc2tIMjEwQThvYjlXZUNIYjd3c0RaZm1UUERKYkFOUVNrd1FRRGFzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOX09jRFZaYkxhM1lEdlJwX21nUmY2S29TT1N4Rzc2bGJzM1BxWmFJMzRDOWJtWlNKaGMtdU51MTJpMk5UOEc0UWNTdTJ0LU1EektycFJnR2dBWDNNQ0dpb1B6TGhrdVhHZ3NsMDlRUVdHWUZKU09pcmNYalhrMU1qaHltSy1ZVGc3aFlabFVwRnV1cmFYUVdPVlFFZGw3NVYzaWZyUm9acW94S0c3VWNBVmRqYW5GYm1IS2o4OXQ3TG9pczV3S09iSWRHWlRwRUFHcy1jYU8zeUt2UTNiakQtUV9uZHBIRVhiblZvSnQyYjNhYjJNNEVZR1k3NG1wUDN0OHhxQ1FHVGVIWFlV?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46039.5315625</v>
+        <v>46040.08333333334</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fluvia fire brigade conducts diving exercise at Avelgem container port - Brussels Morning</t>
+          <t>Bayern Munich Takes on RB Leipzig with Jamal Musiala Back in Squad - SSBCrack News</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 12:41:42 GMT</t>
+          <t>Sat, 17 Jan 2026 17:22:42 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOemhnamdVbkU1QV84U2RMVGxqVXhNenhtVXJMSzlZcFBKVlV2RHFCNlRJNmpvQS1QalBHTld1OXJlZ08wYjlSbW4zallBSUFfNE45LU5sMUNQNTFmVTFhckdwNWVjVWkwZTlUSW05b0NTTjNtOWxtXzFhRUEyM0dJeWpwTTdWWno5RUEtRlFMbm5ZZUNac1kwSV9yMG14eHFiMzkycUI1Q1Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNZ1JYVkljTVFTdTUyVkpXOUh1SWh6anZaczVWUm9UTENwbm5MY0dfRDFyZkhJS19MM29NSUR2VG9BZ1N4bi1COWM3VTlheDl5S0wtZVhCbEIya1NMTHBQQy1DYWFXSDNqcFpjSm41cUJRZlAzaDVWSmx5aEpoRmlZTGxCUUc3VkR3WExmeUptbkcwVHB4SlNpbw?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46039.52895833334</v>
+        <v>46039.72409722222</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>XR and JSO Broad search</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>"Extinction Rebellion"</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Video: XR disrupts Tata Steel Chess Tournament, dumps 2,025 Kg of coal at the venue - NL Times</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 14:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNOU9XRmNFVkE5bEk3M0ozSWRtdy1kam1UQXp6Z0xhWnBZeWdsZHU2ZE82SHJ6NFFhNy13QzBsb05KenNTNHFYQno5aHNESDM1ZG9Xa3FDZkFsUHJFNXhxeThTQy1fSzczdWlMNU1VZTB2WlE4VEpuUUZERHNwS1dIalNVWlVManZRMmppRGVERVZxN3J4VjloYm5TaFBNQklMZlE?oc=5</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>46039.60763888889</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>US lawmakers face pressure over organised retail crime bill - Retail Insight Network</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 04:09:57 GMT</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOYXdsZHVuN1pSbnNnd1VlTHA0WUw1Z0hiOU81QWRxMlNFeVdvUDluTmZQQjRvNGQzMW9lZDNvV0NBUUdiUlhwVy1JQndvekg1TVphNTFjYmhIanhnZVBHU3lwVjI2cFBZTy1LbUpCNFBMT1J6NFVLRFRDWF9JNkJjNmFpbmNYZEZpcXE0YXZ3ZTJjMWJYYXpaVEtIN2ZfRV9nNTZ1akxBWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>46040.17357638889</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Telford shop thefts: Police release pictures of four they want to speak to in connection with crimes - Shropshire Star</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 15:46:42 GMT</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOVDhGLXhlNzBLRkF5elJ3bVpUZUV3R0FmUGZybjZ2VWIzOXV3QWpUa0xhanN2V1hRenNVWmY3VmI1WXYyc1JRTGJBTWo0S1RjWVFGZnVPWDlaaXFLSGYzaTV4c2JzaENhMGpFMU1qd3BEN25kRDFxTHJuSGJzQ3FhVEFCSm9tNzVmS3M1QmJhWjMtSnNOQm4xUTNJaXNuVm5pWmRYR1dxYlpVZDJXUnQ5TEF4TGI5SnZ1dW5jQkkyVjBCQ1pXbEtrVGdRU2RyZkdycU9VVEdibHRKeFU1NXoxa016MU1hWGRsWTJENlZKTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>46039.65743055556</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Prolific shoplifter banned from Northallerton and Thirsk - Hambleton Today</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 15:35:11 GMT</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOR0N1QXlIUEJiWWtQbEdmS295X3A3WjdLd1ZHSm1sT2YwZ1BKUmV4UDZ3T0Y4dG01Z0JHcTB2SGk3TXo3SWNTYjFWbWlNcTBxT3R0VFc2NGY2eWZSNmQyc1JiOXZGODVCRVRDRmwtbU1KRWx4RkIzNV95eXhUcDMxd0lZaV9naVJ1ZkRpQ0xsZUh2UVJB?oc=5</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46039.64943287037</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Man, 33, charged with 10 shop thefts in Sandwell appears in court - Express &amp; Star</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 14:47:25 GMT</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPOW9Rd0ZZaGVWMGJ3NjRUS2dnMDZCWVpvanh1Q0V3VGZ3MEItdjJ0bjZZT0pqMlpjMEQta2NDYWRlMVpES0ZTbXBPVXQtU0ZaV1lKUDhPU3h2WDJodGJHNFBiNkhoV3ZWZklBR3NYOTNJRXJzVXVuR2gtdEdQRmZodGR4WmlHQVBwbEQ5QWQyMGZkQkJnaUFfS3BXWHdNQ2R6dHZFUF9EcGVfU2c5eXhqME8xNE9pQzZK?oc=5</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46039.61626157408</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Details of new citizen's arrest rules unveiled - MSN</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 17:55:54 GMT</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AJBVV95cUxPclR5dzJtWlVvYk9rMmFiWmY3YTNsWnVhNFV0aDNUX20wR1JYVWdTdm15a3UtZE9RR0RsMGhTRndKUlVJai1kZTBqQUtyWFpIUXRTZGIwY0hwWmVDX0FERDZON09ZYm4wWV9BMVZPVTQ5R0ZCZmJkeUc3aEVyRjU3N2NNT1dMT05wdVYyeGVuOGh3eHpVcWJkUGJFaDZjblNFcFVQaGFrMlc1WWZ4aFhvalpGUlZWOTBmRzRyVmpWSXZkcWdpTjRHR2lpclBLSndXZEV3SGM5RU15SzU2a2oyN25FMkEyRnFkSGlkTU5FR3dPai02M01UU3VSYkNjajNzOGw4YjB3RlUwU2J6b1RPTTF0Ym1jdWN3VXNtUlluSDlUZ1Jwb2diVVJoZVJkS3liTVJVNi1lODZZZFMxTjhQOENPTUVEb0g5SlNsMHg1UGx1OUdE?oc=5</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46039.74715277777</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Jailed in Essex: 6 individuals put behind bars in January so far - Harwich and Manningtree Standard</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOMUFfN1liMEg0TmNRY2thUFN5aUNsWVdyWllQY2NzbHhJVXNfc0RwOU53UFpoLUlJNFktWG1CQUxlZ21XYlo0T1JJTzh0T0ZDR0l0bGo0NTI3M2tzbjluQTFONFl5WThJMFczUEUtd1VfSm5tRzlTWl9oUVF2RDlGOXNzRzFMRlU2Ml9wQTh4VnUzcXlUT1A2aUZZeWxka1drU3YyRzR1ajR2Y0xLUmdXS3dn?oc=5</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>46040.20833333334</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>'Privacy' law to ban common system from stores over dynamic pricing fears - The US Sun</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 19:08:33 GMT</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPSUZsVnFrMGhqRW8wdFZqMWZRR1pYYzQ1bVd6cjlsY2V3RG5mb0NpMXpuT0RUSXBZVG5mSWNhREpkMk5GLVdUVlJJVkplTWxxVEJUVHV4QlI5RTVRc1JNejI2YXUwWnl0NWZkLTkzT1JHTUxnM29OZnJNMmY2eVE1T0k2ZENmMXRobzVYb0pSNG0wQk5wSjNGZzAweERDcVk1VWow?oc=5</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>46039.79760416667</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Two Foreigners Arrested in Thika Over Mobile Shop Theft - ynews.digital</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 08:13:36 GMT</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPS3UtQ1Z3TzRHRUZKMDE5bVBLcXV3bHVmX0xDVUFENTJjZVhUODl3MWJKR3FabU1Xa0g4Q0JtcUZfdXBjcmtXY3N1MHZNOGtQSEdMNmdQOGV6QmR2cDEtWVRQZHMxLUZ6NFY4bmNJRTU0dDhoSk5PajVQT0VRZmFOdW1xbl9zcU5Z?oc=5</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>46040.34277777778</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Brahim Diaz: How Spain-born Real Madrid forward became Morocco icon at Afcon - BBC</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 06:43:13 GMT</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE52VlQ3OEF2cEhBM19mMGNiTnlCeVBPM2hHanUyUUdrZmFoWkNrUHRPZFdhaXRRZU5GZXI1SkxXUy1HU293ZlR3cVFhV2ZCYU9oNU5fNXZnd2JpcDl4WHJ4WHdyNVdfQUk?oc=5</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46040.28001157408</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Passenger jet is escorted by warplanes and makes emergency landing in Barcelona - MSN</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 04:33:50 GMT</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNaE1wSjFiUVVabm1SZkI2c1FIUF82aVJLRjlnb1JQMFZLXy1KNDcxTnNyR1VwZ2ltd0hHVjVaQ2VUN3N4VzVaRGxnOXcwM0c3NjRlUGZSa1VCRm4xRThsSjBkRnMzMEtWQkk3UG85WWFxWjc2UE9UeTRvSThfTDlKalU4VjF5c1VUQkxlOGN2VU1mT3RrRk1TdmgtamMwUmJMaEZmMkYtTHEwTVU3REtvMmFZS0dNcWVIbDQ2QTBSRHU1d1k4N2Fn?oc=5</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>46040.19016203703</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Real Madrid Triumphs 2-0 Over Levante: Key Takeaways - filmogaz.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 16:59:33 GMT</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiRkFVX3lxTE5pa3BPUHNmUXdWSDV1UWNEVE8tdVFHYmJxRVFzcjBMNE5faEw2cEFIUXdkV1JGV25HYnkxTi1uelpNOThhOHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46039.70802083334</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>UNRWA: Aid to Gaza Remains Insufficient Despite Ceasefire - AL24 News</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 00:45:50 GMT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQS2JpeVdnY05lMVFtVFBRTVNZcldZbUxJakFKRllUMU9hS0dDNE5vV1lEdTR4WktPZ0ZBVW9EQVVQYy1rbHpZWEVmUUFrVFhKcUI2VjhIQXd0WXI5OWkzWGFQQ1dVLWJnVG9jRWowWlJfQnJEenhfeFlHVnM1ZjA5Nk5vS0ZDeUk?oc=5</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>46040.0318287037</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Why financing is a ticking time bomb for Feijóo - Diari ARA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 17:20:00 GMT</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNQVdNb1R6Y1FtdENNLUV6MGdxc3Rjd3FPQWpldWtvS1B2WG9iZjJVYkVQSmdiTzFfc08yb1kyejViSVh4V0pUcjJCZGpOdzZEbEd6cFhkYXpsbS1peFB6UlFTQ2pDUy1rSlhQZ1pxYkpRSFhDYlk3SHRfcmlPZGFHeHdqdGFGNlBvS0pPSk44R0FkWkxh0gGaAUFVX3lxTFBGVWVPVnFiY09IeXZ5ei16S2ZLRFRDc09oV0taZUxyTFVtZVRxQ3J6MVd4WU44LUFCZkVZWVd3WV9mdEZSbWg5REw3bGJ2d0ljbF8xVkozUEpXOUNJaFpWVXpBYThvTzNqU1RqdlhXNkpTdHkteDQzY29QMEJDRU1SZTJlM3RHWF9tT2RKUVVSSmVKYlBjSDNucFE?oc=5</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>46039.72222222222</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Megan Rapinoe takes aim at Donald Trump, condemns ICE shooting as protests spread nationwide - MARCA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 21:48:47 GMT</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE45bDRMVGZFXzZveHJCREtkYWw0SmZaZWRqclctR19kTlhoSjhWOTRELS1HZVVmU3VjUzBaeFpRb0FMRzlRemtraldJVDNJeVctQUNFQUhQb1pDX1JFQ3h3dzBMYkR3T0ZrczVqR3hzT1B1NWZMTkJCX19fRk5Uc0XSAX9BVV95cUxNaGY4Z0xyMlB5VDZUTGlDMkc3LW5aVG1JLUJCN3pRQklKRzZZREFkSmwxOHNMM0paYTlvQ1J0Z2dMeUZCWUp3NXdtbndOS3Z5Z2ZrQnJEakZ3YTBzVEt6dUdEdVlnUzl2TEFtbVNmV3Z0YlB6UzgzY1NmTHE0NkU4?oc=5</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>46039.90887731482</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Australian Open Ticket Chaos: Fans Fume Over Halted Sales - Devdiscourse</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 03:58:05 GMT</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNeE9uMTI5RGZycjV6ak9TemVDRGI4LXRCM0lvXzF3NUgxS2t3UHVoamxEQ0lIN2ZrY3JjSkdkZUotM2F1eVpJUXJCZnRHWlZXWDkxQXIxMElWWm02aTZXUHFORjVuMUZMX1ZvdkZmQnNDNEp6bExkX1gySmpWRHJUdUVpc0p0VkpyQ0pqV043V3hVdHFCUUxXQW1XSmlUTTVtd21nRzBYd09IYi1HTDZSTjRvMVVNQzl6MkHSAboBQVVfeXFMTXhPbjEyOURmcnI1empPU3plQ0RiOC10QjNJb18xdzVIMUtrd1B1aGpsRENJSDdma2NyY0pHZGVKLTNhdXlaSVFyQmZ0R1pWV1g5MUFyMTBJVlptNmk2V1BxTkY1bjFGTF9Wb3ZGZkJzQzRKemxMZF9YMkpqVkRyVHVFaXNKdFZKckNKaldON1d4VXRxQlFMV0FtV0ppVE01bXdtZ0cwWHdPSGItR0w2Uk40bzFVTUM5ejJB?oc=5</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>46040.16533564815</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>NBA chief wants to tap into soccer fan culture for new European competition - The Straits Times</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 22:06:27 GMT</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPYjZDMU5wRlBJRUZ5dXJYajZJTDREY29YTHZrei1RQ1VwNVk2MjlCNG9JbUpJVy1OcVVMYldBQWMzczU1NEhWWURDMnJlSExQTnR5ZzVoaXRkd1RLcHJ1R3NzQ3QyZWFOT0h6RGhGRkNqRjVYcGxWbXNwUklObncza0VTYmh3aG83OTBlVG8xSExPTmFmMFFOWjdLSVZMV2FrZHhWSDJPLVNJVjA5enRIV0JIeWlDT0w4LWdDT3lUSWRhSHJkaUZ1Tzk0cVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>46039.92114583333</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Man United DESTROY Man City in one key metric during Manchester Derby win - it's Pep Guardiola's worst defeat in this statistic - Tribuna.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 16:39:28 GMT</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOYjdyZ1ZtcWRvTHFyRTlQajVxeUl0Q1BvZHV4QjViYThXVWRnVGtzMzZVYUF0N0RSN0VCc1FQSjZfajdFektqdTZRN0IwdlVHdTU3cTZkY3NmZ1NXVTFCeGU5SkhzNG53ZmNqSUJzR0NJd05qWmRpOEE2M0kxV215ZmRUbXdEanlQMXR4NDdzQi1fWnI4YTRNYjRn0gGaAUFVX3lxTE5iN3JnVm1xZG9McXJFOVBqNXF5SXRDUG9kdXhCNWJhOFdVZGdUa3MzNlVhQXQ3RFI3RUJzUVBKNl9qN0V6S2p1NlE3QjB2VUd1NTdxNmRjc2ZnU1dVMUJ4ZTlKSHM0bndmY2pJQnNHQ0l3TmpaZGk4QTYzSTFXbXlmZFRtd0RqeVAxdHg0N3NCLV9acjhhNE1iNGc?oc=5</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46039.69407407408</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Haiti - News : Zapping... - HaitiLibre.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 15:23:19 GMT</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBKckxlQ19Ueng3MU1jNkJFQ0lJbGlmSTMzTGxhc1ZhdlBVQ3JTampwdWV1RmwxYjVhdDVlU2VoRmJsbWprNktxVnQ0VFFnejBLS2RtbWNBNDYtZHVtZzBHYms5RUZ0MVlPdVZ0Y2xfdUZWQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46039.64119212963</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Airlines race to fix Airbus planes after warning solar radiation could cause pilots to lose control - AOL.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 18:06:18 GMT</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNeEZmNzJOdW41U1V4R3VQOUxIYTk1U28yeDdQSU1rOURyMTllYzNnMU1UOFdqMWtHNlFLOGxMODBLZktSd1A3NUFMSlE2bFJWVzlBbkxOckdlQmI3b3V6UmpyQWFYN3JPZm9STnk1Q3BOWFB6VElTVWJrcTBqM0VFcEdWdEs?oc=5</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46039.754375</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>David Bernabéu lashes out at Florentino over the ‘request’ to stop the whistles at the Bernabéu: ‘madrid belongs to the members’ - madrid-barcelona.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPaXZDSWQwUWxvTTk3Uy1GengyZFBhLU10QVdLUThEakZVMlBxaV84Z0RxQlc3T2pWX29xcGhQNkYwVFFrYTBrbXJ1a01rZ2pjYkdFWEoyTnVvSWRkOWY4MERONm9zNTF5YVE1UVNxMHQ2aWY2RHNWaWxlUWF2eDJDdENtOVh6em0zYU1EX2hGdEZoanduMzRQUWs5c1ZOMmZtd19CVWxkdmtyMUNZRVFSVmJGWm5kQThSSXpEMGFFVi00YWJzbTBlZ0lXTXdfWmFNeDIwZEhyX2xScW1veV9IajV3?oc=5</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>46039.79166666666</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>First time Hansi Flick speaks clearly about Dro Fernández's imminent exit: 'There are people around him…' - madrid-barcelona.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 17:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOVW1lOUdsWDYyOXRoSnVabk94dm5Ed0oxOEdaMDhBVDJzaXpDVjVUSVlZNU9mamhSaFh2djJJUUVHSjRCQnB5Wlp4ZkNTYl9WS1hIcWpxR3BLR29nSW92RjJySjNRaTZaci15Mmp4OE1HaGp1eGd4V0hVOUFTcEN5cmZsTUdzX1JGdWlVRU40d2NYanBZc0lpb21Vdzg2ZFJ0cGVtdmRnVGdzVUtIWm5wZXk3VEhnOS1jQllXRFFuSVhYSTVYTUJWOTFmaFdTZnB3bVVhX3ZnQnVUNmk4dUJxcDdzN0ZmZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>46039.72916666666</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Who is the mysterious celebrity guest of the anniversary project - russpain.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 17:18:15 GMT</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOai1RdkFCQ1dpUmFSUXEzYWgxLVZ1QzBFT193eV9MLWFxYkcyRVNMVFdzMWo1T2IwXzRnelFIaTRlVkFWNlFQNlp0VEFVcUhoQV9BM2YxVEIzbUlzYnRULTBEOVRkSndtVFlMUy1CR18zWE1PN3BCa2s3WjhFZ1FkUzNFMmJ2b2dTMmhjbzQwZlFjY2NJTWd1amVUeUZ4cnI2Q3RBX0xuQVlzRzZHNDBEMUJRQWVib2RBVWJSLUNjUDh2S2tzMkdQVlJ2TQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46039.72100694444</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Yamal embraces his roots: his family's multicultural background fuels his on-pitch personality - Pasión Fútbol</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 15:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxONU1YdllaX0NYeEN6U0dGd2ljOHFRNHIydm95Z2pxa0hfYjVBQ0Y1V0ItcGJ6V0dxN2F5dng2cFR2bGxZa3NoWjAxNzRDcnU4TDR2YmdxYmhURmhTNG5iaUpUUjJjLXRDdmJtMURqYU5ZRDBlODBiMU8yenVtWm5jY01GWG1KTEFNVFdzMUJieU1oLTJlMkdUNUc1WFBlQVdWTGplUlh2YzZiLUFNd0JzZTFkNzNUdUFXb2xNU3F3OWMyV1JOYUhDNjYwNUdwY2M5TEIwV1Zid04zQS0wYmRZbA?oc=5</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46039.64930555555</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Jaylen Brown shows out in hometown to help Celtics rout Hawks - FASTBREAK.com.ph</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 03:32:55 GMT</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPWmNPRUpHbU5VSXVlZmlGdjdmejlNdTNfZXhOd1U3QVRzUXBZa1UzMkE5ZUl2V2xwX2l2OURqZUdMQlM2UzNoNUR1UjhINmFMVWRzX2hqS0hJSFB2OFZLVVZlVEpPV2FyVng4M0tGelMzT1NfbWtCcGY0YUE3cTI3VUx2QTJRckZNRlBhQmVsSjRiazdHazhIN05sclV3NkNDdmJN?oc=5</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>46040.1478587963</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Firebreak Filming Locations – Where Was the Netflix Movie Shot? - 4 Filming</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 15:40:27 GMT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE00c2hDekZvQ1BxVC1rNjF2RVpQYUJmdU9NNkV0N0x1eHo0Wm92emdqUlA4dW1QeTNmdnRudzViTlNjdXdsOEd0cHdjX25ad1cyQ0lLTXVvbWJldFJuUzMtRmVCN24?oc=5</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46039.65309027778</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, Spanish   language</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomba" OR "amenaza de bomba"  OR "explosión" OR "paquete sospechoso" OR "paquete desatendido" OR "explosivos" OR "explosiva" OR "tiroteo"  OR "puñalada")</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ter Stegen rechazó una cesión al West Ham - Mundo Deportivo</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 18:42:00 GMT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNdXFYdnR4WGJqcTVMeVdQWExPM0RMQmJhWHY2NGxVTVhScno5UzMtaTc5RDUwWGp5bmQ1TEZCaGZpakJqRzRLZDZrbUJaak8zVjExdDVqZzJGN0NEbEFxVEVmZGZ3WDlFdTgzODBkTUUtQ3lzSGE1dW54S1VEQ2M2RC03dEN5VlFWc1BONkVhZjNqckhLSzE4Q3lRSEFaaTdjdW42bjZ1bzFOOVpfLUJB0gG8AUFVX3lxTE15elloTU9yUm1UTzNrLW5BQl9QY0gyYzZJTTV3LWRtVHBRdUYtel9Ea1VaUEp1TTlwQW1tNnpyNjFTUk5ZSm9tRDVBTXZHYmxYTHhaRHBqbDE1bDZPUnpfNUFBdlptWlVZNlVUeXpOZFFIcFNIWThVV0VrRlZXR1ZUdThpV3NlUVZBNEt5V1BiQ2VFa1g1NkJ6ZEhoelFYWUwtT3VwQVlWNDdlZmVGOTRVRHZ2bzhUZ1NKV09o?oc=5</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46039.77916666667</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Businessman, 21, runs company spreading across London 4 months after being shot in crossfire - MyLondon</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 07:31:03 GMT</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNWHNSVTYtME1QeFh0OGhpOGk5M2FaM2FHaWRsUElCWVlRMjRBMDRkWURDLUZudF8xa1Y4bVpCRXdCWjFGVngwc2EyWnpBajI2Q2VEZHBnbTFNRFF6VnhSSHhVZXNiNnFVbUNkenFESnhWczBsM1NtUE1MbWlDQUpRSE9zQ3hVRlh0RF9uWEJWLWLSAZYBQVVfeXFMTzBZbHN2V1prR2hobUxoVkJERFFzU1hKbnZiS252UFJnNVcxYlZwa2xZcFc4RHhvLXVUOU5PeGhfWXNJSHc2RDB6Y2xIMkI2Z1drelBib0IxaFFDbEpnUktLbTk1R19VTU1DVnZ4NVJEQVpnZU5RN1dXM1VQbzFOX2dJRFFJeGdzU0RacnliSW5UQ1FERHRn?oc=5</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>46040.31322916667</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Special Branch allowed RUC officers killed in bomb blast to travel into ‘out of bounds’ area - MSN</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 18:52:02 GMT</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7AJBVV95cUxPVGZTWlNXZ3VIY21MVUFYNk9lTVZVLVMybmlYNnZqQi1GVjZxcF9fVWNxeFRLRFdENXJocHNqV2tLMFpqbmRLODR5QnR5NV9jblA3NmpJVEd2U0R0bk5kOUhGSkdYMmw0YnlCX1pJQXBRdXp5Q3lzWnJHQXluZnVSR3pPNkRkU0NWQm5oSHNNTVQ2b2hlMVFHZUloc1lKbU9kMmtvZG45YjVqQWNSa29WdUNZbWhGOFl2cEVLNnlOR0ZaUTJlMk9SQ0kxa3d0YW1EWE1lYlpvYlVId0xPSlp4b1lINTB6VnlrbUpybW01cUlMMUpyZXk5NmlSY3JHSUtCTFZzNllqU1hBM2luR3lGWGtTUjd6LWRwdGJ1SHlfZXUweG1iUW9XVTVKV3RGaU9HckZONDNHNUxaU0hNWmZxb2kxRGF0dkxDUXZTU1FPNnhJbm5iYlRkdUtsaVB5X1ltTWpnYXg0R0hISU85?oc=5</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>46039.78613425926</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Match Report | Wilson's late show earns West Ham win at Spurs - West Ham United</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 17:10:32 GMT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQQUgzaWQ1QmxRRElLR2VpdzFmRXlEbW1PS3RmQWo1YVlCN1ZCcGRGRkJSWDhObmJ2QnhjZjR0dnRmdE12N2F0N1NyVDNNb3c0dFAydXNTcl9Na2J1QnRZN0RJeXpVU0pScnlYZGxTNjh3NmFOdVZvenlrR3NSS0VTS1RVWFVUd2F2OF9uUnJpYkQ3YzhYaXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46039.71564814815</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Teen killed in horror London crash that left boy with life-changing injuries - The Mirror</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 16:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNc3ZOZkZwWi1tZlBsdXpVOTFXUjhPSEtqSDA2M3dtaDFkUTZsNTgzVnRQZmJOQkVxWENSanozRnRBc1JUZm1YLTJVUWE1M3duNmhyeGtlOFMzZEF1aXEzNTd6RzMwQV9mbWpMQjZ1anFPSEZpV09KRE9RRmF2d0hQSl9vU1N5UTg1cjhXRzF30gGOAUFVX3lxTE1zdk5mRnBaLW1mUGx1elU5MVdSOE9IS2pIMDYzd21oMWRRNmw1ODNWdFBmYk5CRXFYQ1JqejNGdEFzUlRmbVgtMlVRYTUzd242aHJ4a2U4UzNkQXVpcTM1N3pHMzBBX2ZtakxCNnVqcU9IRmlXT0pET1FGYXZ3SFBKX29TU3lRODVyOFdHMXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46039.68263888889</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Karen McDonald accused of misconduct in historic Crumbley prosecutions - Detroit Free Press</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 02:49:00 GMT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxPWnhpSHhaa1ljQ1cxREtOMUNaVDdwNlEzd2tIY3J5bkVUS25xb1Yyc1NsVzNYc3hCanlWdk1kYlJJWXNHVmduMExLbTRNNlVwaWcxbHlybWlZQmhiZkxxbERweWRfRlBOSEVJcG0zZFAyT2ZlTGlTWm42QU5md0J5TWZpZEFjaFkzSmZKc0NLMm1IcDI1M3I0cmpXMjlLTUdPQWx1QVBRRmxMWjhCeVQ4Y3ZDR2R0TnFucWZELUtxSVIzUWdjcWRDcldkZTV2YzJISUJSWndZeERFcXVoMkdWRWl0cFNsMDkzTXBWTlNXZnlXUHhLSjlLb2FyZnhOT1h6SHN3?oc=5</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>46040.11736111111</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Sarnia police investigating early morning stabbing - CTV News</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 16:07:45 GMT</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQUURPTktrN09lcERBak1QNWxIb0IzejJiV2FXVUxMZ0plUEhUVndUWUxLcUhRTGItcmU4RnVoa3EzRU5sUnpoLVlQeGtxOFlFSlRNRS1hY2pkMlZZZXZFNXJONHNKUGV0T2ppT052UnNnaFctdmlnQTMzdkoyWTZEV1FLRGVOVjNNS0o2MElCalgzZ2s?oc=5</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46039.67204861111</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Opponents protest against China's planned UK 'mega embassy' as decision deadline loons - WPLG Local 10</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 17:18:48 GMT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOY05YLUlkVUZPXzdZQ2hDTWROenVka3NwZ2hOaDhVRGpYR2hqTmZpNmc2SkFqUV9lNGJXUDR1TXNLVlhTc28zN1RGU243MkxiamFxc1A4YlBEbklhdjB5ajAtNFdpNkU2MHMwZEh4bmJDZHk1SVItbDdzRjB3WWdQYjM1c2pjYmNzQTN2QjJCWkcyYVctS1VpY2c0bmtqTkhKaGVyd2NGY0hSdzJfdC02aWxNYnBnVHNTLU4wdC0tU3FyVC1vUmNB?oc=5</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>46039.72138888889</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Bondi shooting: First, we mourn. And mourn again. Then, life must go on” - The Age</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 18:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNSWFNc2dIYkh4MnQtN0pJWjNqQTVtMEdCWEl3NXZhOXJMcUNrUHRCSWc2ZTJWMzRrOEtzUEdNd1Vfc1dUNWFMaFdOZklMZ3Nibzc2OHdSeGVMbjlnczF6bmVldTlxem80eUVSemhJc25NdzFtbVRUVFdyZnJxT2pfamJqZE9IZW93bFU4Zkk0ZXZpNjB6RGVzVGVVQ2ZZV3ZDUnBIWVNMYVRNM21Lb1BTX3NyVlkxdEV0WlVscUtBWkYzc1A1Y05TSzY5SQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>46039.77083333334</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Desert King is back as Qatar's al-Attiyah claims sixth Dakar crown| Gulf Times - Gulf Times</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQazlPV3J3WmVnU2FwMTRwWGYxRzktOTY0UXlHV25MRnF5anAxb3liekNrNGhMVlRxYjFERlJtbGhhdTdHd0RkUGZZV3BVeVpsZDBrYkk1US1DX01JMGJkbm5IUXpGdFhmWUlXaVhWc1J1Z0w5dmU0RkV6MGJzU28wUGJUeU9ybjdWLUV0djF4UXBxWVd6UjFpOEY5RDFUdTRhb2NpRWtnbkVYZzZZNV9CY1dmZ9IBuAFBVV95cUxQS3EtdVlUSUtKMjV3NVlKVEpFUEdRTWlvVG5TUHZXZjVyallyc1ljM0xqd3hNQWotMGN5M3M0ZDBYSDZYa0RyOUI0clJ3TmZ1enRQNFEwNjU4NEhRV2Z6eHZnemZ0emkzZWdSRnZWUGRsWmcxanppS1RnVkVPTXpZWG1nNXljbXhkVEJwc0xiSEt2YjE4c1NGeDBzVlJ5SkFINEh0RXY0UE8xbEExNGFwT0E4czl2UFky?oc=5</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46039.875</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>How a Tube driver travelled the world as Will Smith's double - BBC</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 06:01:23 GMT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1KeTdWWkxwRnFGalNwTDFQZlZIRk9TMEltWDVBajdMQWM2Q2RHbjQ4UnJia2NjOE84UUE3ck9kUnBHdEUxY1NWS1hZT1MyeUxnNWltMjhIS3JFTy1q0gFiQVVfeXFMT1FqdFZteGNOTHVFb0E5X3pScVp6TXJqWHQyTzBPenJOM21WbWN0T3JMWTZRQk4tUzdzVUI1aWswT0RrVFBpaV9FM3NDbTY0Um5UQ1ZkSVVTRkFpMkFvcTFxTGc?oc=5</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46040.25096064815</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Secretary-General on UN at 80: Humanity strongest when we stand as one - UN News</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 16:54:56 GMT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE1UTkFmc0thTEhwWVdIVHlmTk84ekNaRlZEUXh3UWFVSUVsZlBQWWQwT3pUQVlWZTJkc1I0cFVySzV3WkVMM2dZMjZONWxjS0ZOc2pkRExQVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46039.70481481482</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Anthony Black ‘had no clue’ Magic dunk was so special as one of his four victims reveals aftermath - talkSPORT</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 18:58:52 GMT</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOUXpLUldjeHI4VVNRMmJwWE94Nl91YXBsUHBHUzJUcXlEWHVWbUFUaDNwbEg2RHl3UmxUZW1Jekc1elU3SEU4ZXhhOWlJTTB3Q0hJUlB6UGNyVHc4RzBpNWVQNFRwUDdfUnQzQjJfNUVVUVN4cklsempfVDE2MjQ5UlJUa2wwMERtcjFuZG5FN1JuUDg5SWh3VzJDaDUzUVMwLUY3djdnMmE?oc=5</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46039.79087962963</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Grizzlies coach optimistic Ja Morant will play vs Magic in London game - FOX13 Memphis</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 14:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxPaFBpaVFZWlV2MmhqUmJnOXFoNFF3bnZUejRoWVhWTVgzb0lqcG1IejZhdERPLXVGZExqbnFOdXNiVDdEV0RVbUJDNldlUkJsRU9fU3BYUEp5VHJyaWRKalgtRlhSOC1oZ2I5aEN3NEhUeXB1MHVPbWVPdzBGSkJqV05MSG5WZ0NtZXRSYkM0TXBzeWRaWERULWVXdVVVVEhrSEhPN3VQSFNFa0t5aHlRUGI4UmcwdlFaTTJSZGZRTmtRdkF1d2FxRU94cURSQnJpU2lSbkdFajg0RDlrSEs0RlVpM1paRzdDVVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>46039.61458333334</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Arrest made in connection with Fort Worth park shooting that left two dead, authorities say - CBS News</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 22:46:40 GMT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQcjlIVUhGaklCT2JhLVZma1JZV1ZOck5BZERuMGtrRUFOM3puMWpYbV83a0drMkl0eko4cHczZUJMd2w5VHlZVE1acTNpYk84WmgwVTJ0b1NWZnlfMmJtb1lNZXh0Q3ZsVkpLTmloVW50VWZtTk1OMWRRS0N4T3dOZ2RYOXVMRXhMQmJ1U2JySzk?oc=5</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>46039.94907407407</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Video of Clashes in Israeli Bomb Shelter Is Outdated - موقع مسبار</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 20:28:23 GMT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPUTlsS2xHQ2Fpemk5VTVLR01hY2J4SGt3N09vcklaX2xmMllaUnBuZmRza0x4dFM4bnN0UDBYdzJJUVBEVUxYZDQzY2M4bndYcnRHaUVfZk5vSGZRRHdfeTVkdWJvNXlkcDFvWFVqdUVuOFluQWR0RzAzRjhrT2pzbkYzYmYtNXA2Sk5PTnpNMHdnWlNjdHlz?oc=5</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>46039.85304398148</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Suder, Miami (OH) beat Buffalo 105-102 in OT - Houston Chronicle</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 23:13:13 GMT</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOd0pZTFY5X3FBR19IZEJTT3RCWWdoM2NMZjA2ck9WdmxWZ0hUeFlNMHFMT1BjSUpLX1ZYRW5GZFpFUV9ueC1uSmJ4S1laeG9keEJkZDJsMEZqZmQyX2NFNmlBckI1YWd0R3Y0aG5sZGZQZWI3MEpPSi05TXkwODN3MnZiVnlpT25Ub19TWXQ4RUxteEVaLUY3TmZfVi13enRHeGlVVA?oc=5</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>46039.96751157408</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Visit the Vulcan on Father's Day at London Southend Airport - Southend Echo</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 18:12:14 GMT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQTmpjakVlcVl0YXBkN0p6cUh1dklWbVR2WU80M2NKUjQwNGRnZXhydUdMRmdzUHg2bzF3OExQbGluNDZPMEVBMmpscm8wRzdMaHlUeDhLRFRIS0c2UmVJWms2SEZ4bGdkQVVDVElpV3lQRC1XR2t3RDZSR29KdC1iQWEweVlQc3hLUldiSVhtOVN5eTZzVXZ6Qmg2Z1FLeS1fWThVLUxHbUUyOEtTY2Q5UkdLa2dLN1V5eDdvd2NUeUhBbEJNZWNUV3ZXSDNmQS04cWkxYXJFOUx5ZkplRHh3WjdLckhhcjBJLTlDZ0dscU5NNFJp?oc=5</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>46039.75849537037</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Shots fired at home of innocent female relative of gang boss Devon Hennessy - Sunday World</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 01:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOLWtMUV9YczF1ZHdZWTdaM1pxOGZQYWQ1SHlpZ3Y5Q3A1NDVpcTQ2bkFUQy1qbVFzaXdubmhVZmFKMmhzWkNvSEppbkZXN3gtTm51RUhHaUJ0cmVyQTlIMnNFTnYyczhaZ21FbXI3U0ZueWhXQ3h5UjVlMkxFdFlfR2htYnJfSGRUWVg2MlJyWEtJU2tXX3pRblJRVHlsTXAxR2ZMSHZDM0hELUhKalIyYUJUNGJkZ2xnLUVVbTJXSVRtakMzRVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46040.0625</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Paris Mourns The Passing Of Stewart Carroll: Funeral To Commemorate His Life - sohh.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 21:49:18 GMT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNZ3piWXJDTUhEVFNMU1ZrMmJ2aldsdGlMWXFGZUZrbWw1VEEtMlZ4Ny0zQWhkdHZWTG9wdFl0cnVTRWJSZGk0TjJqQWhjODhONEpRRGVXTkVLSGhPUDEzVFl6YzlFb3ZpcG54Z1dxNDRtVFhsQlM2WDVGLU5xYmU3aGVEUEI0RXVUbVlZaXJXUXRFWnJoUVB4MWZ6QXFLdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46039.90923611111</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Hundred Shake-Up: Rashid Khan and Nicholas Pooran Join Forces at MI London - Crictips</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 18:37:29 GMT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQb1Y2cE1DSl9KT2djSFlqMHM2VVZyVGVYMHZYWnNvMUlMYXFDUzEzS2J6ODVfVmR4Z0wwZ2tYT3hEanl3MEMxbkdpdGszOVNXWFZIengxak51MW9kZ25XSnVMVzdsaEVONnBPdzY0UlF1QXZzVEpjRnZNZWVCVm04V3BzbzREOXQwRDVJbmVQeUFKLXYzR3hYN0xJa2RoM2hYUlEybTlB?oc=5</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46039.77603009259</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>An undercover reporter joined France’s anti-Israel movement. Here’s what she found - The Times of Israel</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 17:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxONGpxNWRwT2xpRXFJclhWYUdXWnpFVjZMUjc4X2RZWjdmVUFRVC1LQmN4Rno0WlhfNTlzbHpQenMxZWtzcTA3YmZQSl9sTmQ3NGVNR1JSLTMwQUE3eEFveERkNTIwSHZvRkROUXRmb0luM0dlRE9oSlJsZXFMYUhoa2l6a3kwVS1UUkJZZ0xEVXRXYnVvVFdWQjJUaS03R0N0SXZIOFp1UG9fUnhIbEx3?oc=5</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>46039.72569444445</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Groom in Viral $59 Million Paris Wedding, Who Was Facing Possible 99 Years, Pleads Guilty, Given Probation for 7 Years - AOL.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 15:45:51 GMT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5OSEo3V2J5NWROMHBfRlFyeTJVT1I0VWRwNHZNTkNPcW5nX3FTbTFFa2F3S0liOVBQeFpRSDhuTktpMnlFUm9WSDcyZkxQTjRwWHlKa0NuMktlOXpsVXRwYWlpdWFMR3UtQ200YWFEVGNCVndMYnJ0emZ0cEY?oc=5</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46039.65684027778</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Meet FWD-LM01, the Indian drone that flies 100km, finds targets, and hits on its own - MSN</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 23:26:52 GMT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wJBVV95cUxOQ2tpUGJ6X3NVckdCOElIYzZJR2ppYTUxbEN1aG9Qcy0xbDVyNVo0OExCN1dVazdYWXpkdllaeDlqakQzV1REYUZHUkVmS0FXdjhjVlpiSTJRZlZGQ3d6aHB4RUFGcElVeHNiS0RMcy1XaXUxdVlIZUM3RHRrY0wwNGN1RTNQMDZodElnbElTREVSQ2NPVDJ0MG5vQXhFN3JRd2ZrazM1VkstQUdKMmE1dVB0Z3ZwTGxnVm1iZW1sWkpCMnRaUXVEZldDeFQ3MDBzX0g4MGdrUTFzcVktVG1qYWJXa25fbG4xSEtCSVRVUHZJaEdMeDBac0NFRGRRSGdZQjM2ejl3NFZkdlhkS01RZUpWQU9NZm8wbjJZMDY1LWUxSjFFYkVqN0lXUjJfVmJlbzBaWFpDOWFGdy0wX3hnUHBXNVhDVmd3NUdfUzhnTUZEY3RWdk9ockNTUi1Yd0ZfdUxZNjY1cTRNMW8?oc=5</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46039.97699074074</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Manu Bhaker, Swapnil Kusale and 150 other shooters set for national trials - IANS LIVE</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 07:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNczI0dnNXMFhlQ0VKbFZ5d1VLbFE5NEFjaUZTamR4SURYRV9mODl2dHlnd1NCajM2emw4dy1rZ1JSQ0FBNThYQU5xY3VEVUVEXzQtR0QtRW9pWHZVUGE2cVJZTUw1S3JkM2wwWm9nMjd1dkZhUFlKc0FDdGlwNGE5Si1PbFQ3X1phRURVRzZHT05NWWp0WW50ZjBET1BQNW5FR2l3MnFSeDdaYUJMcnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>46040.30972222222</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>TOT MOM CASEY ANTHONY CHEWS OUT VP VANCE, PARTIES W/REAL HOUSEWIVES - crimeonline.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 14:51:06 GMT</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPSkpWemJLdm9LRGtGc0FNOVlHYXd3aW81ZlFCWmtNNWRJNUhMRFlhVHU3WjVZbGxvR19kUkRodnlrN1hOb1RjbDNOUTF3dFViZ0RlMjZWVWx4RWEwYkd5SXhlWm5XNG5lbkNWWmd5NUQxdFdjTG1mdlR5RTJRaGdpOGFwWnNacmhWWDZNd2VOcWNEYjlIZEFRM2xOT2hmdHFXdk52YWM1ckFDZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46039.61881944445</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Czech Jets Could Free Up Ukraine's F-16s To Do What They Do Best: Bomb The Russians - Trench Art | David Axe</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 22:54:56 GMT</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE05cmM4dm1PNDZnOHNJTDMtYVVfem5ORU9WRnZCQ0kxYndhMVgtZ21KajhVYm96ZE53QlRwX1BrUTRQUkFNZUZhUWRNcFdQdGJDUkdtVWNDMnhMUVpwVUd3MG9fZmpvcmJuY241aQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>46039.95481481482</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>No. 2 Iowa State men's basketball drops second straight in road loss to Cincinnati - NCAA.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 21:28:26 GMT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPWFh0QWNkUklhRXZYZjBtVXhRUlpqbUhqckRuUVNmck40UE83ckVSRlY1dFZMRDlnVDE0ejllNldzMzJuRjd1V2l1ZHJpMWxrRzdEWVhiOUZWdXB2T0RpdGdnY1ZXMXBmSW91LWtZZlNSeUd6MXNfdFB1WHlfcFJoSmVWZnljaTM0THZ2NG5xM3hWdllSV3JwdEJVdGt2cjhXWVREZDQtSFlDMEZlcmR1aDFkMnpETzB1NGU2NEliR0VSLWxpXzNOcDZhX3JnVUZiVVhycdIB1AFBVV95cUxPWFh0QWNkUklhRXZYZjBtVXhRUlpqbUhqckRuUVNmck40UE83ckVSRlY1dFZMRDlnVDE0ejllNldzMzJuRjd1V2l1ZHJpMWxrRzdEWVhiOUZWdXB2T0RpdGdnY1ZXMXBmSW91LWtZZlNSeUd6MXNfdFB1WHlfcFJoSmVWZnljaTM0THZ2NG5xM3hWdllSV3JwdEJVdGt2cjhXWVREZDQtSFlDMEZlcmR1aDFkMnpETzB1NGU2NEliR0VSLWxpXzNOcDZhX3JnVUZiVVhycQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>46039.89474537037</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Your biggest legal questions about ICE and the Minneapolis shooting, answered - KTVZ</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 15:57:24 GMT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNeW5TNzRSNnpIaHhWbGxXdDluMzlEYXp3UlR2ZjRzWWNvZHROMTVBbm9uZXZ6VHh2bzNRaXZqWGZKZnRQaVBFbzdGMTY4bXJsVVA4LU92VjltSmpWeU1VS1RMODNlTW5QV1JldWhQdW1ucDBZQ25PUE14WXRHb19aTHNEQURYX2otLWUzNlIxRlVmdUliRkRaeW5Td2lKbWVuUk5GOGlnWmdJeEx0aWFHTDBOVDdaX3c3Tld6clZUNXc5M0xGako1cTN3?oc=5</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>46039.66486111111</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Jaxon Olvera's dramatic 3-pointer lifts Cajuns to revenge win over South Alabama - The Advocate</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 23:51:00 GMT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPWnE4UnIyem9jTWxLTTlZRTBwTjlqWEpjTHNqTkpENG9PWlhiV2xBY3ZqTlN5UDJUYXdIYjd0dGQxbFdBTFJ3TTBWLVJQdG9VcWFYcUpiQXJLSEpZX25RU0RlVlhIMEtVaEtycGlIWkxoSlNicVpUNFgySmI2V0V2emJWU3RlNTE4N2ctcFZYN3Fvc2drSFlRemlucWtEMjJscVRmRUZlSXl0elJXVUx4cjF3QjhRdXRNcklTeUR4YnV4V1VvUHVSTS1BMTJrSURDNzVDZ0ZTMmwzeC1halQ4VDUzN054ejlZRU02LUw1eGgtYzQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>46039.99375</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Brindisi prevails against Urania Milano, the report cards - backdoorpodcast.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 23:32:26 GMT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPdjQ2NG15RXpsLWpLTWJOcm9ydFRGeVlqZ3dneXdMY3FCWExmSlhLRHBhcmkxeDFWVjktU3dkTUVmeWIxU25xXzlBTHl5UHVpLTRLWUZlT1l3ZU55ZUMxNTNQRjh0alQzQUJlelAwWEJwSWo1NjFsQlFBRGVfUDJla3Z1Q1VFdlNkek5mbExCbHE?oc=5</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>46039.98085648148</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Pick and Preview: Iowa State at Cincinnati - 247Sports</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 17:01:15 GMT</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOY1BxQThEUDJwZmh2dmRSMzNBdGRTX2pCQ3JzUmJVWTlQT21Oam9NX21tVVFLSDVqS3NjZnVKVDVfcmY3OU5HdlVUS09wU2VUUDlvU1BaamszeHA3UjNGbE1XR3FTOGlVYndlTll0NUw3bGtIZ205eGFUTTdtV3Q4ZWFld24tVFBhVXlRRTJEZUpGLUVvNmxtaTVLamtneHc1eHNB?oc=5</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>46039.70920138889</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Milano-Cortina 2026 Winter Olympics: Venues, Medals, and Epic Opening Ceremony Stars - express-dz.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 17:03:43 GMT</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNUGgwWU1UWmUxNWxQZEZOQVlaREpiVTUza0dQcHpyc3hWWW1JT0x1dTZiMzhqaHYyTERUY25McThmOGRIc0xaYWx4VVRsWU9kSGIwOUhZZ1FPcHJIQ3lHUWlQa3VCV1pLeEE2NThyRU5iV3RhM3B3UVdyQW9iZF9DOTVHRGdoNEdWSjZNVDFjTVh3NkFlcnBPUV92NmJOOEdQZTV4ai13aXE?oc=5</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>46039.71091435185</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>A special derby at the Dall'Ara. Bologna secures crucial points for Europe. Fiorentina plays for Commisso. - Quotidiano Sportivo</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 07:16:12 GMT</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOaU1Yc0NQTXNxeFBoYlh1QkRpTEtTbTFtM0VLYmhBY1h4NGQyNER0eS1KRzdTTWRTcDRoWkwyQk50cjNTZTg2NF95Ri14SG56cFd5SFFGSFR3VG9idjFTR1cxU3JCWXgwaWpCdVc5dlVEaDRPWGk5NFdJVW81clFGSUkxRW96VmFTMjItNWltSDE?oc=5</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>46040.30291666667</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Basketball, Serie A: Milan defeats Tortona 87-78 with a super Bolmaro. - Quotidiano Sportivo</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 21:51:01 GMT</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOSGpmOS0yY1BSUUlkekFnSjE1LWJ6a2t2RzdnQjZoYkU5d09DS0tlUVgtVkt1RGpqSTlDQkZRUjF2QlB4ZkVGcGlEaXN6Q0k3ZkNJMFBGNjF6SlVqVFdlRktBUHVZQnB2WTBkcll5TVZVdUdrTWVLdURubS1UQzlMdTlfc1l0NG5FdEZzZmItS3NmMUg4SFNjYmt1QldIeXY2MnNwV2VERFl1OU5iLUNFTg?oc=5</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>46039.91042824074</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Brussels police accidentally fire shot after Africa Cup semi-final - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 02:40:52 GMT</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxONVNPbWM3eHRSUDBjOTBENmNycU1BOWVMY2ttd0hwZ3RnaWdVMHYwYW1wZjRyZ1QxSEhfZ1M4ZDEzV1JncHNCYnhjRzBBWlVXZ3RBaG53bU1kZ0NKeHVyVEpvb2M1eHZoRDl6dnJKQjhYZzVybWU5cTVwU2pZQ0ZkZXNpR3JhWEd4NFJra3RPSnhic2hsWWVBWlhRMGtrS3liMEZBMlhDcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>46040.11171296296</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>French farmers wrongly accuse Brussels of betrayal. Macron’s complicity could help the far right to victory - The Guardian</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 17:44:00 GMT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOelBoSC1uYXI0UF9CV2VLZGtpWWRrdWhtRnRLblNMS01BMmFYRDBRdkpMbFdqYTZucm5kcXA5WnNHZ0JuQTRkNkZDZUtkNEE0Z2V4WDFsekNkT0pOTGRacnZpWFRCdGVQdzIyMHVlaVl4LWZGQjZjWE5KX0YwQjA4alRJNGF5cTdSMTY4Q1gxTzB4MHlCMkE4Y0JRQmVsR3U0OFlsSUU1eG9PSENObUNkaU5EcUw1YUJVcWRfU1Z5R3o2Y3NkcnNQcFBGOWtTcFBGYlpnVl85cDF4WmljUllGVUpTTTRnY01oWXlhRzY5WGo?oc=5</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>46039.73888888889</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>EU, Mercosur bloc of South American nations sign landmark free trade agreement - The Hindu</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 02:11:00 GMT</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQbXRGVnZuWWtFM0prdEJHX2R4U2g2X0lMWFJ2ejJLeEtmV0l6RVNXY2tXQ2lOTzZpamE1N1dOc1ZRd2FpcmNiYjlnNXNsODlwYWdZOV9oMFhwWkNiV29ianFhMERwZjU4Y0ZhZV9rMnRYMEpNdFY0S2l1dmhia2JEd0tJWFRndVVDRDA4Mi1UenZKcHZrWUJCd1VOY3hMV0YtdVpHd1oxeUJza0JmU3p0X1BYNGlfNEZfMjctNzY4XzI4T01YWlpYOG54b0p2XzEtd0FyZFFWb2_SAd8BQVVfeXFMTVlwTm11amZKdE5MMndEaFk0RW1DRWNvdkMtN1A2RFNCTlFQZi16VHAwMzhvTjBuQXNFVVhXTndxMzJLaElxRHFNU0lpNkpCRnRaQ0tpS1RpQndOX29BT0ZEWThES0Uyb3k2WXZsR2dKSzJxUUtoakxwSDl2TVhJdWhGOXZTSUE0SFZyVDE0MVdfUDBKX1FXOWU5R2hybEZHVzVxZmR0ZXEtTHV2dzQ4V2NucEpuODV0T0luWWVkVDVnbF9UUlFLSTFDcGo2dW1IU2pVY0g4MkdEWkRIWXhLRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>46040.09097222222</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Police prevent illegal drift meeting at car park - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 18:05:25 GMT</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOU2c4b3huT0VucTBfSEJFSTloQndLV1dsWmc3OVFfS3RyOUdpUVNDZUZOQXdSa3huQWZPNnhqVTFHeVp2RXJ1LXRWSnUwRWFCYnlZMlRIRWNuWTdzd210YllQNm4wUTdWRUJlUm83c3ptNDFjNk5OMktucXRtWWZKY1BaS25xOUxSOUgwc1JtOA?oc=5</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>46039.75376157407</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>One of Belgium's most wanted criminals finally behind bars after 10 years on the run - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 18:06:12 GMT</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPSTVHM2U1WHRYUDdpRThEM28yQ0Q2MTdDYlp3RllpaVBJNTVERDB1aVFoOEVNR1hPNk1NVzJ0dzMzSTRjbmlZU3FnNDFWelMzdkJWU2VaZEgzcFFFclhiTm5jOFBWWkdYa0VEZmxPQ3BtaGNPcVQ2ZjhEay1SeDJHYmJfOExKd3hrblZ2QzJXQXQxZlFnaFZWMVprNEw4X1BocEtsb19SLUFBSHFoNndVUk9xcDJ1Z2xyd0FuZklQbmo5VUNsUFlERg?oc=5</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>46039.75430555556</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Liège restaurant opening goes up in smoke - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 02:37:30 GMT</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPME9IWFNyWHpzVGRnbzVLLVRjSDdRWHJQN0o1YllKVXdTTy1vblNZdUtMV0hqNVd4TlROdk5Cc0dtbDZfNlBRS085eHBmY2xmc0R2cGo5WHhFY0FFdHBocUxCTnp5X2xCSWpEU3VSS3YwdlNHSlc0UEIzWVVaQmxvRnl3Vl8tdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>46040.109375</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Dendermonde police launch probe into Oude Vest street racing disturbance - Brussels Morning</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 15:44:01 GMT</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQRDFfZW1ocUZCLXMtd1RIUWZSR1hMWHFZYlAtRVZsWlVsV2RlMkJldWxuakF5TGx0M28waXNYWVc3ZURUUjlUMnZZRUNLNVRDUzZDSlBsV1NPcGtjUnIyUThrTElESjQxNThkUGpsd1RIdkJLcTl1UUtteWttd0xOVUduc05fSWFSRWZoeE1uR0Jjai1DRms0YmVOVWVWb2ZTMlRQNmdVQ19LMVU?oc=5</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>46039.65556712963</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Racing Genk and Lommel SK issue joint condemnation of racist fan remarks - Brussels Morning</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 15:20:09 GMT</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPZlFfeFVaZzFDUzI1OXJlT294bEs3bWVWZG1ZNTN6YW9jMHJvZWJ6VTNHM0hlLWYxS3EzeTNGa1JwY3RCb2hYckRZUTliZU1wSUM1LWU1TzgtaW5vOURKSHVndE1sY3piSDMxQlFNa3JfSDh0QzcyenFGa3hHRDB5UlJfYnRhTENfeUJPZmxaQThNN1I1S1lRbklWT256OWp6VnlZYmZ1MDNQOFE?oc=5</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>46039.63899305555</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Antwerp residents queue for free tulips at Opera Square - Brussels Morning</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 16:05:02 GMT</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNWERVaUh4MXpycGNCTkRReFNQVXhKVjBJa2ZHN2FIX1RXOEYydU5tV3B3dHcwc3BaUmtYVER5Vi1oZFdJVm52d2hxVzlXNXA2dEVHNTBJSHplR2ZsYXJQeUl0UkdxdzI3N3JHY1lUMl9BYVRIUHF0YnV1czdfQkJ2NG95UEMtem5EbGljN1RmQ2EySXF3?oc=5</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>46039.67016203704</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>RFE/RL: Brussels again calls on Serbia to investigate allegations of use of sonic cannon - vijesti.me</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 16:16:26 GMT</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPaTRlMnVTZHZ6amVRYWdNVlkxZXVRWFVlYWJhNDh6X2h6dDI3blV5bWtRNE54T2wxOG5UOHE5UV9DbFJqbUxRSGVaZmdCRzRWWllhYVBVd0Q4MkU1Ri1Pa245SDFBSlVZZjdnbXRnTTAtV2VLVXo4ZzdtOXFCZzJXWlp5Z0hYdTlOR2s1SFpZLXhxYlNZWV9kVTh5bjByRlJmcHplV0JQOFJPLXdlWkxsVWNjaHZBekJn0gG4AUFVX3lxTE9pNGUydVNkdnpqZVFhZ01WWTFldVFYVWVhYmE0OHpfaHp0MjduVXlta1E0TnhPbDE4blQ4cTlRX0NsUmptTFFIZVpmZ0JHNFZaWWFhUFV3RDgyRTVGLU9rbjlIMUFKVVlmN2dtdGdNMC1XZUtVejhnN205cUJnMldaWnlnSFh1OU5HazVIWlkteHFiU1lZX2RVOHluMHJGUmZwemVXQlA4Uk8td2VaTGxVY2NodkF6Qmc?oc=5</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>46039.67807870371</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Belgium hikes 2026 salary thresholds for Work Permit B and EU Blue Card - VisaHQ</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 23:10:13 GMT</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPSXVOUUZ5VTJPMHNIZFNpOURDaFlJLVdpdFBweV9EbVAxdUc5MWxoRld2Tk1hR2NGN1NoVkppZ0NxMGJtRDBkMkdDdVdkTnJjVzg1UTUzck9QR2U1OGk4VDQ0NUhHU0xXMGNaRFRwTWx6UE5IazRsNGVvb1pFYTktOGFfYmJMakdaOVRDOGdJZ3hxajU4d0Z1VEJwOWRNTG9saXk3bjBnNHpGQnFuajI4RFVrNGE?oc=5</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>46039.96542824074</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Trump tariff threat over Greenland 'unacceptable', European leaders say - BBC</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 06:45:08 GMT</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1Ca3RnUmFrSjRMNDZVUzFXMGJPZjNzcThUS3JLZVoxbGp6eDVZSGFnQWJyZUlwTmpGdzdmRVRfQzNiUU83amQtOXVOY1B5aUs2Y3JQS0p1Vm5hQdIBX0FVX3lxTE1Kc0RVUER5cFBuU3dWM3JVTldtTzRuQjFuMGZaenJMbGpOTFoxdjJVdFdHaWVuOVlQUlVnU1NqUXdXWC1WeFphNTVmQzJ5M1drczZYeXdZbUJQYkQxT0hz?oc=5</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>46040.28134259259</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Emergency calls now require language choice in two provinces - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 20:11:52 GMT</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOTHA0ZGZVTWMzVzYyLUZlSjRlUEZ1S1dCbDFORTg2d1ZFR2FVdXdpMTZoT3A0Q0p2WktFd05kRzZwakFvY0FWaVdwS3E3TlItY1lSTHlpNVBCS0hFVEJJc052THZkU3RCazVBU05wUmpZWWtfbXpYOXY2U2tvYUhxS0c5WlVsQUpyc0J1VFh4TGFrbFJCY2lpeEQ2QWZhT0U?oc=5</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>46039.84157407407</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Local Town Searches Wertheim German Terms</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>("Wertheim" OR "Wurzburg" OR "Aschaffenburg") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR boycott)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Bondi beach terror attack - The Guardian</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 07:49:55 GMT</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxONlVLV2lSbGRXVHRsZk5NSHdwOFhZV0RSNktPd1FzWnhvbUtNYUtodXZ3VVNMeEZySWhEcXgzQzZ3Ty1WWHhQejRwZG9UTXpRSWp5QVc5Tl9Qc0VjekptUmI4MjJQVmlZcGpxX1lRamFlQXlWTVpTUDhXd25HYlVDS25UelE2eWM?oc=5</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>46040.32633101852</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
           <t>Ireland / Kildare Protest Groups - Social Media</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Four arrested in murder investigation in Co Derry - kildare-nationalist.ie</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Sat, 17 Jan 2026 10:31:40 GMT</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOSF9RYW1BSFNRanZhZy0wVmpJMEIxUVFiMGpQWDgyeHRNX3dqMng2MmEwdUxsOGpTOTd6X0dvM0xHNEpNOHJQanREQWFEOFI0N1FxNEdmaUdFWEtuOWN5RUszeTJaYWRkUXB5U1htQjA4SnNMaHc0QWdrTUpka0VKRGREdG1FSll1R1B1b1NTQllLbGItWmhOQy1Wb2ZkdENxS2Fyc3hyTWk?oc=5</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>46039.43865740741</v>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Asylum-seeker tent protest outside Dublin department demands residency amnesty - VisaHQ</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 21:27:41 GMT</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQSjctQkVvVWJCZVpUN1I3UUFNeFJhUThIaGZVVEJ2Vk5QVThGYlc4VlhtVTVFYlRld2RzWGVmM3JUNTd6THYyX0VNcnp5ZExpaDZOa19BcWtxZ3RJVGxnYlBHNnFWMVA2VmpsbjV3dHk3N2kwTEFJdG96OVZUdFRDY1pFX3BUdXRCOTVMZEVSUkgya2FVanUxWW9qNlYwdkx5UGdDMFFnaDlBakVsbi1QdThtMkRRWnJVS0V1X01R?oc=5</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>46039.89422453703</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Where's the nearest one to you? - Ireland Live</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 20:39:44 GMT</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPbVlhU1paMFpqRlpRNVE2bzZacGNEU2pCdmk0UzcwMFFXbGpaS1BpVzVxR1lDQ1d1UGFWOFUxUzJDdVVKaE9xLTFWVmdZMHhPSFNnaUpIV0Q3Tk1qY1QxWUM1LXNnT21hNThoX05GMHFyTFFDTmRsZVJGNzRQT2s5M3VWcVpDb25vWGN0MFk0R2VVWkNqUTRuR2RFemo4bE1ycERlRENkODdGdVdIbDJiZGg2aS11SlpiRGJiTkI2M2VGdGRIVDRuTGtHVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>46039.86092592592</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Protest outside X offices in Dublin over AI deepfakes - kildare-nationalist.ie</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 19:31:47 GMT</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNeFhubjdYek9sVDZFeDYzVFhuM24tY1BkUHMxV0JIMnJhN25nODFEeHgxVjhxZTgtWTBSM3BfWkQ2V3hqbTZDVU56T2stdndVQXgxeFhxcTc0dTNGMVlDYVd3bEtHeVEyNlkyZ0pyY2ZRUzlJTFdWNzAtRHBPczdzdXJFWk1JRlMzVEcyeHNRUG1DRktMbTY4NXJkSF9VeXZvMVVIbTh6cmdIOE9JOWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>46039.81373842592</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Edinburgh M9 drivers stuck in 'standstill' traffic as emergency services close road - Edinburgh Live</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 19:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQSl9fcWw4di0xdU1FM211aVVJb2hFTDdyUWhhNG1SdW1XSmh0VEdWMGJXVjhlT19WcmVPM3dmR04zYmcyb3JlOG4tOEpXNXg4M044T2pzOUVncjR3cThqdDNjSFdUdWdlekVkOGswclc3anpuaFZTZGxEN0NTZ2NsZkdUTU9KdkxieUlBaUJlNDBrYmgxUkx0Mjlza0pGSzTSAaQBQVVfeXFMUE9vRjNCZjRUYnlMRmNXV0NNM0pJSkhGZUU3c1hCSmc1cHVidmtBQ0FialF6VEprbFRfUmI5VC1Wbmk3dHR1RG0tYVkxdG1YQlNXMHhvWEtYckRURkxIMjVTbXd6ZG9DZHZxZHk3dnBqMm53YlRBSzRHMUNQemVoNEJ1WVlIOGtRUy1sZ2pHclJWQk1fdjI4VFBMRVhOX1psT19EZjc?oc=5</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>46039.83263888889</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Horror moment car bursts into flames near Edinburgh Airport - Daily Record</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 18:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQVlU4dEl5VERkYlFrazl5ZG5mem04RXJJOVFKV3l6N1ZlTFE3bXpQTXRwc3hEWEpiZUlsNnFaSjY5TWE5cE1sTU5xR1dwRXdVQVFnWUo4VXhaTUxmUlZYUjJFako5YUhIdWtRckdwME0tNGhJbmVXUGhFNHk4OURrc3pJVEJHUExqYXBuZ2lNWUZucENkQU5icdIBmAFBVV95cUxQVlU4dEl5VERkYlFrazl5ZG5mem04RXJJOVFKV3l6N1ZlTFE3bXpQTXRwc3hEWEpiZUlsNnFaSjY5TWE5cE1sTU5xR1dwRXdVQVFnWUo4VXhaTUxmUlZYUjJFako5YUhIdWtRckdwME0tNGhJbmVXUGhFNHk4OURrc3pJVEJHUExqYXBuZ2lNWUZucENkQU5icQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>46039.76041666666</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Weekly Equities Outlook: Netflix, Intel, Burberry - FOREX.com</t>
+          <t>Former model Ashton Kutcher says he was fired by Gucci for being 'too fat' - Daily Mail</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 09:52:36 GMT</t>
+          <t>Mon, 19 Jan 2026 00:14:00 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOS3BPZTJfN3MwLVRVX0tHNWM1VWJBU0g2bmFTeUNEM3dpOTZhaHZqdnpmVEFLN3BNQ242TzhyOWZJRWIwVkVwVVBNdnViR2trZmc4RXJldjlyR0ZkYjM1Z01rSnJ5LUp6WkJlcm5Qdks3Y0NwOVdkMWVCY2VqVmtvOHVqWV9XUElmUEZNQmlNTGhoOXBDTm1zZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNT0R3NXkyc2hNQkdNZWhGX0k1LWNpOXJodmZYYVhCdjE5dWlFZ0ZtaGxvcld5MThhSXU0bzhudV9PWVdoWXI4c01lZHJwNnF1WG9kZVJWcVpGUDRXRm1tbEYzRXRxVG5fZU16R05BZlRjaFBiU3o2eEg3X3M2M3Y4TXNaNHBxdHRubHBDU1IyVGJRMDJxaVlpQWpsaDhoeUNjeG41SGZn0gGrAUFVX3lxTE9QeVhmRTN1VnlHQzFEamJuV2ctcE5pU2VsNWFvQmhkZ1JQZVhYeDc3OEc1c2R0bktvNl9IMlAtTGlHWU92ZExlN0c0TklOYWU5YVBHR1lTaDJNcFFGUGpMTWVkTW9HQlNtc0FkNUtvM05CcnBMeVdXU3VWanhHT1c5MDFHQncwb0lWaE9rU3hjenJkbG0wNGZHdm91UkRnc3l5VHJDNzVtWm1jMA?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46040.41152777777</v>
+        <v>46041.00972222222</v>
       </c>
     </row>
     <row r="3">
@@ -515,24 +515,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>What It’s Like Onboard Giorgio Armani’s Stunning 236-Foot Superyacht - Robb Report</t>
+          <t>Louis Vuitton renews partnership with Unicef - Professional Jeweller</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 14:00:00 GMT</t>
+          <t>Mon, 19 Jan 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQS3YzZWhUazIxQ3BDaS1pYlVKcU1BdTJTRVR5aWxHOF8tM1lzX1pydXZuTFlmWmF3QV9qWjZLRnNYQnRwMExxOEdxWjRWdVFySnB2Rl9ERGI2MV84ekdHR3dIRGNDU1R2ZmlORi1LNVVibHdNd1d3UFpFVXdJeVdOX0ZtRjJXMENtcEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFA1MHUtUDE0REhzOTdJYThWXzhjS25IY0dGT2M0OHlkRDBtS21KeVBBcC1NNVVWb1A1RUNZMzBEM2VWbm4wb1RIa2pGOGdMY01XMWZPMkNVVDhyVkFKTVA5S0hDMHBJSkpXWjVjcWV1a1FTaUdsUmVFQ2d5SHU?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46040.58333333334</v>
+        <v>46041.33333333334</v>
       </c>
     </row>
     <row r="4">
@@ -548,24 +548,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bookworm chic is hot right now – even if you don’t actually read - The Globe and Mail</t>
+          <t>Prada show rejects political elite, as Dolce &amp; Gabbana criticised for ‘50 shades of white’ - The Guardian</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 11:00:00 GMT</t>
+          <t>Mon, 19 Jan 2026 02:30:00 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQQms0NXB4azliRlIxaUpodkRoOHc1dTA2S0NsOUw5eFlRTkxENWRCUzgyRkIwR1JFY1llaU40Ul9mOGMyUk94VUZZVXc5YkItX01iM2NNdHpYbUJKLTBra3c3c0I2djJJZUNKemwtbDl2ZUJscDRUbHVMUGVyWkNwMnBiRzFpZXNHMlM2QW9FbzU0b2ZGRVRKNTRKWGFpSm9BNldESi1odTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNTVUxZFVpdzN1QXkzcnYzMmJHZGhxMjRrUVVsQzRTZjRNWkJOVXVLYkowQl9FR0F3OVlUWHV5RlBjckg1RXFPR0Y5djJtNXpzVlZoWWlpUWh3OHVLTHRIR25pc0N0QWQ0VjN2MUUweWUzaXAxZXZaMGVkMmMwVDhuZ3phcElpS3lVbUs3QV9waGs5alNnbWtweHh6Z1NNRTVpaGtkRkhrRXU0dWxOd0dlekd2TFIzcFg4U002TWZwbw?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46040.45833333334</v>
+        <v>46041.10416666666</v>
       </c>
     </row>
     <row r="5">
@@ -581,1212 +581,3390 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ralph Lauren Corporation (NYSE:RL) Sees Significant Growth in Short Interest - MarketBeat</t>
+          <t>EXCLUSIVE: Dior Names Drew Starkey Brand Ambassador - WWD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 12:03:19 GMT</t>
+          <t>Mon, 19 Jan 2026 06:00:27 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOWFhbHNnRlFGT2JHc2lPOGlpNzFMQ19IYzc0b293SmpSN3FMTzE2MlgxZnItZl9WczQtd2lHLVR5Vkg4a2N0aTVWMmUxTk1PSFg5eXF3a1FRN0tqWjlvX1dSZzBHeGZybm03ME43V0dRV2JOdDNDcmUtWDJkS09KYkFmdmRzWVY1YlZmSlJ0SUJIMFNNR3lwSC1nWHI0aFNUNjRxWjFRVTg2Mi1PemJxWTFfcDFvSllybGw2dnVwSFVLWElwUHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNOHd2T2RoSXZHVmRtZHhrd1VqY0tTQU90NXB3eWtTMFB2UGxaLTNuTmNWYlgxanh2SkVkV0RkeGY0a3p6dzNlMUNoZloyalZaVVQtTm0xWTdOVTA5OHFjWXluMVhHdVNjdkpTWkd3WTZiLTl0UG9kNGtDOU4yVV9GQlFjOFEzemFMazFMd1R4S3FkRU5VQ3RKMG02MnI2aXp4SzVwcHVoRWZ0bThK?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46040.50230324074</v>
+        <v>46041.2503125</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How DHL is Cutting Emissions for Waitrose's Value Chain - Procurement Magazine</t>
+          <t>Dolce &amp; Gabbana: Menswear AW26 - 10 Magazine</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 09:07:41 GMT</t>
+          <t>Sun, 18 Jan 2026 15:03:42 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQQ0VHRGxLNWZUb3h4UVhLOHJYdFhaRGYtampsTVZQbjBqMk9oMmVfNE1tMEEyYW9fbHh4eEFLQmRkSXlvTThDalVYbVBFX3AyVXZ5cFdPOHVYVjhjRlJTcG1jUEt1Zjd0TnJSM3UzNENTWkFDZGwwcHVLcERMc1B3Tw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFB5Um56S2pkaUhQeS1GMDZDZUllM29sd1pGQ1ZNekFBRTJ2MFZ0dEd3bTZYc2UxdWxOMnI1VVNTNnN2NVRFV1k5NW1DNlpuaHdWRUw1UzBILUh3Mm4wYVVvUA?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46040.38033564815</v>
+        <v>46040.62756944444</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Peter Moore: An unauthorized tour of the “new” Amazon warehouse in Loveland - The Colorado Sun</t>
+          <t>Milan menswear fashion week heads to the slopes - fashionunited.uk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 10:28:00 GMT</t>
+          <t>Mon, 19 Jan 2026 08:03:47 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOQ29WMFh5YnRkMXF2ODVyemtsT2RwYVBZR2FZNFBvRElleUdVWFVwUXhrd1RQbFFxcWZVRFFTcDhqTm5FRjNka3dTV18yTjNpaURaUDRrYklvRVltclFmZUZxSGlvRGpWc3pBZmMyT3N2cEVVLUZvNk1BWldxM0h6VmtGTUVJSWxG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPd1RKU2w2dTRsclpGQ25URDgwOVQwZGlRU2N3RnBGUDJnclRjWGYxY3JNblNzT0ZCSlBZNklKR2NFcnljOXFzRVNrNFFXcTA5WExFQml0S1NHUnRMd2FrUlZMNWVsUXNmNWNLVWlwV3ZVS2Q5cDF3SnV3RGJMb0JHamtVWjJkYnZCYU0zQTNzQ0EyRng5RUViUG1ielJGTERK?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46040.43611111111</v>
+        <v>46041.33596064815</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amazon Has a ‘Super Bright’ Cordless LED Work Light on Sale for Only $16 - Autoblog</t>
+          <t>Hudson Williams Joins Tom Blyth &amp; More at Giorgio Armani Dinner During Milan Fashion Week - Just Jared</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 12:45:00 GMT</t>
+          <t>Mon, 19 Jan 2026 02:45:40 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9KeU5jUXZ4eUNJOE9ZTXNwX0F4cnM0bE41Rklqc3pwdFNfdEtvVnhLU1NDdmVxZ2FQTjNBc2o5SjR5WGZGMWJKQlBZTGI3R0U0Z1JJYzMxS2pUQllOUDUzZjRZSjBGSXRCOVBOV1NBbm5tRm85MWtpVGI3Ulg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxONGFISWY2TTB3M3UwMUVvLVc2NHVLVDJWM0txcW56ZFZXZ2dzeTQwaXF6V205LVdxSEZZWVVmWnY5RV9xNWdlTDdPT180aTlUdUVSVzRObGxkaGVZMjZlZWt4S1JXLURMZnJFaDMzcDVqVDdOenNkWVBTYjV6OFZtX1V3aGRzSWM2dmhDY09TZndPcHo5SDNaMVNZbV8zTzRzZWVWYm5OVGlXMzFYZ18zbDJ6MlRWRkp2UUwwQTVOTWtlczg?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46040.53125</v>
+        <v>46041.1150462963</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>North Korean agents are trying to infiltrate Amazon, chief security officer says - AOL.com</t>
+          <t>Shoplifter who stole Gucci fragrances and coats ordered to pay £2,000 compensation - Yahoo News UK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 09:24:35 GMT</t>
+          <t>Mon, 19 Jan 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPemdDUXVHcHFHVEFoeVhBUjFXUmdfazRyUloyRzFPOURqMDc0QXRDWmtoWFdVNFg0TDAta2RMN0RPQ0NCY196VkM3Q1FhSk1GVW1TQXJYRVEyNFRSd0Q4TDlrdmdkNzAzZEhRdzVESjRxSVN4RkdBZlRnTS03VklmN1ZTeDRKYnZo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPeERHaG5YRS1nc0tHZ1UzTlAyZnF4dWN5VTgtWXloeFZ5a3FPYTVNM2pYOElja3BBSXg5YkN5dmtGaFBQcm91d1liQktZZUxxRmRENl92QWZydGRDSnFDQmk4TngwSEVic3kwMDB1d2hrZTRON3R1OFEtc0JkS3d4MXNDZlVjVjA?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46040.39207175926</v>
+        <v>46041.20833333334</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Crypto Watchlist: Trading Tips for Monday - TMAStreet.com</t>
+          <t>Ralph Lauren FW26: Worth the 24-Year Wait? - mens-folio.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 09:23:50 GMT</t>
+          <t>Mon, 19 Jan 2026 04:23:43 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1UOWlnUWN4NXJXN0dRaHdFNmRUVnlmOUpjZlVmSDYtRjlOV2xpYnJQSTZCMHFrSU9hd2JubkdmRGE5U1ZPVFVLekZKZVFsZ1VFYi1PTHR3SWxnWHlIRTNyUUpVaEhMb1B0ZnVQWW9zUW0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9fU2lBVXlXNG1sbW9oV1NZakFwTlVwR0o2aDJvNm1udlhoR1VMN3ZYSm51Y2VkWGY0T01aemlZUTVsdDA2UFhEQlcyRzg4eGVKRGxiV01WWVoycDZNa252QVVVc0hUaFVoQVQ0b3FyeEZuX0tfRElDQllLNVNZQ0E?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46040.39155092592</v>
+        <v>46041.18313657407</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Smiths Group: 52-Week High! Buyback Watch Next Week - TMAStreet.com</t>
+          <t>What Valentino Rossi said after doing one lap of ‘very dangerous’ Isle of Man TT circuit - hitc.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 10:38:13 GMT</t>
+          <t>Sun, 18 Jan 2026 19:00:00 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFB6THRrcWVhcWNWUXRyb1VNdThaWEt6QUphZUZvU1l1S0ZnYTlySm5oS2NpQUdMajNrYkE4WUxMVXBaQTByX2JGRUcxOFp5RU5GMjZwMTV2NDU4eTRsbnpsQTg3QjNZd2c2YW9VZWR5M1RiekpBZnlYWm5OQ2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOckl3aGoweVBWNm5OUHM4ZldfeWEtRHB3SFQ0cnRCSTFpaVVNYnduTUM5MU9vUXd1NUVxd1FYVlVpWHhpQnc1TTJVbFVudDFoZDBGQWpkcFBLQWVIVkxET0QteXc0Vm1uNDlmN3ZnSUtNbW9aZmVudEZ1NjV1ZHZlOVUyQzF4dy10NjR3M2V5ekRaQkdEY29lVmppeFBIdzFGRzZMcHBJV2ZyWElu?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46040.44320601852</v>
+        <v>46040.79166666666</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NCR Nigeria: 76% Rally Forecast in 2026? - TMAStreet.com</t>
+          <t>Jennifer Connelly embraces a quiet intimacy for the Louis Vuitton Spring-Summer 2026 Women's collection - senatus.net</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 10:14:08 GMT</t>
+          <t>Mon, 19 Jan 2026 02:18:08 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9yTjlaTl9NQ2Y5SHA3UGJCZ0tMRFJINUVHVmRrWW45SUYwS0QyOUFYaUVXRDlFeHY1MWNNN1NQWEpUYmI0UFB4bE05Y3dWdC1mR2diM3lOeTZGUVoxV19ZQVRNaTY4MU1iVjJ0bw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOc3AwelRidkdjQXBseWJndWg4cEhkLVo1Y2J5NEo1dk9WcVJ5TkdRdTRiTUw2VHlFMkJ1cTlPd1dZQmpQX0tMZDlSbGY1cGdKSXpOaHFZczBHd2hRQ1pGRmk0dkhiWk1IV0RYUWwzOVpYUHhsaHhoUHlERG1iY0ZicDRuZ1V1WVptSEs4WmowWXhIOUFsX1ZwZlo1WUJHWTdsZHVTRzRxWFhQclBLUWpRWlB3NUxsa3lsd2p6S3Z3?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46040.42648148148</v>
+        <v>46041.09592592593</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Coreum (COREUM) in 2026: An In-Depth Look at its Enterprise Blockchain Potential - TMAStreet.com</t>
+          <t>Is Louis Vuitton Getting into Surfing? - SURFER Magazine</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 09:19:48 GMT</t>
+          <t>Mon, 19 Jan 2026 01:15:00 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNMjVXX09XUG0xcmVTRTM5ZGlRT1FpVzh6Z0RYZWtsM0FTNFlSUG1Nb25GMERFODc2bzUxWDdzeXltUm82Sm94TmFHVmEyRHpwSENTSFJ0SkJ5SnoxcHBnbkhUNXItTXY3Wjh1M2w2aEswSkRiY2cwdEdpaHhjS1hSajc1NTctcktWc2pmV1pDc1h0OFpCR0xHS0xYSXpxWFZQWHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcEhlUGk1SnVGWW4wN3pJVzN4eVlRaE9wMmZFdWN3ZFpyZUt4ZFpPTU1WanRtV3FiZzZhc0RlTkVjazlwQ2lUaS03TXF4LTY5S0l1ZXNFYWhQNzBJbzV2a09jMk5Ub2hNYWYtVFRJb3BrLUY2dThMckJiUzlIZ2JrWA?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46040.38875</v>
+        <v>46041.05208333334</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'We want everyone who lives in Dudley, visits the area, or works here to feel safe' - West Midlands Police team updates on its latest crime crackdown in Dudley - Express &amp; Star</t>
+          <t>Demna's Gucci is the centre of attention - Harper's Bazaar Australia</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 12:25:52 GMT</t>
+          <t>Mon, 19 Jan 2026 01:59:10 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxPTGwyYmZTNVdyZnhsS2NtZHBFWDE5d2lIaWlEckFqVEhwQm9oMXBjUXJ5NmFocUo2WDhETkdrd2dSNW5paDk0N1FkQVViWnBsZEM1LVUxd29Bb0V3WGJrTXhUZlZkT2pJQW84SWhyXzFFSVQ2NGdBdFI4RV91ejctYnZrQkdUS3NkWkxQTDRaQjdsbGFVSTJxd3l0YlM5RmNCTVNONmVLUnhtWk9Ob0dUZm9za2FNT1doTzk4ZXFTcDdlcnRmM1RkSTY3ckU3cVp0ckl6Y0lxaFNIdVZURkFqb1dpY3U0Uk5BaXFVQkdvbWYzdHZBb3JreDVXamJCQk0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5TemRqVlptVG90YnpYR3ZCSG5seHp5eGN5eHdIeTBOdndQV0M3WDk1VnAxU0Npc1VhNERSQy1HMm5YM2hGOVdnM0VPRllZV0M1bzl3cWhSWUI2eFNvSFo2MzJzc0dCWjcyRm53d0tlM015UQ?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46040.51796296296</v>
+        <v>46041.08275462963</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2 Iranians arrested after stealing Sh15,000 from Thika shopkeeper - Capitalfm.co.ke</t>
+          <t>Paris Fashion Week Men’s Fall/Winter 2026 and Couture Cheat Sheet - Vogue</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 10:09:32 GMT</t>
+          <t>Mon, 19 Jan 2026 05:30:00 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNbWZucDNkby1VTnFfOFFzZzBaQzRWVlBOY1dZRnBHOFd2dnNwMWtNRS10b2NlUUY5VEQ3ZGJwT2FDSlFZbFQ4NElBdjJ1VHJNOTczUVJYQnFoeFh6NXAtdUFuc3BzWEItOHNaN1NqaWxnWU1MdHVFNHFlUkJsOHVoVVZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOREdjZERwZDVIbkl4a2tHUWI2Vnk0dXVHR2UydmFIZW9UYXRFaC1yVXBxVk5EWkM1dks1dHNxV3ZWZ2QzeUJVRG8tMWVtN2l0S2xZYzhxN0NzaTRaNXZzSXpXbjV0eTNtdlpDU2c4MGU5WWtUSkJtRFlkQWM0cWM4WFV2ZmN1c3MxR1daaEkxbzlTU2FQbmEydDdR?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46040.42328703704</v>
+        <v>46041.22916666666</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Armed Robbers Hit NYC Pokémon Card Shop During Packed Event, Steal Over $100,000 in Merchandise - news.meaww.com</t>
+          <t>Valentino Rossi link-up with Pedro Acosta still on the table, says manager - Crash.net</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 12:39:16 GMT</t>
+          <t>Sun, 18 Jan 2026 15:52:25 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPYUlCbnNaa050YnJ2MDh3MHhvM0pJbkhkR1hyTW1aYTBiNUN2TGpUcm91NmgyODlRTHpzX05BbkNRZzFWRnZMOTZGbU91WXI2UFVLNnNydlpSQkUxd2NFb2lSeDlLeFY3YlNxNFUzaW4wSk9wMjN1cGEwTzNXOWRVWEF6Q09Ed3JjUm80N0lTM3B0dlJZMHluczRqdjlLeHdwVmdsMEhNalZja0ZUX1JNUkd3cUdDTkVwR0NBVnN0TQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNck5tZW5sWXhIWWttUFUtV2hHWnMyQjM3Q2t1NVNtdTRwWV93dFF1aVJEMzVYMk1iS0hNTW9rY0t1Sjh2LTEwUTdtdHM2YmNWUlpKMkM2X1M3TWlYWlJ1dzA2cVpFUjZlS3I2dFVlZzVlTjA2NWU0d1YteWtTQXB6R1I3cFd6QWJHYnhjWFlDeHdaN1QwTlJpQ19HZkpWSG9EVG52cg?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46040.52726851852</v>
+        <v>46040.66140046297</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Marcus Rashford told harsh reality of life at Barcelona – 'Probably not a place for him' - MSN</t>
+          <t>EA7 Emporio Armani Kicks Off Milano Cortina 2026 Olympic Celebrations With Immersive Initiatives in the City - WWD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 10:14:03 GMT</t>
+          <t>Sun, 18 Jan 2026 17:52:02 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQbmV6Z09XZFRIUWVoNEpmSmdtVjNUaXFNcEVtSlAzTWlVLXhDVlZiM1dvd0dzN2FfSTlSZGx2dy1oTzVDQXJGam45OHpCQ1NqZVl1cWpBQUg4dGJDd3E3N3hfT0lsdmdSNGpjSG1RWnJLMm44aERVeHBQVVU2QW5ZZi05NDdoa0c5RHVIMHdGY25jV2o2RFhwMU85UF8xajhOMkZIX3VwbmRlQ0YtaXNaQmplbWxRaGxNd1JjQjhaYVJmSnllbmRvdzllS1R0QWZsb2Rncm9MVEhRUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPd2FaZXpodHhvNjN6bnVkOHJRZEhnMUdBbnM2QktGSnlLSzg0bGVHQUpMTUE0b21IaFNKai1oUHpKS1htR3VtQ2tZVW5ySzhhdHMxZjk3TlNWM09HRGg1ZE5FZ3BYSmtlaGYtMnhIQk1yQ3hMUldZdnByY2xtY3hDSFJWUS12SVFtLW9iOGphTFlNdlJmQnNMbWRUZUZYZkk5ZmJLTjhSdHJHcktRWlNvcF9jV2cxZw?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46040.42642361111</v>
+        <v>46040.74446759259</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>The Spurs survive Anthony Edwards’ 55-point masterpiece - Mundo Deportivo</t>
+          <t>Spring 2026's First Viral Shoe Is Already Here - Who What Wear</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 12:05:00 GMT</t>
+          <t>Mon, 19 Jan 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNUlRYRy1QNDgtZHJJSVJGb3ZZSlNuWlJBdm9lcmJXblpXSlRqdWRKdGt4Q3U1Zl9jemsyZnFLQlU1bGtjWkloS3J0SDVKYlk0SDRIU0cyUXo4VzZVSmw5amdsNFZRcnFfTFJOTURIYjlyX2lxY0NzdU9KcmFSODZKT0ZZRzZkcUdVc1FTVmxmMTJkMTI3by0xR1VxRDZfQ3V5N0VDOVFVaTB5WEJNOFBXVHdB0gG_AUFVX3lxTE1zdGZLdXFYWXVBV2JheHZTblZNYTc4bVlfenh4VVdGUFdrYXd4c2p3MFVvMExCN2F1dHNHMm8tRlNvSkhrWW5XQ3l6MHFRbjJFZ1ZCNGFBMUNaZ0cyeHN6bW9nODJPemU2ZEZtWUd4TnNMX1JELXJTZ281czFqVnlMamdYQ3ZzYnQtd1BnMzAzOGdLcERuMjJkVGJXdmd6OXJjcE5RZlp6UXoxMzFpdS0tNk1YcXJWRzdXUFJNLTI4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQZEN0bzJqd0xfMV96OWdVZ3luUktsNzFNaUUyNVk1M2Y2ZWlGYUNUem93dDl3SGMxWjY1U1UwaEp4TldiSGRlUHFVcUtJTkJTbDFXMkVhcE83ajdzci1UdUF3NGVQQ2xjUVR2VTJ0OFNQWVNZTkRuaHlfdVVxbkJvc3pNVGg?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46040.50347222222</v>
+        <v>46041.33333333334</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Barcelona defeats Burgos on the road in Liga Endesa as Kevin Punter goes scoreless - basketballsphere.com</t>
+          <t>Dior Book Tote Gets Literary With Iconic Book Covers - MEGA Magazine</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 12:56:32 GMT</t>
+          <t>Sun, 18 Jan 2026 23:56:17 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPREJBYXFURk43LXVMXzd4RXNXVThqbjhCQlhuVjFqZlBzZ01LbVF1dUpyWktkYVJvY1BJanlBX0R0RkVoSHdXcHgyUy0wMmJSc3NKRlVWVklzdlIwUVk0TUUyd2FMYXlkV3NLZHYtd05NcU40NHhZbHJOeHJFOFJBSHRHaGd0bV9yaFV2dkpPSmpSS0ZoSndHcE03dURYd29mb0RZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE92aWtUSmJZdGRrOGItWHVLZjc5ZUpkdDdkSTZFUGRsWDNuamVibFVzaFJzbUpsWkxsN2pZNXUxVVlNVHhscWE4V1dqd0tRbXNrakV5NWUtcWE?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46040.53925925926</v>
+        <v>46040.99741898148</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Village Search Bicester and Kildare</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Famous Oxfordshire town mispronounced on Saturday night quiz show - Oxford Mail</t>
+          <t>Bella Hadid Calls Out Dolce &amp; Gabbana After Controversial Fall 2026 Show - Preview.ph</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 12:00:00 GMT</t>
+          <t>Mon, 19 Jan 2026 07:59:35 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQellVbGpodk5ia2wzMkZ1enFkOHRsZ3BDZVYtZWZITlBJNkZFelg4VU5Wa29oSzlPODVIUTRmbVVnQS1FQTVLMjZCU1N2NjFlZFZ4T3ZTVEY5WnhVaDlnRHdNclEtSU9HTWVCVUNQSnozdlk5Y2dhXzVxMUN0dmlwbjEzWFBkQ3pfbXl2akpQUS0xR3M2dDk5N251ODRDTUc5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPVWt6eURuaWNBTG9DMEdjZ2ZKd2hvbFI2ZVB1c2lmSlBwaWpEMHhTUEEzSUJzQ1NiRHBoWFZwNnA3bFdsdDZ2UDFoRTVuNUE3Y1pETkhMYzRxMXo5T0x3T2ZydmY5YlhHa2xJam1wdHFQOHk5TG1tMEdsVGdGdVJzbDFLWEpWdnk3ZjBzdVltVDVQckNNb1FkU21uSWhKLTBJN25paWg4ZV8?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46040.5</v>
+        <v>46041.33304398148</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tooting stabbing victim rushed to hospital as police set up large crime scene - MyLondon</t>
+          <t>Is B&amp;M European Value Retail S.A.'s (LON:BME) ROE Of 35% Impressive? - Yahoo Finance</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 12:57:18 GMT</t>
+          <t>Mon, 19 Jan 2026 05:55:00 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNZmdHem43bmFfZExUaVNYb19vUzd6cTNWNl90eHk0UUUtemJKckJ6UUgtUVlwVDJHc3ZNVUExVEFkMU9MaUV2N25xNjJYRER1bjdqb2RGVnNDWlVVRzNPWF9RaVh4eVBqdlBHTWZZc1p4UGw5cTdFN1BJV2VuUWRJUWlHcE8tbGtFX1Y2RG42eHNEbnNFSTBBWDNCNnMyZ9IBowFBVV95cUxQajFkQ21uWjN3RmhBaEdaS2VfdDh1cVBSRHVSQnI0S25VLXBxT2FVVWZmT3I4QkM4d01KQkZfRkdlM2NPeUtxR2Q3eGdZVnM3NmMweUE0b1BWNGpDbDhIM2Z2WWU4MmEtN29YbGh6TDZhb1ZNdUdfdjQ0eG54WnhrZ1FFMmloZkNFdGduVWxRTHFLUEtTOGhEc1F3THY4WV9XVHFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE80TWU0Slk5TzZ0M1dyUlFRZXJ1MTB3Z09MaXU2UENUQXdnaUlxTW1oRVVvUjI0YVRzSFB2SEZkS21xbWVlVWR0c2s2NzdpTmhvaTE4bFUtbERKbkdYbnFRZUtfTHR3WGE5Ql9vRlZkcmpINFBYeXFSOUxxMA?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46040.53979166667</v>
+        <v>46041.24652777778</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Man in hospital after stabbing near McDonald’s in south London - london-now.co.uk</t>
+          <t>Amazon delivery driver is shot and killed by homeowner who thought he was his daughter's boyfriend, prosecutors say - Daily Mail</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 13:00:08 GMT</t>
+          <t>Sun, 18 Jan 2026 22:08:41 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNVjlXZ0lJTUw0S0NaZmlBRDRIbFc2YW1nOW5Bc0h4cWppNFFWTEphUC1jVkdTMEkwTXRNcXpaNnB2dUJ2NkFQTmxsd3U2N0o1b3ZhOTdMejA0Q2tPNS1WVV9TRlZFajBFSThEMzVKTE5HYVN4UjFwYUkwVVdpRnZHNnpJTmIxZFB6OW5tRE5hSUJEZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPaTF4UXZ5NzdTUzFKM3dEN1BjblVFT2lRSHp3YzdjWTlnWDVkQVlnZnlJOHhMWHI2dmRVeVpOWGpzVDRZcDFhWUVlZTcyX1QxYnUwMW4tbEY4VExoYUhmNHYxQUhEbjVYX25qS1ZNQWZJYjBXRTU0ZzQ4Tlc2NzcyelBIX1YyQlhza0k0dEZfbDJ0dEdPYmNVU1VFQdIBoAFBVV95cUxPSzNEUG5EY1p5TWw1UHRLejRHaFkzZXhSc1JCZGRmZ1FFajNVTHhFbFg5TnN4aU9IX3hCMkcwMTVZcHdQNTVhTVhXRnZmc1pBNmtoUUpIeWZxUjcya3YtdHNPYU5rSkItUTBQSFdaWFFhcVhSVXo2WDZjcEF0U2xuMllRUl9waTI5Q0IxNGhQQlo5VnNDSXY2QWRXX0VIYjk1?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46040.54175925926</v>
+        <v>46040.92269675926</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>‘Too Much's Meg Stalter Would "Literally Start Crying" While Shooting Fergie's ‘London Bridge' Remix Video - MSN</t>
+          <t>First Amazon Now quick commerce site goes live in UK following launches in India and UAE - Retail Technology Innovation Hub</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 12:05:41 GMT</t>
+          <t>Mon, 19 Jan 2026 06:11:35 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0ANBVV95cUxOSm85TklrNEx0LTJZbThycEN5d05OZGpJSzFtRWdNb3NpdHZuV2s1ZHI4UFdFYjJHVFQ0MEpqd1RnNnAyUnlMMDJ2WHBsSm1BU3VuN0lWd19udm5EY0l0QUdfVFVEZUpfSjVrZFQ5Y1JxMk10Rm9xRlVnSnNrclJ4S3ZlcGZYX2hXN3ZwczZTMVZpNlRCbEx6WkdOQ3FtdU5ZR2g0ekZLdE81MmZzbXFhMnV3WFBVZVpwOEh3bDhHVHZLYTljN1RyZ3RKQlFCLTJOX1pyOVZKaUdnZjNrZDc5emVlNklEdEh1VU9LLXRZb0RsSmdnYW9FRm5NSW1zWUxTb0lDUUFROUVBaktSV2RXa0Etekh2c1JGV0ZPSXgwZzZ6R1VrV1ZJckE1Yno3OGRBVUFPaGtoZnljOVQ3c3RzOFlfMVVqVWNlR3ZzUGh4QVZnMmdGaWhqc0wyQlg1dHhIT3luWmoxUGtRVnA2Q2o0TENnaUpxYVBJaWVWLWZZSGtNVlFzNWFMbEdDVW93cUxhYmxfT2MxcmlPMUZBT1Rqdlh6MFlhWTBnX3VlUG1mV1dtVUFiRGhKaE9aaEV0RjJDbmpYYUttX1pwS2E2Nkpwdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNTk54N1Vfa3I4RUFhaE5xek5PLXBKYjdBRXVpQ1dTcHlvTzVaZy1WN0ZGb1MyQ0M1TUJpeWFHdEx4RkNzWWdmYzRpSlpvdDlfelpZUi1wQ1loUmIycWY2MWFwbzJCa0VVY1JqektTRnNtNWFVZXJTVlRYWFVtMVJsTzkweXJzNTlVcWhheUczamVjOElZdDk5TlpmMVYyWTRfZE5PQkRsdDJQaGJENWUwMURXY3VSWWU0WmF0REVYUmJnVlptRFpENEZPUGpUY1puVmdkekd3?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46040.50394675926</v>
+        <v>46041.25804398148</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Roy Keane left red-faced following explosive rant ​ - Dublin City FM</t>
+          <t>Amazon driver leaves dog owner in stitches with proof of delivery photo - The Mirror</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 09:38:29 GMT</t>
+          <t>Mon, 19 Jan 2026 04:00:00 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5vejRUZVdoSlJDN0Jsc2p5akhHQUkwRjZPSGdUQU81RHBQZjMxVU5OSWFCLVdlNGZyajlURnhCdkZBOWZTcElCbEhpRFZ3UHBoX0NkRDRWTFZNeURBOFdWbEVyUDRnRWhkdVl5dTJmazByUlVLMXdvenhhUjduU1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPWGItN0w0emZpY29wRGhXLUYtV1FxRjRLd0FodUdmYXBnWkJuTElGLUZJcVF6V2tPNS14T2Y2RFN5WTlfOTBFcmttMzFydURyb1VNMVRlVjhfTWktUkM1R0ZTVDh6bG14Wm9Ka3dTUTRlalBsd0JqckU0SVV3MGxGVDFER25BYmfSAYwBQVVfeXFMT2pGY1lqbUxjNHZSR0FQZFE5UWJwbGpSNjdLeVZLSmtVSWd3dHdTbkxVTGtlckRNZzBSQVIyaTN5V0hDOHZENGY4MEY3VWlUM3lvV0pMb3Q3MjJkU003MlVDWG50TVM5UFc3Vm94NEZwZXZENk4wSERiVGJlOTZLQ3NKcFdWTm9OMVlWdWc?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46040.40172453703</v>
+        <v>46041.16666666666</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New owner of cherished 'John's wood' refused permission to chop down trees - Eastern Daily Press</t>
+          <t>Mexican Marvel: how an international business got a much-needed health boost with flexible, scalable fulfillment - DHL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 11:00:00 GMT</t>
+          <t>Mon, 19 Jan 2026 03:38:16 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQX0lsOGV4WGZ2Q0lxRXdZTGlrM2kzRHFGYURQSHg1WVNNYXgwTm5OMy00ZmRwaGNIU2stXzUxd3lBWG45RmV4RkM4aTFwcGlpdkhuQ01ZWHcwRkczaHFYMzFycm1JT2pvdzVrQUwtMU0yWWJkWVFmLWdKamdtR0ZnU1hVaWc2UEprbUZIMWRjSFhCVmVX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxORG5kdlVudldFQzJZc0dGYk5OYVVDeG9EQ1BQT0xpdGpXRTZka1l1NzVCMWM4UU9LemlWcVVvRmdwc04wQ0ttUTYxRFlNdjlJMzdxNVE5TGU4eTRaRmRjdl9Va1Q1SDN5X21acnR6bzhvWEVwcHE4Nk9EMXU5UjJTM0Z3RGFXcF9jZVRiSzFNY2JiT29zZXFjRmxGc3hoVnk5a25mOGFTaU9odFhNRU00RFFRSUc3VUVCbUgtUUJpR2xGV0xtQTFpcnhHTnhfbWxweUFMZ0NtRWpLa1pqeVA0ZG5GYi0xbEJVZndheVNFTzQ3NFMyeGMxTkhXdC1YUC1TTFQ4dDRjSHkxZmo4UFV5aU1CdjM0T3JVVEpDTm9LX1hBbGFVeXc?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46040.45833333334</v>
+        <v>46041.15157407407</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ex-employee says Oxford Center brushed off safety concerns years before hyperbaric chamber death - ClickOnDetroit | WDIV Local 4</t>
+          <t>Hayes steps up Evri fight in Commons - Bournemouth One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 10:00:00 GMT</t>
+          <t>Sun, 18 Jan 2026 19:16:24 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPUmlJY2Vkb1ViOHpkWTM1TXAzalloa21yTkI3dnhrSnZ2NXZfMDBZOE5Vb3VxNHQ3OVN6eWVEb0QxRGhvZEJNZmktQ3JLRGVrZDJtTDU4NW8xUkhoeWM1R3g2MVhPcXhuN0lzNERBLUNwS1ZCYVo0Wnk4SU4tMlJ1VmJFeXZZcG96WWtiSlMyS1VOUkZJY2F3cTE1VFF0NTJUaTBCWnpaa0Z2dVBQOHFlSEhGbGcway01ZzdZMHcxa0VCOThjX196MWZ4V1RtazE5YmxRSkNOWHZ5Mm5vbFJyYWxmREE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE1FcHJaVlBldmFfOTB0MXpFZDRNSlRwQUljSVJmZXR3ek1JUmU2VVFWem9YTzJHcWFHdmEyanZ1S2JIcUFUSmxZUmdLZUd2RDQ?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46040.41666666666</v>
+        <v>46040.80305555555</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Unsolved murders in south east London including Petts Wood 'train ripper' killing - london-now.co.uk</t>
+          <t>US-listed group Assurant acquires reverse logistics player in Australia - The Loadstar</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 12:00:00 GMT</t>
+          <t>Mon, 19 Jan 2026 06:37:58 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPLVNFc3M5QjhUa0ZQTGo0ZWV6aENzZUtXLWhNMXVVN2dINjRPLWZlX2trdlA4cl9qQXpSS3dVd3RuLUs1cEpoNldaSmY1Y0ZoMm5hSlQwSVVENng4YmJzdlo3MFp0cnNvX1BTQUNKQ2JkWDVzeExZc2ctNGlQaFl0bHROdktpcUhJc0JZSHZFNTVpTHgyYXFOcnBJN2tONFZxVWlaSE5uc2k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOeV9waHozb29xN3NKb0FIdUZTYVFkS2hXeFZjaUloei16cHRSZkRLY0syeEhfb3lBWi13WDMxQUl3S0luRlprWXQwdlREb2YtMFZVSW9ndUp3UUp6Nno5TFJ5M1lERDdtRG5GZnZ2eHFXWGlYejd2blJHVzl5QXpDY2wxODdRdUUzcndxaS1OWkJGamlkX0pKeXcyQ3U?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46040.5</v>
+        <v>46041.27636574074</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>The London property market might be about to implode - The Spectator Australia</t>
+          <t>Can the EU-Mercosur Agreement Meet EUDR Standards? Testing Deforestation-Free Supply Chains Among the Amazon's Tipping Point - Intelligent Living</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 10:01:10 GMT</t>
+          <t>Sun, 18 Jan 2026 19:06:46 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNEtWUFpQV1hRYmRhYzBlb2p5ZFJzMlR3eGtCeWtuWFlSbTRYVFIzN2gyRWdTSElZX0FFejU4UHFxN19jLXhSeFdKdUlpc0dmRkEzbjZmQW1IRGx5WGVFNXF4ZXY5M2UyOHMtb0RDUGJkM0JQT3RkYmVUY0pvTVJTZFhSVzBnWEFCMGFTcHY2NjlIQlhS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5iZVo0WG81aWZtcjQ5R2daZ3c4M2tnSnFNNmpYS3pQMEo2TFk1RWpIeEtYWDVVYWtIXzJJbE9DcGxQSFFicXJPQ2pVTUx2eEhVemRMTERRZWtqU3JPaEU3R0FQUWQ1TzdwTjYwMjRmaFV3TUFFV2RMeE42YVg0Vms?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46040.41747685185</v>
+        <v>46040.79636574074</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Adolescence's Erin Doherty reveals telling off from mum after explosive Emmy's speech - The Mirror</t>
+          <t>Is the post office open today on MLK Day 2026? UPS hours, USPS hours, FedEx hours - NJ.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 12:59:00 GMT</t>
+          <t>Mon, 19 Jan 2026 07:01:00 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOV0lJN2Q3aUhzNXJPVjM2eFBxYWpiY3JFZWNtM2tYdUFiOG5rVVVzd1NXOHJpcGp4RHZhZmFmTG53eGo4LXI4QjlkVF84Z2ZEWVo0Y2JmSk5aQlFEcktPVkg0NmJpZTVqSHotZDROdDlsVkY0SFVab0hWLXQ2cndDOVNzaGEzUndYZWl3QTdJc1Zic21tZmhyOTZTVGQ2REXSAZ8BQVVfeXFMTldJSTdkN2lIczVyT1YzNnhQcWFqYmNyRWVjbTNrWHVBYjhua1VVc3dTVzhyaXBqeER2YWZhZkxud3hqOC1yOEI5ZFRfOGdmRFlaNGNiZkpOWkJRRHJLT1ZINDZiaWU1akh6LWQ0TnQ5bFZGNEhVWm9IVi10NnJ3QzlTc2hhM1J3WGVpd0E3SXNWYnNtbWZocjk2U1RkNkRF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQdC1oTmJQV3R3U2g2Nnl6R2hLT0laZmZjUldsTnpITlZXWGN4RTNDQWI0bm1KNVBDa0NkRUJOMjBpMm01dFVHc0xoSFJLT0NoS3FIYUY2V1FPRUYzWDFpVzFWcHhBUFczZ2JiMVdnbzVnSkx0cjNmT0VEeGJ1WkJpNGVIa2NFZERvaXlhdjFKOVJHSDRaLVBxNnVfeE1jZk8zM3oyRnAtUW1qNzhEQU1vUENzdDVNZF90SDdR0gHPAUFVX3lxTE4tdnhKT0ZPRkNoMFY1MXhJZlY0SWxOUFVWLUdMcWFVbGM2bjJFc1QwYlZ3UDM1dW5QYlRzWUJJdndDdkdPQW9fVlNTV1BjdnFKVTNWNWgzTW9mLV95SFlfMkJqWVR1eDVhLS1TWEo4X29Md2tJR3BhUEViNlAwcmtDTEU2enNoQmthLVZNazZfd3c1RldiclFST1VyYlJmeTh3WU4wWUJ4WWtmaGw1clE5ODNBdU04S1RaQW9PcXpVWHRfcS1KNi16Qi04NFJubw?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46040.54097222222</v>
+        <v>46041.29236111111</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Massive explosion at Swindon industrial estate rattles homes as fireball is spotted from miles away - MSN</t>
+          <t>Last-minute gift deals at Amazon: DoorDash gift cards, Fire Sticks, Keurig, more with same-day delivery - Mashable</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 10:30:14 GMT</t>
+          <t>Sun, 18 Jan 2026 20:30:47 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AJBVV95cUxQSkxfV2VFSUM3aU0tSTg0QXFhVThfXzJRMnJXTUFEczZtZnRpU2FpUU1aTi1zbnlRakNTU25FYjRySkNPYkFEMjdoRHlNSGdadkYxLUFFNUxwSU1KZmJwVUMwQlJqWndmX2JReXRfQmFSSFJQZ0hxbFY1TXR0bVpveldueVYyNHNJRndkczltcmdaTFprNnczOUJpenJYRzlab2Q5cHNFZ1NLRi1Kc2ltT2g4U0NvVW1LaElBUUdXMmRicVNxT1JTdnJZVGVnNTVteGNPY0hoUVRkQW9JT1RlZ00xSm9ZbS0wSnF2ZGZKZ3ZpVlVOcHNwNHVkSkdSVVViX3NSaUpJR1Z3V2p4Ty1nMkpnMDIwZDFqU3hPeXNOdzBrOEZPenpLSnNpWTI2cWRrc1VVMjR4cWM1bldsNWxxU2N0b19FczZlQ09jTTltUnNyNjdxdWw5dGl4UnAtM1p1dDlQNnloeGJLWlNMZWNHRHJaZUJNNDZU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNSFhiRVZGeUNZWEk3QXd4Y3A1WnZyMWJpa2c2ZmhlYmVTcUdaT1VDRnNBX0Rvd3puNGNPSEZqMkxTems1MkJjazFJOHhscDBGTG1LUGx6S0Q2clJDY0tWNXpjOWI1UUVOci0wb19zYmktc0hMX3ZnUXZVVkxwVU0xQw?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46040.43766203704</v>
+        <v>46040.85471064815</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>The Hundred Heats Up: Rashid Khan and Nicholas Pooran Join MI London as Welsh Fire Snap Up Ravindra - Crictips</t>
+          <t>No injuries after vehicle fire on Dare Road in York County - WAVY.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 11:37:37 GMT</t>
+          <t>Sun, 18 Jan 2026 14:47:49 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNRHE4dVp3SnlONUhwVERUblRldk5aYTJPRWZiQW1ncWh2V0NwMmxWblVQYzNua3o3Sm9rNjRlNkFLUkJhSG0zYXhtR1VQNm9KQVpobWp3T0dJTFZ6UFlpZ01xRjYwUVRMMjc1ODhDZllmaU9ZTjROZi1fdHV5QzNESW1jX3NWWGVKS0hqSHhyNjFLc1hWUmk2bmwzYTZQWWYxaGxPSFdUWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPeHhvVXZoNUplWXhqSXpHYU4ydTUwY0N3RnBaRE1uWW5nLUtqQ2Mwc05GUHlpMmhEVGxpTFV5UUJqOUhJVUJiUE9OaFFmTGxkSmxuNlZIZU1yUnJiNWVzNlVhWTk3SVdBcmxXTzZvRWl0R282YkVxZ1Fmb3Y1djFjUmJCZmx0T3B5UUJ6QXJyQnhZTXVBYldUdmF6WHhRM0lEV1MzUUllVjJpeE5iT3lfN3VnZHZ5ZUNCV0xiVtIBwgFBVV95cUxPbWJYSVRJb1k4Z1lIb28xQkk5dklBakl2ekZnSnFnbUtiSlVyMm9UU2pzTGlLWUFBcEdvRmhXYmRWVkh6VEN5SjZkVmdTTXBRTzNEUGxUNDhCZmJFM2pfN0IwU2hWams2VE1XVUxwdVZnUFBYeEZBUllUU2dUempHQ2NVcFRsNlFjTHQ4VnlUUnFEaW1yelFIMzFzTmtyTEkxNVVZbTBoSUNJb01kUGIzXzhGYlI2S2pSdTBOMXVhbGNzUQ?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46040.48445601852</v>
+        <v>46040.61653935185</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FLIGHT BAN Piers Morgan in Hospital After Fracturing Femur in London Fall - UK News in Pictures</t>
+          <t>MP is full of praise for logistics operator after a visit to London Gateway site and says: - Thurrock Nub News</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 11:50:00 GMT</t>
+          <t>Sun, 18 Jan 2026 17:05:40 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNSm1yNlJpVkdnakhIOEpDMnAzTDN1SkVjWkVuWE52WTd2TDVMUkxzM3IwcTJvYjM3bmJDX3ZId1F2NGRJblpGTkRzOTE0N0NFdVJXVXZyTUxwRFB0QXM5ZkI2c3VZcXhkYnJKc0RJbm9SSkU0NXdBbVBBUFp1dTd3X0ZOOU10QW5MY2c2VWo4TzB4THMxeWhxTUhRQ09uVXd3Zmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwJBVV95cUxOa2xHZDk1Rm9SZDdmSS1OMGpLRVJzSEsyTm56WjVERThnbzhiTEJodXhvLWpqQVhqaE4zZkF5UkNIckpqelJGYVNoODRJVXJaeW43TGNJVTBWRTFPakhMdFVzaWFLZy1ZQi1nOE9FZ0g3V0RuMGFBTHRPRlEtMGswZnRmVEU0S0l3SGptMjU2VDNheGJ3OHZBSjVrSV9Yd01vc0U1WHYtYmhIdXMzb3Nsbmx1c0VPbmtnSFJQUm1DU01HZGFOWmN0YXl5YWhERFBzb290bjVMTWVEVE5icHNlRFUxamZmVXA5Wk1lODZmYkdZTy1mVlZkRWhvUjFiMjdMdGVncGw0MWxQUXRIeUlDM3NuemZCdW9DYjF6TUJwTHVQVWxfdm1z?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46040.49305555555</v>
+        <v>46040.71226851852</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Paris flat collapses during party, one badly injured - Arab News</t>
+          <t>Asian Courier Giants SF, J&amp;T to Target European, US Markets, ATM Capital Founder Says - Yicai Global</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 11:44:05 GMT</t>
+          <t>Mon, 19 Jan 2026 03:09:28 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE11eHVoY1ZYRkdNdXlEamxEblB1YVlWMXFkTVZkMDF4S1RicUZmN3FkVFJUQ3VXUHEybGZsZFgyMEZtMmZXREpuZm1pajdYZ0x1MW5v?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQSTJuN2FvMWpiLWpXRFc3OWhIWllfUVpEUzlYOWJBeEdPMjdmd0g1S0toRmRKU0tvUXJRaUJ1RXVPV09pdGNzZjZaMlNJM1BfVnJzQzRBYTlIc1pwbHhVQ1pzdE9id3BwZVhXVUNTVlJEdGlWa0JqREczUHR6VDY2cFgxbUhVaHRDRE9NUjI0bFM4cWNmUWpEdW1Nc1FsbS11ZUFlbkU2TFp2Rnl1TWdyelJsYUY?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46040.48894675926</v>
+        <v>46041.13157407408</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kevin faces the end in Coronation Street as Tyrone witnesses his explosion - Metro.co.uk</t>
+          <t>Amazon’s Strategic $35 Billion Commitment to Elevate Logistics and AI in India by 2030 - GetTransport.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 09:00:00 GMT</t>
+          <t>Mon, 19 Jan 2026 06:57:39 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQY2RaSDRpb2xZNjYxVlUtbjFsT2JTX1QyNnRwTzVPQVNhLUlTM2pDRjROcU5GSVd4YThQaUNIWUVraVNGOE9ORi1jLUtWVnoxZm8wNmUwS3otSnB3aHYwZ09IY08tbkNpWjBGTW05TnVIZy1neHNrVlEtVVdMaEpHbTFCZVZjN25Nd0tSVE9LUHl4ZkV3SVo4RlZOdXpWTVcxWjE00gGoAUFVX3lxTE1UeVY0RjY0cC1JZXpxb2dMQjk3MEhiZkFTUXFfTFNrOHRjVUJKUndpSWFQXzVqVThva1hhRHFLTmoyd3BZb0tEeU9tRVZoSUgySmtVVUVYVWwyUm5LVnVLa1B4bXEzb2RmRGhoc1RMSXNVS0RwYXpZRzVuXzJuUVViMTY1WlMxdHNfWkgzclpfY1lKN19CZmZxd19aXzBJTVgzWGU0cTNEYQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFB5R3JCX2w4eXVkb0JLUGVQR1hJSHFTaWtTVGhUYmJoZVRqUFM1akpEakcyZFhmOWlaMmF3cFhRZnJzRHdsUzRJYm9LYjRVdkNRX0RFS2g2dk04dFdUM29tdE1pY0RhQW9WcTk4bUxkZThuRHRyTDNENWt0OWdiQQ?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46040.375</v>
+        <v>46041.29003472222</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3 takeaways from Iowa State basketball's loss to Cincinnati - The Des Moines Register</t>
+          <t>Philippines DHL EV Fleet Rollout Amid Limited Charging Infrastructure - Global Fleet</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 12:01:00 GMT</t>
+          <t>Mon, 19 Jan 2026 00:22:44 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNWmtqSHFtLVNRTTI4Y2JZOU5uTHFCSGhuR0hzYWhNM2w0bHIzSE9yRENyOTd2d0N1NEhPWllyWnF6QUtCenpJRHAydWVFcDJtRDU0U1QwQTZVQllqeHBMU3pOanJUZjQ5QjVUSHFiTUdsV2JwcVo0cGRma3pYY3NRU29ES3ByVWV2WUhidTVGZ0JmX1FHUW9aM3NuU19jc0pPcTcwYzY4empObENvVTBwY3FnenlpYmhPbEUwZkFtcTgxN0ZVNlFmb2hwbXAxekYwZDFuSGRGaGpLUFFwYVF5djBDYXNSTU0wUnVvQXJ2ZFZZNGFTSkpTT1llUTBKZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQWmFWa0ktQmlTMGI3ZXAxN1F5ZlRtNnZKRS01aGdpNVJIVWs3QjJCVEg4ZjlJSGdxUlQyZ05MMGYyTnVjU3BGMzVxdnQ1MWVCc3ppU1ZMMjZJc3EwSW9RakdMQlpmT0lLRUdjakhyS1E1TC1PWnVnQzdOSVpwSTI3bG44V01mUDhFSXFhRXZzZXlXN3pBZGVYZ05lOEgxMS1vUEVoMnlVbUtKUFJucHN3b1M4TmNKdUprVnZlMlREb0dhODExM0M1Sw?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46040.50069444445</v>
+        <v>46041.01578703704</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Udinese 0-1 Inter Milan: Flaws Laid Bare Despite Win After 11th Clean Sheet - SempreInter.com</t>
+          <t>Tech voices: US.-Taiwan chip deal, Rio Tinto-Amazon copper deal - MSN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 11:08:31 GMT</t>
+          <t>Mon, 19 Jan 2026 02:23:46 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBmdG1qblZTZXlDQ1diZS1iQV9YaFBfeko4QXE4UlR3LW42TXdIWWRSQWhFLUdLa0FNbmpRcnY4Wms1WE1ZQ2JERVRRZUgycXBNRnh6LUhTYXlkTkg1VUU1ZU5RNFdhOWNSZ3Q0YVJhaWZGVWlSV2JqU3RuYzPSAYIBQVVfeXFMUGRWdEZEa283UEtLTlJ0LW9fdXBSZ3lGVGRXRUtJZ2pHaVJMem1IR3FvdGstaTVENXBITmoyWTFla0VhZDh6cTdueU1ELU1OcktfYlFad2E5SWhLU2d2Y0FEVElSMDgxVWQ0TmVrWXhkeGptQnBLalQwYUtWaU5jRXpSQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gJBVV95cUxNbG16RUMzN1cxUkIyLTVOZlFDa2RaZGlNQXlEMkNfazI1aFBUX2RRNUtSNVE2MF9JVDJJemdERnRXTG9LNDF4cGJJSk1GOHRxbkl2UFZvMGszRUYwMWxoeWpYVGlYTkFrRmZuWlJ2WHFwVXpWRXZ0cDJQMlhhc1Y2NHBfUUk1NlZjVUtNY0h5eWJfM05GRHdCaVVVZW4xSXRWUnc2c1YwakdURDRFYmp4dENTMHZjOUpRQnVVRThwT1FoQU9fNnI5eXk5bGNMMHhUVDBOc0UzMnhnSlBXX3ZnWUZtWU1uMWhQWGhKZ0VSSmp6cG9ISzRaMm5NdGw4RGV5YUNHVXpvMnZQazlYQTJxMWQ3R19qRkJJOGNkRWxRVzd3Y2M5Zk9UYVlxdVpjUWQwQmpqRDFoU1FKcjRFTmtpZ3dqd1lqTFNGMnRYMDNEQVlWS1lVZzZIZE1jM1JhVUE0UkpKcHNEcXo5Zw?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46040.46424768519</v>
+        <v>46041.09983796296</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>What is biathlon? Rules, events for 2026 Winter Olympics - MSN</t>
+          <t>Asda job cuts: 150 roles at risk as depot shake-up and Evri move follow Christmas slump - TechStock²</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 08:47:58 GMT</t>
+          <t>Sun, 18 Jan 2026 21:55:42 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNeTdJQm1keHVMVlZQVkoxLWt4Y3Q3TkF3dDREbGFOVmhraDBERWtrVEVhQnJpLXY4N3F0aFNtUmFHWUZncGlBUHpCYmp4Mk9RUE4ycUlzRkx3SkJ5TUUweFNEMlVPU1pFVC1ieUVEUERpazU3aEpDTTB4ZFFaZmx5T29EcGlLX2JUcmV5TUYxZHAxRDIzSEluZ1FHLXpPcTc0TUdUU3FEMkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPNGJKb0VBdjJoMkMxNGx2dDdBUWZ3M3NqMUhUUVprWk82U2o2ZzI2RzhOTDZQeUtabW45NkhnY1ltQzV6T3NSWUZvR3NEUnZ5TFU0STV2dnVKZmJZeS04RU5uLUNSd3pNaV9FY0pfbENSUUdQeDlKNmFiaWFubGl4Qi0yYzNkZ3owaklkTC1GMkFDZ19ST0oyaUhOYWN5RmlFOHZ3ZVcybUxMS1U?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46040.36664351852</v>
+        <v>46040.91368055555</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>'Be in no doubt' EU will retaliate to any new US tariffs, Ireland says - Reuters</t>
+          <t>Get Up to $200 Off M5 iPad Pro on Amazon, Starting at $899.99 - MacRumors</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 13:34:52 GMT</t>
+          <t>Sun, 18 Jan 2026 15:21:04 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQUm5veE9NaVJjZHhYTDNnTjZrdWtXR3hNTkdBWFZER21aZTZ3dTZBM3Q2WFUyT0g4TXFNMzItdHplYTExcGZ5SGdGUzhsVkRMN2JlYnRyYVMzMmY3cHg1NzdaTDJLY2phejE5Q09selhCRmN1ZDFMY1dWd3oxSGJ3ZWl3STViMTlrcGpOSE84TEFfTmpGcEt2cHFhd1ZFYjNicXNKMXZDQk45bVFJOVdZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9nYjFadVIwT2ZlLWk1eFlId0ZPQXhZTWlEVXdzWTBGdXRMQmRoUVdpeDEwd1pqTnJOblE2aDIwdzdZVzFJZGpCd0pfdVdnQk1mcWFYN1QtUEJkV1pYVU9wQTNUVENfaW9Y?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46040.56587962963</v>
+        <v>46040.63962962963</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>After Trump Reignites a Trade War Over Greenland, Europe Weighs Going All-Out - The New York Times</t>
+          <t>Amazon’s Strategic Pivot: Securing Energy and Expanding Cloud Reach - AD HOC NEWS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 13:27:47 GMT</t>
+          <t>Mon, 19 Jan 2026 02:42:05 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNWHRzcEMyQk53TTV4ZVU0V24wYUQySFFoejFDLWxIcV9neGQ0QlgyeUZmRnBqcDk2eGJESFBZLWF0UXh0RE9sRk1oeXM0NS0wRUN6ZkJFU1NVVG8zTjlzanlUUVYxODlFdTNJOVFYR01nd3U1SzZoWjAzdS1fQ3o2Tg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOenJ5XzRELXpja2IwSVFNZzNvc0FuYjIwWHBIMnpXM1M4M1hacW5WSTFUV0k3RjhsVEFrVExtd0ZGUlFlQUEzUlFCdGdIaGhDdUpUd0t3UjlrM0V2bW1nR28wTWZUUkhqaDN5M08xbXFEaEZLZ2JqTFdkTG1BTk9DeS1ZRUdyR0stSnZtUENfNW9hOFhsaEUxVUVYSmZKaDRPa0l4cnJ0bURybDdjQm1jQnRGV1lBWWZTSndodVlCa2Uxc00?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46040.56096064814</v>
+        <v>46041.11255787037</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Local Town Searches Wertheim German Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("Wertheim" OR "Wurzburg" OR "Aschaffenburg") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR boycott)</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bondi beach terror attack - The Guardian</t>
+          <t>Motorcyclist injured after crash with Amazon van in Sun Valley - MSN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sun, 18 Jan 2026 13:33:25 GMT</t>
+          <t>Mon, 19 Jan 2026 00:18:29 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxONlVLV2lSbGRXVHRsZk5NSHdwOFhZV0RSNktPd1FzWnhvbUtNYUtodXZ3VVNMeEZySWhEcXgzQzZ3Ty1WWHhQejRwZG9UTXpRSWp5QVc5Tl9Qc0VjekptUmI4MjJQVmlZcGpxX1lRamFlQXlWTVpTUDhXd25HYlVDS25UelE2eWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwJBVV95cUxNdE5nSWRmcGxkYzJ6X3YxOE1KeEtwVTRtZjNHS0duUGFDcU5MYnVyaFUtUGQzWGhCOVdxVVJPVl9sb3phT1EzSmpORERVOGtPTzZ4LUVQUXVFQjV6a1NtUlNGd3BLMzVCU2FuVnUtOU1aNUJrRkl3WjVkNFhETVpoc3UwQW5FUlFuRUtIRGJWRmNRMVFFSWZ6QVVxZUo0MUNUbXlpVGpJUHpYMkw5T0hpU2drbEdrSjBoTDBXajZyOU5US1dkNHZXUjdtT2UzaV9naU5LQkhUMUdQOE81QWFDQTZmRGxSUVRXNkRHclh0LVFMMWZnOEFpZTIzUmMwUnExWUdFRW03NmdpcGdhZVl6RDRTLWVuNWFmZmFmV3NhVHU2LWszNEhhT3F2SkFfaG90c2dqMGVpMDZ3Vm9BQlk0WDdKdw?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46040.56487268519</v>
+        <v>46041.01283564815</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>BV Logistics Companies</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>'Why are you here?': Amazon worker turns tables on Karen 'policing' his every move as he delivered packages to residential building - MSN</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 01:39:48 GMT</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgNBVV95cUxNOHRDX1pueVNuYzFTOWZmb2J2ZUs3UGxIUTUwNU1VTmljZ3E4Tlp6a0ZrYXdNdng2Y19yYTc2XzVURml5Rk9ab3RxMkpkdUw0T2ktOHpoVkpDSjNnWjNiZjhYanlrc3dIV0I5b1dsQTAyUEhGOVpYQ2pjanVCcGpRWVM4UU9SZVhjYmxlMEVPZGlzbGJEX1h6bTVWWjNUN1NxUFF0ZjE1NnNoVGRITVF5Y3Q2VzZHaTdVMGpzYlN2NmdiVU1aSVFCUExyMFVmUlRrUUo5UFRXNHBmOG91LTRfcmUtVk1EYkd6Z3V2ekdiUFVFVjZabHQtUVlyVzdabmpjNVFrcEJaTTQ1QzIzSlB5LUdWWkRCZFhnWFo5SFl3SWdmV0lnNXUxRUxoRjZVX0hXQmhRcnNGWUV0MTRWN1o5dWJLdWRHcS1Zd0VCWW0tRDFRb2hNUC1HRU5BTDNlS2RWem42X29uMEM1VkpCc1VabTdmMmNIaHI3cThNM0pMWkdMZDFkZlQyd2YtNnNILXpfNzlxQ1B0YU5yTWdVTGhuNjc3NnpkT1FqYkhfZEhOZnAxTFRNQ2NOcHhzZFgzMVRBYnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46041.06930555555</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BV Logistics Companies</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DHL Hiring Driver Lead -Nairobi - Opportunities for Young Kenyans</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 06:29:12 GMT</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOa3o1bnBRelM3Tm5oT2F1bmpiV2xCT0xhbGRBSWoxTnB5amxlTzBYQy16TFhQUkFTZW9OWndYWVJCd2MwbVc1aEVEanlMTDdtWV9DWGRoWU0tZkd1aU5YV1E3X0E4bE9KWXZfUVBBZjFYR2JzOTdnZG1pdTZjQ1ZFekRuRXpMV3ZCU1ZSZEpn?oc=5</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46041.27027777778</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>High Level City searches   Germany, English Terms</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Five Observations from Bayern Munich’s crushing 5-1 win over RB Leipzig - Bavarian Football Works</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 22:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOX09jRFZaYkxhM1lEdlJwX21nUmY2S29TT1N4Rzc2bGJzM1BxWmFJMzRDOWJtWlNKaGMtdU51MTJpMk5UOEc0UWNTdTJ0LU1EektycFJnR2dBWDNNQ0dpb1B6TGhrdVhHZ3NsMDlRUVdHWUZKU09pcmNYalhrMU1qaHltSy1ZVGc3aFlabFVwRnV1cmFYUVdPVlFFZGw3NVYzaWZyUm9acW94S0c3VWNBVmRqYW5GYm1IS2o4OXQ3TG9pczV3S09iSWRHWlRwRUFHcy1jYU8zeUt2UTNiakQtUV9uZHBIRVhiblZvSnQyYjNhYjJNNEVZR1k3NG1wUDN0OHhxQ1FHVGVIWFlV?oc=5</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46040.91666666666</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>High Level City searches   Germany, English Terms</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Toppmöller out as Frankfurt coach ahead of crucial Champions League games - The Washington Post</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 20:51:47 GMT</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZU5KeDhqVWRJdWJrSXpHNEFnMF9DeDZOMklWNG9YQkstTks5WmhDSkRpZHFoT2lCWW0wZVlPREo1OGwtOXFzbzZSUGliUUpTYU9rejhYdlhUVnFmRFMtS0tYR0JOUFRPbkRpRGxDR3VCSmhNN21xb1R5WVJEZ0NxemtweVlKNkVwYUxKTWRoV3pXZnk4THhRUzhmRmk0ejRyc1lvcnlKbnVHcFE4clJwV2lLRWJfc1AwNHR5RHI5OURPZWlnMWFESTMtU1A0TWhGMzhyekZ3?oc=5</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>46040.86929398148</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>High Level City searches   Germany, English Terms</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>EasyJet’s 2026 Flight Explosion: New Routes to Italy, Spain, Greece, Portugal, Turkey, Egypt &amp; More! - Travel And Tour World</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 06:26:31 GMT</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQZzJUQ0tiVzhJNzRBT3VodzZrYXRuSnNVUU1scHpESm9pZ2VmTy1teTZTOElTVzUxZHFPOVU0LWVJeXRTUEFrT3NTV29heFRlMWdHdldkRUJrbnFBMGFrb1A2UnFBVVBTZkNvSXgzeHlRMG5ibnRLRnFIRE1Ja09ra2V4YWNTaHM0aVNQQXdma3hyR09fVTd0aC03OE9GWVFnbk9QSXdBNkI3OEhNaVJNNkdCOGpKQkl6NzZPTlhCNExBWWVOeWV2VnYxMHR0S3RwaC0yU2pB?oc=5</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>46041.26841435185</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>XR and JSO Broad search</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>"Extinction Rebellion"</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Santos We Are Watching You - Green Left</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 03:31:48 GMT</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9YVm1UOERDbDNqYVc4bFQ0emJtaVZtLTlrV3hQU2FoVE4yZHpHbG4yTkpHZVdYa0t1ZVROUUtyaEpvSmJjT2NYZmhvdXZ2TXNUNHNlU0RxSjZNMi1peDVCUlluNlJRclZHQ2dfcmlkN1BwR2szMHcxZA?oc=5</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>46041.14708333334</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>XR and JSO Broad search</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>"Extinction Rebellion"</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Four homes fitted with solar panels costing £35,000 thanks to community trust - Hampshire Chronicle</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNSktnejI2QTgzMFN4R1NrUDNobU5Jb3pDMUxaYTB3QXMwZW4yNE51YVRUMkJxZmkwS2ttVXF2dkF0cGI1M2VDemFGeExkaXZIb09IUEl4REswQS10MFlMWVhhaU9aNkxjM2NidmkxcDgwRENjOWUwd1FrUkJNYWJOZy1VeFpwaE4tZUhwZnI5QjQzNVhTTnFERURiTnkyb2MtLW05a0VwdHRGVXpLU3c?oc=5</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46041.20833333334</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>XR and JSO Broad search</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>"Extinction Rebellion"</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Environmental groups condemn appeal over Canford Magna incinerator plans - Rayo</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 05:02:25 GMT</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNWGVkNTUydGFPVTZMMnV6XzlOakV0VHZhM2VmUTBmZjhHWWZQdmU1UnBUUUgxbG9ha0t0MUQ1Sk12MTY4VHh0dHhVVHJSeVJVTUhVMlEtYTdjQ29tTHJZUGVtUk5JcUFFV1ZlYUJWU2Fmckc4eEUwMTRxNlBEcVVia2hPU0VjdzgwdkFQWkNvUm1ydXJBS0NwU0hJS2VZVmU2MzBBcVJORWFpMzZjenZ4bVFKN1Z0MGZVak44WmVaSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>46041.21001157408</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>XR and JSO Broad search</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>"Extinction Rebellion"</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Pro-Palestine activist to take on Mali in Croydon state election - InDaily</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 01:48:11 GMT</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQRWdDYjBPWks2MFRaV1EwOWlDeDJ5UjdFZWVLcEFyYVR1N25tRXh0elFRWXhFUG5QZW9LNzVCenZMaVYzcjhlaEpwemQ3ZnVBZy1GWDdUUnJ0Xy04QjhMbGhtbG5ZQUZLZmtmY0FpNE1VSjhGUzUxMWRLelNpaDBoOWlWX1FNbDRQR2pBQkRDbkJiVzdhMklVWURUVjVXX19wQnlCWA?oc=5</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46041.07512731481</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>XR and JSO Broad search</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>"Extinction Rebellion"</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>'No Chess On Dead Planet': Activists Dump 2025 Kg Coal Outside Tata Steel Chess Tournament Venue | Netherlands - Republic World</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 16:04:54 GMT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxON1paNFVzVlBwQ2RheUtPa1RxZHJmX3Q4ZkRzblcyc3FpdTViNjhGUzV6TVJDZHgtbk9uTlYxdDl4c3RVcTl1VHFQRl9MUjZGUGdmckxHdlh1RkhzM2dTa2JaN0lkNjRfaUJURHJhMVN0NVNneEJTWUpjTXBpem1Za1dlUlhlMnRuTWFhTnNja1lod25jLTYyQWlNVkFsWDJMSzdiNFU4ZGoyeVZBT1ZGTGE2eGNrMU56ZkxILWpaQTUySnBzcG0xQkNSc2RhbkJ5YW5TeGdEbUd2SlJ5TUHSAeQBQVVfeXFMUEhUNHhibXBOOGp1T0VyUmRLdXlRMmFISTM5aVJXQng5ZGhkWGc2Q3VjazU1YXFYZVh3dHlhQThuSUJ0TW9zV1dfa2lUblNUUE9sOG9HMHVHeTFLLTllRXFzSWswVE0xZjJ3MUdpSlk0cnBWdEpBV3VEeGZGdThsaG9mYzVFMHBCWGFwcTNhZWJfaFh0ZkFhQjAyYVQyNmNqbDVOUlBzNXlIV19jVkZmT2J3Si1kcUZYWkR3QWdPSnVjQ0V4c1FUWXNKbkZQRzFiYzFpai1DZkkxRjN1NFRITGk0YjRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>46040.67006944444</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Devon's capital of shoplifting revealed as retail crime spirals in theft epidemic - Devon Live</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 16:02:51 GMT</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZzFmcDQ0a0tHWTQzeWpKYVItcWtMbmpQTURVRGxWTTNSUTV5c19jLTN1M2lhWTJQVmEyd191ZzVrbDZLYTByN1lQVUNMc1lJdVNnV1Q3RkF5alZBTHJ4SzR2Qk5fM3RpRWpUdElqVXR0X3JQa2xDSmJ3eWRQdTcySHlLd3VjYkdLQkR4cFJsczhrYlNyQmlvU9IBngFBVV95cUxQX1pVMzBweFJzakxscHJhOGhSNVc5MWZfZnc1VmsxVkNYSE5kVEZzc3lwc3BGMkswLW03Y2JsOGJ1dUx6WVhsMHRoaENFVGxZclQ0U2tBWjM1MHhhQTV2OS1jNUFidGlwdS1JbDFVNTVIRDFjZjIxSnVYZFJrQ2NxYzVNX3lCUmM3ZzR6VU9sN0p5cVV5cXlYYTJSZ0VwUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>46040.66864583334</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Two men wanted in connection with shoplifting offence at Sainsbury's supermarket in Morecambe - Lancashire Evening Post</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 16:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxObE1fUlBsR0p3U2VJQzJOeEVMcVB4bkM0YVJ6OEhrNjNYVGd2cXcxaENsUkdmekR6UEFkemduNm1tTEk0Wk1veEhGWW1JVWlROEhqZmFFWlFMbndrcnNyMHF6R2h2Q2QtNDFQU2dVRzVPU1pNa1E2UFFuQ0V4djkwc0hNc3JmTjNYQUVNOHpGeklYekRZeTBmaFF4R2ZXS0lYa0d5SXJ0ZmRjMWc1MTBfbWdMLUN1TDBlTG43UWN5Q0l0UDE1bWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>46040.67013888889</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Appeal after Northallerton shop left - Hambleton Today</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 16:51:44 GMT</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE0tcXNvUkgwbDlXZGJmTHo3N2xvdGhqT1JiWVl1QjR5NzllRTFZalpPZVNNXzVwdUFjeEh0NzlTQnJ2eVdRaHFPWGVwdU5KYUpxUDByQ2I3bW55U3hlZ0RGUjJCeVN3WHU2NDd2YmZHVkRTWDAxbWNzaEtR?oc=5</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>46040.70259259259</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Shoplifting UK</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Tackling Tauranga’s policing challenges together - SunLive</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNM2p2c3FnY09feFhUbExCbnhESTFQUS0zdG9GSFNtN21FNmJHX3M5UVR0cFdIX3JoU05maHZxeTdRV3VqNFFveV9MaWktSkowcUZka2htLXRucUJZV2JiRlJqVW9uZExGdVFEYm00N0ZBQmNfMTRmbXFUWm5WTGExS0IyamVRNlZKa3hmSXpiTHptNmpFbjNIaQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>46040.70833333334</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Bomb scare triggers emergency landing in Barcelona - MSN</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 05:53:23 GMT</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQZTVRMlNiYjU2azdGNUdaTVdQSm44LUNWd3hmNkNYY0RBcEdTajVsMlhKbjlleExpOXBkOVktS3dyUmI3ek4tS3FhOE50cWVGc2FoenFQd1hmNE9obE5uRVlHLVE2aktPckRLOEZhbW5PRnVZX2VyMk95S1lzQVVoUHZDNWRBOWNOMWE4d3Y4SGJHMFJCaXNHNmFqWVVIMG9GRGtz?oc=5</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46041.2454050926</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>At least 10 killed in head-on train collision in southern Spain - The Irish News</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 22:53:38 GMT</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPenhscGF6T18wZnNUdDg5bnFzNHZRWndVUG85UnFLbFFMQm94dFdOSUF3Mk5GN0JrQXZvTV9rQW5pTGp0NEdtZXNqSEMtd1BURDV4R1RzNDBxNlg4V0tFcmVIODdnRkpKeEZrUzRYMGR0OS1UMHFtMFJocmY2LVh3cEFLOVdNQW9qWWxaaE9rdFRnOGwzRVR3RTZxLWpEcDF3ZzFJbTFlV3Q2eTY5amE2bEZ5SERHcFNrRk5RNV9XUjN6Vm92andTNEMtQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46040.95391203704</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Defeat in Madrid (94-79) - Valencia Basket Club</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 00:10:16 GMT</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFB5N1hXdE8xcGRCQVFRYVkxM1NoTHZVOE1mLWVuNVl6b0I4OU1nMzJSMDFGVXRWVEtmTlFSYjZuRXA3ckNLdmdVbG1fdWpRRThlWUxFbzkxamNpNmstVEhTMFo4c1FDVkk?oc=5</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46041.00712962963</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Real Sociedad vs Barcelona: Guedes' goal hands Real Madrid boost in title race - Pulse Sports Nigeria</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 02:10:38 GMT</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNNDVYQWo0YmM4VEU1VXBjdGRRSXB3c0NKdG8tMk9wQjVPOVhfNHVtYUhZNUhvbExYLWVSYkFYSnFzLXdaM0dRTGxTbHF5ZU9JQ3p2WEJHOUZUTWR4ZHRzb3VpR1JVZExtUmZNUUEzSTdJSHlKbUw0dnp1S3EtS0ZJczB2Y3FaOENmdVJMOGp3bUpLWmxlZlRqckdlMXNNY0Q2WWw2SXZkeHRaclNTNG5rY3RuVG1nMm0yYUs0SnNPRWNaZXNCX1hvYU1od3N2aGJ6WDRxQw?oc=5</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>46041.09071759259</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Real Madrid eye ex-Chelsea boss as next permanent manager after Alonso exit - Pulse Sports Nigeria</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 17:23:01 GMT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPaUQ4TklkVFVmUkFJUG5sVEZrVUtWbFVzMURyZDBjUHYwaHRhR3R4eUVsVXp3QlhiVkV2cV9TUHpHSzU0MWZEcXltdUNGdXVGSUhTQVR6NmE2Qmh5T1Z0M3lZb05xZG1XTnJJaWoxTDVtWHpJVVZrT1cxSEtfZ1Bqai1CYVRYV2FPWFlCQkNLZldTaVo2UV9kamtiUmZDQXo1aDhSOFAtakpCOTF4dWptTGc0ZkQtRVVjYUpQUnVkY3FVWFlRdnFYLThfdnVJVUJRN2lB?oc=5</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>46040.72431712963</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Report: Vinicius reveals he does not want to play where he is unwanted as tensions with Real Madrid intensify - Pulse Sports Nigeria</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 04:15:19 GMT</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxPMXFvd2NrWVA5ZWlaOXk0TFEya1p4aUxpcl9kM1NKTG1BUFEyOWlZclhNcVNqWGpOQ3B6WndrWkdvZDdoc2pROEI4ZG1jaTFxZTAtWjVCalVHWHFxeFlyVjZJNzhlOGlxQUx1b2k0b0ZaamNiMFowTFVnN0s0b3pqc1djdkxhSlRfOTBTMnY3VG93X2pFazFReDF3Y0FOX2N1RTN5MVpBU2pYV1g4dm16MnpQcHhBaS1iTy1JUUV5UnNNVlQ0bUtneXlqM1pWNGlna2VwemtRdUJtMmY4a0hET3o2eWtteEZmcmFaamwwVFZidmVlR3k4NDdLcGhZQnM?oc=5</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46041.17730324074</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>‘Without PSG, Ligue 1 can be compared to the Algerian or Tunisian league’ — Ex-Real Madrid star fumes - Pulse Sports Nigeria</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 04:40:51 GMT</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxNRGVabUdoVjJpcF80Z2p5eEpXQzFMd1UyQkdnYTBVM2dsYXk0VEEwUjk1WEFBMW9xRkduZVVMQUhlX1cyekR5NHdSSTJOSG5qd2FyS2lkVWVPcUNCWG5BMU1nTVJCSFJQZ0hneFJDZ1V6dkJVQkRscV9keWJmSWVJRDJrNGpSRGtQZGFPOTF5aUhGSERfaHctaWRKd3VIOV9ZcjdVaXZxbHBsUkh0eUVJZTRBRDV1VW50RHVoUDZKSkh4M2w1SlVGcGg0NWNuenJXSVFqVU4xYUN6eFNSY1JfRXpLeUthaGpVR0N4MnNYWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46041.19503472222</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>‘It's insane!' - Frenkie de Jong vents fury at Barcelona vs Real Sociedad referee after La Liga leaders see THREE goals disallowed in surprise defeat - Goal.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 08:12:54 GMT</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQeFZjVG9XX2pfelZIaGNTdXp3NUdqTnNfSEljMW9qMzVEeHlmWjIwMDdYOE9oMGJNTHdQbHZaYUxYaGM5MXFiZDN5X25lSW5XSTFaZ2tpTG1RbG81blV4dHBpS0xDUGNnRzJoLVRZSzJnNDVJS2FINTYtcS1LVVhCSGN1VUdOb180ZTF1YmlaMjZwaXBDLWtJNkR6X1htNzUxOVVCckFkRWd1VnlCZzRnYU9wdEFPVlJUZ0pOalE1Tk42VWlqamNycUtzS2g3SWhLNGlXZWxxdllaaFpPQVJRTmNtMjlINXZHYVdvWkFjZjRXYjJvalRIZA?oc=5</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>46041.34229166667</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Barça: the least worrying defeat in history - Diari ARA</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 22:06:55 GMT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOYWZhNjNwVzRNbUI2X1Vya0Z4aV84QnR0dS1odUEtdUJicG16MUQzaGhiNC1CX3dSbXNHZVdCRmRDem4xRjBrYUlsTmhFWHlWb043OXY2ZWVUYkptalktTXJ6MlU1anVnSkJ6TFVPTWVkeHpGMExXdUVVNVRncHFYUUFYek0xTEdaRWMzUV8yYmlORG9PNEVEcS1PYzhsWm5vcVMtN2Uzb3ZpTTQ4Y3NDcWZaYl9KN1pKUnBlMEhfT2hIZ9IBxwFBVV95cUxONS1XWml4bk8ycXNtOXdOZnZLZFFkSHllUUR3YVJ4cDlfOG9ieFg3akFicExBeWNjc3BTTWFvdVdDRXoxMU15YXY5b0pMU1pra2pCUHViVU40TzZrSlo3NWxMdUwzanBuUE0zOEktVTBmSGpQXzA3S2VjMVJCR2YzY1J4c3hRVkJUaFdSaGRKdl9venRhbjRDdWh4eklHZUx1UDNaTUc5WklHUTlqekhrMGhuUEpEYWx3Zng2eEZEZDJlWERJOXFj?oc=5</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46040.92146990741</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Justice Dept. Confirms FBI Closed Minneapolis Shooting Investigation - filmogaz.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 06:47:34 GMT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiRkFVX3lxTE05Tmg2amRQZmFXZDVFbDg1Z00xM1Z4YkZLOWtvLTFzSmNwbzhMUmNTamJJakdfN25Vc2pKYk05M1g5ZGpscHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46041.28303240741</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2:1! Real Sociedad stopped Barcas winning streak VIDEO ᐉ Новини от Fakti.bg - Sport - fakti.bg</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 03:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOMGJDb25BTVJ1ZlV0SXFLQTN6ZTJLeHVuVXpCQlcya0NrUDhydUVCOGU3dUpZRWc3RGMxTERaLVk3Y3hhNmhJeXVjYmRIWjBjendVajQyNWVZd3puYWgxdW01Qmp4eUQ5UDVwcTM5SGJqVDBxTGN6cDVwTHNmYUJDQWhDRFVYSURqMGFtckhrYk5lM0lqSFdv?oc=5</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>46041.13125</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Endrick just made Real Madrid look a little better for firing Xabi Alonso - The Trivela Effect</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 01:05:26 GMT</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNaVRBeFdieVdyamctei1xNGJZcGhMenBNeFhqd3RaZjVGT3pwcUFUTXpsSE1vWVhLY0JCV1R0R3dYMTZBMlRBNTE4SUEwdkhFVGJDbVlZVUVRRU95V2t1RWIxSlNjeHB2ejJQdUp5WHpvNUc0bXZNVHBLSjUzODhjX3ppYmNJVkZVT1JoVy15dW5oeUFUNlBYcXBpVU1mSDhhNzU2WDJ3?oc=5</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>46041.04543981481</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Toni Kroos analyzed Real Madrid’s poor form and defended Xabi Alonso - El Futbolero US</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 18:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPX2dKT05Bc09Ma202SDJEUzJsUjEwOWNidzFFaHhOb1dEelFCRElVUXRhdHg4aTFycFF3ZENfOUp6d0ZiRW84UlhBUkRzZ1hrX09TLTZ6NDNESE03aVRnekppQ0xTV3BYUlhFaTlIdHR6dllhc3VtQzZvUHlCMkVfaEdTWUVuTE9yWmJ4ZjdsemtNTXhYSzRyMENWdkp1Z3ZIWlAwYTlld3JtczNLNE1haVhlWVNMNEYtWU1z?oc=5</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46040.77083333334</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Real Madrids Brahim Diaz In TEARS After Missing Crucial Penalty In Senegal vs Morocco AFCON Final Loss | - Free Press Journal</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 04:29:17 GMT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNeG9QWDVfMjRwRG9Ec1M4SUREa1MtZk1MSXJlTUtLeFB1dTBINHlobnFvVG1tZE5SMXMwRFBqclFSYVp0dkxUNGtmNEdORVhyNGVtenhXaElNSGpvTktLNzdUb01pbk9qa3lsSEN0eDlNeUtORlpqRmFPcnh4UmVuZ0t5bThHUWo2c1ZzdFprWk1GUmpHVmxoNGRsQ1JWdmY4RDdOR3lWbUdmRG9hMEZlbkN4VXE4OFVueXc4clNwSVUzOEJxV2ZsU0ZnRTVKSjBDTDZidWZaWEJqVlBjM2p5ctIB5gFBVV95cUxPcWNpZnBaNDVDdWh2UXhGOUhlUGVTV2FoS05qVkNRT1BWbFVGWXp3N1gxZXVTb1FleGxEQ1lzVW5CNHVmZGdxQzhiai1nUk90LW5wRjhuZlFPSlRDTVE3U2RzOXlnbVB3NUU0SlpDd21nTThKQURlQTBZdHQtMUs4clpFOTFoU2l3VkRrNnRsS0xmdUlhc0Etalhhc1VFXzlLOEFnZkIyQ09RRmx1aXd5WUVHRnZqc1Q1REFFb3RuVUVfUWtvZ1pvN2NaMjVYYWswelo5cHdfRUEwdDBKdEFxOVRac294UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46041.18700231481</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Real Madrid vs. Barcelona: Live Coverage of EuroLeague 2025/26 Today - El-Balad.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 01:32:15 GMT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiR0FVX3lxTE1GQmVSZ1MtbjU0NGZXaXlHS3hDNmloWFI3eWc5Z1lnYldaQVZtVUZWWFd0LXlxNkkxNk1wM0R5ZjIwSGpJQUNv?oc=5</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>46041.0640625</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, Spanish   language</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomba" OR "amenaza de bomba"  OR "explosión" OR "paquete sospechoso" OR "paquete desatendido" OR "explosivos" OR "explosiva" OR "tiroteo"  OR "puñalada")</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Descarrilan dos trenes de alta velocidad en Córdoba y se corta el tráfico entre Andalucía y Madrid - La Voz de Almería</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 19:59:04 GMT</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxOaC1Ya2VBc19GV2R2R1ZPR1hIMkFPU0ljdGdKSXZHaDBnV2ktVlJYLXBDS0U4Z04zdzJpcFIwVEpZRHprT3N3SzVCZGs2Snd2Y2QzZ2JrZXZ3UnpkUlpZbGNkN1NDQ2duNG11LXZTbnZuZkNQVWY5cmtfck5ieVdmZ0dhc1loWEYzX3pyZDF2Wk1DR2J4TlRPUXVUa0RNU28xX0JVRkRuQjkzZGt4bnZ6VU1MeU1BcG9LazVkZC1DQlZmT3Zvc0hZdE1ibUI4WEo1WlRLdnBpRk8wVVZZSElCMzRtdFhUT2FCVDZRNQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46040.83268518518</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>The London Underground station where a World War II crush killed 173 - it was kept quiet for years - MyLondon</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 05:37:43 GMT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPbTlzeHVtaVRLSEJmSm5fbDJLdXZIc3RCcVIxVjF4YkljTHZ1WG12NjhINmstc2oyTWduZXJmazloUFYxSjV4eWdNWE5mVmR4cWVmenh2Q192NklVVEFqVmFtaTlLNHJvVXpkaGJYaTRpa3VxWU9yUUFGdjdGVU80QS15MjhRNk5YVVJzLXJPY9IBlAFBVV95cUxNcVpaclFnd2MzY1pmLXhBRFNHWlM1UC1nTzNxcEppd2RBa09lNEVUc05yNU5HLVFBUVlFcjlidUR6UWJaTWRKM1FNdkJYRzVpR0ZWazVQb2RJMnQzLV9fV0FlNUpIdU1CNnV0VThRNXFlLWplNm5vRTFRUFdrQTFFeG95TWdKdW1aeFRldlFxQjVYRXJG?oc=5</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>46041.23452546296</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Brian Brobbey Is Sunderland’s Explosive Spearhead! - Roker Report</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 06:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPUjJhUDY1ODIwUFZQbXlHZzhrMV9veFZKZ0R0U1p0bk5kaHUxbDEzV3ByTmZOUE1RWE1xV0ZSQm9DQ2E1azRBMnJSUWFtV1RMRkhfU1ZHRnFLS3RrbzRZaWlSSUVaWEJaYTRKTUJ1OUljNlgwa0dtZVVGZnZuUElvUEZpQzdwbGd3a3BBYkdJbFgzZ2N4ZzlFd0NwbzE?oc=5</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>46041.25</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>No arrests made after stabbing near Tooting McDonald’s leaves man in hospital - london-now.co.uk</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 14:37:24 GMT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOSUdBcXpLRG1ST1JFWDcycVAwaTVENDRkSkdXOG45RG1nNkJsS2x0YXk1aE5BS09HUjdYbUNkQnBLUVVUbEhxcVR0eE52MGpaRktRZGtJOEtuY2s0dW96bGNXRTlZanhyUkRpWFpXZEZaN0NOVVJIS0szczk2Rkw3aVZUQXFveGgwYVhEdnZlX1dncl9nYmc?oc=5</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46040.60930555555</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>North Dublin road artery reopened after removal of suspicious device - The Irish Times</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 17:37:30 GMT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOWlk2TzFEVUEyM1ZlblhyRHZnbjA1TGJiei04WFVNYVpHc2hZQXpMZ0JlZ183azFDei1QWFRlQjJmc0tGalRrUEVaZDhHbWtHcXlhR3BQeXRnaXkzZnIwOXQ1REdtd0FHaVJuaFUza0dIbFdwUkVtNFhMeXdUbWlZbmNiR2h3Q21uWU5BZUwtZldIWFVVNDJBTzdnTENRNXhtYWRGVkoyTEt6ZE9fS25rcG9B?oc=5</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46040.734375</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies vs Orlando Magic in London, Ja Morant returns from injury see top photos - The Commercial Appeal</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 02:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQNGo5Q1FEZjF4dmUyZ0lTck5zNktwX1lqM0JLQlowaVZZWDAxQWxYdGtqOHktaGxraWVrRDBPbVJjT0VkQXdOeFUxM2VaSF9LbHZ3N2hmb05GQWtabDZiTGhmS2lPNzlaTGJhWEZGOVowaFJGYXN2bDhJNVFpZ1NlMmpzS3EtU190UHl2OEtwQ1ZjVnFRb1hpY1p0NzdVYzAzUUtlNk1NQzllTjFUcmh4cWdVV3FMTFZweWtrckJqQzJoaGRZZHNQZk5mMmxEVUdkLWdJaDFzTDBnMGpDdm5MMU9RWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46041.12430555555</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>- Everything Horse Magazine</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 01:31:35 GMT</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQOVlaVnpmZU95bWhZTDQxWHNPWVM0V0l3bS1McjFick9ZN29JNGFBUTNLdlRVV1RCclR3dHlXM0VQcUVxaDhVU1lkb1g5SWttdE1EZWgtRjQtWFZGeENPcVF0ckQ4NlUxaXc4TUxXdHpuVGpmSmJCYnF0bkduWTBQQUIyOVhoclQxdjg0OFRGcmtiUXV2SGhsQlBFc3lHVkYwX1BRSXZYbjhvakc5RWJhc3BiWkxucE0?oc=5</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46041.06359953704</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Sunday Best: Saw so much love for Ja Morant ... - The Stein Line</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 01:20:08 GMT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1Pd0tkRkVOR0t4YlV2N1NaUDFySnphdDVZYTlpSTNzZG5XUkhhOGJCQmxrLS1LWWp6RkxIZGRDTUVNYnU5NndaMlRNWGlGZFF1Q2Q0a0piMEdEVDhVVlJ2R0R2SVI2aXNWYTBWZERQd0trS3M?oc=5</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>46041.05564814815</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Heckler yells 'leave Greenland alone!' during US national anthem at NBA game in London - ClickOnDetroit | WDIV Local 4</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 18:25:12 GMT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQSy1qaUU4QzR2TFp4akJJdXRuRlV0eE51eTdaaWZHV3JkX1VfZVJMSlZqeUhxQmU1cVRKU08yVUg0UkVBSi1GOUZacGI5MXZuYnlrVnNxVzk2eFpLNHQ1cmN6MDJfU3hRVFpaODVFQzdMTEdIbWEwcHV6SnI0M1hWV3NpRjBpRDQwSVhBN3ZFX1h6NVhVWG56ektVVDhiaklZUVh1dWg1UEZGVzhwMzRuSWVtMzdJdzhsYWlvX1JkdjFGRWZPUHFYdmtzT0M2QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>46040.7675</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Factory explosion in China’s Inner Mongolia region kills 2 and hospitalizes 84 - breitbart.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 04:01:16 GMT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPYmNyM2l0ZGx4d09HSXlSQ1Q3QkxuaW1UUHpmeW1nVy04ek8wUUlWd291VnRCNHFQT29qcU9zbEd1THZoVmdoUFRNUEhDbGNvd2YtLW9pRHdudWc2Vkc0VlRMSDZCZWtCUUdncGxjMzh5Nl9vX3Fud3FscXN4QW15V3U3QlpUdFROaTVpeXQzbEF0MERvckNnYUgzNjJTUlBZMW1tVDBNcDhxOWg5aWFmR3R5UdIBswFBVV95cUxPYmNyM2l0ZGx4d09HSXlSQ1Q3QkxuaW1UUHpmeW1nVy04ek8wUUlWd291VnRCNHFQT29qcU9zbEd1THZoVmdoUFRNUEhDbGNvd2YtLW9pRHdudWc2Vkc0VlRMSDZCZWtCUUdncGxjMzh5Nl9vX3Fud3FscXN4QW15V3U3QlpUdFROaTVpeXQzbEF0MERvckNnYUgzNjJTUlBZMW1tVDBNcDhxOWg5aWFmR3R5UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>46041.1675462963</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Imperial Paris faces Le Mans - Paris Basketball</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 20:24:27 GMT</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5vMTdoOEEyWTBzMDE0LXlxRnBCaWJHT29xd05XdXZLRnl2ckY3MmFqZ0Z1YnNraXJFNHp6TTAzTlhKeWMwRUtxTzZQTFR5ZHFOR09ocm9ERTNSNlRqZDR3Y2hBOXdhcHdBN1ZtbHRKeFhiVzQtRWtB?oc=5</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>46040.8503125</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Paris bans fan gatherings on Champs-Élysées ahead of AFCON final - MSN</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 00:50:24 GMT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxPckw0NjQzU1J1UkNHaEt4LUItS3RsZGwtcUNkaDB6WVR5bEdDbUU5SGZST0Eyd2lfcGJyUWZMU3JzQmtEYjRobWdpdFFEbG45dW1QeFo4bDUxV2JBQ0NoM2ZCb3dsWUNvc210ekpDWUFKdFREcWp3REtEZ2JDN2tTZkNrS2ZxZWhlZmRaNGpvcWpjSVA4SWFUM0VtOG5nWmQ2TzJkZVV0bGw3QnJPWkQ3TkRYbzBuOU5abWt2V25OdU9GX1R5aDV1UEVoaHdtZTRYeFY0Q3J6bWl1MEZsWHlkcEhINklIV3ZwSnUzOERNY1hkX0lJYzUyLXVCcEx6QlpOXzluYXZJeU9LbXV5MnNMVFVPdEhoSzBxdkpCWWxtT2pfdmhxMnFzdnZDX0ZKby1DcEVTbWRsQlRLTkgxdEk5UU1TQnJDMnB6UG9reUY2MEd5SGt6V1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>46041.035</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Scripps Howard Foundation gives to Paris Gibson Square - KRTV</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 05:26:14 GMT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPTkczaXJpZS0zSXRuQ0ktNlRqNDg1XzRmU25UQndlNTFsVWE3cDF0SHpvTjIxTWVCZG4wVVlRdGNseTFvdTZaT1NlOTBTbENRa2VZZEFCWEpreW03LXlkY3pERjJGSVRXMDctV2djMnRmbndTMjVSYkpJQ2VlNDZodkswZ1NITm1tWXZ3OVN6d3BjSWdxME51R09idWowcms5?oc=5</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46041.22655092592</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ISSF’s new rifle clothing rule a test for shooters | Hindustan Times - Hindustan Times</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 17:29:51 GMT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNd0phOG9tTGwteS1VTnIwNUF3MWYyQU5VT3Fsc2R6Vy1fT3NOeVNWVWVSNVBFenAyb0ZtcXBGVHQybU1WaXpjd19uamMtSm5GM3ZLZHlaQjdhRlNBOEZCbmFNU0VYeWRsUFdPdDNOX2tDenU2cEhKNFljSFZTbDZibzdzNHlBRS1yQjNwelA3aWk3TUlNUFhfNXIxRFVMYm9wNFhjUDZfZXBveFdnLW93UFNremNiSTV0YjNr0gG7AUFVX3lxTE13SmE4b21MbC15LVVOcjA1QXcxZjJBTlVPcWxzZHpXLV9Pc055U1ZVZVI1UEV6cDJvRm1xcEZUdDJtTVZpemN3X25qYy1KbkYzdktkeVpCN2FGU0E4RkJuYU1TRVh5ZGxQV090M05fa0N6dTZwSEo0WWNIVlNsNmJvN3M0eUFFLXJCM3B6UDdpaTdNSU1QWF81cjFEVUxib3A0WGNQNl9lcG94V2ctb3dQU2t6Y2JJNXRiM2s?oc=5</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46040.7290625</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Durant climbs to 6th on NBA career scoring list in Rockets' 119-110 win over Pelicans - theScore.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 05:22:04 GMT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE9RTGVuOEgwZTh1bmJCc3g1TFlmbUdZNTFaempmV1BwYmV4ci1MdDkxc09CaUxWSzRkeGNraUJOSjJ0Q3gtSzZmTXBSTXhmRFVuUnU4?oc=5</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46041.2236574074</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>‘He hoped Trump’s help would arrive’: why protesters in Iran feel betrayed - The Guardian</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 02:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNcm81VGZRZi02S0dJVzBldThkcTFvM2tXWmVBaUJrSDB4NFNBc0hhSlkxLUY4VGN0c2ZlNWt5QkNnXzd2OWNzcHZZQTFLSmRzMVIwaDB6Mk1UYnNvczZzZ1prVVVqdkxla3FaY3UxWUNKMlR5QkVFTzNodHVERnlUWlZDUmYzRFkwalVjd0VxbUtVWGVYczF3?oc=5</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>46041.10416666666</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Fullkrug scores as AC Milan edge Lecce to keep heat on rivals Inter Milan - TribalFootball</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 22:22:47 GMT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxQSXN2dTl5OFNsN2VJUE1sd1RZVmUwN01JRU1xQ3dsakZWaGJNZVYxOTZ6UnZhT1BqN3VxRXB1WHczVjBDRmQwcGZocnd6anVaWHdHNHVLcksyaUU3NzlOSUc0MDdKSGFLcjhjMHNSZzJHeS0yWWpweWhuOGJraXZDTUEzUGJLdkpSU1p6dVhnSGhMQkd1cjZHQXNMcm5xQ214aWVXaDNXaUs0Xy1ObTQ4MC15ejZnN2wzY05fV0VtbDhSUU9uUmxRYjZxU3Z5VDVtbC03WDR1R21uWEFkTFFDNEYycWpKRldRVjI1cnZ3QmxEUmhaZ3hZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46040.93248842593</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Frank's Tottenham future is in the balance, Palace left blindsided by Glasner - talkSPORT</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 19:53:50 GMT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNNXZfMEpnUTZjYTNxa0c5MVJwSnN4Y0RhNFU4Q1d4NlUxWXE5YThhSjNza2xtd25oYndFWkRzTlZELUxvV2NTLXNYa1lNUHV2ZFRNOTB0bGJGYlNJd250Z2dLaHFCMWhmWlNEWEtqbjZ2RE1aRzNnc082YnRSZEVURnlGZ1N5NXl5SFhvVzRVNE41MHFJVndaeW9jRmNwa0otU2JNdGJkYXlkX1p4NjZibGg3Tmo4U29HOE5Za29ocGc?oc=5</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46040.82905092592</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Dream debut for Donyell Malen with Roma. Füllkrug ends goal drought in Milan victory - WSLS</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 16:16:52 GMT</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOaGhOTFdsY0hqOFN5TXRhOERyLXlQaDY2YjRWMmNZX0MyR1ItV3BwV0hRdDhJY2JYWGhqUUtETG5OeGc0OFBDNzBBSUN1bzIza3pFVUozeW1oN0VRaEtLOF9hSlRhR1Jpc05NWXFCdG92azlmSk5hZkZHejk5cDlRSG8tci1CaEdPYkdDTndSQ1FWTzBaODlwdklzNWJULWJhTFFjMEhrMW1HTm5OS3hiOEZVdWo2NHpvTXgyaWVVbHE?oc=5</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>46040.67837962963</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Raphael Onyedika: Two Milan giants blocking Super Eagles star's reunion with Osimhen - Pulse Sports Nigeria</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 18:23:10 GMT</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNbFNFWDJqLXB1Z2pCZWp2S2NrMklaVVpyQ3B4R0pMYVZDZm1fc1RjQk5tMUxrX1NCUklSMlNkWkpXMU9rY2c2c3gwZXlKeHdXVkVEVXBVSnpHRkNGNnFoRXpXUHNGRTU1MFRSN2ItQmhXTEs4RkxYWFY3ZzJucC1BRGxuNkNhc3pxMTZUYXBhYVZ1OE9FSklDMWFaWFA5TzZEZDd5blJ4eFU3VXdmVmxxNW9JMHdoMGpNLXNia2pXUGdJUk5lMVJJakI4LUpSYjM5YUZlYUtIdmYtV2lnSHJGVzhn?oc=5</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46040.76608796296</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>PETERSON: Iowa State’s Milan Momcilovic, one of the nation’s best, can’t always go solo - Cyclone Fanatic</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 16:00:34 GMT</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOS2V6NENLaUJ3N0hKUWdncXhER3EzOWZGTGt3aC1ISVJtakoxOS02eElmTXc1a2trMUpCc1lHS2kwSXJxUW93ZTFmNmFhRTY3dm4xQjVBY1FQcmZmUWd3ZExteVJNMjZkOS0zN2d6UUc2eGJlcnEtX09nS1lyb2pianpTTW9HY2IxRndQSG45Q2cxQjVuTjBlNlU2WUVPX2NQd085d2g1ei1CVFVISGRyNUdhZGpyQ19X?oc=5</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>46040.66706018519</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Farmers end three-day blockade at Brussels Airport, cargo flows resume - VisaHQ</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 00:31:35 GMT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNdHZVa3VsV2VwLW5pMW11OUVYU2x3dGdUSTEyMDZSZUVvWUpTSzZVQTIwX2drSlRoN3p1WmRpbFdSYkV0eFVGZHFKWktUNTB2bWtDVlg0eFdEVHVwbHJoRHJrVXNybHFFb0hHRUF5R1JYLWhXOVVxbUlKclNOVGNYeklPeFQ2NGN2QW5FQkNnWTI3Um9IOUFCRmNCYUU2V2lacVRjNnN6anRvV0RoNzVLTkV3?oc=5</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>46041.02193287037</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>i-Police and the Politics of Promise - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 05:41:15 GMT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBDUm1xZmpobW1nSFVvdUpnc1pGSGh3REYxTHJPU1BiWGhwTHpwX21YeDFyMmVFc21jX1pfc2djWGgxOG9lTU1yMEwtZzRJQUgzVC1Cdld2SFQ2dFpvY3RXeTJkdkV2eUFyZk81WnBDNVI0QkMzdUlTM096aVBKU1U?oc=5</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>46041.23697916666</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>European Officials Lean Toward Negotiating, Not Retaliating, Over Trump Threat - The New York Times</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 03:39:23 GMT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE5xU1E3UE5NWVpma09xVWdsOXNlVENJekItRERPcHgyX1pQcVQ4UGJGZGZrRnE2Tnp0eW44NW9MVmZYZ01iT1hVbkZRc3lFZGw2V3JkSWtFWjVRU1NIbzZUcERHRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>46041.15234953703</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>EU scrambles to avert Trump Greenland tariffs, prepares retaliation - Reuters</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 22:41:17 GMT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNN1hqZWJXT2phWjBpZFdrNmJvME1Ra29WMUMzQk9NOV8yVElSOVl5bTFvT09qNVJVYlNyX3JaMzlNZXFkQm9IeVNGYU9YMGRSd0E4TnhXUGFTTF9Tc2EwcFc1UElZWV9IWXdqNHBzNVpSMmY4WmxWaDJTOTRYSWMzRFFiUTFRcEtrTDBWVXVyQ2lDRXJscDVPMWszek9ISUxVOGJIbDl3RWluTWJ5d0c2QmUzTFBzVEVBSkhrVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>46040.94533564815</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Belgium lifts 2026 salary bar for Work Permit B and EU Blue Card - VisaHQ</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 23:32:48 GMT</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNcTh5dGhrWWQ4N1NXcXFaakdTMTRlc0JqRGtzNERseGpXaUtrdk9oMVI0dzJXMFRGSWNDbGxveUNRWFZJZ0xERU5uSWNKZnZwd3VLWUhqSTZwcVF2aXdxQlZjb0F2STNCbWIwN0tEczNFT0RUY1lPWGxiUHR5RFFzS1dEME11Vm1USXRFeDREVG9YOEF5dXR4Q3lvbTI2QjBFTGQ4dUwyY2NKRDA?oc=5</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>46040.98111111111</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>The Brussels barrister who refuses to defend sex offenders - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 05:41:14 GMT</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPTDlmS3hYcHkwZUdPejRqZm12cW9PeFN4VmtSOXdOWEs1REozTlNtWEF3Z3VQUks4TFlfek4yZWFvenp4cUxqT0dGX0FoRjk4aW1hQmdveVdmanZkWjlHTVRmZU1ZRDBvbVBOOUJ4Z0Q5VVJTZ0xrZkkxM1pqdXNHXy1yTlRtaW5KcEt0MnZMeUJwOE4tRzl1Y0dMRnZhSlVTLVI0SVRPYmZGNmRkMGlERQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>46041.23696759259</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Tariff row rattles EU, Iran protest death toll soars, Portugal faces tight presidential race - Daily Friend</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 04:14:29 GMT</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOQ3VTUFdtTzNVdERQQXo1R2EzRXNKM3JlaThVQUNBc1JjeFFmVzFjZjR2MFVsSGlXX2dEUTNqUlZHb3JNaHYtaG5rQ0ZPSzEyd1VzNGFCeW02N3o5WUpTOHpaTlFaelBmczZsNGRtZTNZRmlMdkI0MEU0MjEzT0lnZERmUjl5OHhGTjJQSFZfeGZIZjRDYzZtY0RtbnJXd0JLcHFfOXVGQlBTSGx4WldPTmVySFhtaDQ1SlpaeG5laHd1YmI2cExR?oc=5</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>46041.17672453704</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Pair of creeps who raped and sexually abused vulnerable minor migrants extradited to Belgium - MyLondon</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 16:09:34 GMT</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQcHZEZnBncFRYN0lCMUlaaC1kNzl4ZUI3WE5DVXpoSGllUHlQZ012MjNlNVJNTzJtalE0a2lXM2RlUWtoX0VlV0lyNWJKUVdYM3FsOWJUU2V5XzlWM0Y1TGlEYVJZYTViQzNVSEVQVHNGbVRtdjgwLTd0eDJTMG1BMklrV1BDUno4ZldUedIBkgFBVV95cUxNR3hYNEVEZ284Z0NBRXJual9SNjMxZUVOSm5vQ1c2dVNKay11d25rU3JUaFBrOWpYTklCbmRZMmsxVk1NcjFtb1dXV1FKSUdNUEpRZ1UzdDdXcE53Q2ZzNTBrV3Y4b1prS2VWcXFtVHVoOEZkX25GdVVYOFBfeU1XZC1sdDBBQmxMUy1OUnd5SXlDdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>46040.67331018519</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Hundreds of thousands left without power in Russian occupied southern Ukraine as energy war intensifies - Firstpost</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 15:02:49 GMT</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPdDFWTUdtcnV3eW9OdDdzNjBpUVZiVzZORC1CaElWSldhNThBYmphT1c0MGRFT3N4ckhCYkpSRHVlaVhtQ3lvSlJBT1Job0Z6OUJyMXowTkRQWTMtQ0VYdFVIdFRsWWc4ZFN1WDZmYmtza1l6RDdqSTUzNndtQlFaajZmRnpQd2ZfUTVfMTIxLW50VThFZFBTWUYxdUJraGZqNXZHbTQzVl9Jek0tOXFXVmpfYjl3VmlvQ0EtWmR4UFlMUUtsREFEMnJhN3VHc3AxQ0NpRVJEdjRudDdPUUJqLXA4c9IB6AFBVV95cUxNMVJHUHAyOFg2LVRueTE4dE1ibjNhWTdlbTRWb0taQTZiTHJJbXRLZFF1a29yVjRQWndqNDhkX0JRenNpNXFJZWpBSVl3NlNyX1o2a1BibmZlYS0waGFDZzdqa2U0LS1qUVFWQnFCbE01XzRVbnhJRmJpOUtBNE1EbTNZdWRZSmZJUTdQTEZGY0NjdWpfWFlNMHpyMHpCYlVPc3c3YTVZZDlaQTZVbDdfRkc1eVpRTWljc3g1WC1lOHJNbHNGcFE3VTVFekp6Sm5idlc0QzA3M0liSm9abVh0VVR0Qm1tMkw3?oc=5</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>46040.62695601852</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Agriculture Minister wants EU trade deal axed - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 23:53:33 GMT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNWVMyTThuamNhd3RBQU10ZWNKZVc5VmFmeEtidWd0U2FEM1VWZlFUSXY1YjJ6Q3pDaEVKMkpDSVRWQzVhVWFEa2RMcGJFUXRnMnlQQmtWNDZ3VUgxb1pHbFR1VnhNcDBpTF9nVnF6TDF1bUQzeUdOYmxxLWtIWkpneUliREZMY3VaUGJn?oc=5</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>46040.99552083333</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Molenbeek prepares for Africa Cup final - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 20:38:43 GMT</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPdVpTWjZyTkRNUlJwcFdhbHFwY1libFAybDNsRloyLWpsZFZFa0w2cFdoX3NBdzNUYlpnQ2FTNXlscHFrN1Q4QjhuRUpHTGlYWC1GU0ZIWkdxYnNCbE8yQ0lSMk10clB5T2dBZDlWT1FkSmY3MU9sOEp4emhGSEVDaF9GYw?oc=5</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>46040.86021990741</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Laois IFA President to join Mercosur protest in Strasbourg next week - Laois Today</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 16:00:56 GMT</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPVnI2NllpSVdiSDZvaGgxYVJXMGZpUGRjYjJNWmlaQ2FVQjFjNVhCRWh2YjFtcmNEdTFMeFRwNE01VUhuNnRYeUEwalJjWmhQRTZXVW1kWHlFdlZwUFFiYVlXcmk2MnZ1TGlPbl9sUmtyVHZZd1AzZlhvUFRlMjJ5dFVEdm51S3R2SERqeDFKUlNXZnpKbFhSd3I0c0VscUVYX3lRSy0zdzBnT0p4c2lJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>46040.66731481482</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Trump invites India to join proposed ‘Board of Peace’ to oversee post-war Gaza: Report - Firstpost</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 16:18:41 GMT</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOczJZMi1FUzF3UTZrV0k0UUpfeGc0RTBjYWVIYVJJYmpuU01qTmpIYTdXMHVtSnpva2JxclpGQUlUNUhzX0phZF92NHZ1VTdOVTZZcjNNQzBIZm1zZzlVa2w1RFl3T2hmTzZvS0ZxajJ3VUNyUUxUMFAza3dOdUpIREhPZk9fMjJaYnJNTlFwMWdzb2RJci1VNm1kb0Z2a09xQ1QxekNpNzJ4MGtiZFhSTk5KVW16UGhvTkYwMGVhYmtncFR3VV82cER0cmxhRzdlYTkxXzZfRlo0LUxuYXBqb3lxWdIB6AFBVV95cUxPN1AyU3hLM1NqbVhKZjM4TGp2SUVQUktJQUhiNklUNFhHdm1NZTFpR01QSDNqbko3bl83QUpINTNVNmNTR2ZXZjlsZzFETjlMWWJSSEZxcUhHV0VJSDNGcGZHMTZBSnJXLXdpNjl3VG81Y1RqQlRESjNRYWI1c3JRZlREOGUycWxNUHN2M2w5bDVWVVhjUlFXMnJVemhlZWsyaFQ3M1BCMGdORDNxNmRSVV9ocUNlTjYwdkZPb3RJVGdPUG1SaFFsVUR3WHFyNDF0ZXNqQVV1SVJkZVhzcXd6dXRWZGxpVmda?oc=5</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>46040.6796412037</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Cyprus deploys 2,300 Schengen-connected tablets to cut passport-control time to 30 seconds - VisaHQ</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 23:32:47 GMT</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPenFwMklmLXJvWl9TTmNUb05jNjNZSl9vTUZHNVZhRUpEa0VCNHZPQ2FBTkY0MTAyMEFzZFZ4Y1A4U2thRFdyeGUtbWJ3OEl2SjJyV1lrM0dKTWR2MmoyYXZvNTNJeEI2eEdsM3NPb3dNQ25mWlRTa2pEQjNJaHQ2aW13d3kwU0F4TExsOGlleHIyYVNFMUppTWpDdG44THpRblR2MjdGRWdaT3ZucXJFZGRjMW40ZTR1VVFET0M0SE0zenl3b0dCbEZzQTU?oc=5</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>46040.98109953704</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>From European countries to Trump PROTEST - Modern.az</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 15:21:45 GMT</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQVUJrWmhWMzJQSG9YeE9QNEdia0htanNQM1BWVTRVUUxVUG1JU2FkUlZadFY0eTNfR1VlRWc0dDlWR1RSV013UVgxQmo0UHpyRXhIMWhHNmlfeWtIbEhGMVpkVG9Mb0drcmJsV1pHT3VFZGl3Tzcwc3p3VTVIWTRKeA?oc=5</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>46040.64010416667</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>Ireland / Kildare Protest Groups - Social Media</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Edinburgh woman rushed to hospital and 'police vehicle struck' after terrifying M9 fire - Yahoo News UK</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Sun, 18 Jan 2026 14:03:09 GMT</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQREpQdXJQSV9IUy10Y0VUcVdNeUlpQjVUaXZuQnJfclgtRm9NUW52NGhLUEU4NzJRRFg0YU5IODBuaEV5cVdXOWF4LTZaQjlyQ3lKRERRWmItQVE0S1JUb0F6UVpDUXBhZnZEa2N2Ulpwdk5rSzJpTkQ2OGwzQS1tYlV1QkVVdw?oc=5</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>46040.58552083333</v>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>New inquiry to investigate ‘pimping websites’ in Northern Ireland - kildare-nationalist.ie</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 07:03:10 GMT</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNclpyUHdNaE5SR0tsV3RUR0pnNjVHNlRHOWVaTFVKSl9za0lyeE1KUVhRaFZSQTlHRUhBbzUyM05PclRZa2s2QnNHY2ZkRjBPWWNiajZtTUZvNzJwRjJLaXFVUnJFWV9ac0U3eFNJbTZhSldjb1hwT29wSGt0LW5PS1dwSGI1SUxoZVdhM0NlbFdzcnQ1WnNJd3ZIeWF4VFdHVGhJVm45N3NySkI5QklsTVE4RGVvNDdsSkJB?oc=5</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>46041.29386574074</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Woman in hospital after crash and car fire on motorway - STV News</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 15:21:34 GMT</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPcWYtWldQMmZWUU1melpOTkd1RXp0d2dfZVZ1cWNiTWlCdkF3Y3pNUUFJQlpDS0pvc0l4SmZ3WHhJSm9McF9vUTFCV3B4Uk1QOVd4Umg1TldJUUtEQm9jc21HRXRJNHZKclBjU3RGQ1JZMllpOEIwZmNDQlBvNFVKRlZIUy1nc3VBendLUUd3TVp1RmFGVWZ4TVZ3?oc=5</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>46040.63997685185</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,27 +487,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Value Retail</t>
+          <t>London Marylebone</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>"Value Retail" OR "Bicester Collection"</t>
+          <t>("London Marylebone" OR "Marylebone station") AND (incident OR disruption OR delay OR closure OR police OR protest OR bomb OR explosion OR stabbing OR shooting OR "suspicious package")</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B&amp;M shopper says 'stunning' new £4 'Japandi' decor 'looks expensive' - Liverpool Echo</t>
+          <t>Major delays and cancellations on rail routes serving King’s Cross - live updates - London Evening Standard</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 11:58:00 GMT</t>
+          <t>Mon, 19 Jan 2026 15:57:59 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNdDJmZUV2Mk4wZTZzLUZRRE9oaTllRE0teU44QjFpZUs4Z1RQM015SlF1T0JJdGIwSktEMGU5SmNZRDZGQTZlb3FWd2ExbEFGdnVhQngyZF93TGdsZGJYMXctUk1jT3d6YzF3eTlrRzFLUTJrMF80dHFsY2dCamxYQ1dVUUIzSUlTM3pJNUFjUFTSAZYBQVVfeXFMT1cwcXYwZEtuX2VIclRkM2pCdU5ka3Frb25sOENLQ2llWnMzWGhUd2FZcXhBX0dMYTQxU0JKSmEydzk4VW1BMEVPWW9qbUl2WTJ6QzFOM1NkNXUweFpwSXlRcmtjODctX3NDNzVxN0VuV2pIS3VaMjhVOUYzRk13ZzU2WHRkZ2RhZVZVcXFuYTNWT3hqdmJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOX0U3emtnMHpKanU2QVJMUEhSYmtvY3B1ckFldzhTdkRrOExxZV8zZEJoN0NkOEU0RXFHb3p0U1ItVHFJRlM3WVNNbHpHY3dIQVRMdmNEeS1ieXZIdzEzQjRVLXY0V3VHOXlHZUhKOTFaRXNIT1N4NmxkZjFTOXhhQmxxaEpybzYxOTFSQzRIejNYazNMRzlMVkt5QmgyM3E0b2JxU3AzczJpRDVvdmVXWWxoM1JvcnpO?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -529,33 +529,33 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>46041.49861111111</v>
+        <v>46041.6652662037</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>London Marylebone</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>("London Marylebone" OR "Marylebone station") AND (incident OR disruption OR delay OR closure OR police OR protest OR bomb OR explosion OR stabbing OR shooting OR "suspicious package")</t>
+          <t>("DHL" OR "UPS" OR "DPD" OR "FedEx" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI") AND (delivery OR supply OR logistics)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Major delays and cancellations on rail routes serving King’s Cross - live updates - London Evening Standard</t>
+          <t>Amazon Launches 30-Minute Delivery Service in London - About Amazon UK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 09:33:58 GMT</t>
+          <t>Tue, 20 Jan 2026 08:20:38 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPZHIyN3RoZERTakNSRTVScVNJd2JkaHZzazZvZHlOalpyRXFibVJMMkF5dld0SmNkajNBSGdhN01NWmFjYl8tSjNESEJvdVZhLUZjR0NCYmdJSk4zX2RWalJYRDVFRjZMWlhidHNYVC1laHZYRGgtVy1PdE85QjlrMTEtZm9JTUhsY1lSOC1oT0NuRDV0Z0JFM2F1bWpIZkJBdkVxWHROM2ZzRE9CZWJPdmdXSEJYUlpR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTFBEeGp0NWlhMUZUNWxMR1lSYnUwMDZ3WW80a2tCZndWeENsTGR3TlUybFBCRThWZEVhZDF6eHVrWWs5eW5FaEtDTFJUaFNoYmZOZmRzZWJPcVNQZDNaSkZnVG5B?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -577,33 +577,33 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46041.39858796296</v>
+        <v>46042.34766203703</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>London Marylebone</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>("London Marylebone" OR "Marylebone station") AND (incident OR disruption OR delay OR closure OR police OR protest OR bomb OR explosion OR stabbing OR shooting OR "suspicious package")</t>
+          <t>("DHL" OR "UPS" OR "DPD" OR "FedEx" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI") AND (delivery OR supply OR logistics)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Anti-genocide art exhibition closes early after ‘right-wing’ vandal attack - thecanary.co</t>
+          <t>Rio Tinto and Amazon Web Services (AWS) Join Forces to Supply Low-Carbon Copper for U.S. Data Centers - CarbonCredits.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 10:43:46 GMT</t>
+          <t>Mon, 19 Jan 2026 18:56:15 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9Za01XbzFBcXNkdGhIWFg0RE9HSDBhVE5uNzdyZ1B4NVRReW50QmpFam14em9uRmRWUE1Cbm82OUtVTmw1eFhUWWZyMndVWjVLaGdZV1dBeE1iTWhUeUhxWkpMbFlEeU02VzNQR2g5bWtiZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQcTdZSy1JbDRzcEJzbE8yb1VHU3M2VTJoSTZuYWJ6alRnMW56WFJVTGdtaUUxR0FGQVk1YmdyRE0yWXhzc0ZEYmVURGthN3lRY1BMYmRHU0g0b24ybDhkZndRcExHQXNuTXVRUmVDUWQtV3dZeTcxbzc2OWJfWUY0dC03S1RvMTZYOFhjWWFJc1FsUlJWWkZkVnpqeGJLSmVnUkZmeF85UjlZdGNJZzYwODF3X1FldDVaR0dCNmdoSDVlUlU?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46041.44706018519</v>
+        <v>46041.7890625</v>
       </c>
     </row>
     <row r="5">
@@ -641,17 +641,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turn Shipping Challenges Into Customer Confidence - DHL</t>
+          <t>Amazon driver leaves customer in hysterics with proof of delivery photo - Edinburgh Live</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 10:36:22 GMT</t>
+          <t>Mon, 19 Jan 2026 15:28:00 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOc0JsZF9FSUYwZUVDNGFMLXJzMVFwWW50el9MVkdCODcwR0xldnhIVGk2VFltX1hnbURYQ09vNHRJd2J2Z01tb3I4UmdfZXlpS3hIMXJ0eTY3N0taWlVpTWhZQWJJd2h6TzlnWVg5VHMyX1NaOWRTTjNjUGJUcjZhSmU4dDV1SW93MGsycGFYQ1pNRTJxREUxLWw2cUlPRjVRLUxYUWljSmt2UEVsMjVhbHc0VklxRlBkeFJreg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNblNublNXancyRXpaLXBnUE5COG9wclp1MkJXMWgzUHBCd2pYMUdna1M3M1htc3dDZDJKa2trbm1INTFZN0RpSzJ1MjJ4dnQ5VjBvY1AwSkFCZEJSR2ZQSFpKOEFQS1dCVmdCRWo0cGpfZXBEb2pMWDFudG1BemhYaXRZanFlaklnSm5lSUJpQmVsb3hfTC1idjdQMNIBoAFBVV95cUxQMmpkZkpLMGNWN1FucG9ZZF9seHFWUktFMWtMMzZLcDJFNUQtNjFQZHVKa0NtUnU3MTAxM0xZOVZ4X09YeFFxZmpsbTNwOHdpMzE5c09GaHJJM2lTdldPLVlOeWczaDVfeExiVWdCSVNvR0RCNWRxNUlZeHVfRXZxQzRnMmRDYVpaTE10LWltR0ktNDNkSmFzbTF4Y1I2YmRD?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>46041.4419212963</v>
+        <v>46041.64444444444</v>
       </c>
     </row>
     <row r="6">
@@ -689,17 +689,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How Can DHL Help Waitrose Build Sustainable Supply Chains? - Sustainability Magazine</t>
+          <t>Evri delivery jobs: Parcel firm to recruit 2,500 UK workers amid expansion and BBC Panorama scrutiny - MSN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 09:31:31 GMT</t>
+          <t>Tue, 20 Jan 2026 01:01:22 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQdi1EaEkya1otMVZoOElmak5kdjdrWno5R3VuY0hzRi1ldVZOV3FBVWxsYzJobjR0eEtWdVpQZmIxQlg2UFYxYm5zNFBtdWM5SEUtVWtxb0w1a3JWWURtdTlndFFYb09WODNmcHlmTEpNbFQwVk1XYXZpa3ZkZFBlZWJRYlQ5RFFFNUhr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwNBVV95cUxPZWs0WG16MXo3cFlNUTFfbExMMUtMMHBIVlZiRnBhVHkwd1czZHZGaTFONlh2SDV5cVVLVjZOMjQ2WmVzb1duN285dzcyTnZLSm80X3ppNWp5TVlfaGNlYWJNOE5KYk8wbWlMekY1cmdMUFhKaU5yOWd1MjdSN3N4SjEtZXdKR09qTVZBUkw4dHFOLTRSSElOaW1fREVOcWFEZ28xMEdKekk2SWlhRE5QaWN2NFVISEJ6MWtHQW1lRWYyZHhENmZxRTNVRkpqamF5b3E2V0Z5UmZxUUpxcTBsb3hyQWJ3TWpwdHNySG9leVhBXzEyUDRmYWUtQ2FYVVNpUE1nM2J5YmZSYW1McVR3NlNBMlAzZVhYbmdsZzR2enIyVGx1ZWxWSEl3ZUp4dFBnakVXSnBZd3dmQm9tU2Z1U0VZWG1GVThiWFk4UDNGY3lEekJQaEgwV3BvcExPLUtHZUdWZGRXbWRoZklWUXVKcGFWSlQ5eDlBYlZ2WVY0VzRGV2RZTWZ0czFKdmpaLWRGeWZELTRkR2x4LVk?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46041.39688657408</v>
+        <v>46042.04261574074</v>
       </c>
     </row>
     <row r="7">
@@ -737,17 +737,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DHL Supply Chain Expands Electric Freight Operations with First Tesla Semi Delivery - GetTransport.com</t>
+          <t>Big in Japan: FedEx adds electric box vans to last-mile delivery fleet - Electrek</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 09:58:21 GMT</t>
+          <t>Mon, 19 Jan 2026 19:29:00 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1ob09TMWFXTnlJNnJOVDBBSS1DNTlEU1JWWUhMdzdHSGZITEFwLTQ5UUdDeUFjd0ZGUWNwVzJQRTVxblFreHkzTXl1RXY2SUJZVHk0bzR0ZGVRT3lRajlSVGlnZmRydEN5WGRrWFVLYW92akVnRjk0SmpvNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNOTFGSE1ZNTdzOGFiYllXalh2WVBvbUJCTjB5ZlIyWXc4TVVCTVJjV3VyTTdySHlldFVkXy0zYW03aGxaaUVBYlZDUUxrREdOOXdMVGE4ME5FMzZxYUtiQTRnd21lUW1SVVU1TDJCV3RnM2hNRXlZVVpXQVNXWnNsSVZvWlJ1Q0FSV1h1azlWbk9UWVNmc0pXMklVaFczcFNMRW1V?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>46041.41552083333</v>
+        <v>46041.81180555555</v>
       </c>
     </row>
     <row r="8">
@@ -785,17 +785,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MLK Day holiday: What’s open and closed - LiveNOW from FOX</t>
+          <t>Rapid Grocery Pickups - Trend Hunter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 12:06:26 GMT</t>
+          <t>Mon, 19 Jan 2026 16:09:19 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNTnRMWGI4NFEtMi1LdHkxLV8yWG9WUlg4eFl6N3B5X2huUWdqNVJCdEpwZi1uZHF2eUp4SFFVRG5fTXRibUE2NkYzaUJGVTFLY2JqM2hEUUV2SkxYNll6NUFPU05yOGZuNGhLZHNaNjREOWx4eGpFVnRjWW9ORkk2R0Z0NWd4eTNuMmVwblJTLUduRFVmSVBCNjR0QUYwYVNMdmIw0gGoAUFVX3lxTE5WeW9GeHZBNnZOZFZ6bm5kd1VZQ0hlV3hvRzNucW5MOEhpMVd6OHRFaVJ5bUdEbzZ5MmJsRTMySFk0RlUyOFpZNUtuQzBrQUN3Rkt3Q1ZubWF0bUswRFAtUFZSU1VjalhhTkRwRXNObkNnNW5yRFptYldaLUJwM3dYVXhLMUdUWFN4SHp3M0tUTmJJdTB2Q2JNUVhDRS11M2JWdzlpYmZNcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE84WHBsY3BqQmIwbkotNFZDTDBOZXVoNGxUNVE2dHdPWGZRXy16ODNSbU5OWUxlcGs4TVhWSkRRSDR2Zm9HWDRXSG5yOUJXbXVGXzZVajhySWRseHBzZ1RV0gFfQVVfeXFMTzhYcGxjcGpCYjBuSi00VkNMME5ldWg0bFQ1UTZ0d09YZlFfLXo4M1JtTk5ZTGVwazhNWFZKRFFINHZmb0dYNFdIbnI5QldtdUZfNlVqOHJJZGx4cHNnVFU?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46041.50446759259</v>
+        <v>46041.67313657407</v>
       </c>
     </row>
     <row r="9">
@@ -833,17 +833,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Is Mail Delivered on MLK Day 2026? USPS, FedEx, UPS Hours Explained - Newsweek</t>
+          <t>No more waiting for delivery drivers in the United States—Walmart speeds up deliveries with drones and takes on Amazon head-on - Blanquivioletas</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 11:00:00 GMT</t>
+          <t>Mon, 19 Jan 2026 23:00:36 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNN0ZWZDM2ZHp1X1FCTjU3Zm94c3ZQdFliTjFVVGZqOFJ5cWd1LVFtYWoxbzkyZFppRGtrNUNQeUY2Ry1hUHFSMFhoNWhTZl8zNDlNMEp2Tl9yX1Y1OERIbW1ZZnd1LVZObElCSFZLVWhZQTRmMEtIY0wwazBoZnpRZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE02RHVGaGx3eDJTYl9GQmRhNDBRNk8zMWFucTVJNlVDdWRZMzItd0RUZE0zcHI0SkpVNXhEckVkaDFDQ3JFblE0NXJGNTVlSXYwMWxySXoydXJhaU02M0tTUGZlLWlCSUQ1QWpYTjUydlhCUEFhTnJz?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>46041.45833333334</v>
+        <v>46041.95875</v>
       </c>
     </row>
     <row r="10">
@@ -881,17 +881,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amazon Now live in London, European expansion imminent - Ecommerce News - Europe</t>
+          <t>FedEx announces June 1 'customized' change amid battle with Walmart and Amazon - The US Sun</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 13:52:45 GMT</t>
+          <t>Mon, 19 Jan 2026 20:31:38 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOMm92eVBLVW5UVU1sNjMzZG53d2daNVVzYmNyMTk3T005Y2xCVWhnc0txcXB6YTJ6cHBCUFZZOFFBcVVCcEJiQkg5ajZaSXFrcHpUaXZwam8wV01NbXZxVC12SEFabEw2QU1lbnV5alhoNGp4OXprVzBNeHJGalQ5bGRkZ0JBQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNRnFGNUJFbHNoZ1lsWXAyUXpVb1ZJYVo1VjhHUHNZaUlab0tta2xQck9LdF9QWnJSX2k0WUo3c2RYSDhSLUtlVFRYcWFqLXVTN2JfS1NmemVJakdUU2JIN29qeVFjeE8xajZmVXBhMkVmM2M4ZHpuMTNYWGg5b3hxdmNPdTdkb2lNZ2JoMkhDOVBCV3ly?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>46041.57829861111</v>
+        <v>46041.85530092593</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +929,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>‘Remarkable’ UPS driver ran into burning home to save woman, 101 - The Guardian</t>
+          <t>DHL and CMA CGM Expand Biofuel Partnership to Slash Ocean Freight Emissions - LM - Logistics Manager</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 11:02:00 GMT</t>
+          <t>Tue, 20 Jan 2026 06:24:04 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNcmV3c3MwVDE2dFNZNFB1bEZjNENiT1pHcGI5N29xcGhNb2YzeXJVS1kteGFDaXItZ1hVSC1HMFpMQm1wLVMwRVpzUG1pS0JVcnNLSkp2dkNvUFhGcVZ3eFJSVTVkYkdaaUlYZHJ3c3pmbXVudllUVmdnWUR2bHZpd1FsVmR3RUhjUE9Yeg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQRExTWlc3ZnBLWkRJWmlZazNqR044WU9GRmlITnFEbi1FSXZOY2o0bjRzTk5jYVowV1FVQVNhb1VpMDVRTkEwclJHemdwWTgwaDdJQmt0azNWNFpULTZTRi1QYkRBU044MHFyXzl2UnVUSEVRSF9sR2dtSWVGclI5aDBHREtwLW51emtQVHZQd3EwZ2EtRDd5cTl5MEdCemVhYUVhaDBPV01sdw?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>46041.45972222222</v>
+        <v>46042.26671296296</v>
       </c>
     </row>
     <row r="12">
@@ -977,17 +977,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Royal Mail Today, January 19: Ballymena Undelivered Mail Probe - Meyka</t>
+          <t>Amazon Brings Quick Commerce Offering to UK - PYMNTS.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 13:23:15 GMT</t>
+          <t>Mon, 19 Jan 2026 20:11:41 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNQTdLOUM4WnZ0bUJ2dzc2Y3BNOE1wSXRPb0VkRm9iZlZsNEsyU1NsRE92OXdybXJ1SXppS0dSWkRVT1RpcG96Z0R1TUpqTG5tU2tYY0ZFV094RUJVUGtBb2lzRkxMZVUyMTlFRG9OdlJfd240cXhUc1RYVGYtdkFfVnFMZmdBY0s3eGlzTHhwamdwR1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQaGNYdGg1d1N1SFp2RTNYNEVySzdjd2tqOFJPNk9YbnNaZjBra3A3S0hTQ1FEaE1mb1ZTRUxaS1lwN3BZYzBlVmVscmZLTDVrWExqOFhPWG1ua0cySWlZVFROZHg3U3JnaktwS2U3S3pBTG9HejB1ODg1QTFuQkp6YkY4Mk9NUQ?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>46041.5578125</v>
+        <v>46041.84144675926</v>
       </c>
     </row>
     <row r="13">
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amazon Italia’s €180 Million Settlement Ends Labor Fraud Investigation and Affects Logistics Practices - GetTransport.com</t>
+          <t>Royal Mail says it's working to restore full service after residents in Wolverhampton complain of not receiving letters for six weeks - Express &amp; Star</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 10:03:44 GMT</t>
+          <t>Mon, 19 Jan 2026 16:42:11 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5QNEU1akMtaElnd2lmdHRqcGtoNU9OUjlYZ0ZGNjd3M3JMenBoSWZPZEd6Umt4RlJoVF91cnN3M1RLeVpTREp0cjY3Rmw1UXQxUGd1ZGRPNXYtVGJlSE9FdDYxazlLd2t2NnRiN0l6cUNTRjBCQWROREEwbTk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAJBVV95cUxQWFRpRFUzQWpMb2NPSFc3WXRXYUc0RzVhSXpMdE9Pb0dQcDlSZlVGSGpsSnA0T3EwbWpOUnRRb1A5U1FMMVFMRXNnZ0l1MFFLUFMtdGpWXzVmWFpSTWhoYzUxa3lKVFZma25zUVRqMWhneldnZDBHaXVVZ0ZvNmJMOElzSlJfRmQ2bzY5QUFmQlY2em5GYjRzNDlkdHdUblBPR20xVzNUbl9PUXF0NGdmTlptMENfR0hzWkpGMmNBUlNwQU13STFCeU00d0JzT1g2b3dyVmRIU1I3OUdheWd4Q0dKV3hlUGdhM0o3SkRlSF9oRmVPTE5nV0tCdFBKOVRycHk5bDZ3NFZLdVFoVW5lV0FQOFNfVGhC?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>46041.41925925926</v>
+        <v>46041.69596064815</v>
       </c>
     </row>
     <row r="14">
@@ -1073,17 +1073,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How FedEx Shapes Economic Growth and Drives Innovation Across Asia Pacific’s Logistics Landscape - GetTransport.com</t>
+          <t>How FedEx's CEO Uses AI Automation as Part of His Strategy - Business Chief</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 11:53:01 GMT</t>
+          <t>Mon, 19 Jan 2026 14:43:19 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE0taS1WbHVLNEhoVjZKUm9Rek1ld0c3QndublJ1dUpCRUwyeDkybVlWWHM5UGNCdGdFcFVkelZ4NFJEeThnWUdwWTBoVjFsVHpSVjNmQWdYQlYzd0NBa3R6aWtBN2FOb0ZTZlE2WERDMGVzclFTWHI0cQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPcDRsVl9LWVBxUURCYUFuVlhWZDZwVzhVYWhndFhSZHRPMTlYUWdLN0FWVDRaMUxQaEVQQkE4QngzSF9PdlFlUXNDVjhITTgyZnEyUll3d2pJQ3F6VXQ3a1ZtWEtTTVBBbnFvT3hMN2RNTnVfU050Z1UxZ25mQTVVZHZTSVJxMHJIQlQ3d0s5bXFDRGUxbnc?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>46041.49515046296</v>
+        <v>46041.61341435185</v>
       </c>
     </row>
     <row r="15">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UPS boosts cargo capacity by adding 737-800F and A321F aircraft during MD-11F downtime - GetTransport.com</t>
+          <t>VIDEO: The Amazon effect: Gen Z now expect super-fast online deliveries - Australian Broadcasting Corporation</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 10:14:33 GMT</t>
+          <t>Tue, 20 Jan 2026 07:20:33 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBQUnhYNFBpZFh6UGlsM21ubmNGZ1B6a1hhdkZkeTRrVXVOTC0yVUc5TGhTUzFWeDE3VkhPSWw3U2ZmWXUtaWRRNFE1SEY0cXg2S0pmdTY5cjJXalBQbFNVWVBwakFIZHFJbXJ5VUhJRFluazB1OU53?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNNnhmUzFWYzFFWUNIRFdPVEJLc3dRRDdUM18tODJzbFhLNkFZZjc1MlRzZzk1QXBTcTdrMzg4UzgySTlKQm1WWEowUW85c0Rua3owcXRodFBTaTdBRGFraHpEazBJekhIZno5TWFvR21taWhBVWk4MW9velUta18tc0wwTUtmNW9IWGM3WW91QWFLVHoxTEZfRjVXTXVSYXBlV3N6T094VndMMk1CNUZZaVRJZUhSZm1tOF84QVNSTGxfaG1WVlo3TVFQNktabVE?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1153,33 +1153,33 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>46041.42677083334</v>
+        <v>46042.3059375</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City searches Belgium Dutch language</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>("DHL" OR "UPS" OR "DPD" OR "FedEx" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI") AND (delivery OR supply OR logistics)</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bom OR bommelding OR explosie OR schieten OR steekincident OR "verdacht pakket")</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What’s open, what’s closed on Martin Luther King Jr Day 2026 in the US: Banks, schools, post offices, mar - Times of India</t>
+          <t>Défi legt bom onder Guinness-gesprekken - BRUZZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 11:40:00 GMT</t>
+          <t>Mon, 19 Jan 2026 18:47:01 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPWW9BUnd1YWZNUUZ5Vzh2aF84VnNxSWhRbVFPRl9Nd2lsVVV4MXN3QW1QQjg0YXItQjFSWnlzUVNuS2liRjY0YzZtVnhPcDNhUi1qcWdKWnZ3NlJzX0xKRTVvUkVCaXVVa3ludFRJbWREYnRrTEp6SzNyYmFVcVYxTU5PaWkzRXFzTDZsQ3dfSGVKU2FTUG9aMG00RHhCNkRRV3Q3dnRQLTc5b0Y5UW5QOTJIWUxSdlltQ1picnBxdDg5elo2YkRGSUNwUXBES2JWeGVWbVAwNFd1N3g2WU4zYWh6cmhGdE12Y21NdDZoX3p2ZnA5QmlOenlIZHhoSEVWYzdUS3FhbnRNS3hkeXdUOVpWVnFPUXljYUNBa2xsMU4tUzTSAagCQVVfeXFMUF9fTUYwWS1lRnh1MGJYSHU5b3l2SlhETjVucDE0bFliVjNMV3pCS1hLUnJhQi1TWWJ1YlJOUVhLMG1zRDVESk1sT01JbEtyd3lMNXp6ZXItNllpUUNZY1pvVVNQcURkYzlCeFhZNExuRWwtekh3b243bTNRd1RPOEVadjh6d3lIbW4tbUxzUmpsdTk0U2ZKSHFjd0ZLdFpuS1JuRDF0WXViMl9XNWhnT2diV1lhWndLaUJqMGxoZ0xWMURSczcyendWR0ZWNW5wZ3MxT1RsUEVpMGxNblQ2NnpkcmFMTWFMYmdRM1YtVXpPMEtod3dITVp3N3BybUc4MW9jai1ZVE4yTm05MWRyNmlkYklaNDZtakVULVd3OThnVnk1VURwTkw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQdVFCVWFkTmxTeHdZbXlJV0NWNko0X2hCS0tucU9kLUllMVFFanE0ZVhldnBpLWV2Tkc5RkVYcUZUZjVrZWZPckpDc2VndzJWb3NndWhZU1NmVzZCeDJsNlhEOVpYbG5EUGZLb09qLWRIV0N5TnRHc3NwcnAtd2VFS3BRTWR5NFpURjZ1a1cxdEw1c0FqeUxkdl9OZEVGdUNTOVpzZzJBVVVRMlJVb3RYX0JpOXdBU2N3Z0E?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1187,47 +1187,47 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl-BE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>46041.48611111111</v>
+        <v>46041.78265046296</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City searches Belgium English language</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>("DHL" OR "UPS" OR "DPD" OR "FedEx" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI") AND (delivery OR supply OR logistics)</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Board of directors of future standalone FedEx Freight named - The Loadstar</t>
+          <t>Suspicious package disrupts rail traffic at Walloon station - The Brussels Times</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 12:31:33 GMT</t>
+          <t>Mon, 19 Jan 2026 15:33:45 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFA2NW5POE4zSVgxUkUwM1VIT0EtLVF1X3hYN1JKLVZrMlNTMTBYQzBoSnBuTUE1Q29QbThPb2RKdC05WlVucndPRVZJU2lLRHlnV2NyblBuTmtjSll6TTJ2Um44Q3hZejg3Nm5jcGlXdGtDX01SZEhGVTBTb0o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOVUd1TVpaVHh0a1gwSUxqMTFNRkk5SDJ3SVdCSW1NaXN0OThYLTczV0FGRm9WWUxuU3RfbTRDTkFjNG8zQmlLOWVhQXlrdTEtMXZKbHVoR0cwZ1R4U2IxRXhVUGNyMmxLckQxX0NSZU51WHlXVXZMVVhpQ21FTW1JOFRLa2c0NG9KNzZsUUUwSEJoVDE5THE4SnVhQU9UUQ?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1240,42 +1240,42 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>46041.52190972222</v>
+        <v>46041.6484375</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City searches Belgium English language</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>("DHL" OR "UPS" OR "DPD" OR "FedEx" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI") AND (delivery OR supply OR logistics)</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indian-origin FedEx CEO speaks out amid H-1B hiring row and job-cut claims - Business Standard</t>
+          <t>EU to Hold Emergency Summit Over Trump’s Greenland Tariff Threats - kurdistan24.net</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 08:50:46 GMT</t>
+          <t>Mon, 19 Jan 2026 19:53:07 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPMFVLMDNDeTNIbXBZRUZpTXg2TWNqUklXalZpU2FxUFVzcEFrdDk5NXh4aVBiNXNNTkt2elJmaThmWkNHaFQ0VERwQVptM1NEbEp3eFBFbllaS1VjTXlMUHNPQVRDUXRva3dUZzBHTkd0LXZhRk1CY2wxdHZ3VWZzX2c2THlnZHpyM1B2RU9FcDg3d0JYWkJURzduMWppMkpGb0hVdnZhM1Y2WFY4d2ZfUXVxbnRreUt6eTEwcVVmUkxJSTROVFJJSHl1dFdpV3UwMmR5V295anJ1SW5N0gHcAUFVX3lxTE8wVUswM0N5M0htcFlFRmlNeDZNY2pSSVdqVmlTYXFQVXNwQWt0OTk1eHhpUGI1c01OS3Z6UmZpOGZaQ0doVDRURHBBWm0zU0RsSnd4UEVuWVpLVWNNeUxQc09BVENRdG9rd1RnMEdOR3QtdmFGTUJjbDF0dndVZnNfZzZMeWdkenIzUHZFT0VwODd3QlhaQlRHN24xamkySkZvSFV2dmEzVjZYVjh3Zl9RdXFudGt5S3p5MTBxVWZSTElJNE5UUklIeXV0V2lXdTAyZHlXb3lqcnVJbk0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPaWM5MnZESFJOcEpCNm81TlVCMVR0NVNSN0NiU2J3aXFHekRRamxna0NoNUJFTjdHem83eGxWakFGWnNEeDhScjlhQ3JHcjVDYzVTdXBkdlc2bTZ5VjVER2t5WGJtRlVoM0luaWg5MHNCT1QtNzN4cU4zaWZIUjdDREtBU3NXbnhad3BNek92bVZCdlVmOTZ2eVhnNlVSYnBKOGJubVRQRHduZGVm?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1288,16 +1288,16 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>46041.36858796296</v>
+        <v>46041.82855324074</v>
       </c>
     </row>
     <row r="19">
@@ -1313,17 +1313,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EU to Hold Emergency Summit Over Trump’s Greenland Tariff Threats - kurdistan24.net</t>
+          <t>Eight people ‘linked to Albanian mafia’ arrested over plot to kill Brussels’ chief prosecutor - AOL.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 12:16:00 GMT</t>
+          <t>Tue, 20 Jan 2026 00:22:45 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPaWM5MnZESFJOcEpCNm81TlVCMVR0NVNSN0NiU2J3aXFHekRRamxna0NoNUJFTjdHem83eGxWakFGWnNEeDhScjlhQ3JHcjVDYzVTdXBkdlc2bTZ5VjVER2t5WGJtRlVoM0luaWg5MHNCT1QtNzN4cU4zaWZIUjdDREtBU3NXbnhad3BNek92bVZCdlVmOTZ2eVhnNlVSYnBKOGJubVRQRHduZGVm?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQRHFFYko4UGRsdWhuN1MzeTNqekNYc0lOd1BpMXBROC1kUUViR0E4bjVLOGo5TVBBbEg4N0pJcWozUGxGNkhZaW1XT0tXRFhVc2w1OHYxc0hzQWhaSkd4TWFRZEJMNXk5d29zb09teDc4b3lkMkJNVkRWdTJEQmg0VHNDMTE?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>46041.51111111111</v>
+        <v>46042.01579861111</v>
       </c>
     </row>
     <row r="20">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Interior minister condemns violence after Africa Cup final - belganewsagency.eu</t>
+          <t>Denmark proposes NATO start surveillance mission in Greenland | Daily Sabah - Daily Sabah</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 11:04:00 GMT</t>
+          <t>Mon, 19 Jan 2026 19:05:00 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOOGZsYTAtYjh3bHkxZ1RYelBRb1FkbUFaZ2NTUmRJMlAtaldPX2tHdHhYYW0xMXVza012MGd1azNoT2hSbjJGVUY4dHN3clBjVEpaM1VCeWdieHI1em15dG9rYllXb0hMWEwxQ09BQUhuOWJzUzFJU3ZDRjRVMHQtaV9HOTJwYWRQSHd4VjdqbGpKb1lyekhoRmtNVkI3UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQZGJIOVBkOXpMbFRPa2pSd1dHZUhCRWNNTjYxeldwMWZrTF90a0NhSjVRUnJfRmt3YXBfLUVVT3FLSmY3VHA1VnNfR3FsdUh6ZV9IbjRKOERGY3E1R1N5OE5vLW9DUTZ2c01tb1d6ci1TUmJBX0JCdUR2b0JMMkVOSk9qTHFIMjVMdjlySDFzWHJNc2x4d2J3X055QjVfQUdwOXZz0gGoAUFVX3lxTE9vTU0xaWpMT1QtbDV2OENpMGc1S1BWSWtVTTRobVhOSVM4cGhRU1pYZVBmbS1TZlFHcnYxc1RQUkxTN2pwb1ZXSWNzbGRfZWlfbEtENlZ4ZVpQMGo2WG9SYWgyV3lNdm81S01qTFdNZ2ljSlRBTHQwdHZWZ0sxb1JUYVR1RWN2MndPUE9yMEJ5ZkJnRThobEV4bUhFSUdTSGdSM1RFamxRdw?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1393,33 +1393,33 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>46041.46111111111</v>
+        <v>46041.79513888889</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>High Level City searches Belgium French language</t>
+          <t>High Level City searches Belgium English language</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bombe OR explosion OR "colis suspect" OR poignarder OR fusillade)</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Un colis suspect entraîne l'interruption du trafic à la gare de La Louvière-Sud - La Libre.be</t>
+          <t>EU moves to hit US with retaliatory tariffs as trade clash escalates - CHOSUNBIZ - Chosunbiz</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 12:10:00 GMT</t>
+          <t>Tue, 20 Jan 2026 06:52:00 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNUEFSbUNzVG5SOUR4eEJuYms1S0I1dHF0NjZ1VE9EaXdnTVQtQlBrSVVmY1dKSXp2R0pOZVpqdzNQT1lmdEdhUmtkZUY1bFEwcTdieG9OQXFFTjA3YjVqcFJndXdKQ0lMejZqcjFsWDFIek5wTmtIVTgwQng5VElfV1d6UllSUlJlZ3FiT1ZxX0Y3N1B2cmVMYXBaTEthWmRsdUk5YUZUSHI1RVVxUmxWQ1lHNE9FcVk5NnBhWnZSX09sRTY1c01uSEJSZjhRX2dDTnVpRGhQOHdrelVRZ29GaXhoMHlWZmVSeFlOMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOR1pEMDJ3TThVME9fY1VCaTU5QjIwY2VDT2N0MDdhSS1BWHdIQmVBZnV4N0ZTRzlPeXB1MGNHa2FNSk9GV2twQXFBVHFSVVpkamM0bXdCeU40el9LYWEtZnhzb2U0dzZ5N2ZPa1RuTlM4N2lMbGRKbFZaLTdpdUItUW9hUjdxR2xl0gGcAUFVX3lxTE5pVTJmYjh2aGpzNGtrTFVTYUQ0Sm5SS2duRm05QkNtRzhqaVhoa2l3OHRWZGFWYU90NGtqV3hrVmhza3k2T0VaU3B6UWxLV0huV1FHdmdKSGVNaW1xc1hHRUdmeXlxZ2xWZzA5V1lMMzVleElHb2tubHlic3ZaLXRJMkIwM3pIcnpoQTJoakd1LVIwTHd1R0swZU9WSw?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>fr-BE</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1437,37 +1437,37 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>46041.50694444445</v>
+        <v>46042.28611111111</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>High Level City searches Germany German</t>
+          <t>High Level City searches Belgium English language</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>("Frankfurt" OR "Cologne" OR "Munich") AND (bombe OR explosion OR schießen OR messer OR "verdächtiges paket")</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gesund und lecker: Profi-Koch bringt Kindern in Frankfurt das Kochen bei - fnp.de</t>
+          <t>Global Stocks Drop 5 Critical Signals Warning Markets - Brussels Morning</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 10:00:00 GMT</t>
+          <t>Mon, 19 Jan 2026 14:39:13 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPOWd4QURJMWE5QVkwWnYtQUhtNHdnLUU2elEwM01FU011dVU2enBJZWE3bnYySmlMRndzMjkySW9weXN3VWE1b3MtNEhTQmxteWI1UVoyZk5WdFllRWNhTU94dVk2d0drbldpZXhENkwwRmVNZFJZZVB2TzZOZTY1VFVPbl9SWEdjMy1fVG9TRlhFcExsMl9WUFZCb1p1TWk2QkZ3WXpoT1l4Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1BTmF3RFc5a0dnQkNHOEFzSjFKSHBNdF9pRl9iSFhTVHVSZzFSOGZsSDJuWTBTN2JjV29rLVNCZ2dCdnMzcFI0LWhsakgtdkFBajl6NzVER2FLdmxTNkFUcng4SWc0U2RwS2RBc09xSFFkaGs?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1475,47 +1475,47 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>de-DE</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>46041.41666666666</v>
+        <v>46041.61056712963</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>High Level City searches Germany German</t>
+          <t>High Level City searches Belgium English language</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>("Frankfurt" OR "Cologne" OR "Munich") AND (bombe OR explosion OR schießen OR messer OR "verdächtiges paket")</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Deutschland News Ticker (aktuell) - neopresse.com</t>
+          <t>Man stabbed in Uccle after noise dispute - The Brussels Times</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 11:57:01 GMT</t>
+          <t>Mon, 19 Jan 2026 15:06:17 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBLWU1UWXRGeVdpWTc2SVRxYUpCZHdkTGNRT2FLTHhjdUlweWxGcUlkVEZmY25tak1pdm5Yc3lfdHVnSGtkMDNZSVh4ZlRhUGhMWTd3R0tldmtTVnROME5mRTRmRDlUTTNBaWpOekFMajBRRk43cHlwRU5Maw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNcjhXd3JlM0VNalYtV1lUTGhwS3phM2p5Z09ETHVONHRqRzJ3c0pvekRKa1FXVThvTEpCUl8wNU84d2wtUm5KMHBnYVNxYWFMTWhuWFN3blB0cFFzRWtmZV9HcjNOVnZUQ2czSHNfdVIxZW1kZktlb1BCcUxzRGNfVjZRWnZ6N0YyTkVLcnhlbWYxSW8?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1523,47 +1523,47 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>de-DE</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>46041.49792824074</v>
+        <v>46041.62936342593</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>High Level City searches Belgium English language</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>("Extinction Rebellion" OR "Just Stop Oil")</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Faith Matters: Luton Wassail event at People’s Park - Luton Today</t>
+          <t>Playlist tailored by STIB staff to play in Brussels metro stations today - The Brussels Times</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 08:55:00 GMT</t>
+          <t>Mon, 19 Jan 2026 15:09:50 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOVVZkM1RMaTJxdjc3dmMtOFhNQ3k5d0JrSndFWE1HeW5RQ01YWU5WZ1BPbThUNUdmcGJfSEhRQmZ5ZnV1N2loZkxJaTNjZDJDOWNxNzJmN19GcUYxay13U2Izcm1wUGM3WHg1WGhxUTFwQWhaSWtvTER1VjFESV9KdlhOUWU4a1FPMzlZV2tOQlRqV1Y0YlNUdnZ0dHQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQOWY0MGx5SDJieDB5RldVTnpLdkQxQ3F0cEhzRnB5WWhfVXFyWVpFcElpVUIyWlNfTEV1V3R0T2UwX2lOVzVGelJJX3U3aTIybGlwZHhTcEVKQXYydDhqWjA3Qm5wc25xUmZLTEpuRXdoRVR6SVhqWWJpNDVWTFFFU2IyVXZFZ2VzSEJxdFhkM3ZFbFZFTXBTNjdVVzZ2R3BDdS1zMHFCUEJ3ajJUekpqY2NUWm5OUUU0Zm0w?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1576,42 +1576,42 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>46041.37152777778</v>
+        <v>46041.63182870371</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches Germany English</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
+          <t>("Frankfurt" OR "Cologne" OR "Munich") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Two brothers jailed for shoplifting in Farnborough - hampshire.police.uk</t>
+          <t>Five Observations from Bayern Munich’s crushing 5-1 win over RB Leipzig - Bavarian Football Works</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 11:48:00 GMT</t>
+          <t>Mon, 19 Jan 2026 18:00:00 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNQWNWNXJ5TlRudWVUNHRTR0V2NjdRRGxKdXdHVzJON09aSm1pY1kxcHVza2ZzbkhxQjVjU2d2WUthdzQ2dWVEOVZQaVc3YkRZTGEyRDNWeUdDWDI4d1czWDZpckFKbFFqZzZaODF3WXNOZ0RCOTUzYnM4TzZxaUJTbDJ3NmpCaktfRzVPd1JNOGMzOFVha21pOTBsdE1CX25TMnBWaXJsLWpKNkN5NmFGamxNcUZRbGpqZ2xiWWJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOX09jRFZaYkxhM1lEdlJwX21nUmY2S29TT1N4Rzc2bGJzM1BxWmFJMzRDOWJtWlNKaGMtdU51MTJpMk5UOEc0UWNTdTJ0LU1EektycFJnR2dBWDNNQ0dpb1B6TGhrdVhHZ3NsMDlRUVdHWUZKU09pcmNYalhrMU1qaHltSy1ZVGc3aFlabFVwRnV1cmFYUVdPVlFFZGw3NVYzaWZyUm9acW94S0c3VWNBVmRqYW5GYm1IS2o4OXQ3TG9pczV3S09iSWRHWlRwRUFHcy1jYU8zeUt2UTNiakQtUV9uZHBIRVhiblZvSnQyYjNhYjJNNEVZR1k3NG1wUDN0OHhxQ1FHVGVIWFlV?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1624,42 +1624,42 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>DE:en</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>46041.49166666667</v>
+        <v>46041.75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches Germany German</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
+          <t>("Frankfurt" OR "Cologne" OR "Munich") AND (bombe OR explosion OR schießen OR messer OR "verdächtiges paket")</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>West Midlands PCC answers retail crime questions in meeting with Fed members - Talking Retail</t>
+          <t>Warum jede Form von Nikotinkonsum der Gesundheit schadet - FAZ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 10:47:57 GMT</t>
+          <t>Mon, 19 Jan 2026 18:16:13 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOTEpablBtQUpZWVNCZGhNdmR0eThWZ1lGNFlvU196bFBvSlNJWTZqcEU3ZGlVNmZBenF3WllFcE42Yk16eHJtVUlIV0Q2TWJvYmtjWC1ZRlEtdmpRa0RnZDZWSnBlUDhfekdXdUNkYjFETUR3NmhPcnQ4ajNFaGNQLXNmMzc4ZGNUWGVtMzBLNnRZcEdhVkJEUVY0R1QwbTVwRk9jdHAxZWNtTDQwRkNpWlZQbkNJaW5CQVV0RFhRWW9Fb2FfaGhoZ3NPUzlBR0Z3cUJZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNVW9FREpTV29DVThEVFltVXptVDFEREMwcnFialplbjJTNUhZbWVjamZXamNfdS1XTHU5RFQyTXdQeEp3Q1lkUkdQajg2VzhESVBCSTVnNnVfdXZsX2QzYk12cHJWdFFJdDZYZWpMMjZvRzl5QXFlb0tmWlJMcU1RRkhhaXU0MTFiTzVKOVpQVC0yOE5KcGpoLTc5VVhFNWVIdDhiMW9CTDhUMmVWMllNRVROeE1mME91dWpycXNHdFk5OEdmYm9jc1BIYlM?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1667,47 +1667,47 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>de-DE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>46041.44996527778</v>
+        <v>46041.76126157407</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches Germany German</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
+          <t>("Frankfurt" OR "Cologne" OR "Munich") AND (bombe OR explosion OR schießen OR messer OR "verdächtiges paket")</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CCTV appeal after shoplifting in Morecambe store - Lancaster Guardian</t>
+          <t>Vorfall mit Messer: Alkoholisierter Lkw-Fahrer in Gewahrsam - Mittelhessen</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 09:51:00 GMT</t>
+          <t>Mon, 19 Jan 2026 16:30:00 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOOXZrZmU1S2cxWHMxeVM4MlRsQ3h6bjRtR0djX3lTV0VnSGxUa1RncWl1M1QxY28tMTVRbXNLcGF1WVJ2eXZXanJMMkpycDFJWHFvUlFTQVJFRW1GNXBDUWpDREV3cVRodi1USEpCdkVYTUZ4dGFyajFjRHBuR2h4c3JpbzJ2V1hibGRPQUJ5eUh6N3daTEtwOXlDcmlLanc5dVcyeXl6ZkZNZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNam5qUDd6OUYwNF9mamVYd3NiRnpmbnV6R1NySENyWU85R0ktVG9NdlNTMW5aZ2MzcmI5Tl8ycUo1WWJjbHp6b1dxbS05T1BoRng0WEtsVTZmRzJ4QzJaVXd4c09TaW40cmczOFhYekhSS1prd1pIZ2Z4bG5jeEIxNVl4dTg4MlhEYXJodHBZcFoyb2VRN1laRWxkdTFXUFNKbU10c0R2c0lIeGxEd2lHd1J2U1lzVVFuZUpvdm9kZ1lHV3dxS3ZocmFDUkViWUdqaF8tcm9xUVQyeVhEdWp4WXdLd0xERTQ?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1715,47 +1715,47 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>de-DE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>46041.41041666667</v>
+        <v>46041.6875</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches Germany German</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
+          <t>("Frankfurt" OR "Cologne" OR "Munich") AND (bombe OR explosion OR schießen OR messer OR "verdächtiges paket")</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Anti-capitalist group that threw custard over the Crown Jewels 'plans mass shoplifting at Waitrose' - MSN</t>
+          <t>Mordprozess in Darmstadt: Tochter soll Mutter erstochen haben - FAZ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 09:35:25 GMT</t>
+          <t>Mon, 19 Jan 2026 16:17:07 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AJBVV95cUxQajNJYVVxSEFQVzZLQ2kyMXpKbnA0MkJjSFpCa2N0b3g4SDg1clBXbXluSGtRUGE2VHZ1ZmJwRF9HYXhpVmY2d0NWTlVQbExlYzI4Z0hwNFJ4RFJWMVowY0FhVVBMNThlMGp5NnNBTEZtRFBBTXozSzdCd3NrRXJiUzh0ZExMNHA0RDJ2d2toMmJwdkFEc3RFd3ZuMjc1SEJTTjN3NVhiZmRLaDNUcjh5NGdldFVIVjJPUlZUQmNTVUx2VWM3aTRNSDZuc0VSNDI3cVc4cWxpZDQ4RFRBSjEwMElsVnlJMDRSVUh5Ny1hdGY4U2tYOWxNbzBPT0FNRjl0RHozZUw5N1kxVHFCd0dUODRvMDVqSmQzSkpJSElzU21wV01kVlJqMlhwVDAwYW5jelNEM1V4QnAyM2dNUzJqb3pWM3JWUi1HWDhpd004dWh6WnJMUUJ0YWVnSk5KLWYyQl9tUF9CZExPa3hpTUprZE9CYTY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNekprTUMzWkUwZm93OF9xRm93LWF4cHppWVdFTEJXbk1yc01hZnh3WGViZ2tIN0phOFBVV0hWTUJTNVFLUlRkeV9kODlSTmxXdDJ0bFNQLVlsR21Zd3Y0ekVoSnJCYUJvLVFEd1VuRFEyOGhOSVdXMVF4Z3hkV2R2WXVUWnptYnU4VjJqWGx3TlB6NlMwR2NQaTgwMS11LXRTRTZ6VlpuUHNWanBFYndva2Rrclo5UnNybGp2U0lpTlRtYnl1ajVvaldTZVE?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1763,47 +1763,47 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>de-DE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>46041.39959490741</v>
+        <v>46041.67855324074</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches Germany German</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
+          <t>("Frankfurt" OR "Cologne" OR "Munich") AND (bombe OR explosion OR schießen OR messer OR "verdächtiges paket")</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nuisance shoplifter banned from every Asda, Tesco and Aldi store in Lancashire - Lancaster Guardian</t>
+          <t>Masthähnchen in Hungen wegen Verdachts auf Geflügelpest getötet: Aktuelle Nachrichten aus Frankfurt &amp; Hessen - FAZ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 10:56:00 GMT</t>
+          <t>Mon, 19 Jan 2026 18:42:45 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQQjRRQUVIcUU0RGh6LXZLaGVQbTlTeUQ1TC1uOUE0ZVg0aDlIRDN0cnVZUDlwaWdFZDFzLUkzTW5lSU5XY1hTdmVpQ3FaYnh3ZVl1NFFEbExoZmQ5Z1NUR3dzeDlua2Vud3o1OW1pakl4WndlX3FfOGs0VGcwRnpvcmUyT1Q4S2xhdG53bnpteHlndzhCUDNDUldsRno3M1NDNEd1N0t0YzB2R2VCNzUyYks2YUNrcHNwRW9zM2k1aTJFN3BwYWl6MlZXRGxBUWZp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNbGRtRGRVVFBKUHRHdVNUdVFHUnBxS2U5RjlZQndGYzhwRWl2RFNSRVlzZENRVFNhNTJRVW1uRHoyQ25ONVE4c1hKbjRFQ2k0UFRJbl9LTElwdWszdF9GRjlIZWZucTJHTkVfNUtJY2N3SXR4bjFERUllMU01NjkxVDdIN1YwMHBtc1VHRy1XLVlEYkxGZkNNY3FLeDNkZUpkelJHRGEwdmZHQXBsMGw1U0Y2WlB6dHU1cWdTZFZyUFpvMEpZd1Y3U0NRYjZ2cUtQM3FlS0FucEtmQ0EteTVoZThSaVNJZkFqZGkzQ0NlYjZFVVBKUFhLdA?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1811,47 +1811,47 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>de-DE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>46041.45555555556</v>
+        <v>46041.7796875</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
+          <t>("Extinction Rebellion" OR "Just Stop Oil")</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Man who breached CBO appears in court after latest 'crime spree' - Swindon Advertiser</t>
+          <t>How to turn Extreme Weather Tragedies into Climate Victories - Informed Comment</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 13:48:36 GMT</t>
+          <t>Tue, 20 Jan 2026 05:06:23 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNaHUtR2NJWF80MWp6WEtWN2JBcUx0dmhTRC14eV9KRkdLRlA2MmgwMUtBWXBib2cxR2VlSl84Wm9IbWdXNnBjY1g3Rm8ybUkzMzdfc2lMZjBTRjd5b3ZmZVJzSlNHbklMMFRvZ0ljcGRLMUlrS0lZOEhFc09vNWFJRUl1UW1FZjA1SnFfWWNzQUtCU3lOSmlHbTh4R1Zvb3lJb041bA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1FSlowQ2tKTi1FX2VBQTBXMmttUDlaZWJEUzBBRno2S0hDRjJjV1AteUZWdktWRnlLaUVnNUZQR0p5VmRTVm9nZWdFM2NRajhCUVdhV3d6eTdlZG16Y05Kc3pNZTVQbnBmbUh5NjRpa3VTWFk?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1873,33 +1873,33 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>46041.57541666667</v>
+        <v>46042.2127662037</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
+          <t>("Extinction Rebellion" OR "Just Stop Oil")</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Police reports - Watauga Democrat</t>
+          <t>Neighbors for Change: A Civic Action Fair - Extinction Rebellion PDX</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 10:00:00 GMT</t>
+          <t>Mon, 19 Jan 2026 19:49:41 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxObV84Z1huN182SFY5TEJTMmxLTjFQWmNqWk8xYTlITG1TWDZkZXdOZTk5bHlta01iTDR2T21aQ3pjNnlzclFlQTZnU21iSHFGRHhiQjdtY0ZVdGhhcEdIc3FjRi1wVWo2WVBWZTBiZUw4RHdNREljdXhHRjhiaGZUajIxNzFtYmxHejJ4MHhYTTZ0dUVBYkdFdlJBcmFOZXQzU1M0U3NGeV9qTUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE5VaDQzVmhBTWZTZkZjVTBmV05RakZ4cGthMzlvcGdmaWE4MU83YzVPclZSMExNcnBESXJFR3M4dXNySVhrVk9aNW9vcXE1dTB1S1lpMnExenN5eFVjRmdYMXhBa3h0UE5NbDBv?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>46041.41666666666</v>
+        <v>46041.82616898148</v>
       </c>
     </row>
     <row r="32">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Drop in theft crimes and public order incidents recorded in Kerry during 2025 - Radio Kerry</t>
+          <t>Two Kent villages with more shoplifters than anywhere else in the UK - Kent Live</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 08:42:20 GMT</t>
+          <t>Tue, 20 Jan 2026 06:01:39 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNdDhETmJuaTRrT0VGUWNQSDdEd1BJN3dPOHItVlhGazY1enlvQkdzb0gzczBTUWducXRvWFJ3dU94WWlPdkQwUjFGS2JlV0pYcUtjZG5kVXk1bzNQVi1FaHdHU2llMXZFWU5WVzZrQjNVMjNPWDRuTTZSWG9hblYzbEZUTS1JaGNMREtBWVozcGdSVHVEdDRHQml4YkVLSVdDandYWXVTU2V3c0NKeDhQRUp3TFhtZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNcnB2QTQxTUwyeEQwaVVEUnpULVk2RmZCcUdqVmRuS1docDV0Y0dwQUd4RWNHNzBWUmZGWlZLdWdMQWpfVUliR1VXOHBqdnJlbzdoMDBzZXVReUozX3hpQ2lQczFtU1h0U0txLWlaNGZWa04xZHFyNVM4dlZIQzR1NlNvYm80Si1MQ0R2ZQ?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1969,33 +1969,33 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>46041.36273148148</v>
+        <v>46042.25114583333</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Level City searches Spain English</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("Madrid" OR "Barcelona") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>‘Worst of my Career’—Hansi Flick Lashes Out After Barcelona Fall to Real Sociedad - Sports Illustrated</t>
+          <t>Leeds named shoplifting capital of Britain - ITVX</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 13:00:00 GMT</t>
+          <t>Mon, 19 Jan 2026 18:19:07 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE0ta2c1WTNneXFrbHB2dTJFUVI1Wkxha25Idmx0LVVVdzdZd3lDdzU1d3YwdU9ua2RKci1LZllsUGFEeENMZ2xVanV0QWZYNnBNajY4UlZqRnBwaENxYWhoc2owdzVEYmVnUDZvRzN4YmtEZm9xdTE0ZllLbTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPSE5NMVJMeUdvMjZOVElsbE1xQVo5RGUxdllQME83WkNBeFlXeVBPcTdOOWc0bXBRdVNnT1l4RnYzRWZlZlFIZ0dFUlBKdVBhN1Q5ZUd3bWp1cHJaSjVwZUhoT1A0VkttY05NenVlTEJDMzZkVW9SRlNBY2Q1MEN2QVV0QWM4QUNO?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -2008,42 +2008,42 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ES:en</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>46041.54166666666</v>
+        <v>46041.76327546296</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City searches Spain English</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Madrid" OR "Barcelona") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Patriarch of Romania expresses compassion after deadly train accident in Spain - Orthodox Times</t>
+          <t>Sainsbury's to roll out crime-busting tech after 'seismic' drop in shoplifting - The Mirror</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 10:12:05 GMT</t>
+          <t>Tue, 20 Jan 2026 00:01:00 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNMGdEb2ZxZmg0M0tYMHFDX2NpZm5VaFIxYk5DaEg1LW5ucEdlSlhXT0ExRXZScW5OV0RTR2QydXMzMXpTZ1UySkxGLVhyMFZqWmF3bklJSkRWX0VYclVrYVFicUlOWXdPcVU5S3B6NnhRRG5IVmNVMkI1eS1kc2NCOThVLUh1Yy05MDZoYnk4VjFGbmZvZ2c3UktrYXlkRXJRN3AxOFVvWEs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFB4UTZJUTE4MEhJQ3BnRUlzM0NvaE91Wk5ySjdPN1lMaE4tMEozVjBVUm1UTFN5T1AxTmY4dlgtcjFjTy1KaGJIRml2OVVyc1puSXc3SmVHRnZiM1NVQ2RZbGZmM2xuWDhNT2pyOVpmcktCbmJWSjNaVkNDYUxPQdIBgwFBVV95cUxNcHI5OEhxUUFBOVJUVWM1Mk1Mc0N1U29HT2V5TXFTbURWQmQtV0s5NHpGTUktMEpWbEhMWjBydzIwU1hOazFXRmVtYkJ4dWJSSEV3aU5wSm1lcW9DX1liaDdzYUdOM29JNmRFTFVFdUNpU2d5MTBIdEdNUGQwdk9xTHQ3RQ?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -2056,42 +2056,42 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ES:en</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>46041.42505787037</v>
+        <v>46042.00069444445</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Level City searches Spain English</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("Madrid" OR "Barcelona") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>The lion has ignited the transfer fire! Another bomb after Noa Lang at Galatasaray. - Haberler</t>
+          <t>Retail crime spikes in Australia, declines in New Zealand - Jeweller Magazine</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 11:53:19 GMT</t>
+          <t>Tue, 20 Jan 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQZFl2ZUQxV3dnNWVYNGRwNGR6c2RPMVBuU3VDSE9xQi1hdGhpcGUyZUVpWXJQbFRyRWFyNlJoSWgwZ0xjOFpoVW9kTnJscmdOQl93Q0lSUFVETDcyNkd4dlhXRGhxb0l6V24zeUNKNlVOWUo2TlFOd0o4VXRDNHJsbVdxc1c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQUTR3Y0xrY0ZORWpmY1p3d2hteTNZb21RcFlUNEpqQWNwTEhkZ1R3aVNLYUtIZWN1YkU5aS1rdk1FRl9RNkNJVzVyUm1NdUNGUU5XbXJDQ2ppaWs5YkVjWXI3NkpLMzdLNjVZcUJDT1REdkstRFNWeG1LSjVYSUpTSjFjcmVHNkRULWh4X3lCV1g3eGZvaF8zYjRpZHR1Y3FqRkZ0TjhR?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2104,42 +2104,42 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ES:en</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>46041.4953587963</v>
+        <v>46042.25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>High Level City searches Spain English</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("Madrid" OR "Barcelona") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Watch: High-Speed Train Crash in Spain Leaves at Least 39 Dead, over 152 Injured - breitbart.com</t>
+          <t>Somerset police are searching for pair linked to shoplifting investigation - MSN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 09:20:58 GMT</t>
+          <t>Mon, 19 Jan 2026 22:36:15 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNYUc5TExHbU5FVjVYbkpnQVZEZk9FQ3pnb0ZjaWFlOXdxQWpIZ192WXZ3ZFBrdU80R3dmdlFoQUVJVTUwakNfaC15MDY3NVdYM0NxaGtWS0dUTXR4ZWx2VkxFRDFvZ0ZiZlFXZWl1eDdFTC1ndjFsWmZteTlvUEZZcENua1kzalJKOHU2UGh5NXBmLU9STm5Ma0dRZmYxR2ZGaldTQ0d3VHBzN3pWeVB4ZXBmWl9oX2lZUnZOZERqVGTSAcYBQVVfeXFMTUM0VUlPUERLRXNnR2haVHc0VGlKUzQ2LTdzV1Bqcmc3TFczTnlIeUlpQjJvV1VhbDVtenFpWGFwUmwwRzltclg3a25aenR2bWNuZThRdHBhQnlma3l6TDZVMlotdHVzdnQwUm9lOGxCRTJ4SUZlN19iQXZwYVV5V2dEU1RkNjMyanJmUjNQQnYxLTBjUkNtU256NlVrLWFkQTFqWU5mWmRxSFFVQ3hGV1dtYXN4aGpTVDZuUkFadkExTjZfYWtR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNelIyQS0tajFTU1hmT3FQcnJaMGNZeUhOVUQ5bzJJalk0eGRWSWhkNHIxY3VaYnZzZDVqUk1DcnVEWjc1bm8tZ01qV2VDS1RTdWpra21PcGNBRUZVQk9NZnc4RVQyZVJjLXVGSnhhYmthSjRoaHljY3BScUxzaEFjZThkU05RM3RGNVJPZExtYzZBMFZsdTJMelBMV296MTIwM01uN3RkSGg3VUp3YngzUWEyczVDV2t2bjNSRThGcVI?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2152,42 +2152,42 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ES:en</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>46041.38956018518</v>
+        <v>46041.94184027778</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Level City searches Spain Spanish</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Madrid" OR "Barcelona") AND (bomba OR explosión OR tiroteo OR puñalada OR "paquete sospechoso")</t>
+          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Real Sociedad vs FC Barcelona - TUDN</t>
+          <t>Face of thief who stole smoked salmon and laundry detergents in £2,100 shoplifting spree - Essex Live</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 11:51:52 GMT</t>
+          <t>Mon, 19 Jan 2026 20:06:50 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOV1VUQk5UV2ozMVJhUk1PT2RrcUpleWxzNWt6WksxRXo3Mnk1TDRVTUNYbDZ4dTZVRXJ1QzQ1Umw4empGd3ZoZWRHQzhFbVdjVU5rbjE2UnJFZUJyLVBRWDFzODlidUR0VWhaRXlLa3g4SVFQYTNLQUg0ejMxS3ZlNTFCSWpEaWR3M1BZTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPU3JfNG9sWjRFLTlFeElNUTJ2LXBvNjQyLU5KQTZyMzd5V2M0YUl1WWRNVnZram1UcVM0MnhZSTBwaTBYZHZobVZSS2dIVXdGUGhPTFRVUVlLd1FxMkNrTGluckxfQjhVLV9ERUFVYWIzVF9mVnpITTRJU0FQTUszVVEyYzVib290LUVZ0gGLAUFVX3lxTE9Tcl80b2xaNEUtOUV4SU1RMnYtcG82NDItTkpBNnIzN3lXYzRhSXVZZE1WdmtqbVRxUzQyeFlJMHBpMFhkdmhtVlJLZ0hVd0ZQaE9MVFVRWUt3UXEyQ2tMaW5yTF9COFUtX0RFQVVhYjNUX2ZWekhNNElTQVBNSzNVUTJjNWJvb3QtRVk?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2195,47 +2195,47 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>es-ES</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ES:es</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>46041.49435185185</v>
+        <v>46041.8380787037</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>High Level City searches Spain Spanish</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("Madrid" OR "Barcelona") AND (bomba OR explosión OR tiroteo OR puñalada OR "paquete sospechoso")</t>
+          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Varias víctimas por una explosión en un hotel de la capital de Afganistán, Kabul - Teleprensa</t>
+          <t>Man arrested for attempted arson, shoplifting in Eloy - PinalCentral.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 12:42:34 GMT</t>
+          <t>Mon, 19 Jan 2026 20:57:34 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPSVBGTk11X2RJcnpnQ3U4QjdxWkpXWTNkR1d1TmY3V3JnRENBUWJyVV9NN3VqTE94Q29wMzlVNVhlNU5iWi1TZlpxei1DaUlmLWY0SThFVTVmM0htLTBjLWlJNzVsSXl6R1FwaDFIUVc1REl0V2ktMGpsNEJkNlZjeGZ5RkcyQV9ZTGUzeVRneTJvWmdjcUxvZDVud0haNGFCeV9Vb1RReVlUS1dOTFNqamFSbGluQTlmNFl6VWYybHlIT24xQ3BNeEI5Ri15Z9IB0wFBVV95cUxPYnJrQ2RrajEwVS1TOGNrdm9QNXd5dElLY0JBdGZfcVVNMWJva0Y4anpKdzFBM3VVM1hYVGlOektwUnRoSjk3ZzEyeDVqUFZqdGdYYlR4ZXNoX0ZOY0cwempUcU9ia29FSkpGNURPQWlla0I5ZnJmMC0wTlQwekhVN1RGaGlnOUZ6VjlPakJ3SzlFeC02YmxrY3Q3WUtRMHAtNG02VVRkTUxKWFZwYkpCa2FBRTczMEVFSGtLcWgwZTV4cXBkcTQtQTFEcTZYQnRWSURV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNOU9QVUYzMXQ0OU1UcVVCWjVMLVlqNy1tR1FRai13UW54YTlHQV80WFZBbkl5VWxnMzY0czFwVF8tSTM3QVZYS2gtb0tCak9ldVJBNUhhS3BMYV9uVF9pOEFoNTAzYTZPVGpuazY3Y2tDS2xTeUxDeWFQX2tvRWs0OGc3TE02RGVzZzZHWXJiMmJ1T2xzOWl1dVBidW54UzBvazZVTXZ1ZXFnRHhheHZhRjJkRFRaM1RPeGFpb01GX05hYTdrY1FJak0tWXZTOWNMd1FmZERWRHR3RjQ5WGZJQQ?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2243,47 +2243,47 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>es-ES</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ES:es</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>46041.52956018518</v>
+        <v>46041.87331018518</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>High Level City searches Spain Spanish</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("Madrid" OR "Barcelona") AND (bomba OR explosión OR tiroteo OR puñalada OR "paquete sospechoso")</t>
+          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Arbeloa defendió a Vinícius Jr. ante llanto provocado por hinchas Real Madrid [VIDEO] - Trome.com</t>
+          <t>Montgomery Township police searching for Best Buy shoplifting suspect - Around Ambler</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 11:45:52 GMT</t>
+          <t>Tue, 20 Jan 2026 01:51:31 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxNOGJZaDA1MUZtOS1NN2tNaVFNaW1zbjY2bFAxQl9rX3ZGalIwTkZoekxDSlp4ZUlaOGtFeVV2N0lkZWZFVl9hd3V5TE1odjhsYXFRdTM1NDh6M1pKZ3pJX2RlOHJsN1dYV1NNNWhtWUJ4WUxEQU1mTVZnUFp4SUJYeE9yaWtFMW85ZFR0YU5KOHRCZGtKc2JzNmd5NHdiVmFCS0prX2RKdlQzeWR5dWU1SFI1OXhqT3JoMS1WZVJVbmpSa1owRk1YRDU1ZTZlTmJ6RmdKbVV4ZFkxWEFJSHdPUHFHdHctc2hCdDJzT282dEY4RkFlRjM0VDJ0NW02RDV0UDZPUzdMNmUxT1pFN1JSZGxjSENpeWxidTZr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOeDQzbXhhQ19DLVUwVzE4TXdYdkdhbHJkbGcxNUFKbGx0cVlWRFloWVhybXFUYXRjOE5rNUF2T3JGU1ZlalZ3MHNCdmFlak50d0JmeWZXSXJHR0tuVWZFdWZiMGw2VWt2MkdFWUZfMDZpODloV2RxbUQtSDlLak5OVU1XbTk2NUd6MDBEaHpmUGxkSTRUV1U3RVJPcw?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>es-ES</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ES:es</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>46041.49018518518</v>
+        <v>46042.07744212963</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>High Level City searches Spain Spanish</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("Madrid" OR "Barcelona") AND (bomba OR explosión OR tiroteo OR puñalada OR "paquete sospechoso")</t>
+          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Al menos un muerto y cuatro heridos por un tiroteo en el Ayuntamiento de la ciudad checa de Chribská - Teleprensa</t>
+          <t>Family Celebrating Nonverbal Daughter’s Birthday at Universal Escorted Out Over Shoplifting ‘Misunderstanding’ - AOL.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 11:32:27 GMT</t>
+          <t>Tue, 20 Jan 2026 00:58:20 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPX2VWTjkxb2JxUFJfUS1CUkxGWXdoWlppenBLeW5zaDVmdUZRRk1WRHpLZmtORllaVFQtblIxcWMxdnRFR3ZDZ3RDSks5d3Rfdi1YZ0pNY2NxSU5tMl84dDhLZDVXQXRfMDc1bzBIbVgwamV4SHE3UVI5TXh2NHBCX1BLX3l1eXhIclJZR3ZjN0o5MjNqd0t4TlBLMTRhLXFxY0Vka3RCczI1X1VOblh1dXRuUC1FR3NwSzd5ekJVUjA4cUEtbXJlTFZ4NFRNaW53eUx2SEFUZEp4RjVhVXR6RtIB5gFBVV95cUxPZWZZdlh1QTdkdHZWajFoNWpuSlpwbWFiM1VoZEhweTUyRnY0bGxvX1dJNHB5WEdmZ2RwanF5d0thNms1dmIyckhqYm0xQjZtVVV2b1c3bS0zQnByUkI0NXNYNkZLNHhxa3FNQU9BamhsRksyRkRBUVZDV0ZqZkx6NWMxZ083MG9XNE9TVndlYTJOTzJ1YV81U0VUeGlUU25DalA2TTNYSENpWUZxR2pEX1lDemRzSHg1MVdlVVJReXNvR2owX3FzLXpxbm1iQ3prMWZwdFNoTGpKUld2MnlTVUZvTDFNdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNNkR6akZhMndTSjhMeHFycFVORENONlBqOTRXT2FTVWhNRnJWa2JhWnFNWU94aV85LXF4NFhqUnBXdlVFa0VDQ2ZNbC1IazV3Zml2eFlPcHJzS0JNbV9LYi1saGhRM05USXd0ZVVqMW1hdXVSY1NBYmQybVEzYktEN2FMVFZEbVFOX1BSTVdzTzdnT2QzdFE?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -2339,47 +2339,47 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>es-ES</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ES:es</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>46041.48086805556</v>
+        <v>46042.04050925926</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>High Level City searches Spain Spanish</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("Madrid" OR "Barcelona") AND (bomba OR explosión OR tiroteo OR puñalada OR "paquete sospechoso")</t>
+          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Andrés Cuenca, muy cerca del Como con formato 'traspaso y cesión' - SPORT</t>
+          <t>Little Egg Harbor Woman Arrested for Felony Shoplifting at Manahawkin Target - TAPinto</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 10:46:58 GMT</t>
+          <t>Mon, 19 Jan 2026 16:15:43 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNc1ZORzBpMnJDTk9MSDdBajR3NmlJUTIwdTBubk9NaXZSZVladGRfUUFsbUNkdFZvVGMwbGFzcUNNc1daMXZ3dXN3aV80Wk9pVWk5NWp5TWZhZFY0UFNBeTNPZEpYT2pyYjVVekVuWG1XSjk2ZU1vTENPaVF0S0lremVZT3NtQ1Qyd0pUdVF30gGOAUFVX3lxTFBXOUZObGpYM3U0SkM2MmpueFVnUkl4a0R2SnBRT3BoZlZ5aW16Ri1VVm1KSDl0ZGl4UGUtLUFmenVvMWhXa1g5c2pINmxDeUlacmRrbml0REpjbFJ0UlRXLVFQalp4U1VsU1dnc1lrcFFXMkZuX29DYWRkSnJyTTByQnZWWXN2NlJCcHQ0NEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxOblJYeXM4emZzajAtOUZkdHoxMFJGV1UtRno3ek94SERhRGVKUVJMRXZuZXNSSlVhZ2tSenJjQ0lFbFZZSVl4bEliUFE3cEp0Q09Kbjl5aHRaenkwSG1JU19hQlBIMVg4RnhBdk9GaVdHa25rRTB2dGJ3WHQwa19RODJmaDNicHRVM01CdkxmQnVNX2ZGaXM2VThmV1BNTmZkY18xTUhsbUlscUh4WGNYMU5mODR4SzE3cUZBWUVFdUgtZlZRUWp3Q3NUY1lMdnYyY0NfRVZoVFlMa19WdmZaX0xrSHdmVEkwMW01Vnp4VmNqQ0trM2ZV?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -2387,47 +2387,47 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>es-ES</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>ES:es</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>46041.4492824074</v>
+        <v>46041.67758101852</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>High Level City searches Spain Spanish</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("Madrid" OR "Barcelona") AND (bomba OR explosión OR tiroteo OR puñalada OR "paquete sospechoso")</t>
+          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tres detenidos por el apuñalamiento de un hombre en un hotel ocupado de San Blas (Madrid) - El Confidencial</t>
+          <t>Austin Woman Walks Out of Ross. Then Workers Accuse Her Of Shoplifting - Patch</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 09:56:00 GMT</t>
+          <t>Mon, 19 Jan 2026 17:32:26 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTXIwcWRrME52MHpiQkJTcWJobXhZSjY2OGdZY2Rma1FwbzVGeFhOcFdiMExqalB1V2p6V0lPY3lPVTRBd0NkeE1MMi1JbnBQUDBlY1ZkbWxYd1prZ0xwY2N2Z0NEdkVHOWw0cWx1U0tPUTRfT0NhaDQxZFpXeVJhVVVxN3RWMGVMYVc0TzN6b2daTENJTU9nVm1KeGRrbmJqaVVseEJGcTl5MUXSAbABQVVfeXFMTlZFYlBxeFRRenNtNGp0R3NxdzM5WkdNUWVaaThmQ3llLXd2eGZiUVdncWpfekpGWmQ5b0g4ZzI5ZXRSMTVYMllBeWZHX1JaTHZNYmNlN24wZHk5UzVyNnBYZVgzWWJOSjU3cHpnLVNYclh5WTBPUVJmbndlSl83amtING1XaWFOYlhiNE9lTU9SRlNqVjBUMXdPc1ZVWlkta2VyZDNZS1l2cXBvWkRNby0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOLTN2enlCeTdGQnBJaEJPSG5UV2VaZm1LWDd4NlNGYmdvQ1dqb0o5blZFSzltc1VBSVBxOG12S3F0RWNiVWlqMHk2VE5tV2ZNWXpOMmx3S1VfMERiZFlqVDlYZ0ZlenF5LU9fVHJ1d205UlJjdEZ4RnpvWTFOZk5IZFF6YVdwSXMxLVRnLV92cFZBSk44NWU2b3ZYZU9jdnhPRVJvONIBvgFBVV95cUxNQWVpcUJiWG5GYWN6NjhpMmpITmZCeUQ2Nkh0RE9YaVpjaWdrQWl6UG5KWVdqQVp0ZHRSVC1nTUhQVVZOQVFzUzRPaWhtVC13VExfRlY0am81bWQwaHJ5V0k0ZTZaSXdDZU93QXlKeVhyeWRTeHF5QUhOQ0gxQ0dVVEhJSU1fcl9tZDdNak01UVlMdV84WThXS0IyV3g2WEJidkVtLVdLdVNYOS14U1ZpWUtlMlRVSno3bko3S1JB?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -2435,47 +2435,47 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>es-ES</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ES:es</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>46041.41388888889</v>
+        <v>46041.73085648148</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>High Level City searches Spain Spanish</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Madrid" OR "Barcelona") AND (bomba OR explosión OR tiroteo OR puñalada OR "paquete sospechoso")</t>
+          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Carabanchel se convierte en el epicentro del cine español: cartelera y homenaje a José Coronado - El Periódico de España</t>
+          <t>'Crimes are going unpunished,' say government sources - with too many officers pulled off street - revolutionradio.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 12:21:41 GMT</t>
+          <t>Tue, 20 Jan 2026 04:24:05 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNSlY3bW5NLWI2YVFhRm1OeTZtUGZRWV80M1IzSkljcnFhYU9uLUwzSFl5UWpzNWFhMUczVVl2ekNoN0lzTTYyUG5fNmMwSkFYUU5UTEpRRVZYWktudjU1UWZybjNKdnBMa2ZDNG1JcHdIWUtUaXR3Z2hSZ3Bzd2FZOTA0NG9HeXJhUDZRTmI3WXl5dmN6MVMwZmVwSDVKYzBIbkVmdUhDSXLSAagBQVVfeXFMTW1LS1dBdnR2RVhIblUzUWpTWEZqc2V4QzkwTE9kUlE4cHZBQkRTcGFuTGgtVGdXb0ZTdHN6NzRVVFFJMTA1NmFhUmlzSlNNTUJ1N3luTncxNTlFRmdRQ2dYTlBrTmYwQ29Hc2JvaVlEa3B5dDZjRl9UdW9sbkxOXzRFNTBSdlpaeEZsWHVvcTk0RzlCU25UcmdzYmlHT3Y4WVRobVI4Qk1Z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNeWtUTFFFMHk1bUo4QnBJa3ZaYzFXam1pcmFDSlVHSTRvdTRndWJfaXBrSU9neGVJcjRPOWdsR3RXMUFYZ3dqWURzQklIV1N3dFZMNFJvN1VSVTZGeVROV2F2SjZYaGdEUEJmdjhNOVpsMElOWGo1Qi1MSnN1ekR2SXh5YnAtcy1CUXNRMkJVTXZuVzI5TDJFU3c5aTc0TERLSnI2LXdEMWNMMGZCTDRxb3RuTnQxX3djRUl4djZvRkg4Y1hjY2RTWmpCbC15VVhxbWh2TlYyUEpXVTg?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -2483,47 +2483,47 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>es-ES</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ES:es</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>46041.51505787037</v>
+        <v>46042.1833912037</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Level City searches Spain Spanish</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Madrid" OR "Barcelona") AND (bomba OR explosión OR tiroteo OR puñalada OR "paquete sospechoso")</t>
+          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Se elevan a 39 los muertos en el accidente de trenes en España - Noticias SIN</t>
+          <t>Met claims 103 arrests during facial recognition camera trial - Inside Croydon</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 11:44:30 GMT</t>
+          <t>Mon, 19 Jan 2026 16:59:31 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQblBCNnpKTXkzU3NHVGl0ek5BdkExVjRlQk0zTkNzWldXSW96dVFqcnVzWEhKQlg3bzljUUR6c3pFb0NLem9COXVYOHZLVlZzaFJlZmNvM3ZVb1FnS0djT0tQVzUxZmJRQkxOZ1VpaldhZF80Y1lDNUgycHM1RGFZZTV0NjJtMVU5a2lSdU80T0NhUnQ1YlZWT1ctNTIwVjNoYkHSAaIBQVVfeXFMUG5QQjZ6Sk15M1NzR1RpdHpOQXZBMVY0ZUJNM05Dc1pXV0lvenVRanJ1c1hISkJYN285Y1FEenN6RW9DS3pvQjl1WDh2S1ZWc2hSZWZjbzN2VW9RZ0tHY09LUFc1MWZiUUJMTmdVaWpXYWRfNGNZQzVIMnBzNURhWWU1dDYybTFVOWtpUnVPNE9DYVJ0NWJWVk9XLTUyMFYzaGJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNR2Rkd3E4UTRrWGZ2bkdTemtvSjhUU1ZhVDY3VWFpdXpqRHFheTFkYXdFVm11NmEzMTBHZWo2QXlyYjVtekExT1ZyNk11YmlFR2lBbE5mNDdaVkNpSVQ0Q1M4RU5XcnNXbVBVUVFCYzFxODFVYXRlYXVEOVZZWWM1T244RlpCOWxkQ1B3T1J3TFA1YkZmd3JHYUhOLS1MMGNj0gGmAUFVX3lxTFBhU2tkeGF2ZXpHdE1UZHJJUno0dTdaeXEyMlQtbVo2N290TFFLUDRUM0tqai1oeHdqSHNJa0RmeEQwSTh1WDZyOVlxdF95T1BHTTBzUHU2ZEN2QU9QaFp2VnFTa1ozM0V5SmFYM2R6Tk45bDhxdXg3NjZEbC1COWVFekhQZllLN01iU2lxcXVpNTEtZHBNcDY0VUIzc2l6cE5tS0o2Znc?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -2531,47 +2531,47 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>es-ES</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>ES:es</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>46041.48923611111</v>
+        <v>46041.70799768518</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Level City searches Spain Spanish</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("Madrid" OR "Barcelona") AND (bomba OR explosión OR tiroteo OR puñalada OR "paquete sospechoso")</t>
+          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ampliación de cobertura EFE Audiovisual Internacional 19 ene (11.00 GMT) - Infobae</t>
+          <t>Leatherhead : man charged in connection with October High Street assault - Leatherhead Living</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 11:18:00 GMT</t>
+          <t>Mon, 19 Jan 2026 15:40:00 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOVWg2alFFS04wVVJNNHJmcHlvLVRTSXdrSlV4NVhrZDJ2aWpSQkE4cU9oR2tKblZLMEtteERRaG5UbUNZY20yRjBKazFNNDBkeXdwT09fMnA1UzlPVTlRcTk5TlBKeFlnOGhBUUp2blUzTkFNNXJXcDFkWU5kY28xRndmcnRXdU9aUjhWNS1QV2tianllOGw2NlRBeW5oY3Bwc3k3NmZxZlhCRzIzS0lOSFhEamhmQi1MRDN0Zll2UXdsV2xIOENmalp3bmVJbWEyUjBEWkowejNtUdIB2gFBVV95cUxOVWg2alFFS04wVVJNNHJmcHlvLVRTSXdrSlV4NVhrZDJ2aWpSQkE4cU9oR2tKblZLMEtteERRaG5UbUNZY20yRjBKazFNNDBkeXdwT09fMnA1UzlPVTlRcTk5TlBKeFlnOGhBUUp2blUzTkFNNXJXcDFkWU5kY28xRndmcnRXdU9aUjhWNS1QV2tianllOGw2NlRBeW5oY3Bwc3k3NmZxZlhCRzIzS0lOSFhEamhmQi1MRDN0Zll2UXdsV2xIOENmalp3bmVJbWEyUjBEWkowejNtUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTEdLcndhaWE2MVZ4eFpBaWJ4akl0ampiRHdESFNhS1pVRmY0MjZJVWZNa3ZWT2YwcHk5dFFkMWFnUUFsNjBFNl9aTk1DaldCczlLMW9kNUZWRVVXLWVtNXZjVFctaTRxT3FreTUtMUJRenlIeFllQ2l5UXprbTdpMk9RU0FEMVhialowSkZHZHFEcXBhV1FneW9faTZWNjhaR2RwVDE3T0dya3IzcGRGZTB5MlFlUlZmRnc1Mi1Helh5X0U?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -2579,47 +2579,47 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>es-ES</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ES:es</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>46041.47083333333</v>
+        <v>46041.65277777778</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Local Town Searches Bicester &amp; Kildare</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>("Bicester" OR "Kildare" OR "Newbridge") AND (protest OR boycott OR bomb OR explosion OR shooting OR stabbing)</t>
+          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Senegal set to be sanctioned for walk-off protest in Africa Cup of Nations final - Bicester Advertiser</t>
+          <t>Man sentenced following Northwich burglary - Cheshire's Silk 106.9</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 11:23:20 GMT</t>
+          <t>Mon, 19 Jan 2026 16:23:14 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNWm8xVTBfOEFKWGdOTUQ0ZXlNcV9BVThoTE5vVmlrdEdLSUpsZEtuaUk1bnhZeHMxSXN3R3R3Mk14cjhTWkhacmJGY3RUam5vS0p3a3V5cEFFQVR4WkhOTUw0SlUzVFk1ODZ2eEUwMFB6ZXpwSXA5SDNiMTc5eTlNU0lybEFYVGg4S0lwOTA4X2lMa0xPVWh0blZycUdEaU9OZk9wRWdEVG9iYnVjZHplRDh2U2t1RnphVlNqQlAzQ0dhQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQUi1LbG9mSGZ5Qlhxb1Fzb3RjS2I4X25uSjJ4ak1DNjVMaUdFNDFFTUJHcUIzc3NTYmc5MmFSQ1dLcUxiUUtYbWNZcV9NMExZdWFObS1JQUlhcEdmMXpVZXJWOW1SbmlJdmg2UWw3ZVNieEVKUW5xSjJMYVhvTFN0WWJrQmtUektLMlJEZw?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -2641,33 +2641,33 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>46041.47453703704</v>
+        <v>46041.68280092593</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Local Town Searches Bicester &amp; Kildare</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("Bicester" OR "Kildare" OR "Newbridge") AND (protest OR boycott OR bomb OR explosion OR shooting OR stabbing)</t>
+          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sadio Mane believes Senegal would have been ‘crazy’ to maintain AFCON protest - Ireland Live</t>
+          <t>Footfall rises and crime falls as more shoppers choose Preston city centre - Lancashire Evening Post</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 08:57:25 GMT</t>
+          <t>Mon, 19 Jan 2026 16:52:00 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQUU96bS14QUhGNlByTGRFc1Fvc1kwY1pxYkxiWW9Gdk5hS1VCb0E5aHVHZGhhekVuOEZ3VlQySEw3czYzQV82OC1lQkhlSWRhbklvTVZkWkU5OXVUdFBLQVBvVWxURWo4RE80ckNnc04tM19GOG9IMUVFNmlpWXhvNksyRmhfTlM2bEI1YkZBcU5WNTBEVDRuMHJ5Vk5sc0UxckFkM1BXU3V2bi00YVJnOGhVaFUzSjZrdzREanBuUWw3VVU1ckxkdUtR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPaW5wYmQtRnRlN3ZHQlVUZGRJMGxscVVpMGJVOXRZZVgtZFRQNkkxSTNOdFk2U2xSaVpFcmxxdDladk9iUHR6XzJlVGZSTEY3eVFYc2V5VEV1MTVNVFNxcXp5VEl5cGUtR1BscGFuSXlWTkszQ1g2QTVSZXVaOUFwQjVicjZpVFZDS0M4anNScXhWWW9NY24xZ2d6TlFOMld6NFU4TDNYcy04eWx6c3RuRk5fSkpQZEFhXzhURk40eVozRzRGSUtFSUNhLVFKRVJFM1ctZUpKemc?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2689,33 +2689,33 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>46041.37320601852</v>
+        <v>46041.70277777778</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>High Level City searches UK &amp; Ireland</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Man tracked online knife delivery moments before North London bus stop stabbing, court told - MyLondon</t>
+          <t>Strange sight greets customers at doomed Plymouth Poundland - Plymouth Live</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 13:47:50 GMT</t>
+          <t>Mon, 19 Jan 2026 16:28:55 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPeHA4d19FX09CZkJSRzhIT0IxdFc1YlM3Uml2NFF0ajVVSWNrVVNNV0hhaHRDOHZfVHZUZFF3bS1JVXZJWUczOTJ1QU5BMF91eWdPSjNreFNkS0t0eWxuRXVPRHloVFl1YlZUeTk1Zk1HaVB0aFY2bmxLWnhrREI4NXhzaFdXT21CYTNDcGZGMXpOWmowRGfSAZsBQVVfeXFMTnByOFY1MkhPLVBvUEtxRThrQ3lXbDViVm5hS09NUC1KdkFUblVmLWRiNVdCcmsxb3pNcXdENWFvZGxnMmVFcnVlRm1tQzR2UzVnVzFjMmxUaDNxNHdlQ0Z1X1drNGFCQ0tUbFFCRXNfaGM0aWJsanMyR1dqbldzSl9qVHZISjRrTkozV1ZVcTIzSFJtbE1TdXZPOUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQa3hsN2FJTHVlSmJHS04xNl9oeTZOYVE3M0QwcFY2cHRBcGNFRy1kUVczTXFYMncyaWZDNURrODQ0YlU0Y3lxNTV1ZnFoR0s5MGstdXpMOVdxOEFYSnk1Rng2TkVjWFFURGkxUFlTNXc1aFZHQWNHbFl5SjEtYXA0S2RxWGp4QjlwZ2FtNVBneTQyRHpRcnR4VHBFRG44cHFpQ1ljSEIwM1A1UdIBrwFBVV95cUxPX2NKejNfLUJUMFdiX2pzUEJTYnNueE03M0trLXJ6SmpiemtxSGE2eGpFZmNJLW9QZHhzQXBHWkJwN2pJTjdPWXJ5ejNMWk9hTGVFRzVHX1dxN0pIVHFIOUVSelhCNm9lc0c4QV9nTDBROFZfZkZCR2RvS1A5QUFtZkdzQ2RSUUd5aGFaWHJsQkFEd2RSbmpTR2N5Rml5czRDYkxMSk1ZakZ2ZU5SUDRN?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2737,33 +2737,33 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>46041.57488425926</v>
+        <v>46041.68674768518</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>High Level City searches UK &amp; Ireland</t>
+          <t>High Level City searches Spain English</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+          <t>("Madrid" OR "Barcelona") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Medical update as man rushed to hospital after stabbing near Tooting McDonald’s - london-now.co.uk</t>
+          <t>Turkish Airlines flight makes emergency landing after bomb hoax - AeroTime</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 12:08:56 GMT</t>
+          <t>Mon, 19 Jan 2026 22:02:00 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQZkduaG81d0xwRUljSTRTQXVWWEtNU09OazB4QWQxSTBfYjVCRUNqaWlKb1R4emV2VndjeFJXODdXeVB1WFZoZnlYdWoyVEdEVVpjLTRmZ1M2NWMxUG5oaC0yS1ZDWmtJakFHSHBZQ2JlVnl6UU5PSkRNeWx1azZoOUtqX194Y1FfYTNGckRnVnBRM2wtSU1ZbG02YTJPRzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPMFU3dVMyd2U5dkkyeE9zeG1feFBOZ0R6bmxjcEZNQ21yVjhPMEVGQVlLYTlJUGIxTzZKVlRFcFhBT0RHNDBNM1ZJbThoYmNMblZjRWxTc1l4Sm42UjdVMXZmYjVLU3FpeWZVYWtWOUh3MkZVNEhoWWhNNFN0T3Job0xR0gGHAUFVX3lxTFA4WUVkV3d1TFF3SkJiOGZzQ1dPNlNNWkxxbURGcXhTM1BCWVdxZDh5T1BwUjRXYXJPQXNlUHJ6QUxweVVwNjd3OU5lblNPR1pha1FiZS1aSFhtd1RfSGNMb0dWaENFLUEyWkYtYW80cV80NFIyeVdhMmpvMXJNT0FXc1lxcXFaSQ?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2776,42 +2776,42 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>ES:en</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>46041.50620370371</v>
+        <v>46041.91805555556</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>High Level City searches UK &amp; Ireland</t>
+          <t>High Level City searches Spain English</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+          <t>("Madrid" OR "Barcelona") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hutch family member who has PTSD after shooting jailed for Dealz store robbery - Irish Mirror</t>
+          <t>How the water gun has become a symbol for Barcelona residents 'fed up' with the tourism industry - MSN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 13:04:15 GMT</t>
+          <t>Tue, 20 Jan 2026 05:19:25 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQaWszbzhSN1dPQXFBT2JMZEVWQU5mWVdCUUxrcW9senZCMm5ieU1wYlZuODJIeUw2VE5YRkE3S3dNWHZYd2JXcGJnRldwYmRoYzNidHU0ZjFxQ1RLcHdCT2UxcGlTTVJrUmZhQ3VVZ283TEU1UWdhZUVmdDFZLVFIT0ZIekE1YkVBTWl1bVJ3TdIBlAFBVV95cUxNUC1NdlZ1RmRWY3R6ZkN3MktUakhadVNoeWJ4bFhhNWhWS0RKbGR5azVCdUxhenVUZENBNXRVN1dwNElZNUlucDF2TUtha1VWWUloT1gtczBGajJCZHNVcHY0dXNzN0RoY09jQXFVOUtpSnRabl9UZ09lNmlySlFVTmVvSnBvamJLNGVWa0VyZHQzTTNC?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gJBVV95cUxPek9DNzdVYnBLYWpLT2Vmdzg2WEdMTjNMUDFPZTNic0lwZkJDd0Z4UGg4M2EwUTZIdGw2VHJpa1BodndUbHM5MG9lb1JjZk5ERW91WGhtMHBFRHpWRkZuQmZlQnB3NVUxOWtuMXNtVDltMGlKVVY1OV9PM0ZXelNTblVpc0t6eFZlcGpQdndJVDVoRDlfTllEenpiVFJWNno4S1ZreWg3ODNGRlk4aGU5Y01DOUNkdjYwZkh3MlBJbVRTNzJvd0FhNzNBcXR3WGZ0TTAxQ2xpbndyT1RnU3RNM1hPYjN4a3NzdnpPWEdHT2E2V2p1bm55encwaGFCMnBmT3V6cUtOci1JS0VBZG1mYzhIUVUtVlhVUHZxRDhVMzBxZ05LWjl3dEozQ0R6QVVTVkJ2VXdQTnY2dWRrbktsbkVjTl92UEhFeWtRZGtNVlBDb0o0TXk1ckx1SWF5RktPenEwRHpKYWNiWm9xZVJqUUNB?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2824,42 +2824,42 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>ES:en</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>46041.54461805556</v>
+        <v>46042.22181712963</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>High Level City searches UK &amp; Ireland</t>
+          <t>High Level City searches Spain English</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+          <t>("Madrid" OR "Barcelona") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>One killed in Czech town hall shooting, gunman also dead, police say - The Straits Times</t>
+          <t>Olimpia in Madrid, Poeta: “We face a very hot team” - olimpiamilano.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 11:52:00 GMT</t>
+          <t>Mon, 19 Jan 2026 15:36:00 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPQ3NqTld3dGRKUTFzUVBNNVRZYUs3a0pGdmlzR2c3eXdyMXlIZ3ZaZGtlUllGSU1RLVlIQlhGOTV6Q2dueXI2Unlqel9zaVJmN3g1V2hQMWgwWFNod2ItNDA3S1B5bnlIUlR5ZS14ZV81NFAxM1d1ZTJ2Z3VjRVFxSE91S3B4dUhLRTZ2aXZFYkdrSFl6eEFKQVNhc05JYUx5X1ptZWJ4NlUwYlpk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQSWZCRGxjMi1lcmVjWlV1aGlyeERPeFMwTnBTYUROempkbFhqa3Qxa2ZCNkx4UGUtWlU5RTM5TkVFVDFBQVMzaWp2WDZhWEhfNjVFZGtOalhCUTljMENDSkhIMWdpU2JYSFlFeDh1RGJMT0RrSjBxVWhiQWR6ak5NdUtiVjAweVBC?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2872,42 +2872,42 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>ES:en</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>46041.49444444444</v>
+        <v>46041.65</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>High Level City searches UK &amp; Ireland</t>
+          <t>High Level City searches Spain English</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+          <t>("Madrid" OR "Barcelona") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Man Rushed To Hospital After Hartford Shooting: Police - Patch</t>
+          <t>EU Pushes ETIAS Launch to Late 2026 While Spain Accelerates EES Roll-out - VisaHQ</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 12:15:10 GMT</t>
+          <t>Mon, 19 Jan 2026 20:27:42 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNMU9PdGZEOGxvMlBwcm5IdXlOdm1GZU1Ebld4RkRiSFpXZnQybnRqczFENDVGbEFjUkhZcjloQzNEVW80R0tZSmJ0emZFbldBSTVkZlBVeTBlclVjOU00TjJkX2ZkTFlHREx6UzNxbUczb296aHRIM21QYVhZazJwZTBCRTM4Y0tRSjA2RzBGcmoyazTSAagBQVVfeXFMT3NjOUVLWm4yQUliLUctQ3RONEUtS3VnYldJcG92c0g1M3ptSU92UGp4cHZMM2tZZzVxMUFwTHRpcDVjYUxHc0N1RFJnOFFtRmY1X2tYbWFSZjg4dFRWNlE4Z2NmQUhrTVVnOGw3aXVENExTZmhqM1FuQzNPUTY2T2dlTzZJQk9ZcHQ4TXdxd055TUthWlZ5VEdTYmRjd19YTUptb3NjWkVP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTzhkMFRBUE9rZ2R2NENoOE5tZ0RlcjctdS1kNFhVV0g1N1lDTmdDcE9ZYUMzSDZUSE5vdVY1WnRRZzFTMjY3alRQY1k4VEpFcXJmR2Z6TEVxXzg4WFkwYng4VXFyNjVUSENUWXp4Z1pFdnlWUXFYbnBpek5aNjU5dmdrQXV6QzFneHVlU2dxNWpVX0huTWExZHFSclB2SndHYlhXRUp4OFZBbEhINks3OS1FU21wUQ?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2920,42 +2920,42 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>ES:en</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>46041.51053240741</v>
+        <v>46041.85256944445</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>High Level City searches UK &amp; Ireland</t>
+          <t>High Level City searches Spain English</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+          <t>("Madrid" OR "Barcelona") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>London Lions take down Sheffield on the road - Guardian Series</t>
+          <t>UNRWA: Aid to Gaza Remains Insufficient Despite Ceasefire - AL24 News</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 10:40:48 GMT</t>
+          <t>Tue, 20 Jan 2026 05:37:28 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPZkNMQy1vYmhLX1g3cEI1OG1lTFFoZWtWNWdOazRPUTk2bE9hZmpQV2VmZzNGWWxWZkJZR3RkT3FVLXZzV3JkcFp4Yk50SWlyLXhDZ20zVEU4SDlDeklGM2JtQm9jUEtnZW5JSzJnS3YyNUFPbWcyaXRrZm1BbWhxXzE3bEM4MmdSNnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQS2JpeVdnY05lMVFtVFBRTVNZcldZbUxJakFKRllUMU9hS0dDNE5vV1lEdTR4WktPZ0ZBVW9EQVVQYy1rbHpZWEVmUUFrVFhKcUI2VjhIQXd0WXI5OWkzWGFQQ1dVLWJnVG9jRWowWlJfQnJEenhfeFlHVnM1ZjA5Nk5vS0ZDeUk?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2968,42 +2968,42 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>ES:en</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>46041.445</v>
+        <v>46042.23435185185</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>High Level City searches UK &amp; Ireland</t>
+          <t>High Level City searches Spain English</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+          <t>("Madrid" OR "Barcelona") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Celtic transfer bulletin as David Datro Fofana on brink of Chelsea exit and bomb squad Bamba 'for the off' - Daily Record</t>
+          <t>Good news for Arsenal as Saka returns to training ahead of UCL showdown against Real Madrid; see post - MSN</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 13:14:00 GMT</t>
+          <t>Tue, 20 Jan 2026 02:47:20 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPdEJpS1VERHdDX2lXbTZMZzZrbS1VS1FrZVlxaXd6ZE82QW9qWEJkQkI5Qzl3TjBIcFNjMlBFVUNja3dUNC16WUVmZjh5RFlEZ0VsV1Y0Nlg4X3F1R3FtOG8wR2NLWGdJWTgyWGFwSWNPbHd2WXhIa080Z2RHampYOGpPaFpreWo4QU1XTVM3RnpwMHZCWWpSS2FuS2FPc2E3R0JLVVJDZ05VX3RoTVFSVjJyRdIBuAFBVV95cUxORTItdUJYdlFzMm5vd2daZEpTOVdVVjBneVBUc3lXZVRHOFVnMWIxS3VLOVI4UzhwZWtEYUlMVTBFdW1UbkphNkNlZWd2U09DdTdOazdGcjQxUFpHdmZCelJQUHQxYlJHS1ZqN05BejZ3VXdfY0pOOWxGeEFCVmIzOG9SbDVPLTRnaU9XV2FKV3FKY0sxeFhyTnUtMEVVakJhLXdTMzctZGphUTZIMjU0TUphV3RuclQ5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigANBVV95cUxQNXdEbEdnX3ExV3lVVDBHNWdybUpsWXRxbzVFc05FRGhKWVhzR05EUWJlTnp3MHlHNi1EM3FBamlkNzVlc0tGbU01RWt5cDdqNk5ycnFxSnFVOVhGTnc3Y3FIM1o2bWpBY3ZUVUlVREtxdmIyTUVwVHNOVGR4ZVNydDFhWW42ck13b3RfZmRjN0lVTjY2MTdQOXlTUzB0UUIyOHhyckpsb3pDVnFfY2xXc3FWNHo5bGxnOGZQZ2tKVHNlalh1MjdWdm9WdkIwTmhCcHNTenlvcEkzSWNqSDhRUzRMbWlDRzdwNHh2NTNZUmJTa0dnaWdKU2ZBSDZ2NkdVRkt6R3ZZRFBiSUZUQzZjSm95UzBldXN6U1ByS0pmWi1kRjFMbmgwcmpqVUk4VWRPdFo3Zk9yVmR4ZXVCVkFUbXp3dnBBM3UtbHh4anllSzIyOWczRkpjRXoyTmNjWUg5Tmw2RGdrandhaFA0YmY3NHRtd3hTbmNfNWhEOTB4VmM?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -3016,42 +3016,42 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>ES:en</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>46041.55138888889</v>
+        <v>46042.11620370371</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>High Level City searches UK &amp; Ireland</t>
+          <t>High Level City searches Spain English</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+          <t>("Madrid" OR "Barcelona") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>'People need to be remembered' - Call for North Strand Bombing Memorial to have names added - Newstalk</t>
+          <t>40 dead after high-speed train collision in southern Spain - The Irish News</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 11:44:04 GMT</t>
+          <t>Mon, 19 Jan 2026 18:49:56 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9Oa2RSb0dGcHg1Tl9mQjNOc3VHa2hzNnozeTVKaUpYdDl4QWh2cjBlU0JCQXI1VHlmbzNZYmRzZkctaV82UWdURHp3ekJGTnBlU2laMndaMDNfLUhWckFta3g3SU5mUFNpdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPVklMd1JmRFp6QVYzV1FhNDUzME5SbkhTcjFUVlg5enZXY25QTGswbG9ERGJoTXVWRkhfVEd3Q1BMQWdyQjlJNl9Wc0NUQVdoejMyWVNtazYzX09mblNIYWVzMDV0QzBMSGhtRU15QUY5OWUzS051N2wxVTJXZWlQZGFkbjA3VFZZVGxVN04walA2bHVfeHlPVU9qVGMtX0lsQVQtYWZ5MEZ4endtMnJTbnJPWmJBSFkxWG9Zcm1OZHY?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -3064,42 +3064,42 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>ES:en</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>46041.48893518518</v>
+        <v>46041.78467592593</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>High Level City searches France English</t>
+          <t>High Level City searches Spain English</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>"Paris" AND (bomb OR explosion OR shooting OR stabbing)</t>
+          <t>("Madrid" OR "Barcelona") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Alison Saar by Melissa Joseph - BOMB Magazine</t>
+          <t>Spain to Activate Biometric Entry/Exit Scanners at Gibraltar Border in February - VisaHQ</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 12:04:45 GMT</t>
+          <t>Mon, 19 Jan 2026 20:53:12 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOQ29oRTcyNHdENkVZb2gtRWtUQ1pza1ZmWXNoNk83bEtQX2J3OVkyMEotc1pWOVBQS191cG41OFNGVllWM1NvZnV6ZDRtdnRuSFJ3VnoybU4wbVBYSFI0UFVLdVlVUXlhR3ZHODZ2a0pKd2JYSXBjSklZMC1abzBpVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQRmFrcHBDQVZla242N1daMlVkNThwWlBwYzAweXJYMllja0dqN0JFR0I5ZWFjcjRDYXVDTm91QmFzQkZYdXV3Q1pqRm5GTDRyMmJyYUs2eTdMX2tXbm5HS2huSTNjemw5LUY2YVZ6Vk01cWNVRjlNbjZsNlFpMmM3b2FJdFFuWlpfME9EQ1ZUQ0x5UC1jNXRuajRneFpVSEd1enZkWnl0N1B5ZllHS2VMSWI4WXp6TnF3bnhnMEVR?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -3112,42 +3112,42 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>FR:en</t>
+          <t>ES:en</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>46041.50329861111</v>
+        <v>46041.87027777778</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>High Level City searches France English</t>
+          <t>High Level City searches Spain English</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>"Paris" AND (bomb OR explosion OR shooting OR stabbing)</t>
+          <t>("Madrid" OR "Barcelona") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Morant returns as Grizzlies roll past Magic in London - TalkBasket.net</t>
+          <t>Passenger jet is escorted by warplanes and makes emergency landing in Barcelona - MSN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 08:30:15 GMT</t>
+          <t>Tue, 20 Jan 2026 00:32:02 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQRmI5ZTV2S1BSRWVYMVE3b0s1RDE4SE9VYkZvaFZ3ZmRsUGJVY25URUgybFZkWm1YbExOSnBza1pidGxMaDNscXRHdzFfOXkwT0lzaHFWdnRhNFVQVFk3Sk9xV0xUeW9CTzhuUXZMZ0dyM183UHgwakRrMXBnSmFmQ2FlY2ZBRUljdllVZW1nblTSAZgBQVVfeXFMTW1DZ21ZOFBMQS12Q1I1TG9sS1p0dGJrc3BneG1OLXZ5dHpFaFg3U3hPVHE3WjUydzNpT3k4TmtOMnFkNUUzaXN3NXBNT09GV1lkTDdEekFYbVFMZzFjdENNcEpEN3JmZExIVGdwWndCNVg2dmV1YUxPcHk0NnpxaDk4TUZYUnNNRk5pNTdwN1lzd0dRRTYxN1g?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gJBVV95cUxQWjlUMTNWTmdSSHhydkd5U05UdFRRd0RyLUxsVFRDaDRYYXowbEVpS252RkRjbHQ1NDdJVzgwRnoxVFU4UVBPYm9Fa3lrTEI0M09LYU5kc0dsOWJFZ2c3TWxVblJMSGNtYUdxenlXSkNTa3VzbXBUWGQyTjMzdWRzWGYydlJDVFlUbm13eGF4MWsxUDlPYmJrVWY0ZEV6bEFKYmlWcjdhbmQ4NU9IdUFFcHRhSFlLb2dIWFZOdDhSMVZYbGlobFRVbTVPWjBTbE1MSU9MQVdFSVRUbzMwWTlIa29Hc0tvamNmWXBFWVBkc0htUWczUEZVZEVWTlNKcE1xc1pVNTVVMWU2eWJEVGdLRnN3dEZTZzY4SU9hMExSOFF2R3RpdVZja3RFeDNXR3BLZExGaWdXMll2dVlZTkhDaGxCLXhpMFpfbU1pSTBPdk94TUJNc0RlRVdkTEk2QQ?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -3160,42 +3160,42 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>FR:en</t>
+          <t>ES:en</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>46041.35434027778</v>
+        <v>46042.02224537037</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>High Level City searches France French</t>
+          <t>High Level City searches Spain English</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>"Paris" AND (bombe OR explosion OR fusillade OR poignarder)</t>
+          <t>("Madrid" OR "Barcelona") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Le direct - Paris Normandie</t>
+          <t>Passenger on first BA Concorde flight donates mementoes to museum - Newswav</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 12:30:28 GMT</t>
+          <t>Tue, 20 Jan 2026 00:21:21 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBoSWU2RFVnZXdPV0Q3TVJZeF9UUUZra2MyUmNVa1BBVmRNa0tfa2hrMW13TnFmWlcyWTg1ajNJSFhMNlFvMTk2cjV2cVlQU3AtVWFvSkc5WXp2WklxeUUxMndDYXJnZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQTm92VkxLQmpCRHZKdC1xdmdHYzRLMXdocERjOUg2cHdXbm43SXZVdVE2OXI2X0VHWkNERlBoUG5mQThWdVRfNWtXZEJXVlg0c2pFT19FSlo1VW02bFBXZ3dJbG5wMXQ5SnBFTWlXQ1ByM2duNWg0U2EzQThvOWg1dDVuM1ZxTEZESWZOX2FOaVR0Snh4VjZWU25zN0RQekYxeGJkczFLUVVNdw?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -3203,47 +3203,47 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>fr-FR</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>FR:fr</t>
+          <t>ES:en</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>46041.52115740741</v>
+        <v>46042.01482638889</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>High Level City searches France French</t>
+          <t>High Level City searches Spain English</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>"Paris" AND (bombe OR explosion OR fusillade OR poignarder)</t>
+          <t>("Madrid" OR "Barcelona") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CAN 2025 : après une finale dantesque, explosion de joie à Dakar - France Info</t>
+          <t>Lion has stepped on the gas in the transfer market! Double bomb from Galatasaray. - Haberler</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 12:44:29 GMT</t>
+          <t>Tue, 20 Jan 2026 05:40:54 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQV2lDTi1PN1ZUdlVaR01NY1hoenFLZE1oamxoaVRzQjJOQ1V1U0xCN3RVbTJ6Y0h1S2JEcDZ0dmtpckRGMmlaeHF4Ym9KVGpfRzZ4RTlLVWlCeGpVUVFIOFVvSkJmZWMtRkFVamVvQnZFOHF3YkFzZWhHZnM3MTBzcGp3M1RFdFZ5clJPM0tHV1Y4UGJLRzJLempsWHh0Vzhma1poWkk5WGVQVHdIdDVTbEdrbndzYjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOUHRpOHJaRE15REVSRlJNeWM4aVVPbTJtbURHS0hFc3hQeUxGVGRNZDdPa3Q4RVRMQ2FveGRmQkptS1ZRWkZHbWl3VDQ4YUZmalZEMjg0UVlNWTctSFhOMUdZVVZ2c3NUTkdvWTNBSWZLNGhFcDVnU3FwaFNtV0FobEk5cUphdkRIbGlz?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -3251,47 +3251,47 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>fr-FR</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>FR:fr</t>
+          <t>ES:en</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>46041.53089120371</v>
+        <v>46042.23673611111</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>High Level City searches France French</t>
+          <t>High Level City searches Spain English</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>"Paris" AND (bombe OR explosion OR fusillade OR poignarder)</t>
+          <t>("Madrid" OR "Barcelona") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>À l'Affiche à Nashville : la musique country, un genre en pleine explosion (1/2) - France 24</t>
+          <t>Edu Aguirre drops the bomb after Lamine Yamal's offside and exposes VAR - xcatalunya.cat</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 13:39:29 GMT</t>
+          <t>Mon, 19 Jan 2026 16:00:00 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxPR01ZUlp2bTc2RkNxcHpwMkxVZHg0MEVZYldCa1VCVFFSam9zMjRSVmVFa2VuQWMyZG1FdnM5ZF90eFdtd2tuVVpLRGV3LWZ1dFU2WnJ4MUlsdmNjRHVjblFvZHFQLXFwMHZ6VThKUzRtb0kyVDZjSDZ1VWJnLVF2YmZMSG9xR3lrMjZTZlV6VE1KTVByZUp6enE1c3owQWhNVHRvQ2dvMTE4U0lBRkhDQzJ2SEctSUc3cGpaWWJoZVZzcEV5ZFB1ZEVSZzhCZUlOWkxIS2s4a1RYUXVOdjhEZFZqNFNuM3pUS1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOXzNIWnNROTVoYzNmX2t1WGxfR2NzTklVdVloejk0Q1VxcTFlX2Utb0hZSlBuRG91ZGdQVEQyQ2E5UHRKRGlwM181bmFibXNGOUJmSzJZVnRSUlgzRVJQbFIxUE5hdGZSWFZOVVFsWnRkMUV2aFd2OHpXVTJ5SG53MHpfT05lV2hWWFpBdmN5MURyS0J5YnJ5VkFEck5mZw?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -3299,47 +3299,47 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>fr-FR</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>FR:fr</t>
+          <t>ES:en</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>46041.56908564815</v>
+        <v>46041.66666666666</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>High Level City searches France French</t>
+          <t>High Level City searches Spain Spanish</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>"Paris" AND (bombe OR explosion OR fusillade OR poignarder)</t>
+          <t>("Madrid" OR "Barcelona") AND (bomba OR explosión OR tiroteo OR puñalada OR "paquete sospechoso")</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Europlasma, Riber... les valeurs à suivre aujourd'hui à Paris - - Boursorama</t>
+          <t>Hace 25 años | Roban cien millones en joyas en la calle Barcelona - El Ideal Gallego</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 08:45:00 GMT</t>
+          <t>Mon, 19 Jan 2026 23:05:00 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPOWxGbzhTeGYwRkE2eXBIbnhWWFJfQXNPYzk0TGZzaF9ydnF0cGRTcTc4UXFUUl9pMV9penk2ckdndzJjSUlIQXpVNnR3ZENhdVNWaXJlQjhPV1RrTWszcjMtSGc2TWIwZTRBOVlOVDFVeVc2aXlaR01MVnA5OXYwY2g5dVhDTF9PUGF1bW1BZms1aXYwYzNWX2hPUGpOODdfZ2t2aV9pbkptZExhUHp0R3dJSnBwLXp1OTZxYU1GRVFydDJiMTczS0J0TEJYS3FuVkhudGV30gHWAUFVX3lxTE85bEZvOFN4ZjBGQTZ5cEhueFZYUl9Bc09jOTRMZnNoX3J2cXRwZFNxNzhRcVRSX2kxX2l6eTZyR2d3MmNJSUhBelU2dHdkQ2F1U1ZpcmVCOE9XVGtNazNyMy1IZzZNYjBlNEE5WU5UMVV5VzZpeVpHTUxWcDk5djBjaDl1WENMX09QYXVtbUFmazVpdjBjM1ZfaE9Qak44N19na3ZpX2luSm1kTGFQenRHd0lKcHAtenU5NnFhTUZFUXJ0MmIxNzNLQnRMQlhLcW5WSG50ZXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQT1g0ekFxV2d3ajhNODZyRVlRWFRNeGVGNjg0TVlzMTA0Y0M3S1ZCejRmLVRzNzFSYlluQnFvdWVReXdBVXE2bFJKbUJqZ2ljREE2RXAtQUVFS3psajFldHZwTkV4anMtc3Utei1Kb1dBOHhIRnZIOEp1aHFJTkptWVFZOG9vb0NxbnMxX01GY0hNWGUxMXB4OUwwbVpoVll1eDNTSE1HbkhzUnV3dzZzaWp0UnpyUkdoNHgxdXdCSnFoVDZm?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -3347,47 +3347,47 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>fr-FR</t>
+          <t>es-ES</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>FR:fr</t>
+          <t>ES:es</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>46041.36458333334</v>
+        <v>46041.96180555555</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>High Level City searches France French</t>
+          <t>High Level City searches Spain Spanish</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>"Paris" AND (bombe OR explosion OR fusillade OR poignarder)</t>
+          <t>("Madrid" OR "Barcelona") AND (bomba OR explosión OR tiroteo OR puñalada OR "paquete sospechoso")</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Un champion de Call of Duty alerte sur la dérive des paris sportifs - Esports.net</t>
+          <t>Al menos un muerto y seis heridos por un tiroteo en el Ayuntamiento de la ciudad checa de Chribská - Teleprensa</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 09:35:49 GMT</t>
+          <t>Mon, 19 Jan 2026 17:07:30 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNNXg0eEM1NW9SbUl2cHJrWDNvTW8zQzBmMUQ5X0xUNXdVTXhaSHI4dlVVZEM5WEV1UFZvWGFFdE0wTy1scDNydDBJdTVxZ0diU0tBcjBEaUJKVDh6Z0NMTTM3ZTRLYmQ0RUJRZ1FLTlpaTDN5cmFPTVF6NlAyRnhoWm80SjBfN2xxNTRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPR0pHTVVZdHVMejFZTGZ3SXByazNaUXA5S0R2VmF4MEFlTUEzdVg1OTduNWRRalZwYk5qRXhidFhFc3Joby05dUpUZHFkV21uaVlnTFQzZUw4NnhIVzZCRDlGdW5HWnpYQUhjSkJSR09wWjYzVjlfS3N0UmlOXzhqbVRRcDI1eDNDemxpejcxczBlS0o5LU1STEdTa2FjZC0tRXlidmZ1TldBNDdsVUFGVjJxU183Z05taU5BU19pRzNNSW9SVlJZT1RrQVVqaTFGcDJHZWNIdUNlRmUxQ1HSAeMBQVVfeXFMTnBZdmZhUnlTWHVKb1JZV3VYeUgycDNGTkU5dnRjMGRYNmNWbHdtbjc1WVJFQnNncFk1YkRmQmxSWGMyUlRoVU5OdDFxVFdMdzF6ZFhBQzk3cnN5SVJURVVpaS1BbENlUk45R2tzUUkyeDBOSVUwbXIzSUluMnR5cEVNWXgya2dvdHNvQUNBNFUxMGhodkYySzk5ZzVCZUcyWjh3bUs4ak93RGtkQzRqT05acTZMb0F3Q3RUdzBJVmdZUGFYMzl1ZkJwQ0lMa0dEcFBzVGZKX3JQQ3NYUjlUQWEzTXc?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -3395,47 +3395,47 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>fr-FR</t>
+          <t>es-ES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>FR:fr</t>
+          <t>ES:es</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>46041.39987268519</v>
+        <v>46041.71354166666</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>High Level City searches Italy English</t>
+          <t>High Level City searches Spain Spanish</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND (bomb OR explosion OR shooting OR stabbing)</t>
+          <t>("Madrid" OR "Barcelona") AND (bomba OR explosión OR tiroteo OR puñalada OR "paquete sospechoso")</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>UCF vs. Iowa State (Jan 20, 2026) Pregame - ESPN</t>
+          <t>UEFA: FC Barcelona anuncia fichaje BOMBA; Joan García firma para las próximas 6 temporadas de Liga de España - MSN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 09:54:39 GMT</t>
+          <t>Mon, 19 Jan 2026 15:56:59 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1FRHFWRklnREZmc1hfUTBMVFY1R1I5VmJxNXNxSlNWM0hEbGFtM0hrbDlSdUJfamNHVng2MEtGa29mSjlpdGUxWWZEUXctLUFDN0VvX3NwVXEyRmlUTzNmRzhvaGNoaFc3bXEza1V6bTFSNjBYWDdqZGVOUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwNBVV95cUxOaWZmR19BZ1dRUE1kR1ZLYm96VmNWX012TXdZVTROZ1VYX0ZuNkVjc0R5T05sYWtRMWc0TnJpU09RSEdwM3dUN1M5WUxjYnJocVBOVVQwdlBBSXY5ZV9lSmZYS2dQVjBDWXlDU1h2TU5hMU1CVTRhdnlqTWxpZG8tLVI1U3lXOVU2LWJFVklmcU9xSzhacDJDTG11MWRIM2k5em5UUXFOb1FXRENhanFZMWlDbl9VNkJrSm53eUFldE9HcHoyaUNvLThkUXh3Y0drYXRyQUZCQzMyMEtaWVlmaFdKZUd4UGczSWVWd19oMV9WT2xQbXpqcFlqbEJNcTNYa1BreC1BNldWUFdGNmhOb0daZGNTMU5nWFVWejNOT3AyVXBwdUFjQm1XRU12RUY5aVgzU2tfUTlzaUwzTHNmaXluaXE2R2J4ZmRobnBBZFZHUEJIR2ktSzJ3WEhuTTNXT0RST2hRc1RJUVM3dm9ld1hWb3o3WWw4MUl1X1R6TTFrRVJhU2NCSkN5clRFa0hTangwbjhFV3FxN2c?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -3443,47 +3443,47 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>es-ES</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>IT:en</t>
+          <t>ES:es</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>46041.41295138889</v>
+        <v>46041.66457175926</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>High Level City searches Italy English</t>
+          <t>High Level City searches Spain Spanish</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND (bomb OR explosion OR shooting OR stabbing)</t>
+          <t>("Madrid" OR "Barcelona") AND (bomba OR explosión OR tiroteo OR puñalada OR "paquete sospechoso")</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fullkrug scores as AC Milan edge Lecce to keep heat on rivals Inter Milan - TribalFootball</t>
+          <t>Al menos seis muertos en una explosión en una acería del norte de China - Teleprensa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 08:33:48 GMT</t>
+          <t>Mon, 19 Jan 2026 16:42:26 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxQSXN2dTl5OFNsN2VJUE1sd1RZVmUwN01JRU1xQ3dsakZWaGJNZVYxOTZ6UnZhT1BqN3VxRXB1WHczVjBDRmQwcGZocnd6anVaWHdHNHVLcksyaUU3NzlOSUc0MDdKSGFLcjhjMHNSZzJHeS0yWWpweWhuOGJraXZDTUEzUGJLdkpSU1p6dVhnSGhMQkd1cjZHQXNMcm5xQ214aWVXaDNXaUs0Xy1ObTQ4MC15ejZnN2wzY05fV0VtbDhSUU9uUmxRYjZxU3Z5VDVtbC03WDR1R21uWEFkTFFDNEYycWpKRldRVjI1cnZ3QmxEUmhaZ3hZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNSVRJSnpubUF3Mk56V3FZaWo3MGpiR2ZIdk50aV80NkVBUUlGaEFwbmdMRGowN0FHSy1idG9uYmpmLXAxeHhwdWNWWVdJTDBOSFlRamFpYmtfMXFTSTFUWHZtYVhyTzFfS29uLTVIZXpaaEdjNTFhRmN4OEs5eXQ4Um9oTVY5azZPS0hINnl2eEdjLWZLRy1ZRkFYRHJfc2xXLVFiM29ucmZoNTNoTzk2VnJtT09iN3ZuVWpGMXJVWmlsQdIBxwFBVV95cUxQbzdYQTdhX1FEb0tMUlBvNElzUWRmcXY4QmktWXB1X3I0RkQ0ZllYdVEyckJaLTdYSWJwUlhYSGNSSndkdjdXbTA3UHhqU0VtUkhSd2hsbko0d0xrOEprYjM0dkxVM0puNEJ0MTE2SFJFWC1WWWtLV21BUlR6QTF5WnpZY1JEVXlvZGRUWGhYaWN3bVg4M0F2NWFCNWJoU0MyQmxFZ0RNVlV5MXF6M0hUNWdnYTI1RmRiUjgzQVpManREaUxIUnVB?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -3491,47 +3491,47 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>es-ES</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>IT:en</t>
+          <t>ES:es</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>46041.35680555556</v>
+        <v>46041.69613425926</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>High Level City searches Italy English</t>
+          <t>High Level City searches Spain Spanish</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND (bomb OR explosion OR shooting OR stabbing)</t>
+          <t>("Madrid" OR "Barcelona") AND (bomba OR explosión OR tiroteo OR puñalada OR "paquete sospechoso")</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Google Adds “Answer Now” Button to Gemini for Faster AI Replies - Windows Report</t>
+          <t>Lucía y más jóvenes se unen a la "moda" de ser cristianas: "Yo me reenganché por mis amigas cuando estaba en Bachillerato" - El Español</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 12:46:28 GMT</t>
+          <t>Tue, 20 Jan 2026 01:00:00 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQclZ3eGtJM01tMFFiTFB2ZFEtOW1fcE8zcDdaRE5uWjZfR296Sm5fYnlMeUtEVnFCd0hfVHdLa0g0OXdpNmd3ZHpoLUwtVk85b3MxVTBROWNqazhlekFYYzRKUzFRX2FMZnFwLWJicDZQVlpCVnZ4X1FiVVJYcEREVDJzdy1VY045MXUyOVNXd2Jvdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOOGJicnZFZEVHa3lyU3o4Wnh6eGs4dF9FTUtBWkE5SnpXZk1IT2RMVDgtOWtxMW9oalpBZ3lFWmpaUjFrWVdaV3pkS3lvcm5wY1I2aFdmM0FVZWRHS2RwTE9BSjlHVW93a1QzNHlIQllMa0VVZXZKblVNd1d3RmNwT1RoNlFqNVl4ZjNWelZndG1vWDM1WlI4VGVtQjhjejJSZUtyVzhXNzBqMEVnaHM5UFV3VXN1STQ1UlVETVF5OHE1Y3V5OFhyUVc1SEF2UUU3amNPdklsUmvSAdgBQVVfeXFMTjhiYnJ2RWRFR2t5clN6OFp4enhrOHRfRU1LQVpBOUp6V2ZNSE9kTFQ4LTlrcTFvaGpaQWd5RVpqWlIxa1lXWld6ZEt5b3JucGNSNmhXZjNBVWVkR0tkcExPQUo5R1Vvd2tUMzR5SEJZTGtFVWV2Sm5VTXdXd0ZjcE9UaDZRajVZeGYzVnpWZ3Rtb1gzNVpSOFRlbUI4Y3oyUmVLclc4VzcwajBFZ2hzOVBVd1VzdUk0NVJVRE1ReThxNWN1eThYclFXNUhBdlFFN2pjT3ZJbFJr?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -3539,47 +3539,47 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>es-ES</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>IT:en</t>
+          <t>ES:es</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>46041.53226851852</v>
+        <v>46042.04166666666</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>High Level City searches Italy English</t>
+          <t>High Level City searches Spain Spanish</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND (bomb OR explosion OR shooting OR stabbing)</t>
+          <t>("Madrid" OR "Barcelona") AND (bomba OR explosión OR tiroteo OR puñalada OR "paquete sospechoso")</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Allegri is back on track. Füllkrug, a decisive move. The alternative is Milan. - Quotidiano Sportivo</t>
+          <t>Familiares de jóvenes asesinados en protestas en Venezuela exigen a la CPI orden de arresto contra Maduro - Confidencial Digital</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 08:42:46 GMT</t>
+          <t>Mon, 19 Jan 2026 19:53:00 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOVHhidzNNdWxqUVo4VjZwU1NsYnI4T19XRW1lRUFnTXFiSXEwV3g5RXdmVllrakRrcWk0d2t3OVFCdzJyOW1Td1o2aVVhblBjRUoyVW9kU1lkemtqR1BhMEQzN3Q5TlFtTEhSSmpxS0cyeXZBVlJxZjY5RFpiYmFwOWZDc2xOOGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxPQlIyOUVBTVVoWmdrNmxMbTZKXzZocjRrbXZ1NTFyaGNERVQ5dGVrVlAteWY0M09QOGMyMHlWTC04eU9NWFZoR2JYWTQ5M3FtdUNSRzFmdmwtbmZTNVpIUTVXTE42ZlZBaGtlUWVmXzc3cUVoaEMtOTBpUy1YaWlHa2lWbS1WdkRYVGcyVTBBczlPTG5iMzA4aHVWeTVlUWx6aEhSajZHNW1TbExfaWtSYTFMTnhzcUFXaE9TQVBvekdudTN3NWFiWjN2UkFmdDNnR0NrN3VwZWhpRFQtanVSSHhudGs5c2Y4U1NHVmNiVlUtV2p1cURPNzUtTlFTZ9IB_gFBVV95cUxPQlIyOUVBTVVoWmdrNmxMbTZKXzZocjRrbXZ1NTFyaGNERVQ5dGVrVlAteWY0M09QOGMyMHlWTC04eU9NWFZoR2JYWTQ5M3FtdUNSRzFmdmwtbmZTNVpIUTVXTE42ZlZBaGtlUWVmXzc3cUVoaEMtOTBpUy1YaWlHa2lWbS1WdkRYVGcyVTBBczlPTG5iMzA4aHVWeTVlUWx6aEhSajZHNW1TbExfaWtSYTFMTnhzcUFXaE9TQVBvekdudTN3NWFiWjN2UkFmdDNnR0NrN3VwZWhpRFQtanVSSHhudGs5c2Y4U1NHVmNiVlUtV2p1cURPNzUtTlFTZw?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -3587,47 +3587,47 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>es-ES</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>IT:en</t>
+          <t>ES:es</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>46041.3630324074</v>
+        <v>46041.82847222222</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>High Level City searches Italy English</t>
+          <t>High Level City searches Spain Spanish</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND (bomb OR explosion OR shooting OR stabbing)</t>
+          <t>("Madrid" OR "Barcelona") AND (bomba OR explosión OR tiroteo OR puñalada OR "paquete sospechoso")</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Resident Evil 5 Remake Speculation Grows After Actress Teases March Announcement - Windows Report</t>
+          <t>La sorpresiva sentencia de Mbappé sobre el despido de Xabi Alonso del Real Madrid: "Decir que no ha triunfado es..." - MDZ Online</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 11:14:38 GMT</t>
+          <t>Mon, 19 Jan 2026 18:27:00 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQRmROcThzQi0wWmQ4VjVTOUJFNV9rcDlmVVowck42aUtPU0FKb1NScFhkaXJ2d3ZiWl8zeEg4N1psZzZMTWdiWkswUndtVkZIaEhWT2ZoWkphUm0tR1V6WjI4WXQ3OVpNNUNwUFVWa0RTeFRXRnNna196bDl4aV9wcVZVNTRfRFJRNFpVUEFsZEhqYVdDSTFLblZGMW0zMTRiclAzUUZhVkxRaDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPdDhXbGhEY3ZBejAxUE1zRnVDRF9PejJZaXRRUU1Xek1QbXBJMF83bjZsOGpTZU5ZQ3RqaFpEemxfcWJBUzk5eDZxMWtIbnhCOTAwdmc1bG4zTmlnLXNhVDZQaEpiZ2dTaVc5UkhTTjBDNlp5NUhqamRiTk0yYVR2NHpFTkRkMGIxZ0FDUEhpQVh2OGZabFhSbHlYOFlkTFVIcW15MDBueEpLYVB0Vi1HNC1EUWJYV21sMzBQaExzS1BqdlFWQ0FObUdweW15TGtYR0VfeFFQLXd2UdIB2gFBVV95cUxPdDhXbGhEY3ZBejAxUE1zRnVDRF9PejJZaXRRUU1Xek1QbXBJMF83bjZsOGpTZU5ZQ3RqaFpEemxfcWJBUzk5eDZxMWtIbnhCOTAwdmc1bG4zTmlnLXNhVDZQaEpiZ2dTaVc5UkhTTjBDNlp5NUhqamRiTk0yYVR2NHpFTkRkMGIxZ0FDUEhpQVh2OGZabFhSbHlYOFlkTFVIcW15MDBueEpLYVB0Vi1HNC1EUWJYV21sMzBQaExzS1BqdlFWQ0FObUdweW15TGtYR0VfeFFQLXd2UQ?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -3635,47 +3635,47 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>es-ES</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>IT:en</t>
+          <t>ES:es</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>46041.46849537037</v>
+        <v>46041.76875</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>High Level City searches Italy Italian</t>
+          <t>High Level City searches Spain Spanish</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND (bomba OR esplosione OR sparatoria OR accoltellamento)</t>
+          <t>("Madrid" OR "Barcelona") AND (bomba OR explosión OR tiroteo OR puñalada OR "paquete sospechoso")</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Stazione di Bologna: Bellini ha trasportato la bomba e la P2 di Gelli mandante della Strage - Ore12</t>
+          <t>¿Hubo pacto? La pregunta bomba al arquero de Senegal que le atajó el penal a Brahim en la final de la Copa Africana - MDZ Online</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Mon, 19 Jan 2026 11:50:50 GMT</t>
+          <t>Mon, 19 Jan 2026 16:37:00 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPZlh2Q1RiUVp5NFZJUEJReGFObzhNRDkxU3RFamtBLS1Ea1NOZFRqa3ZpX3Uza2ZyUDRVVTZIQnpuektHWW9JTmdJakFMQ1hQUjB5TExyUXhlaXYwcm1HZkRpbHhWYmhNSDVLcHVTbVNVZVZKSm1jV25GRlk2WE13ZTl3SVZ5cU5TVTNYTlF0ZC1fbTJRc1VVX2F0VWlkV09OZnZJTlk3VDhPeEY5b2l3MTFKNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPaV9DMWwwMkpvMzB3UzBTNHlTSThaX1Q2d1Z6ZHJfX1o5OTFEaXRoZDVHVHZaN1VjM1REYzRIUHB1SE9SZUIxQTQ0dVFJZXUwNTVreUY2UVVTTUladzF5NVl0czA4cTBBcDhpYU9iSUtiSmx2X2g3OGRBLXNBZ3pYSVQzbUx6NHd4R3I3RjIyV1NMNVctb29hazFYYkdndHhaUklIeEt3UkFVVGpUemczc2tnZlE0R1hXTTlaeV9kY0ZEczFyVmVsR0xzNXR0ZFlGMEp6NlRMeEx1QdIB3wFBVV95cUxQRE9zNmNnWDVybUlnaGFUSEJHeTR4RHdvMTd6RzcwY3ZIYlhaZXBwR3c3S180QkZLU0FrY1lJTmZNenlLTVhJa0F3OFQ2d3d3THItem1vYlhvckphUlRyXzFBczJrQU1ucjlybnJ0VWFvTWZvTFJXX0JTZUZfNVJ0dnhzTnBtT1ZHcW5haXlldjdIclh0WkJaODdWV3RGek5BM1NINGE5ZHFfYnBTYWZkalc5ZDhtZUUwOHBOaEo4VHp5M0M5bDA0UXNqYzh1UTFRcmNKU1VuVkVTcnFsQ25Z?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -3683,21 +3683,1653 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>it-IT</t>
+          <t>es-ES</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>ES:es</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>46041.69236111111</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>High Level City searches Spain Spanish</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>("Madrid" OR "Barcelona") AND (bomba OR explosión OR tiroteo OR puñalada OR "paquete sospechoso")</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>«Ya empiezan…»: La confirmación bomba de una figura internacional a Marley en Por el mundo - El Intransigente</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 15:04:15 GMT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPdmg4eDMwU3hqZWpCSlBUS0ExQXdpYlJ5dnlQUEJSaTRncVA5ZDFsOUZPUEdfOTlXdmJJUlk1Vk5ZdmlsWUVqdzBVQXdHQ1QzTDVIMFBSNU9tSEFFX05wVno0OGgwbEZZaWNQaWJkVTlMcjhxV1ZTNnA5ZUszZ0VuQlpha1ZhZXdOd0VRRXJVQTFQamJSN0Y4OENOMEprNHRKcjFxSFUwTVR1SmtIa0pQS2RfQzJNTm5ENXRFRWZnd2I?oc=5</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>es-ES</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>ES:es</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>46041.62795138889</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Village Search Bicester &amp; Kildare</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>("Bicester Village" OR "Kildare Village")</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Lululemon founder Chip Wilson seeks Advent's ouster in proxy fight, Semafor reports - Reuters</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 01:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNS1BUUGsxNzd3d3lSYVhJX0t0aUxIb1VwZWMwYzFtZkRXRVhObzQ1aDYwTHZVMU1wVlRoM0VJbVRTTTVGOUI4NHFDcWh6ZDV4M1h3djBGamwzWjV1cVppeUdCWHhoMW5BRjN5Vm1wWlJLdjhaQVctY1RlclFxQ0pxQU5CbjZhRFZUYndzaXdJY28zMTdlSmJCYnlsSjkweVJNZTZaaXo4Z2dqT2VDMjU2RHl5d0xBM1poTm9pN09WRGJWamFId2NZTHFpYi1ub0xOYUU1MV9QYzA5MzZCM2Z4RE1YWTllUHAwcjhzTFk1RWE?oc=5</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>46042.04513888889</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>High Level City searches UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>🔴 Man, 21, remains in critical condition after being blasted in horror shooting in Greater Manchester - facebook.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 22:59:13 GMT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPWjkzY090LVNKQ01CbHhWSHh2N1lSeF9ucC1qQ3BKUnRiSF84WktzaVBaSU5idkdhYkh3V3Y3RTg2azNCU0p0d0pGcXZVQkhoRVR4dHdCcVFXSjdESWtibzlmZzFSaWJiVnFBbXBMT2Y2dGRnbmVzM0NEX0hKa21ZUmpfWExxdW1HT0YzbkY1MGc1MzdhSXozYjVtYVNnVmd3SjVSUWlRRURUanlDWFB6UUFreEZld05kYkZCRU1lX1Z1Nm9ZOGR0VjRBejlzOGdpMGJGZW8yVXVLeXdmYTRiR1pBZjJaZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>46041.95778935185</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>High Level City searches UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Man (26) jailed over ‘totally unprovoked’ stabbing of grandmother in central Dublin - The Irish Times</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 15:07:43 GMT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOQWhpLVgwX2lUNXVQQnBLcDNNV2dBVlVUYWNiZkk5ZXN6RGppWmFiQVhmMDdmRGRMYWlHTG9aZjdzd1RYM1h4VzRjMTUwZ1RDSXdqMlM2MGYweFJUenBZbzJ6TWtGWUNmRkV6eVQzTGZTYkhraFZsTzE4SFFOeDlGLTQ1RGV2X2d5V1pBSzRGTU0wU3REVXhrZlZHX3UyWFF0Z0lfM0hxc1o3N09Zc3pCeHhqZHU1azlwWnZIVnF2RXJ5dS1lcFVJSk1zelpBc2Q5?oc=5</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>46041.6303587963</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>High Level City searches UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Man accused of hunting knife stabbing at Edgware Road bus stop - BBC</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 16:22:21 GMT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBnaE90SzFtWThEc29pUGJzYmZXNnNRQzMtRjhWZHRvMDQyQmYzNHJmVnJnRnpXV0dZa1hFeldFN2NzaWxlZXY2MGl1TXg2YkRtRlpqX2ZvY3FFQdIBX0FVX3lxTE1meUl1ZGVXMFdoc3JPLU0wNEl4a0plaFVfSENiQ1l2cW9obkFoQVdKMGdpcmJVTTdILTRka05yNlQtYjl1Ny0wYjRCTUFES3lVSFlDZFdfQ0k2OXk1b1hv?oc=5</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>46041.6821875</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>High Level City searches UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Man charged in fatal stabbing lived at building where victim was found - London Free Press</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 19:08:01 GMT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQQ3EzSXEwTUk1WXZlSTZxTGZJSlU0TTZxbi16TjZuLWVfczZhMUt0RmpiaFJvVHd0S2EtcUVCRnlHM0RyN2Y4WkNZWDFub2FJUjhybGNmT245WjBJRmVLTmNvRWY0bkxzbzJiTnV6YVU4X19fcm5OcUkxcl9PWGlENTBZVWVDYW1CR3RwV2s5eVJNSXI5MFlBa2lROU5hazdFZVR3Y3hRbW5RQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>46041.79723379629</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>High Level City searches UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Omg, Keira Knightley and Ambika Mod were spotted filming outside KCL Strand Campus - The Tab</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 15:18:00 GMT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQUmE5azFxUC04Q2pfY01UbWZYVVJtV1huZXpkQmNIb1dzWktQWTlsQkZEdmdtX1JvOTd2UzVuRU9YZ0Qta0V3S0lhSXl6SEJENFRuRHBXaEN3Uk1RdWhSbFFmUkZpemc4cFFyYXlSTmFxc2VCQ3d0UzE4Uk94a0lBQVJEdkpmZUgxa2QxTXY2aVFHdjgwMUxoa0xSUDE1N3I2ZnR4bXNnT2hURDNza09UUG84emFYaGlGeERR?oc=5</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>46041.6375</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>High Level City searches UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Teenager dies in North London crash between car and van - MyLondon</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 17:56:33 GMT</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQQkU2MWpwR05ielAxR2hEUjhVRzdsRFJQWlY4bnNSaDNySUU2aWJHQ19tekFyYXA5a0RtVFdQUndJZmp2WXZVdTZLNkNvOEVpcnNhdDUxYVQ1RzFQRVZ6OXRnTkdRWk03QjJwVndHaFh3YjYwTjdpN1ExT1pqQzhVSnoxNkNsYklRWHp3aWlzeTFkV1l5aEMtY0tn0gGaAUFVX3lxTFBCRTYxanBHTmJ6UDFHaERSOFVHN2xEUlBaVjhuc1JoM3JJRTZpYkdDX216QXJhcDlrRG1UV1BSd0lmanZZdlV1Nks2Q284RWlyc2F0NTFhVDVHMVBFVno5dGdOR1FaTTdCMnBWd0doWHdiNjBON2k3UTFPWmpDOFVKejE2Q2xiSVFYendpaXN5MWRXWXloQy1jS2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>46041.74760416667</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>High Level City searches UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ramping up Venezuela oil production could risk "methane bomb", data shows - Global Witness</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 20:11:04 GMT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQWkNmUjhTaFhvTXRVNFhZTDBlOVA3cFlVRkIzRl9kWnI2R3FZS1E5WVdZZkYzYzVWYnExQzJCSjZ1OF9makxPMUZFaHU4YWVGYURxVzBCa25TU1VZc3dDUWZxMGktdHEwZTN5Y3lNUFpKT2RONTJqcjFfNFp5TkNnNmFJeF9BV0NnZ3VsRG16Ul90VkhURmlRaWdtREVBNEpidnJCUXRzOE1RSVA0dTduNU5QcUVvZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>46041.84101851852</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>High Level City searches UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>First look at December 10's new music video as Simon Cowell's boyband announce debut single - The Sun</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 17:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNUTNZcWpXVmZOTXdxdUpoR21sQWFGZlJPbXA2aUhyS0NMMVhkYnQwTXdIZjVzOG1tMXQwNVBtblI4TlFIVnB4dEhiamRmaDdoMUJ3MmJ2dy1oc3FxaUNJem1XYXloYUx5N3pCanBNV2xzZUFyeFZaOHJ4cFBBUFBVTWlrZm03TkdqaG4xdE9LdWd0eVk3?oc=5</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>46041.70902777778</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>High Level City searches UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Celtic transfer bulletin as David Datro Fofana on brink of Chelsea exit and bomb squad Bamba 'for the off' - Daily Record</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 19:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPdEJpS1VERHdDX2lXbTZMZzZrbS1VS1FrZVlxaXd6ZE82QW9qWEJkQkI5Qzl3TjBIcFNjMlBFVUNja3dUNC16WUVmZjh5RFlEZ0VsV1Y0Nlg4X3F1R3FtOG8wR2NLWGdJWTgyWGFwSWNPbHd2WXhIa080Z2RHampYOGpPaFpreWo4QU1XTVM3RnpwMHZCWWpSS2FuS2FPc2E3R0JLVVJDZ05VX3RoTVFSVjJyRdIBuAFBVV95cUxORTItdUJYdlFzMm5vd2daZEpTOVdVVjBneVBUc3lXZVRHOFVnMWIxS3VLOVI4UzhwZWtEYUlMVTBFdW1UbkphNkNlZWd2U09DdTdOazdGcjQxUFpHdmZCelJQUHQxYlJHS1ZqN05BejZ3VXdfY0pOOWxGeEFCVmIzOG9SbDVPLTRnaU9XV2FKV3FKY0sxeFhyTnUtMEVVakJhLXdTMzctZGphUTZIMjU0TUphV3RuclQ5?oc=5</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>46041.79513888889</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>High Level City searches UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Fair City's Sorcha Fahy has a second job in London and it's what she always wanted - RSVP Live</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 18:46:37 GMT</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQS0NvYjlVWTZ6NmtFN2ZHc2VXZVhUYmJlaDhRQnlMSldCTkpILWZCWTVvRmNGQmNTdC1Td2NINFhIM3NKcDNmYUNJc242cEdNUkJjZUZ2MTlfbkJFV3BrYVVKckFUeEc0QUJxNXlxalJ5dk4xd0trSW50alV1TEQxVXR4TlDSAYQBQVVfeXFMUEtDb2I5VVk2ejZrRTdmR3NlV2VYVGJiZWg4UUJ5TEpXQk5KSC1mQlk1b0ZjRkJjU3QtU3djSDRYSDNzSnAzZmFDSXNuNnBHTVJCY2VGdjE5X25CRVdwa2FVSnJBVHhHNEFCcTV5cWpSeXZOMXdLa0ludGpVdUxEMVV0eE5Q?oc=5</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>46041.78237268519</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>High Level City searches UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>'I'm going to cut your throat' - son of murdered criminal tried to murder ex-wife's friend - BreakingNews.ie</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 16:28:02 GMT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOTlJBOS1PbTRNTDBuQmRKVXdXUThvdjNTYldfNjB5LWNESUpsbzZiTXA4WUY0UnJNdmlXaG9pYVJaMk5lSVdzTnRnMzNGOWEtbmFPZE54QU8zMk1WU0c4aDFJTUJsaWwwbHVGRERQUW9NVW1fS2xVNnAtVjcta0JHS25ILU5oQzFtUEZqUE13UmI1Skt2UnpoVEpZNldkaWNtMndmd0hnZ2pPdVZzYUg3Rk1qcjh6S3l2TFBkS181OG9oazU5Ry1zUEpmb0RUZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>46041.68613425926</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>High Level City searches UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Two Ohio men among three killed in Florida shooting; suspect charged with murder - NBC4 WCMH-TV</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 18:19:15 GMT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNQjVZZVlqWWppM3U2NXdacWV1ak05a1Q2VmhhRmZYbHVMMGZSM2loV1ZURlZwOW1qTkY2THNXSFRaV3dpY0VfMGVKRmpya2xHMUwtWUtEMlF1V3V0UDYtbDRxckp1d2RXVktHN0t3WGRELUlzOWNNLURzbFZpTVYtVDFCbEFfVUIzcUhVX3pDZjZUTFFQWlV4QjZ0LXJ4Nl9qU3VhZUVibENPZ1HSAbABQVVfeXFMTUttSWRyUlgwUm15aktmLVZrcnJQc0hSeU1CcHhxZktGdUhBNXprbTVrcUtoWUxELUNyWVJEQ09GNlozTUFKMkVVbXpQOXotdF80TG1ETGpLM1JTTXJHdWJRVzZ2VDJMeFlIZFE0NkJuLTB1amJwbThnQnNHdTl6M2ZlWlBFSFRZTVk0N3NFUDBMVU9xdFhfQV96cUVwcXJVTWhsUkFKRHNBVmVkVHVCdlo?oc=5</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>46041.76336805556</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>High Level City searches UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>FLYIN' TO THE HOOP: Bryce Curry and Joshua Tyson shine, Jacob Webber has big shooting night, and more - 247Sports</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 18:15:58 GMT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxPbDZtazVCMWZhRnJvUVJXQmZZZTFjN2Vfcm5sSmt1WDBUd09pTnE1b0FIeTRDX0ZNNV9Vd1YzTHB4OGpONHoySXhlSTZsSGFpYjJST0xxX2FUZGRtQmoydHo2YXBVTTFOc2twamgtcExpUWRnblBSWTZBa0FvbzBaS29mR3gzeldEUnAyUjFTUmpLR3VOTTMyTlhibzdFZWJYQ1BwaEd6d21ka18yM05pdGpYLW5vNlFKTmVnQjdpbF9sM0ZFQTUzSlBZZlRBRWFzM2ZEOWU3bEo0SzVXaHp1VFpsajhESV9pMXFNVEc2MFBwSVZXWk1V?oc=5</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>46041.76108796296</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>High Level City searches UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>("London" OR "Oxford" OR "Dublin") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Julius Malema sentencing: What jail would mean for Mzansi - Briefly News</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 06:19:09 GMT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQcGk4VGFKSm5HQ3lwTUpYekZqTFZ3SjBiY1JaLWJEb0txSDhQLVAyNG0tbWpRMDZjSlVMcm1Sc1VQS0VmNmZBekZ2YldjU3BIemJRdEV3U1dGMTVxb2JJZUZvYzg0NzlXYmY3OVRReE16bVFxSEdXa2FYb2VNenZSYWI0aTVSdVRPZlFmelVoQ1ZiRWlfYUdHREx5UHRSeVpCUFVSeUtXejFLLVMwd05BbkNISlo5MnZQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>46042.26329861111</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>High Level City searches France English</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>"Paris" AND (bomb OR explosion OR shooting OR stabbing)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Gamecocks Return Home, Face Oklahoma Tuesday - University of South Carolina Athletics</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 19:36:29 GMT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPVUFkMjBkeHBzakh6TjB6a2hzS0l0WTFkS1E2SGs5ZVpkcG9SSU4xTHlVREhwVTFxRFRRLW1HWnJ2VWJvbVdReTZPODZNSl9WM0FxTXlEbDM3SEhldGFmNU5HWWUtMndPSHl6OURaVHI4aDZhUndJZklicWpDdGQzTXJLWUVQRm8wdzJkbUVoUDFiZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>FR:en</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>46041.81700231481</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>High Level City searches France English</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>"Paris" AND (bomb OR explosion OR shooting OR stabbing)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Trump Drops 200% Tariff Bomb On French Wines And Champagne Over Peace Board Snub - Menafn</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 06:11:40 GMT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPd25pOHpUWHd6M3ZOd1d5cFNsQ0Fya2J2emdWTlllWV9RSTVKQ0puN21nNk5ZdkViYUZTSkFMRzhRNDUwejY3UlRScHMtRkdNTnJKNnFoNlZkTjZWUk9SNjhWcVhWcURvaHYxUklEUEtfREVJWTZKT2tDd0J2VWpsYURlaXFqSldVa2Zld1VsakZLcUhnaV9VRjNWbXhrUTVtQzg1WndLYVlKbi1GYXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>FR:en</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>46042.25810185185</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>High Level City searches France English</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>"Paris" AND (bomb OR explosion OR shooting OR stabbing)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Iran’s crackdown: why security forces are shooting demonstrators straight in the eye - The Conversation</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 15:30:24 GMT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPNjAtV2FhXzVNdkhPTXpKYVIwOWhXNUtFRG9QcHN3SHZrb01sUUszZTN0VWdsRWVteDFMd3FfU2dSeXE4UC1uczktZFBkMDVzNTVlblFiWmJhVDBoOGotbFgtWUQ2YkJXQkVVaS1WcGFyNU54WDhaTWFIcUQxWmlMVm9FRkgyb2VvMDY3RTRsZmxMd0JqeDEwem1vUnB6bmo3N3NnU2ttYlRmeHpiY295cUdHaXF1bVJa?oc=5</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>FR:en</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>46041.64611111111</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>High Level City searches France English</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>"Paris" AND (bomb OR explosion OR shooting OR stabbing)</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>'Chef Curry' finally finds his shot and ignites USA basketball in slim victory over Serbia - AOL.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 03:02:53 GMT</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5kNE9xd0xnLWxhTzFkUC1Ca2ozZGpyMUhRR2lfWFFaNmFxbHkzdDhXODAydS0ycTAxdjgtcVkzNHdwSlIzMmN3S3NScmkwUFJrZUwzZThiVFlzVm5yTmNpQ2NtY2FwSVpsWk1YYTNUWWpIZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>FR:en</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>46042.12700231482</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>High Level City searches France English</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>"Paris" AND (bomb OR explosion OR shooting OR stabbing)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Australian lawmakers back stricter gun, hate crime laws - RFI</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 07:08:13 GMT</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOVHV1WmdNemhQWlV6RjdaQXJITHpYM3lwYVpkU1ZvTUJHZl82Ry1YLW5IZHhNNmdacVBlcGc0TTk4THdVTEYta1d4azZ2V01EaDVBMDBsLTVuVGFZRGxWUVN1SkpXU1RPenNKS0tnZE5MTEJMT3BETkJYTDNfQzBPeXpWcmNiaWNxS1dDQXVjb1ViZVE0ZjVncDJPcVpVUU5VMEc2NnNmZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>FR:en</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>46042.29737268519</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>High Level City searches France English</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>"Paris" AND (bomb OR explosion OR shooting OR stabbing)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>NoctiRaid 2026: Team Race Featuring Shooting, Mountain Biking, Trail Running, and Orienteering in Essonne - Sortir à Paris</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 17:31:43 GMT</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxPdkJZcFo5azlrN29haVAyT3NPTk5vZnVjRGFzRTRtTGwzSDBmWDJZOU1jOFVqSHFMSE9qeklCMTFtNEJ0dWJWeHNQNHB6UUo4VTFYcF9NMmRLRy04UVpRZlh2NmhJNWJDRFhSdEZlUDkyR3FNdFc2RnJSYU1Bc3BNMWJhVnRFM3FpYzZ2dVNmMlZxUWx3TVVmYVlkc1dGcXdQeEQ5YTZreFFTT3AtVlkyRVlqYzU2RDZxNTg1Wm1aZFQxSmJFcnRmR215WXFDc0FqMmtRbWo1WTNNUm9tZmtCRTBpdmpWbEtjYXJZRXdvQTVXLXVESEhteURQZEZYdTFGdWxvTm9ObVAySVlPN3RtWENCTFZJYXp6MVE5TGp3TDY?oc=5</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>FR:en</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>46041.7303587963</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>High Level City searches France English</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>"Paris" AND (bomb OR explosion OR shooting OR stabbing)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>NSP investigating officer-involved shooting - norfolkneradio.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 16:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOa2dQVUlEdHJPRU1ycEw3ajd1bnFBdk0zVFd5UzdOTHFYQ0x1NEFZNVdjWlRITUM3Vmt4aHVqTjc0eGg1bHVGZVFza25jVHJxeFdXNjEzZ3F6ZDN6WDlPX3hEcHZSQnZ2UW1ITFVaYWlUVmRsOV9ZbjRxNWlaMUduRFBxYWFiUEhya19zQ1JwN3BTVllUZzJiUUs3WHlCYlIyT3JEd1ZLZXJFbkI5YVNzZngxMjQ3Q0dtUHcxMmlaRUpLbnZUU3haeQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>FR:en</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>46041.69097222222</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>High Level City searches France English</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>"Paris" AND (bomb OR explosion OR shooting OR stabbing)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Balancing Act announce 2026 UK and EU headline tour dates - Music-News.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 14:34:55 GMT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxON0hkc2h0b2JRVTh4X0I2NWRSZEhGcWpDS2FBVzZMTDZ6azltcXhFWFpZRTFzbzVaMnZ4ZjJtQkFwLUFoY3l1Ql84aEpRTngtdC1Gcm41V05NWWcxa085WjE5ekVHVGpOSVp3ZXY0eVN2ZUF5SHlEQTNvTDV4WXJyaTZEUDVDV0wxLXFxcFNobkNJR0RoLUZHN2VaOGgwMzhRR1g4LS1UWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>FR:en</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>46041.60758101852</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>High Level City searches France English</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>"Paris" AND (bomb OR explosion OR shooting OR stabbing)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Somizi Mhlongo and Thando Thabethe enjoy international vacations in Paris - IOL</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 03:37:32 GMT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOWUVRTVd6dmpFSmVzRUR1c1g2UW5DaklxaFVOazQxTmoyS2x1UmRBU2ZoVVV0Q3hPWHQ2LXk2c3RXc1EzLU1RbnNhMGlhbWdISjFxR0lxZ01CLVZYb2ZKVEpPREdWMFp1YkJDSzVfajlCbTdrRURBV2IzS1dEZ1R5Tk5Cb3VRc3c1UHUzaXU1S1JYdkJiUFpkOU92bG9Ta3d4VkpkRVVwRmk3TUNBYmdv?oc=5</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>FR:en</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>46042.15106481482</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>High Level City searches France English</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>"Paris" AND (bomb OR explosion OR shooting OR stabbing)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>6 died, 4 missing in north China steel plant blast - usmuslims.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 15:14:35 GMT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPdkVhdVFLSk1LTnZQWFF0cDIyRXNWVmRuVE0wa3UwVDM4THQ5WFVzSDNkc01OazFtRW1BSWVwX05NWlZqNzZqYWpaNy1LWTl0cjV5UVRjdkJqNm9VV2FNaEoxTUhqVy1fdjdSUE13T2kzN2lFVFBLX0dTRFVTbUwzMnotM1dORjhGQzhpNFp6SmvSAaABQVVfeXFMTml0NVlEZGhlOExCVzJIUnpXazhQdUhVc0xLRlBudkliUWxRNEpNSEJwdU94RmNYTjFYYXJTZFBWbUMzUXhsamFKamxvdjdTQU00VTlaYlBybTM3S1FRZzJlVEZhMGtVSDZXTEdCdEVVa2IwTlBnTk0yazZKMjRlOS1IZ3RCcEdQZlZueVlONkVSbVdnZkkySEg3c21CaE84SQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>FR:en</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>46041.63512731482</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>High Level City searches France French</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>"Paris" AND (bombe OR explosion OR fusillade OR poignarder)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Le direct - Paris Normandie</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 04:54:14 GMT</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBoSWU2RFVnZXdPV0Q3TVJZeF9UUUZra2MyUmNVa1BBVmRNa0tfa2hrMW13TnFmWlcyWTg1ajNJSFhMNlFvMTk2cjV2cVlQU3AtVWFvSkc5WXp2WklxeUUxMndDYXJnZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>fr-FR</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>FR:fr</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>46042.2043287037</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>High Level City searches France French</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>"Paris" AND (bombe OR explosion OR fusillade OR poignarder)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Un premier défilé hommes sans Giorgio Armani - La Presse</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 15:38:53 GMT</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQSnZCcUdVWHJCUWlNV1U3bnJ3eHUySHBaZS1HSExMeGlDcVZTeENSaDVUNzhKOGtKNm9jWTQ1RjNmdElZWGluY1htTWgxSlF2Ni1xOFR5S2dfOVpud0M3UU9lbXhQSV81S2owQXRWMVR2UFk5Ymw0MmhlY2JFWFhYLVB0WmZadlFqaUcxMFRRaGRzSGhQQjZ5SlkwQWVMR2RFZUExb0xEdjRQdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>fr-FR</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>FR:fr</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>46041.65200231481</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>High Level City searches France French</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>"Paris" AND (bombe OR explosion OR fusillade OR poignarder)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Deux habitants d’Étretat à l’honneur pour leur « sang-froid et leur bravoure » après l’explosion d’une maison - Paris Normandie</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 16:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOTTFPWHhubUowdnlac0lTT1ZUSkFFbnc2Z0FVcFk5bXdEb18zZTFjbW8tT3dyelQwN3JKb3pKM0NvZW93SEtqQ1ZFdVpEdWNQUmd0SmMyUFYtbG9kNUZMOXVEZV90X0FkZ0hkNU9UWG1IXzdzQV9tSVBHd1lkdHhuZnVCWlB3YVR5ZzJVVVRDVDhCSldRUnBEOUs1S29FWHJhRFdRQXlyTjVhcmUyb3JfTzEtZVZybVFDTWhmMUxMU0MxaVd2ZkdvMXRZMkxSMEhWcVFQS1NB?oc=5</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>fr-FR</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>FR:fr</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>46041.67152777778</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>High Level City searches France French</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>"Paris" AND (bombe OR explosion OR fusillade OR poignarder)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>«C’est terrible, c’est comme une bombe atomique» : au Chili, des incendies meurtriers ravivent les traumatismes des victimes de 2010 - Le Figaro</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 07:09:12 GMT</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxQSllaQjZZdk9hR1VxQTRPalFPU0lOanVpd3pNUVN1c3U2NV81cy03V3pWT05CT1Y0d0VydzFvS2xOTjFCbUlYR0RmdFVsdm5IODNNNEZELVhOblJkUGRQYWZYdHVUejExNHBvZFQwejVkcThGelB1eGdGaW9Nc1M5WGNScG5zZWcwLUFMOEJaNjU2MEF5WVBqeVVWcFlZaHN3X2RIRkptcWZKZUVhY0ZlanNnazNJZGNVc0pxQ05ZYjAtNERhQ01Nemhic2JPOGhkek1WcjdRblIzMzNaVk1mUUpiZXBrbmV5RVpSRTR5em15bXhETU5LbGxGWVl2WktibW9j?oc=5</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>fr-FR</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>FR:fr</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>46042.29805555556</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>High Level City searches France French</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>"Paris" AND (bombe OR explosion OR fusillade OR poignarder)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>"La justice de Dieu" : les images de l'explosion de joie d'Omar Sy après la victoire folle du Sénégal à la CAN - RTL.fr</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 17:16:04 GMT</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQRmhnaU5RbS1kaXFkMWNzMmhjWGNVSjVOd0VWV2lLdG9GMEs0WGJtMnZ3TGJEZ3R4c0FzVDQzb2VQemtyNGJoY25saVNwYmMyWi01eC1oY285QUs1aGNSTGx3cHlZNlJsSjhaaERXU1NudXUyOGZ5OFZuMDRJTXdWQ0pRbWxtdUp6NFdiblROVG0zaGY4R2p0OGNrUGQ3WTU5cEt5dkdocHJFSUtGZXJwRUkyTS1DMF9hcnhGMDNla2gzMURGazZ3Z3ZabTRLWG04b2E0?oc=5</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>fr-FR</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>FR:fr</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>46041.71949074074</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>High Level City searches France French</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>"Paris" AND (bombe OR explosion OR fusillade OR poignarder)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Des criminels présumés peuvent-ils être libérés pour cause de manque de moyens des tribunaux - L’Écho Républicain</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 17:04:00 GMT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxPdFFuMHBkbGlXRExOd3hnR0dsSHBvaXc3N2NwVlVsc096S21SN0JUR3dDcnNoUTZPbi0ycC1xMGRoUU8zZlFIdHczNGR5bzNIQzlPZXo3bzFQN254Vkh1RVdGSWl6R3k4SkRIMTR6LUFpNm91SVF2Ymx5OVZ6YVBoOWQ3X0hCNzhfWEpQeFZFWWNHTlU0VUg1RzBWWHdiSGJiUmhJZGxuNkxsc19mVDZVSkVlU084b2V4M0ZwNlFBcU9xMklIS3M3d3RSSkRRczRCNW5QQXQ4eVBrQ1gyNzlqdDliU0Q5OU85Vm5va0x3?oc=5</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>fr-FR</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>FR:fr</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>46041.71111111111</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>High Level City searches Italy English</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND (bomb OR explosion OR shooting OR stabbing)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Milan bourse closes down 1.32%, €14.4 billion lost amid Greenland tariff row - MSN</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 18:04:20 GMT</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxQLURuNjU3LWN4bWJPVWVuODE4dXNUT294WTRUNndETVpIRE84c0E0TmNDTEg0bTg3VFdoaUlQXzJMeGppUWNVQVRNOGhzb2RmRTFhZGF3bkVnWTZfVG42Ull3YTVHZndmLUFhU3BVdWl2QVpNYW5iVW5vUGNGb1A5SzlOeGRqMkF1QU9kX1VGNm9BVm1Sc1BYMDJORmhEZndMNjRYYlZUbVc4dzFqQmhWZjJhc2ZpYmRyQ0NBbElZRmlmR1duSVFyaDFEUlFCTGl2bk00QlN3ZDJQbmdycm1TVW5kN242dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="n">
-        <v>46041.49363425926</v>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>IT:en</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>46041.75300925926</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>High Level City searches Italy English</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND (bomb OR explosion OR shooting OR stabbing)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Giorgio Armani launches new era with iridescent colors and a star-studded front row - WPLG Local 10</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 20:00:15 GMT</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPcHltOHN5Y19SV0o0UEhDYlJJbzBERl9SMmtzUEJPcF93QXdmSWVac2RMZ01na1d5ekh2aHlJLTRYMHhnU3kwOF9kNzF2SjhWMXozOU44NFE3NllQTHU2TXJBLTYzZE9HOGZ6M1JHYkYzYWo5Q0dUTW5aT2hfTE52dDROaWYxU3JOeWxsdVBLVHRvLVlSWU1hT3h5cWNiWFVaT0ZEU0xiU0R6eV9kUThsUDNPZFhfQnF2NjM5dGNlcTIxWDdFWEVMTW44NWUzZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>IT:en</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>46041.83350694444</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,27 +487,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Value Retail</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>"Value Retail" OR "Bicester Collection"</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "Louis Vuitton" OR "Valentino" OR "Burberry" OR "Dolce Gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein" OR "Tommy Hilfiger" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose") AND protest</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Appoints Anshul Asawa As CEO And Managing Director - Textile Excellence</t>
+          <t>Men’s Fashion Week kicks off in Paris with Louis Vuitton show - borneobulletin.com.bn</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 13:43:39 GMT</t>
+          <t>Wed, 21 Jan 2026 02:45:24 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNbV9pX2FENlhqLURTYVR3ZWEya1JEVFNDbFJJVm9uOVFibmRZS2puRmpsVmRwQnBTMVFYbmQ2NE9Pbk9rU1NTVmdiSVhONjJqTU0zdmJOblpmcDFIbVdXQXZDNWtiWnZ5YW1lWG9hcFRzcnpUVjRGVl9TTTViZzU0NEVFcFRvNTQ5UjFQRnJ0SUZhd1lYX1ZNVmhfZUFTWHFYVWQxWjV5cU91ckRwQzZNVmxWNmI5YkJXMW1R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNbENEYmIzZ2c5dk40X1FyQW90VlVPRnl2OXJRRklUWXVNMXZoQUZjWExTaW1DZEZHRDVQbGJBNUYwTmItbzRDSnBFdGV1QnFXMzNGSEFKQ1RhNnZ2YVZZUXRrSjQtcEgwR3lzQTF0aHp0ZTBGdUp5bkdLZHFES0FySktFOWgxY21pdnZBZFdYVGxpaW0wY1E?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -529,33 +529,33 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>46042.57197916666</v>
+        <v>46043.11486111111</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>("DHL" OR "UPS" OR "DPD" OR "FedEx" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI") AND (delivery OR supply OR logistics)</t>
+          <t>"Value Retail" OR "Bicester Collection"</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Panattoni finishes DPD distribution hub - Logistics Manager</t>
+          <t>B&amp;M European Value Retail S.A. (LON:BME) Given Average Rating of "Moderate Buy" by Analysts - MarketBeat</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 09:41:45 GMT</t>
+          <t>Wed, 21 Jan 2026 08:03:42 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFA3Yl9QMjFRSGRpeGY5elB0eDBRVHNtcUxidG9WWGZXWm9ybnYwRWtoVUFWZmVOQ1M3enNCM0tZUUx1eFR3dGFFV0ltdTJxZlF0OWZ2dTdBTTJXNWpqSmNCcl9GaUFkTXZBT2RURXctbTRXbWp4UjNIb25BdEItZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNTklCRk9IekdNVFFWUTVyWHRpMkl3aElDUnVJT3htZS02ZG40TzR2VlJHS1F3cUI0S1ptaVFFUXR3d3VRRW9ZOXhTUGRYeFVxTW9pTFpIcExfd1M0N2tnQzhUR2RlUEdJYUVmbzVzcW5rdTlqYUctejFHaEZBZFhIQ3UwSmdDajl1b3Z1dmwzbnNXaWRFTnFaY05odTNNNG1UcXZreG9TRHBlWDVEZ01FeWQ4ZVRDRklCQzdMTEl2R1NsTnR2U0hKbDJTSmxHLTRmVTBN?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46042.40399305556</v>
+        <v>46043.33590277778</v>
       </c>
     </row>
     <row r="4">
@@ -593,17 +593,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amazon launches Amazon Now fast grocery delivery service in the UK - RetailDetail EU</t>
+          <t>Amazon launches rapid grocery delivery service - Better Retailing</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 13:37:14 GMT</t>
+          <t>Tue, 20 Jan 2026 14:37:01 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNbjA3c1d1UjdWUjVRVWYtWjRxT3llcnVKeDRBTkJoX3pGcVBaT0VEdlB3a0NYbEhsY0J1Nk5sM1lTYzVRcGVvTjY0ZnEwcllwOVBfMS1veGllOUEtVjd6UjJ6YS1lZG5WRkFiZ2tiVERSOXdGWl9XWFlFTURHa3JkVTFrOTZlUlN1anI5SmtYaGJ5MWM0NVZKc0J0dEhPUXJpUmppRWQ4cUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBPcm42dGJkaFNBdGFLR2E5eXFaaXBmRW96Q25rOV9SWTQxTU8wLUtEaXQ1cldKaTBWbXJ2aFVyeWpPSlZ6UmhyWDdHLWhycUFLSmZrQm1oSWwxYnhPb2JGa1ptbHdVQmVEcXI0NE44ZVI1SndGS0dENnA5cw?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46042.56752314815</v>
+        <v>46042.60903935185</v>
       </c>
     </row>
     <row r="5">
@@ -641,17 +641,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Inside FedEx CEO Raj Subramaniam's AI Strategy for Logistics - Supply Chain Digital Magazine</t>
+          <t>Amazon Now’s 30-Minute Pledge Raises the Bar for Customer Service - CX Today</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 09:44:53 GMT</t>
+          <t>Tue, 20 Jan 2026 16:20:02 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNU3BvajdaSjNWbXRjRl9Rc29pNGFFR2xQSTN5YzhHczlTMlZWN3FDWDNFN0cwTUk1Zm83SzVrcmVkNnUyTEtLc3NiZnhOcERvTHNtcTZCM1dQQ0FRTTlLTTNieEZONzR5X2NaZHlPR1F6ZEVTQWpjbWxMNnhMOThnRklqX1pRMll5SHRV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPT25lMmtUUFpsaXFsVEZxTnF1al9tcWFybTZfWThmcVZWeS1nVmVDeG5KMC1WNXgyZEY0UWpKSDRxSV9LTHdHazRqLXRHdm5sbzliWWxJVnVFVUpKdnM1Umd4RFhuZzZwT3R5cFJHcjY5T2QtVGNEeTZnYmMyRTZIeXY0QmpBWFEyYkpFUlFhUmFJWTNLZHc?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>46042.40616898148</v>
+        <v>46042.6805787037</v>
       </c>
     </row>
     <row r="6">
@@ -689,17 +689,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amazon delivery driver 'steals cat from doorstep' in shocking doorbell footage - The Mirror</t>
+          <t>UPS, FedEx discounts heat up, but shipping costs still surging - Supply Chain Dive</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 13:07:00 GMT</t>
+          <t>Tue, 20 Jan 2026 15:23:58 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNNU9USE84b004RGlwaGE2NEw5WG5KYndaRm1IVHphNDNKVjdQbDhPSDRITnVtRElXajhGNlZNY2x5Sm16eWVtZUhTUWxvSjBXdjQtamhWZUVHNXFsM3dIbmlIYlV1UW5Jek5ZSThuNnFsNTNxclZwX2IweXlPVy1yNlJCcy11Y1nSAYwBQVVfeXFMTWYyQ2pRSGpWMktvNEVxd3dHQUc3X2Z0TG5tQU80QXdLOTkxb19YeFdyai1TZFQtOEVISWVnWTNjR3YyM3VrX0NIYUFpS1hnNDdpNHFXdHZCNXA4WC1yVnJVTXJ2ZGhOZkFxakZZMVBfSnYyWW9zTkhTRmFlYTFTaGpQQ28yWTRHY19LVV8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPZ2syc0VpbWNQUHZtVi05WVc2b19TNzZDZzI5TUJzSFJUekJRSzdibml3TWhRWHFHSHJwLVhOUlFiYWt0VVFSQTlaTE5EaWZUdjFNUEhleFd2Q2FHdjYxOWxSZjNvN05tSUEyMWRlU2JpUkV6Y0NRMUVpT01DU1d2NVlsTkctV1IxSlZFYWRB?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46042.54652777778</v>
+        <v>46042.64164351852</v>
       </c>
     </row>
     <row r="7">
@@ -737,17 +737,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BHP Ups Copper Outlook To Catch Record Pricing, Competitors' Supply Hits Help - Benzinga</t>
+          <t>1,200 Asda workers face transfer as George clothing delivery shifts to DHL in 2027 - upday News</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 12:24:05 GMT</t>
+          <t>Tue, 20 Jan 2026 16:31:35 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQZlFMcVprYUd4NlEzVUVRclUyZEQ4R3BOMFNjSmcybzRxZlc0Q1c5VGVGN1BOcEc1SnpzMzg2NXNFMjBxS0VBOFNjM2kzYmUyb3oyLWlod044YjdwRXNIUzVINnBvRE9lSWlYWGRqcnkzclNfSW9qTGcwUHd5QU5ieTUxd2ZtcHljYlBSSnlMU0g4NXRiTnlzZjNnQVdNUzRGeXVybGJlU1NOaWxNb3I5bHQ3MGVybmFvSnRrT1BPOEItdmpHVmh6cUNINFRlbzZ0elE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQVHJwdThVUFdVYmVFZkhWRUFXT3IzY04zYmh2TlJMZVNJaFMwSlBSaFFac3NGMGRWb0NZTkxRQVhjbVJEUlVISXlKeTVabm51WDZPUzhBaDdNYWlrVEVSY3U2aFVuYVJyM1hoeGN6MDlIMjFPdkc3M3VhbVEzQnVkdGZGeFR1cV81TFFLRUdMbUwxT2lRTXd3RDFicUN0aVI5a3laQ2FCNXh2dlpVaDVyb21DN0psY2RpZTQ5Z1pR?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>46042.51672453704</v>
+        <v>46042.68859953704</v>
       </c>
     </row>
     <row r="8">
@@ -785,17 +785,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OFCOM regulator backs the Council over Royal Mail postal delay concerns - The Impartial Reporter</t>
+          <t>News | Amazon expands logistics footprint in Massachusetts with major Uxbridge lease - CoStar</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 10:27:31 GMT</t>
+          <t>Tue, 20 Jan 2026 20:28:55 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQLWhiM19QZ1FhREpkdjJ3Zm5MaHVmMExqVkNMWVJtUDF2LUg4ZzZIUVNVMjFNZXBVbTYxODRCcnBXc1RfTkw3YU5NYWlsaHk1QlZOYUtZOVlLb0t5VHJjVDU4S0NnWFBnb2ZQbzJBcXp2emtrSDdJbk5YNHhCbFNmWjlkUXdFdnUzMUpwVkc5YkJncVV6dHBIYkY1b3c0Q2k0WHozdQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQZVJVTGpqU0xxU211Wmhpb3hTTnIzc1NzVlBOTGJSakI5YUlyWGt3V2YzVV9ZX0h1ZE9PTXlBQ3Q2X2ZfckpfN1AxMEN4M2lSWVNIV3RkWFR2YzdDQUlmd2htcjVxYm1Fczl0bllzVlhqM293ajNVTy1iRVRXU2VuOW9XZFVsNkM2R3VCOGZPcWZ5cXVMcG9NWlRXYkV6X010azNrWlhXYWFmOWtVODk0a3RvUUUwcTdiLUE?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46042.43577546296</v>
+        <v>46042.85341435186</v>
       </c>
     </row>
     <row r="9">
@@ -833,17 +833,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DHL Supply Chain unveils life sciences and healthcare center of excellence to enhance pharmaceutical logistics - FleetOwner</t>
+          <t>Woman claims Amazon delivery box came stuffed with hundreds of blank ballots - AOL.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 13:23:17 GMT</t>
+          <t>Wed, 21 Jan 2026 03:53:15 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwJBVV95cUxNbzJpanI2S01XUV9YMVVzTHdkSkltT2pCeTdJdzhiSDJ0WFB5THFxOEMxYU42Q2NobXZERGlfcEhqNUFFczF4cDl6bXlXcl9rc0xTUFdadTJlSy1mbHVxQmhtZW5lS3dYNUcteks1bzdaeGZvaVVERnZoUFNRallBYjM4SDNWalFoc0RwbHZQSXVJWEFLemJHa09Nc2dKbl9Oa29wSGtKUEE2Wko1aHNjaU9HV2VuWFJMNVBjSmlqTHgwNlF4bklELTR2MnhQQUFTRVV3WmlSN2lDa2xybTBGczdMeFRRc19NbER5bXF3Q1Y2ZkY0Rng3bkNTbnY0QjY2QzN6M1BEZDFhS2V4TXI5MEk4THVBQm1GcWd2UjdNX084eVU5ZFVV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPWHlJdEh4OVBjSFFPWUhjRTZZcTFpbzVXV0c4Sk05UnlrVmNxTnhLa18tLVFHb0NvQjJCT0VKLXcwTnpKV1FBNHROai04QmxxQW5VUFhhR293VlJ1VzBUMC0zSU5wSVUzYmdxUkNIM20zaUpVOF9vZDM1VFRScE14RW9B?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>46042.55783564815</v>
+        <v>46043.16197916667</v>
       </c>
     </row>
     <row r="10">
@@ -881,17 +881,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sheboygan Officially Approves Amazon Deal - whbl.com</t>
+          <t>FedEx announces 10-member board of directors for Freight spin-off - logisticsmgmt.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 11:21:01 GMT</t>
+          <t>Tue, 20 Jan 2026 16:14:56 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFAwUy1wQldBXzh2LTdvSDgxSWNhQ3Y4ZkNydm9BUmF3Vnhla0owVlBVa0NhM3ZQY1JKa21naVhlcF9WUWxnSVlfVnNZNGliZmdGUERPdTNQckU5MDdqekgtN3pYSzFMUkNIMXUtakxyek5nQkhsTmtSc2ln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOcUo1Q09TQ2JVcWJRaGJxRXZVS1RCZ19TNUFkdV9nQTNuQ2NMVHlNeGZzOHN6OFZwbUYxU0dwVlVYa1E4OC1mRVp3T05JUjZNQW50LWtqRDQ0ZnhySU42M3FWRmtGRlJ1TnUxNm5DeEhQQ3l6R1RpSUExUnBsRmppZVgzT0QxMkJUNkQ1VmFveVdadWpZZGh2c3pvNVFLWG9xMDZSMHln?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -913,33 +913,33 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>46042.47292824074</v>
+        <v>46042.67703703704</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>High Level City searches Germany English</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>("Frankfurt" OR "Cologne" OR "Munich") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package")</t>
+          <t>("DHL" OR "UPS" OR "DPD" OR "FedEx" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI") AND (delivery OR supply OR logistics)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Transfer ‘bomb’ as Chelsea in rapid negotiations – ‘XXL offer’ from Blues can seal signing - Sport Witness</t>
+          <t>Wikipedia signs agreements with Amazon, Meta, and Microsoft for content supply to AI companies - De Último Minuto</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 09:19:07 GMT</t>
+          <t>Wed, 21 Jan 2026 00:51:07 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOWU40VkYxWkYzcDZCT2VVSURIOVNNUEUyU1NEQ3hFZDhmNzIxdnJ3b011Z2cxWl9OcTUtQ1g2ZXpVNU1kRVE3N1FVR25qUnp1dFRPOERFdUxxQU5GVTMzOS1XTThQS2JFMGptT3RUa29kbnBwcG1OdEdyYWtUT1ZYZVRYNlRtdmVZa1RsNXZKWHdoY3dRdDZDamVCS191ZEtVSEttYklzclU4Z0NNc1ZQT3FB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZVhKUmpyN3A1ZUt0UW5iMUhrVklsQW5STnk2d1QtTE1rb3RMRUdXTzBxVHpndUZpdkplS2w3ZklEaUZyN1RjenhoM2hwVDRfSURSVDhjby1oaHFXbHdmMnRVZUhhaHBER1BrT1Yyb05jZndqWEJja01BbF9sdXFOVkZWREVQTkszenJvR1ozd0ZoU1lPY2VFeTVTZlF4SEtFRlNZdFp4cHcycXV0cFdUZS1YQmc3d2ZrM2JhdGhjdTU0alVTaWpzM3d4amNrZXQ3NEt3?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -952,42 +952,42 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DE:en</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>46042.38827546296</v>
+        <v>46043.03549768519</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>High Level City searches Germany German</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>("Frankfurt" OR "Cologne" OR "Munich") AND (bombe OR explosion OR schießen OR messer OR "verdächtiges paket")</t>
+          <t>("DHL" OR "UPS" OR "DPD" OR "FedEx" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI") AND (delivery OR supply OR logistics)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spezialkräfte im Einsatz: Mann ruft Polizei und sticht auf einen Beamten ein - STERN.de</t>
+          <t>Here's Why You're Seeing Amazon Trucks Everywhere In Pittsfield - live959.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 12:08:02 GMT</t>
+          <t>Tue, 20 Jan 2026 19:10:47 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPZHNRczE0ZzRKc2dQS2t6UXlXTURlOVROdjZiRGpzWGlNN0VCX1VvTWRMeWp3X2dVWjRmZTRucTRfUUNfUWxvLW9JSTZlbzZ5NlhSNm55VDFzOG1LdWFUN0VTaW9NUmYtZVB6VjY0UmlLQi1tU1R4dzI2X09SZkR4bmVienpLUDh0dGlxMTVmaUdzTWtoVU1pRmcyN1hZaGNUbTBaOEI1QWRiRkdqNTFJazNJWHRyNVB5WGZkTTNFZUxKc3V4amhhQ0w1am9FTzFudlB1S1Rqa0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE9YYUlnUFNqQ1dPUGJCV3duZVNTYXNqd3diZnFOZ2VSMno1WVlNcWt2LUdaV05ncV9qQ0ZId2piVlVodmZfcG1XNnlFcjhzUjdmbTR0SE5MRm96YWVYNzVqT0VB?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -995,47 +995,47 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>de-DE</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>46042.50557870371</v>
+        <v>46042.79915509259</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>("Extinction Rebellion" OR "Just Stop Oil")</t>
+          <t>("DHL" OR "UPS" OR "DPD" OR "FedEx" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI") AND (delivery OR supply OR logistics)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Why a red-robed group in white face paint walk a Cape Cod bridge around Labor Day - AOL.com</t>
+          <t>Johnson Camp Copper Mine reopens to supply Amazon data centers - kgun9.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 08:42:17 GMT</t>
+          <t>Wed, 21 Jan 2026 00:40:55 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5mOW83Y3Q3WTlRQlNWb2d0ZTJMRzFINTlKR0UtZldlcWl0bHRVTWdrc2dpLXY3Wi00QmFTZldPSkJOXzBwdDR0cTB4NjVyb2VOOTlPR1laemhORE0xUGNRalM0ZjJXUUV5UVU3YzNPRGJkQnk5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOQWFoSmNPc09IQm5NOXJWd24zMm1Oak9jb0RWcmNJaDl5N0U5UE5OaGRPZDZDdXlVczZ2ZTBKSzRydEJmLW9RNUxKSGxFU1NmRC1KOE1VZm9IMXhJN2FjRlFnWjY0WDZ4THYzOXdTS21EWGFxNjRUT3g0N00yM0lVbVctQm91cFB6ZElrSzZ2ajZPRXdjZ1dUVFBTT255YlAxS043cGVjanBHcFlZZG9IV3U0dkRPa21GaERISU43ZGVINXhFbDkySVJ4X1B0dlk?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1057,33 +1057,33 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>46042.36269675926</v>
+        <v>46043.02841435185</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
+          <t>("DHL" OR "UPS" OR "DPD" OR "FedEx" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI") AND (delivery OR supply OR logistics)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Man charged with shoplifting from Waitrose - Bishop's Stortford Independent</t>
+          <t>Amazon delivery station in Sheboygan could open in fall 2027 - sheboyganpress.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 14:20:00 GMT</t>
+          <t>Tue, 20 Jan 2026 22:54:21 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNcFF6b0dsbTZVS0JRVnNlZUNNbXN6SHNqVktoREFxSXVZWEI5UDRRcnNJU20zdFptTUVsbElyRHpEZURpal9nS09NQzNtbXk5OWFiZlRhRkoxeUFnRU5uZkpzWlV2bjhlOW9ieXVPSzFZUm5oRjRHZ0tkTURvWWwtam9GOF9rVzRVY2x6Q0xjZ09SWEtSTUs2bHQ4Z1NhUHVWb2ZGRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNQkE1azNTVURiczd3MjRsdFpKSFVZaWU5X3FOVDFZNHRJclczZjJGWHYzQmR3RndMQ0NoSEZoMDQwTU91R2hQemo0eVlGVFRuSWpmQWczMVh6NXFZRFpGWGdBdXlrTlhWN3UyWXlBLWl6Sm1KM3YwRDl4QVlINV9wNWE2NVlmRVNFalhEazhhYmt2TUVWaWpTWnVfWlVsc25NV3Rrb1VYNGlxRzV5MHVwRGVpNmZIS1o1RmVrbFR4T1RoT0w1U05DNVlveUYtOE1WSFVVV1VKbnVDQQ?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1105,33 +1105,33 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>46042.59722222222</v>
+        <v>46042.95440972222</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
+          <t>("DHL" OR "UPS" OR "DPD" OR "FedEx" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI") AND (delivery OR supply OR logistics)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Glasgow thug jailed after shoplifting spree and assaulting retail worker - Glasgow Live</t>
+          <t>UAE backs logistics, food processing tie-ups with Andhra Pradesh - The New Indian Express</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 11:01:00 GMT</t>
+          <t>Wed, 21 Jan 2026 03:43:00 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQWkhOSExuNERIblBPMWszaVljQWNDMjNRNlNSVlQ0c2drSzBmTi1aZlNYTEs0YnRkaEtkQWZrNWg4NVNzU1dJc2ZDMjFjb0VlRE8yaF9MZHpHZVduZ25YSU91SC03LXY3ZFFMV1dYVG95X0IydmJfeHQ5SThoRWhmQS1pcV82TF9zbzhMbG8wcmh1cDZCUjduUFZ30gGfAUFVX3lxTFBxTy1wTk5sS0NlZmZpNzUwQnBCcVlHeDFZMEtETTQ2QlB0VXZMaUZXMkxnX045N05IQ09GZnAtY1NyQ0huWXBELVpuWHNnMUZxLU5sUUE0Zk1lMHJqNWlWYTZlMUZaRWUtYjBzZGUzZjNkWGM1UFV3X2ZpTXRwVlpNd3NibFpwcUprT0pUdkhNTVhZMnRKTzE2SWRjZ1lKZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPVExBWG9tM0Nkc2l2Vy1fbHp1T1huQkUyeEV0ZVBiSXMtTmV0UkxnZENpWmkwZEtSY3Y1SFZxS0hiZ3R1MFBLOGtkZXdWUGpsLTZJLUJ0dXdpc2FJUHNsR3k2elNtNWRaT1JGaDFVeWc3UW1JTWpxaXZ1U1Jtc3NISTRReC1QNXdqOFJwMHhlWEdnbGpUSWdBRkNpeEx4ZTdXTFJuM3FzNW5JS0h1N2lqRGxFN0hfNFEtR2wyZy0wUWhmenhDblBZSEpMT0ZCZE9mQy16aWk5c9IB1wFBVV95cUxPVExBWG9tM0Nkc2l2Vy1fbHp1T1huQkUyeEV0ZVBiSXMtTmV0UkxnZENpWmkwZEtSY3Y1SFZxS0hiZ3R1MFBLOGtkZXdWUGpsLTZJLUJ0dXdpc2FJUHNsR3k2elNtNWRaT1JGaDFVeWc3UW1JTWpxaXZ1U1Jtc3NISTRReC1QNXdqOFJwMHhlWEdnbGpUSWdBRkNpeEx4ZTdXTFJuM3FzNW5JS0h1N2lqRGxFN0hfNFEtR2wyZy0wUWhmenhDblBZSEpMT0ZCZE9mQy16aWk5cw?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1153,33 +1153,33 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>46042.45902777778</v>
+        <v>46043.15486111111</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
+          <t>("DHL" OR "UPS" OR "DPD" OR "FedEx" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI") AND (delivery OR supply OR logistics)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>‘Robin Hood’ activists who targeted Crown Jewels plan London Waitrose raids - London Evening Standard</t>
+          <t>Belfast man hits out at Evri after "constant issues" with deliveries - belfastlive.co.uk</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 09:49:01 GMT</t>
+          <t>Tue, 20 Jan 2026 16:27:00 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOOWZiejRMdTN5YURsR2c0NWxZXy03OUNtT3J3SV9rTDJTUTlNaW14MEdLZjR2MTFXVEUwODhyc3RNQnFfeTFIZThzUVdvSm9JSkpFemstU2U4V28zSVdVQUt1RXJ6eGY3aVZBWE5GaVFLQWhBTGp4bWtRTmw0ZWxkRFp5YVBTMG1hNjUwWXllWE41b2I5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNS09DYmNadXdpMS1NeFhXYWRFcmlDN0hlTW1UeDk0OVRiMl85dFpQeFRMMXZTdVVYTDdhSEFOMWc4ZWF3UjB0cl9rYVZjdXVwZ04tV2JKbGhBeXFwVEZrTGtWOUhfbVUxci1PblpJOHlKRGVCbHg2S2dhY0oxSmpVWFAzZ0lWV3gtaWfSAY8BQVVfeXFMTVdHc3YyOXhpWjhmUVo3TldBNWVUeXlLVmxDZzVUZlpVXzF0WVJCeGdRU0hRSHRNbjd4VVhlNm0yU2otMWt3Vy0yNFhlcUhyaGRPVkxGekc5Und1OEZnSEJDYVBjWVc1OHJyajdKVXVsYWJGOE9LNE54S19TUUtJem0xQ0wwWV9QSWlLb2ZZUnM?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1201,33 +1201,33 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>46042.40903935185</v>
+        <v>46042.68541666667</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches Belgium English language</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>eBay, Facebook Marketplace and Vinted warning as crime figures hit 20-year high - The Herald</t>
+          <t>BODY FOUND AFTER KEW STABBING Victoria Police The body of a man has been found in Antwerp this morning as part of the ongoing investigation into a stabbing in Kew overnight. Local police made the discovery following a call to Triple Zero around 6.15 - facebook.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 14:31:54 GMT</t>
+          <t>Wed, 21 Jan 2026 02:33:20 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQd1VaYnpIN3Q4VHBPNmlycXh0c0FDdHhoZ291STBEVlQ2T05XLUNyVjVqMUk5dV9HOHpaZGZ2UGNqR1g4a3UzSUFwNVNMb2tTU0xHUl9fWjU0bkhyLTRCR2d2Y3UyczI1UGlhRGhvdE8yRGNzUkoyNHJRcXd6Y0taSUhEYTM5QjJzamN5SzhwQ2RHY2JsbWR6cFU4T2V4OFRtLXlaZWl2WnFXcWJUaTJqdFcyVHU1aDA1dTZ6Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQYTN1azVZbFBBVHk5N21VRkthQ3pTbXl2QVFKUi00LV9uN2huVFliQjdJNVJDb2VPdUZhV0R4NWFrVzBuWThSOFZEd2xFU0g3dWhCb1BmTXBmbEhXSk5GcHh3eV9aRi1HbkhneVBZaHN5WXpaWTZIRU5RY2FwS1ZhRDVWN3M3ZFdrUVpTazBwX3hucnRudlRWaWRwdUpkR3ptQUhMQlkzM0FnalJKSmJ4TG9DelNOTFBKWWNTVXBZLVVobnZLRF96UHB3d3BWNkZlcGU4NFBBd1V4QW9mZXctRA?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1240,42 +1240,42 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>46042.60548611111</v>
+        <v>46043.10648148148</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches Belgium English language</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oconee Blotter: Athens man charged in alleged razor knife attack at car wash - Online Athens</t>
+          <t>EU to Hold Emergency Summit Over Trump’s Greenland Tariff Threats - kurdistan24.net</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 09:01:00 GMT</t>
+          <t>Tue, 20 Jan 2026 22:57:00 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQVlozNmhjMThrX0dPQVlwdXFISFJWQ29Gc1lCem51Nm9TMHJIQ2Y2M0puaTNUeTIwQW42Z0Rvbnhqb19SdVhEZ1ljOTZJSGVhUy1jODA4dWZfTmlKQ3RyVVh5TVQ4NDVMWTAwSS1UYjk1dS0yQS0zcjM0Wm02RktBdU9nd2l1OGZSQXJrTWhNV1VDRkNrT0ZPX1JMNzhaU21yeGgzelo0em1kamJSaFh4WDM4S0tNb0dzS25UTUgxWjAxeVFFdTlUWkwxSUpzQzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPaWM5MnZESFJOcEpCNm81TlVCMVR0NVNSN0NiU2J3aXFHekRRamxna0NoNUJFTjdHem83eGxWakFGWnNEeDhScjlhQ3JHcjVDYzVTdXBkdlc2bTZ5VjVER2t5WGJtRlVoM0luaWg5MHNCT1QtNzN4cU4zaWZIUjdDREtBU3NXbnhad3BNek92bVZCdlVmOTZ2eVhnNlVSYnBKOGJubVRQRHduZGVm?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1288,42 +1288,42 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>46042.37569444445</v>
+        <v>46042.95625</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches Belgium English language</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Police seek help identifying Best Buy shoplifting suspect - North Penn Now</t>
+          <t>Brussels shootings investigation leads to police raid in Panama - brusselstimes.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 13:29:37 GMT</t>
+          <t>Tue, 20 Jan 2026 18:50:44 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUzlWTDBpcWUyVmp3X2U2SHhWUWplajZKOWhHWndCcmR2YV9SVmpyd0lxT0lSb2E2aEoxSUJLVkR4dnpGcnRTOE1uYjJhbW11RkRYU3BIQVdmSHFMX0x4VmVwVWZVN2t5d1pwbVFlcjFDNDBDWnJFaDhIOEl5RU52R0RvaktzWW85WkM2N0R2bndSeDF6TFM0QW1yMTY3b0trMGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQcnpkQlVGMDdhVVN2aHRkSWpTZkU5RkJJczBMTDVDSXVWYXpTRkozNkdyTTdjZzZGMjh3bmtCRUhzUF93VkprY2llalV4RGl3dDYtX2FnM2ZNa2Y4RUJWZE5fa01SaDUwZW9iSE9uNUFQQmh0RlE4Y2tQNkVrcGIyNTlFSzNXckVHOHRzZXpvaVlldE1zNEZlZERmRmlSakRzUlhV?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1336,42 +1336,42 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>46042.5622337963</v>
+        <v>46042.78523148148</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches Belgium English language</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Three arrested, accused of shoplifting at Target in Amsterdam - WRGB</t>
+          <t>Edgerton Controls Tempo in Road Win Over Antwerp at The Range - westbendnews.net</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 11:55:30 GMT</t>
+          <t>Tue, 20 Jan 2026 17:08:00 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSkFnRG1qVjBsWERWek5oTk83ekVjTWpuVS1VaVYtajdaRWk4Y3J4QXdXaHluZnZzeXdZeUxYRXF5TU1aM21lYjNmQm1qeC03R2E4ZjF6cThvYVdBLTJlTzVzX3RLeXVyQW9RWXBNX3NFWGJXalUydTRGQnRROVB4Q2F1d3B6emNNMWhMLVBzbDhaRmdRdXFNcHJfY3NXaEpzekNsdE4tbW9jQkhlWHlaN2xGdUIycXVjZW9oazF1Y0FlS2JsNk5hUnpsdmExbHJ2N2docA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNM2lvLXE3VXQ2c3hETU1oRGFRUjRwYkprWklqTkJFdVlZcWNrNWZUc05VcDFsMm9OalprTTM5ZTNSYjI2Z1ZtdXRkQjBzUk1qU1FIZkdyUUJTWDh0czctUFNzd25TaTBhN1NqR2Y5Vi0wSzNtUXlxM1BIaE1ucHpWVnNXbl84VGxpd1p5NjU5a0F1YjRxbm9mMFZjSUhya3dPWEE?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1384,42 +1384,42 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>46042.496875</v>
+        <v>46042.71388888889</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches Belgium English language</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"shoplifting" OR "retail crime" OR "theft from person" OR "pickpocket gang"</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nina Lin Has Twitch Account Deactivated Once Again After Clip of Her Allegedly Shoplifting - MSN</t>
+          <t>Teen lay in wait for Kew girl before frenzied kitchen knife attack - heraldsun.com.au</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 20 Jan 2026 09:18:43 GMT</t>
+          <t>Wed, 21 Jan 2026 07:12:04 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gJBVV95cUxORDd4Zk1FVThTS2tXNkgybTZiWEhYRWNuYlR3ZkYyY05NUnlFeURjUDdWSms5RTFfQmR5YkRiVzlXMFdXUjRWaFZFN2NmY3ZWbk5GOEZnZmdXVmZvTlRmT2FjRy1GVC0xbHRFT1J6NWhyQXI0eVdpUGZYQTVYWTNTNFctcHhwWUlTSF9VZkNtZ3ZpX1IxSWVtLTFscVQzX2NWZ2VvXzNNWERsNUhHM2M4ODVBMUxLM3JhQ2R4eUhtX1kwRHY0dkJlZ1FNTGUtN0pxVEd0UmJ1ZmE1bkNyMzRhLTUycjFRdEtPQm1OSHFFblF2enVxQVBKSFQ3cW1TS2phcUp2dTFKVGpkMGtHanNlWUM3QjJQOVdvMkh5ZW5vajBuNk5zRmVKSGhvVWhSODFKWnY0aVB1TTBTT0NLRG5fZzZjZ2xnNmpFTlNtellyb29aN2FGdXVzdk1IbnJobzAzOVdXb3RJN29hanc5MEdYNC1NbmY1dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxObjNKUmRfYnpKS2o4TUEwNHlxVktJUW1PVG9RZmRtazFpZ001Q2M3WW4tOFpQSFdUQUxHQ3owUzcxUTJHR1VGWXVYRWFrWFNZS1l5WjhGOVhPdXJCRVp1SHc3WUR2ZXJLekRYN1B1VTZSejR3RXhmTTkwUFV0N1AtSFRaSWdTU0JBNHcyOTBmME1MT3RLc0hjcDc1YlZESEpHa3hQRTZzcFJXRVpETjBHc1E2bERmU0xDLVRoNFdNV3liUllaLV9kQURnN0NWdXl0VXBaeTVKc0NGZXdaZUVPV3dHLU1Qb2hiamxNWVJKMy1jQdIB9wFBVV95cUxOVXNsc3NpUGR